--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A930DAD-8399-4168-9CF7-A119724234BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6E97E3-9380-439A-8DC6-1D1A8CA3C6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2130" yWindow="1230" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="264">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -166,19 +166,6 @@
   </si>
   <si>
     <t>バブル・ミスト</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アロマの泡を作り出す</t>
-    <rPh sb="4" eb="5">
-      <t>アワ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ダ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2085,63 +2072,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>アロマの泡を作り出す。
-中にアロマポーションの霧が入っており、泡が割れることで霧の演出が可能になる。
-泡を作るためには、各お花に対応する「アロマポーション」が必要。</t>
-    <rPh sb="4" eb="5">
-      <t>アワ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ナカ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>キリ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ハイ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>アワ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>キリ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>エンシュツ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>カノウ</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>アワ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="80" eb="82">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>お菓子を作った際に、MPを少し回復する。
 LVが上がると、回復量が上昇する。</t>
     <rPh sb="1" eb="3">
@@ -2768,22 +2698,6 @@
     </rPh>
     <rPh sb="73" eb="74">
       <t>ウゴ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>風の力で、水あめ・チョコレートを羽飾りに変形する</t>
-    <rPh sb="5" eb="6">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ハネ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>カザ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ヘンケイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2890,18 +2804,6 @@
   </si>
   <si>
     <t>Rainbow_Rain</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>サラマンダー</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ウンディーネ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>シルフェイド</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3105,51 +3007,6 @@
     </rPh>
     <rPh sb="53" eb="54">
       <t>ヒカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>風の力で、水あめ・チョコレートを羽飾りに変形する
-特定のお菓子と組み合わせると、かっこよくてオシャレなお菓子の出来上がり！
-風を感じるお菓子を作ることができる。
-ウィンドアークをかけたあとは、素材が不安定なため、フリージングで固定する。
-派生：
-LV1で、各ウィンド系の魔法の習得可</t>
-    <rPh sb="5" eb="6">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ハネ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>トクテイ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ク</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="56" eb="59">
-      <t>デキア</t>
-    </rPh>
-    <rPh sb="122" eb="124">
-      <t>ハセイ</t>
-    </rPh>
-    <rPh sb="131" eb="132">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="136" eb="137">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="138" eb="140">
-      <t>マホウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3207,6 +3064,200 @@
     </rPh>
     <rPh sb="207" eb="209">
       <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アロマの泡をお菓子の周りに浮かせる</t>
+    <rPh sb="4" eb="5">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アロマの泡を作り出す。
+おかしの周りに泡を浮かべることができる。
+浮いた泡の効果で、
+風を表現したお菓子になる。
+また、見た目もアップする。</t>
+    <rPh sb="4" eb="5">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Fire_Flowers</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ファイアーフラワー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お菓子に花火の演出効果を加える。</t>
+    <rPh sb="1" eb="3">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハナビ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>クワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お菓子の周りに花火を飛ばした演出が可能になる。
+見た目を派手にすることができる。
+パーティに向けたお客さんに喜んでもらうことができる。</t>
+    <rPh sb="1" eb="3">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハナビ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ハデ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ほのおの煌めき</t>
+    <rPh sb="4" eb="5">
+      <t>キラ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>みずの呼び声</t>
+    <rPh sb="3" eb="4">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゴエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かぜの囁き</t>
+    <rPh sb="3" eb="4">
+      <t>ササヤ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風の演出をおかしに加える。</t>
+    <rPh sb="2" eb="4">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>クワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風の演出をおかしに加える。
+また、水あめ・チョコレートにかけると、羽飾りに変形する。
+派生：
+LV1で、各ウィンド系の魔法の習得可</t>
+    <rPh sb="18" eb="19">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ハネ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ハセイ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>マホウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3639,7 +3690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:T61"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -3660,7 +3711,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -3690,10 +3741,10 @@
         <v>12</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
@@ -3705,21 +3756,21 @@
         <v>10</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
-        <f t="shared" ref="A2:A60" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A61" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="5">
@@ -3732,7 +3783,7 @@
         <v>18</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>15</v>
@@ -3756,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N2" s="5">
         <v>1</v>
@@ -3771,10 +3822,10 @@
         <v>6</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T2" s="5">
         <v>0</v>
@@ -3789,16 +3840,16 @@
         <v>1002</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="G3" s="3">
         <v>6</v>
@@ -3819,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N3" s="3">
         <v>0</v>
@@ -3834,10 +3885,10 @@
         <v>6</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T3" s="3">
         <v>0</v>
@@ -3855,13 +3906,13 @@
         <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -3882,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N4" s="5">
         <v>1</v>
@@ -3897,10 +3948,10 @@
         <v>6</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T4" s="5">
         <v>0</v>
@@ -3915,16 +3966,16 @@
         <v>1010</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G5" s="3">
         <v>6</v>
@@ -3945,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N5" s="3">
         <v>0</v>
@@ -3960,10 +4011,10 @@
         <v>6</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T5" s="3">
         <v>0</v>
@@ -3978,16 +4029,16 @@
         <v>1003</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="G6" s="3">
         <v>2</v>
@@ -4008,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N6" s="3">
         <v>1</v>
@@ -4023,10 +4074,10 @@
         <v>6</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T6" s="3">
         <v>0</v>
@@ -4041,16 +4092,16 @@
         <v>1004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="G7" s="3">
         <v>2</v>
@@ -4071,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N7" s="3">
         <v>0</v>
@@ -4086,10 +4137,10 @@
         <v>6</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T7" s="3">
         <v>0</v>
@@ -4104,16 +4155,16 @@
         <v>1006</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>83</v>
+        <v>255</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>87</v>
+        <v>257</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
@@ -4128,13 +4179,13 @@
         <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="N8" s="3">
         <v>1</v>
@@ -4149,327 +4200,327 @@
         <v>6</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="T8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="7">
+    <row r="9" spans="1:20" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="7">
-        <v>1007</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G9" s="7">
-        <v>6</v>
-      </c>
-      <c r="H9" s="7">
-        <v>1</v>
-      </c>
-      <c r="I9" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J9" s="7">
-        <v>0</v>
-      </c>
-      <c r="K9" s="7">
-        <v>1</v>
-      </c>
-      <c r="L9" s="7">
-        <v>0</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="N9" s="7">
-        <v>1</v>
-      </c>
-      <c r="O9" s="7">
+      <c r="B9" s="3">
+        <v>1006</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="3">
+        <v>6</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N9" s="3">
+        <v>1</v>
+      </c>
+      <c r="O9" s="3">
         <v>9</v>
       </c>
-      <c r="P9" s="7">
+      <c r="P9" s="3">
         <v>100</v>
       </c>
-      <c r="Q9" s="7">
-        <v>6</v>
-      </c>
-      <c r="R9" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="S9" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="T9" s="7">
-        <v>0</v>
+      <c r="Q9" s="3">
+        <v>6</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T9" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10">
+    <row r="10" spans="1:20" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10">
-        <v>1008</v>
-      </c>
-      <c r="C10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" t="s">
-        <v>185</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="B10" s="7">
+        <v>1007</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="G10">
-        <v>6</v>
-      </c>
-      <c r="H10">
-        <v>3</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>2</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10" t="s">
-        <v>97</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="O10">
+      <c r="G10" s="7">
+        <v>6</v>
+      </c>
+      <c r="H10" s="7">
+        <v>1</v>
+      </c>
+      <c r="I10" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7">
+        <v>1</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" s="7">
+        <v>1</v>
+      </c>
+      <c r="O10" s="7">
         <v>9</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="7">
         <v>100</v>
       </c>
-      <c r="Q10">
-        <v>6</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="S10" t="s">
-        <v>83</v>
-      </c>
-      <c r="T10">
-        <v>1</v>
+      <c r="Q10" s="7">
+        <v>6</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="T10" s="7">
+        <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="3">
+    <row r="11" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="3">
-        <v>1009</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="G11" s="3">
-        <v>6</v>
-      </c>
-      <c r="H11" s="3">
+      <c r="B11">
+        <v>1008</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
+      <c r="H11">
         <v>3</v>
       </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3">
-        <v>3</v>
-      </c>
-      <c r="L11" s="3">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="N11" s="3">
-        <v>1</v>
-      </c>
-      <c r="O11" s="3">
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>96</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
         <v>9</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11">
         <v>100</v>
       </c>
-      <c r="Q11" s="3">
-        <v>6</v>
-      </c>
-      <c r="R11" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T11" s="3">
-        <v>0</v>
+      <c r="Q11">
+        <v>6</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="S11" t="s">
+        <v>82</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12">
+    <row r="12" spans="1:20" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>1009</v>
       </c>
-      <c r="C12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" t="s">
-        <v>228</v>
-      </c>
-      <c r="E12" t="s">
-        <v>247</v>
-      </c>
-      <c r="F12" t="s">
-        <v>230</v>
-      </c>
-      <c r="G12">
-        <v>6</v>
-      </c>
-      <c r="H12">
-        <v>20</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
+      <c r="C12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G12" s="3">
+        <v>6</v>
+      </c>
+      <c r="H12" s="3">
         <v>3</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="s">
-        <v>97</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12">
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N12" s="3">
+        <v>1</v>
+      </c>
+      <c r="O12" s="3">
         <v>9</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12">
-        <v>6</v>
-      </c>
-      <c r="R12" t="s">
-        <v>230</v>
-      </c>
-      <c r="S12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T12">
+      <c r="Q12" s="3">
+        <v>6</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="T12" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="3">
+    <row r="13" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="3">
-        <v>2004</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G13" s="3">
-        <v>2</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3">
-        <v>5</v>
-      </c>
-      <c r="L13" s="3">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="N13" s="3">
-        <v>0</v>
-      </c>
-      <c r="O13" s="3">
-        <v>1</v>
-      </c>
-      <c r="P13" s="3">
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
+        <v>226</v>
+      </c>
+      <c r="E13" t="s">
+        <v>259</v>
+      </c>
+      <c r="F13" t="s">
+        <v>228</v>
+      </c>
+      <c r="G13">
+        <v>6</v>
+      </c>
+      <c r="H13">
+        <v>20</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>3</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>96</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>9</v>
+      </c>
+      <c r="P13">
         <v>100</v>
       </c>
-      <c r="Q13" s="3">
-        <v>6</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T13" s="3">
+      <c r="Q13">
+        <v>6</v>
+      </c>
+      <c r="R13" t="s">
+        <v>228</v>
+      </c>
+      <c r="S13" t="s">
+        <v>96</v>
+      </c>
+      <c r="T13">
         <v>0</v>
       </c>
     </row>
@@ -4479,25 +4530,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>53</v>
+        <v>176</v>
       </c>
       <c r="G14" s="3">
         <v>2</v>
       </c>
       <c r="H14" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -4512,10 +4563,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>1</v>
@@ -4527,10 +4578,10 @@
         <v>6</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>259</v>
+        <v>179</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -4545,37 +4596,37 @@
         <v>2001</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>192</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>196</v>
+        <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>204</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3">
         <v>2</v>
       </c>
       <c r="H15" s="3">
+        <v>2</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>5</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
-        <v>1</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N15" s="3">
         <v>1</v>
@@ -4590,264 +4641,264 @@
         <v>6</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="T15" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" s="5" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="5">
+    <row r="16" spans="1:20" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="5">
-        <v>2002</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="5">
+      <c r="B16" s="3">
+        <v>2001</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G16" s="3">
         <v>2</v>
       </c>
-      <c r="H16" s="5">
-        <v>1</v>
-      </c>
-      <c r="I16" s="5">
-        <v>9999</v>
-      </c>
-      <c r="J16" s="5">
-        <v>0</v>
-      </c>
-      <c r="K16" s="5">
-        <v>1</v>
-      </c>
-      <c r="L16" s="5">
-        <v>0</v>
-      </c>
-      <c r="M16" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="N16" s="5">
-        <v>1</v>
-      </c>
-      <c r="O16" s="5">
-        <v>1</v>
-      </c>
-      <c r="P16" s="5">
+      <c r="H16" s="3">
+        <v>5</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3">
+        <v>1</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N16" s="3">
+        <v>1</v>
+      </c>
+      <c r="O16" s="3">
+        <v>1</v>
+      </c>
+      <c r="P16" s="3">
         <v>100</v>
       </c>
-      <c r="Q16" s="5">
-        <v>6</v>
-      </c>
-      <c r="R16" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="S16" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="T16" s="5">
-        <v>0</v>
+      <c r="Q16" s="3">
+        <v>6</v>
+      </c>
+      <c r="R16" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="T16" s="3">
+        <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:20" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="3">
+    <row r="17" spans="1:20" s="5" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="3">
-        <v>2003</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="B17" s="5">
+        <v>2002</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="5">
         <v>2</v>
       </c>
-      <c r="H17" s="3">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="H17" s="5">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5">
+        <v>9999</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>1</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1</v>
+      </c>
+      <c r="O17" s="5">
+        <v>1</v>
+      </c>
+      <c r="P17" s="5">
         <v>100</v>
       </c>
-      <c r="Q17" s="3">
-        <v>6</v>
-      </c>
-      <c r="R17" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="Q17" s="5">
+        <v>6</v>
+      </c>
+      <c r="R17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="S17" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="T17" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18">
+    <row r="18" spans="1:20" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="3">
         <v>2003</v>
       </c>
-      <c r="C18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" t="s">
-        <v>227</v>
-      </c>
-      <c r="E18" t="s">
-        <v>248</v>
-      </c>
-      <c r="F18" t="s">
-        <v>229</v>
-      </c>
-      <c r="G18">
+      <c r="C18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G18" s="3">
         <v>2</v>
       </c>
-      <c r="H18">
-        <v>20</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
+      <c r="H18" s="3">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>5</v>
       </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18" t="s">
-        <v>97</v>
-      </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-      <c r="P18">
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N18" s="3">
+        <v>1</v>
+      </c>
+      <c r="O18" s="3">
+        <v>1</v>
+      </c>
+      <c r="P18" s="3">
         <v>100</v>
       </c>
-      <c r="Q18">
-        <v>6</v>
-      </c>
-      <c r="R18" t="s">
-        <v>229</v>
-      </c>
-      <c r="S18" t="s">
-        <v>97</v>
-      </c>
-      <c r="T18">
+      <c r="Q18" s="3">
+        <v>6</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="T18" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" s="3" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="3">
+    <row r="19" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="3">
-        <v>3006</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G19" s="3">
+      <c r="B19">
+        <v>2003</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
+        <v>225</v>
+      </c>
+      <c r="E19" t="s">
+        <v>260</v>
+      </c>
+      <c r="F19" t="s">
+        <v>227</v>
+      </c>
+      <c r="G19">
         <v>2</v>
       </c>
-      <c r="H19" s="3">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3">
+      <c r="H19">
+        <v>20</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
         <v>5</v>
       </c>
-      <c r="L19" s="3">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="N19" s="3">
-        <v>0</v>
-      </c>
-      <c r="O19" s="3">
-        <v>2</v>
-      </c>
-      <c r="P19" s="3">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="s">
+        <v>96</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
         <v>100</v>
       </c>
-      <c r="Q19" s="3">
-        <v>6</v>
-      </c>
-      <c r="R19" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T19" s="3">
+      <c r="Q19">
+        <v>6</v>
+      </c>
+      <c r="R19" t="s">
+        <v>227</v>
+      </c>
+      <c r="S19" t="s">
+        <v>96</v>
+      </c>
+      <c r="T19">
         <v>0</v>
       </c>
     </row>
@@ -4857,31 +4908,31 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>3001</v>
+        <v>3006</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>17</v>
+        <v>167</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>14</v>
+        <v>166</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
       </c>
       <c r="H20" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>5</v>
@@ -4890,10 +4941,10 @@
         <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>2</v>
@@ -4905,46 +4956,46 @@
         <v>6</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>256</v>
+        <v>175</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:20" s="3" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G21" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H21" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" s="3">
         <v>0</v>
       </c>
       <c r="J21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="3">
         <v>5</v>
@@ -4953,7 +5004,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N21" s="3">
         <v>1</v>
@@ -4968,13 +5019,13 @@
         <v>6</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="T21" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -4983,25 +5034,25 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>252</v>
+        <v>19</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="G22" s="3">
         <v>4</v>
       </c>
       <c r="H22" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -5010,13 +5061,13 @@
         <v>0</v>
       </c>
       <c r="K22" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N22" s="3">
         <v>1</v>
@@ -5031,13 +5082,13 @@
         <v>6</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="T22" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -5046,25 +5097,25 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="G23" s="3">
         <v>4</v>
       </c>
       <c r="H23" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I23" s="3">
         <v>0</v>
@@ -5073,16 +5124,16 @@
         <v>0</v>
       </c>
       <c r="K23" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L23" s="3">
         <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="N23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="3">
         <v>2</v>
@@ -5094,75 +5145,75 @@
         <v>6</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24">
+    <row r="24" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24">
-        <v>3005</v>
-      </c>
-      <c r="C24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" t="s">
-        <v>130</v>
-      </c>
-      <c r="E24" t="s">
-        <v>132</v>
-      </c>
-      <c r="F24" t="s">
-        <v>129</v>
-      </c>
-      <c r="G24">
+      <c r="B24" s="3">
+        <v>3004</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24" s="3">
         <v>4</v>
       </c>
-      <c r="H24">
-        <v>10</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>5</v>
       </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24" t="s">
-        <v>97</v>
-      </c>
-      <c r="N24">
-        <v>1</v>
-      </c>
-      <c r="O24">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>2</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24">
-        <v>6</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="S24" t="s">
-        <v>97</v>
-      </c>
-      <c r="T24">
+      <c r="Q24" s="3">
+        <v>6</v>
+      </c>
+      <c r="R24" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="T24" s="3">
         <v>0</v>
       </c>
     </row>
@@ -5175,22 +5226,22 @@
         <v>3005</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="E25" t="s">
-        <v>241</v>
+        <v>131</v>
       </c>
       <c r="F25" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="G25">
         <v>4</v>
       </c>
       <c r="H25">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5205,7 +5256,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -5220,75 +5271,75 @@
         <v>6</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>251</v>
+        <v>130</v>
       </c>
       <c r="S25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="3">
+    <row r="26" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="3">
-        <v>4010</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G26" s="3">
-        <v>6</v>
-      </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="B26">
+        <v>3005</v>
+      </c>
+      <c r="C26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E26" t="s">
+        <v>238</v>
+      </c>
+      <c r="F26" t="s">
+        <v>239</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26">
+        <v>20</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
         <v>5</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="s">
+        <v>96</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>2</v>
+      </c>
+      <c r="P26">
         <v>100</v>
       </c>
-      <c r="Q26" s="3">
-        <v>6</v>
-      </c>
-      <c r="R26" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="Q26">
+        <v>6</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="S26" t="s">
+        <v>96</v>
+      </c>
+      <c r="T26">
         <v>0</v>
       </c>
     </row>
@@ -5298,19 +5349,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>237</v>
+        <v>161</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G27" s="3">
         <v>6</v>
@@ -5331,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N27" s="3">
         <v>0</v>
@@ -5346,10 +5397,10 @@
         <v>6</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>166</v>
+        <v>240</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T27" s="3">
         <v>0</v>
@@ -5361,25 +5412,25 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>4001</v>
+        <v>4011</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>22</v>
+        <v>235</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>239</v>
+        <v>164</v>
       </c>
       <c r="G28" s="3">
         <v>6</v>
       </c>
       <c r="H28" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" s="3">
         <v>0</v>
@@ -5388,16 +5439,16 @@
         <v>0</v>
       </c>
       <c r="K28" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L28" s="3">
         <v>0</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="3">
         <v>3</v>
@@ -5409,37 +5460,37 @@
         <v>6</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>258</v>
+        <v>165</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T28" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:20" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B29" s="3">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>215</v>
+        <v>262</v>
       </c>
       <c r="G29" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H29" s="3">
         <v>2</v>
@@ -5457,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="N29" s="3">
         <v>1</v>
@@ -5472,10 +5523,10 @@
         <v>6</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -5487,19 +5538,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -5508,7 +5559,7 @@
         <v>2</v>
       </c>
       <c r="I30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3">
         <v>0</v>
@@ -5520,7 +5571,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N30" s="3">
         <v>1</v>
@@ -5535,13 +5586,13 @@
         <v>6</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="T30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -5550,19 +5601,19 @@
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>186</v>
+        <v>135</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -5583,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N31" s="3">
         <v>1</v>
@@ -5598,7 +5649,7 @@
         <v>6</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="S31" s="3" t="s">
         <v>24</v>
@@ -5613,19 +5664,19 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -5646,7 +5697,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N32" s="3">
         <v>1</v>
@@ -5661,7 +5712,7 @@
         <v>6</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>24</v>
@@ -5679,16 +5730,16 @@
         <v>4012</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -5697,19 +5748,19 @@
         <v>2</v>
       </c>
       <c r="I33" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
       </c>
       <c r="K33" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L33" s="3">
         <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N33" s="3">
         <v>1</v>
@@ -5724,7 +5775,7 @@
         <v>6</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>24</v>
@@ -5742,16 +5793,16 @@
         <v>4012</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -5772,7 +5823,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N34" s="3">
         <v>1</v>
@@ -5787,7 +5838,7 @@
         <v>6</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="S34" s="3" t="s">
         <v>24</v>
@@ -5796,28 +5847,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:20" s="3" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B35" s="3">
-        <v>4003</v>
+        <v>4012</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>27</v>
+        <v>196</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>74</v>
+        <v>202</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>25</v>
+        <v>197</v>
       </c>
       <c r="G35" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35" s="3">
         <v>2</v>
@@ -5829,13 +5880,13 @@
         <v>0</v>
       </c>
       <c r="K35" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L35" s="3">
         <v>0</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N35" s="3">
         <v>1</v>
@@ -5850,55 +5901,55 @@
         <v>6</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>110</v>
+        <v>211</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="T35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:20" s="3" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="3">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G36" s="3">
         <v>3</v>
       </c>
       <c r="H36" s="3">
+        <v>2</v>
+      </c>
+      <c r="I36" s="3">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
         <v>3</v>
       </c>
-      <c r="I36" s="3">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3">
-        <v>0</v>
-      </c>
-      <c r="K36" s="3">
-        <v>1</v>
-      </c>
       <c r="L36" s="3">
         <v>0</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N36" s="3">
         <v>1</v>
@@ -5913,138 +5964,138 @@
         <v>6</v>
       </c>
       <c r="R36" s="4" t="s">
-        <v>213</v>
+        <v>109</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T36" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:20" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="7">
+    <row r="37" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="3">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B37" s="7">
-        <v>4005</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" s="7">
-        <v>12</v>
-      </c>
-      <c r="H37" s="7">
-        <v>5</v>
-      </c>
-      <c r="I37" s="7">
-        <v>0</v>
-      </c>
-      <c r="J37" s="7">
-        <v>0</v>
-      </c>
-      <c r="K37" s="7">
+      <c r="B37" s="3">
+        <v>4004</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G37" s="3">
         <v>3</v>
       </c>
-      <c r="L37" s="7">
-        <v>0</v>
-      </c>
-      <c r="M37" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="N37" s="7">
-        <v>1</v>
-      </c>
-      <c r="O37" s="7">
+      <c r="H37" s="3">
         <v>3</v>
       </c>
-      <c r="P37" s="7">
+      <c r="I37" s="3">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
+        <v>0</v>
+      </c>
+      <c r="K37" s="3">
+        <v>1</v>
+      </c>
+      <c r="L37" s="3">
+        <v>0</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N37" s="3">
+        <v>1</v>
+      </c>
+      <c r="O37" s="3">
+        <v>3</v>
+      </c>
+      <c r="P37" s="3">
         <v>100</v>
       </c>
-      <c r="Q37" s="7">
-        <v>6</v>
-      </c>
-      <c r="R37" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="S37" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="T37" s="7">
+      <c r="Q37" s="3">
+        <v>6</v>
+      </c>
+      <c r="R37" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="T37" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="3">
+    <row r="38" spans="1:20" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="7">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B38" s="3">
-        <v>4006</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G38" s="3">
+      <c r="B38" s="7">
+        <v>4005</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38" s="7">
+        <v>12</v>
+      </c>
+      <c r="H38" s="7">
+        <v>5</v>
+      </c>
+      <c r="I38" s="7">
+        <v>0</v>
+      </c>
+      <c r="J38" s="7">
+        <v>0</v>
+      </c>
+      <c r="K38" s="7">
         <v>3</v>
       </c>
-      <c r="H38" s="3">
+      <c r="L38" s="7">
+        <v>0</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="N38" s="7">
+        <v>1</v>
+      </c>
+      <c r="O38" s="7">
         <v>3</v>
       </c>
-      <c r="I38" s="3">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3">
-        <v>0</v>
-      </c>
-      <c r="K38" s="3">
-        <v>3</v>
-      </c>
-      <c r="L38" s="3">
-        <v>0</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="N38" s="3">
-        <v>1</v>
-      </c>
-      <c r="O38" s="3">
-        <v>3</v>
-      </c>
-      <c r="P38" s="3">
+      <c r="P38" s="7">
         <v>100</v>
       </c>
-      <c r="Q38" s="3">
-        <v>6</v>
-      </c>
-      <c r="R38" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T38" s="3">
+      <c r="Q38" s="7">
+        <v>6</v>
+      </c>
+      <c r="R38" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="S38" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="T38" s="7">
         <v>0</v>
       </c>
     </row>
@@ -6054,19 +6105,19 @@
         <v>37</v>
       </c>
       <c r="B39" s="3">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G39" s="3">
         <v>3</v>
@@ -6087,7 +6138,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N39" s="3">
         <v>1</v>
@@ -6102,10 +6153,10 @@
         <v>6</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T39" s="3">
         <v>0</v>
@@ -6120,16 +6171,16 @@
         <v>4007</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>220</v>
+        <v>87</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>221</v>
+        <v>89</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>222</v>
+        <v>106</v>
       </c>
       <c r="G40" s="3">
         <v>3</v>
@@ -6150,7 +6201,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N40" s="3">
         <v>1</v>
@@ -6165,10 +6216,10 @@
         <v>6</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>222</v>
+        <v>106</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T40" s="3">
         <v>0</v>
@@ -6180,19 +6231,19 @@
         <v>39</v>
       </c>
       <c r="B41" s="3">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>89</v>
+        <v>218</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>91</v>
+        <v>219</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="G41" s="3">
         <v>3</v>
@@ -6213,7 +6264,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N41" s="3">
         <v>1</v>
@@ -6228,10 +6279,10 @@
         <v>6</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T41" s="3">
         <v>0</v>
@@ -6243,16 +6294,16 @@
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>108</v>
@@ -6276,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N42" s="3">
         <v>1</v>
@@ -6294,100 +6345,100 @@
         <v>108</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43">
+    <row r="43" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43">
-        <v>4013</v>
-      </c>
-      <c r="C43" t="s">
-        <v>40</v>
-      </c>
-      <c r="D43" t="s">
-        <v>173</v>
-      </c>
-      <c r="E43" t="s">
-        <v>249</v>
-      </c>
-      <c r="F43" t="s">
-        <v>171</v>
-      </c>
-      <c r="G43">
-        <v>6</v>
-      </c>
-      <c r="H43">
-        <v>20</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>5</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43" t="s">
-        <v>97</v>
-      </c>
-      <c r="N43">
-        <v>1</v>
-      </c>
-      <c r="O43">
+      <c r="B43" s="3">
+        <v>4009</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G43" s="3">
         <v>3</v>
       </c>
-      <c r="P43">
+      <c r="H43" s="3">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N43" s="3">
+        <v>1</v>
+      </c>
+      <c r="O43" s="3">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43">
-        <v>6</v>
-      </c>
-      <c r="R43" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="S43" t="s">
-        <v>97</v>
-      </c>
-      <c r="T43">
+      <c r="Q43" s="3">
+        <v>6</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="T43" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B44">
-        <v>5004</v>
+        <v>4013</v>
       </c>
       <c r="C44" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D44" t="s">
+        <v>172</v>
+      </c>
+      <c r="E44" t="s">
+        <v>261</v>
+      </c>
+      <c r="F44" t="s">
         <v>170</v>
       </c>
-      <c r="E44" t="s">
-        <v>169</v>
-      </c>
-      <c r="F44" t="s">
-        <v>210</v>
-      </c>
       <c r="G44">
         <v>6</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -6402,13 +6453,13 @@
         <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P44">
         <v>100</v>
@@ -6417,103 +6468,103 @@
         <v>6</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>253</v>
+        <v>171</v>
       </c>
       <c r="S44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="3">
+    <row r="45" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45" s="3">
-        <v>5001</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G45" s="3">
-        <v>6</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="N45" s="3">
-        <v>1</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="B45">
+        <v>5004</v>
+      </c>
+      <c r="C45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" t="s">
+        <v>169</v>
+      </c>
+      <c r="E45" t="s">
+        <v>168</v>
+      </c>
+      <c r="F45" t="s">
+        <v>209</v>
+      </c>
+      <c r="G45">
+        <v>6</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>5</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="s">
+        <v>96</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45">
         <v>100</v>
       </c>
-      <c r="Q45" s="3">
-        <v>6</v>
-      </c>
-      <c r="R45" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T45" s="3">
+      <c r="Q45">
+        <v>6</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="S45" t="s">
+        <v>96</v>
+      </c>
+      <c r="T45">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:20" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="3">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="G46" s="3">
         <v>6</v>
       </c>
       <c r="H46" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" s="3">
         <v>0</v>
@@ -6528,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="N46" s="3">
         <v>1</v>
@@ -6543,10 +6594,10 @@
         <v>6</v>
       </c>
       <c r="R46" s="4" t="s">
-        <v>208</v>
+        <v>141</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T46" s="3">
         <v>0</v>
@@ -6558,19 +6609,19 @@
         <v>45</v>
       </c>
       <c r="B47" s="3">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>209</v>
+        <v>125</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="G47" s="3">
         <v>6</v>
@@ -6591,7 +6642,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N47" s="3">
         <v>1</v>
@@ -6606,10 +6657,10 @@
         <v>6</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -6621,19 +6672,19 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>5005</v>
+        <v>5003</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>226</v>
+        <v>147</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>224</v>
+        <v>146</v>
       </c>
       <c r="G48" s="3">
         <v>6</v>
@@ -6654,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>254</v>
+        <v>96</v>
       </c>
       <c r="N48" s="3">
         <v>1</v>
@@ -6669,10 +6720,10 @@
         <v>6</v>
       </c>
       <c r="R48" s="4" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -6684,19 +6735,19 @@
         <v>47</v>
       </c>
       <c r="B49" s="3">
-        <v>5006</v>
+        <v>5005</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="G49" s="3">
         <v>6</v>
@@ -6711,13 +6762,13 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>97</v>
+        <v>248</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
@@ -6732,264 +6783,264 @@
         <v>6</v>
       </c>
       <c r="R49" s="4" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="7">
+    <row r="50" spans="1:20" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="3">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B50" s="7">
-        <v>6001</v>
-      </c>
-      <c r="C50" s="7" t="s">
+      <c r="B50" s="3">
+        <v>5006</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D50" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G50" s="7">
-        <v>6</v>
-      </c>
-      <c r="H50" s="7">
+      <c r="D50" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G50" s="3">
+        <v>6</v>
+      </c>
+      <c r="H50" s="3">
         <v>3</v>
       </c>
-      <c r="I50" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J50" s="7">
-        <v>0</v>
-      </c>
-      <c r="K50" s="7">
-        <v>10</v>
-      </c>
-      <c r="L50" s="7">
-        <v>0</v>
-      </c>
-      <c r="M50" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="N50" s="7">
-        <v>1</v>
-      </c>
-      <c r="O50" s="7">
-        <v>5</v>
-      </c>
-      <c r="P50" s="7">
+      <c r="I50" s="3">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3">
+        <v>0</v>
+      </c>
+      <c r="K50" s="3">
+        <v>1</v>
+      </c>
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N50" s="3">
+        <v>1</v>
+      </c>
+      <c r="O50" s="3">
+        <v>4</v>
+      </c>
+      <c r="P50" s="3">
         <v>100</v>
       </c>
-      <c r="Q50" s="7">
-        <v>6</v>
-      </c>
-      <c r="R50" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="S50" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="T50" s="7">
+      <c r="Q50" s="3">
+        <v>6</v>
+      </c>
+      <c r="R50" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="T50" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="3">
+    <row r="51" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="7">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B51" s="3">
-        <v>6002</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G51" s="3">
-        <v>6</v>
-      </c>
-      <c r="H51" s="3">
+      <c r="B51" s="7">
+        <v>6001</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G51" s="7">
+        <v>6</v>
+      </c>
+      <c r="H51" s="7">
         <v>3</v>
       </c>
-      <c r="I51" s="3">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3">
-        <v>0</v>
-      </c>
-      <c r="K51" s="3">
+      <c r="I51" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J51" s="7">
+        <v>0</v>
+      </c>
+      <c r="K51" s="7">
+        <v>10</v>
+      </c>
+      <c r="L51" s="7">
+        <v>0</v>
+      </c>
+      <c r="M51" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="N51" s="7">
+        <v>1</v>
+      </c>
+      <c r="O51" s="7">
         <v>5</v>
       </c>
-      <c r="L51" s="3">
-        <v>0</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="N51" s="3">
-        <v>1</v>
-      </c>
-      <c r="O51" s="3">
-        <v>5</v>
-      </c>
-      <c r="P51" s="3">
+      <c r="P51" s="7">
         <v>100</v>
       </c>
-      <c r="Q51" s="3">
-        <v>6</v>
-      </c>
-      <c r="R51" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="S51" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T51" s="3">
+      <c r="Q51" s="7">
+        <v>6</v>
+      </c>
+      <c r="R51" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S51" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="T51" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A52">
+    <row r="52" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="3">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B52">
-        <v>6003</v>
-      </c>
-      <c r="C52" t="s">
-        <v>153</v>
-      </c>
-      <c r="D52" t="s">
-        <v>45</v>
-      </c>
-      <c r="E52" t="s">
-        <v>43</v>
-      </c>
-      <c r="F52" t="s">
-        <v>44</v>
-      </c>
-      <c r="G52">
-        <v>6</v>
-      </c>
-      <c r="H52">
+      <c r="B52" s="3">
+        <v>6002</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G52" s="3">
+        <v>6</v>
+      </c>
+      <c r="H52" s="3">
         <v>3</v>
       </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <v>1</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52" t="s">
-        <v>97</v>
-      </c>
-      <c r="N52">
-        <v>1</v>
-      </c>
-      <c r="O52">
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>5</v>
       </c>
-      <c r="P52">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N52" s="3">
+        <v>1</v>
+      </c>
+      <c r="O52" s="3">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52">
-        <v>6</v>
-      </c>
-      <c r="R52" t="s">
-        <v>181</v>
-      </c>
-      <c r="S52" t="s">
-        <v>97</v>
-      </c>
-      <c r="T52">
+      <c r="Q52" s="3">
+        <v>6</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="T52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="8">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53" s="8">
-        <v>7001</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G53" s="8">
-        <v>6</v>
-      </c>
-      <c r="H53" s="8">
-        <v>15</v>
-      </c>
-      <c r="I53" s="8">
-        <v>0</v>
-      </c>
-      <c r="J53" s="8">
-        <v>0</v>
-      </c>
-      <c r="K53" s="8">
-        <v>1</v>
-      </c>
-      <c r="L53" s="8">
-        <v>0</v>
-      </c>
-      <c r="M53" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="N53" s="8">
-        <v>1</v>
-      </c>
-      <c r="O53" s="8">
-        <v>6</v>
-      </c>
-      <c r="P53" s="8">
+      <c r="B53">
+        <v>6003</v>
+      </c>
+      <c r="C53" t="s">
+        <v>152</v>
+      </c>
+      <c r="D53" t="s">
+        <v>44</v>
+      </c>
+      <c r="E53" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" t="s">
+        <v>43</v>
+      </c>
+      <c r="G53">
+        <v>6</v>
+      </c>
+      <c r="H53">
+        <v>3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" t="s">
+        <v>96</v>
+      </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
+      <c r="O53">
+        <v>5</v>
+      </c>
+      <c r="P53">
         <v>100</v>
       </c>
-      <c r="Q53" s="8">
-        <v>6</v>
-      </c>
-      <c r="R53" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="S53" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="T53" s="8">
+      <c r="Q53">
+        <v>6</v>
+      </c>
+      <c r="R53" t="s">
+        <v>180</v>
+      </c>
+      <c r="S53" t="s">
+        <v>96</v>
+      </c>
+      <c r="T53">
         <v>0</v>
       </c>
     </row>
@@ -6999,25 +7050,25 @@
         <v>52</v>
       </c>
       <c r="B54" s="8">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D54" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E54" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E54" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="F54" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G54" s="8">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H54" s="8">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I54" s="8">
         <v>0</v>
@@ -7032,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N54" s="8">
         <v>1</v>
@@ -7047,10 +7098,10 @@
         <v>6</v>
       </c>
       <c r="R54" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="S54" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T54" s="8">
         <v>0</v>
@@ -7062,25 +7113,25 @@
         <v>53</v>
       </c>
       <c r="B55" s="8">
-        <v>8001</v>
+        <v>7002</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G55" s="8">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H55" s="8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I55" s="8">
         <v>0</v>
@@ -7095,13 +7146,13 @@
         <v>0</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N55" s="8">
         <v>1</v>
       </c>
       <c r="O55" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P55" s="8">
         <v>100</v>
@@ -7110,10 +7161,10 @@
         <v>6</v>
       </c>
       <c r="R55" s="8" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="S55" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T55" s="8">
         <v>0</v>
@@ -7125,25 +7176,25 @@
         <v>54</v>
       </c>
       <c r="B56" s="8">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D56" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F56" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E56" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>34</v>
-      </c>
       <c r="G56" s="8">
         <v>6</v>
       </c>
       <c r="H56" s="8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I56" s="8">
         <v>0</v>
@@ -7158,7 +7209,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N56" s="8">
         <v>1</v>
@@ -7173,103 +7224,103 @@
         <v>6</v>
       </c>
       <c r="R56" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S56" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T56" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:20" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="3">
+    <row r="57" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="8">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B57" s="3">
-        <v>9001</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3">
-        <v>10</v>
-      </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="B57" s="8">
+        <v>8002</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G57" s="8">
+        <v>6</v>
+      </c>
+      <c r="H57" s="8">
         <v>8</v>
       </c>
-      <c r="P57" s="3">
+      <c r="I57" s="8">
+        <v>0</v>
+      </c>
+      <c r="J57" s="8">
+        <v>0</v>
+      </c>
+      <c r="K57" s="8">
+        <v>1</v>
+      </c>
+      <c r="L57" s="8">
+        <v>0</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="N57" s="8">
+        <v>1</v>
+      </c>
+      <c r="O57" s="8">
+        <v>7</v>
+      </c>
+      <c r="P57" s="8">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
-        <v>6</v>
-      </c>
-      <c r="R57" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T57" s="3">
+      <c r="Q57" s="8">
+        <v>6</v>
+      </c>
+      <c r="R57" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S57" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="T57" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:20" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="3">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B58" s="3">
-        <v>9002</v>
+        <v>9001</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="G58" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H58" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -7284,7 +7335,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="N58" s="3">
         <v>1</v>
@@ -7299,138 +7350,201 @@
         <v>6</v>
       </c>
       <c r="R58" s="4" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59">
+    <row r="59" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="3">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B59">
-        <v>9004</v>
-      </c>
-      <c r="C59" t="s">
-        <v>71</v>
-      </c>
-      <c r="D59" t="s">
-        <v>102</v>
-      </c>
-      <c r="E59" t="s">
+      <c r="B59" s="3">
+        <v>9002</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G59" s="3">
+        <v>6</v>
+      </c>
+      <c r="H59" s="3">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
+        <v>10</v>
+      </c>
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N59" s="3">
+        <v>1</v>
+      </c>
+      <c r="O59" s="3">
+        <v>8</v>
+      </c>
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" t="s">
-        <v>101</v>
-      </c>
-      <c r="G59">
-        <v>2</v>
-      </c>
-      <c r="H59">
-        <v>5</v>
-      </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <v>5</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
-      <c r="M59" t="s">
-        <v>97</v>
-      </c>
-      <c r="N59">
-        <v>1</v>
-      </c>
-      <c r="O59">
-        <v>8</v>
-      </c>
-      <c r="P59">
-        <v>100</v>
-      </c>
-      <c r="Q59">
-        <v>6</v>
-      </c>
-      <c r="R59" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="S59" t="s">
-        <v>97</v>
-      </c>
-      <c r="T59">
+      <c r="Q59" s="3">
+        <v>6</v>
+      </c>
+      <c r="R59" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="T59" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:20" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="3">
+    <row r="60" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60">
+        <v>9004</v>
+      </c>
+      <c r="C60" t="s">
+        <v>70</v>
+      </c>
+      <c r="D60" t="s">
+        <v>101</v>
+      </c>
+      <c r="E60" t="s">
+        <v>99</v>
+      </c>
+      <c r="F60" t="s">
+        <v>100</v>
+      </c>
+      <c r="G60">
+        <v>2</v>
+      </c>
+      <c r="H60">
+        <v>5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>5</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" t="s">
+        <v>96</v>
+      </c>
+      <c r="N60">
+        <v>1</v>
+      </c>
+      <c r="O60">
+        <v>8</v>
+      </c>
+      <c r="P60">
+        <v>100</v>
+      </c>
+      <c r="Q60">
+        <v>6</v>
+      </c>
+      <c r="R60" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="S60" t="s">
+        <v>96</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="3">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B61" s="3">
         <v>9003</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E60" s="3" t="s">
+      <c r="C61" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G60" s="3">
-        <v>6</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1</v>
-      </c>
-      <c r="K60" s="3">
-        <v>1</v>
-      </c>
-      <c r="L60" s="3">
-        <v>1</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="N60" s="3">
-        <v>1</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="E61" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G61" s="3">
+        <v>6</v>
+      </c>
+      <c r="H61" s="3">
+        <v>1</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>1</v>
+      </c>
+      <c r="K61" s="3">
+        <v>1</v>
+      </c>
+      <c r="L61" s="3">
+        <v>1</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="N61" s="3">
+        <v>1</v>
+      </c>
+      <c r="O61" s="3">
         <v>8</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P61" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3">
-        <v>6</v>
-      </c>
-      <c r="R60" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="T60" s="3">
+      <c r="Q61" s="3">
+        <v>6</v>
+      </c>
+      <c r="R61" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="S61" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="T61" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6E97E3-9380-439A-8DC6-1D1A8CA3C6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99758EA1-ED32-432F-8A8C-B81B4F6F5DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="735" yWindow="735" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
@@ -6063,7 +6063,7 @@
         <v>5</v>
       </c>
       <c r="I38" s="7">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="J38" s="7">
         <v>0</v>
@@ -6351,66 +6351,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="3">
+    <row r="43" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="5">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="5">
         <v>4009</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="5">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="5">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="I43" s="5">
+        <v>9999</v>
+      </c>
+      <c r="J43" s="5">
+        <v>0</v>
+      </c>
+      <c r="K43" s="5">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="N43" s="3">
-        <v>1</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="L43" s="5">
+        <v>0</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="N43" s="5">
+        <v>1</v>
+      </c>
+      <c r="O43" s="5">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P43" s="5">
         <v>100</v>
       </c>
-      <c r="Q43" s="3">
-        <v>6</v>
-      </c>
-      <c r="R43" s="3" t="s">
+      <c r="Q43" s="5">
+        <v>6</v>
+      </c>
+      <c r="R43" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="T43" s="3">
+      <c r="S43" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="T43" s="5">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99758EA1-ED32-432F-8A8C-B81B4F6F5DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BDB290-DD8C-4011-A986-5D640A1D6B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3819,7 +3819,7 @@
         <v>100</v>
       </c>
       <c r="Q2" s="5">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R2" s="6" t="s">
         <v>137</v>
@@ -3882,7 +3882,7 @@
         <v>100</v>
       </c>
       <c r="Q3" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R3" s="4" t="s">
         <v>174</v>
@@ -3945,7 +3945,7 @@
         <v>100</v>
       </c>
       <c r="Q4" s="5">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R4" s="6" t="s">
         <v>138</v>
@@ -4008,7 +4008,7 @@
         <v>100</v>
       </c>
       <c r="Q5" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>177</v>
@@ -4071,7 +4071,7 @@
         <v>100</v>
       </c>
       <c r="Q6" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>158</v>
@@ -4134,7 +4134,7 @@
         <v>100</v>
       </c>
       <c r="Q7" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>231</v>
@@ -4197,7 +4197,7 @@
         <v>100</v>
       </c>
       <c r="Q8" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>258</v>
@@ -4260,7 +4260,7 @@
         <v>100</v>
       </c>
       <c r="Q9" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R9" s="4" t="s">
         <v>230</v>
@@ -4323,7 +4323,7 @@
         <v>100</v>
       </c>
       <c r="Q10" s="7">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R10" s="7" t="s">
         <v>111</v>
@@ -4386,7 +4386,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>244</v>
@@ -4449,7 +4449,7 @@
         <v>100</v>
       </c>
       <c r="Q12" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R12" s="4" t="s">
         <v>233</v>
@@ -4512,7 +4512,7 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R13" t="s">
         <v>228</v>
@@ -4575,7 +4575,7 @@
         <v>100</v>
       </c>
       <c r="Q14" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R14" s="4" t="s">
         <v>179</v>
@@ -4638,7 +4638,7 @@
         <v>100</v>
       </c>
       <c r="Q15" s="3">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="R15" s="4" t="s">
         <v>252</v>
@@ -4701,7 +4701,7 @@
         <v>100</v>
       </c>
       <c r="Q16" s="3">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="R16" s="4" t="s">
         <v>204</v>
@@ -4764,7 +4764,7 @@
         <v>100</v>
       </c>
       <c r="Q17" s="5">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="R17" s="5" t="s">
         <v>91</v>
@@ -4827,7 +4827,7 @@
         <v>100</v>
       </c>
       <c r="Q18" s="3">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="R18" s="4" t="s">
         <v>178</v>
@@ -4890,7 +4890,7 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R19" t="s">
         <v>227</v>
@@ -4953,7 +4953,7 @@
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R20" s="4" t="s">
         <v>175</v>
@@ -5016,7 +5016,7 @@
         <v>100</v>
       </c>
       <c r="Q21" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R21" s="4" t="s">
         <v>250</v>
@@ -5079,7 +5079,7 @@
         <v>100</v>
       </c>
       <c r="Q22" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R22" s="4" t="s">
         <v>251</v>
@@ -5142,7 +5142,7 @@
         <v>100</v>
       </c>
       <c r="Q23" s="3">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="R23" s="4" t="s">
         <v>234</v>
@@ -5205,7 +5205,7 @@
         <v>100</v>
       </c>
       <c r="Q24" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R24" s="4" t="s">
         <v>212</v>
@@ -5268,7 +5268,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R25" s="2" t="s">
         <v>130</v>
@@ -5331,7 +5331,7 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R26" s="2" t="s">
         <v>245</v>
@@ -5394,7 +5394,7 @@
         <v>100</v>
       </c>
       <c r="Q27" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R27" s="4" t="s">
         <v>240</v>
@@ -5457,7 +5457,7 @@
         <v>100</v>
       </c>
       <c r="Q28" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R28" s="4" t="s">
         <v>165</v>
@@ -5520,7 +5520,7 @@
         <v>100</v>
       </c>
       <c r="Q29" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R29" s="4" t="s">
         <v>263</v>
@@ -5583,7 +5583,7 @@
         <v>100</v>
       </c>
       <c r="Q30" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R30" s="4" t="s">
         <v>216</v>
@@ -5646,7 +5646,7 @@
         <v>100</v>
       </c>
       <c r="Q31" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R31" s="4" t="s">
         <v>215</v>
@@ -5709,7 +5709,7 @@
         <v>100</v>
       </c>
       <c r="Q32" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R32" s="4" t="s">
         <v>199</v>
@@ -5772,7 +5772,7 @@
         <v>100</v>
       </c>
       <c r="Q33" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R33" s="4" t="s">
         <v>201</v>
@@ -5835,7 +5835,7 @@
         <v>100</v>
       </c>
       <c r="Q34" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R34" s="4" t="s">
         <v>217</v>
@@ -5898,7 +5898,7 @@
         <v>100</v>
       </c>
       <c r="Q35" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R35" s="4" t="s">
         <v>211</v>
@@ -5961,7 +5961,7 @@
         <v>100</v>
       </c>
       <c r="Q36" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R36" s="4" t="s">
         <v>109</v>
@@ -6024,7 +6024,7 @@
         <v>100</v>
       </c>
       <c r="Q37" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R37" s="4" t="s">
         <v>254</v>
@@ -6087,7 +6087,7 @@
         <v>100</v>
       </c>
       <c r="Q38" s="7">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R38" s="9" t="s">
         <v>181</v>
@@ -6150,7 +6150,7 @@
         <v>100</v>
       </c>
       <c r="Q39" s="3">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="R39" s="3" t="s">
         <v>105</v>
@@ -6213,7 +6213,7 @@
         <v>100</v>
       </c>
       <c r="Q40" s="3">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="R40" s="3" t="s">
         <v>106</v>
@@ -6276,7 +6276,7 @@
         <v>100</v>
       </c>
       <c r="Q41" s="3">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>220</v>
@@ -6339,7 +6339,7 @@
         <v>100</v>
       </c>
       <c r="Q42" s="3">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>108</v>
@@ -6402,7 +6402,7 @@
         <v>100</v>
       </c>
       <c r="Q43" s="5">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R43" s="5" t="s">
         <v>107</v>
@@ -6465,7 +6465,7 @@
         <v>100</v>
       </c>
       <c r="Q44">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R44" s="2" t="s">
         <v>171</v>
@@ -6528,7 +6528,7 @@
         <v>100</v>
       </c>
       <c r="Q45">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R45" s="2" t="s">
         <v>247</v>
@@ -6591,7 +6591,7 @@
         <v>100</v>
       </c>
       <c r="Q46" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R46" s="4" t="s">
         <v>141</v>
@@ -6654,7 +6654,7 @@
         <v>100</v>
       </c>
       <c r="Q47" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R47" s="4" t="s">
         <v>207</v>
@@ -6717,7 +6717,7 @@
         <v>100</v>
       </c>
       <c r="Q48" s="3">
-        <v>6</v>
+        <v>480</v>
       </c>
       <c r="R48" s="4" t="s">
         <v>229</v>
@@ -6780,7 +6780,7 @@
         <v>100</v>
       </c>
       <c r="Q49" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R49" s="4" t="s">
         <v>221</v>
@@ -6843,7 +6843,7 @@
         <v>100</v>
       </c>
       <c r="Q50" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R50" s="4" t="s">
         <v>249</v>
@@ -6906,7 +6906,7 @@
         <v>100</v>
       </c>
       <c r="Q51" s="7">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R51" s="7" t="s">
         <v>43</v>
@@ -6969,7 +6969,7 @@
         <v>100</v>
       </c>
       <c r="Q52" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>98</v>
@@ -7032,7 +7032,7 @@
         <v>100</v>
       </c>
       <c r="Q53">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R53" t="s">
         <v>180</v>
@@ -7095,7 +7095,7 @@
         <v>100</v>
       </c>
       <c r="Q54" s="8">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R54" s="8" t="s">
         <v>49</v>
@@ -7158,7 +7158,7 @@
         <v>100</v>
       </c>
       <c r="Q55" s="8">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R55" s="8" t="s">
         <v>50</v>
@@ -7221,7 +7221,7 @@
         <v>100</v>
       </c>
       <c r="Q56" s="8">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R56" s="8" t="s">
         <v>36</v>
@@ -7284,7 +7284,7 @@
         <v>100</v>
       </c>
       <c r="Q57" s="8">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R57" s="8" t="s">
         <v>33</v>
@@ -7347,7 +7347,7 @@
         <v>100</v>
       </c>
       <c r="Q58" s="3">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="R58" s="4" t="s">
         <v>206</v>
@@ -7410,7 +7410,7 @@
         <v>100</v>
       </c>
       <c r="Q59" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R59" s="4" t="s">
         <v>236</v>
@@ -7473,7 +7473,7 @@
         <v>100</v>
       </c>
       <c r="Q60">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R60" s="2" t="s">
         <v>210</v>
@@ -7536,7 +7536,7 @@
         <v>100</v>
       </c>
       <c r="Q61" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="R61" s="4" t="s">
         <v>190</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BDB290-DD8C-4011-A986-5D640A1D6B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B824C203-94AF-4C22-9780-A02EA564E025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2145" yWindow="525" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="265">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -1359,39 +1359,6 @@
   </si>
   <si>
     <t>Chocolate_Philosophy</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>クッキーについて勉強することで、よりさくさく感の高いクッキーを焼けるようになる。
-ラスクにも効果がある。
-LV1: さくさく感+10
-LV2: さくさく感+20
-LV3: さくさく感+30
-LV4: さくさく感+40
-LV5: さくさく感+50
-LV6: さくさく感+60
-LV7: さくさく感+70
-LV8: さくさく感+80
-LV9: さくさく感+90
-LV10: さくさく感+100</t>
-    <rPh sb="8" eb="10">
-      <t>ベンキョウ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>カン</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1538,29 +1505,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>アイス水溶液に魔法をかけながら混ぜて、なめらかさを出す
-習得するだけでOK。
-LVに応じて、なめらかさをより出す。
-LV1: なめらかさ+10
-LV2: なめらかさ+20
-LV3: なめらかさ+30
-LV4: なめらかさ+40
-LV5: なめらかさ+50</t>
-    <rPh sb="25" eb="26">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>シュウトク</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>プランターに種を植えることができるようになる。</t>
     <rPh sb="6" eb="7">
       <t>タネ</t>
@@ -2865,48 +2809,6 @@
   </si>
   <si>
     <t>バタフライ・ルミネ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>星について勉強する。
-LVが上がるにつれて、星魔法の効果をアップする。
-星魔法を使ったときの、お菓子の食感・見た目が底上げされる。</t>
-    <rPh sb="0" eb="1">
-      <t>ホシ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ベンキョウ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="22" eb="25">
-      <t>ホシマホウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="37" eb="40">
-      <t>ホシマホウ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ショクカン</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ソコア</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3161,48 +3063,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>お菓子の周りに花火を飛ばした演出が可能になる。
-見た目を派手にすることができる。
-パーティに向けたお客さんに喜んでもらうことができる。</t>
-    <rPh sb="1" eb="3">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>マワ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハナビ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>エンシュツ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カノウ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ハデ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>キャク</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>ヨロコ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ほのおの煌めき</t>
     <rPh sb="4" eb="5">
       <t>キラ</t>
@@ -3258,6 +3118,248 @@
     </rPh>
     <rPh sb="61" eb="63">
       <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お菓子の周りに花火を飛ばした演出が可能になる。
+見た目を派手にすることができる。
+パーティに向けたお客さんに喜んでもらうことができる。
+チョコレートのお菓子など、火に弱いお菓子にかけると失敗する。</t>
+    <rPh sb="1" eb="3">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハナビ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ハデ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ヨロコ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>ヨワ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コンテストの時間を巻き戻す
+ただし、作っていた材料やお菓子は、巻き戻らない。</t>
+    <rPh sb="6" eb="8">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クッキーについて勉強することで、よりさくさく感の高いクッキーを焼けるようになる。
+ラスクにも効果がある。
+成功率も少し上昇する。
+LV1: さくさく感+10, 成功率+1%
+LV2: さくさく感+20, 成功率+2%
+LV3: さくさく感+30, 成功率+3%
+LV4: さくさく感+40, 成功率+4%
+LV5: さくさく感+50, 成功率+5%
+LV6: さくさく感+60, 成功率+6%
+LV7: さくさく感+70, 成功率+7%
+LV8: さくさく感+80, 成功率+8%
+LV9: さくさく感+90, 成功率+9%
+LV10: さくさく感+100, 成功率+10%</t>
+    <rPh sb="8" eb="10">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="53" eb="56">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="81" eb="84">
+      <t>セイコウリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>星について勉強する。
+LVが上がるにつれて、星魔法の効果をアップする。
+星魔法を使ったときの、お菓子の食感・見た目・成功率が底上げされる。
+また、星魔法使用時の時間も短縮する。</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>ホシマホウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="37" eb="40">
+      <t>ホシマホウ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ショクカン</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="59" eb="62">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ソコア</t>
+    </rPh>
+    <rPh sb="74" eb="77">
+      <t>ホシマホウ</t>
+    </rPh>
+    <rPh sb="77" eb="80">
+      <t>シヨウジ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アイス水溶液に魔法をかけながら混ぜて、なめらかさを出す
+習得するだけでOK。
+LVに応じて、なめらかさをより出す。
+また、アイスクリームの制作時、成功率アップ・制作時間を少し短縮する。
+LV1: なめらかさ+10, 成功率+2, 時間短縮+4%
+LV2: なめらかさ+20, 成功率+4, 時間短縮+8%
+LV3: なめらかさ+30, 成功率+6, 時間短縮+12%
+LV4: なめらかさ+40, 成功率+8, 時間短縮+16%
+LV5: なめらかさ+50, 成功率+10, 時間短縮+20%</t>
+    <rPh sb="25" eb="26">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>シュウトク</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="74" eb="77">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="81" eb="85">
+      <t>セイサクジカン</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>タンシュク</t>
+    </rPh>
+    <rPh sb="110" eb="113">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="119" eb="121">
+      <t>タンシュク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3347,7 +3449,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3374,6 +3476,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3885,7 +3990,7 @@
         <v>30</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>174</v>
+        <v>262</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>96</v>
@@ -3972,7 +4077,7 @@
         <v>173</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>157</v>
@@ -4011,7 +4116,7 @@
         <v>30</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>96</v>
@@ -4044,7 +4149,7 @@
         <v>2</v>
       </c>
       <c r="H6" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I6" s="3">
         <v>0</v>
@@ -4137,7 +4242,7 @@
         <v>30</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="S7" s="3" t="s">
         <v>96</v>
@@ -4158,19 +4263,19 @@
         <v>154</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
       </c>
       <c r="H8" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -4200,7 +4305,7 @@
         <v>30</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>96</v>
@@ -4233,7 +4338,7 @@
         <v>6</v>
       </c>
       <c r="H9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
@@ -4263,7 +4368,7 @@
         <v>30</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>63</v>
@@ -4287,7 +4392,7 @@
         <v>83</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>111</v>
@@ -4350,7 +4455,7 @@
         <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F11" t="s">
         <v>110</v>
@@ -4359,7 +4464,7 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -4389,7 +4494,7 @@
         <v>30</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="S11" t="s">
         <v>82</v>
@@ -4416,13 +4521,13 @@
         <v>139</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G12" s="3">
         <v>6</v>
       </c>
       <c r="H12" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I12" s="3">
         <v>0</v>
@@ -4452,7 +4557,7 @@
         <v>30</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>96</v>
@@ -4473,13 +4578,13 @@
         <v>66</v>
       </c>
       <c r="D13" t="s">
+        <v>224</v>
+      </c>
+      <c r="E13" t="s">
+        <v>255</v>
+      </c>
+      <c r="F13" t="s">
         <v>226</v>
-      </c>
-      <c r="E13" t="s">
-        <v>259</v>
-      </c>
-      <c r="F13" t="s">
-        <v>228</v>
       </c>
       <c r="G13">
         <v>6</v>
@@ -4515,7 +4620,7 @@
         <v>30</v>
       </c>
       <c r="R13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="S13" t="s">
         <v>96</v>
@@ -4542,7 +4647,7 @@
         <v>115</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G14" s="3">
         <v>2</v>
@@ -4578,7 +4683,7 @@
         <v>30</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>179</v>
+        <v>264</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>96</v>
@@ -4611,7 +4716,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -4641,7 +4746,7 @@
         <v>120</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>96</v>
@@ -4662,19 +4767,19 @@
         <v>151</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G16" s="3">
         <v>2</v>
       </c>
       <c r="H16" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I16" s="3">
         <v>0</v>
@@ -4704,7 +4809,7 @@
         <v>120</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>53</v>
@@ -4728,7 +4833,7 @@
         <v>92</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>91</v>
@@ -4800,7 +4905,7 @@
         <v>2</v>
       </c>
       <c r="H18" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I18" s="3">
         <v>0</v>
@@ -4830,7 +4935,7 @@
         <v>120</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>96</v>
@@ -4851,13 +4956,13 @@
         <v>37</v>
       </c>
       <c r="D19" t="s">
+        <v>223</v>
+      </c>
+      <c r="E19" t="s">
+        <v>256</v>
+      </c>
+      <c r="F19" t="s">
         <v>225</v>
-      </c>
-      <c r="E19" t="s">
-        <v>260</v>
-      </c>
-      <c r="F19" t="s">
-        <v>227</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -4893,7 +4998,7 @@
         <v>30</v>
       </c>
       <c r="R19" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="S19" t="s">
         <v>96</v>
@@ -4956,7 +5061,7 @@
         <v>30</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>96</v>
@@ -4989,7 +5094,7 @@
         <v>2</v>
       </c>
       <c r="H21" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" s="3">
         <v>0</v>
@@ -5019,7 +5124,7 @@
         <v>30</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>96</v>
@@ -5052,7 +5157,7 @@
         <v>4</v>
       </c>
       <c r="H22" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -5082,7 +5187,7 @@
         <v>30</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>17</v>
@@ -5106,7 +5211,7 @@
         <v>112</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>74</v>
@@ -5115,7 +5220,7 @@
         <v>4</v>
       </c>
       <c r="H23" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I23" s="3">
         <v>0</v>
@@ -5145,7 +5250,7 @@
         <v>60</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>96</v>
@@ -5208,7 +5313,7 @@
         <v>30</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>96</v>
@@ -5241,7 +5346,7 @@
         <v>4</v>
       </c>
       <c r="H25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5292,19 +5397,19 @@
         <v>38</v>
       </c>
       <c r="D26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E26" t="s">
+        <v>236</v>
+      </c>
+      <c r="F26" t="s">
         <v>237</v>
-      </c>
-      <c r="E26" t="s">
-        <v>238</v>
-      </c>
-      <c r="F26" t="s">
-        <v>239</v>
       </c>
       <c r="G26">
         <v>4</v>
       </c>
       <c r="H26">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -5334,7 +5439,7 @@
         <v>30</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="S26" t="s">
         <v>96</v>
@@ -5397,7 +5502,7 @@
         <v>30</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>96</v>
@@ -5421,7 +5526,7 @@
         <v>163</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>164</v>
@@ -5487,13 +5592,13 @@
         <v>22</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G29" s="3">
         <v>6</v>
       </c>
       <c r="H29" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -5523,7 +5628,7 @@
         <v>30</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>96</v>
@@ -5550,13 +5655,13 @@
         <v>23</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
       </c>
       <c r="H30" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I30" s="3">
         <v>0</v>
@@ -5586,7 +5691,7 @@
         <v>30</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="S30" s="3" t="s">
         <v>96</v>
@@ -5613,13 +5718,13 @@
         <v>135</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
       </c>
       <c r="H31" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I31" s="3">
         <v>1</v>
@@ -5649,7 +5754,7 @@
         <v>30</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="S31" s="3" t="s">
         <v>24</v>
@@ -5670,19 +5775,19 @@
         <v>39</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
       </c>
       <c r="H32" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I32" s="3">
         <v>1</v>
@@ -5712,7 +5817,7 @@
         <v>30</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>24</v>
@@ -5733,19 +5838,19 @@
         <v>39</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
       </c>
       <c r="H33" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I33" s="3">
         <v>1</v>
@@ -5775,7 +5880,7 @@
         <v>30</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>24</v>
@@ -5796,19 +5901,19 @@
         <v>39</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
       </c>
       <c r="H34" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I34" s="3">
         <v>0</v>
@@ -5838,7 +5943,7 @@
         <v>30</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S34" s="3" t="s">
         <v>24</v>
@@ -5859,19 +5964,19 @@
         <v>39</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
       </c>
       <c r="H35" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I35" s="3">
         <v>0</v>
@@ -5901,7 +6006,7 @@
         <v>30</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>24</v>
@@ -5934,7 +6039,7 @@
         <v>3</v>
       </c>
       <c r="H36" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I36" s="3">
         <v>0</v>
@@ -5991,13 +6096,13 @@
         <v>28</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G37" s="3">
         <v>3</v>
       </c>
       <c r="H37" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I37" s="3">
         <v>0</v>
@@ -6027,7 +6132,7 @@
         <v>30</v>
       </c>
       <c r="R37" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="S37" s="3" t="s">
         <v>96</v>
@@ -6090,7 +6195,7 @@
         <v>30</v>
       </c>
       <c r="R38" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="S38" s="7" t="s">
         <v>96</v>
@@ -6114,7 +6219,7 @@
         <v>72</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>105</v>
@@ -6123,7 +6228,7 @@
         <v>3</v>
       </c>
       <c r="H39" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I39" s="3">
         <v>0</v>
@@ -6186,7 +6291,7 @@
         <v>3</v>
       </c>
       <c r="H40" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I40" s="3">
         <v>0</v>
@@ -6237,19 +6342,19 @@
         <v>39</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="G41" s="3">
         <v>3</v>
       </c>
       <c r="H41" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I41" s="3">
         <v>0</v>
@@ -6279,7 +6384,7 @@
         <v>60</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>96</v>
@@ -6312,7 +6417,7 @@
         <v>3</v>
       </c>
       <c r="H42" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -6375,7 +6480,7 @@
         <v>3</v>
       </c>
       <c r="H43" s="5">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I43" s="5">
         <v>9999</v>
@@ -6429,7 +6534,7 @@
         <v>172</v>
       </c>
       <c r="E44" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F44" t="s">
         <v>170</v>
@@ -6438,7 +6543,7 @@
         <v>6</v>
       </c>
       <c r="H44">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -6495,7 +6600,7 @@
         <v>168</v>
       </c>
       <c r="F45" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G45">
         <v>6</v>
@@ -6531,7 +6636,7 @@
         <v>30</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="S45" t="s">
         <v>96</v>
@@ -6564,7 +6669,7 @@
         <v>6</v>
       </c>
       <c r="H46" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I46" s="3">
         <v>0</v>
@@ -6627,7 +6732,7 @@
         <v>6</v>
       </c>
       <c r="H47" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I47" s="3">
         <v>0</v>
@@ -6657,7 +6762,7 @@
         <v>30</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>96</v>
@@ -6681,7 +6786,7 @@
         <v>147</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>146</v>
@@ -6690,7 +6795,7 @@
         <v>6</v>
       </c>
       <c r="H48" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I48" s="3">
         <v>0</v>
@@ -6720,7 +6825,7 @@
         <v>480</v>
       </c>
       <c r="R48" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>96</v>
@@ -6741,19 +6846,19 @@
         <v>68</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G49" s="3">
         <v>6</v>
       </c>
       <c r="H49" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -6768,7 +6873,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
@@ -6783,7 +6888,7 @@
         <v>30</v>
       </c>
       <c r="R49" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>96</v>
@@ -6804,19 +6909,19 @@
         <v>68</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
       </c>
       <c r="H50" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I50" s="3">
         <v>0</v>
@@ -6846,7 +6951,7 @@
         <v>30</v>
       </c>
       <c r="R50" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>96</v>
@@ -6942,7 +7047,7 @@
         <v>6</v>
       </c>
       <c r="H52" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -7035,7 +7140,7 @@
         <v>30</v>
       </c>
       <c r="R53" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="S53" t="s">
         <v>96</v>
@@ -7068,7 +7173,7 @@
         <v>6</v>
       </c>
       <c r="H54" s="8">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I54" s="8">
         <v>0</v>
@@ -7107,7 +7212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:20" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="8">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -7131,7 +7236,7 @@
         <v>18</v>
       </c>
       <c r="H55" s="8">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="I55" s="8">
         <v>0</v>
@@ -7160,8 +7265,8 @@
       <c r="Q55" s="8">
         <v>30</v>
       </c>
-      <c r="R55" s="8" t="s">
-        <v>50</v>
+      <c r="R55" s="10" t="s">
+        <v>261</v>
       </c>
       <c r="S55" s="8" t="s">
         <v>96</v>
@@ -7194,7 +7299,7 @@
         <v>6</v>
       </c>
       <c r="H56" s="8">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="I56" s="8">
         <v>0</v>
@@ -7257,7 +7362,7 @@
         <v>6</v>
       </c>
       <c r="H57" s="8">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="I57" s="8">
         <v>0</v>
@@ -7320,7 +7425,7 @@
         <v>2</v>
       </c>
       <c r="H58" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -7350,7 +7455,7 @@
         <v>120</v>
       </c>
       <c r="R58" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>96</v>
@@ -7383,7 +7488,7 @@
         <v>6</v>
       </c>
       <c r="H59" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I59" s="3">
         <v>0</v>
@@ -7413,7 +7518,7 @@
         <v>30</v>
       </c>
       <c r="R59" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>96</v>
@@ -7446,7 +7551,7 @@
         <v>2</v>
       </c>
       <c r="H60">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -7476,7 +7581,7 @@
         <v>30</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="S60" t="s">
         <v>96</v>
@@ -7539,7 +7644,7 @@
         <v>30</v>
       </c>
       <c r="R61" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="S61" s="3" t="s">
         <v>96</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B824C203-94AF-4C22-9780-A02EA564E025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EED478-A914-4849-A2CB-8300AC5CD8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2145" yWindow="525" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2835" yWindow="1215" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EED478-A914-4849-A2CB-8300AC5CD8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525855EE-8EAE-4A93-B30F-2AB2CF73A4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2835" yWindow="1215" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="266">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -3360,6 +3360,55 @@
     </rPh>
     <rPh sb="119" eb="121">
       <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>草花のエキスを抽出し、ポーションを作る
+レベルが上がると成功率が上がるほか、一度にできあがる個数も増える。
+LV1: +5%成功Up, 個数1個
+LV2: +10%成功Up , 個数2個
+LV3: +15%成功Up , 個数3個
+LV4: +20%成功Up , 個数4個
+LV5: +25%成功Up , 個数5個</t>
+    <rPh sb="0" eb="2">
+      <t>クサバナ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>チュウシュツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t>コ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -7023,7 +7072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:20" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -7076,8 +7125,8 @@
       <c r="Q52" s="3">
         <v>30</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>98</v>
+      <c r="R52" s="4" t="s">
+        <v>265</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>96</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525855EE-8EAE-4A93-B30F-2AB2CF73A4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A82866-7FE7-4301-AC86-7E70E8F7EED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="1215" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -91,10 +91,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ルミナス・シュガー</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>クッキーをまとめて包装する。</t>
     <rPh sb="9" eb="11">
       <t>ホウソウ</t>
@@ -3410,6 +3406,10 @@
     <rPh sb="94" eb="95">
       <t>コ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ルミナス・シュガー</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3865,7 +3865,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -3895,10 +3895,10 @@
         <v>12</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
@@ -3910,16 +3910,16 @@
         <v>10</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3934,13 +3934,13 @@
         <v>13</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" s="5">
         <v>6</v>
@@ -3961,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N2" s="5">
         <v>1</v>
@@ -3976,10 +3976,10 @@
         <v>30</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T2" s="5">
         <v>0</v>
@@ -3994,16 +3994,16 @@
         <v>1002</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="G3" s="3">
         <v>6</v>
@@ -4024,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N3" s="3">
         <v>0</v>
@@ -4039,10 +4039,10 @@
         <v>30</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="3">
         <v>0</v>
@@ -4060,13 +4060,13 @@
         <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N4" s="5">
         <v>1</v>
@@ -4102,10 +4102,10 @@
         <v>30</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T4" s="5">
         <v>0</v>
@@ -4120,16 +4120,16 @@
         <v>1010</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G5" s="3">
         <v>6</v>
@@ -4150,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N5" s="3">
         <v>0</v>
@@ -4165,10 +4165,10 @@
         <v>30</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T5" s="3">
         <v>0</v>
@@ -4183,16 +4183,16 @@
         <v>1003</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="G6" s="3">
         <v>2</v>
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N6" s="3">
         <v>1</v>
@@ -4228,10 +4228,10 @@
         <v>30</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T6" s="3">
         <v>0</v>
@@ -4246,16 +4246,16 @@
         <v>1004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="G7" s="3">
         <v>2</v>
@@ -4276,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N7" s="3">
         <v>0</v>
@@ -4291,10 +4291,10 @@
         <v>30</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T7" s="3">
         <v>0</v>
@@ -4309,16 +4309,16 @@
         <v>1006</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
@@ -4339,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N8" s="3">
         <v>1</v>
@@ -4354,10 +4354,10 @@
         <v>30</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -4372,16 +4372,16 @@
         <v>1006</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G9" s="3">
         <v>6</v>
@@ -4402,7 +4402,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N9" s="3">
         <v>1</v>
@@ -4417,10 +4417,10 @@
         <v>30</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T9" s="3">
         <v>1</v>
@@ -4435,16 +4435,16 @@
         <v>1007</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G10" s="7">
         <v>6</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N10" s="7">
         <v>1</v>
@@ -4480,10 +4480,10 @@
         <v>30</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T10" s="7">
         <v>0</v>
@@ -4498,16 +4498,16 @@
         <v>1008</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G11">
         <v>6</v>
@@ -4528,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -4543,10 +4543,10 @@
         <v>30</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="S11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T11">
         <v>1</v>
@@ -4561,16 +4561,16 @@
         <v>1009</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G12" s="3">
         <v>6</v>
@@ -4591,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N12" s="3">
         <v>1</v>
@@ -4606,10 +4606,10 @@
         <v>30</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T12" s="3">
         <v>0</v>
@@ -4624,16 +4624,16 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G13">
         <v>6</v>
@@ -4654,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -4669,10 +4669,10 @@
         <v>30</v>
       </c>
       <c r="R13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="S13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T13">
         <v>0</v>
@@ -4687,16 +4687,16 @@
         <v>2004</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G14" s="3">
         <v>2</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -4732,10 +4732,10 @@
         <v>30</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -4750,16 +4750,16 @@
         <v>2001</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="G15" s="3">
         <v>2</v>
@@ -4780,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N15" s="3">
         <v>1</v>
@@ -4795,10 +4795,10 @@
         <v>120</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -4813,16 +4813,16 @@
         <v>2001</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G16" s="3">
         <v>2</v>
@@ -4843,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N16" s="3">
         <v>1</v>
@@ -4858,10 +4858,10 @@
         <v>120</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T16" s="3">
         <v>2</v>
@@ -4876,16 +4876,16 @@
         <v>2002</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G17" s="5">
         <v>2</v>
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N17" s="5">
         <v>1</v>
@@ -4921,10 +4921,10 @@
         <v>120</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T17" s="5">
         <v>0</v>
@@ -4939,16 +4939,16 @@
         <v>2003</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G18" s="3">
         <v>2</v>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N18" s="3">
         <v>1</v>
@@ -4984,10 +4984,10 @@
         <v>120</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T18" s="3">
         <v>0</v>
@@ -5002,16 +5002,16 @@
         <v>2003</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N19">
         <v>1</v>
@@ -5047,10 +5047,10 @@
         <v>30</v>
       </c>
       <c r="R19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T19">
         <v>0</v>
@@ -5065,16 +5065,16 @@
         <v>3006</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
@@ -5095,7 +5095,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -5110,10 +5110,10 @@
         <v>30</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -5128,16 +5128,16 @@
         <v>3001</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>14</v>
+        <v>265</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" s="3">
         <v>2</v>
@@ -5158,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N21" s="3">
         <v>1</v>
@@ -5173,10 +5173,10 @@
         <v>30</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T21" s="3">
         <v>0</v>
@@ -5191,16 +5191,16 @@
         <v>3002</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="G22" s="3">
         <v>4</v>
@@ -5221,7 +5221,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N22" s="3">
         <v>1</v>
@@ -5236,10 +5236,10 @@
         <v>30</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T22" s="3">
         <v>3</v>
@@ -5254,16 +5254,16 @@
         <v>3003</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G23" s="3">
         <v>4</v>
@@ -5284,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N23" s="3">
         <v>1</v>
@@ -5299,10 +5299,10 @@
         <v>60</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T23" s="3">
         <v>0</v>
@@ -5317,16 +5317,16 @@
         <v>3004</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="G24" s="3">
         <v>4</v>
@@ -5347,7 +5347,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -5362,10 +5362,10 @@
         <v>30</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -5380,16 +5380,16 @@
         <v>3005</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G25">
         <v>4</v>
@@ -5410,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -5425,10 +5425,10 @@
         <v>30</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T25">
         <v>0</v>
@@ -5443,16 +5443,16 @@
         <v>3005</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E26" t="s">
         <v>235</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>236</v>
-      </c>
-      <c r="F26" t="s">
-        <v>237</v>
       </c>
       <c r="G26">
         <v>4</v>
@@ -5473,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -5488,10 +5488,10 @@
         <v>30</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="S26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T26">
         <v>0</v>
@@ -5506,16 +5506,16 @@
         <v>4010</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="G27" s="3">
         <v>6</v>
@@ -5536,7 +5536,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N27" s="3">
         <v>0</v>
@@ -5551,10 +5551,10 @@
         <v>30</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T27" s="3">
         <v>0</v>
@@ -5569,16 +5569,16 @@
         <v>4011</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="G28" s="3">
         <v>6</v>
@@ -5599,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N28" s="3">
         <v>0</v>
@@ -5614,10 +5614,10 @@
         <v>30</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T28" s="3">
         <v>0</v>
@@ -5632,16 +5632,16 @@
         <v>4001</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G29" s="3">
         <v>6</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N29" s="3">
         <v>1</v>
@@ -5677,10 +5677,10 @@
         <v>30</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -5695,16 +5695,16 @@
         <v>4002</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -5725,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N30" s="3">
         <v>1</v>
@@ -5740,10 +5740,10 @@
         <v>30</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T30" s="3">
         <v>0</v>
@@ -5758,16 +5758,16 @@
         <v>4010</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="F31" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -5788,7 +5788,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N31" s="3">
         <v>1</v>
@@ -5803,10 +5803,10 @@
         <v>30</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
@@ -5821,16 +5821,16 @@
         <v>4011</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N32" s="3">
         <v>1</v>
@@ -5866,10 +5866,10 @@
         <v>30</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T32" s="3">
         <v>1</v>
@@ -5884,16 +5884,16 @@
         <v>4012</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N33" s="3">
         <v>1</v>
@@ -5929,10 +5929,10 @@
         <v>30</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T33" s="3">
         <v>1</v>
@@ -5947,16 +5947,16 @@
         <v>4012</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -5977,7 +5977,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N34" s="3">
         <v>1</v>
@@ -5992,10 +5992,10 @@
         <v>30</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T34" s="3">
         <v>1</v>
@@ -6010,16 +6010,16 @@
         <v>4012</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -6040,7 +6040,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N35" s="3">
         <v>1</v>
@@ -6055,10 +6055,10 @@
         <v>30</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T35" s="3">
         <v>1</v>
@@ -6073,16 +6073,16 @@
         <v>4003</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G36" s="3">
         <v>3</v>
@@ -6103,7 +6103,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N36" s="3">
         <v>1</v>
@@ -6118,10 +6118,10 @@
         <v>30</v>
       </c>
       <c r="R36" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T36" s="3">
         <v>0</v>
@@ -6136,16 +6136,16 @@
         <v>4004</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G37" s="3">
         <v>3</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N37" s="3">
         <v>1</v>
@@ -6181,10 +6181,10 @@
         <v>30</v>
       </c>
       <c r="R37" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T37" s="3">
         <v>0</v>
@@ -6199,16 +6199,16 @@
         <v>4005</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E38" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="G38" s="7">
         <v>12</v>
@@ -6229,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N38" s="7">
         <v>1</v>
@@ -6244,10 +6244,10 @@
         <v>30</v>
       </c>
       <c r="R38" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="S38" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T38" s="7">
         <v>0</v>
@@ -6262,16 +6262,16 @@
         <v>4006</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G39" s="3">
         <v>3</v>
@@ -6292,7 +6292,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N39" s="3">
         <v>1</v>
@@ -6307,10 +6307,10 @@
         <v>60</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T39" s="3">
         <v>0</v>
@@ -6325,16 +6325,16 @@
         <v>4007</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G40" s="3">
         <v>3</v>
@@ -6355,7 +6355,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N40" s="3">
         <v>1</v>
@@ -6370,10 +6370,10 @@
         <v>60</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T40" s="3">
         <v>0</v>
@@ -6388,16 +6388,16 @@
         <v>4007</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="F41" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="G41" s="3">
         <v>3</v>
@@ -6418,7 +6418,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N41" s="3">
         <v>1</v>
@@ -6433,10 +6433,10 @@
         <v>60</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T41" s="3">
         <v>0</v>
@@ -6451,16 +6451,16 @@
         <v>4008</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G42" s="3">
         <v>3</v>
@@ -6481,7 +6481,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N42" s="3">
         <v>1</v>
@@ -6496,10 +6496,10 @@
         <v>60</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -6514,16 +6514,16 @@
         <v>4009</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G43" s="5">
         <v>3</v>
@@ -6544,7 +6544,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N43" s="5">
         <v>1</v>
@@ -6559,10 +6559,10 @@
         <v>30</v>
       </c>
       <c r="R43" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="S43" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T43" s="5">
         <v>0</v>
@@ -6577,16 +6577,16 @@
         <v>4013</v>
       </c>
       <c r="C44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E44" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F44" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G44">
         <v>6</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N44">
         <v>1</v>
@@ -6622,10 +6622,10 @@
         <v>30</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T44">
         <v>0</v>
@@ -6640,16 +6640,16 @@
         <v>5004</v>
       </c>
       <c r="C45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E45" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F45" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G45">
         <v>6</v>
@@ -6670,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N45">
         <v>0</v>
@@ -6685,10 +6685,10 @@
         <v>30</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="S45" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T45">
         <v>0</v>
@@ -6703,16 +6703,16 @@
         <v>5001</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G46" s="3">
         <v>6</v>
@@ -6733,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N46" s="3">
         <v>1</v>
@@ -6748,10 +6748,10 @@
         <v>30</v>
       </c>
       <c r="R46" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T46" s="3">
         <v>0</v>
@@ -6766,16 +6766,16 @@
         <v>5002</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E47" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="G47" s="3">
         <v>6</v>
@@ -6796,7 +6796,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N47" s="3">
         <v>1</v>
@@ -6811,10 +6811,10 @@
         <v>30</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -6829,16 +6829,16 @@
         <v>5003</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G48" s="3">
         <v>6</v>
@@ -6859,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N48" s="3">
         <v>1</v>
@@ -6874,10 +6874,10 @@
         <v>480</v>
       </c>
       <c r="R48" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -6892,16 +6892,16 @@
         <v>5005</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G49" s="3">
         <v>6</v>
@@ -6922,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
@@ -6937,10 +6937,10 @@
         <v>30</v>
       </c>
       <c r="R49" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -6955,16 +6955,16 @@
         <v>5006</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
@@ -6985,7 +6985,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N50" s="3">
         <v>1</v>
@@ -7000,10 +7000,10 @@
         <v>30</v>
       </c>
       <c r="R50" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T50" s="3">
         <v>0</v>
@@ -7018,16 +7018,16 @@
         <v>6001</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G51" s="7">
         <v>6</v>
@@ -7048,7 +7048,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N51" s="7">
         <v>1</v>
@@ -7063,10 +7063,10 @@
         <v>30</v>
       </c>
       <c r="R51" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T51" s="7">
         <v>0</v>
@@ -7081,16 +7081,16 @@
         <v>6002</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G52" s="3">
         <v>6</v>
@@ -7111,7 +7111,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N52" s="3">
         <v>1</v>
@@ -7126,10 +7126,10 @@
         <v>30</v>
       </c>
       <c r="R52" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -7144,16 +7144,16 @@
         <v>6003</v>
       </c>
       <c r="C53" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D53" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E53" t="s">
+        <v>41</v>
+      </c>
+      <c r="F53" t="s">
         <v>42</v>
-      </c>
-      <c r="F53" t="s">
-        <v>43</v>
       </c>
       <c r="G53">
         <v>6</v>
@@ -7174,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N53">
         <v>1</v>
@@ -7189,10 +7189,10 @@
         <v>30</v>
       </c>
       <c r="R53" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="S53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T53">
         <v>0</v>
@@ -7207,16 +7207,16 @@
         <v>7001</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D54" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>49</v>
       </c>
       <c r="G54" s="8">
         <v>6</v>
@@ -7237,7 +7237,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N54" s="8">
         <v>1</v>
@@ -7252,10 +7252,10 @@
         <v>30</v>
       </c>
       <c r="R54" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S54" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T54" s="8">
         <v>0</v>
@@ -7270,16 +7270,16 @@
         <v>7002</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G55" s="8">
         <v>18</v>
@@ -7300,7 +7300,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N55" s="8">
         <v>1</v>
@@ -7315,10 +7315,10 @@
         <v>30</v>
       </c>
       <c r="R55" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="S55" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T55" s="8">
         <v>0</v>
@@ -7333,16 +7333,16 @@
         <v>8001</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G56" s="8">
         <v>6</v>
@@ -7363,7 +7363,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N56" s="8">
         <v>1</v>
@@ -7378,10 +7378,10 @@
         <v>30</v>
       </c>
       <c r="R56" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S56" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T56" s="8">
         <v>0</v>
@@ -7396,16 +7396,16 @@
         <v>8002</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G57" s="8">
         <v>6</v>
@@ -7426,7 +7426,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N57" s="8">
         <v>1</v>
@@ -7441,10 +7441,10 @@
         <v>30</v>
       </c>
       <c r="R57" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S57" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T57" s="8">
         <v>0</v>
@@ -7459,16 +7459,16 @@
         <v>9001</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G58" s="3">
         <v>2</v>
@@ -7489,7 +7489,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N58" s="3">
         <v>1</v>
@@ -7504,10 +7504,10 @@
         <v>120</v>
       </c>
       <c r="R58" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -7522,16 +7522,16 @@
         <v>9002</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E59" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="G59" s="3">
         <v>6</v>
@@ -7552,7 +7552,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N59" s="3">
         <v>1</v>
@@ -7567,10 +7567,10 @@
         <v>30</v>
       </c>
       <c r="R59" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
@@ -7585,16 +7585,16 @@
         <v>9004</v>
       </c>
       <c r="C60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D60" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E60" t="s">
+        <v>98</v>
+      </c>
+      <c r="F60" t="s">
         <v>99</v>
-      </c>
-      <c r="F60" t="s">
-        <v>100</v>
       </c>
       <c r="G60">
         <v>2</v>
@@ -7615,7 +7615,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N60">
         <v>1</v>
@@ -7630,10 +7630,10 @@
         <v>30</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T60">
         <v>0</v>
@@ -7648,16 +7648,16 @@
         <v>9003</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G61" s="3">
         <v>6</v>
@@ -7678,7 +7678,7 @@
         <v>1</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N61" s="3">
         <v>1</v>
@@ -7693,10 +7693,10 @@
         <v>30</v>
       </c>
       <c r="R61" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A82866-7FE7-4301-AC86-7E70E8F7EED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91A60B6-3CBE-4F69-9145-ED1AF94DD728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="267">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -3410,6 +3410,10 @@
   </si>
   <si>
     <t>ルミナス・シュガー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Abra</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4489,66 +4493,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11">
+    <row r="11" spans="1:20" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>1008</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="3">
         <v>6</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="3">
         <v>8</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
         <v>2</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11" t="s">
-        <v>95</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11">
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N11" s="3">
+        <v>1</v>
+      </c>
+      <c r="O11" s="3">
         <v>9</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="3">
         <v>100</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="3">
         <v>30</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="R11" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="S11" t="s">
+      <c r="S11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="3">
         <v>1</v>
       </c>
     </row>
@@ -4615,66 +4619,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13">
+    <row r="13" spans="1:20" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="7">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="7">
         <v>1009</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="7">
         <v>6</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="7">
         <v>20</v>
       </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
+      <c r="I13" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0</v>
+      </c>
+      <c r="K13" s="7">
         <v>3</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13" t="s">
-        <v>95</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13">
+      <c r="L13" s="7">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="N13" s="7">
+        <v>1</v>
+      </c>
+      <c r="O13" s="7">
         <v>9</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="7">
         <v>100</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="7">
         <v>30</v>
       </c>
-      <c r="R13" t="s">
+      <c r="R13" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="S13" t="s">
-        <v>95</v>
-      </c>
-      <c r="T13">
+      <c r="S13" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="T13" s="7">
         <v>0</v>
       </c>
     </row>
@@ -4993,66 +4997,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19">
+    <row r="19" spans="1:20" s="7" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="7">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="7">
         <v>2003</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="7">
         <v>2</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="7">
         <v>20</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
+      <c r="I19" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J19" s="7">
+        <v>0</v>
+      </c>
+      <c r="K19" s="7">
         <v>5</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19" t="s">
-        <v>95</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-      <c r="P19">
+      <c r="L19" s="7">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="N19" s="7">
+        <v>1</v>
+      </c>
+      <c r="O19" s="7">
+        <v>1</v>
+      </c>
+      <c r="P19" s="7">
         <v>100</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="7">
         <v>30</v>
       </c>
-      <c r="R19" t="s">
+      <c r="R19" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="S19" t="s">
-        <v>95</v>
-      </c>
-      <c r="T19">
+      <c r="S19" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="T19" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5371,66 +5375,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25">
+    <row r="25" spans="1:20" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="7">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="7">
         <v>3005</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="7">
         <v>4</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="7">
         <v>20</v>
       </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
+      <c r="I25" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J25" s="7">
+        <v>0</v>
+      </c>
+      <c r="K25" s="7">
         <v>5</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" t="s">
-        <v>95</v>
-      </c>
-      <c r="N25">
-        <v>1</v>
-      </c>
-      <c r="O25">
+      <c r="L25" s="7">
+        <v>0</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="N25" s="7">
+        <v>1</v>
+      </c>
+      <c r="O25" s="7">
         <v>2</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="7">
         <v>100</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="7">
         <v>30</v>
       </c>
-      <c r="R25" s="2" t="s">
+      <c r="R25" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="S25" t="s">
-        <v>95</v>
-      </c>
-      <c r="T25">
+      <c r="S25" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="T25" s="7">
         <v>0</v>
       </c>
     </row>
@@ -6568,66 +6572,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44">
+    <row r="44" spans="1:20" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="7">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="7">
         <v>4013</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="7">
         <v>6</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="7">
         <v>30</v>
       </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
+      <c r="I44" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J44" s="7">
+        <v>0</v>
+      </c>
+      <c r="K44" s="7">
         <v>5</v>
       </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44" t="s">
-        <v>95</v>
-      </c>
-      <c r="N44">
-        <v>1</v>
-      </c>
-      <c r="O44">
+      <c r="L44" s="7">
+        <v>0</v>
+      </c>
+      <c r="M44" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="N44" s="7">
+        <v>1</v>
+      </c>
+      <c r="O44" s="7">
         <v>3</v>
       </c>
-      <c r="P44">
+      <c r="P44" s="7">
         <v>100</v>
       </c>
-      <c r="Q44">
+      <c r="Q44" s="7">
         <v>30</v>
       </c>
-      <c r="R44" s="2" t="s">
+      <c r="R44" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="S44" t="s">
-        <v>95</v>
-      </c>
-      <c r="T44">
+      <c r="S44" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="T44" s="7">
         <v>0</v>
       </c>
     </row>
@@ -7609,13 +7613,13 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>95</v>
+        <v>266</v>
       </c>
       <c r="N60">
         <v>1</v>
@@ -7627,7 +7631,7 @@
         <v>100</v>
       </c>
       <c r="Q60">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="R60" s="2" t="s">
         <v>207</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91A60B6-3CBE-4F69-9145-ED1AF94DD728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0F3432-1E5A-4CCB-82C7-039023A42B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1905" yWindow="1185" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0F3432-1E5A-4CCB-82C7-039023A42B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3E2A14-5B1A-4303-A544-114815AEF65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1185" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="900" yWindow="690" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2367,51 +2367,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>豆類を焼いて香りや味を出す。豆殻も一緒に取る。
-派生：
-LV1でテンパリング習得可</t>
-    <rPh sb="0" eb="1">
-      <t>マメ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>ルイ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>カオ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>アジ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>マメ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>カラ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>イッショ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ハセイ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>シュウトク</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>焼く際に、温度を細かく指定できる。
 材料選択後、
 クッキーの場合、時間と温度を決めることができる画面になる。
@@ -2744,43 +2699,6 @@
   </si>
   <si>
     <t>Rainbow_Rain</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>カカオマスの温度調整をし、なめらかにする。
-温度調節はかなり繊細な作業なので、慎重に。
-３つゲージがでてきて、
-各ゲージを赤い点になるべく近づけてストップ。</t>
-    <rPh sb="6" eb="10">
-      <t>オンドチョウセイ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>オンド</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>チョウセツ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>センサイ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>サギョウ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>シンチョウ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>アカ</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>テン</t>
-    </rPh>
-    <rPh sb="71" eb="72">
-      <t>チカ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3118,64 +3036,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>お菓子の周りに花火を飛ばした演出が可能になる。
-見た目を派手にすることができる。
-パーティに向けたお客さんに喜んでもらうことができる。
-チョコレートのお菓子など、火に弱いお菓子にかけると失敗する。</t>
-    <rPh sb="1" eb="3">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>マワ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハナビ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>エンシュツ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カノウ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ハデ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>キャク</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>ヨロコ</t>
-    </rPh>
-    <rPh sb="78" eb="80">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="83" eb="84">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="85" eb="86">
-      <t>ヨワ</t>
-    </rPh>
-    <rPh sb="88" eb="90">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="95" eb="97">
-      <t>シッパイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>コンテストの時間を巻き戻す
 ただし、作っていた材料やお菓子は、巻き戻らない。</t>
     <rPh sb="6" eb="8">
@@ -3414,6 +3274,182 @@
   </si>
   <si>
     <t>Abra</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>豆類を焼いて香りや味を出す。豆殻も一緒に取る。
+一度に多く焼くと、その分だけ味も凝縮される。
+派生：
+LV1でテンパリング習得可</t>
+    <rPh sb="0" eb="1">
+      <t>マメ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ルイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>マメ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カラ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イッショ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ギョウシュク</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ハセイ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>シュウトク</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>カカオマスの温度調整をし、なめらかにする。
+温度調節はかなり繊細な作業なので、慎重に。
+３つゲージがでてきて、
+各ゲージを赤い点になるべく近づけてストップ。
+LVを上げると、少しゆっくりにできる。</t>
+    <rPh sb="6" eb="10">
+      <t>オンドチョウセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>オンド</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>チョウセツ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>センサイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>シンチョウ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="90" eb="91">
+      <t>スコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お菓子の周りに花火を飛ばした演出が可能になる。
+LVが上がると効果が高まる。
+見た目を派手にすることができる。
+パーティに向けたお客さんに喜んでもらうことができる。
+チョコレートのお菓子など、火に弱いお菓子にかけると失敗する。</t>
+    <rPh sb="1" eb="3">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハナビ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ハデ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ヨロコ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="98" eb="99">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>ヨワ</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>シッパイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4043,7 +4079,7 @@
         <v>30</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>95</v>
@@ -4295,7 +4331,7 @@
         <v>30</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S7" s="3" t="s">
         <v>95</v>
@@ -4316,13 +4352,13 @@
         <v>153</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>253</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
@@ -4358,7 +4394,7 @@
         <v>30</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>95</v>
@@ -4421,7 +4457,7 @@
         <v>30</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>62</v>
@@ -4547,7 +4583,7 @@
         <v>30</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>81</v>
@@ -4574,7 +4610,7 @@
         <v>138</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G12" s="3">
         <v>6</v>
@@ -4610,7 +4646,7 @@
         <v>30</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>95</v>
@@ -4634,7 +4670,7 @@
         <v>223</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>225</v>
@@ -4736,7 +4772,7 @@
         <v>30</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>95</v>
@@ -4799,7 +4835,7 @@
         <v>120</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>95</v>
@@ -5012,7 +5048,7 @@
         <v>222</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>224</v>
@@ -5138,7 +5174,7 @@
         <v>16</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>15</v>
@@ -5177,7 +5213,7 @@
         <v>30</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>95</v>
@@ -5240,7 +5276,7 @@
         <v>30</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>16</v>
@@ -5264,7 +5300,7 @@
         <v>111</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>73</v>
@@ -5303,7 +5339,7 @@
         <v>60</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>95</v>
@@ -5450,13 +5486,13 @@
         <v>37</v>
       </c>
       <c r="D26" t="s">
+        <v>233</v>
+      </c>
+      <c r="E26" t="s">
         <v>234</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>235</v>
-      </c>
-      <c r="F26" t="s">
-        <v>236</v>
       </c>
       <c r="G26">
         <v>4</v>
@@ -5492,7 +5528,7 @@
         <v>30</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="S26" t="s">
         <v>95</v>
@@ -5555,7 +5591,7 @@
         <v>30</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>95</v>
@@ -5579,7 +5615,7 @@
         <v>162</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>163</v>
@@ -5645,7 +5681,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G29" s="3">
         <v>6</v>
@@ -5681,7 +5717,7 @@
         <v>30</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>95</v>
@@ -6149,7 +6185,7 @@
         <v>27</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G37" s="3">
         <v>3</v>
@@ -6185,7 +6221,7 @@
         <v>30</v>
       </c>
       <c r="R37" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="S37" s="3" t="s">
         <v>95</v>
@@ -6587,7 +6623,7 @@
         <v>171</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>169</v>
@@ -6689,7 +6725,7 @@
         <v>30</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="S45" t="s">
         <v>95</v>
@@ -6926,7 +6962,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
@@ -6962,13 +6998,13 @@
         <v>67</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
@@ -7004,7 +7040,7 @@
         <v>30</v>
       </c>
       <c r="R50" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>95</v>
@@ -7130,7 +7166,7 @@
         <v>30</v>
       </c>
       <c r="R52" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>95</v>
@@ -7319,7 +7355,7 @@
         <v>30</v>
       </c>
       <c r="R55" s="10" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="S55" s="8" t="s">
         <v>95</v>
@@ -7571,7 +7607,7 @@
         <v>30</v>
       </c>
       <c r="R59" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>95</v>
@@ -7619,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="N60">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3E2A14-5B1A-4303-A544-114815AEF65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F363CC-9C18-4039-BB5F-B97215788ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="690" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1575" yWindow="1245" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1186,22 +1186,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>お菓子の見た目をきれいに整える。</t>
-    <rPh sb="1" eb="3">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>トトノ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Nappe</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1355,43 +1339,6 @@
   </si>
   <si>
     <t>Chocolate_Philosophy</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>お菓子の見た目をきれいに整える。
-LVがあがると、見た目の美しさもアップ！！
-LV1: お菓子の見た目+10
-LV2: お菓子の見た目+20
-LV3: お菓子の見た目+30
-LV4: お菓子の見た目+40
-LV5: お菓子の見た目+50</t>
-    <rPh sb="1" eb="3">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>トトノ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>ウツク</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="49" eb="50">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>メ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3449,6 +3396,65 @@
     </rPh>
     <rPh sb="110" eb="112">
       <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>光り系のお菓子のキラキラ感を強める。</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツヨ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>光り魔法の効果を高めて、光り系のお菓子のキラキラ感を強くする。
+LVがあがると、効果をアップする。
+LV1: 光のおかし品質+6%
+LV2: 光のおかし品質+12%
+LV3: 光のおかし品質+18%
+LV4: 光のおかし品質+24%
+LV5: 光のおかし品質+30%</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ヒンシツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4079,7 +4085,7 @@
         <v>30</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>95</v>
@@ -4163,10 +4169,10 @@
         <v>149</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>156</v>
@@ -4205,7 +4211,7 @@
         <v>30</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>95</v>
@@ -4331,7 +4337,7 @@
         <v>30</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="S7" s="3" t="s">
         <v>95</v>
@@ -4352,13 +4358,13 @@
         <v>153</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>251</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
@@ -4394,7 +4400,7 @@
         <v>30</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>95</v>
@@ -4457,7 +4463,7 @@
         <v>30</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>62</v>
@@ -4481,7 +4487,7 @@
         <v>82</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>110</v>
@@ -4544,7 +4550,7 @@
         <v>83</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>109</v>
@@ -4583,7 +4589,7 @@
         <v>30</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>81</v>
@@ -4610,7 +4616,7 @@
         <v>138</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G12" s="3">
         <v>6</v>
@@ -4646,7 +4652,7 @@
         <v>30</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>95</v>
@@ -4667,13 +4673,13 @@
         <v>65</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>225</v>
       </c>
       <c r="G13" s="7">
         <v>6</v>
@@ -4709,7 +4715,7 @@
         <v>30</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="S13" s="7" t="s">
         <v>95</v>
@@ -4736,7 +4742,7 @@
         <v>114</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G14" s="3">
         <v>2</v>
@@ -4772,7 +4778,7 @@
         <v>30</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>95</v>
@@ -4835,7 +4841,7 @@
         <v>120</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>95</v>
@@ -4856,13 +4862,13 @@
         <v>150</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G16" s="3">
         <v>2</v>
@@ -4898,7 +4904,7 @@
         <v>120</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>52</v>
@@ -4922,7 +4928,7 @@
         <v>91</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>90</v>
@@ -5024,7 +5030,7 @@
         <v>120</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>95</v>
@@ -5045,13 +5051,13 @@
         <v>36</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>222</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>224</v>
       </c>
       <c r="G19" s="7">
         <v>2</v>
@@ -5087,7 +5093,7 @@
         <v>30</v>
       </c>
       <c r="R19" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="S19" s="7" t="s">
         <v>95</v>
@@ -5108,13 +5114,13 @@
         <v>147</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>158</v>
+        <v>265</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
@@ -5150,7 +5156,7 @@
         <v>30</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>173</v>
+        <v>266</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>95</v>
@@ -5174,7 +5180,7 @@
         <v>16</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>15</v>
@@ -5213,7 +5219,7 @@
         <v>30</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>95</v>
@@ -5276,7 +5282,7 @@
         <v>30</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>16</v>
@@ -5300,7 +5306,7 @@
         <v>111</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>73</v>
@@ -5339,7 +5345,7 @@
         <v>60</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>95</v>
@@ -5402,7 +5408,7 @@
         <v>30</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>95</v>
@@ -5486,13 +5492,13 @@
         <v>37</v>
       </c>
       <c r="D26" t="s">
+        <v>231</v>
+      </c>
+      <c r="E26" t="s">
+        <v>232</v>
+      </c>
+      <c r="F26" t="s">
         <v>233</v>
-      </c>
-      <c r="E26" t="s">
-        <v>234</v>
-      </c>
-      <c r="F26" t="s">
-        <v>235</v>
       </c>
       <c r="G26">
         <v>4</v>
@@ -5528,7 +5534,7 @@
         <v>30</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="S26" t="s">
         <v>95</v>
@@ -5549,13 +5555,13 @@
         <v>38</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="G27" s="3">
         <v>6</v>
@@ -5591,7 +5597,7 @@
         <v>30</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>95</v>
@@ -5612,13 +5618,13 @@
         <v>38</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="G28" s="3">
         <v>6</v>
@@ -5654,7 +5660,7 @@
         <v>30</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>95</v>
@@ -5681,7 +5687,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G29" s="3">
         <v>6</v>
@@ -5717,7 +5723,7 @@
         <v>30</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>95</v>
@@ -5744,7 +5750,7 @@
         <v>22</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -5780,7 +5786,7 @@
         <v>30</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="S30" s="3" t="s">
         <v>95</v>
@@ -5807,7 +5813,7 @@
         <v>134</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -5843,7 +5849,7 @@
         <v>30</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="S31" s="3" t="s">
         <v>23</v>
@@ -5864,13 +5870,13 @@
         <v>38</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -5906,7 +5912,7 @@
         <v>30</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>23</v>
@@ -5927,13 +5933,13 @@
         <v>38</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -5969,7 +5975,7 @@
         <v>30</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>23</v>
@@ -5990,13 +5996,13 @@
         <v>38</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -6032,7 +6038,7 @@
         <v>30</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="S34" s="3" t="s">
         <v>23</v>
@@ -6053,13 +6059,13 @@
         <v>38</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -6095,7 +6101,7 @@
         <v>30</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>23</v>
@@ -6185,7 +6191,7 @@
         <v>27</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G37" s="3">
         <v>3</v>
@@ -6221,7 +6227,7 @@
         <v>30</v>
       </c>
       <c r="R37" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="S37" s="3" t="s">
         <v>95</v>
@@ -6284,7 +6290,7 @@
         <v>30</v>
       </c>
       <c r="R38" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="S38" s="7" t="s">
         <v>95</v>
@@ -6308,7 +6314,7 @@
         <v>71</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>104</v>
@@ -6431,13 +6437,13 @@
         <v>38</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="G41" s="3">
         <v>3</v>
@@ -6473,7 +6479,7 @@
         <v>60</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>95</v>
@@ -6620,13 +6626,13 @@
         <v>38</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G44" s="7">
         <v>6</v>
@@ -6662,7 +6668,7 @@
         <v>30</v>
       </c>
       <c r="R44" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S44" s="7" t="s">
         <v>95</v>
@@ -6683,13 +6689,13 @@
         <v>67</v>
       </c>
       <c r="D45" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F45" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G45">
         <v>6</v>
@@ -6725,7 +6731,7 @@
         <v>30</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="S45" t="s">
         <v>95</v>
@@ -6851,7 +6857,7 @@
         <v>30</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>95</v>
@@ -6875,7 +6881,7 @@
         <v>146</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>145</v>
@@ -6914,7 +6920,7 @@
         <v>480</v>
       </c>
       <c r="R48" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>95</v>
@@ -6935,13 +6941,13 @@
         <v>67</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G49" s="3">
         <v>6</v>
@@ -6962,7 +6968,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
@@ -6977,7 +6983,7 @@
         <v>30</v>
       </c>
       <c r="R49" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>95</v>
@@ -6998,13 +7004,13 @@
         <v>67</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
@@ -7040,7 +7046,7 @@
         <v>30</v>
       </c>
       <c r="R50" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>95</v>
@@ -7166,7 +7172,7 @@
         <v>30</v>
       </c>
       <c r="R52" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>95</v>
@@ -7229,7 +7235,7 @@
         <v>30</v>
       </c>
       <c r="R53" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="S53" t="s">
         <v>95</v>
@@ -7355,7 +7361,7 @@
         <v>30</v>
       </c>
       <c r="R55" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="S55" s="8" t="s">
         <v>95</v>
@@ -7544,7 +7550,7 @@
         <v>120</v>
       </c>
       <c r="R58" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>95</v>
@@ -7607,7 +7613,7 @@
         <v>30</v>
       </c>
       <c r="R59" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>95</v>
@@ -7655,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N60">
         <v>1</v>
@@ -7670,7 +7676,7 @@
         <v>60</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="S60" t="s">
         <v>95</v>
@@ -7733,7 +7739,7 @@
         <v>30</v>
       </c>
       <c r="R61" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="S61" s="3" t="s">
         <v>95</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F363CC-9C18-4039-BB5F-B97215788ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B109A56D-674B-49AA-BEB3-09AE9A414F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1575" yWindow="1245" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2340" yWindow="960" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3167,55 +3167,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>草花のエキスを抽出し、ポーションを作る
-レベルが上がると成功率が上がるほか、一度にできあがる個数も増える。
-LV1: +5%成功Up, 個数1個
-LV2: +10%成功Up , 個数2個
-LV3: +15%成功Up , 個数3個
-LV4: +20%成功Up , 個数4個
-LV5: +25%成功Up , 個数5個</t>
-    <rPh sb="0" eb="2">
-      <t>クサバナ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>チュウシュツ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="29" eb="32">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>コスウ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>コスウ</t>
-    </rPh>
-    <rPh sb="73" eb="74">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="91" eb="93">
-      <t>コスウ</t>
-    </rPh>
-    <rPh sb="94" eb="95">
-      <t>コ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ルミナス・シュガー</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3455,6 +3406,55 @@
     </rPh>
     <rPh sb="61" eb="63">
       <t>ヒンシツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>草花のエキスを抽出し、ポーションを作る
+レベルが上がると成功率が上がるほか、一度にできあがる個数も増える。
+LV1: +3%成功Up, 個数1個
+LV2: +6%成功Up , 個数2個
+LV3: +9%成功Up , 個数3個
+LV4: +12%成功Up , 個数4個
+LV5: +15%成功Up , 個数5個</t>
+    <rPh sb="0" eb="2">
+      <t>クサバナ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>チュウシュツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>コ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4400,7 +4400,7 @@
         <v>30</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>95</v>
@@ -4463,7 +4463,7 @@
         <v>30</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>62</v>
@@ -4589,7 +4589,7 @@
         <v>30</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>81</v>
@@ -5120,7 +5120,7 @@
         <v>164</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
@@ -5156,7 +5156,7 @@
         <v>30</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>95</v>
@@ -5180,7 +5180,7 @@
         <v>16</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>15</v>
@@ -7172,7 +7172,7 @@
         <v>30</v>
       </c>
       <c r="R52" s="4" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>95</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N60">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B109A56D-674B-49AA-BEB3-09AE9A414F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2E7E7E-FB51-4C75-B60A-9E93A5BE8E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="960" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView minimized="1" xWindow="1350" yWindow="945" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6134,7 +6134,7 @@
         <v>3</v>
       </c>
       <c r="H36" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I36" s="3">
         <v>0</v>
@@ -6197,7 +6197,7 @@
         <v>3</v>
       </c>
       <c r="H37" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I37" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2E7E7E-FB51-4C75-B60A-9E93A5BE8E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8F9CB0-CDF9-415E-8636-37A5FF87B7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1350" yWindow="945" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3150" yWindow="1080" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5756,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="3">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I30" s="3">
         <v>0</v>
@@ -6323,7 +6323,7 @@
         <v>3</v>
       </c>
       <c r="H39" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I39" s="3">
         <v>0</v>
@@ -6386,7 +6386,7 @@
         <v>3</v>
       </c>
       <c r="H40" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I40" s="3">
         <v>0</v>
@@ -6449,7 +6449,7 @@
         <v>3</v>
       </c>
       <c r="H41" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I41" s="3">
         <v>0</v>
@@ -6512,7 +6512,7 @@
         <v>3</v>
       </c>
       <c r="H42" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>3</v>
       </c>
       <c r="H43" s="5">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I43" s="5">
         <v>9999</v>
@@ -6890,7 +6890,7 @@
         <v>6</v>
       </c>
       <c r="H48" s="3">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I48" s="3">
         <v>0</v>
@@ -6953,7 +6953,7 @@
         <v>6</v>
       </c>
       <c r="H49" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8F9CB0-CDF9-415E-8636-37A5FF87B7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4E550B-A6FD-4CFB-9930-3331A8FE454C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="1080" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2730" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4244,7 +4244,7 @@
         <v>2</v>
       </c>
       <c r="H6" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I6" s="3">
         <v>0</v>
@@ -4370,7 +4370,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>6</v>
       </c>
       <c r="H11" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I11" s="3">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         <v>6</v>
       </c>
       <c r="H12" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I12" s="3">
         <v>0</v>
@@ -4811,7 +4811,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -4874,7 +4874,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I16" s="3">
         <v>0</v>
@@ -5000,7 +5000,7 @@
         <v>2</v>
       </c>
       <c r="H18" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I18" s="3">
         <v>0</v>
@@ -5189,7 +5189,7 @@
         <v>2</v>
       </c>
       <c r="H21" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" s="3">
         <v>0</v>
@@ -5252,7 +5252,7 @@
         <v>4</v>
       </c>
       <c r="H22" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -5315,7 +5315,7 @@
         <v>4</v>
       </c>
       <c r="H23" s="3">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I23" s="3">
         <v>0</v>
@@ -5504,7 +5504,7 @@
         <v>4</v>
       </c>
       <c r="H26">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -5693,7 +5693,7 @@
         <v>6</v>
       </c>
       <c r="H29" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -5756,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I30" s="3">
         <v>0</v>
@@ -5819,7 +5819,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I31" s="3">
         <v>1</v>
@@ -5882,7 +5882,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I32" s="3">
         <v>1</v>
@@ -5945,7 +5945,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I33" s="3">
         <v>1</v>
@@ -6008,7 +6008,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I34" s="3">
         <v>0</v>
@@ -6071,7 +6071,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I35" s="3">
         <v>0</v>
@@ -6134,7 +6134,7 @@
         <v>3</v>
       </c>
       <c r="H36" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I36" s="3">
         <v>0</v>
@@ -6197,7 +6197,7 @@
         <v>3</v>
       </c>
       <c r="H37" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I37" s="3">
         <v>0</v>
@@ -6323,7 +6323,7 @@
         <v>3</v>
       </c>
       <c r="H39" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I39" s="3">
         <v>0</v>
@@ -6386,7 +6386,7 @@
         <v>3</v>
       </c>
       <c r="H40" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I40" s="3">
         <v>0</v>
@@ -6449,7 +6449,7 @@
         <v>3</v>
       </c>
       <c r="H41" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I41" s="3">
         <v>0</v>
@@ -6512,7 +6512,7 @@
         <v>3</v>
       </c>
       <c r="H42" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -6764,7 +6764,7 @@
         <v>6</v>
       </c>
       <c r="H46" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I46" s="3">
         <v>0</v>
@@ -6890,7 +6890,7 @@
         <v>6</v>
       </c>
       <c r="H48" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I48" s="3">
         <v>0</v>
@@ -6953,7 +6953,7 @@
         <v>6</v>
       </c>
       <c r="H49" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -7016,7 +7016,7 @@
         <v>6</v>
       </c>
       <c r="H50" s="3">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I50" s="3">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>6</v>
       </c>
       <c r="H52" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>6</v>
       </c>
       <c r="H54" s="8">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I54" s="8">
         <v>0</v>
@@ -7331,7 +7331,7 @@
         <v>18</v>
       </c>
       <c r="H55" s="8">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I55" s="8">
         <v>0</v>
@@ -7394,7 +7394,7 @@
         <v>6</v>
       </c>
       <c r="H56" s="8">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I56" s="8">
         <v>0</v>
@@ -7457,7 +7457,7 @@
         <v>6</v>
       </c>
       <c r="H57" s="8">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="I57" s="8">
         <v>0</v>
@@ -7520,7 +7520,7 @@
         <v>2</v>
       </c>
       <c r="H58" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -7583,7 +7583,7 @@
         <v>6</v>
       </c>
       <c r="H59" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I59" s="3">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>2</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I60">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4E550B-A6FD-4CFB-9930-3331A8FE454C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C109F210-2E86-4096-A331-EA21A5485E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1950" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C109F210-2E86-4096-A331-EA21A5485E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A230D4-3D16-4E98-97D3-18E48CF0739F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2610" yWindow="1590" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -161,10 +161,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>バブル・ミスト</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Bubble_Mist</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1055,14 +1051,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ほしのかけらを飲み物にトッピングする
-ジュースやソーダとの相性がいい。</t>
-    <rPh sb="30" eb="32">
-      <t>アイショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ポーションや液体を固めて、シュガーを作り出す</t>
     <rPh sb="6" eb="8">
       <t>エキタイ</t>
@@ -1354,36 +1342,6 @@
     </rPh>
     <rPh sb="25" eb="26">
       <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>チョコレートについて勉強することで、よりなめらかなチョコレートを仕上げるようになる。
-LVに応じて、成功率も上がる。
-LV1: なめらか+10, 成功率+2%
-LV2: なめらか+20, 成功率+4%
-LV3: なめらか+30, 成功率+6%
-LV4: なめらか+40, 成功率+8%
-LV5: なめらか+50, 成功率+10%
-LV6: なめらか+60, 成功率+12%
-LV7: なめらか+70, 成功率+14%
-LV8: なめらか+80, 成功率+16%
-LV9: なめらか+90, 成功率+18%
-LV10: なめらか+100, 成功率+20%</t>
-    <rPh sb="10" eb="12">
-      <t>ベンキョウ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="50" eb="53">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="74" eb="77">
-      <t>セイコウリツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1757,79 +1715,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>できたてのお菓子に対し、こころをこめることで、
-お菓子の食感を底上げし、おいしくする。すべてのお菓子に効果がある。
-使用時に、ハートを少し消費する。
-ハートが少ないと使用できない。
-仕上げ回数を一回消費する。
-仕上げ回数がないと、使用できない。
-パネルにお菓子がセットされていないと、使用できない。</t>
-    <rPh sb="6" eb="8">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ショクカン</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ソコア</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="59" eb="62">
-      <t>シヨウジ</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>ショウヒ</t>
-    </rPh>
-    <rPh sb="80" eb="81">
-      <t>スク</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="93" eb="95">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="96" eb="98">
-      <t>カイスウ</t>
-    </rPh>
-    <rPh sb="99" eb="101">
-      <t>イッカイ</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>ショウヒ</t>
-    </rPh>
-    <rPh sb="107" eb="109">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>カイスウ</t>
-    </rPh>
-    <rPh sb="117" eb="119">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="131" eb="133">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="145" eb="147">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>コーヒー・カフェラテについて勉強する。
 覚えるだけでコーヒー系の品質の底上げ。
 さらに、カフェラテの仕上げに魔法をかけることで、
@@ -2469,55 +2354,6 @@
     </rPh>
     <rPh sb="138" eb="140">
       <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>光で作ったちょうちょや葉っぱを飛ばす
-お菓子をさらにかわいく演出できる。
-特定のお菓子でないと、効果が発動しない。
-木やお城などをモチーフにしたお菓子と相性がいい。</t>
-    <rPh sb="0" eb="1">
-      <t>ヒカ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ハ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>エンシュツ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>トクテイ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ハツドウ</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="77" eb="79">
-      <t>アイショウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2847,56 +2683,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>アロマの泡を作り出す。
-おかしの周りに泡を浮かべることができる。
-浮いた泡の効果で、
-風を表現したお菓子になる。
-また、見た目もアップする。</t>
-    <rPh sb="4" eb="5">
-      <t>アワ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>マワ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>アワ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>アワ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>カゼ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ヒョウゲン</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>メ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Fire_Flowers</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2944,41 +2730,6 @@
     <t>かぜの囁き</t>
     <rPh sb="3" eb="4">
       <t>ササヤ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>風の演出をおかしに加える。</t>
-    <rPh sb="2" eb="4">
-      <t>エンシュツ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>クワ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>風の演出をおかしに加える。
-また、水あめ・チョコレートにかけると、羽飾りに変形する。
-派生：
-LV1で、各ウィンド系の魔法の習得可</t>
-    <rPh sb="18" eb="19">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ハネ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ハセイ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>マホウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3008,52 +2759,6 @@
     </rPh>
     <rPh sb="34" eb="35">
       <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>クッキーについて勉強することで、よりさくさく感の高いクッキーを焼けるようになる。
-ラスクにも効果がある。
-成功率も少し上昇する。
-LV1: さくさく感+10, 成功率+1%
-LV2: さくさく感+20, 成功率+2%
-LV3: さくさく感+30, 成功率+3%
-LV4: さくさく感+40, 成功率+4%
-LV5: さくさく感+50, 成功率+5%
-LV6: さくさく感+60, 成功率+6%
-LV7: さくさく感+70, 成功率+7%
-LV8: さくさく感+80, 成功率+8%
-LV9: さくさく感+90, 成功率+9%
-LV10: さくさく感+100, 成功率+10%</t>
-    <rPh sb="8" eb="10">
-      <t>ベンキョウ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="53" eb="56">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ジョウショウ</t>
-    </rPh>
-    <rPh sb="75" eb="76">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="81" eb="84">
-      <t>セイコウリツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3283,74 +2988,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>お菓子の周りに花火を飛ばした演出が可能になる。
-LVが上がると効果が高まる。
-見た目を派手にすることができる。
-パーティに向けたお客さんに喜んでもらうことができる。
-チョコレートのお菓子など、火に弱いお菓子にかけると失敗する。</t>
-    <rPh sb="1" eb="3">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>マワ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハナビ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>エンシュツ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カノウ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ハデ</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="66" eb="67">
-      <t>キャク</t>
-    </rPh>
-    <rPh sb="70" eb="71">
-      <t>ヨロコ</t>
-    </rPh>
-    <rPh sb="93" eb="95">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="98" eb="99">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="100" eb="101">
-      <t>ヨワ</t>
-    </rPh>
-    <rPh sb="103" eb="105">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>シッパイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>光り系のお菓子のキラキラ感を強める。</t>
     <rPh sb="0" eb="1">
       <t>ヒカ</t>
@@ -3455,6 +3092,339 @@
     </rPh>
     <rPh sb="93" eb="94">
       <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>水あめ・チョコレートにかけると、羽飾りに変形する。
+派生：
+LV1で、各ウィンド系の魔法の習得可</t>
+    <rPh sb="0" eb="1">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ハネ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ハセイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>水あめやチョコレートにかけると、羽飾りを作る。</t>
+    <rPh sb="0" eb="1">
+      <t>ミズ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ハネ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カザ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコレートについて勉強することで、よりなめらかなチョコレートを仕上げるようになる。
+LVに応じて、成功率も上がる。
+LV1: なめらか+30, 成功率+2%
+LV2: なめらか+60, 成功率+4%
+LV3: なめらか+90, 成功率+6%
+LV4: なめらか+120, 成功率+8%
+LV5: なめらか+150, 成功率+10%
+LV6: なめらか+180, 成功率+12%
+LV7: なめらか+210, 成功率+14%
+LV8: なめらか+240, 成功率+16%
+LV9: なめらか+270, 成功率+18%
+LV10: なめらか+300, 成功率+20%</t>
+    <rPh sb="10" eb="12">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="50" eb="53">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="74" eb="77">
+      <t>セイコウリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クッキーについて勉強することで、よりさくさく感の高いクッキーを焼けるようになる。
+ラスクにも効果がある。
+成功率も少し上昇する。
+LV1: さくさく感+30, 成功率+1%
+LV2: さくさく感+60, 成功率+2%
+LV3: さくさく感+90, 成功率+3%
+LV4: さくさく感+120, 成功率+4%
+LV5: さくさく感+150, 成功率+5%
+LV6: さくさく感+180, 成功率+6%
+LV7: さくさく感+210, 成功率+7%
+LV8: さくさく感+240, 成功率+8%
+LV9: さくさく感+270, 成功率+9%
+LV10: さくさく感+300, 成功率+10%</t>
+    <rPh sb="8" eb="10">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="53" eb="56">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="81" eb="84">
+      <t>セイコウリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お菓子の周りに花火を飛ばした演出が可能になる。
+LVが上がると効果が高まる。
+見た目を派手にすることができる。
+パーティに向けたお客さんに喜んでもらうことができる。
+仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="1" eb="3">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハナビ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ハデ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>光で作ったちょうちょや葉っぱを飛ばす
+お菓子をさらにかわいく演出できる。
+特定のお菓子でないと、効果が発動しない。
+木やお城などをモチーフにしたお菓子と相性がいい。
+仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>アイショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ほしのかけらを飲み物にトッピングする
+ジュースやソーダとの相性がいい。
+仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="30" eb="32">
+      <t>アイショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>できたてのお菓子に対し、こころをこめることで、
+お菓子の食感を底上げし、おいしくする。すべてのお菓子に効果がある。
+使用時に、ハートを少し消費する。
+ハートが少ないと使用できない。
+仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="6" eb="8">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ショクカン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ソコア</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="59" eb="62">
+      <t>シヨウジ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="80" eb="81">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>イッカイ</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>カイスウ</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あわあわ・デコレーション</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アロマの泡を作り出して、
+おかしの周りに泡を浮かべることができる。
+見た目がアップする。
+仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="4" eb="5">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>メ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3911,7 +3881,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -3941,10 +3911,10 @@
         <v>12</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>8</v>
@@ -3956,16 +3926,16 @@
         <v>10</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3983,7 +3953,7 @@
         <v>17</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>14</v>
@@ -4007,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N2" s="5">
         <v>1</v>
@@ -4022,10 +3992,10 @@
         <v>30</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T2" s="5">
         <v>0</v>
@@ -4040,16 +4010,16 @@
         <v>1002</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="G3" s="3">
         <v>6</v>
@@ -4070,7 +4040,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N3" s="3">
         <v>0</v>
@@ -4085,10 +4055,10 @@
         <v>30</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T3" s="3">
         <v>0</v>
@@ -4106,13 +4076,13 @@
         <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -4133,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N4" s="5">
         <v>1</v>
@@ -4148,10 +4118,10 @@
         <v>30</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T4" s="5">
         <v>0</v>
@@ -4166,16 +4136,16 @@
         <v>1010</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G5" s="3">
         <v>6</v>
@@ -4196,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N5" s="3">
         <v>0</v>
@@ -4211,10 +4181,10 @@
         <v>30</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>173</v>
+        <v>259</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T5" s="3">
         <v>0</v>
@@ -4229,16 +4199,16 @@
         <v>1003</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="G6" s="3">
         <v>2</v>
@@ -4259,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N6" s="3">
         <v>1</v>
@@ -4274,10 +4244,10 @@
         <v>30</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T6" s="3">
         <v>0</v>
@@ -4292,16 +4262,16 @@
         <v>1004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="G7" s="3">
         <v>2</v>
@@ -4322,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N7" s="3">
         <v>0</v>
@@ -4337,10 +4307,10 @@
         <v>30</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T7" s="3">
         <v>0</v>
@@ -4355,16 +4325,16 @@
         <v>1006</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
@@ -4385,7 +4355,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N8" s="3">
         <v>1</v>
@@ -4400,10 +4370,10 @@
         <v>30</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -4418,16 +4388,16 @@
         <v>1006</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3">
         <v>6</v>
@@ -4448,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N9" s="3">
         <v>1</v>
@@ -4463,13 +4433,13 @@
         <v>30</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="T9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:20" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -4481,16 +4451,16 @@
         <v>1007</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G10" s="7">
         <v>6</v>
@@ -4511,7 +4481,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N10" s="7">
         <v>1</v>
@@ -4526,10 +4496,10 @@
         <v>30</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T10" s="7">
         <v>0</v>
@@ -4544,16 +4514,16 @@
         <v>1008</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G11" s="3">
         <v>6</v>
@@ -4574,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N11" s="3">
         <v>1</v>
@@ -4589,10 +4559,10 @@
         <v>30</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T11" s="3">
         <v>1</v>
@@ -4607,16 +4577,16 @@
         <v>1009</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G12" s="3">
         <v>6</v>
@@ -4637,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N12" s="3">
         <v>1</v>
@@ -4652,10 +4622,10 @@
         <v>30</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T12" s="3">
         <v>0</v>
@@ -4670,16 +4640,16 @@
         <v>1009</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G13" s="7">
         <v>6</v>
@@ -4700,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N13" s="7">
         <v>1</v>
@@ -4715,10 +4685,10 @@
         <v>30</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T13" s="7">
         <v>0</v>
@@ -4733,16 +4703,16 @@
         <v>2004</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G14" s="3">
         <v>2</v>
@@ -4763,7 +4733,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -4778,10 +4748,10 @@
         <v>30</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -4796,16 +4766,16 @@
         <v>2001</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="G15" s="3">
         <v>2</v>
@@ -4826,7 +4796,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N15" s="3">
         <v>1</v>
@@ -4841,10 +4811,10 @@
         <v>120</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -4859,16 +4829,16 @@
         <v>2001</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G16" s="3">
         <v>2</v>
@@ -4889,7 +4859,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N16" s="3">
         <v>1</v>
@@ -4904,10 +4874,10 @@
         <v>120</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T16" s="3">
         <v>2</v>
@@ -4922,16 +4892,16 @@
         <v>2002</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G17" s="5">
         <v>2</v>
@@ -4952,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N17" s="5">
         <v>1</v>
@@ -4967,10 +4937,10 @@
         <v>120</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T17" s="5">
         <v>0</v>
@@ -4985,16 +4955,16 @@
         <v>2003</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G18" s="3">
         <v>2</v>
@@ -5015,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N18" s="3">
         <v>1</v>
@@ -5030,10 +5000,10 @@
         <v>120</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T18" s="3">
         <v>0</v>
@@ -5048,16 +5018,16 @@
         <v>2003</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G19" s="7">
         <v>2</v>
@@ -5078,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N19" s="7">
         <v>1</v>
@@ -5093,10 +5063,10 @@
         <v>30</v>
       </c>
       <c r="R19" s="7" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T19" s="7">
         <v>0</v>
@@ -5111,16 +5081,16 @@
         <v>3006</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
@@ -5141,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -5156,10 +5126,10 @@
         <v>30</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -5174,13 +5144,13 @@
         <v>3001</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>15</v>
@@ -5204,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N21" s="3">
         <v>1</v>
@@ -5219,10 +5189,10 @@
         <v>30</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T21" s="3">
         <v>0</v>
@@ -5237,7 +5207,7 @@
         <v>3002</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>20</v>
@@ -5267,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N22" s="3">
         <v>1</v>
@@ -5282,7 +5252,7 @@
         <v>30</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>16</v>
@@ -5300,22 +5270,22 @@
         <v>3003</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G23" s="3">
         <v>4</v>
       </c>
       <c r="H23" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I23" s="3">
         <v>0</v>
@@ -5330,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N23" s="3">
         <v>1</v>
@@ -5345,10 +5315,10 @@
         <v>60</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T23" s="3">
         <v>0</v>
@@ -5363,16 +5333,16 @@
         <v>3004</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="G24" s="3">
         <v>4</v>
@@ -5393,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -5408,10 +5378,10 @@
         <v>30</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -5426,16 +5396,16 @@
         <v>3005</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G25" s="7">
         <v>4</v>
@@ -5456,7 +5426,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N25" s="7">
         <v>1</v>
@@ -5471,75 +5441,75 @@
         <v>30</v>
       </c>
       <c r="R25" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T25" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26">
+    <row r="26" spans="1:20" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="7">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="7">
         <v>3005</v>
       </c>
-      <c r="C26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" t="s">
-        <v>231</v>
-      </c>
-      <c r="E26" t="s">
-        <v>232</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="C26" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G26" s="7">
+        <v>4</v>
+      </c>
+      <c r="H26" s="7">
+        <v>10</v>
+      </c>
+      <c r="I26" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J26" s="7">
+        <v>0</v>
+      </c>
+      <c r="K26" s="7">
+        <v>5</v>
+      </c>
+      <c r="L26" s="7">
+        <v>0</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N26" s="7">
+        <v>1</v>
+      </c>
+      <c r="O26" s="7">
+        <v>2</v>
+      </c>
+      <c r="P26" s="7">
+        <v>100</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>30</v>
+      </c>
+      <c r="R26" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="G26">
-        <v>4</v>
-      </c>
-      <c r="H26">
-        <v>10</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>5</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" t="s">
-        <v>95</v>
-      </c>
-      <c r="N26">
-        <v>1</v>
-      </c>
-      <c r="O26">
-        <v>2</v>
-      </c>
-      <c r="P26">
-        <v>100</v>
-      </c>
-      <c r="Q26">
-        <v>30</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="S26" t="s">
-        <v>95</v>
-      </c>
-      <c r="T26">
+      <c r="S26" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T26" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5552,16 +5522,16 @@
         <v>4010</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="G27" s="3">
         <v>6</v>
@@ -5582,7 +5552,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N27" s="3">
         <v>0</v>
@@ -5597,10 +5567,10 @@
         <v>30</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T27" s="3">
         <v>0</v>
@@ -5615,16 +5585,16 @@
         <v>4011</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G28" s="3">
         <v>6</v>
@@ -5645,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N28" s="3">
         <v>0</v>
@@ -5660,10 +5630,10 @@
         <v>30</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T28" s="3">
         <v>0</v>
@@ -5678,7 +5648,7 @@
         <v>4001</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>23</v>
@@ -5687,7 +5657,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="G29" s="3">
         <v>6</v>
@@ -5708,7 +5678,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="N29" s="3">
         <v>1</v>
@@ -5723,10 +5693,10 @@
         <v>30</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -5741,7 +5711,7 @@
         <v>4002</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -5750,7 +5720,7 @@
         <v>22</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -5771,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N30" s="3">
         <v>1</v>
@@ -5786,10 +5756,10 @@
         <v>30</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T30" s="3">
         <v>0</v>
@@ -5804,16 +5774,16 @@
         <v>4010</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="F31" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -5834,7 +5804,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N31" s="3">
         <v>1</v>
@@ -5849,7 +5819,7 @@
         <v>30</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="S31" s="3" t="s">
         <v>23</v>
@@ -5867,16 +5837,16 @@
         <v>4011</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -5897,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N32" s="3">
         <v>1</v>
@@ -5912,7 +5882,7 @@
         <v>30</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>23</v>
@@ -5930,16 +5900,16 @@
         <v>4012</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -5960,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N33" s="3">
         <v>1</v>
@@ -5975,7 +5945,7 @@
         <v>30</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>23</v>
@@ -5993,16 +5963,16 @@
         <v>4012</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -6023,7 +5993,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N34" s="3">
         <v>1</v>
@@ -6038,7 +6008,7 @@
         <v>30</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="S34" s="3" t="s">
         <v>23</v>
@@ -6056,16 +6026,16 @@
         <v>4012</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -6086,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N35" s="3">
         <v>1</v>
@@ -6101,7 +6071,7 @@
         <v>30</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>23</v>
@@ -6110,66 +6080,66 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:20" s="3" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="3">
+    <row r="36" spans="1:20" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="7">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="7">
         <v>4003</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="3" t="s">
+      <c r="C36" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="E36" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F36" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="7">
         <v>3</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="7">
         <v>2</v>
       </c>
-      <c r="I36" s="3">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3">
-        <v>0</v>
-      </c>
-      <c r="K36" s="3">
+      <c r="I36" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J36" s="7">
+        <v>0</v>
+      </c>
+      <c r="K36" s="7">
         <v>3</v>
       </c>
-      <c r="L36" s="3">
-        <v>0</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N36" s="3">
-        <v>1</v>
-      </c>
-      <c r="O36" s="3">
+      <c r="L36" s="7">
+        <v>0</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N36" s="7">
+        <v>1</v>
+      </c>
+      <c r="O36" s="7">
         <v>3</v>
       </c>
-      <c r="P36" s="3">
+      <c r="P36" s="7">
         <v>100</v>
       </c>
-      <c r="Q36" s="3">
+      <c r="Q36" s="7">
         <v>30</v>
       </c>
-      <c r="R36" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="T36" s="3">
+      <c r="R36" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="S36" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T36" s="7">
         <v>0</v>
       </c>
     </row>
@@ -6182,16 +6152,16 @@
         <v>4004</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>27</v>
+        <v>265</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G37" s="3">
         <v>3</v>
@@ -6212,7 +6182,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N37" s="3">
         <v>1</v>
@@ -6227,10 +6197,10 @@
         <v>30</v>
       </c>
       <c r="R37" s="4" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T37" s="3">
         <v>0</v>
@@ -6245,16 +6215,16 @@
         <v>4005</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E38" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="G38" s="7">
         <v>12</v>
@@ -6275,7 +6245,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N38" s="7">
         <v>1</v>
@@ -6290,10 +6260,10 @@
         <v>30</v>
       </c>
       <c r="R38" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="S38" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T38" s="7">
         <v>0</v>
@@ -6308,16 +6278,16 @@
         <v>4006</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G39" s="3">
         <v>3</v>
@@ -6338,7 +6308,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N39" s="3">
         <v>1</v>
@@ -6353,10 +6323,10 @@
         <v>60</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T39" s="3">
         <v>0</v>
@@ -6371,16 +6341,16 @@
         <v>4007</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G40" s="3">
         <v>3</v>
@@ -6401,7 +6371,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N40" s="3">
         <v>1</v>
@@ -6416,10 +6386,10 @@
         <v>60</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T40" s="3">
         <v>0</v>
@@ -6434,16 +6404,16 @@
         <v>4007</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G41" s="3">
         <v>3</v>
@@ -6464,7 +6434,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N41" s="3">
         <v>1</v>
@@ -6479,10 +6449,10 @@
         <v>60</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T41" s="3">
         <v>0</v>
@@ -6497,16 +6467,16 @@
         <v>4008</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G42" s="3">
         <v>3</v>
@@ -6527,7 +6497,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N42" s="3">
         <v>1</v>
@@ -6542,10 +6512,10 @@
         <v>60</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -6560,16 +6530,16 @@
         <v>4009</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G43" s="5">
         <v>3</v>
@@ -6590,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N43" s="5">
         <v>1</v>
@@ -6605,10 +6575,10 @@
         <v>30</v>
       </c>
       <c r="R43" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S43" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T43" s="5">
         <v>0</v>
@@ -6623,16 +6593,16 @@
         <v>4013</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G44" s="7">
         <v>6</v>
@@ -6653,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N44" s="7">
         <v>1</v>
@@ -6668,75 +6638,75 @@
         <v>30</v>
       </c>
       <c r="R44" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="S44" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T44" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45">
+    <row r="45" spans="1:20" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="7">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="7">
         <v>5004</v>
       </c>
-      <c r="C45" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" t="s">
-        <v>167</v>
-      </c>
-      <c r="E45" t="s">
-        <v>166</v>
-      </c>
-      <c r="F45" t="s">
-        <v>204</v>
-      </c>
-      <c r="G45">
+      <c r="C45" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="G45" s="7">
         <v>6</v>
       </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
+      <c r="H45" s="7">
+        <v>0</v>
+      </c>
+      <c r="I45" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J45" s="7">
+        <v>0</v>
+      </c>
+      <c r="K45" s="7">
         <v>5</v>
       </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45" t="s">
-        <v>95</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
+      <c r="L45" s="7">
+        <v>0</v>
+      </c>
+      <c r="M45" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N45" s="7">
+        <v>0</v>
+      </c>
+      <c r="O45" s="7">
         <v>4</v>
       </c>
-      <c r="P45">
+      <c r="P45" s="7">
         <v>100</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="7">
         <v>30</v>
       </c>
-      <c r="R45" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="S45" t="s">
-        <v>95</v>
-      </c>
-      <c r="T45">
+      <c r="R45" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="S45" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T45" s="7">
         <v>0</v>
       </c>
     </row>
@@ -6749,16 +6719,16 @@
         <v>5001</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G46" s="3">
         <v>6</v>
@@ -6779,7 +6749,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N46" s="3">
         <v>1</v>
@@ -6794,10 +6764,10 @@
         <v>30</v>
       </c>
       <c r="R46" s="4" t="s">
-        <v>140</v>
+        <v>263</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T46" s="3">
         <v>0</v>
@@ -6812,16 +6782,16 @@
         <v>5002</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E47" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="G47" s="3">
         <v>6</v>
@@ -6842,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N47" s="3">
         <v>1</v>
@@ -6857,10 +6827,10 @@
         <v>30</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -6875,16 +6845,16 @@
         <v>5003</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G48" s="3">
         <v>6</v>
@@ -6905,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N48" s="3">
         <v>1</v>
@@ -6920,10 +6890,10 @@
         <v>480</v>
       </c>
       <c r="R48" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -6938,16 +6908,16 @@
         <v>5005</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G49" s="3">
         <v>6</v>
@@ -6968,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
@@ -6983,10 +6953,10 @@
         <v>30</v>
       </c>
       <c r="R49" s="4" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -7001,16 +6971,16 @@
         <v>5006</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
@@ -7031,7 +7001,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N50" s="3">
         <v>1</v>
@@ -7046,10 +7016,10 @@
         <v>30</v>
       </c>
       <c r="R50" s="4" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T50" s="3">
         <v>0</v>
@@ -7064,16 +7034,16 @@
         <v>6001</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G51" s="7">
         <v>6</v>
@@ -7094,7 +7064,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N51" s="7">
         <v>1</v>
@@ -7109,10 +7079,10 @@
         <v>30</v>
       </c>
       <c r="R51" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T51" s="7">
         <v>0</v>
@@ -7127,16 +7097,16 @@
         <v>6002</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G52" s="3">
         <v>6</v>
@@ -7157,7 +7127,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N52" s="3">
         <v>1</v>
@@ -7172,75 +7142,75 @@
         <v>30</v>
       </c>
       <c r="R52" s="4" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A53">
+    <row r="53" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="7">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="7">
         <v>6003</v>
       </c>
-      <c r="C53" t="s">
-        <v>151</v>
-      </c>
-      <c r="D53" t="s">
-        <v>43</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="C53" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F53" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="F53" t="s">
-        <v>42</v>
-      </c>
-      <c r="G53">
+      <c r="G53" s="7">
         <v>6</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="7">
         <v>3</v>
       </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>1</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53" t="s">
-        <v>95</v>
-      </c>
-      <c r="N53">
-        <v>1</v>
-      </c>
-      <c r="O53">
+      <c r="I53" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J53" s="7">
+        <v>0</v>
+      </c>
+      <c r="K53" s="7">
+        <v>1</v>
+      </c>
+      <c r="L53" s="7">
+        <v>0</v>
+      </c>
+      <c r="M53" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N53" s="7">
+        <v>1</v>
+      </c>
+      <c r="O53" s="7">
         <v>5</v>
       </c>
-      <c r="P53">
+      <c r="P53" s="7">
         <v>100</v>
       </c>
-      <c r="Q53">
+      <c r="Q53" s="7">
         <v>30</v>
       </c>
-      <c r="R53" t="s">
-        <v>175</v>
-      </c>
-      <c r="S53" t="s">
-        <v>95</v>
-      </c>
-      <c r="T53">
+      <c r="R53" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="S53" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T53" s="7">
         <v>0</v>
       </c>
     </row>
@@ -7253,16 +7223,16 @@
         <v>7001</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D54" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>47</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>48</v>
       </c>
       <c r="G54" s="8">
         <v>6</v>
@@ -7283,7 +7253,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N54" s="8">
         <v>1</v>
@@ -7298,10 +7268,10 @@
         <v>30</v>
       </c>
       <c r="R54" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S54" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T54" s="8">
         <v>0</v>
@@ -7316,16 +7286,16 @@
         <v>7002</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G55" s="8">
         <v>18</v>
@@ -7346,7 +7316,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N55" s="8">
         <v>1</v>
@@ -7361,10 +7331,10 @@
         <v>30</v>
       </c>
       <c r="R55" s="10" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="S55" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T55" s="8">
         <v>0</v>
@@ -7379,16 +7349,16 @@
         <v>8001</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G56" s="8">
         <v>6</v>
@@ -7409,7 +7379,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N56" s="8">
         <v>1</v>
@@ -7424,10 +7394,10 @@
         <v>30</v>
       </c>
       <c r="R56" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S56" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T56" s="8">
         <v>0</v>
@@ -7442,16 +7412,16 @@
         <v>8002</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G57" s="8">
         <v>6</v>
@@ -7472,7 +7442,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N57" s="8">
         <v>1</v>
@@ -7487,10 +7457,10 @@
         <v>30</v>
       </c>
       <c r="R57" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S57" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T57" s="8">
         <v>0</v>
@@ -7505,16 +7475,16 @@
         <v>9001</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G58" s="3">
         <v>2</v>
@@ -7535,7 +7505,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N58" s="3">
         <v>1</v>
@@ -7550,75 +7520,75 @@
         <v>120</v>
       </c>
       <c r="R58" s="4" t="s">
-        <v>201</v>
+        <v>264</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="3">
+    <row r="59" spans="1:20" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="7">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="7">
         <v>9002</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E59" s="3" t="s">
+      <c r="C59" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F59" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="7">
         <v>6</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="7">
         <v>5</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="I59" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J59" s="7">
+        <v>0</v>
+      </c>
+      <c r="K59" s="7">
         <v>10</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="L59" s="7">
+        <v>0</v>
+      </c>
+      <c r="M59" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N59" s="7">
+        <v>1</v>
+      </c>
+      <c r="O59" s="7">
         <v>8</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="7">
         <v>100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="7">
         <v>30</v>
       </c>
-      <c r="R59" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="R59" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="S59" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T59" s="7">
         <v>0</v>
       </c>
     </row>
@@ -7631,16 +7601,16 @@
         <v>9004</v>
       </c>
       <c r="C60" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E60" t="s">
+        <v>97</v>
+      </c>
+      <c r="F60" t="s">
         <v>98</v>
-      </c>
-      <c r="F60" t="s">
-        <v>99</v>
       </c>
       <c r="G60">
         <v>2</v>
@@ -7661,7 +7631,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="N60">
         <v>1</v>
@@ -7676,10 +7646,10 @@
         <v>60</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="S60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T60">
         <v>0</v>
@@ -7694,16 +7664,16 @@
         <v>9003</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G61" s="3">
         <v>6</v>
@@ -7724,7 +7694,7 @@
         <v>1</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N61" s="3">
         <v>1</v>
@@ -7739,10 +7709,10 @@
         <v>30</v>
       </c>
       <c r="R61" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A230D4-3D16-4E98-97D3-18E48CF0739F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6CD397-C1F0-40D5-BB01-F8C2E7895446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="1590" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2610" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2287,77 +2287,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>クッキーなどの焼き菓子をさらに焼くことで、サクサク感を増す。
-LVが上がると、より効果が高まる。
-ゲージが出現するので、
-焦げるギリギリのポイントでゲージを止めると、
-サクサク感が増す。
-ポイントを超えると、焦げて失敗。
-仕上げ回数を一回消費する。
-仕上げ回数がないと、使用できない。</t>
-    <rPh sb="7" eb="8">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ガシ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>シュツゲン</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="79" eb="80">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="89" eb="90">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="91" eb="92">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="101" eb="102">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="106" eb="107">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="109" eb="111">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="114" eb="116">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="117" eb="119">
-      <t>カイスウ</t>
-    </rPh>
-    <rPh sb="120" eb="122">
-      <t>イッカイ</t>
-    </rPh>
-    <rPh sb="122" eb="124">
-      <t>ショウヒ</t>
-    </rPh>
-    <rPh sb="128" eb="130">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="131" eb="133">
-      <t>カイスウ</t>
-    </rPh>
-    <rPh sb="138" eb="140">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>アパレイユのお勉強</t>
     <rPh sb="7" eb="9">
       <t>ベンキョウ</t>
@@ -3212,11 +3141,16 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>あわあわ・デコレーション</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>お菓子の周りに花火を飛ばした演出が可能になる。
 LVが上がると効果が高まる。
 見た目を派手にすることができる。
 パーティに向けたお客さんに喜んでもらうことができる。
-仕上げ回数を一回消費する。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
 仕上げ回数がないと、使用できない。</t>
     <rPh sb="1" eb="3">
       <t>カシ</t>
@@ -3266,60 +3200,94 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>光で作ったちょうちょや葉っぱを飛ばす
-お菓子をさらにかわいく演出できる。
-特定のお菓子でないと、効果が発動しない。
-木やお城などをモチーフにしたお菓子と相性がいい。
-仕上げ回数を一回消費する。
+    <t>クッキーなどの焼き菓子をさらに焼くことで、サクサク感を増す。
+LVが上がると、より効果が高まる。
+ゲージが出現するので、
+焦げるギリギリのポイントでゲージを止めると、
+サクサク感が増す。
+ポイントを超えると、焦げて失敗。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
 仕上げ回数がないと、使用できない。</t>
-    <rPh sb="0" eb="1">
-      <t>ヒカ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
+    <rPh sb="7" eb="8">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガシ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="91" eb="92">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="106" eb="107">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アロマの泡を作り出して、
+おかしの周りに泡を浮かべることができる。
+見た目がアップする。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="4" eb="5">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
       <t>ツク</t>
     </rPh>
-    <rPh sb="11" eb="12">
-      <t>ハ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>エンシュツ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>トクテイ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ハツドウ</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="74" eb="76">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="77" eb="79">
-      <t>アイショウ</t>
+    <rPh sb="8" eb="9">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>メ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ほしのかけらを飲み物にトッピングする
 ジュースやソーダとの相性がいい。
-仕上げ回数を一回消費する。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
 仕上げ回数がないと、使用できない。</t>
     <rPh sb="30" eb="32">
       <t>アイショウ</t>
@@ -3331,7 +3299,8 @@
 お菓子の食感を底上げし、おいしくする。すべてのお菓子に効果がある。
 使用時に、ハートを少し消費する。
 ハートが少ないと使用できない。
-仕上げ回数を一回消費する。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
 仕上げ回数がないと、使用できない。</t>
     <rPh sb="6" eb="8">
       <t>カシ</t>
@@ -3369,62 +3338,57 @@
     <rPh sb="84" eb="86">
       <t>シヨウ</t>
     </rPh>
-    <rPh sb="93" eb="95">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="96" eb="98">
-      <t>カイスウ</t>
-    </rPh>
-    <rPh sb="99" eb="101">
-      <t>イッカイ</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>ショウヒ</t>
-    </rPh>
-    <rPh sb="107" eb="109">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>カイスウ</t>
-    </rPh>
-    <rPh sb="117" eb="119">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>あわあわ・デコレーション</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アロマの泡を作り出して、
-おかしの周りに泡を浮かべることができる。
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>光で作ったちょうちょや葉っぱを飛ばす
+お菓子をさらにかわいく演出できる。
 見た目がアップする。
-仕上げ回数を一回消費する。
+木、またはお城をモチーフにしたお菓子と組み合わせると・・。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
 仕上げ回数がないと、使用できない。</t>
-    <rPh sb="4" eb="5">
-      <t>アワ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
+    <rPh sb="0" eb="1">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
       <t>ツク</t>
     </rPh>
-    <rPh sb="8" eb="9">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>マワ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>アワ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
+    <rPh sb="11" eb="12">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
       <t>ミ</t>
     </rPh>
-    <rPh sb="36" eb="37">
+    <rPh sb="39" eb="40">
       <t>メ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t>ツカ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4055,7 +4019,7 @@
         <v>30</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>94</v>
@@ -4181,7 +4145,7 @@
         <v>30</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>94</v>
@@ -4328,13 +4292,13 @@
         <v>151</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
@@ -4433,7 +4397,7 @@
         <v>30</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>94</v>
@@ -4559,7 +4523,7 @@
         <v>30</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>80</v>
@@ -4622,7 +4586,7 @@
         <v>30</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>223</v>
+        <v>262</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>94</v>
@@ -4646,7 +4610,7 @@
         <v>217</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>219</v>
@@ -4748,7 +4712,7 @@
         <v>30</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>94</v>
@@ -4811,7 +4775,7 @@
         <v>120</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>94</v>
@@ -5024,7 +4988,7 @@
         <v>216</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>218</v>
@@ -5090,7 +5054,7 @@
         <v>162</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
@@ -5126,7 +5090,7 @@
         <v>30</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>94</v>
@@ -5150,7 +5114,7 @@
         <v>16</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>15</v>
@@ -5189,7 +5153,7 @@
         <v>30</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>94</v>
@@ -5252,7 +5216,7 @@
         <v>30</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>16</v>
@@ -5276,7 +5240,7 @@
         <v>110</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>72</v>
@@ -5315,7 +5279,7 @@
         <v>60</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>94</v>
@@ -5462,13 +5426,13 @@
         <v>36</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="F26" s="7" t="s">
         <v>227</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>228</v>
       </c>
       <c r="G26" s="7">
         <v>4</v>
@@ -5504,7 +5468,7 @@
         <v>30</v>
       </c>
       <c r="R26" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S26" s="7" t="s">
         <v>94</v>
@@ -5567,7 +5531,7 @@
         <v>30</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>94</v>
@@ -5591,7 +5555,7 @@
         <v>159</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>160</v>
@@ -5657,7 +5621,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G29" s="3">
         <v>6</v>
@@ -5693,7 +5657,7 @@
         <v>30</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>94</v>
@@ -6158,10 +6122,10 @@
         <v>27</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G37" s="3">
         <v>3</v>
@@ -6197,7 +6161,7 @@
         <v>30</v>
       </c>
       <c r="R37" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="S37" s="3" t="s">
         <v>94</v>
@@ -6599,7 +6563,7 @@
         <v>168</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>166</v>
@@ -6701,7 +6665,7 @@
         <v>30</v>
       </c>
       <c r="R45" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="S45" s="7" t="s">
         <v>94</v>
@@ -6764,7 +6728,7 @@
         <v>30</v>
       </c>
       <c r="R46" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>94</v>
@@ -6938,7 +6902,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
@@ -6974,13 +6938,13 @@
         <v>66</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
@@ -7016,7 +6980,7 @@
         <v>30</v>
       </c>
       <c r="R50" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>94</v>
@@ -7142,7 +7106,7 @@
         <v>30</v>
       </c>
       <c r="R52" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>94</v>
@@ -7331,7 +7295,7 @@
         <v>30</v>
       </c>
       <c r="R55" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="S55" s="8" t="s">
         <v>94</v>
@@ -7520,7 +7484,7 @@
         <v>120</v>
       </c>
       <c r="R58" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>94</v>
@@ -7583,7 +7547,7 @@
         <v>30</v>
       </c>
       <c r="R59" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S59" s="7" t="s">
         <v>94</v>
@@ -7631,7 +7595,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N60">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A6CD397-C1F0-40D5-BB01-F8C2E7895446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950E781B-F828-475C-BD96-22A510BDE8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView minimized="1" xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950E781B-F828-475C-BD96-22A510BDE8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB5B231-0D8A-47AB-B84D-2456D21E3CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1215,20 +1215,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>生地をきれいに混ぜる技術を磨く。
-クレープやケーキ生地などのふわふわ感を底上げする。</t>
-    <rPh sb="26" eb="28">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ソコア</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>美の研究</t>
     <rPh sb="0" eb="1">
       <t>ビ</t>
@@ -1711,45 +1697,6 @@
     <t>リムービング・シェル※未使用</t>
     <rPh sb="11" eb="14">
       <t>ミシヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>コーヒー・カフェラテについて勉強する。
-覚えるだけでコーヒー系の品質の底上げ。
-さらに、カフェラテの仕上げに魔法をかけることで、
-ミルクに絵柄を描き、かわいく見せることができる。
-失敗することもある。
-コーヒー系の
-LV1: 見た目+30
-LV2: 見た目+60
-LV3: 見た目+90</t>
-    <rPh sb="14" eb="16">
-      <t>ベンキョウ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>エガラ</t>
-    </rPh>
-    <rPh sb="73" eb="74">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="91" eb="93">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="107" eb="108">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="115" eb="116">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="117" eb="118">
-      <t>メ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2750,57 +2697,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>アイス水溶液に魔法をかけながら混ぜて、なめらかさを出す
-習得するだけでOK。
-LVに応じて、なめらかさをより出す。
-また、アイスクリームの制作時、成功率アップ・制作時間を少し短縮する。
-LV1: なめらかさ+10, 成功率+2, 時間短縮+4%
-LV2: なめらかさ+20, 成功率+4, 時間短縮+8%
-LV3: なめらかさ+30, 成功率+6, 時間短縮+12%
-LV4: なめらかさ+40, 成功率+8, 時間短縮+16%
-LV5: なめらかさ+50, 成功率+10, 時間短縮+20%</t>
-    <rPh sb="25" eb="26">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>シュウトク</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="72" eb="73">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="74" eb="77">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="81" eb="85">
-      <t>セイサクジカン</t>
-    </rPh>
-    <rPh sb="86" eb="87">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="88" eb="90">
-      <t>タンシュク</t>
-    </rPh>
-    <rPh sb="110" eb="113">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="117" eb="119">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="119" eb="121">
-      <t>タンシュク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ルミナス・シュガー</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3061,82 +2957,6 @@
     </rPh>
     <rPh sb="20" eb="21">
       <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>チョコレートについて勉強することで、よりなめらかなチョコレートを仕上げるようになる。
-LVに応じて、成功率も上がる。
-LV1: なめらか+30, 成功率+2%
-LV2: なめらか+60, 成功率+4%
-LV3: なめらか+90, 成功率+6%
-LV4: なめらか+120, 成功率+8%
-LV5: なめらか+150, 成功率+10%
-LV6: なめらか+180, 成功率+12%
-LV7: なめらか+210, 成功率+14%
-LV8: なめらか+240, 成功率+16%
-LV9: なめらか+270, 成功率+18%
-LV10: なめらか+300, 成功率+20%</t>
-    <rPh sb="10" eb="12">
-      <t>ベンキョウ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="50" eb="53">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="74" eb="77">
-      <t>セイコウリツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>クッキーについて勉強することで、よりさくさく感の高いクッキーを焼けるようになる。
-ラスクにも効果がある。
-成功率も少し上昇する。
-LV1: さくさく感+30, 成功率+1%
-LV2: さくさく感+60, 成功率+2%
-LV3: さくさく感+90, 成功率+3%
-LV4: さくさく感+120, 成功率+4%
-LV5: さくさく感+150, 成功率+5%
-LV6: さくさく感+180, 成功率+6%
-LV7: さくさく感+210, 成功率+7%
-LV8: さくさく感+240, 成功率+8%
-LV9: さくさく感+270, 成功率+9%
-LV10: さくさく感+300, 成功率+10%</t>
-    <rPh sb="8" eb="10">
-      <t>ベンキョウ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="53" eb="56">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>ジョウショウ</t>
-    </rPh>
-    <rPh sb="75" eb="76">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="81" eb="84">
-      <t>セイコウリツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3389,6 +3209,185 @@
     </rPh>
     <rPh sb="101" eb="102">
       <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クッキーについて勉強することで、クッキーを焼くときの成功率が上がる。
+ラスクにも効果がある。
+ほんのわずかに、さくさく感も上昇する。
+LV1: 成功率+1%
+LV2: 成功率+2%
+LV3: 成功率+3%
+LV4: 成功率+4%
+LV5: 成功率+5%
+LV6: 成功率+6%
+LV7: 成功率+7%
+LV8: 成功率+8%
+LV9: 成功率+9%
+LV10: 成功率+10%</t>
+    <rPh sb="8" eb="10">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="73" eb="76">
+      <t>セイコウリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコレートについて勉強することで、よりなめらかなチョコレートを仕上げるようになる。
+LVに応じて、成功率が上がる。
+また、ほんの少しなめらか感を上昇する。
+LV1: 成功率+2%
+LV2: 成功率+4%
+LV3: 成功率+6%
+LV4: 成功率+8%
+LV5: 成功率+10%
+LV6: 成功率+12%
+LV7: 成功率+14%
+LV8: 成功率+16%
+LV9: 成功率+18%
+LV10: 成功率+20%</t>
+    <rPh sb="10" eb="12">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="50" eb="53">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="85" eb="88">
+      <t>セイコウリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コーヒー・カフェラテについて勉強する。
+カフェラテの仕上げに魔法をかけることで、
+ミルクにかわいい絵柄を描ける。
+失敗することもある。
+習得時、コーヒー系の
+LV1: 見た目+30
+LV2: 見た目+60
+LV3: 見た目+90</t>
+    <rPh sb="14" eb="16">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>エガラ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="70" eb="73">
+      <t>シュウトクジ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生地をきれいに混ぜる技術を磨く。
+クレープ生地やケーキ生地など生地系の品質を、少しだけ底上げする。</t>
+    <rPh sb="22" eb="24">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ソコア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アイス水溶液に魔法をかけながら混ぜて、アイスクリーム制作時の成功率アップ・制作時間を少し短縮する。
+習得するだけでOK。
+LVに応じて、ほんのわずかになめらかさを出す。
+LV1: 成功率+2, 時間短縮+4%
+LV2: 成功率+4, 時間短縮+8%
+LV3: 成功率+6, 時間短縮+12%
+LV4: 成功率+8, 時間短縮+16%
+LV5: 成功率+10, 時間短縮+20%</t>
+    <rPh sb="26" eb="29">
+      <t>セイサクジ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>シュウトク</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="82" eb="83">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="92" eb="95">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>タンシュク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4019,7 +4018,7 @@
         <v>30</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>94</v>
@@ -4103,10 +4102,10 @@
         <v>147</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>154</v>
@@ -4145,7 +4144,7 @@
         <v>30</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>94</v>
@@ -4271,7 +4270,7 @@
         <v>30</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="S7" s="3" t="s">
         <v>94</v>
@@ -4292,13 +4291,13 @@
         <v>151</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
@@ -4334,7 +4333,7 @@
         <v>30</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>94</v>
@@ -4397,7 +4396,7 @@
         <v>30</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>94</v>
@@ -4421,7 +4420,7 @@
         <v>81</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>109</v>
@@ -4484,7 +4483,7 @@
         <v>82</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>108</v>
@@ -4523,7 +4522,7 @@
         <v>30</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>80</v>
@@ -4550,7 +4549,7 @@
         <v>137</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G12" s="3">
         <v>6</v>
@@ -4586,7 +4585,7 @@
         <v>30</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>94</v>
@@ -4607,13 +4606,13 @@
         <v>64</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>217</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>219</v>
       </c>
       <c r="G13" s="7">
         <v>6</v>
@@ -4649,7 +4648,7 @@
         <v>30</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="S13" s="7" t="s">
         <v>94</v>
@@ -4676,7 +4675,7 @@
         <v>113</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G14" s="3">
         <v>2</v>
@@ -4712,7 +4711,7 @@
         <v>30</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>94</v>
@@ -4775,7 +4774,7 @@
         <v>120</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>94</v>
@@ -4796,13 +4795,13 @@
         <v>148</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G16" s="3">
         <v>2</v>
@@ -4838,7 +4837,7 @@
         <v>120</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>51</v>
@@ -4862,7 +4861,7 @@
         <v>90</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>89</v>
@@ -4964,7 +4963,7 @@
         <v>120</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>94</v>
@@ -4985,13 +4984,13 @@
         <v>35</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>216</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>218</v>
       </c>
       <c r="G19" s="7">
         <v>2</v>
@@ -5027,7 +5026,7 @@
         <v>30</v>
       </c>
       <c r="R19" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="S19" s="7" t="s">
         <v>94</v>
@@ -5048,13 +5047,13 @@
         <v>145</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
@@ -5090,7 +5089,7 @@
         <v>30</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>94</v>
@@ -5114,7 +5113,7 @@
         <v>16</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>15</v>
@@ -5153,7 +5152,7 @@
         <v>30</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>94</v>
@@ -5216,7 +5215,7 @@
         <v>30</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>16</v>
@@ -5240,7 +5239,7 @@
         <v>110</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>72</v>
@@ -5279,7 +5278,7 @@
         <v>60</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>94</v>
@@ -5342,7 +5341,7 @@
         <v>30</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>94</v>
@@ -5426,13 +5425,13 @@
         <v>36</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>225</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>227</v>
       </c>
       <c r="G26" s="7">
         <v>4</v>
@@ -5468,7 +5467,7 @@
         <v>30</v>
       </c>
       <c r="R26" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="S26" s="7" t="s">
         <v>94</v>
@@ -5531,7 +5530,7 @@
         <v>30</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>94</v>
@@ -5555,7 +5554,7 @@
         <v>159</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>160</v>
@@ -5594,7 +5593,7 @@
         <v>30</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>161</v>
+        <v>265</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>94</v>
@@ -5621,7 +5620,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G29" s="3">
         <v>6</v>
@@ -5657,7 +5656,7 @@
         <v>30</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>94</v>
@@ -5684,7 +5683,7 @@
         <v>22</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -5720,7 +5719,7 @@
         <v>30</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="S30" s="3" t="s">
         <v>94</v>
@@ -5747,7 +5746,7 @@
         <v>133</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -5783,7 +5782,7 @@
         <v>30</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="S31" s="3" t="s">
         <v>23</v>
@@ -5804,13 +5803,13 @@
         <v>37</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -5846,7 +5845,7 @@
         <v>30</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>23</v>
@@ -5867,13 +5866,13 @@
         <v>37</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -5909,7 +5908,7 @@
         <v>30</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>23</v>
@@ -5930,13 +5929,13 @@
         <v>37</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -5972,7 +5971,7 @@
         <v>30</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="S34" s="3" t="s">
         <v>23</v>
@@ -5993,13 +5992,13 @@
         <v>37</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -6035,7 +6034,7 @@
         <v>30</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>23</v>
@@ -6122,10 +6121,10 @@
         <v>27</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G37" s="3">
         <v>3</v>
@@ -6161,7 +6160,7 @@
         <v>30</v>
       </c>
       <c r="R37" s="4" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="S37" s="3" t="s">
         <v>94</v>
@@ -6224,7 +6223,7 @@
         <v>30</v>
       </c>
       <c r="R38" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="S38" s="7" t="s">
         <v>94</v>
@@ -6248,7 +6247,7 @@
         <v>70</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>103</v>
@@ -6371,13 +6370,13 @@
         <v>37</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="G41" s="3">
         <v>3</v>
@@ -6413,7 +6412,7 @@
         <v>60</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>94</v>
@@ -6560,13 +6559,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G44" s="7">
         <v>6</v>
@@ -6602,7 +6601,7 @@
         <v>30</v>
       </c>
       <c r="R44" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S44" s="7" t="s">
         <v>94</v>
@@ -6623,13 +6622,13 @@
         <v>66</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G45" s="7">
         <v>6</v>
@@ -6665,7 +6664,7 @@
         <v>30</v>
       </c>
       <c r="R45" s="9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="S45" s="7" t="s">
         <v>94</v>
@@ -6728,7 +6727,7 @@
         <v>30</v>
       </c>
       <c r="R46" s="4" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>94</v>
@@ -6791,7 +6790,7 @@
         <v>30</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>198</v>
+        <v>264</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>94</v>
@@ -6815,7 +6814,7 @@
         <v>144</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>143</v>
@@ -6854,7 +6853,7 @@
         <v>480</v>
       </c>
       <c r="R48" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>94</v>
@@ -6875,13 +6874,13 @@
         <v>66</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G49" s="3">
         <v>6</v>
@@ -6902,7 +6901,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="N49" s="3">
         <v>1</v>
@@ -6917,7 +6916,7 @@
         <v>30</v>
       </c>
       <c r="R49" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>94</v>
@@ -6938,13 +6937,13 @@
         <v>66</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
@@ -6980,7 +6979,7 @@
         <v>30</v>
       </c>
       <c r="R50" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="S50" s="3" t="s">
         <v>94</v>
@@ -7106,7 +7105,7 @@
         <v>30</v>
       </c>
       <c r="R52" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>94</v>
@@ -7169,7 +7168,7 @@
         <v>30</v>
       </c>
       <c r="R53" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S53" s="7" t="s">
         <v>94</v>
@@ -7295,7 +7294,7 @@
         <v>30</v>
       </c>
       <c r="R55" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="S55" s="8" t="s">
         <v>94</v>
@@ -7484,7 +7483,7 @@
         <v>120</v>
       </c>
       <c r="R58" s="4" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>94</v>
@@ -7547,7 +7546,7 @@
         <v>30</v>
       </c>
       <c r="R59" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="S59" s="7" t="s">
         <v>94</v>
@@ -7595,7 +7594,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N60">
         <v>1</v>
@@ -7610,7 +7609,7 @@
         <v>60</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S60" t="s">
         <v>94</v>
@@ -7673,7 +7672,7 @@
         <v>30</v>
       </c>
       <c r="R61" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S61" s="3" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB5B231-0D8A-47AB-B84D-2456D21E3CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495520B8-F703-4A48-9FDB-4A3E5051BCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="1035" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2385" yWindow="1575" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495520B8-F703-4A48-9FDB-4A3E5051BCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FA7D44-E40F-4697-8AB6-5690E707832E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2385" yWindow="1575" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2565" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="269">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -3389,6 +3389,14 @@
     <rPh sb="101" eb="103">
       <t>タンシュク</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill_KosuSelect</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KetteiKosu</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3823,7 +3831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:T61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -3832,14 +3840,14 @@
     <col min="6" max="6" width="19.75" customWidth="1"/>
     <col min="7" max="7" width="7.5" customWidth="1"/>
     <col min="8" max="8" width="8.125" customWidth="1"/>
-    <col min="9" max="14" width="6.75" customWidth="1"/>
-    <col min="15" max="15" width="9" customWidth="1"/>
-    <col min="16" max="16" width="10.375" customWidth="1"/>
-    <col min="17" max="17" width="7.875" customWidth="1"/>
-    <col min="18" max="18" width="25.125" customWidth="1"/>
+    <col min="9" max="15" width="6.75" customWidth="1"/>
+    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="17" max="17" width="10.375" customWidth="1"/>
+    <col min="18" max="18" width="7.875" customWidth="1"/>
+    <col min="19" max="19" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3880,28 +3888,31 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
         <f t="shared" ref="A2:A61" si="0">ROW()-2</f>
         <v>0</v>
@@ -3942,29 +3953,32 @@
       <c r="M2" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="N2" s="5">
-        <v>1</v>
+      <c r="N2" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="O2" s="5">
+        <v>1</v>
+      </c>
+      <c r="P2" s="5">
         <v>9</v>
       </c>
-      <c r="P2" s="5">
+      <c r="Q2" s="5">
         <v>100</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="R2" s="5">
         <v>30</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="S2" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="S2" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="T2" s="5">
+      <c r="T2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="U2" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -4005,29 +4019,32 @@
       <c r="M3" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N3" s="3">
-        <v>0</v>
+      <c r="N3" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O3" s="3">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3">
         <v>9</v>
       </c>
-      <c r="P3" s="3">
+      <c r="Q3" s="3">
         <v>100</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="R3" s="3">
         <v>30</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="S3" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="S3" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T3" s="3">
+      <c r="T3" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U3" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:21" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -4068,29 +4085,32 @@
       <c r="M4" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="N4" s="5">
-        <v>1</v>
+      <c r="N4" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="5">
         <v>9</v>
       </c>
-      <c r="P4" s="5">
+      <c r="Q4" s="5">
         <v>100</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="R4" s="5">
         <v>30</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="S4" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="S4" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="T4" s="5">
+      <c r="T4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="U4" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -4131,29 +4151,32 @@
       <c r="M5" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N5" s="3">
-        <v>0</v>
+      <c r="N5" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O5" s="3">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
         <v>9</v>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="3">
         <v>100</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="R5" s="3">
         <v>30</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="S5" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="S5" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T5" s="3">
+      <c r="T5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U5" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -4194,29 +4217,32 @@
       <c r="M6" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N6" s="3">
-        <v>1</v>
+      <c r="N6" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O6" s="3">
+        <v>1</v>
+      </c>
+      <c r="P6" s="3">
         <v>9</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <v>100</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="R6" s="3">
         <v>30</v>
       </c>
-      <c r="R6" s="4" t="s">
+      <c r="S6" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="S6" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T6" s="3">
+      <c r="T6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U6" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:21" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -4257,29 +4283,32 @@
       <c r="M7" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N7" s="3">
-        <v>0</v>
+      <c r="N7" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
         <v>9</v>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <v>100</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="R7" s="3">
         <v>30</v>
       </c>
-      <c r="R7" s="4" t="s">
+      <c r="S7" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="S7" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T7" s="3">
+      <c r="T7" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U7" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -4320,29 +4349,32 @@
       <c r="M8" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="N8" s="3">
-        <v>1</v>
+      <c r="N8" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="O8" s="3">
+        <v>1</v>
+      </c>
+      <c r="P8" s="3">
         <v>9</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>30</v>
       </c>
-      <c r="R8" s="4" t="s">
+      <c r="S8" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U8" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -4383,29 +4415,32 @@
       <c r="M9" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N9" s="3">
-        <v>1</v>
+      <c r="N9" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O9" s="3">
+        <v>1</v>
+      </c>
+      <c r="P9" s="3">
         <v>9</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>30</v>
       </c>
-      <c r="R9" s="4" t="s">
+      <c r="S9" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U9" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:21" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -4446,29 +4481,32 @@
       <c r="M10" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="N10" s="7">
-        <v>1</v>
+      <c r="N10" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="O10" s="7">
+        <v>1</v>
+      </c>
+      <c r="P10" s="7">
         <v>9</v>
       </c>
-      <c r="P10" s="7">
+      <c r="Q10" s="7">
         <v>100</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="R10" s="7">
         <v>30</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="S10" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="S10" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="T10" s="7">
+      <c r="T10" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U10" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -4509,29 +4547,32 @@
       <c r="M11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N11" s="3">
-        <v>1</v>
+      <c r="N11" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O11" s="3">
+        <v>1</v>
+      </c>
+      <c r="P11" s="3">
         <v>9</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <v>100</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="R11" s="3">
         <v>30</v>
       </c>
-      <c r="R11" s="4" t="s">
+      <c r="S11" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="T11" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T11" s="3">
+      <c r="U11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:20" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -4572,29 +4613,32 @@
       <c r="M12" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="N12" s="3">
-        <v>1</v>
+      <c r="N12" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="O12" s="3">
+        <v>1</v>
+      </c>
+      <c r="P12" s="3">
         <v>9</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>30</v>
       </c>
-      <c r="R12" s="4" t="s">
+      <c r="S12" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T12" s="3">
+      <c r="T12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U12" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:21" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="7">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -4635,29 +4679,32 @@
       <c r="M13" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="N13" s="7">
-        <v>1</v>
+      <c r="N13" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="O13" s="7">
+        <v>1</v>
+      </c>
+      <c r="P13" s="7">
         <v>9</v>
       </c>
-      <c r="P13" s="7">
+      <c r="Q13" s="7">
         <v>100</v>
       </c>
-      <c r="Q13" s="7">
+      <c r="R13" s="7">
         <v>30</v>
       </c>
-      <c r="R13" s="7" t="s">
+      <c r="S13" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="S13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="T13" s="7">
+      <c r="T13" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U13" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -4698,29 +4745,32 @@
       <c r="M14" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O14" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>30</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="S14" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -4761,29 +4811,32 @@
       <c r="M15" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N15" s="3">
-        <v>1</v>
+      <c r="N15" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O15" s="3">
         <v>1</v>
       </c>
       <c r="P15" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="3">
         <v>100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>120</v>
       </c>
-      <c r="R15" s="4" t="s">
+      <c r="S15" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U15" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -4824,29 +4877,32 @@
       <c r="M16" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N16" s="3">
-        <v>1</v>
+      <c r="N16" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O16" s="3">
         <v>1</v>
       </c>
       <c r="P16" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="3">
         <v>100</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="R16" s="3">
         <v>120</v>
       </c>
-      <c r="R16" s="4" t="s">
+      <c r="S16" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="S16" s="3" t="s">
+      <c r="T16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="T16" s="3">
+      <c r="U16" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:20" s="5" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:21" s="5" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -4887,29 +4943,32 @@
       <c r="M17" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="N17" s="5">
-        <v>1</v>
+      <c r="N17" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="O17" s="5">
         <v>1</v>
       </c>
       <c r="P17" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="5">
         <v>100</v>
       </c>
-      <c r="Q17" s="5">
+      <c r="R17" s="5">
         <v>120</v>
       </c>
-      <c r="R17" s="5" t="s">
+      <c r="S17" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="S17" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="T17" s="5">
+      <c r="T17" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="U17" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:20" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -4950,29 +5009,32 @@
       <c r="M18" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N18" s="3">
-        <v>1</v>
+      <c r="N18" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O18" s="3">
         <v>1</v>
       </c>
       <c r="P18" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="3">
         <v>100</v>
       </c>
-      <c r="Q18" s="3">
-        <v>120</v>
-      </c>
-      <c r="R18" s="4" t="s">
+      <c r="R18" s="3">
+        <v>30</v>
+      </c>
+      <c r="S18" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U18" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" s="7" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:21" s="7" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="7">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -5013,29 +5075,32 @@
       <c r="M19" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="N19" s="7">
-        <v>1</v>
+      <c r="N19" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="O19" s="7">
         <v>1</v>
       </c>
       <c r="P19" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="7">
         <v>100</v>
       </c>
-      <c r="Q19" s="7">
+      <c r="R19" s="7">
         <v>30</v>
       </c>
-      <c r="R19" s="7" t="s">
+      <c r="S19" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="T19" s="7">
+      <c r="T19" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U19" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:20" s="3" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:21" s="3" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -5076,29 +5141,32 @@
       <c r="M20" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>2</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>30</v>
       </c>
-      <c r="R20" s="4" t="s">
+      <c r="S20" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:20" s="3" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:21" s="3" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -5139,29 +5207,32 @@
       <c r="M21" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N21" s="3">
-        <v>1</v>
+      <c r="N21" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O21" s="3">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3">
         <v>2</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>30</v>
       </c>
-      <c r="R21" s="4" t="s">
+      <c r="S21" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U21" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -5202,29 +5273,32 @@
       <c r="M22" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N22" s="3">
-        <v>1</v>
+      <c r="N22" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O22" s="3">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3">
         <v>2</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>30</v>
       </c>
-      <c r="R22" s="4" t="s">
+      <c r="S22" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="T22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -5265,29 +5339,32 @@
       <c r="M23" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="N23" s="3">
-        <v>1</v>
+      <c r="N23" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="O23" s="3">
+        <v>1</v>
+      </c>
+      <c r="P23" s="3">
         <v>2</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>60</v>
       </c>
-      <c r="R23" s="4" t="s">
+      <c r="S23" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U23" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -5328,29 +5405,32 @@
       <c r="M24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>2</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>30</v>
       </c>
-      <c r="R24" s="4" t="s">
+      <c r="S24" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="7">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -5391,29 +5471,32 @@
       <c r="M25" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="N25" s="7">
-        <v>1</v>
+      <c r="N25" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="O25" s="7">
+        <v>1</v>
+      </c>
+      <c r="P25" s="7">
         <v>2</v>
       </c>
-      <c r="P25" s="7">
+      <c r="Q25" s="7">
         <v>100</v>
       </c>
-      <c r="Q25" s="7">
+      <c r="R25" s="7">
         <v>30</v>
       </c>
-      <c r="R25" s="9" t="s">
+      <c r="S25" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="S25" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="T25" s="7">
+      <c r="T25" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U25" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="7">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -5454,29 +5537,32 @@
       <c r="M26" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="N26" s="7">
-        <v>1</v>
+      <c r="N26" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="O26" s="7">
+        <v>1</v>
+      </c>
+      <c r="P26" s="7">
         <v>2</v>
       </c>
-      <c r="P26" s="7">
+      <c r="Q26" s="7">
         <v>100</v>
       </c>
-      <c r="Q26" s="7">
+      <c r="R26" s="7">
         <v>30</v>
       </c>
-      <c r="R26" s="9" t="s">
+      <c r="S26" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="S26" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="T26" s="7">
+      <c r="T26" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U26" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:21" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -5517,29 +5603,32 @@
       <c r="M27" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
+      <c r="N27" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>3</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>30</v>
       </c>
-      <c r="R27" s="4" t="s">
+      <c r="S27" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U27" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:21" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="3">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -5580,29 +5669,32 @@
       <c r="M28" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N28" s="3">
-        <v>0</v>
+      <c r="N28" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
         <v>3</v>
       </c>
-      <c r="P28" s="3">
+      <c r="Q28" s="3">
         <v>100</v>
       </c>
-      <c r="Q28" s="3">
+      <c r="R28" s="3">
         <v>30</v>
       </c>
-      <c r="R28" s="4" t="s">
+      <c r="S28" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="S28" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T28" s="3">
+      <c r="T28" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U28" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:21" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -5643,29 +5735,32 @@
       <c r="M29" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N29" s="3">
-        <v>1</v>
+      <c r="N29" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O29" s="3">
+        <v>1</v>
+      </c>
+      <c r="P29" s="3">
         <v>3</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>30</v>
       </c>
-      <c r="R29" s="4" t="s">
+      <c r="S29" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -5706,29 +5801,32 @@
       <c r="M30" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N30" s="3">
-        <v>1</v>
+      <c r="N30" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O30" s="3">
+        <v>1</v>
+      </c>
+      <c r="P30" s="3">
         <v>3</v>
       </c>
-      <c r="P30" s="3">
+      <c r="Q30" s="3">
         <v>100</v>
       </c>
-      <c r="Q30" s="3">
+      <c r="R30" s="3">
         <v>30</v>
       </c>
-      <c r="R30" s="4" t="s">
+      <c r="S30" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="S30" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T30" s="3">
+      <c r="T30" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U30" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -5769,29 +5867,32 @@
       <c r="M31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N31" s="3">
-        <v>1</v>
+      <c r="N31" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O31" s="3">
+        <v>1</v>
+      </c>
+      <c r="P31" s="3">
         <v>3</v>
       </c>
-      <c r="P31" s="3">
+      <c r="Q31" s="3">
         <v>100</v>
       </c>
-      <c r="Q31" s="3">
+      <c r="R31" s="3">
         <v>30</v>
       </c>
-      <c r="R31" s="4" t="s">
+      <c r="S31" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="S31" s="3" t="s">
+      <c r="T31" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T31" s="3">
+      <c r="U31" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -5832,29 +5933,32 @@
       <c r="M32" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N32" s="3">
-        <v>1</v>
+      <c r="N32" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O32" s="3">
+        <v>1</v>
+      </c>
+      <c r="P32" s="3">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>30</v>
       </c>
-      <c r="R32" s="4" t="s">
+      <c r="S32" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="S32" s="3" t="s">
+      <c r="T32" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -5895,29 +5999,32 @@
       <c r="M33" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N33" s="3">
-        <v>1</v>
+      <c r="N33" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O33" s="3">
+        <v>1</v>
+      </c>
+      <c r="P33" s="3">
         <v>3</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>30</v>
       </c>
-      <c r="R33" s="4" t="s">
+      <c r="S33" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="S33" s="3" t="s">
+      <c r="T33" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -5958,29 +6065,32 @@
       <c r="M34" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N34" s="3">
-        <v>1</v>
+      <c r="N34" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O34" s="3">
+        <v>1</v>
+      </c>
+      <c r="P34" s="3">
         <v>3</v>
       </c>
-      <c r="P34" s="3">
+      <c r="Q34" s="3">
         <v>100</v>
       </c>
-      <c r="Q34" s="3">
+      <c r="R34" s="3">
         <v>30</v>
       </c>
-      <c r="R34" s="4" t="s">
+      <c r="S34" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="S34" s="3" t="s">
+      <c r="T34" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T34" s="3">
+      <c r="U34" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -6021,29 +6131,32 @@
       <c r="M35" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N35" s="3">
-        <v>1</v>
+      <c r="N35" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O35" s="3">
+        <v>1</v>
+      </c>
+      <c r="P35" s="3">
         <v>3</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>30</v>
       </c>
-      <c r="R35" s="4" t="s">
+      <c r="S35" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="S35" s="3" t="s">
+      <c r="T35" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:20" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:21" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="7">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -6084,29 +6197,32 @@
       <c r="M36" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="N36" s="7">
-        <v>1</v>
+      <c r="N36" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="O36" s="7">
+        <v>1</v>
+      </c>
+      <c r="P36" s="7">
         <v>3</v>
       </c>
-      <c r="P36" s="7">
+      <c r="Q36" s="7">
         <v>100</v>
       </c>
-      <c r="Q36" s="7">
+      <c r="R36" s="7">
         <v>30</v>
       </c>
-      <c r="R36" s="9" t="s">
+      <c r="S36" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="S36" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="T36" s="7">
+      <c r="T36" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U36" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -6147,29 +6263,32 @@
       <c r="M37" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="N37" s="3">
-        <v>1</v>
+      <c r="N37" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="O37" s="3">
+        <v>1</v>
+      </c>
+      <c r="P37" s="3">
         <v>3</v>
       </c>
-      <c r="P37" s="3">
+      <c r="Q37" s="3">
         <v>100</v>
       </c>
-      <c r="Q37" s="3">
+      <c r="R37" s="3">
         <v>30</v>
       </c>
-      <c r="R37" s="4" t="s">
+      <c r="S37" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="S37" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T37" s="3">
+      <c r="T37" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U37" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:21" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="7">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -6210,29 +6329,32 @@
       <c r="M38" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="N38" s="7">
-        <v>1</v>
+      <c r="N38" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="O38" s="7">
+        <v>1</v>
+      </c>
+      <c r="P38" s="7">
         <v>3</v>
       </c>
-      <c r="P38" s="7">
+      <c r="Q38" s="7">
         <v>100</v>
       </c>
-      <c r="Q38" s="7">
+      <c r="R38" s="7">
         <v>30</v>
       </c>
-      <c r="R38" s="9" t="s">
+      <c r="S38" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="S38" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="T38" s="7">
+      <c r="T38" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U38" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A39" s="3">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -6273,29 +6395,32 @@
       <c r="M39" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N39" s="3">
-        <v>1</v>
+      <c r="N39" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O39" s="3">
+        <v>1</v>
+      </c>
+      <c r="P39" s="3">
         <v>3</v>
       </c>
-      <c r="P39" s="3">
+      <c r="Q39" s="3">
         <v>100</v>
       </c>
-      <c r="Q39" s="3">
-        <v>60</v>
-      </c>
-      <c r="R39" s="3" t="s">
+      <c r="R39" s="3">
+        <v>30</v>
+      </c>
+      <c r="S39" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="S39" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T39" s="3">
+      <c r="T39" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U39" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A40" s="3">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -6336,29 +6461,32 @@
       <c r="M40" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N40" s="3">
-        <v>1</v>
+      <c r="N40" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O40" s="3">
+        <v>1</v>
+      </c>
+      <c r="P40" s="3">
         <v>3</v>
       </c>
-      <c r="P40" s="3">
+      <c r="Q40" s="3">
         <v>100</v>
       </c>
-      <c r="Q40" s="3">
-        <v>60</v>
-      </c>
-      <c r="R40" s="3" t="s">
+      <c r="R40" s="3">
+        <v>30</v>
+      </c>
+      <c r="S40" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="S40" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T40" s="3">
+      <c r="T40" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U40" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A41" s="3">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -6399,29 +6527,32 @@
       <c r="M41" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N41" s="3">
-        <v>1</v>
+      <c r="N41" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O41" s="3">
+        <v>1</v>
+      </c>
+      <c r="P41" s="3">
         <v>3</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>100</v>
       </c>
-      <c r="Q41" s="3">
-        <v>60</v>
-      </c>
-      <c r="R41" s="3" t="s">
+      <c r="R41" s="3">
+        <v>30</v>
+      </c>
+      <c r="S41" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T41" s="3">
+      <c r="T41" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U41" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A42" s="3">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -6462,29 +6593,32 @@
       <c r="M42" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N42" s="3">
-        <v>1</v>
+      <c r="N42" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O42" s="3">
+        <v>1</v>
+      </c>
+      <c r="P42" s="3">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>100</v>
       </c>
-      <c r="Q42" s="3">
-        <v>60</v>
-      </c>
-      <c r="R42" s="3" t="s">
+      <c r="R42" s="3">
+        <v>30</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T42" s="3">
+      <c r="T42" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U42" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A43" s="5">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -6525,29 +6659,32 @@
       <c r="M43" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="N43" s="5">
-        <v>1</v>
+      <c r="N43" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="O43" s="5">
+        <v>1</v>
+      </c>
+      <c r="P43" s="5">
         <v>3</v>
       </c>
-      <c r="P43" s="5">
+      <c r="Q43" s="5">
         <v>100</v>
       </c>
-      <c r="Q43" s="5">
+      <c r="R43" s="5">
         <v>30</v>
       </c>
-      <c r="R43" s="5" t="s">
+      <c r="S43" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="S43" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="T43" s="5">
+      <c r="T43" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="U43" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:20" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:21" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="7">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -6588,29 +6725,32 @@
       <c r="M44" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="N44" s="7">
-        <v>1</v>
+      <c r="N44" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="O44" s="7">
+        <v>1</v>
+      </c>
+      <c r="P44" s="7">
         <v>3</v>
       </c>
-      <c r="P44" s="7">
+      <c r="Q44" s="7">
         <v>100</v>
       </c>
-      <c r="Q44" s="7">
+      <c r="R44" s="7">
         <v>30</v>
       </c>
-      <c r="R44" s="9" t="s">
+      <c r="S44" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="S44" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="T44" s="7">
+      <c r="T44" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U44" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:20" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="7">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -6651,29 +6791,32 @@
       <c r="M45" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="N45" s="7">
-        <v>0</v>
+      <c r="N45" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="O45" s="7">
+        <v>0</v>
+      </c>
+      <c r="P45" s="7">
         <v>4</v>
       </c>
-      <c r="P45" s="7">
+      <c r="Q45" s="7">
         <v>100</v>
       </c>
-      <c r="Q45" s="7">
+      <c r="R45" s="7">
         <v>30</v>
       </c>
-      <c r="R45" s="9" t="s">
+      <c r="S45" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="S45" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="T45" s="7">
+      <c r="T45" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U45" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:20" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="3">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -6714,29 +6857,32 @@
       <c r="M46" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="N46" s="3">
-        <v>1</v>
+      <c r="N46" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="O46" s="3">
+        <v>1</v>
+      </c>
+      <c r="P46" s="3">
         <v>4</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>30</v>
       </c>
-      <c r="R46" s="4" t="s">
+      <c r="S46" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U46" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:20" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="3">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -6777,29 +6923,32 @@
       <c r="M47" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N47" s="3">
-        <v>1</v>
+      <c r="N47" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O47" s="3">
+        <v>1</v>
+      </c>
+      <c r="P47" s="3">
         <v>4</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>30</v>
       </c>
-      <c r="R47" s="4" t="s">
+      <c r="S47" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U47" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:20" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="3">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -6840,29 +6989,32 @@
       <c r="M48" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N48" s="3">
-        <v>1</v>
+      <c r="N48" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O48" s="3">
+        <v>1</v>
+      </c>
+      <c r="P48" s="3">
         <v>4</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>480</v>
       </c>
-      <c r="R48" s="4" t="s">
+      <c r="S48" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U48" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:20" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -6903,29 +7055,32 @@
       <c r="M49" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="N49" s="3">
-        <v>1</v>
+      <c r="N49" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O49" s="3">
+        <v>1</v>
+      </c>
+      <c r="P49" s="3">
         <v>4</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>30</v>
       </c>
-      <c r="R49" s="4" t="s">
+      <c r="S49" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T49" s="3">
+      <c r="T49" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U49" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:20" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="3">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -6966,29 +7121,32 @@
       <c r="M50" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N50" s="3">
-        <v>1</v>
+      <c r="N50" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="O50" s="3">
+        <v>1</v>
+      </c>
+      <c r="P50" s="3">
         <v>4</v>
       </c>
-      <c r="P50" s="3">
+      <c r="Q50" s="3">
         <v>100</v>
       </c>
-      <c r="Q50" s="3">
+      <c r="R50" s="3">
         <v>30</v>
       </c>
-      <c r="R50" s="4" t="s">
+      <c r="S50" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="S50" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T50" s="3">
+      <c r="T50" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U50" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A51" s="7">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -7029,29 +7187,32 @@
       <c r="M51" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="N51" s="7">
-        <v>1</v>
+      <c r="N51" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="O51" s="7">
+        <v>1</v>
+      </c>
+      <c r="P51" s="7">
         <v>5</v>
       </c>
-      <c r="P51" s="7">
+      <c r="Q51" s="7">
         <v>100</v>
       </c>
-      <c r="Q51" s="7">
+      <c r="R51" s="7">
         <v>30</v>
       </c>
-      <c r="R51" s="7" t="s">
+      <c r="S51" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="S51" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="T51" s="7">
+      <c r="T51" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U51" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:20" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:21" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -7092,29 +7253,32 @@
       <c r="M52" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N52" s="3">
-        <v>1</v>
+      <c r="N52" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O52" s="3">
+        <v>1</v>
+      </c>
+      <c r="P52" s="3">
         <v>5</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30</v>
       </c>
-      <c r="R52" s="4" t="s">
+      <c r="S52" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A53" s="7">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -7155,29 +7319,32 @@
       <c r="M53" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="N53" s="7">
-        <v>1</v>
+      <c r="N53" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="O53" s="7">
+        <v>1</v>
+      </c>
+      <c r="P53" s="7">
         <v>5</v>
       </c>
-      <c r="P53" s="7">
+      <c r="Q53" s="7">
         <v>100</v>
       </c>
-      <c r="Q53" s="7">
+      <c r="R53" s="7">
         <v>30</v>
       </c>
-      <c r="R53" s="7" t="s">
+      <c r="S53" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="S53" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="T53" s="7">
+      <c r="T53" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U53" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A54" s="8">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -7218,29 +7385,32 @@
       <c r="M54" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="N54" s="8">
-        <v>1</v>
+      <c r="N54" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="O54" s="8">
+        <v>1</v>
+      </c>
+      <c r="P54" s="8">
         <v>6</v>
       </c>
-      <c r="P54" s="8">
+      <c r="Q54" s="8">
         <v>100</v>
       </c>
-      <c r="Q54" s="8">
+      <c r="R54" s="8">
         <v>30</v>
       </c>
-      <c r="R54" s="8" t="s">
+      <c r="S54" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="S54" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="T54" s="8">
+      <c r="T54" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="U54" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:20" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:21" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="8">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -7281,29 +7451,32 @@
       <c r="M55" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="N55" s="8">
-        <v>1</v>
+      <c r="N55" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="O55" s="8">
+        <v>1</v>
+      </c>
+      <c r="P55" s="8">
         <v>6</v>
       </c>
-      <c r="P55" s="8">
+      <c r="Q55" s="8">
         <v>100</v>
       </c>
-      <c r="Q55" s="8">
+      <c r="R55" s="8">
         <v>30</v>
       </c>
-      <c r="R55" s="10" t="s">
+      <c r="S55" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="S55" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="T55" s="8">
+      <c r="T55" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="U55" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A56" s="8">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -7344,29 +7517,32 @@
       <c r="M56" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="N56" s="8">
-        <v>1</v>
+      <c r="N56" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="O56" s="8">
+        <v>1</v>
+      </c>
+      <c r="P56" s="8">
         <v>7</v>
       </c>
-      <c r="P56" s="8">
+      <c r="Q56" s="8">
         <v>100</v>
       </c>
-      <c r="Q56" s="8">
+      <c r="R56" s="8">
         <v>30</v>
       </c>
-      <c r="R56" s="8" t="s">
+      <c r="S56" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="S56" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="T56" s="8">
+      <c r="T56" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="U56" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:20" s="8" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A57" s="8">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -7407,29 +7583,32 @@
       <c r="M57" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="N57" s="8">
-        <v>1</v>
+      <c r="N57" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="O57" s="8">
+        <v>1</v>
+      </c>
+      <c r="P57" s="8">
         <v>7</v>
       </c>
-      <c r="P57" s="8">
+      <c r="Q57" s="8">
         <v>100</v>
       </c>
-      <c r="Q57" s="8">
+      <c r="R57" s="8">
         <v>30</v>
       </c>
-      <c r="R57" s="8" t="s">
+      <c r="S57" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="S57" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="T57" s="8">
+      <c r="T57" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="U57" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:21" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="3">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -7470,29 +7649,32 @@
       <c r="M58" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="N58" s="3">
-        <v>1</v>
+      <c r="N58" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="O58" s="3">
+        <v>1</v>
+      </c>
+      <c r="P58" s="3">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>120</v>
       </c>
-      <c r="R58" s="4" t="s">
+      <c r="S58" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="7">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -7533,29 +7715,32 @@
       <c r="M59" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="N59" s="7">
-        <v>1</v>
+      <c r="N59" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="O59" s="7">
+        <v>1</v>
+      </c>
+      <c r="P59" s="7">
         <v>8</v>
       </c>
-      <c r="P59" s="7">
+      <c r="Q59" s="7">
         <v>100</v>
       </c>
-      <c r="Q59" s="7">
+      <c r="R59" s="7">
         <v>30</v>
       </c>
-      <c r="R59" s="9" t="s">
+      <c r="S59" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="S59" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="T59" s="7">
+      <c r="T59" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U59" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -7596,29 +7781,32 @@
       <c r="M60" t="s">
         <v>247</v>
       </c>
-      <c r="N60">
-        <v>1</v>
+      <c r="N60" t="s">
+        <v>94</v>
       </c>
       <c r="O60">
+        <v>1</v>
+      </c>
+      <c r="P60">
         <v>8</v>
       </c>
-      <c r="P60">
+      <c r="Q60">
         <v>100</v>
       </c>
-      <c r="Q60">
+      <c r="R60">
         <v>60</v>
       </c>
-      <c r="R60" s="2" t="s">
+      <c r="S60" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="S60" t="s">
-        <v>94</v>
-      </c>
-      <c r="T60">
+      <c r="T60" t="s">
+        <v>94</v>
+      </c>
+      <c r="U60">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:20" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:21" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="3">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -7659,25 +7847,28 @@
       <c r="M61" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N61" s="3">
-        <v>1</v>
+      <c r="N61" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="O61" s="3">
+        <v>1</v>
+      </c>
+      <c r="P61" s="3">
         <v>8</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>30</v>
       </c>
-      <c r="R61" s="4" t="s">
+      <c r="S61" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="S61" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="T61" s="3">
+      <c r="T61" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U61" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47FA7D44-E40F-4697-8AB6-5690E707832E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B1F09B-DDAB-43D0-8252-A83A82A535F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2505" yWindow="855" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="270">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -704,52 +704,6 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>ゾウケイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>水あめ、チョコレートをペンギンの形にする。</t>
-    <rPh sb="0" eb="1">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>カタチ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>水あめ、チョコレートをくまの形にする。</t>
-    <rPh sb="0" eb="1">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>カタチ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>水あめ、チョコレートを天使の羽の形にする。</t>
-    <rPh sb="0" eb="1">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>テンシ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ハネ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>カタチ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>水あめ、チョコレートをウサギの形にする。</t>
-    <rPh sb="0" eb="1">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>カタチ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1981,16 +1935,6 @@
     <t>ねこさんの造形</t>
     <rPh sb="5" eb="7">
       <t>ゾウケイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>水あめ、チョコレートをねこの形にする。</t>
-    <rPh sb="0" eb="1">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>カタチ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2921,46 +2865,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>水あめ・チョコレートにかけると、羽飾りに変形する。
-派生：
-LV1で、各ウィンド系の魔法の習得可</t>
-    <rPh sb="0" eb="1">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ハネ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ハセイ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>マホウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>水あめやチョコレートにかけると、羽飾りを作る。</t>
-    <rPh sb="0" eb="1">
-      <t>ミズ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ハネ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>カザ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>あわあわ・デコレーション</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3253,9 +3157,158 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>チョコレートについて勉強することで、よりなめらかなチョコレートを仕上げるようになる。
-LVに応じて、成功率が上がる。
+    <t>コーヒー・カフェラテについて勉強する。
+カフェラテの仕上げに魔法をかけることで、
+ミルクにかわいい絵柄を描ける。
+失敗することもある。
+習得時、コーヒー系の
+LV1: 見た目+30
+LV2: 見た目+60
+LV3: 見た目+90</t>
+    <rPh sb="14" eb="16">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>エガラ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="70" eb="73">
+      <t>シュウトクジ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生地をきれいに混ぜる技術を磨く。
+クレープ生地やケーキ生地など生地系の品質を、少しだけ底上げする。</t>
+    <rPh sb="22" eb="24">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ソコア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill_KosuSelect</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>KetteiKosu</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アイス水溶液に魔法をかけながら混ぜて、アイスクリーム制作時の成功率アップ・制作時間を少し短縮する。
+習得するだけでOK。
+LVに応じて、ほんのわずかになめらかさを出す。
+LV1: 成功率+2, 時間短縮+10%
+LV2: 成功率+4, 時間短縮+20%
+LV3: 成功率+6, 時間短縮+30%
+LV4: 成功率+8, 時間短縮+40%
+LV5: 成功率+10, 時間短縮+50%</t>
+    <rPh sb="26" eb="29">
+      <t>セイサクジ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>シュウトク</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="82" eb="83">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="92" eb="95">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコレートをペンギンの形にする。</t>
+    <rPh sb="12" eb="13">
+      <t>カタチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコレートをくまの形にする。</t>
+    <rPh sb="10" eb="11">
+      <t>カタチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコレートをねこの形にする。</t>
+    <rPh sb="10" eb="11">
+      <t>カタチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコレートをウサギの形にする。</t>
+    <rPh sb="11" eb="12">
+      <t>カタチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコレートを天使の羽の形にする。</t>
+    <rPh sb="7" eb="9">
+      <t>テンシ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ハネ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カタチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコレートについて勉強する。
+LVに応じて、成功率が上がり、チョコレート制作時の時間を短縮する。
 また、ほんの少しなめらか感を上昇する。
+テンパリング時の品質もアップする。
 LV1: 成功率+2%
 LV2: 成功率+4%
 LV3: 成功率+6%
@@ -3269,134 +3322,107 @@
     <rPh sb="10" eb="12">
       <t>ベンキョウ</t>
     </rPh>
-    <rPh sb="46" eb="47">
+    <rPh sb="19" eb="20">
       <t>オウ</t>
     </rPh>
-    <rPh sb="50" eb="53">
+    <rPh sb="23" eb="26">
       <t>セイコウリツ</t>
     </rPh>
-    <rPh sb="54" eb="55">
+    <rPh sb="27" eb="28">
       <t>ア</t>
     </rPh>
-    <rPh sb="65" eb="66">
+    <rPh sb="37" eb="40">
+      <t>セイサクジ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>タンシュク</t>
+    </rPh>
+    <rPh sb="56" eb="57">
       <t>スコ</t>
     </rPh>
-    <rPh sb="71" eb="72">
+    <rPh sb="62" eb="63">
       <t>カン</t>
     </rPh>
-    <rPh sb="73" eb="75">
+    <rPh sb="64" eb="66">
       <t>ジョウショウ</t>
     </rPh>
-    <rPh sb="85" eb="88">
+    <rPh sb="76" eb="77">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="94" eb="97">
       <t>セイコウリツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>コーヒー・カフェラテについて勉強する。
-カフェラテの仕上げに魔法をかけることで、
-ミルクにかわいい絵柄を描ける。
-失敗することもある。
-習得時、コーヒー系の
-LV1: 見た目+30
-LV2: 見た目+60
-LV3: 見た目+90</t>
-    <rPh sb="14" eb="16">
-      <t>ベンキョウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="31" eb="33">
+    <t>チョコレートをくまさんの形にする。
+おかしに子供っぽさを足すことができる。
+ブラックとホワイト2種類がある。</t>
+    <rPh sb="12" eb="13">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生地や液体チョコレートにかけると、ふわふわ感をアップする。</t>
+    <rPh sb="0" eb="2">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生地や液体チョコレートにかけると、ふわふわ感をアップする。
+LVが上がると、効果もアップする。
+派生：
+LV1で、各ウィンド系の魔法の習得可</t>
+    <rPh sb="0" eb="2">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ハセイ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
       <t>マホウ</t>
     </rPh>
-    <rPh sb="50" eb="52">
-      <t>エガラ</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="70" eb="73">
-      <t>シュウトクジ</t>
-    </rPh>
-    <rPh sb="78" eb="79">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="86" eb="87">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="88" eb="89">
-      <t>メ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>生地をきれいに混ぜる技術を磨く。
-クレープ生地やケーキ生地など生地系の品質を、少しだけ底上げする。</t>
-    <rPh sb="22" eb="24">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ヒンシツ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ソコア</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アイス水溶液に魔法をかけながら混ぜて、アイスクリーム制作時の成功率アップ・制作時間を少し短縮する。
-習得するだけでOK。
-LVに応じて、ほんのわずかになめらかさを出す。
-LV1: 成功率+2, 時間短縮+4%
-LV2: 成功率+4, 時間短縮+8%
-LV3: 成功率+6, 時間短縮+12%
-LV4: 成功率+8, 時間短縮+16%
-LV5: 成功率+10, 時間短縮+20%</t>
-    <rPh sb="26" eb="29">
-      <t>セイサクジ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>シュウトク</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="82" eb="83">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="92" eb="95">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="99" eb="101">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>タンシュク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>skill_KosuSelect</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>KetteiKosu</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3888,7 +3914,7 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -3906,10 +3932,10 @@
         <v>53</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -3927,7 +3953,7 @@
         <v>17</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>14</v>
@@ -3969,7 +3995,7 @@
         <v>30</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="T2" s="5" t="s">
         <v>94</v>
@@ -3987,16 +4013,16 @@
         <v>1002</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>54</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G3" s="3">
         <v>6</v>
@@ -4035,7 +4061,7 @@
         <v>30</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>94</v>
@@ -4059,7 +4085,7 @@
         <v>76</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>83</v>
@@ -4101,7 +4127,7 @@
         <v>30</v>
       </c>
       <c r="S4" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="T4" s="5" t="s">
         <v>94</v>
@@ -4119,16 +4145,16 @@
         <v>1010</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G5" s="3">
         <v>6</v>
@@ -4167,7 +4193,7 @@
         <v>30</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>94</v>
@@ -4233,7 +4259,7 @@
         <v>30</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="T6" s="3" t="s">
         <v>94</v>
@@ -4251,7 +4277,7 @@
         <v>1004</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>61</v>
@@ -4299,7 +4325,7 @@
         <v>30</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="T7" s="3" t="s">
         <v>94</v>
@@ -4317,16 +4343,16 @@
         <v>1006</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
@@ -4347,10 +4373,10 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O8" s="3">
         <v>1</v>
@@ -4365,7 +4391,7 @@
         <v>30</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>94</v>
@@ -4383,7 +4409,7 @@
         <v>1006</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>80</v>
@@ -4416,7 +4442,7 @@
         <v>94</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="O9" s="3">
         <v>1</v>
@@ -4431,7 +4457,7 @@
         <v>30</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>94</v>
@@ -4455,10 +4481,10 @@
         <v>81</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G10" s="7">
         <v>6</v>
@@ -4497,7 +4523,7 @@
         <v>30</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="T10" s="7" t="s">
         <v>94</v>
@@ -4521,10 +4547,10 @@
         <v>82</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G11" s="3">
         <v>6</v>
@@ -4539,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="3">
         <v>0</v>
@@ -4563,7 +4589,7 @@
         <v>30</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="T11" s="3" t="s">
         <v>80</v>
@@ -4584,13 +4610,13 @@
         <v>64</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G12" s="3">
         <v>6</v>
@@ -4611,10 +4637,10 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O12" s="3">
         <v>1</v>
@@ -4629,7 +4655,7 @@
         <v>30</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>94</v>
@@ -4650,13 +4676,13 @@
         <v>64</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G13" s="7">
         <v>6</v>
@@ -4695,7 +4721,7 @@
         <v>30</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="T13" s="7" t="s">
         <v>94</v>
@@ -4716,13 +4742,13 @@
         <v>35</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G14" s="3">
         <v>2</v>
@@ -4761,7 +4787,7 @@
         <v>30</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>94</v>
@@ -4779,7 +4805,7 @@
         <v>2001</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>51</v>
@@ -4827,7 +4853,7 @@
         <v>120</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>94</v>
@@ -4845,16 +4871,16 @@
         <v>2001</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G16" s="3">
         <v>2</v>
@@ -4893,7 +4919,7 @@
         <v>120</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="T16" s="3" t="s">
         <v>51</v>
@@ -4917,7 +4943,7 @@
         <v>90</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>89</v>
@@ -4980,13 +5006,13 @@
         <v>35</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G18" s="3">
         <v>2</v>
@@ -5025,7 +5051,7 @@
         <v>30</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>94</v>
@@ -5046,13 +5072,13 @@
         <v>35</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="G19" s="7">
         <v>2</v>
@@ -5091,7 +5117,7 @@
         <v>30</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="T19" s="7" t="s">
         <v>94</v>
@@ -5109,16 +5135,16 @@
         <v>3006</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
@@ -5157,7 +5183,7 @@
         <v>30</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>94</v>
@@ -5175,13 +5201,13 @@
         <v>3001</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>15</v>
@@ -5208,7 +5234,7 @@
         <v>94</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="O21" s="3">
         <v>1</v>
@@ -5223,7 +5249,7 @@
         <v>30</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>94</v>
@@ -5241,7 +5267,7 @@
         <v>3002</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>20</v>
@@ -5274,7 +5300,7 @@
         <v>94</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="O22" s="3">
         <v>1</v>
@@ -5289,7 +5315,7 @@
         <v>30</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>16</v>
@@ -5310,10 +5336,10 @@
         <v>36</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>72</v>
@@ -5337,10 +5363,10 @@
         <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O23" s="3">
         <v>1</v>
@@ -5355,7 +5381,7 @@
         <v>60</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>94</v>
@@ -5376,13 +5402,13 @@
         <v>36</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G24" s="3">
         <v>4</v>
@@ -5421,7 +5447,7 @@
         <v>30</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>94</v>
@@ -5442,13 +5468,13 @@
         <v>36</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G25" s="7">
         <v>4</v>
@@ -5487,7 +5513,7 @@
         <v>30</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="T25" s="7" t="s">
         <v>94</v>
@@ -5508,13 +5534,13 @@
         <v>36</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G26" s="7">
         <v>4</v>
@@ -5553,7 +5579,7 @@
         <v>30</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="T26" s="7" t="s">
         <v>94</v>
@@ -5574,13 +5600,13 @@
         <v>37</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G27" s="3">
         <v>6</v>
@@ -5619,7 +5645,7 @@
         <v>30</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>94</v>
@@ -5640,13 +5666,13 @@
         <v>37</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G28" s="3">
         <v>6</v>
@@ -5685,7 +5711,7 @@
         <v>30</v>
       </c>
       <c r="S28" s="4" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="T28" s="3" t="s">
         <v>94</v>
@@ -5712,7 +5738,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="G29" s="3">
         <v>6</v>
@@ -5733,10 +5759,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>268</v>
+        <v>136</v>
       </c>
       <c r="O29" s="3">
         <v>1</v>
@@ -5745,13 +5771,13 @@
         <v>3</v>
       </c>
       <c r="Q29" s="3">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="R29" s="3">
         <v>30</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>94</v>
@@ -5778,7 +5804,7 @@
         <v>22</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -5802,7 +5828,7 @@
         <v>94</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="O30" s="3">
         <v>1</v>
@@ -5817,7 +5843,7 @@
         <v>30</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="T30" s="3" t="s">
         <v>94</v>
@@ -5838,13 +5864,13 @@
         <v>37</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -5868,7 +5894,7 @@
         <v>94</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="O31" s="3">
         <v>1</v>
@@ -5883,7 +5909,7 @@
         <v>30</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="T31" s="3" t="s">
         <v>23</v>
@@ -5904,13 +5930,13 @@
         <v>37</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -5934,7 +5960,7 @@
         <v>94</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="O32" s="3">
         <v>1</v>
@@ -5949,7 +5975,7 @@
         <v>30</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>23</v>
@@ -5970,13 +5996,13 @@
         <v>37</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -5991,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L33" s="3">
         <v>0</v>
@@ -6000,7 +6026,7 @@
         <v>94</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="O33" s="3">
         <v>1</v>
@@ -6015,7 +6041,7 @@
         <v>30</v>
       </c>
       <c r="S33" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>23</v>
@@ -6036,13 +6062,13 @@
         <v>37</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -6066,7 +6092,7 @@
         <v>94</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="O34" s="3">
         <v>1</v>
@@ -6081,7 +6107,7 @@
         <v>30</v>
       </c>
       <c r="S34" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="T34" s="3" t="s">
         <v>23</v>
@@ -6102,13 +6128,13 @@
         <v>37</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -6132,7 +6158,7 @@
         <v>94</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="O35" s="3">
         <v>1</v>
@@ -6147,7 +6173,7 @@
         <v>30</v>
       </c>
       <c r="S35" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>23</v>
@@ -6213,7 +6239,7 @@
         <v>30</v>
       </c>
       <c r="S36" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="T36" s="7" t="s">
         <v>94</v>
@@ -6237,10 +6263,10 @@
         <v>27</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G37" s="3">
         <v>3</v>
@@ -6261,10 +6287,10 @@
         <v>0</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O37" s="3">
         <v>1</v>
@@ -6279,7 +6305,7 @@
         <v>30</v>
       </c>
       <c r="S37" s="4" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="T37" s="3" t="s">
         <v>94</v>
@@ -6345,7 +6371,7 @@
         <v>30</v>
       </c>
       <c r="S38" s="9" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="T38" s="7" t="s">
         <v>94</v>
@@ -6354,73 +6380,73 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="3">
+    <row r="39" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="7">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="7">
         <v>4006</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G39" s="3">
+      <c r="E39" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="G39" s="7">
         <v>3</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39" s="7">
         <v>5</v>
       </c>
-      <c r="I39" s="3">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3">
-        <v>0</v>
-      </c>
-      <c r="K39" s="3">
+      <c r="I39" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J39" s="7">
+        <v>0</v>
+      </c>
+      <c r="K39" s="7">
         <v>3</v>
       </c>
-      <c r="L39" s="3">
-        <v>0</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="O39" s="3">
-        <v>1</v>
-      </c>
-      <c r="P39" s="3">
+      <c r="L39" s="7">
+        <v>0</v>
+      </c>
+      <c r="M39" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="O39" s="7">
+        <v>1</v>
+      </c>
+      <c r="P39" s="7">
         <v>3</v>
       </c>
-      <c r="Q39" s="3">
+      <c r="Q39" s="7">
         <v>100</v>
       </c>
-      <c r="R39" s="3">
+      <c r="R39" s="7">
         <v>30</v>
       </c>
-      <c r="S39" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="T39" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U39" s="3">
+      <c r="S39" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="T39" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U39" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:21" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="3">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -6438,7 +6464,7 @@
         <v>87</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>104</v>
+        <v>262</v>
       </c>
       <c r="G40" s="3">
         <v>3</v>
@@ -6453,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="K40" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L40" s="3">
         <v>0</v>
@@ -6462,7 +6488,7 @@
         <v>94</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="O40" s="3">
         <v>1</v>
@@ -6476,8 +6502,8 @@
       <c r="R40" s="3">
         <v>30</v>
       </c>
-      <c r="S40" s="3" t="s">
-        <v>104</v>
+      <c r="S40" s="4" t="s">
+        <v>267</v>
       </c>
       <c r="T40" s="3" t="s">
         <v>94</v>
@@ -6486,201 +6512,201 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="3">
+    <row r="41" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="7">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="7">
         <v>4007</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="D41" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="G41" s="7">
         <v>3</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="7">
         <v>5</v>
       </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="I41" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J41" s="7">
+        <v>0</v>
+      </c>
+      <c r="K41" s="7">
         <v>3</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="O41" s="3">
-        <v>1</v>
-      </c>
-      <c r="P41" s="3">
+      <c r="L41" s="7">
+        <v>0</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="O41" s="7">
+        <v>1</v>
+      </c>
+      <c r="P41" s="7">
         <v>3</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="7">
         <v>100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="R41" s="7">
         <v>30</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U41" s="3">
+      <c r="S41" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="T41" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U41" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="3">
+    <row r="42" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="7">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="7">
         <v>4008</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="F42" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="G42" s="7">
         <v>3</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42" s="7">
         <v>5</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
+      <c r="I42" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J42" s="7">
+        <v>0</v>
+      </c>
+      <c r="K42" s="7">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="O42" s="3">
-        <v>1</v>
-      </c>
-      <c r="P42" s="3">
+      <c r="L42" s="7">
+        <v>0</v>
+      </c>
+      <c r="M42" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N42" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="O42" s="7">
+        <v>1</v>
+      </c>
+      <c r="P42" s="7">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="Q42" s="7">
         <v>100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="R42" s="7">
         <v>30</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U42" s="3">
+      <c r="S42" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="T42" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U42" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="5">
+    <row r="43" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="7">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="7">
         <v>4009</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="E43" s="5" t="s">
+      <c r="D43" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E43" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="G43" s="5">
+      <c r="F43" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="G43" s="7">
         <v>3</v>
       </c>
-      <c r="H43" s="5">
+      <c r="H43" s="7">
         <v>8</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I43" s="7">
         <v>9999</v>
       </c>
-      <c r="J43" s="5">
-        <v>0</v>
-      </c>
-      <c r="K43" s="5">
+      <c r="J43" s="7">
+        <v>0</v>
+      </c>
+      <c r="K43" s="7">
         <v>3</v>
       </c>
-      <c r="L43" s="5">
-        <v>0</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N43" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O43" s="5">
-        <v>1</v>
-      </c>
-      <c r="P43" s="5">
+      <c r="L43" s="7">
+        <v>0</v>
+      </c>
+      <c r="M43" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N43" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O43" s="7">
+        <v>1</v>
+      </c>
+      <c r="P43" s="7">
         <v>3</v>
       </c>
-      <c r="Q43" s="5">
+      <c r="Q43" s="7">
         <v>100</v>
       </c>
-      <c r="R43" s="5">
+      <c r="R43" s="7">
         <v>30</v>
       </c>
-      <c r="S43" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="T43" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="U43" s="5">
+      <c r="S43" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="T43" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U43" s="7">
         <v>0</v>
       </c>
     </row>
@@ -6696,13 +6722,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G44" s="7">
         <v>6</v>
@@ -6741,7 +6767,7 @@
         <v>30</v>
       </c>
       <c r="S44" s="9" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="T44" s="7" t="s">
         <v>94</v>
@@ -6762,13 +6788,13 @@
         <v>66</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G45" s="7">
         <v>6</v>
@@ -6807,7 +6833,7 @@
         <v>30</v>
       </c>
       <c r="S45" s="9" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="T45" s="7" t="s">
         <v>94</v>
@@ -6834,7 +6860,7 @@
         <v>38</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G46" s="3">
         <v>6</v>
@@ -6855,10 +6881,10 @@
         <v>0</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O46" s="3">
         <v>1</v>
@@ -6873,7 +6899,7 @@
         <v>30</v>
       </c>
       <c r="S46" s="4" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>94</v>
@@ -6894,13 +6920,13 @@
         <v>66</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G47" s="3">
         <v>6</v>
@@ -6939,7 +6965,7 @@
         <v>30</v>
       </c>
       <c r="S47" s="4" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>94</v>
@@ -6960,13 +6986,13 @@
         <v>66</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G48" s="3">
         <v>6</v>
@@ -7005,7 +7031,7 @@
         <v>480</v>
       </c>
       <c r="S48" s="4" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>94</v>
@@ -7026,13 +7052,13 @@
         <v>66</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G49" s="3">
         <v>6</v>
@@ -7053,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>94</v>
@@ -7071,7 +7097,7 @@
         <v>30</v>
       </c>
       <c r="S49" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>94</v>
@@ -7092,13 +7118,13 @@
         <v>66</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
@@ -7122,7 +7148,7 @@
         <v>94</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="O50" s="3">
         <v>1</v>
@@ -7137,7 +7163,7 @@
         <v>30</v>
       </c>
       <c r="S50" s="4" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="T50" s="3" t="s">
         <v>94</v>
@@ -7158,10 +7184,10 @@
         <v>65</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>41</v>
@@ -7269,7 +7295,7 @@
         <v>30</v>
       </c>
       <c r="S52" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>94</v>
@@ -7287,7 +7313,7 @@
         <v>6003</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>42</v>
@@ -7335,7 +7361,7 @@
         <v>30</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="T53" s="7" t="s">
         <v>94</v>
@@ -7467,7 +7493,7 @@
         <v>30</v>
       </c>
       <c r="S55" s="10" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="T55" s="8" t="s">
         <v>94</v>
@@ -7647,10 +7673,10 @@
         <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O58" s="3">
         <v>1</v>
@@ -7665,7 +7691,7 @@
         <v>120</v>
       </c>
       <c r="S58" s="4" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>94</v>
@@ -7731,7 +7757,7 @@
         <v>30</v>
       </c>
       <c r="S59" s="9" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="T59" s="7" t="s">
         <v>94</v>
@@ -7779,7 +7805,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="N60" t="s">
         <v>94</v>
@@ -7797,7 +7823,7 @@
         <v>60</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="T60" t="s">
         <v>94</v>
@@ -7818,10 +7844,10 @@
         <v>68</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>91</v>
@@ -7863,7 +7889,7 @@
         <v>30</v>
       </c>
       <c r="S61" s="4" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="T61" s="3" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B1F09B-DDAB-43D0-8252-A83A82A535F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D234B2-1A59-4BC4-A730-20798634EECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2505" yWindow="855" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
@@ -3305,10 +3305,75 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>チョコレートをくまさんの形にする。
+おかしに子供っぽさを足すことができる。
+ブラックとホワイト2種類がある。</t>
+    <rPh sb="12" eb="13">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生地や液体チョコレートにかけると、ふわふわ感をアップする。</t>
+    <rPh sb="0" eb="2">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生地や液体チョコレートにかけると、ふわふわ感をアップする。
+LVが上がると、効果もアップする。
+派生：
+LV1で、各ウィンド系の魔法の習得可</t>
+    <rPh sb="0" eb="2">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ハセイ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>チョコレートについて勉強する。
 LVに応じて、成功率が上がり、チョコレート制作時の時間を短縮する。
 また、ほんの少しなめらか感を上昇する。
-テンパリング時の品質もアップする。
+さらに、「テンパリング」時の食感もアップする。
 LV1: 成功率+2%
 LV2: 成功率+4%
 LV3: 成功率+6%
@@ -3349,79 +3414,14 @@
     <rPh sb="64" eb="66">
       <t>ジョウショウ</t>
     </rPh>
-    <rPh sb="76" eb="77">
+    <rPh sb="83" eb="84">
       <t>ジ</t>
     </rPh>
-    <rPh sb="78" eb="80">
-      <t>ヒンシツ</t>
-    </rPh>
-    <rPh sb="94" eb="97">
+    <rPh sb="85" eb="87">
+      <t>ショクカン</t>
+    </rPh>
+    <rPh sb="101" eb="104">
       <t>セイコウリツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>チョコレートをくまさんの形にする。
-おかしに子供っぽさを足すことができる。
-ブラックとホワイト2種類がある。</t>
-    <rPh sb="12" eb="13">
-      <t>カタチ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>コドモ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>シュルイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>生地や液体チョコレートにかけると、ふわふわ感をアップする。</t>
-    <rPh sb="0" eb="2">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>カン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>生地や液体チョコレートにかけると、ふわふわ感をアップする。
-LVが上がると、効果もアップする。
-派生：
-LV1で、各ウィンド系の魔法の習得可</t>
-    <rPh sb="0" eb="2">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ハセイ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>マホウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4193,7 +4193,7 @@
         <v>30</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>94</v>
@@ -5738,7 +5738,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G29" s="3">
         <v>6</v>
@@ -5777,7 +5777,7 @@
         <v>30</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>94</v>
@@ -6503,7 +6503,7 @@
         <v>30</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="T40" s="3" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D234B2-1A59-4BC4-A730-20798634EECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD939B32-21A6-40D4-94D4-5AF463BBA4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2505" yWindow="855" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2100" yWindow="990" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="271">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -3336,40 +3336,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>生地や液体チョコレートにかけると、ふわふわ感をアップする。
-LVが上がると、効果もアップする。
-派生：
-LV1で、各ウィンド系の魔法の習得可</t>
-    <rPh sb="0" eb="2">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ハセイ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>マホウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>チョコレートについて勉強する。
 LVに応じて、成功率が上がり、チョコレート制作時の時間を短縮する。
 また、ほんの少しなめらか感を上昇する。
@@ -3422,6 +3388,47 @@
     </rPh>
     <rPh sb="101" eb="104">
       <t>セイコウリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Buf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生地や液体チョコレートにかけると、ふわふわ感・なめらか感をアップする。
+LVが上がると、効果もアップする。
+派生：
+LV1で、各ウィンド系の魔法の習得可</t>
+    <rPh sb="0" eb="2">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ハセイ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>マホウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4193,7 +4200,7 @@
         <v>30</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>94</v>
@@ -5759,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>136</v>
+        <v>269</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>136</v>
@@ -5777,7 +5784,7 @@
         <v>30</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD939B32-21A6-40D4-94D4-5AF463BBA4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921B3F2F-91F4-454C-A25C-176925A8D64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="990" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1935" yWindow="1080" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1454,36 +1454,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>特定のお菓子に、さらに心をこめて仕上げる。
-通常のおかしには、効果がない。
-使用時、ハートを消費する。</t>
-    <rPh sb="0" eb="2">
-      <t>トクテイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ココロ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="40" eb="43">
-      <t>シヨウジ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ショウヒ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Freezing_OverRun</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3429,6 +3399,47 @@
     </rPh>
     <rPh sb="71" eb="73">
       <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>特定のお菓子に、さらに心をこめて仕上げる。
+強いハートをもっていないと使えない。
+また、通常のおかしには、効果がない。
+使用時、ハートを少し消費する。
+◆パネルにお菓子がセットされた状態でないと使えない。</t>
+    <rPh sb="0" eb="2">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ココロ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="62" eb="65">
+      <t>シヨウジ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>ショウヒ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3921,7 +3932,7 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -4068,7 +4079,7 @@
         <v>30</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>94</v>
@@ -4200,7 +4211,7 @@
         <v>30</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>94</v>
@@ -4332,7 +4343,7 @@
         <v>30</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="T7" s="3" t="s">
         <v>94</v>
@@ -4353,13 +4364,13 @@
         <v>147</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>235</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
@@ -4398,7 +4409,7 @@
         <v>30</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>94</v>
@@ -4449,7 +4460,7 @@
         <v>94</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O9" s="3">
         <v>1</v>
@@ -4464,7 +4475,7 @@
         <v>30</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>94</v>
@@ -4488,7 +4499,7 @@
         <v>81</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>105</v>
@@ -4596,7 +4607,7 @@
         <v>30</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="T11" s="3" t="s">
         <v>80</v>
@@ -4623,7 +4634,7 @@
         <v>133</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G12" s="3">
         <v>6</v>
@@ -4662,7 +4673,7 @@
         <v>30</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>94</v>
@@ -4683,13 +4694,13 @@
         <v>64</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G13" s="7">
         <v>6</v>
@@ -4728,7 +4739,7 @@
         <v>30</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="T13" s="7" t="s">
         <v>94</v>
@@ -4794,7 +4805,7 @@
         <v>30</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>94</v>
@@ -4860,7 +4871,7 @@
         <v>120</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>94</v>
@@ -4881,13 +4892,13 @@
         <v>144</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G16" s="3">
         <v>2</v>
@@ -4926,7 +4937,7 @@
         <v>120</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="T16" s="3" t="s">
         <v>51</v>
@@ -5079,13 +5090,13 @@
         <v>35</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G19" s="7">
         <v>2</v>
@@ -5124,7 +5135,7 @@
         <v>30</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="T19" s="7" t="s">
         <v>94</v>
@@ -5151,7 +5162,7 @@
         <v>157</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G20" s="3">
         <v>2</v>
@@ -5190,7 +5201,7 @@
         <v>30</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>94</v>
@@ -5214,7 +5225,7 @@
         <v>16</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>15</v>
@@ -5241,7 +5252,7 @@
         <v>94</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O21" s="3">
         <v>1</v>
@@ -5256,7 +5267,7 @@
         <v>30</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>94</v>
@@ -5307,7 +5318,7 @@
         <v>94</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O22" s="3">
         <v>1</v>
@@ -5322,7 +5333,7 @@
         <v>30</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>16</v>
@@ -5346,7 +5357,7 @@
         <v>106</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>72</v>
@@ -5388,7 +5399,7 @@
         <v>60</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>94</v>
@@ -5454,7 +5465,7 @@
         <v>30</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>94</v>
@@ -5541,13 +5552,13 @@
         <v>36</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="F26" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="G26" s="7">
         <v>4</v>
@@ -5586,7 +5597,7 @@
         <v>30</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="T26" s="7" t="s">
         <v>94</v>
@@ -5652,7 +5663,7 @@
         <v>30</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>94</v>
@@ -5676,7 +5687,7 @@
         <v>155</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>156</v>
@@ -5718,7 +5729,7 @@
         <v>30</v>
       </c>
       <c r="S28" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="T28" s="3" t="s">
         <v>94</v>
@@ -5745,7 +5756,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G29" s="3">
         <v>6</v>
@@ -5766,7 +5777,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>136</v>
@@ -5784,7 +5795,7 @@
         <v>30</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>94</v>
@@ -5811,7 +5822,7 @@
         <v>22</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G30" s="3">
         <v>1</v>
@@ -5835,7 +5846,7 @@
         <v>94</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O30" s="3">
         <v>1</v>
@@ -5850,7 +5861,7 @@
         <v>30</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="T30" s="3" t="s">
         <v>94</v>
@@ -5877,7 +5888,7 @@
         <v>129</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3">
         <v>1</v>
@@ -5901,7 +5912,7 @@
         <v>94</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O31" s="3">
         <v>1</v>
@@ -5916,7 +5927,7 @@
         <v>30</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="T31" s="3" t="s">
         <v>23</v>
@@ -5943,7 +5954,7 @@
         <v>172</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G32" s="3">
         <v>1</v>
@@ -5967,7 +5978,7 @@
         <v>94</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O32" s="3">
         <v>1</v>
@@ -5982,7 +5993,7 @@
         <v>30</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>23</v>
@@ -6009,7 +6020,7 @@
         <v>174</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
@@ -6033,7 +6044,7 @@
         <v>94</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O33" s="3">
         <v>1</v>
@@ -6048,7 +6059,7 @@
         <v>30</v>
       </c>
       <c r="S33" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>23</v>
@@ -6069,13 +6080,13 @@
         <v>37</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -6099,7 +6110,7 @@
         <v>94</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O34" s="3">
         <v>1</v>
@@ -6114,7 +6125,7 @@
         <v>30</v>
       </c>
       <c r="S34" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T34" s="3" t="s">
         <v>23</v>
@@ -6135,13 +6146,13 @@
         <v>37</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -6165,7 +6176,7 @@
         <v>94</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O35" s="3">
         <v>1</v>
@@ -6180,7 +6191,7 @@
         <v>30</v>
       </c>
       <c r="S35" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>23</v>
@@ -6270,10 +6281,10 @@
         <v>27</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G37" s="3">
         <v>3</v>
@@ -6312,7 +6323,7 @@
         <v>30</v>
       </c>
       <c r="S37" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="T37" s="3" t="s">
         <v>94</v>
@@ -6405,7 +6416,7 @@
         <v>176</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G39" s="7">
         <v>3</v>
@@ -6429,7 +6440,7 @@
         <v>94</v>
       </c>
       <c r="N39" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O39" s="7">
         <v>1</v>
@@ -6444,7 +6455,7 @@
         <v>30</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="T39" s="7" t="s">
         <v>94</v>
@@ -6471,7 +6482,7 @@
         <v>87</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G40" s="3">
         <v>3</v>
@@ -6495,7 +6506,7 @@
         <v>94</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O40" s="3">
         <v>1</v>
@@ -6510,7 +6521,7 @@
         <v>30</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T40" s="3" t="s">
         <v>94</v>
@@ -6531,13 +6542,13 @@
         <v>37</v>
       </c>
       <c r="D41" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="E41" s="7" t="s">
-        <v>204</v>
-      </c>
       <c r="F41" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G41" s="7">
         <v>3</v>
@@ -6561,7 +6572,7 @@
         <v>94</v>
       </c>
       <c r="N41" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O41" s="7">
         <v>1</v>
@@ -6576,7 +6587,7 @@
         <v>30</v>
       </c>
       <c r="S41" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T41" s="7" t="s">
         <v>94</v>
@@ -6603,7 +6614,7 @@
         <v>88</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G42" s="7">
         <v>3</v>
@@ -6627,7 +6638,7 @@
         <v>94</v>
       </c>
       <c r="N42" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O42" s="7">
         <v>1</v>
@@ -6642,7 +6653,7 @@
         <v>30</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="T42" s="7" t="s">
         <v>94</v>
@@ -6669,7 +6680,7 @@
         <v>102</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G43" s="7">
         <v>3</v>
@@ -6708,7 +6719,7 @@
         <v>30</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="T43" s="7" t="s">
         <v>94</v>
@@ -6732,7 +6743,7 @@
         <v>163</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>161</v>
@@ -6801,7 +6812,7 @@
         <v>159</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G45" s="7">
         <v>6</v>
@@ -6840,7 +6851,7 @@
         <v>30</v>
       </c>
       <c r="S45" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="T45" s="7" t="s">
         <v>94</v>
@@ -6906,7 +6917,7 @@
         <v>30</v>
       </c>
       <c r="S46" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>94</v>
@@ -6972,7 +6983,7 @@
         <v>30</v>
       </c>
       <c r="S47" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>94</v>
@@ -6996,7 +7007,7 @@
         <v>140</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>139</v>
@@ -7038,7 +7049,7 @@
         <v>480</v>
       </c>
       <c r="S48" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>94</v>
@@ -7059,13 +7070,13 @@
         <v>66</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G49" s="3">
         <v>6</v>
@@ -7086,7 +7097,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>94</v>
@@ -7104,7 +7115,7 @@
         <v>30</v>
       </c>
       <c r="S49" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>94</v>
@@ -7125,13 +7136,13 @@
         <v>66</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
@@ -7155,7 +7166,7 @@
         <v>94</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O50" s="3">
         <v>1</v>
@@ -7170,7 +7181,7 @@
         <v>30</v>
       </c>
       <c r="S50" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="T50" s="3" t="s">
         <v>94</v>
@@ -7302,7 +7313,7 @@
         <v>30</v>
       </c>
       <c r="S52" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>94</v>
@@ -7500,7 +7511,7 @@
         <v>30</v>
       </c>
       <c r="S55" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="T55" s="8" t="s">
         <v>94</v>
@@ -7698,7 +7709,7 @@
         <v>120</v>
       </c>
       <c r="S58" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>94</v>
@@ -7764,7 +7775,7 @@
         <v>30</v>
       </c>
       <c r="S59" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="T59" s="7" t="s">
         <v>94</v>
@@ -7812,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N60" t="s">
         <v>94</v>
@@ -7830,7 +7841,7 @@
         <v>60</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="T60" t="s">
         <v>94</v>
@@ -7896,7 +7907,7 @@
         <v>30</v>
       </c>
       <c r="S61" s="4" t="s">
-        <v>177</v>
+        <v>270</v>
       </c>
       <c r="T61" s="3" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921B3F2F-91F4-454C-A25C-176925A8D64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1616CA-D116-43BD-B165-954172F3E6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1935" yWindow="1080" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2055" yWindow="1020" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5780,7 +5780,7 @@
         <v>268</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>136</v>
+        <v>258</v>
       </c>
       <c r="O29" s="3">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1616CA-D116-43BD-B165-954172F3E6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042DDFB2-86FA-4A57-BF8B-7F0EB201F943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="1020" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1950" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042DDFB2-86FA-4A57-BF8B-7F0EB201F943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF210BF-9DB8-4BCD-8602-BC5527A2004B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2355" yWindow="1155" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="295">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -2839,61 +2839,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>お菓子の周りに花火を飛ばした演出が可能になる。
-LVが上がると効果が高まる。
-見た目を派手にすることができる。
-パーティに向けたお客さんに喜んでもらうことができる。
-◆パネルにお菓子がセットされた状態でないと使えない。
-◆仕上げ回数を一回消費する。
-仕上げ回数がないと、使用できない。</t>
-    <rPh sb="1" eb="3">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>マワ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハナビ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>エンシュツ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カノウ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ハデ</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="66" eb="67">
-      <t>キャク</t>
-    </rPh>
-    <rPh sb="70" eb="71">
-      <t>ヨロコ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>クッキーなどの焼き菓子をさらに焼くことで、サクサク感を増す。
 LVが上がると、より効果が高まる。
 ゲージが出現するので、
@@ -2941,39 +2886,6 @@
     </rPh>
     <rPh sb="109" eb="111">
       <t>シッパイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アロマの泡を作り出して、
-おかしの周りに泡を浮かべることができる。
-見た目がアップする。
-◆パネルにお菓子がセットされた状態でないと使えない。
-◆仕上げ回数を一回消費する。
-仕上げ回数がないと、使用できない。</t>
-    <rPh sb="4" eb="5">
-      <t>アワ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>マワ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>アワ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>メ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3440,6 +3352,351 @@
     </rPh>
     <rPh sb="72" eb="74">
       <t>ショウヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Rare_FindUP</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レアアイテムを発見したとき、個数を+1する。</t>
+    <rPh sb="7" eb="9">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レアアイテムを発見したとき、個数を+1する。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レアアイテム発見+1</t>
+    <rPh sb="6" eb="8">
+      <t>ハッケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ニーモニック</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Mnemonic</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お菓子の周りに貝殻やおさかなを飛ばす。</t>
+    <rPh sb="1" eb="3">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カイガラ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お菓子の周りに花火を飛ばした演出が可能になる。
+LVが上がると効果が高まる。
+相性が良ければ、お菓子に夏らしさを追加でき、見た目も上がる。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="1" eb="3">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハナビ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>アイショウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お菓子の周りに貝殻やおさかなを飛ばした演出が可能になる。
+LVが上がると効果が高まる。
+海らしさが上がる。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>グリッター</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Glitter</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おかしの周りにキラキラした光りを飛ばす。</t>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヒカ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お菓子の周りにキラキラした光りを飛ばす。
+相性がよいおかしの見た目をアップする。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="16" eb="17">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>アイショウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サンティマン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Santiman</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おかしの周りにハートを飛ばす。</t>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Spring_Pharmacy</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スプリング・ファーマシー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おかしの周りにさくらの花びらを飛ばす。</t>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アロマの泡を作り出して、
+おかしの周りに泡を浮かべることができる。
+相性がよければ、見た目がアップする。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="4" eb="5">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>アワ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>アイショウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Saint_Fleur</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>セイント・フルール</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おかしの周りにお花を飛ばす。</t>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おかしの周りにお花を飛ばす。
+相性がよければ、メルヘンさ・お花感がアップする。
+また、見た目もアップする。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="8" eb="9">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>アイショウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おかしの周りにさくらの花びらを飛ばす。
+相性がよければ、春らしさ・見た目がアップする。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="20" eb="22">
+      <t>アイショウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ハル</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おかしの周りにハートを飛ばし、演出する。
+相性がよければ、おかしの愛らしさ、見た目をアップできる。
+使用時に、ハートを少し消費する。
+ハートが少ないと使用できない。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>アイショウ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>アイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="51" eb="54">
+      <t>シヨウジ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>シヨウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3875,7 +4132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -3932,7 +4189,7 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -3958,7 +4215,7 @@
     </row>
     <row r="2" spans="1:21" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
-        <f t="shared" ref="A2:A61" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A67" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="5">
@@ -4079,7 +4336,7 @@
         <v>30</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>94</v>
@@ -4211,7 +4468,7 @@
         <v>30</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>94</v>
@@ -4409,7 +4666,7 @@
         <v>30</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>94</v>
@@ -4460,7 +4717,7 @@
         <v>94</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O9" s="3">
         <v>1</v>
@@ -4673,7 +4930,7 @@
         <v>30</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>94</v>
@@ -4805,7 +5062,7 @@
         <v>30</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>94</v>
@@ -5078,135 +5335,135 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:21" s="7" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="7">
+    <row r="19" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="7">
-        <v>2003</v>
-      </c>
-      <c r="C19" s="7" t="s">
+      <c r="B19" s="3">
+        <v>2005</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="G19" s="7">
+      <c r="D19" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G19" s="3">
         <v>2</v>
       </c>
-      <c r="H19" s="7">
-        <v>20</v>
-      </c>
-      <c r="I19" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J19" s="7">
-        <v>0</v>
-      </c>
-      <c r="K19" s="7">
-        <v>5</v>
-      </c>
-      <c r="L19" s="7">
-        <v>0</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O19" s="7">
-        <v>1</v>
-      </c>
-      <c r="P19" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="7">
+      <c r="H19" s="3">
+        <v>3</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <v>3</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O19" s="3">
+        <v>1</v>
+      </c>
+      <c r="P19" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="3">
         <v>100</v>
       </c>
-      <c r="R19" s="7">
+      <c r="R19" s="3">
         <v>30</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="T19" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U19" s="7">
+      <c r="S19" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U19" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:21" s="3" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="3">
+    <row r="20" spans="1:21" s="7" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="7">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="3">
-        <v>3006</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="B20" s="7">
+        <v>2003</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="G20" s="7">
         <v>2</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="H20" s="7">
+        <v>20</v>
+      </c>
+      <c r="I20" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J20" s="7">
+        <v>0</v>
+      </c>
+      <c r="K20" s="7">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="L20" s="7">
+        <v>0</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O20" s="7">
+        <v>1</v>
+      </c>
+      <c r="P20" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="7">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="7">
         <v>30</v>
       </c>
-      <c r="S20" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="S20" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="T20" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U20" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5216,31 +5473,31 @@
         <v>19</v>
       </c>
       <c r="B21" s="3">
-        <v>3001</v>
+        <v>3006</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>141</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>240</v>
+        <v>157</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>15</v>
+        <v>244</v>
       </c>
       <c r="G21" s="3">
         <v>2</v>
       </c>
       <c r="H21" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
         <v>0</v>
       </c>
       <c r="J21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>5</v>
@@ -5252,10 +5509,10 @@
         <v>94</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>258</v>
+        <v>94</v>
       </c>
       <c r="O21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="3">
         <v>2</v>
@@ -5267,7 +5524,7 @@
         <v>30</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>94</v>
@@ -5276,37 +5533,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:21" s="3" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G22" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="3">
         <v>5</v>
@@ -5318,7 +5575,7 @@
         <v>94</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O22" s="3">
         <v>1</v>
@@ -5333,13 +5590,13 @@
         <v>30</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="U22" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -5348,25 +5605,25 @@
         <v>21</v>
       </c>
       <c r="B23" s="3">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="G23" s="3">
         <v>4</v>
       </c>
       <c r="H23" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I23" s="3">
         <v>0</v>
@@ -5375,16 +5632,16 @@
         <v>0</v>
       </c>
       <c r="K23" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L23" s="3">
         <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>136</v>
+        <v>256</v>
       </c>
       <c r="O23" s="3">
         <v>1</v>
@@ -5396,16 +5653,16 @@
         <v>100</v>
       </c>
       <c r="R23" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="U23" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -5414,25 +5671,25 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>113</v>
+        <v>225</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="G24" s="3">
         <v>4</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
@@ -5441,19 +5698,19 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="3">
         <v>2</v>
@@ -5462,10 +5719,10 @@
         <v>100</v>
       </c>
       <c r="R24" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>196</v>
+        <v>251</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>94</v>
@@ -5474,160 +5731,160 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="7">
+    <row r="25" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="7">
-        <v>3005</v>
-      </c>
-      <c r="C25" s="7" t="s">
+      <c r="B25" s="3">
+        <v>3008</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="G25" s="7">
+      <c r="D25" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G25" s="3">
         <v>4</v>
       </c>
-      <c r="H25" s="7">
-        <v>20</v>
-      </c>
-      <c r="I25" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J25" s="7">
-        <v>0</v>
-      </c>
-      <c r="K25" s="7">
-        <v>5</v>
-      </c>
-      <c r="L25" s="7">
-        <v>0</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O25" s="7">
-        <v>1</v>
-      </c>
-      <c r="P25" s="7">
+      <c r="H25" s="3">
+        <v>6</v>
+      </c>
+      <c r="I25" s="3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
+        <v>3</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O25" s="3">
+        <v>1</v>
+      </c>
+      <c r="P25" s="3">
         <v>2</v>
       </c>
-      <c r="Q25" s="7">
+      <c r="Q25" s="3">
         <v>100</v>
       </c>
-      <c r="R25" s="7">
-        <v>30</v>
-      </c>
-      <c r="S25" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="T25" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U25" s="7">
+      <c r="R25" s="3">
+        <v>60</v>
+      </c>
+      <c r="S25" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U25" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="7">
+    <row r="26" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="7">
-        <v>3005</v>
-      </c>
-      <c r="C26" s="7" t="s">
+      <c r="B26" s="3">
+        <v>3004</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="G26" s="7">
+      <c r="D26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G26" s="3">
         <v>4</v>
       </c>
-      <c r="H26" s="7">
-        <v>10</v>
-      </c>
-      <c r="I26" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J26" s="7">
-        <v>0</v>
-      </c>
-      <c r="K26" s="7">
+      <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>5</v>
       </c>
-      <c r="L26" s="7">
-        <v>0</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N26" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O26" s="7">
-        <v>1</v>
-      </c>
-      <c r="P26" s="7">
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>2</v>
       </c>
-      <c r="Q26" s="7">
+      <c r="Q26" s="3">
         <v>100</v>
       </c>
-      <c r="R26" s="7">
+      <c r="R26" s="3">
         <v>30</v>
       </c>
-      <c r="S26" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="T26" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U26" s="7">
+      <c r="S26" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U26" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B27" s="3">
-        <v>4010</v>
+        <v>3007</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>152</v>
+        <v>269</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>153</v>
+        <v>272</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>154</v>
+        <v>270</v>
       </c>
       <c r="G27" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27" s="3">
         <v>0</v>
@@ -5639,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L27" s="3">
         <v>0</v>
@@ -5654,7 +5911,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="3">
         <v>100</v>
@@ -5663,7 +5920,7 @@
         <v>30</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>94</v>
@@ -5672,163 +5929,163 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="3">
+    <row r="28" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="7">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="3">
-        <v>4011</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G28" s="3">
-        <v>6</v>
-      </c>
-      <c r="H28" s="3">
-        <v>0</v>
-      </c>
-      <c r="I28" s="3">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3">
+      <c r="B28" s="7">
+        <v>3005</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G28" s="7">
+        <v>4</v>
+      </c>
+      <c r="H28" s="7">
+        <v>20</v>
+      </c>
+      <c r="I28" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J28" s="7">
+        <v>0</v>
+      </c>
+      <c r="K28" s="7">
         <v>5</v>
       </c>
-      <c r="L28" s="3">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O28" s="3">
-        <v>0</v>
-      </c>
-      <c r="P28" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q28" s="3">
+      <c r="L28" s="7">
+        <v>0</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O28" s="7">
+        <v>1</v>
+      </c>
+      <c r="P28" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="7">
         <v>100</v>
       </c>
-      <c r="R28" s="3">
+      <c r="R28" s="7">
         <v>30</v>
       </c>
-      <c r="S28" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U28" s="3">
+      <c r="S28" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="T28" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U28" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="3">
+    <row r="29" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="7">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="3">
-        <v>4001</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="G29" s="3">
-        <v>6</v>
-      </c>
-      <c r="H29" s="3">
+      <c r="B29" s="7">
+        <v>3005</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="G29" s="7">
+        <v>4</v>
+      </c>
+      <c r="H29" s="7">
+        <v>10</v>
+      </c>
+      <c r="I29" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J29" s="7">
+        <v>0</v>
+      </c>
+      <c r="K29" s="7">
+        <v>5</v>
+      </c>
+      <c r="L29" s="7">
+        <v>0</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O29" s="7">
+        <v>1</v>
+      </c>
+      <c r="P29" s="7">
         <v>2</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="O29" s="3">
-        <v>1</v>
-      </c>
-      <c r="P29" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>85</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="Q29" s="7">
+        <v>100</v>
+      </c>
+      <c r="R29" s="7">
         <v>30</v>
       </c>
-      <c r="S29" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="S29" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="T29" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U29" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:21" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>4002</v>
+        <v>4010</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>152</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="G30" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H30" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3">
         <v>0</v>
@@ -5837,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L30" s="3">
         <v>0</v>
@@ -5846,10 +6103,10 @@
         <v>94</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>258</v>
+        <v>94</v>
       </c>
       <c r="O30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" s="3">
         <v>3</v>
@@ -5861,7 +6118,7 @@
         <v>30</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="T30" s="3" t="s">
         <v>94</v>
@@ -5870,41 +6127,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:21" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B31" s="3">
-        <v>4010</v>
+        <v>4011</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>129</v>
+        <v>215</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="G31" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H31" s="3">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3">
         <v>5</v>
       </c>
-      <c r="I31" s="3">
-        <v>1</v>
-      </c>
-      <c r="J31" s="3">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3">
-        <v>3</v>
-      </c>
       <c r="L31" s="3">
         <v>0</v>
       </c>
@@ -5912,10 +6169,10 @@
         <v>94</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>258</v>
+        <v>94</v>
       </c>
       <c r="O31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P31" s="3">
         <v>3</v>
@@ -5927,43 +6184,43 @@
         <v>30</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>199</v>
+        <v>254</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="U31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:21" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>4011</v>
+        <v>4001</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>173</v>
+        <v>23</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>184</v>
+        <v>264</v>
       </c>
       <c r="G32" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H32" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -5975,10 +6232,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>94</v>
+        <v>266</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O32" s="3">
         <v>1</v>
@@ -5987,19 +6244,19 @@
         <v>3</v>
       </c>
       <c r="Q32" s="3">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="R32" s="3">
         <v>30</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>185</v>
+        <v>267</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="U32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -6008,34 +6265,34 @@
         <v>31</v>
       </c>
       <c r="B33" s="3">
-        <v>4012</v>
+        <v>4002</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>174</v>
+        <v>22</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="G33" s="3">
         <v>1</v>
       </c>
       <c r="H33" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
       </c>
       <c r="K33" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L33" s="3">
         <v>0</v>
@@ -6044,7 +6301,7 @@
         <v>94</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O33" s="3">
         <v>1</v>
@@ -6059,13 +6316,13 @@
         <v>30</v>
       </c>
       <c r="S33" s="4" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="U33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -6074,19 +6331,19 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>178</v>
+        <v>129</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="G34" s="3">
         <v>1</v>
@@ -6095,13 +6352,13 @@
         <v>5</v>
       </c>
       <c r="I34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="3">
         <v>0</v>
       </c>
       <c r="K34" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L34" s="3">
         <v>0</v>
@@ -6110,7 +6367,7 @@
         <v>94</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O34" s="3">
         <v>1</v>
@@ -6125,7 +6382,7 @@
         <v>30</v>
       </c>
       <c r="S34" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="T34" s="3" t="s">
         <v>23</v>
@@ -6140,19 +6397,19 @@
         <v>33</v>
       </c>
       <c r="B35" s="3">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G35" s="3">
         <v>1</v>
@@ -6161,13 +6418,13 @@
         <v>5</v>
       </c>
       <c r="I35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="3">
         <v>0</v>
       </c>
       <c r="K35" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L35" s="3">
         <v>0</v>
@@ -6176,7 +6433,7 @@
         <v>94</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O35" s="3">
         <v>1</v>
@@ -6191,7 +6448,7 @@
         <v>30</v>
       </c>
       <c r="S35" s="4" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>23</v>
@@ -6200,70 +6457,70 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:21" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="7">
+    <row r="36" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="3">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B36" s="7">
-        <v>4003</v>
-      </c>
-      <c r="C36" s="7" t="s">
+      <c r="B36" s="3">
+        <v>4012</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G36" s="7">
+      <c r="D36" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G36" s="3">
+        <v>1</v>
+      </c>
+      <c r="H36" s="3">
+        <v>5</v>
+      </c>
+      <c r="I36" s="3">
+        <v>1</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
+        <v>1</v>
+      </c>
+      <c r="L36" s="3">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="O36" s="3">
+        <v>1</v>
+      </c>
+      <c r="P36" s="3">
         <v>3</v>
       </c>
-      <c r="H36" s="7">
-        <v>2</v>
-      </c>
-      <c r="I36" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J36" s="7">
-        <v>0</v>
-      </c>
-      <c r="K36" s="7">
-        <v>3</v>
-      </c>
-      <c r="L36" s="7">
-        <v>0</v>
-      </c>
-      <c r="M36" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N36" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O36" s="7">
-        <v>1</v>
-      </c>
-      <c r="P36" s="7">
-        <v>3</v>
-      </c>
-      <c r="Q36" s="7">
+      <c r="Q36" s="3">
         <v>100</v>
       </c>
-      <c r="R36" s="7">
+      <c r="R36" s="3">
         <v>30</v>
       </c>
-      <c r="S36" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="T36" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U36" s="7">
-        <v>0</v>
+      <c r="S36" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="U36" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -6272,25 +6529,25 @@
         <v>35</v>
       </c>
       <c r="B37" s="3">
-        <v>4004</v>
+        <v>4012</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>247</v>
+        <v>178</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="G37" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I37" s="3">
         <v>0</v>
@@ -6305,10 +6562,10 @@
         <v>0</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>136</v>
+        <v>256</v>
       </c>
       <c r="O37" s="3">
         <v>1</v>
@@ -6323,106 +6580,106 @@
         <v>30</v>
       </c>
       <c r="S37" s="4" t="s">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="U37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:21" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="7">
+    <row r="38" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="3">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B38" s="7">
-        <v>4005</v>
-      </c>
-      <c r="C38" s="7" t="s">
+      <c r="B38" s="3">
+        <v>4012</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G38" s="3">
+        <v>1</v>
+      </c>
+      <c r="H38" s="3">
+        <v>5</v>
+      </c>
+      <c r="I38" s="3">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3">
+        <v>1</v>
+      </c>
+      <c r="L38" s="3">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="O38" s="3">
+        <v>1</v>
+      </c>
+      <c r="P38" s="3">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>100</v>
+      </c>
+      <c r="R38" s="3">
         <v>30</v>
       </c>
-      <c r="E38" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G38" s="7">
-        <v>12</v>
-      </c>
-      <c r="H38" s="7">
-        <v>5</v>
-      </c>
-      <c r="I38" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J38" s="7">
-        <v>0</v>
-      </c>
-      <c r="K38" s="7">
-        <v>3</v>
-      </c>
-      <c r="L38" s="7">
-        <v>0</v>
-      </c>
-      <c r="M38" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N38" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O38" s="7">
-        <v>1</v>
-      </c>
-      <c r="P38" s="7">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="7">
-        <v>100</v>
-      </c>
-      <c r="R38" s="7">
-        <v>30</v>
-      </c>
-      <c r="S38" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="T38" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U38" s="7">
-        <v>0</v>
+      <c r="S38" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="U38" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:21" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="7">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B39" s="7">
-        <v>4006</v>
+        <v>4003</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>176</v>
+        <v>71</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>260</v>
+        <v>24</v>
       </c>
       <c r="G39" s="7">
         <v>3</v>
       </c>
       <c r="H39" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I39" s="7">
         <v>9999</v>
@@ -6440,7 +6697,7 @@
         <v>94</v>
       </c>
       <c r="N39" s="7" t="s">
-        <v>258</v>
+        <v>94</v>
       </c>
       <c r="O39" s="7">
         <v>1</v>
@@ -6454,8 +6711,8 @@
       <c r="R39" s="7">
         <v>30</v>
       </c>
-      <c r="S39" s="7" t="s">
-        <v>260</v>
+      <c r="S39" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="T39" s="7" t="s">
         <v>94</v>
@@ -6464,31 +6721,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="3">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>4007</v>
+        <v>4004</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>87</v>
+        <v>247</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="G40" s="3">
         <v>3</v>
       </c>
       <c r="H40" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I40" s="3">
         <v>0</v>
@@ -6497,16 +6754,16 @@
         <v>0</v>
       </c>
       <c r="K40" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L40" s="3">
         <v>0</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>258</v>
+        <v>136</v>
       </c>
       <c r="O40" s="3">
         <v>1</v>
@@ -6521,7 +6778,7 @@
         <v>30</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="T40" s="3" t="s">
         <v>94</v>
@@ -6530,28 +6787,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:21" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="7">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B41" s="7">
-        <v>4007</v>
+        <v>4005</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>202</v>
+        <v>30</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>203</v>
+        <v>28</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>262</v>
+        <v>29</v>
       </c>
       <c r="G41" s="7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H41" s="7">
         <v>5</v>
@@ -6572,7 +6829,7 @@
         <v>94</v>
       </c>
       <c r="N41" s="7" t="s">
-        <v>258</v>
+        <v>94</v>
       </c>
       <c r="O41" s="7">
         <v>1</v>
@@ -6586,8 +6843,8 @@
       <c r="R41" s="7">
         <v>30</v>
       </c>
-      <c r="S41" s="7" t="s">
-        <v>262</v>
+      <c r="S41" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="T41" s="7" t="s">
         <v>94</v>
@@ -6602,19 +6859,19 @@
         <v>40</v>
       </c>
       <c r="B42" s="7">
-        <v>4008</v>
+        <v>4006</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="G42" s="7">
         <v>3</v>
@@ -6638,7 +6895,7 @@
         <v>94</v>
       </c>
       <c r="N42" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O42" s="7">
         <v>1</v>
@@ -6653,7 +6910,7 @@
         <v>30</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="T42" s="7" t="s">
         <v>94</v>
@@ -6662,97 +6919,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="7">
+    <row r="43" spans="1:21" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43" s="7">
-        <v>4009</v>
-      </c>
-      <c r="C43" s="7" t="s">
+      <c r="B43" s="3">
+        <v>4007</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D43" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G43" s="7">
+      <c r="D43" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G43" s="3">
         <v>3</v>
       </c>
-      <c r="H43" s="7">
-        <v>8</v>
-      </c>
-      <c r="I43" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J43" s="7">
-        <v>0</v>
-      </c>
-      <c r="K43" s="7">
+      <c r="H43" s="3">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
+        <v>1</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="O43" s="3">
+        <v>1</v>
+      </c>
+      <c r="P43" s="3">
         <v>3</v>
       </c>
-      <c r="L43" s="7">
-        <v>0</v>
-      </c>
-      <c r="M43" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N43" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O43" s="7">
-        <v>1</v>
-      </c>
-      <c r="P43" s="7">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="7">
+      <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="7">
+      <c r="R43" s="3">
         <v>30</v>
       </c>
-      <c r="S43" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="T43" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U43" s="7">
+      <c r="S43" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U43" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A44" s="7">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B44" s="7">
-        <v>4013</v>
+        <v>4007</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>161</v>
+        <v>260</v>
       </c>
       <c r="G44" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H44" s="7">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I44" s="7">
         <v>9999</v>
@@ -6761,7 +7018,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L44" s="7">
         <v>0</v>
@@ -6770,7 +7027,7 @@
         <v>94</v>
       </c>
       <c r="N44" s="7" t="s">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="O44" s="7">
         <v>1</v>
@@ -6784,8 +7041,8 @@
       <c r="R44" s="7">
         <v>30</v>
       </c>
-      <c r="S44" s="9" t="s">
-        <v>162</v>
+      <c r="S44" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="T44" s="7" t="s">
         <v>94</v>
@@ -6794,31 +7051,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A45" s="7">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B45" s="7">
-        <v>5004</v>
+        <v>4008</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>193</v>
+        <v>261</v>
       </c>
       <c r="G45" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H45" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I45" s="7">
         <v>9999</v>
@@ -6827,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L45" s="7">
         <v>0</v>
@@ -6836,13 +7093,13 @@
         <v>94</v>
       </c>
       <c r="N45" s="7" t="s">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="O45" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q45" s="7">
         <v>100</v>
@@ -6850,8 +7107,8 @@
       <c r="R45" s="7">
         <v>30</v>
       </c>
-      <c r="S45" s="9" t="s">
-        <v>239</v>
+      <c r="S45" s="7" t="s">
+        <v>261</v>
       </c>
       <c r="T45" s="7" t="s">
         <v>94</v>
@@ -6860,229 +7117,229 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="3">
+    <row r="46" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="7">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B46" s="3">
-        <v>5001</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G46" s="3">
-        <v>6</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="B46" s="7">
+        <v>4009</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G46" s="7">
         <v>3</v>
       </c>
-      <c r="I46" s="3">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3">
-        <v>0</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="H46" s="7">
+        <v>8</v>
+      </c>
+      <c r="I46" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J46" s="7">
+        <v>0</v>
+      </c>
+      <c r="K46" s="7">
         <v>3</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="O46" s="3">
-        <v>1</v>
-      </c>
-      <c r="P46" s="3">
-        <v>4</v>
-      </c>
-      <c r="Q46" s="3">
+      <c r="L46" s="7">
+        <v>0</v>
+      </c>
+      <c r="M46" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N46" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O46" s="7">
+        <v>1</v>
+      </c>
+      <c r="P46" s="7">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="7">
         <v>100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="7">
         <v>30</v>
       </c>
-      <c r="S46" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U46" s="3">
+      <c r="S46" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="T46" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U46" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="3">
+    <row r="47" spans="1:21" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="7">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B47" s="3">
-        <v>5002</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="B47" s="7">
+        <v>4013</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G47" s="7">
         <v>6</v>
       </c>
-      <c r="H47" s="3">
-        <v>6</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="H47" s="7">
+        <v>30</v>
+      </c>
+      <c r="I47" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J47" s="7">
+        <v>0</v>
+      </c>
+      <c r="K47" s="7">
+        <v>5</v>
+      </c>
+      <c r="L47" s="7">
+        <v>0</v>
+      </c>
+      <c r="M47" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N47" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O47" s="7">
+        <v>1</v>
+      </c>
+      <c r="P47" s="7">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O47" s="3">
-        <v>1</v>
-      </c>
-      <c r="P47" s="3">
-        <v>4</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="7">
         <v>100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="7">
         <v>30</v>
       </c>
-      <c r="S47" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="S47" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="T47" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U47" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="3">
+    <row r="48" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="7">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B48" s="3">
-        <v>5003</v>
-      </c>
-      <c r="C48" s="3" t="s">
+      <c r="B48" s="7">
+        <v>5004</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="D48" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="G48" s="7">
         <v>6</v>
       </c>
-      <c r="H48" s="3">
-        <v>6</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O48" s="3">
-        <v>1</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="H48" s="7">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J48" s="7">
+        <v>0</v>
+      </c>
+      <c r="K48" s="7">
+        <v>5</v>
+      </c>
+      <c r="L48" s="7">
+        <v>0</v>
+      </c>
+      <c r="M48" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N48" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O48" s="7">
+        <v>0</v>
+      </c>
+      <c r="P48" s="7">
         <v>4</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="7">
         <v>100</v>
       </c>
-      <c r="R48" s="3">
-        <v>480</v>
-      </c>
-      <c r="S48" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="R48" s="7">
+        <v>30</v>
+      </c>
+      <c r="S48" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="T48" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U48" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B49" s="3">
-        <v>5005</v>
+        <v>5001</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="G49" s="3">
         <v>6</v>
       </c>
       <c r="H49" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -7097,10 +7354,10 @@
         <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="O49" s="3">
         <v>1</v>
@@ -7115,7 +7372,7 @@
         <v>30</v>
       </c>
       <c r="S49" s="4" t="s">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>94</v>
@@ -7130,25 +7387,25 @@
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>5006</v>
+        <v>5002</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>223</v>
+        <v>121</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>222</v>
+        <v>119</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>221</v>
+        <v>120</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
       </c>
       <c r="H50" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I50" s="3">
         <v>0</v>
@@ -7157,7 +7414,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L50" s="3">
         <v>0</v>
@@ -7166,7 +7423,7 @@
         <v>94</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>258</v>
+        <v>94</v>
       </c>
       <c r="O50" s="3">
         <v>1</v>
@@ -7181,7 +7438,7 @@
         <v>30</v>
       </c>
       <c r="S50" s="4" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="T50" s="3" t="s">
         <v>94</v>
@@ -7190,112 +7447,112 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="7">
+    <row r="51" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="3">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B51" s="7">
-        <v>6001</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G51" s="7">
+      <c r="B51" s="3">
+        <v>5003</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G51" s="3">
         <v>6</v>
       </c>
-      <c r="H51" s="7">
+      <c r="H51" s="3">
+        <v>6</v>
+      </c>
+      <c r="I51" s="3">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3">
+        <v>0</v>
+      </c>
+      <c r="K51" s="3">
         <v>3</v>
       </c>
-      <c r="I51" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J51" s="7">
-        <v>0</v>
-      </c>
-      <c r="K51" s="7">
-        <v>10</v>
-      </c>
-      <c r="L51" s="7">
-        <v>0</v>
-      </c>
-      <c r="M51" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N51" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O51" s="7">
-        <v>1</v>
-      </c>
-      <c r="P51" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q51" s="7">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O51" s="3">
+        <v>1</v>
+      </c>
+      <c r="P51" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q51" s="3">
         <v>100</v>
       </c>
-      <c r="R51" s="7">
-        <v>30</v>
-      </c>
-      <c r="S51" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="T51" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U51" s="7">
+      <c r="R51" s="3">
+        <v>480</v>
+      </c>
+      <c r="S51" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="T51" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U51" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:21" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>6002</v>
+        <v>5005</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>96</v>
+        <v>205</v>
       </c>
       <c r="G52" s="3">
         <v>6</v>
       </c>
       <c r="H52" s="3">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>3</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3">
-        <v>5</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>94</v>
+        <v>226</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>94</v>
@@ -7304,7 +7561,7 @@
         <v>1</v>
       </c>
       <c r="P52" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
@@ -7313,7 +7570,7 @@
         <v>30</v>
       </c>
       <c r="S52" s="4" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>94</v>
@@ -7322,597 +7579,993 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="7">
+    <row r="53" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="3">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53" s="7">
-        <v>6003</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G53" s="7">
+      <c r="B53" s="3">
+        <v>5006</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G53" s="3">
         <v>6</v>
       </c>
-      <c r="H53" s="7">
-        <v>3</v>
-      </c>
-      <c r="I53" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J53" s="7">
-        <v>0</v>
-      </c>
-      <c r="K53" s="7">
-        <v>1</v>
-      </c>
-      <c r="L53" s="7">
-        <v>0</v>
-      </c>
-      <c r="M53" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N53" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O53" s="7">
-        <v>1</v>
-      </c>
-      <c r="P53" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q53" s="7">
+      <c r="H53" s="3">
+        <v>12</v>
+      </c>
+      <c r="I53" s="3">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3">
+        <v>0</v>
+      </c>
+      <c r="K53" s="3">
+        <v>1</v>
+      </c>
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="O53" s="3">
+        <v>1</v>
+      </c>
+      <c r="P53" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q53" s="3">
         <v>100</v>
       </c>
-      <c r="R53" s="7">
+      <c r="R53" s="3">
         <v>30</v>
       </c>
-      <c r="S53" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="T53" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U53" s="7">
+      <c r="S53" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="T53" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U53" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="8">
+    <row r="54" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="7">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B54" s="8">
-        <v>7001</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G54" s="8">
+      <c r="B54" s="7">
+        <v>6001</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G54" s="7">
         <v>6</v>
       </c>
-      <c r="H54" s="8">
-        <v>12</v>
-      </c>
-      <c r="I54" s="8">
-        <v>0</v>
-      </c>
-      <c r="J54" s="8">
-        <v>0</v>
-      </c>
-      <c r="K54" s="8">
-        <v>1</v>
-      </c>
-      <c r="L54" s="8">
-        <v>0</v>
-      </c>
-      <c r="M54" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="N54" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="O54" s="8">
-        <v>1</v>
-      </c>
-      <c r="P54" s="8">
-        <v>6</v>
-      </c>
-      <c r="Q54" s="8">
+      <c r="H54" s="7">
+        <v>3</v>
+      </c>
+      <c r="I54" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J54" s="7">
+        <v>0</v>
+      </c>
+      <c r="K54" s="7">
+        <v>10</v>
+      </c>
+      <c r="L54" s="7">
+        <v>0</v>
+      </c>
+      <c r="M54" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N54" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O54" s="7">
+        <v>1</v>
+      </c>
+      <c r="P54" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q54" s="7">
         <v>100</v>
       </c>
-      <c r="R54" s="8">
+      <c r="R54" s="7">
         <v>30</v>
       </c>
-      <c r="S54" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="T54" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="U54" s="8">
+      <c r="S54" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T54" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U54" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:21" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="8">
+    <row r="55" spans="1:21" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="3">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" s="8">
-        <v>7002</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G55" s="8">
-        <v>18</v>
-      </c>
-      <c r="H55" s="8">
-        <v>15</v>
-      </c>
-      <c r="I55" s="8">
-        <v>0</v>
-      </c>
-      <c r="J55" s="8">
-        <v>0</v>
-      </c>
-      <c r="K55" s="8">
-        <v>1</v>
-      </c>
-      <c r="L55" s="8">
-        <v>0</v>
-      </c>
-      <c r="M55" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="N55" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="O55" s="8">
-        <v>1</v>
-      </c>
-      <c r="P55" s="8">
+      <c r="B55" s="3">
+        <v>6002</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G55" s="3">
         <v>6</v>
       </c>
-      <c r="Q55" s="8">
+      <c r="H55" s="3">
+        <v>3</v>
+      </c>
+      <c r="I55" s="3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3">
+        <v>0</v>
+      </c>
+      <c r="K55" s="3">
+        <v>5</v>
+      </c>
+      <c r="L55" s="3">
+        <v>0</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O55" s="3">
+        <v>1</v>
+      </c>
+      <c r="P55" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q55" s="3">
         <v>100</v>
       </c>
-      <c r="R55" s="8">
+      <c r="R55" s="3">
         <v>30</v>
       </c>
-      <c r="S55" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="T55" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="U55" s="8">
+      <c r="S55" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="T55" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U55" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="8">
+    <row r="56" spans="1:21" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="3">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B56" s="8">
-        <v>8001</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G56" s="8">
+      <c r="B56" s="3">
+        <v>6004</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G56" s="3">
         <v>6</v>
       </c>
-      <c r="H56" s="8">
-        <v>12</v>
-      </c>
-      <c r="I56" s="8">
-        <v>0</v>
-      </c>
-      <c r="J56" s="8">
-        <v>0</v>
-      </c>
-      <c r="K56" s="8">
-        <v>1</v>
-      </c>
-      <c r="L56" s="8">
-        <v>0</v>
-      </c>
-      <c r="M56" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="N56" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="O56" s="8">
-        <v>1</v>
-      </c>
-      <c r="P56" s="8">
-        <v>7</v>
-      </c>
-      <c r="Q56" s="8">
+      <c r="H56" s="3">
+        <v>3</v>
+      </c>
+      <c r="I56" s="3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3">
+        <v>0</v>
+      </c>
+      <c r="K56" s="3">
+        <v>3</v>
+      </c>
+      <c r="L56" s="3">
+        <v>0</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O56" s="3">
+        <v>1</v>
+      </c>
+      <c r="P56" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q56" s="3">
         <v>100</v>
       </c>
-      <c r="R56" s="8">
-        <v>30</v>
-      </c>
-      <c r="S56" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="T56" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="U56" s="8">
+      <c r="R56" s="3">
+        <v>60</v>
+      </c>
+      <c r="S56" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="T56" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U56" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="8">
+    <row r="57" spans="1:21" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="3">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B57" s="8">
-        <v>8002</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G57" s="8">
+      <c r="B57" s="3">
+        <v>6005</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G57" s="3">
         <v>6</v>
       </c>
-      <c r="H57" s="8">
-        <v>14</v>
-      </c>
-      <c r="I57" s="8">
-        <v>0</v>
-      </c>
-      <c r="J57" s="8">
-        <v>0</v>
-      </c>
-      <c r="K57" s="8">
-        <v>1</v>
-      </c>
-      <c r="L57" s="8">
-        <v>0</v>
-      </c>
-      <c r="M57" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="N57" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="O57" s="8">
-        <v>1</v>
-      </c>
-      <c r="P57" s="8">
-        <v>7</v>
-      </c>
-      <c r="Q57" s="8">
+      <c r="H57" s="3">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O57" s="3">
+        <v>1</v>
+      </c>
+      <c r="P57" s="3">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="8">
-        <v>30</v>
-      </c>
-      <c r="S57" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="T57" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="U57" s="8">
+      <c r="R57" s="3">
+        <v>60</v>
+      </c>
+      <c r="S57" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U57" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:21" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="3">
+    <row r="58" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="7">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B58" s="3">
-        <v>9001</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2</v>
-      </c>
-      <c r="H58" s="3">
-        <v>7</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>10</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="O58" s="3">
-        <v>1</v>
-      </c>
-      <c r="P58" s="3">
-        <v>8</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="B58" s="7">
+        <v>6003</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G58" s="7">
+        <v>6</v>
+      </c>
+      <c r="H58" s="7">
+        <v>3</v>
+      </c>
+      <c r="I58" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J58" s="7">
+        <v>0</v>
+      </c>
+      <c r="K58" s="7">
+        <v>1</v>
+      </c>
+      <c r="L58" s="7">
+        <v>0</v>
+      </c>
+      <c r="M58" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N58" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O58" s="7">
+        <v>1</v>
+      </c>
+      <c r="P58" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="7">
         <v>100</v>
       </c>
-      <c r="R58" s="3">
-        <v>120</v>
-      </c>
-      <c r="S58" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U58" s="3">
+      <c r="R58" s="7">
+        <v>30</v>
+      </c>
+      <c r="S58" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="T58" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U58" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="7">
+    <row r="59" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="8">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B59" s="7">
-        <v>9002</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G59" s="7">
+      <c r="B59" s="8">
+        <v>7001</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G59" s="8">
         <v>6</v>
       </c>
-      <c r="H59" s="7">
-        <v>5</v>
-      </c>
-      <c r="I59" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J59" s="7">
-        <v>0</v>
-      </c>
-      <c r="K59" s="7">
-        <v>10</v>
-      </c>
-      <c r="L59" s="7">
-        <v>0</v>
-      </c>
-      <c r="M59" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N59" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O59" s="7">
-        <v>1</v>
-      </c>
-      <c r="P59" s="7">
-        <v>8</v>
-      </c>
-      <c r="Q59" s="7">
+      <c r="H59" s="8">
+        <v>12</v>
+      </c>
+      <c r="I59" s="8">
+        <v>0</v>
+      </c>
+      <c r="J59" s="8">
+        <v>0</v>
+      </c>
+      <c r="K59" s="8">
+        <v>1</v>
+      </c>
+      <c r="L59" s="8">
+        <v>0</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="N59" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="O59" s="8">
+        <v>1</v>
+      </c>
+      <c r="P59" s="8">
+        <v>6</v>
+      </c>
+      <c r="Q59" s="8">
         <v>100</v>
       </c>
-      <c r="R59" s="7">
+      <c r="R59" s="8">
         <v>30</v>
       </c>
-      <c r="S59" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="T59" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U59" s="7">
+      <c r="S59" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="T59" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="U59" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60">
+    <row r="60" spans="1:21" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="8">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B60">
-        <v>9004</v>
-      </c>
-      <c r="C60" t="s">
-        <v>68</v>
-      </c>
-      <c r="D60" t="s">
-        <v>99</v>
-      </c>
-      <c r="E60" t="s">
-        <v>97</v>
-      </c>
-      <c r="F60" t="s">
-        <v>98</v>
-      </c>
-      <c r="G60">
-        <v>2</v>
-      </c>
-      <c r="H60">
-        <v>5</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60">
-        <v>1</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60" t="s">
-        <v>241</v>
-      </c>
-      <c r="N60" t="s">
-        <v>94</v>
-      </c>
-      <c r="O60">
-        <v>1</v>
-      </c>
-      <c r="P60">
-        <v>8</v>
-      </c>
-      <c r="Q60">
+      <c r="B60" s="8">
+        <v>7002</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G60" s="8">
+        <v>18</v>
+      </c>
+      <c r="H60" s="8">
+        <v>15</v>
+      </c>
+      <c r="I60" s="8">
+        <v>0</v>
+      </c>
+      <c r="J60" s="8">
+        <v>0</v>
+      </c>
+      <c r="K60" s="8">
+        <v>1</v>
+      </c>
+      <c r="L60" s="8">
+        <v>0</v>
+      </c>
+      <c r="M60" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="N60" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="O60" s="8">
+        <v>1</v>
+      </c>
+      <c r="P60" s="8">
+        <v>6</v>
+      </c>
+      <c r="Q60" s="8">
         <v>100</v>
       </c>
-      <c r="R60">
-        <v>60</v>
-      </c>
-      <c r="S60" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="T60" t="s">
-        <v>94</v>
-      </c>
-      <c r="U60">
+      <c r="R60" s="8">
+        <v>30</v>
+      </c>
+      <c r="S60" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="T60" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="U60" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:21" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="3">
+    <row r="61" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="8">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="8">
+        <v>8001</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G61" s="8">
+        <v>6</v>
+      </c>
+      <c r="H61" s="8">
+        <v>12</v>
+      </c>
+      <c r="I61" s="8">
+        <v>0</v>
+      </c>
+      <c r="J61" s="8">
+        <v>0</v>
+      </c>
+      <c r="K61" s="8">
+        <v>1</v>
+      </c>
+      <c r="L61" s="8">
+        <v>0</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="N61" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="O61" s="8">
+        <v>1</v>
+      </c>
+      <c r="P61" s="8">
+        <v>7</v>
+      </c>
+      <c r="Q61" s="8">
+        <v>100</v>
+      </c>
+      <c r="R61" s="8">
+        <v>30</v>
+      </c>
+      <c r="S61" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T61" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="U61" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="8">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B62" s="8">
+        <v>8002</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G62" s="8">
+        <v>6</v>
+      </c>
+      <c r="H62" s="8">
+        <v>14</v>
+      </c>
+      <c r="I62" s="8">
+        <v>0</v>
+      </c>
+      <c r="J62" s="8">
+        <v>0</v>
+      </c>
+      <c r="K62" s="8">
+        <v>1</v>
+      </c>
+      <c r="L62" s="8">
+        <v>0</v>
+      </c>
+      <c r="M62" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="N62" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="O62" s="8">
+        <v>1</v>
+      </c>
+      <c r="P62" s="8">
+        <v>7</v>
+      </c>
+      <c r="Q62" s="8">
+        <v>100</v>
+      </c>
+      <c r="R62" s="8">
+        <v>30</v>
+      </c>
+      <c r="S62" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="T62" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="U62" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="3">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B63" s="3">
+        <v>9001</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G63" s="3">
+        <v>2</v>
+      </c>
+      <c r="H63" s="3">
+        <v>7</v>
+      </c>
+      <c r="I63" s="3">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3">
+        <v>0</v>
+      </c>
+      <c r="K63" s="3">
+        <v>10</v>
+      </c>
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O63" s="3">
+        <v>1</v>
+      </c>
+      <c r="P63" s="3">
+        <v>8</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>100</v>
+      </c>
+      <c r="R63" s="3">
+        <v>120</v>
+      </c>
+      <c r="S63" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="T63" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="3">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B64" s="3">
+        <v>9005</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="G64" s="3">
+        <v>2</v>
+      </c>
+      <c r="H64" s="3">
+        <v>7</v>
+      </c>
+      <c r="I64" s="3">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3">
+        <v>0</v>
+      </c>
+      <c r="K64" s="3">
+        <v>3</v>
+      </c>
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O64" s="3">
+        <v>1</v>
+      </c>
+      <c r="P64" s="3">
+        <v>8</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>100</v>
+      </c>
+      <c r="R64" s="3">
+        <v>60</v>
+      </c>
+      <c r="S64" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="T64" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="7">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B65" s="7">
+        <v>9002</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G65" s="7">
+        <v>6</v>
+      </c>
+      <c r="H65" s="7">
+        <v>5</v>
+      </c>
+      <c r="I65" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J65" s="7">
+        <v>0</v>
+      </c>
+      <c r="K65" s="7">
+        <v>10</v>
+      </c>
+      <c r="L65" s="7">
+        <v>0</v>
+      </c>
+      <c r="M65" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N65" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O65" s="7">
+        <v>1</v>
+      </c>
+      <c r="P65" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q65" s="7">
+        <v>100</v>
+      </c>
+      <c r="R65" s="7">
+        <v>30</v>
+      </c>
+      <c r="S65" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="T65" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U65" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>9004</v>
+      </c>
+      <c r="C66" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" t="s">
+        <v>99</v>
+      </c>
+      <c r="E66" t="s">
+        <v>97</v>
+      </c>
+      <c r="F66" t="s">
+        <v>98</v>
+      </c>
+      <c r="G66">
+        <v>2</v>
+      </c>
+      <c r="H66">
+        <v>5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66" t="s">
+        <v>241</v>
+      </c>
+      <c r="N66" t="s">
+        <v>94</v>
+      </c>
+      <c r="O66">
+        <v>1</v>
+      </c>
+      <c r="P66">
+        <v>8</v>
+      </c>
+      <c r="Q66">
+        <v>100</v>
+      </c>
+      <c r="R66">
+        <v>60</v>
+      </c>
+      <c r="S66" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="T66" t="s">
+        <v>94</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="3">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B67" s="3">
         <v>9003</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D67" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="E67" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="F67" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G67" s="3">
         <v>6</v>
       </c>
-      <c r="H61" s="3">
-        <v>1</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3">
-        <v>1</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1</v>
-      </c>
-      <c r="L61" s="3">
-        <v>1</v>
-      </c>
-      <c r="M61" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N61" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O61" s="3">
-        <v>1</v>
-      </c>
-      <c r="P61" s="3">
+      <c r="H67" s="3">
+        <v>1</v>
+      </c>
+      <c r="I67" s="3">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3">
+        <v>1</v>
+      </c>
+      <c r="K67" s="3">
+        <v>1</v>
+      </c>
+      <c r="L67" s="3">
+        <v>1</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O67" s="3">
+        <v>1</v>
+      </c>
+      <c r="P67" s="3">
         <v>8</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="Q67" s="3">
         <v>100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="R67" s="3">
         <v>30</v>
       </c>
-      <c r="S61" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="T61" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U61" s="3">
+      <c r="S67" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="T67" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U67" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF210BF-9DB8-4BCD-8602-BC5527A2004B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A340421F-C912-4F5F-B163-59B44A1098C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2355" yWindow="1155" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="299">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -2193,60 +2193,6 @@
     </rPh>
     <rPh sb="12" eb="14">
       <t>テツダ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ケーキの見た目をきれいに仕上げる。
-クリームをきれいにぬる技術のこと。
-クリームを塗る工程の際に、成功率を少し上げる。
-LVがあがると、きれいにクリームを塗れて、見た目がよくなる。
-LV1: なめらかさ+15, 成功率+3%
-LV2: なめらかさ+30, 成功率+6%
-LV3: なめらかさ+45, 成功率+9%
-LV4: なめらかさ+60, 成功率+12%
-LV5: なめらかさ+75, 成功率+15%</t>
-    <rPh sb="4" eb="5">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ギジュツ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>コウテイ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="49" eb="52">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="78" eb="79">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="82" eb="83">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="84" eb="85">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="108" eb="111">
-      <t>セイコウリツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2683,50 +2629,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>カカオマスの温度調整をし、なめらかにする。
-温度調節はかなり繊細な作業なので、慎重に。
-３つゲージがでてきて、
-各ゲージを赤い点になるべく近づけてストップ。
-LVを上げると、少しゆっくりにできる。</t>
-    <rPh sb="6" eb="10">
-      <t>オンドチョウセイ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>オンド</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>チョウセツ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>センサイ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>サギョウ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>シンチョウ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>アカ</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>テン</t>
-    </rPh>
-    <rPh sb="71" eb="72">
-      <t>チカ</t>
-    </rPh>
-    <rPh sb="85" eb="86">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="90" eb="91">
-      <t>スコ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>光り系のお菓子のキラキラ感を強める。</t>
     <rPh sb="0" eb="1">
       <t>ヒカ</t>
@@ -3697,6 +3599,159 @@
     </rPh>
     <rPh sb="76" eb="78">
       <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコレートを作るために必須の魔法。
+カカオマスの温度調整をし、なめらかにする。
+温度調節はかなり繊細な作業なので、慎重に。
+３つゲージがでてきて、
+各ゲージを赤い点になるべく近づけてストップ。
+LVを上げると、少しゆっくりにできる。</t>
+    <rPh sb="7" eb="8">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="26" eb="30">
+      <t>オンドチョウセイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>オンド</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>チョウセツ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>センサイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>シンチョウ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="91" eb="92">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="105" eb="106">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="110" eb="111">
+      <t>スコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ソーダのお勉強</t>
+    <rPh sb="5" eb="7">
+      <t>ベンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ソーダについて勉強する。</t>
+    <rPh sb="7" eb="9">
+      <t>ベンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Soda_Study</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ソーダについて勉強する。
+LVが上がるにつれて、ジュース・ソーダを作る際の成功率が上昇する。
+また、わずかに、ソーダののどごしもアップする。
+LV1: 成功率+5%
+LV2: 成功率+10%
+LV3: 成功率+15%</t>
+    <rPh sb="7" eb="9">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="37" eb="40">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ケーキの見た目をきれいに仕上げる。
+クリームをきれいにぬる技術のこと。
+クリームを塗る工程の際に、成功率を少し上げる。
+LVがあがると、きれいにクリームを塗れて、見た目がよくなる。
+LV1: ふわふわ+15, 成功率+3%
+LV2: ふわふわ+30, 成功率+6%
+LV3: ふわふわ+45, 成功率+9%
+LV4: ふわふわ+60, 成功率+12%
+LV5: ふわふわ+75, 成功率+15%</t>
+    <rPh sb="4" eb="5">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="49" eb="52">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="82" eb="83">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="107" eb="110">
+      <t>セイコウリツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4132,7 +4187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:U67"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -4189,7 +4244,7 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -4215,7 +4270,7 @@
     </row>
     <row r="2" spans="1:21" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
-        <f t="shared" ref="A2:A67" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A68" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="5">
@@ -4306,7 +4361,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="3">
         <v>0</v>
@@ -4336,7 +4391,7 @@
         <v>30</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>94</v>
@@ -4438,7 +4493,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="3">
         <v>0</v>
@@ -4468,7 +4523,7 @@
         <v>30</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>94</v>
@@ -4477,40 +4532,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="G6" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H6" s="3">
         <v>2</v>
       </c>
       <c r="I6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
       </c>
       <c r="K6" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
@@ -4519,7 +4574,7 @@
         <v>94</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>94</v>
+        <v>254</v>
       </c>
       <c r="O6" s="3">
         <v>1</v>
@@ -4534,7 +4589,7 @@
         <v>30</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="T6" s="3" t="s">
         <v>94</v>
@@ -4543,40 +4598,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:21" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>59</v>
+        <v>171</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="G7" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H7" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
       </c>
       <c r="K7" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="3">
         <v>0</v>
@@ -4588,7 +4643,7 @@
         <v>94</v>
       </c>
       <c r="O7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="3">
         <v>9</v>
@@ -4600,13 +4655,13 @@
         <v>30</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>213</v>
+        <v>293</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="U7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -4621,13 +4676,13 @@
         <v>147</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>234</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
@@ -4636,7 +4691,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -4666,49 +4721,49 @@
         <v>30</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="U8" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:21" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="G9" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H9" s="3">
         <v>2</v>
       </c>
       <c r="I9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
       </c>
       <c r="K9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" s="3">
         <v>0</v>
@@ -4717,7 +4772,7 @@
         <v>94</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>256</v>
+        <v>94</v>
       </c>
       <c r="O9" s="3">
         <v>1</v>
@@ -4732,145 +4787,145 @@
         <v>30</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>242</v>
+        <v>151</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="U9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="7">
+    <row r="10" spans="1:21" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="7">
-        <v>1007</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="G10" s="7">
-        <v>6</v>
-      </c>
-      <c r="H10" s="7">
-        <v>1</v>
-      </c>
-      <c r="I10" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J10" s="7">
-        <v>0</v>
-      </c>
-      <c r="K10" s="7">
-        <v>1</v>
-      </c>
-      <c r="L10" s="7">
-        <v>0</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O10" s="7">
-        <v>1</v>
-      </c>
-      <c r="P10" s="7">
+      <c r="B10" s="3">
+        <v>1004</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
         <v>9</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="Q10" s="3">
         <v>100</v>
       </c>
-      <c r="R10" s="7">
+      <c r="R10" s="3">
         <v>30</v>
       </c>
-      <c r="S10" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U10" s="7">
+      <c r="S10" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U10" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="3">
+    <row r="11" spans="1:21" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="7">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="3">
-        <v>1008</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="B11" s="7">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="D11" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="7">
         <v>6</v>
       </c>
-      <c r="H11" s="3">
-        <v>3</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3">
-        <v>3</v>
-      </c>
-      <c r="L11" s="3">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O11" s="3">
-        <v>1</v>
-      </c>
-      <c r="P11" s="3">
+      <c r="H11" s="7">
+        <v>1</v>
+      </c>
+      <c r="I11" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0</v>
+      </c>
+      <c r="K11" s="7">
+        <v>1</v>
+      </c>
+      <c r="L11" s="7">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O11" s="7">
+        <v>1</v>
+      </c>
+      <c r="P11" s="7">
         <v>9</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="7">
         <v>100</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="7">
         <v>30</v>
       </c>
-      <c r="S11" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="U11" s="3">
-        <v>1</v>
+      <c r="S11" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="T11" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U11" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -4900,7 +4955,7 @@
         <v>5</v>
       </c>
       <c r="I12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -4930,7 +4985,7 @@
         <v>30</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>94</v>
@@ -4954,7 +5009,7 @@
         <v>209</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>211</v>
@@ -5032,7 +5087,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -5062,7 +5117,7 @@
         <v>30</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>94</v>
@@ -5098,7 +5153,7 @@
         <v>3</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -5128,7 +5183,7 @@
         <v>120</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>94</v>
@@ -5296,7 +5351,7 @@
         <v>3</v>
       </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="3">
         <v>0</v>
@@ -5347,13 +5402,13 @@
         <v>35</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>275</v>
       </c>
       <c r="G19" s="3">
         <v>2</v>
@@ -5362,7 +5417,7 @@
         <v>3</v>
       </c>
       <c r="I19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="3">
         <v>0</v>
@@ -5392,7 +5447,7 @@
         <v>30</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="T19" s="3" t="s">
         <v>94</v>
@@ -5416,7 +5471,7 @@
         <v>208</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>210</v>
@@ -5485,7 +5540,7 @@
         <v>157</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G21" s="3">
         <v>2</v>
@@ -5524,7 +5579,7 @@
         <v>30</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>94</v>
@@ -5548,7 +5603,7 @@
         <v>16</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>15</v>
@@ -5560,7 +5615,7 @@
         <v>2</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3">
         <v>1</v>
@@ -5575,7 +5630,7 @@
         <v>94</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O22" s="3">
         <v>1</v>
@@ -5590,7 +5645,7 @@
         <v>30</v>
       </c>
       <c r="S22" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>94</v>
@@ -5626,7 +5681,7 @@
         <v>3</v>
       </c>
       <c r="I23" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="3">
         <v>0</v>
@@ -5641,7 +5696,7 @@
         <v>94</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O23" s="3">
         <v>1</v>
@@ -5656,7 +5711,7 @@
         <v>30</v>
       </c>
       <c r="S23" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>16</v>
@@ -5680,7 +5735,7 @@
         <v>106</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>72</v>
@@ -5692,7 +5747,7 @@
         <v>6</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -5722,7 +5777,7 @@
         <v>60</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>94</v>
@@ -5743,13 +5798,13 @@
         <v>36</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>280</v>
       </c>
       <c r="G25" s="3">
         <v>4</v>
@@ -5758,7 +5813,7 @@
         <v>6</v>
       </c>
       <c r="I25" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="3">
         <v>0</v>
@@ -5788,7 +5843,7 @@
         <v>60</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="T25" s="3" t="s">
         <v>94</v>
@@ -5875,13 +5930,13 @@
         <v>36</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G27" s="3">
         <v>4</v>
@@ -5920,7 +5975,7 @@
         <v>30</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>94</v>
@@ -6052,7 +6107,7 @@
         <v>30</v>
       </c>
       <c r="S29" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="T29" s="7" t="s">
         <v>94</v>
@@ -6118,7 +6173,7 @@
         <v>30</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>220</v>
+        <v>298</v>
       </c>
       <c r="T30" s="3" t="s">
         <v>94</v>
@@ -6154,7 +6209,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="3">
         <v>0</v>
@@ -6184,7 +6239,7 @@
         <v>30</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="T31" s="3" t="s">
         <v>94</v>
@@ -6211,7 +6266,7 @@
         <v>21</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G32" s="3">
         <v>6</v>
@@ -6220,7 +6275,7 @@
         <v>2</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -6232,10 +6287,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O32" s="3">
         <v>1</v>
@@ -6250,7 +6305,7 @@
         <v>30</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>94</v>
@@ -6301,7 +6356,7 @@
         <v>94</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O33" s="3">
         <v>1</v>
@@ -6367,7 +6422,7 @@
         <v>94</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O34" s="3">
         <v>1</v>
@@ -6433,7 +6488,7 @@
         <v>94</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O35" s="3">
         <v>1</v>
@@ -6499,7 +6554,7 @@
         <v>94</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O36" s="3">
         <v>1</v>
@@ -6565,7 +6620,7 @@
         <v>94</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O37" s="3">
         <v>1</v>
@@ -6631,7 +6686,7 @@
         <v>94</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O38" s="3">
         <v>1</v>
@@ -6736,10 +6791,10 @@
         <v>27</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G40" s="3">
         <v>3</v>
@@ -6748,7 +6803,7 @@
         <v>3</v>
       </c>
       <c r="I40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="3">
         <v>0</v>
@@ -6778,7 +6833,7 @@
         <v>30</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="T40" s="3" t="s">
         <v>94</v>
@@ -6871,7 +6926,7 @@
         <v>176</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G42" s="7">
         <v>3</v>
@@ -6895,7 +6950,7 @@
         <v>94</v>
       </c>
       <c r="N42" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O42" s="7">
         <v>1</v>
@@ -6910,7 +6965,7 @@
         <v>30</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="T42" s="7" t="s">
         <v>94</v>
@@ -6937,7 +6992,7 @@
         <v>87</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G43" s="3">
         <v>3</v>
@@ -6946,7 +7001,7 @@
         <v>5</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -6961,7 +7016,7 @@
         <v>94</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O43" s="3">
         <v>1</v>
@@ -6976,7 +7031,7 @@
         <v>30</v>
       </c>
       <c r="S43" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>94</v>
@@ -7003,7 +7058,7 @@
         <v>203</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G44" s="7">
         <v>3</v>
@@ -7027,7 +7082,7 @@
         <v>94</v>
       </c>
       <c r="N44" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O44" s="7">
         <v>1</v>
@@ -7042,7 +7097,7 @@
         <v>30</v>
       </c>
       <c r="S44" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="T44" s="7" t="s">
         <v>94</v>
@@ -7069,7 +7124,7 @@
         <v>88</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G45" s="7">
         <v>3</v>
@@ -7093,7 +7148,7 @@
         <v>94</v>
       </c>
       <c r="N45" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O45" s="7">
         <v>1</v>
@@ -7108,7 +7163,7 @@
         <v>30</v>
       </c>
       <c r="S45" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="T45" s="7" t="s">
         <v>94</v>
@@ -7135,7 +7190,7 @@
         <v>102</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G46" s="7">
         <v>3</v>
@@ -7174,7 +7229,7 @@
         <v>30</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="T46" s="7" t="s">
         <v>94</v>
@@ -7198,7 +7253,7 @@
         <v>163</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>161</v>
@@ -7306,7 +7361,7 @@
         <v>30</v>
       </c>
       <c r="S48" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="T48" s="7" t="s">
         <v>94</v>
@@ -7321,28 +7376,28 @@
         <v>47</v>
       </c>
       <c r="B49" s="3">
-        <v>5001</v>
+        <v>5007</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>39</v>
+        <v>296</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>38</v>
+        <v>294</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>134</v>
+        <v>295</v>
       </c>
       <c r="G49" s="3">
         <v>6</v>
       </c>
       <c r="H49" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -7354,13 +7409,13 @@
         <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="O49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49" s="3">
         <v>4</v>
@@ -7372,7 +7427,7 @@
         <v>30</v>
       </c>
       <c r="S49" s="4" t="s">
-        <v>249</v>
+        <v>297</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>94</v>
@@ -7381,34 +7436,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="3">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="G50" s="3">
         <v>6</v>
       </c>
       <c r="H50" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="3">
         <v>0</v>
@@ -7420,10 +7475,10 @@
         <v>0</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="O50" s="3">
         <v>1</v>
@@ -7438,7 +7493,7 @@
         <v>30</v>
       </c>
       <c r="S50" s="4" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="T50" s="3" t="s">
         <v>94</v>
@@ -7453,19 +7508,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="3">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>192</v>
+        <v>119</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="G51" s="3">
         <v>6</v>
@@ -7474,7 +7529,7 @@
         <v>6</v>
       </c>
       <c r="I51" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="3">
         <v>0</v>
@@ -7501,16 +7556,16 @@
         <v>100</v>
       </c>
       <c r="R51" s="3">
-        <v>480</v>
+        <v>30</v>
       </c>
       <c r="S51" s="4" t="s">
-        <v>212</v>
+        <v>251</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="U51" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -7519,25 +7574,25 @@
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>5005</v>
+        <v>5003</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>207</v>
+        <v>140</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>205</v>
+        <v>139</v>
       </c>
       <c r="G52" s="3">
         <v>6</v>
       </c>
       <c r="H52" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -7552,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>226</v>
+        <v>94</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>94</v>
@@ -7567,10 +7622,10 @@
         <v>100</v>
       </c>
       <c r="R52" s="3">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="S52" s="4" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>94</v>
@@ -7585,43 +7640,43 @@
         <v>51</v>
       </c>
       <c r="B53" s="3">
-        <v>5006</v>
+        <v>5005</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="G53" s="3">
         <v>6</v>
       </c>
       <c r="H53" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="3">
         <v>0</v>
       </c>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>94</v>
+        <v>225</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>256</v>
+        <v>94</v>
       </c>
       <c r="O53" s="3">
         <v>1</v>
@@ -7636,144 +7691,144 @@
         <v>30</v>
       </c>
       <c r="S53" s="4" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="U53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="7">
+    <row r="54" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="3">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B54" s="7">
-        <v>6001</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G54" s="7">
+      <c r="B54" s="3">
+        <v>5006</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G54" s="3">
         <v>6</v>
       </c>
-      <c r="H54" s="7">
-        <v>3</v>
-      </c>
-      <c r="I54" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J54" s="7">
-        <v>0</v>
-      </c>
-      <c r="K54" s="7">
-        <v>10</v>
-      </c>
-      <c r="L54" s="7">
-        <v>0</v>
-      </c>
-      <c r="M54" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N54" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O54" s="7">
-        <v>1</v>
-      </c>
-      <c r="P54" s="7">
-        <v>5</v>
-      </c>
-      <c r="Q54" s="7">
+      <c r="H54" s="3">
+        <v>12</v>
+      </c>
+      <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3">
+        <v>1</v>
+      </c>
+      <c r="L54" s="3">
+        <v>0</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="O54" s="3">
+        <v>1</v>
+      </c>
+      <c r="P54" s="3">
+        <v>4</v>
+      </c>
+      <c r="Q54" s="3">
         <v>100</v>
       </c>
-      <c r="R54" s="7">
+      <c r="R54" s="3">
         <v>30</v>
       </c>
-      <c r="S54" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="T54" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U54" s="7">
+      <c r="S54" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U54" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:21" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="3">
+    <row r="55" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="7">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" s="3">
-        <v>6002</v>
-      </c>
-      <c r="C55" s="3" t="s">
+      <c r="B55" s="7">
+        <v>6001</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="D55" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G55" s="7">
+        <v>6</v>
+      </c>
+      <c r="H55" s="7">
+        <v>3</v>
+      </c>
+      <c r="I55" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J55" s="7">
+        <v>0</v>
+      </c>
+      <c r="K55" s="7">
+        <v>10</v>
+      </c>
+      <c r="L55" s="7">
+        <v>0</v>
+      </c>
+      <c r="M55" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N55" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O55" s="7">
+        <v>1</v>
+      </c>
+      <c r="P55" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q55" s="7">
         <v>100</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G55" s="3">
-        <v>6</v>
-      </c>
-      <c r="H55" s="3">
-        <v>3</v>
-      </c>
-      <c r="I55" s="3">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3">
-        <v>0</v>
-      </c>
-      <c r="K55" s="3">
-        <v>5</v>
-      </c>
-      <c r="L55" s="3">
-        <v>0</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N55" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O55" s="3">
-        <v>1</v>
-      </c>
-      <c r="P55" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q55" s="3">
-        <v>100</v>
-      </c>
-      <c r="R55" s="3">
+      <c r="R55" s="7">
         <v>30</v>
       </c>
-      <c r="S55" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="T55" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U55" s="3">
+      <c r="S55" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T55" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U55" s="7">
         <v>0</v>
       </c>
     </row>
@@ -7783,19 +7838,19 @@
         <v>54</v>
       </c>
       <c r="B56" s="3">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>285</v>
+        <v>101</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>286</v>
+        <v>100</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>287</v>
+        <v>96</v>
       </c>
       <c r="G56" s="3">
         <v>6</v>
@@ -7810,16 +7865,16 @@
         <v>0</v>
       </c>
       <c r="K56" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L56" s="3">
         <v>0</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="O56" s="3">
         <v>1</v>
@@ -7831,10 +7886,10 @@
         <v>100</v>
       </c>
       <c r="R56" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="S56" s="4" t="s">
-        <v>293</v>
+        <v>244</v>
       </c>
       <c r="T56" s="3" t="s">
         <v>94</v>
@@ -7849,19 +7904,19 @@
         <v>55</v>
       </c>
       <c r="B57" s="3">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="G57" s="3">
         <v>6</v>
@@ -7870,7 +7925,7 @@
         <v>3</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
@@ -7900,7 +7955,7 @@
         <v>60</v>
       </c>
       <c r="S57" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>94</v>
@@ -7909,163 +7964,163 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="7">
+    <row r="58" spans="1:21" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="3">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B58" s="7">
-        <v>6003</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G58" s="7">
+      <c r="B58" s="3">
+        <v>6005</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G58" s="3">
         <v>6</v>
       </c>
-      <c r="H58" s="7">
+      <c r="H58" s="3">
         <v>3</v>
       </c>
-      <c r="I58" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J58" s="7">
-        <v>0</v>
-      </c>
-      <c r="K58" s="7">
-        <v>1</v>
-      </c>
-      <c r="L58" s="7">
-        <v>0</v>
-      </c>
-      <c r="M58" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N58" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O58" s="7">
-        <v>1</v>
-      </c>
-      <c r="P58" s="7">
+      <c r="I58" s="3">
+        <v>1</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O58" s="3">
+        <v>1</v>
+      </c>
+      <c r="P58" s="3">
         <v>5</v>
       </c>
-      <c r="Q58" s="7">
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="7">
-        <v>30</v>
-      </c>
-      <c r="S58" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="T58" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U58" s="7">
+      <c r="R58" s="3">
+        <v>60</v>
+      </c>
+      <c r="S58" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="8">
+    <row r="59" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="7">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B59" s="8">
-        <v>7001</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G59" s="8">
+      <c r="B59" s="7">
+        <v>6003</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G59" s="7">
         <v>6</v>
       </c>
-      <c r="H59" s="8">
-        <v>12</v>
-      </c>
-      <c r="I59" s="8">
-        <v>0</v>
-      </c>
-      <c r="J59" s="8">
-        <v>0</v>
-      </c>
-      <c r="K59" s="8">
-        <v>1</v>
-      </c>
-      <c r="L59" s="8">
-        <v>0</v>
-      </c>
-      <c r="M59" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="N59" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="O59" s="8">
-        <v>1</v>
-      </c>
-      <c r="P59" s="8">
-        <v>6</v>
-      </c>
-      <c r="Q59" s="8">
+      <c r="H59" s="7">
+        <v>3</v>
+      </c>
+      <c r="I59" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J59" s="7">
+        <v>0</v>
+      </c>
+      <c r="K59" s="7">
+        <v>1</v>
+      </c>
+      <c r="L59" s="7">
+        <v>0</v>
+      </c>
+      <c r="M59" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N59" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O59" s="7">
+        <v>1</v>
+      </c>
+      <c r="P59" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="7">
         <v>100</v>
       </c>
-      <c r="R59" s="8">
+      <c r="R59" s="7">
         <v>30</v>
       </c>
-      <c r="S59" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="T59" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="U59" s="8">
+      <c r="S59" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="T59" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U59" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:21" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A60" s="8">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B60" s="8">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>69</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G60" s="8">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H60" s="8">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I60" s="8">
         <v>0</v>
@@ -8097,8 +8152,8 @@
       <c r="R60" s="8">
         <v>30</v>
       </c>
-      <c r="S60" s="10" t="s">
-        <v>238</v>
+      <c r="S60" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="T60" s="8" t="s">
         <v>94</v>
@@ -8107,55 +8162,55 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:21" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="8">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B61" s="8">
-        <v>8001</v>
+        <v>7002</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G61" s="8">
+        <v>18</v>
+      </c>
+      <c r="H61" s="8">
+        <v>15</v>
+      </c>
+      <c r="I61" s="8">
+        <v>0</v>
+      </c>
+      <c r="J61" s="8">
+        <v>0</v>
+      </c>
+      <c r="K61" s="8">
+        <v>1</v>
+      </c>
+      <c r="L61" s="8">
+        <v>0</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="N61" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="O61" s="8">
+        <v>1</v>
+      </c>
+      <c r="P61" s="8">
         <v>6</v>
-      </c>
-      <c r="H61" s="8">
-        <v>12</v>
-      </c>
-      <c r="I61" s="8">
-        <v>0</v>
-      </c>
-      <c r="J61" s="8">
-        <v>0</v>
-      </c>
-      <c r="K61" s="8">
-        <v>1</v>
-      </c>
-      <c r="L61" s="8">
-        <v>0</v>
-      </c>
-      <c r="M61" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="N61" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="O61" s="8">
-        <v>1</v>
-      </c>
-      <c r="P61" s="8">
-        <v>7</v>
       </c>
       <c r="Q61" s="8">
         <v>100</v>
@@ -8163,8 +8218,8 @@
       <c r="R61" s="8">
         <v>30</v>
       </c>
-      <c r="S61" s="8" t="s">
-        <v>34</v>
+      <c r="S61" s="10" t="s">
+        <v>237</v>
       </c>
       <c r="T61" s="8" t="s">
         <v>94</v>
@@ -8179,25 +8234,25 @@
         <v>60</v>
       </c>
       <c r="B62" s="8">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>67</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G62" s="8">
         <v>6</v>
       </c>
       <c r="H62" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I62" s="8">
         <v>0</v>
@@ -8230,7 +8285,7 @@
         <v>30</v>
       </c>
       <c r="S62" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T62" s="8" t="s">
         <v>94</v>
@@ -8239,69 +8294,69 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:21" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="3">
+    <row r="63" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="8">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B63" s="3">
-        <v>9001</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G63" s="3">
-        <v>2</v>
-      </c>
-      <c r="H63" s="3">
+      <c r="B63" s="8">
+        <v>8002</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G63" s="8">
+        <v>6</v>
+      </c>
+      <c r="H63" s="8">
+        <v>14</v>
+      </c>
+      <c r="I63" s="8">
+        <v>0</v>
+      </c>
+      <c r="J63" s="8">
+        <v>0</v>
+      </c>
+      <c r="K63" s="8">
+        <v>1</v>
+      </c>
+      <c r="L63" s="8">
+        <v>0</v>
+      </c>
+      <c r="M63" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="N63" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="O63" s="8">
+        <v>1</v>
+      </c>
+      <c r="P63" s="8">
         <v>7</v>
       </c>
-      <c r="I63" s="3">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3">
-        <v>0</v>
-      </c>
-      <c r="K63" s="3">
-        <v>10</v>
-      </c>
-      <c r="L63" s="3">
-        <v>0</v>
-      </c>
-      <c r="M63" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="N63" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="O63" s="3">
-        <v>1</v>
-      </c>
-      <c r="P63" s="3">
-        <v>8</v>
-      </c>
-      <c r="Q63" s="3">
+      <c r="Q63" s="8">
         <v>100</v>
       </c>
-      <c r="R63" s="3">
-        <v>120</v>
-      </c>
-      <c r="S63" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="T63" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U63" s="3">
+      <c r="R63" s="8">
+        <v>30</v>
+      </c>
+      <c r="S63" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="T63" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="U63" s="8">
         <v>0</v>
       </c>
     </row>
@@ -8311,19 +8366,19 @@
         <v>62</v>
       </c>
       <c r="B64" s="3">
-        <v>9005</v>
+        <v>9001</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>68</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>283</v>
+        <v>78</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>284</v>
+        <v>93</v>
       </c>
       <c r="G64" s="3">
         <v>2</v>
@@ -8338,7 +8393,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L64" s="3">
         <v>0</v>
@@ -8359,10 +8414,10 @@
         <v>100</v>
       </c>
       <c r="R64" s="3">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="S64" s="4" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="T64" s="3" t="s">
         <v>94</v>
@@ -8371,201 +8426,267 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="7">
+    <row r="65" spans="1:21" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="3">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B65" s="7">
-        <v>9002</v>
-      </c>
-      <c r="C65" s="7" t="s">
+      <c r="B65" s="3">
+        <v>9005</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D65" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G65" s="7">
-        <v>6</v>
-      </c>
-      <c r="H65" s="7">
-        <v>5</v>
-      </c>
-      <c r="I65" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J65" s="7">
-        <v>0</v>
-      </c>
-      <c r="K65" s="7">
-        <v>10</v>
-      </c>
-      <c r="L65" s="7">
-        <v>0</v>
-      </c>
-      <c r="M65" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N65" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O65" s="7">
-        <v>1</v>
-      </c>
-      <c r="P65" s="7">
+      <c r="D65" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G65" s="3">
+        <v>2</v>
+      </c>
+      <c r="H65" s="3">
+        <v>7</v>
+      </c>
+      <c r="I65" s="3">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3">
+        <v>0</v>
+      </c>
+      <c r="K65" s="3">
+        <v>3</v>
+      </c>
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O65" s="3">
+        <v>1</v>
+      </c>
+      <c r="P65" s="3">
         <v>8</v>
       </c>
-      <c r="Q65" s="7">
+      <c r="Q65" s="3">
         <v>100</v>
       </c>
-      <c r="R65" s="7">
-        <v>30</v>
-      </c>
-      <c r="S65" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="T65" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U65" s="7">
+      <c r="R65" s="3">
+        <v>60</v>
+      </c>
+      <c r="S65" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="T65" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U65" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66">
+    <row r="66" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="7">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B66">
-        <v>9004</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="B66" s="7">
+        <v>9002</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D66" t="s">
-        <v>99</v>
-      </c>
-      <c r="E66" t="s">
-        <v>97</v>
-      </c>
-      <c r="F66" t="s">
-        <v>98</v>
-      </c>
-      <c r="G66">
-        <v>2</v>
-      </c>
-      <c r="H66">
+      <c r="D66" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G66" s="7">
+        <v>6</v>
+      </c>
+      <c r="H66" s="7">
         <v>5</v>
       </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>1</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66" t="s">
-        <v>241</v>
-      </c>
-      <c r="N66" t="s">
-        <v>94</v>
-      </c>
-      <c r="O66">
-        <v>1</v>
-      </c>
-      <c r="P66">
+      <c r="I66" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J66" s="7">
+        <v>0</v>
+      </c>
+      <c r="K66" s="7">
+        <v>10</v>
+      </c>
+      <c r="L66" s="7">
+        <v>0</v>
+      </c>
+      <c r="M66" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N66" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O66" s="7">
+        <v>1</v>
+      </c>
+      <c r="P66" s="7">
         <v>8</v>
       </c>
-      <c r="Q66">
+      <c r="Q66" s="7">
         <v>100</v>
       </c>
-      <c r="R66">
-        <v>60</v>
-      </c>
-      <c r="S66" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="T66" t="s">
-        <v>94</v>
-      </c>
-      <c r="U66">
+      <c r="R66" s="7">
+        <v>30</v>
+      </c>
+      <c r="S66" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="T66" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U66" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:21" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="3">
+    <row r="67" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67">
+        <v>9004</v>
+      </c>
+      <c r="C67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>99</v>
+      </c>
+      <c r="E67" t="s">
+        <v>97</v>
+      </c>
+      <c r="F67" t="s">
+        <v>98</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="H67">
+        <v>5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="s">
+        <v>240</v>
+      </c>
+      <c r="N67" t="s">
+        <v>94</v>
+      </c>
+      <c r="O67">
+        <v>1</v>
+      </c>
+      <c r="P67">
+        <v>8</v>
+      </c>
+      <c r="Q67">
+        <v>100</v>
+      </c>
+      <c r="R67">
+        <v>60</v>
+      </c>
+      <c r="S67" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="T67" t="s">
+        <v>94</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="3">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="B68" s="3">
         <v>9003</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F68" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G67" s="3">
+      <c r="G68" s="3">
         <v>6</v>
       </c>
-      <c r="H67" s="3">
-        <v>1</v>
-      </c>
-      <c r="I67" s="3">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3">
-        <v>1</v>
-      </c>
-      <c r="K67" s="3">
-        <v>1</v>
-      </c>
-      <c r="L67" s="3">
-        <v>1</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O67" s="3">
-        <v>1</v>
-      </c>
-      <c r="P67" s="3">
+      <c r="H68" s="3">
+        <v>1</v>
+      </c>
+      <c r="I68" s="3">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3">
+        <v>1</v>
+      </c>
+      <c r="K68" s="3">
+        <v>1</v>
+      </c>
+      <c r="L68" s="3">
+        <v>1</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O68" s="3">
+        <v>1</v>
+      </c>
+      <c r="P68" s="3">
         <v>8</v>
       </c>
-      <c r="Q67" s="3">
+      <c r="Q68" s="3">
         <v>100</v>
       </c>
-      <c r="R67" s="3">
+      <c r="R68" s="3">
         <v>30</v>
       </c>
-      <c r="S67" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="T67" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U67" s="3">
+      <c r="S68" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="T68" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U68" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A340421F-C912-4F5F-B163-59B44A1098C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8E6A82-9CBC-4F31-AC6B-E2E74B84B75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4201,6 +4201,8 @@
     <col min="17" max="17" width="10.375" customWidth="1"/>
     <col min="18" max="18" width="7.875" customWidth="1"/>
     <col min="19" max="19" width="25.125" customWidth="1"/>
+    <col min="20" max="20" width="11.625" customWidth="1"/>
+    <col min="21" max="21" width="6.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
@@ -4538,25 +4540,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="G6" s="3">
         <v>6</v>
       </c>
       <c r="H6" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I6" s="3">
         <v>1</v>
@@ -4565,16 +4567,16 @@
         <v>0</v>
       </c>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="O6" s="3">
         <v>1</v>
@@ -4589,7 +4591,7 @@
         <v>30</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="T6" s="3" t="s">
         <v>94</v>
@@ -4604,25 +4606,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3">
         <v>6</v>
       </c>
       <c r="H7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" s="3">
         <v>1</v>
@@ -4631,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" s="3">
         <v>0</v>
@@ -4640,7 +4642,7 @@
         <v>94</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>94</v>
+        <v>254</v>
       </c>
       <c r="O7" s="3">
         <v>1</v>
@@ -4655,10 +4657,10 @@
         <v>30</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>293</v>
+        <v>241</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="U7" s="3">
         <v>1</v>
@@ -4670,25 +4672,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>232</v>
+        <v>171</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>233</v>
+        <v>104</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
       </c>
       <c r="H8" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I8" s="3">
         <v>1</v>
@@ -4703,10 +4705,10 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="O8" s="3">
         <v>1</v>
@@ -4721,13 +4723,13 @@
         <v>30</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="U8" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:21" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -4796,52 +4798,52 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>61</v>
+        <v>231</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>59</v>
+        <v>232</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>60</v>
+        <v>233</v>
       </c>
       <c r="G10" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
       </c>
       <c r="K10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" s="3">
         <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="O10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="3">
         <v>9</v>
@@ -4853,144 +4855,144 @@
         <v>30</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>213</v>
+        <v>274</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="U10" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="7">
+    <row r="11" spans="1:21" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="7">
-        <v>1007</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="G11" s="7">
-        <v>6</v>
-      </c>
-      <c r="H11" s="7">
-        <v>1</v>
-      </c>
-      <c r="I11" s="7">
-        <v>9999</v>
-      </c>
-      <c r="J11" s="7">
-        <v>0</v>
-      </c>
-      <c r="K11" s="7">
-        <v>1</v>
-      </c>
-      <c r="L11" s="7">
-        <v>0</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O11" s="7">
-        <v>1</v>
-      </c>
-      <c r="P11" s="7">
+      <c r="B11" s="3">
+        <v>1004</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="3">
+        <v>2</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
+        <v>1</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3">
         <v>9</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="3">
         <v>100</v>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="3">
         <v>30</v>
       </c>
-      <c r="S11" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="T11" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U11" s="7">
+      <c r="S11" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="U11" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="3">
+    <row r="12" spans="1:21" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="7">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="3">
-        <v>1009</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="B12" s="7">
+        <v>1007</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="D12" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" s="7">
         <v>6</v>
       </c>
-      <c r="H12" s="3">
-        <v>5</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3">
-        <v>3</v>
-      </c>
-      <c r="L12" s="3">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="H12" s="7">
+        <v>1</v>
+      </c>
+      <c r="I12" s="7">
+        <v>9999</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0</v>
+      </c>
+      <c r="K12" s="7">
+        <v>1</v>
+      </c>
+      <c r="L12" s="7">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O12" s="7">
+        <v>1</v>
+      </c>
+      <c r="P12" s="7">
         <v>9</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="7">
         <v>100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="R12" s="7">
         <v>30</v>
       </c>
-      <c r="S12" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U12" s="3">
+      <c r="S12" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="T12" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U12" s="7">
         <v>0</v>
       </c>
     </row>
@@ -5186,10 +5188,10 @@
         <v>229</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="U15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -5330,19 +5332,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>118</v>
+        <v>272</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>111</v>
+        <v>271</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>135</v>
+        <v>273</v>
       </c>
       <c r="G18" s="3">
         <v>2</v>
@@ -5357,16 +5359,16 @@
         <v>0</v>
       </c>
       <c r="K18" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L18" s="3">
         <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="O18" s="3">
         <v>1</v>
@@ -5381,13 +5383,13 @@
         <v>30</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>166</v>
+        <v>275</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="U18" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -5396,19 +5398,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="3">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>272</v>
+        <v>118</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>271</v>
+        <v>111</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>273</v>
+        <v>135</v>
       </c>
       <c r="G19" s="3">
         <v>2</v>
@@ -5423,16 +5425,16 @@
         <v>0</v>
       </c>
       <c r="K19" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L19" s="3">
         <v>0</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>136</v>
+        <v>94</v>
       </c>
       <c r="O19" s="3">
         <v>1</v>
@@ -5447,7 +5449,7 @@
         <v>30</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>275</v>
+        <v>166</v>
       </c>
       <c r="T19" s="3" t="s">
         <v>94</v>
@@ -5780,10 +5782,10 @@
         <v>249</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="U24" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -6308,10 +6310,10 @@
         <v>265</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -6836,10 +6838,10 @@
         <v>286</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="U40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:21" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -7034,10 +7036,10 @@
         <v>261</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="U43" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
@@ -7496,10 +7498,10 @@
         <v>247</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>94</v>
+        <v>296</v>
       </c>
       <c r="U50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -7694,10 +7696,10 @@
         <v>204</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>39</v>
+        <v>296</v>
       </c>
       <c r="U53" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8E6A82-9CBC-4F31-AC6B-E2E74B84B75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA2636D-F577-4C28-A7C5-837608E3C2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1755" yWindow="1035" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3276,13 +3276,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>レアアイテム発見+1</t>
-    <rPh sb="6" eb="8">
-      <t>ハッケン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ニーモニック</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3752,6 +3745,13 @@
     </rPh>
     <rPh sb="107" eb="110">
       <t>セイコウリツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>レアもの発見+1</t>
+    <rPh sb="4" eb="6">
+      <t>ハッケン</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4723,7 +4723,7 @@
         <v>30</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>80</v>
@@ -4855,7 +4855,7 @@
         <v>30</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>54</v>
@@ -5338,13 +5338,13 @@
         <v>35</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="G18" s="3">
         <v>2</v>
@@ -5383,7 +5383,7 @@
         <v>30</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>51</v>
@@ -5800,13 +5800,13 @@
         <v>36</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="G25" s="3">
         <v>4</v>
@@ -5845,7 +5845,7 @@
         <v>60</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="T25" s="3" t="s">
         <v>94</v>
@@ -5935,7 +5935,7 @@
         <v>267</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>270</v>
+        <v>298</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>268</v>
@@ -6175,7 +6175,7 @@
         <v>30</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="T30" s="3" t="s">
         <v>94</v>
@@ -6835,7 +6835,7 @@
         <v>30</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T40" s="3" t="s">
         <v>23</v>
@@ -7384,13 +7384,13 @@
         <v>66</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E49" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="G49" s="3">
         <v>6</v>
@@ -7429,7 +7429,7 @@
         <v>30</v>
       </c>
       <c r="S49" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>94</v>
@@ -7498,7 +7498,7 @@
         <v>247</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="U50" s="3">
         <v>1</v>
@@ -7696,7 +7696,7 @@
         <v>204</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="U53" s="3">
         <v>3</v>
@@ -7912,13 +7912,13 @@
         <v>65</v>
       </c>
       <c r="D57" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="F57" s="3" t="s">
         <v>284</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>285</v>
       </c>
       <c r="G57" s="3">
         <v>6</v>
@@ -7957,7 +7957,7 @@
         <v>60</v>
       </c>
       <c r="S57" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>94</v>
@@ -7978,13 +7978,13 @@
         <v>65</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="G58" s="3">
         <v>6</v>
@@ -8023,7 +8023,7 @@
         <v>60</v>
       </c>
       <c r="S58" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>94</v>
@@ -8440,13 +8440,13 @@
         <v>68</v>
       </c>
       <c r="D65" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>281</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="G65" s="3">
         <v>2</v>
@@ -8485,7 +8485,7 @@
         <v>60</v>
       </c>
       <c r="S65" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T65" s="3" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA2636D-F577-4C28-A7C5-837608E3C2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0494E7BF-4DCC-491D-A506-0E0EC79BA124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="1035" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1335" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4600,28 +4600,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:21" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" s="3">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="G7" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H7" s="3">
         <v>2</v>
@@ -4633,7 +4633,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="3">
         <v>0</v>
@@ -4642,7 +4642,7 @@
         <v>94</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>254</v>
+        <v>94</v>
       </c>
       <c r="O7" s="3">
         <v>1</v>
@@ -4657,10 +4657,10 @@
         <v>30</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>241</v>
+        <v>151</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="U7" s="3">
         <v>1</v>
@@ -4672,34 +4672,34 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="G8" s="3">
         <v>6</v>
       </c>
       <c r="H8" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -4708,7 +4708,7 @@
         <v>94</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>94</v>
+        <v>254</v>
       </c>
       <c r="O8" s="3">
         <v>1</v>
@@ -4723,43 +4723,43 @@
         <v>30</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>292</v>
+        <v>241</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="U8" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B9" s="3">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>64</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>56</v>
+        <v>171</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="G9" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H9" s="3">
         <v>2</v>
       </c>
       <c r="I9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -4789,7 +4789,7 @@
         <v>30</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>151</v>
+        <v>292</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>80</v>
@@ -4822,7 +4822,7 @@
         <v>6</v>
       </c>
       <c r="H10" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I10" s="3">
         <v>1</v>
@@ -4858,10 +4858,10 @@
         <v>273</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="U10" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:21" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5152,10 +5152,10 @@
         <v>2</v>
       </c>
       <c r="H15" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -5188,10 +5188,10 @@
         <v>229</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="U15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -5218,7 +5218,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16" s="3">
         <v>0</v>
@@ -5350,7 +5350,7 @@
         <v>2</v>
       </c>
       <c r="H18" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="3">
         <v>1</v>
@@ -5389,7 +5389,7 @@
         <v>51</v>
       </c>
       <c r="U18" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -5452,10 +5452,10 @@
         <v>166</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="U19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:21" s="7" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -5746,7 +5746,7 @@
         <v>4</v>
       </c>
       <c r="H24" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I24" s="3">
         <v>1</v>
@@ -5812,10 +5812,10 @@
         <v>4</v>
       </c>
       <c r="H25" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3">
         <v>0</v>
@@ -6406,7 +6406,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I34" s="3">
         <v>1</v>
@@ -6472,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I35" s="3">
         <v>1</v>
@@ -6538,7 +6538,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I36" s="3">
         <v>1</v>
@@ -6604,7 +6604,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I37" s="3">
         <v>0</v>
@@ -6670,7 +6670,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I38" s="3">
         <v>0</v>
@@ -7528,7 +7528,7 @@
         <v>6</v>
       </c>
       <c r="H51" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I51" s="3">
         <v>1</v>
@@ -7660,7 +7660,7 @@
         <v>6</v>
       </c>
       <c r="H53" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I53" s="3">
         <v>1</v>
@@ -7699,7 +7699,7 @@
         <v>295</v>
       </c>
       <c r="U53" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -7726,7 +7726,7 @@
         <v>6</v>
       </c>
       <c r="H54" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I54" s="3">
         <v>0</v>
@@ -7858,7 +7858,7 @@
         <v>6</v>
       </c>
       <c r="H56" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I56" s="3">
         <v>0</v>
@@ -7924,10 +7924,10 @@
         <v>6</v>
       </c>
       <c r="H57" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
@@ -7990,10 +7990,10 @@
         <v>6</v>
       </c>
       <c r="H58" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -8452,7 +8452,7 @@
         <v>2</v>
       </c>
       <c r="H65" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I65" s="3">
         <v>0</v>
@@ -8584,7 +8584,7 @@
         <v>2</v>
       </c>
       <c r="H67">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I67">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0494E7BF-4DCC-491D-A506-0E0EC79BA124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22021DF-A2A4-4125-8BD2-ACC6EBD0E339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1335" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2055" yWindow="1080" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3276,10 +3276,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ニーモニック</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Mnemonic</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3416,10 +3412,6 @@
     <rPh sb="64" eb="65">
       <t>ツカ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>サンティマン</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3753,6 +3745,14 @@
     <rPh sb="4" eb="6">
       <t>ハッケン</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おさかな・パラダイス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>らぶらぶ・ハ～ト</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4789,7 +4789,7 @@
         <v>30</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>80</v>
@@ -4855,7 +4855,7 @@
         <v>30</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>58</v>
@@ -5338,13 +5338,13 @@
         <v>35</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="G18" s="3">
         <v>2</v>
@@ -5383,7 +5383,7 @@
         <v>30</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>51</v>
@@ -5776,7 +5776,7 @@
         <v>100</v>
       </c>
       <c r="R24" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="S24" s="4" t="s">
         <v>249</v>
@@ -5800,13 +5800,13 @@
         <v>36</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>276</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>277</v>
       </c>
       <c r="G25" s="3">
         <v>4</v>
@@ -5842,10 +5842,10 @@
         <v>100</v>
       </c>
       <c r="R25" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="T25" s="3" t="s">
         <v>94</v>
@@ -5887,7 +5887,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L26" s="3">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>267</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>268</v>
@@ -6175,7 +6175,7 @@
         <v>30</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="T30" s="3" t="s">
         <v>94</v>
@@ -6835,7 +6835,7 @@
         <v>30</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T40" s="3" t="s">
         <v>23</v>
@@ -7384,13 +7384,13 @@
         <v>66</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G49" s="3">
         <v>6</v>
@@ -7429,7 +7429,7 @@
         <v>30</v>
       </c>
       <c r="S49" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>94</v>
@@ -7498,7 +7498,7 @@
         <v>247</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="U50" s="3">
         <v>1</v>
@@ -7696,7 +7696,7 @@
         <v>204</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="U53" s="3">
         <v>1</v>
@@ -7912,13 +7912,13 @@
         <v>65</v>
       </c>
       <c r="D57" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F57" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>284</v>
       </c>
       <c r="G57" s="3">
         <v>6</v>
@@ -7954,10 +7954,10 @@
         <v>100</v>
       </c>
       <c r="R57" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="S57" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>94</v>
@@ -7978,13 +7978,13 @@
         <v>65</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="G58" s="3">
         <v>6</v>
@@ -8020,10 +8020,10 @@
         <v>100</v>
       </c>
       <c r="R58" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="S58" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>94</v>
@@ -8440,13 +8440,13 @@
         <v>68</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E65" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>281</v>
       </c>
       <c r="G65" s="3">
         <v>2</v>
@@ -8482,10 +8482,10 @@
         <v>100</v>
       </c>
       <c r="R65" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="S65" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="T65" s="3" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22021DF-A2A4-4125-8BD2-ACC6EBD0E339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F14DFB7-D9DD-4230-9512-B8BF513A18AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="1080" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2565,70 +2565,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>豆類を焼いて香りや味を出す。豆殻も一緒に取る。
-一度に多く焼くと、その分だけ味も凝縮される。
-派生：
-LV1でテンパリング習得可</t>
-    <rPh sb="0" eb="1">
-      <t>マメ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>ルイ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>カオ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>アジ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>マメ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>カラ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>イッショ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="28" eb="29">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="36" eb="37">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>アジ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ギョウシュク</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ハセイ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>シュウトク</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>光り系のお菓子のキラキラ感を強める。</t>
     <rPh sb="0" eb="1">
       <t>ヒカ</t>
@@ -3296,75 +3232,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>お菓子の周りに花火を飛ばした演出が可能になる。
-LVが上がると効果が高まる。
-相性が良ければ、お菓子に夏らしさを追加でき、見た目も上がる。
-◆パネルにお菓子がセットされた状態でないと使えない。
-◆仕上げ回数を一回消費する。
-仕上げ回数がないと、使用できない。</t>
-    <rPh sb="1" eb="3">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>マワ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハナビ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>エンシュツ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カノウ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>アイショウ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="51" eb="52">
-      <t>ナツ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>お菓子の周りに貝殻やおさかなを飛ばした演出が可能になる。
-LVが上がると効果が高まる。
-海らしさが上がる。
-◆パネルにお菓子がセットされた状態でないと使えない。
-◆仕上げ回数を一回消費する。
-仕上げ回数がないと、使用できない。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>グリッター</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3748,11 +3615,134 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>おさかな・パラダイス</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>らぶらぶ・ハ～ト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>豆類を焼いて香りや味を出す。豆殻も一緒に取る。
+派生：
+LV1でテンパリング習得可</t>
+    <rPh sb="0" eb="1">
+      <t>マメ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ルイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>マメ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カラ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イッショ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ハセイ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>シュウトク</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>かいがら・パラダイス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お菓子の周りに花火を飛ばした演出が可能になる。
+LVが上がると効果が高まる。
+相性が良ければ、お菓子に夏らしさ・子供らしさを追加でき、見た目も上がる。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="1" eb="3">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハナビ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>アイショウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お菓子の周りに貝殻やおさかなを飛ばした演出が可能になる。
+LVが上がると効果が高まる。
+相性がよければ、海らしさ・子供らしさが上がる。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="44" eb="46">
+      <t>アイショウ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>コドモ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4246,7 +4236,7 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -4393,7 +4383,7 @@
         <v>30</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>94</v>
@@ -4525,7 +4515,7 @@
         <v>30</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>94</v>
@@ -4591,7 +4581,7 @@
         <v>30</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="T6" s="3" t="s">
         <v>94</v>
@@ -4708,7 +4698,7 @@
         <v>94</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O8" s="3">
         <v>1</v>
@@ -4723,7 +4713,7 @@
         <v>30</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>241</v>
+        <v>295</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>164</v>
@@ -4789,7 +4779,7 @@
         <v>30</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>80</v>
@@ -4855,7 +4845,7 @@
         <v>30</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>58</v>
@@ -5119,7 +5109,7 @@
         <v>30</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>94</v>
@@ -5338,13 +5328,13 @@
         <v>35</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="G18" s="3">
         <v>2</v>
@@ -5383,7 +5373,7 @@
         <v>30</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>51</v>
@@ -5542,7 +5532,7 @@
         <v>157</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G21" s="3">
         <v>2</v>
@@ -5581,7 +5571,7 @@
         <v>30</v>
       </c>
       <c r="S21" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>94</v>
@@ -5632,7 +5622,7 @@
         <v>94</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O22" s="3">
         <v>1</v>
@@ -5698,7 +5688,7 @@
         <v>94</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O23" s="3">
         <v>1</v>
@@ -5779,7 +5769,7 @@
         <v>30</v>
       </c>
       <c r="S24" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>20</v>
@@ -5800,13 +5790,13 @@
         <v>36</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G25" s="3">
         <v>4</v>
@@ -5845,7 +5835,7 @@
         <v>30</v>
       </c>
       <c r="S25" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="T25" s="3" t="s">
         <v>94</v>
@@ -5932,13 +5922,13 @@
         <v>36</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="G27" s="3">
         <v>4</v>
@@ -5977,7 +5967,7 @@
         <v>30</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>94</v>
@@ -6175,7 +6165,7 @@
         <v>30</v>
       </c>
       <c r="S30" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="T30" s="3" t="s">
         <v>94</v>
@@ -6241,7 +6231,7 @@
         <v>30</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T31" s="3" t="s">
         <v>94</v>
@@ -6268,7 +6258,7 @@
         <v>21</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G32" s="3">
         <v>6</v>
@@ -6289,10 +6279,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O32" s="3">
         <v>1</v>
@@ -6307,7 +6297,7 @@
         <v>30</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>155</v>
@@ -6358,7 +6348,7 @@
         <v>94</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O33" s="3">
         <v>1</v>
@@ -6424,7 +6414,7 @@
         <v>94</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O34" s="3">
         <v>1</v>
@@ -6490,7 +6480,7 @@
         <v>94</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O35" s="3">
         <v>1</v>
@@ -6556,7 +6546,7 @@
         <v>94</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O36" s="3">
         <v>1</v>
@@ -6622,7 +6612,7 @@
         <v>94</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O37" s="3">
         <v>1</v>
@@ -6688,7 +6678,7 @@
         <v>94</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O38" s="3">
         <v>1</v>
@@ -6793,7 +6783,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>230</v>
@@ -6835,7 +6825,7 @@
         <v>30</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="T40" s="3" t="s">
         <v>23</v>
@@ -6928,7 +6918,7 @@
         <v>176</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G42" s="7">
         <v>3</v>
@@ -6952,7 +6942,7 @@
         <v>94</v>
       </c>
       <c r="N42" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O42" s="7">
         <v>1</v>
@@ -6967,7 +6957,7 @@
         <v>30</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="T42" s="7" t="s">
         <v>94</v>
@@ -6994,7 +6984,7 @@
         <v>87</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G43" s="3">
         <v>3</v>
@@ -7018,7 +7008,7 @@
         <v>94</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O43" s="3">
         <v>1</v>
@@ -7033,7 +7023,7 @@
         <v>30</v>
       </c>
       <c r="S43" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>155</v>
@@ -7060,7 +7050,7 @@
         <v>203</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G44" s="7">
         <v>3</v>
@@ -7084,7 +7074,7 @@
         <v>94</v>
       </c>
       <c r="N44" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O44" s="7">
         <v>1</v>
@@ -7099,7 +7089,7 @@
         <v>30</v>
       </c>
       <c r="S44" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T44" s="7" t="s">
         <v>94</v>
@@ -7126,7 +7116,7 @@
         <v>88</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G45" s="7">
         <v>3</v>
@@ -7150,7 +7140,7 @@
         <v>94</v>
       </c>
       <c r="N45" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O45" s="7">
         <v>1</v>
@@ -7165,7 +7155,7 @@
         <v>30</v>
       </c>
       <c r="S45" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="T45" s="7" t="s">
         <v>94</v>
@@ -7192,7 +7182,7 @@
         <v>102</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G46" s="7">
         <v>3</v>
@@ -7231,7 +7221,7 @@
         <v>30</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="T46" s="7" t="s">
         <v>94</v>
@@ -7384,13 +7374,13 @@
         <v>66</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G49" s="3">
         <v>6</v>
@@ -7429,7 +7419,7 @@
         <v>30</v>
       </c>
       <c r="S49" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>94</v>
@@ -7495,10 +7485,10 @@
         <v>30</v>
       </c>
       <c r="S50" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="U50" s="3">
         <v>1</v>
@@ -7561,7 +7551,7 @@
         <v>30</v>
       </c>
       <c r="S51" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="T51" s="3" t="s">
         <v>39</v>
@@ -7696,7 +7686,7 @@
         <v>204</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="U53" s="3">
         <v>1</v>
@@ -7744,7 +7734,7 @@
         <v>94</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O54" s="3">
         <v>1</v>
@@ -7891,7 +7881,7 @@
         <v>30</v>
       </c>
       <c r="S56" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="T56" s="3" t="s">
         <v>94</v>
@@ -7912,13 +7902,13 @@
         <v>65</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G57" s="3">
         <v>6</v>
@@ -7957,7 +7947,7 @@
         <v>30</v>
       </c>
       <c r="S57" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>94</v>
@@ -7978,13 +7968,13 @@
         <v>65</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G58" s="3">
         <v>6</v>
@@ -8023,7 +8013,7 @@
         <v>30</v>
       </c>
       <c r="S58" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>94</v>
@@ -8419,7 +8409,7 @@
         <v>120</v>
       </c>
       <c r="S64" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="T64" s="3" t="s">
         <v>94</v>
@@ -8440,13 +8430,13 @@
         <v>68</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G65" s="3">
         <v>2</v>
@@ -8485,7 +8475,7 @@
         <v>30</v>
       </c>
       <c r="S65" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="T65" s="3" t="s">
         <v>94</v>
@@ -8683,7 +8673,7 @@
         <v>30</v>
       </c>
       <c r="S68" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T68" s="3" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F14DFB7-D9DD-4230-9512-B8BF513A18AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA41BAD0-338C-4186-A26D-2AF218494FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3180" yWindow="1215" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="319">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -3615,10 +3615,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>らぶらぶ・ハ～ト</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>豆類を焼いて香りや味を出す。豆殻も一緒に取る。
 派生：
 LV1でテンパリング習得可</t>
@@ -3743,6 +3739,90 @@
     <rPh sb="57" eb="59">
       <t>コドモ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サンティマン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Saint_Fleur</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_True_of_Myheart</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Santiman</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Aroma_Potion</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Wind_Ark</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Wind_Twister</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Wind_Heart</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Wind_FlatBar</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Wind_Crown</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Glitter</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Bubble_Mist</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_SugerPot</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Freezing_OverRun</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Mnemonic</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Heart_of_Icecream</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Cookie_SecondBake</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Cookie_Caramelized</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Chocolate_Philosophy</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Star_Blessing</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Cookie_FireFlower</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4467,7 +4547,7 @@
         <v>1010</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>143</v>
+        <v>316</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>164</v>
@@ -4533,7 +4613,7 @@
         <v>1009</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>64</v>
+        <v>314</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>112</v>
@@ -4599,7 +4679,7 @@
         <v>1003</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>64</v>
+        <v>315</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>58</v>
@@ -4713,7 +4793,7 @@
         <v>30</v>
       </c>
       <c r="S8" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>164</v>
@@ -4797,7 +4877,7 @@
         <v>1006</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>147</v>
+        <v>318</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>231</v>
@@ -4845,7 +4925,7 @@
         <v>30</v>
       </c>
       <c r="S10" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>58</v>
@@ -5061,7 +5141,7 @@
         <v>2004</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>35</v>
+        <v>313</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>110</v>
@@ -5193,7 +5273,7 @@
         <v>2001</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>144</v>
+        <v>311</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>177</v>
@@ -5325,13 +5405,13 @@
         <v>2005</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>269</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>270</v>
@@ -5373,7 +5453,7 @@
         <v>30</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>51</v>
@@ -5391,7 +5471,7 @@
         <v>2003</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>35</v>
+        <v>310</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>118</v>
@@ -5787,7 +5867,7 @@
         <v>3008</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>36</v>
+        <v>308</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>272</v>
@@ -6249,7 +6329,7 @@
         <v>4001</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>37</v>
+        <v>303</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>23</v>
@@ -6315,7 +6395,7 @@
         <v>4002</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>37</v>
+        <v>304</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -6381,7 +6461,7 @@
         <v>4010</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>37</v>
+        <v>305</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>128</v>
@@ -6447,7 +6527,7 @@
         <v>4011</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>37</v>
+        <v>306</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>173</v>
@@ -6513,7 +6593,7 @@
         <v>4012</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>37</v>
+        <v>307</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>175</v>
@@ -6777,7 +6857,7 @@
         <v>4004</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>37</v>
+        <v>309</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>27</v>
@@ -7437,7 +7517,7 @@
         <v>5001</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>66</v>
+        <v>317</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>39</v>
@@ -7833,7 +7913,7 @@
         <v>6002</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>65</v>
+        <v>302</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>101</v>
@@ -7965,7 +8045,7 @@
         <v>6005</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>65</v>
+        <v>299</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>281</v>
@@ -8427,13 +8507,13 @@
         <v>9005</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>68</v>
+        <v>301</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>275</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>276</v>
@@ -8625,7 +8705,7 @@
         <v>9003</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>68</v>
+        <v>300</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>108</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA41BAD0-338C-4186-A26D-2AF218494FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB90252-D024-421B-9B0D-2BF7D695C4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1215" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2835" yWindow="870" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="320">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -3823,6 +3823,10 @@
   </si>
   <si>
     <t>skicon_Cookie_FireFlower</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Appaleil_Study</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -6263,7 +6267,7 @@
         <v>4011</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>37</v>
+        <v>319</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>155</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB90252-D024-421B-9B0D-2BF7D695C4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EA8080-CCF1-4056-8A81-630DE0C10133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="870" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3495" yWindow="1125" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="323">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -3827,6 +3827,18 @@
   </si>
   <si>
     <t>skicon_Appaleil_Study</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Buttelfy_illumination</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Rare_FindUP</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_MP_Regenaration</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -5805,7 +5817,7 @@
         <v>3003</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>36</v>
+        <v>320</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>106</v>
@@ -5937,7 +5949,7 @@
         <v>3004</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>36</v>
+        <v>322</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>115</v>
@@ -6003,7 +6015,7 @@
         <v>3007</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>36</v>
+        <v>321</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>266</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EA8080-CCF1-4056-8A81-630DE0C10133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41357C68-8D10-4E4F-A541-3F7F26B7BEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3495" yWindow="1125" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1950" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2739,52 +2739,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>できたてのお菓子に対し、こころをこめることで、
-お菓子の食感を底上げし、おいしくする。すべてのお菓子に効果がある。
-使用時に、ハートを少し消費する。
-ハートが少ないと使用できない。
-◆パネルにお菓子がセットされた状態でないと使えない。
-◆仕上げ回数を一回消費する。
-仕上げ回数がないと、使用できない。</t>
-    <rPh sb="6" eb="8">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>タイ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>ショクカン</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ソコア</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="59" eb="62">
-      <t>シヨウジ</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>ショウヒ</t>
-    </rPh>
-    <rPh sb="80" eb="81">
-      <t>スク</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>光で作ったちょうちょや葉っぱを飛ばす
 お菓子をさらにかわいく演出できる。
 見た目がアップする。
@@ -3409,52 +3363,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>おかしの周りにハートを飛ばし、演出する。
-相性がよければ、おかしの愛らしさ、見た目をアップできる。
-使用時に、ハートを少し消費する。
-ハートが少ないと使用できない。
-◆パネルにお菓子がセットされた状態でないと使えない。
-◆仕上げ回数を一回消費する。
-仕上げ回数がないと、使用できない。</t>
-    <rPh sb="4" eb="5">
-      <t>マワ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>エンシュツ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>アイショウ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>アイ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="51" eb="54">
-      <t>シヨウジ</t>
-    </rPh>
-    <rPh sb="60" eb="61">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>ショウヒ</t>
-    </rPh>
-    <rPh sb="72" eb="73">
-      <t>スク</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>シヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>チョコレートを作るために必須の魔法。
 カカオマスの温度調整をし、なめらかにする。
 温度調節はかなり繊細な作業なので、慎重に。
@@ -3839,6 +3747,103 @@
   </si>
   <si>
     <t>skicon_MP_Regenaration</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>おかしの周りにハートを飛ばし、演出する。
+相性がよければ、おかしの愛らしさ、見た目をアップできる。
+使用時に、ハートを少し消費する。
+1LVごとに30消費。
+ハートが少ないと使用できない。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="4" eb="5">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>アイショウ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>アイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="51" eb="54">
+      <t>シヨウジ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>できたてのお菓子に対し、こころをこめることで、
+お菓子の食感を底上げし、おいしくする。すべてのお菓子に効果がある。
+使用時に、ハートを少し消費する。
+1LVごとに30消費。
+ハートが少ないと使用できない。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="6" eb="8">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ショクカン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ソコア</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="59" eb="62">
+      <t>シヨウジ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>シヨウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3927,14 +3932,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -4332,7 +4334,7 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -4356,4425 +4358,4425 @@
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="5">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="4">
         <f t="shared" ref="A2:A68" si="0">ROW()-2</f>
         <v>0</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>1001</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <v>6</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>3</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
         <v>9999</v>
       </c>
-      <c r="J2" s="5">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5">
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
         <v>5</v>
       </c>
-      <c r="L2" s="5">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O2" s="5">
-        <v>1</v>
-      </c>
-      <c r="P2" s="5">
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O2" s="4">
+        <v>1</v>
+      </c>
+      <c r="P2" s="4">
         <v>9</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="4">
         <v>100</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="4">
         <v>30</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="T2" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="U2" s="5">
+      <c r="T2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U2" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3">
+    <row r="3" spans="1:21" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>1002</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>6</v>
       </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>1</v>
-      </c>
-      <c r="J3" s="3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="3">
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2">
         <v>10</v>
       </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O3" s="3">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3">
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
         <v>9</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="2">
         <v>100</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3" s="2">
         <v>30</v>
       </c>
-      <c r="S3" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U3" s="3">
+      <c r="S3" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U3" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:21" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="5">
+    <row r="4" spans="1:21" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>1005</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>6</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>3</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <v>9999</v>
       </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
         <v>5</v>
       </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O4" s="5">
-        <v>1</v>
-      </c>
-      <c r="P4" s="5">
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O4" s="4">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
         <v>9</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q4" s="4">
         <v>100</v>
       </c>
-      <c r="R4" s="5">
+      <c r="R4" s="4">
         <v>30</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="S4" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="T4" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="U4" s="5">
+      <c r="T4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U4" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3">
+    <row r="5" spans="1:21" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>1010</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>6</v>
       </c>
-      <c r="H5" s="3">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>1</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3">
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
         <v>10</v>
       </c>
-      <c r="L5" s="3">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O5" s="3">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3">
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O5" s="2">
+        <v>0</v>
+      </c>
+      <c r="P5" s="2">
         <v>9</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <v>100</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="2">
         <v>30</v>
       </c>
-      <c r="S5" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U5" s="3">
+      <c r="S5" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U5" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3">
+    <row r="6" spans="1:21" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>1009</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>6</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <v>5</v>
       </c>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3">
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
         <v>3</v>
       </c>
-      <c r="L6" s="3">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="s">
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="N6" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="O6" s="3">
-        <v>1</v>
-      </c>
-      <c r="P6" s="3">
+      <c r="O6" s="2">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2">
         <v>9</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="2">
         <v>100</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="2">
         <v>30</v>
       </c>
-      <c r="S6" s="4" t="s">
+      <c r="S6" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="T6" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U6" s="3">
+      <c r="T6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U6" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:21" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3">
+    <row r="7" spans="1:21" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>1003</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="C7" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>2</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <v>2</v>
       </c>
-      <c r="I7" s="3">
-        <v>1</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3">
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
         <v>3</v>
       </c>
-      <c r="L7" s="3">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O7" s="3">
-        <v>1</v>
-      </c>
-      <c r="P7" s="3">
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O7" s="2">
+        <v>1</v>
+      </c>
+      <c r="P7" s="2">
         <v>9</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="2">
         <v>100</v>
       </c>
-      <c r="R7" s="3">
+      <c r="R7" s="2">
         <v>30</v>
       </c>
-      <c r="S7" s="4" t="s">
+      <c r="S7" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="T7" s="3" t="s">
+      <c r="T7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="U7" s="3">
+      <c r="U7" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="3">
+    <row r="8" spans="1:21" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>1006</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>6</v>
       </c>
-      <c r="H8" s="3">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O8" s="3">
-        <v>1</v>
-      </c>
-      <c r="P8" s="3">
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O8" s="2">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2">
         <v>9</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="2">
         <v>100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="2">
         <v>30</v>
       </c>
-      <c r="S8" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="T8" s="3" t="s">
+      <c r="S8" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="U8" s="3">
+      <c r="U8" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3">
+    <row r="9" spans="1:21" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>1008</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>6</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <v>2</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
         <v>3</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O9" s="3">
-        <v>1</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O9" s="2">
+        <v>1</v>
+      </c>
+      <c r="P9" s="2">
         <v>9</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="2">
         <v>100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="2">
         <v>30</v>
       </c>
-      <c r="S9" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="T9" s="3" t="s">
+      <c r="S9" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3">
+    <row r="10" spans="1:21" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>1006</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="C10" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <v>6</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <v>4</v>
       </c>
-      <c r="I10" s="3">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
         <v>3</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3" t="s">
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="N10" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="O10" s="3">
-        <v>1</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="O10" s="2">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2">
         <v>9</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="2">
         <v>100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="2">
         <v>30</v>
       </c>
-      <c r="S10" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="T10" s="3" t="s">
+      <c r="S10" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="T10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="3" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="3">
+    <row r="11" spans="1:21" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>1004</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>2</v>
       </c>
-      <c r="H11" s="3">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3">
-        <v>1</v>
-      </c>
-      <c r="L11" s="3">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O11" s="3">
-        <v>0</v>
-      </c>
-      <c r="P11" s="3">
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0</v>
+      </c>
+      <c r="P11" s="2">
         <v>9</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="2">
         <v>100</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="2">
         <v>30</v>
       </c>
-      <c r="S11" s="4" t="s">
+      <c r="S11" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="T11" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U11" s="3">
+      <c r="T11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:21" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="7">
+    <row r="12" spans="1:21" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>1007</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="6">
         <v>6</v>
       </c>
-      <c r="H12" s="7">
-        <v>1</v>
-      </c>
-      <c r="I12" s="7">
+      <c r="H12" s="6">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6">
         <v>9999</v>
       </c>
-      <c r="J12" s="7">
-        <v>0</v>
-      </c>
-      <c r="K12" s="7">
-        <v>1</v>
-      </c>
-      <c r="L12" s="7">
-        <v>0</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O12" s="7">
-        <v>1</v>
-      </c>
-      <c r="P12" s="7">
+      <c r="J12" s="6">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O12" s="6">
+        <v>1</v>
+      </c>
+      <c r="P12" s="6">
         <v>9</v>
       </c>
-      <c r="Q12" s="7">
+      <c r="Q12" s="6">
         <v>100</v>
       </c>
-      <c r="R12" s="7">
+      <c r="R12" s="6">
         <v>30</v>
       </c>
-      <c r="S12" s="7" t="s">
+      <c r="S12" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="T12" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U12" s="7">
+      <c r="T12" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U12" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="7">
+    <row r="13" spans="1:21" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="6">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>1009</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="6">
         <v>6</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>20</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="6">
         <v>9999</v>
       </c>
-      <c r="J13" s="7">
-        <v>0</v>
-      </c>
-      <c r="K13" s="7">
+      <c r="J13" s="6">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
         <v>3</v>
       </c>
-      <c r="L13" s="7">
-        <v>0</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O13" s="7">
-        <v>1</v>
-      </c>
-      <c r="P13" s="7">
+      <c r="L13" s="6">
+        <v>0</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O13" s="6">
+        <v>1</v>
+      </c>
+      <c r="P13" s="6">
         <v>9</v>
       </c>
-      <c r="Q13" s="7">
+      <c r="Q13" s="6">
         <v>100</v>
       </c>
-      <c r="R13" s="7">
+      <c r="R13" s="6">
         <v>30</v>
       </c>
-      <c r="S13" s="7" t="s">
+      <c r="S13" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="T13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U13" s="7">
+      <c r="T13" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U13" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="3">
+    <row r="14" spans="1:21" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>2004</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C14" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <v>2</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O14" s="2">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="2">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="2">
         <v>30</v>
       </c>
-      <c r="S14" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U14" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="3">
+    <row r="15" spans="1:21" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <v>2001</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <v>2</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <v>2</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2">
         <v>5</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O15" s="3">
-        <v>1</v>
-      </c>
-      <c r="P15" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="L15" s="2">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O15" s="2">
+        <v>1</v>
+      </c>
+      <c r="P15" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="2">
         <v>100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="R15" s="2">
         <v>120</v>
       </c>
-      <c r="S15" s="4" t="s">
+      <c r="S15" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="T15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U15" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="3">
+    <row r="16" spans="1:21" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <v>2001</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="C16" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <v>2</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <v>3</v>
       </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3">
-        <v>0</v>
-      </c>
-      <c r="K16" s="3">
-        <v>1</v>
-      </c>
-      <c r="L16" s="3">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O16" s="3">
-        <v>1</v>
-      </c>
-      <c r="P16" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="3">
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O16" s="2">
+        <v>1</v>
+      </c>
+      <c r="P16" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="2">
         <v>100</v>
       </c>
-      <c r="R16" s="3">
+      <c r="R16" s="2">
         <v>120</v>
       </c>
-      <c r="S16" s="4" t="s">
+      <c r="S16" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="T16" s="3" t="s">
+      <c r="T16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="U16" s="3">
+      <c r="U16" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" s="5" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="5">
+    <row r="17" spans="1:21" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>2002</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="4">
         <v>2</v>
       </c>
-      <c r="H17" s="5">
-        <v>1</v>
-      </c>
-      <c r="I17" s="5">
+      <c r="H17" s="4">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4">
         <v>9999</v>
       </c>
-      <c r="J17" s="5">
-        <v>0</v>
-      </c>
-      <c r="K17" s="5">
-        <v>1</v>
-      </c>
-      <c r="L17" s="5">
-        <v>0</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O17" s="5">
-        <v>1</v>
-      </c>
-      <c r="P17" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="5">
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4">
+        <v>1</v>
+      </c>
+      <c r="L17" s="4">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O17" s="4">
+        <v>1</v>
+      </c>
+      <c r="P17" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="4">
         <v>100</v>
       </c>
-      <c r="R17" s="5">
+      <c r="R17" s="4">
         <v>120</v>
       </c>
-      <c r="S17" s="5" t="s">
+      <c r="S17" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="T17" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="U17" s="5">
+      <c r="T17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="U17" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="3">
+    <row r="18" spans="1:21" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <v>2005</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="C18" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="G18" s="2">
+        <v>2</v>
+      </c>
+      <c r="H18" s="2">
+        <v>4</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
+        <v>3</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="O18" s="2">
+        <v>1</v>
+      </c>
+      <c r="P18" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>100</v>
+      </c>
+      <c r="R18" s="2">
+        <v>30</v>
+      </c>
+      <c r="S18" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="G18" s="3">
-        <v>2</v>
-      </c>
-      <c r="H18" s="3">
-        <v>4</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="O18" s="3">
-        <v>1</v>
-      </c>
-      <c r="P18" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>100</v>
-      </c>
-      <c r="R18" s="3">
-        <v>30</v>
-      </c>
-      <c r="S18" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="T18" s="3" t="s">
+      <c r="T18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:21" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="3">
+    <row r="19" spans="1:21" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <v>2003</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D19" s="3" t="s">
+      <c r="C19" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <v>2</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="2">
         <v>3</v>
       </c>
-      <c r="I19" s="3">
-        <v>1</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3">
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2">
         <v>5</v>
       </c>
-      <c r="L19" s="3">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O19" s="3">
-        <v>1</v>
-      </c>
-      <c r="P19" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="3">
+      <c r="L19" s="2">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O19" s="2">
+        <v>1</v>
+      </c>
+      <c r="P19" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="2">
         <v>100</v>
       </c>
-      <c r="R19" s="3">
+      <c r="R19" s="2">
         <v>30</v>
       </c>
-      <c r="S19" s="4" t="s">
+      <c r="S19" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="T19" s="3" t="s">
+      <c r="T19" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U19" s="3">
+      <c r="U19" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:21" s="7" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="7">
+    <row r="20" spans="1:21" s="6" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="6">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="6">
         <v>2003</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="6">
         <v>2</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="6">
         <v>20</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="6">
         <v>9999</v>
       </c>
-      <c r="J20" s="7">
-        <v>0</v>
-      </c>
-      <c r="K20" s="7">
+      <c r="J20" s="6">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6">
         <v>5</v>
       </c>
-      <c r="L20" s="7">
-        <v>0</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O20" s="7">
-        <v>1</v>
-      </c>
-      <c r="P20" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="7">
+      <c r="L20" s="6">
+        <v>0</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O20" s="6">
+        <v>1</v>
+      </c>
+      <c r="P20" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="6">
         <v>100</v>
       </c>
-      <c r="R20" s="7">
+      <c r="R20" s="6">
         <v>30</v>
       </c>
-      <c r="S20" s="7" t="s">
+      <c r="S20" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="T20" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U20" s="7">
+      <c r="T20" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U20" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:21" s="3" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="3">
+    <row r="21" spans="1:21" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="2">
         <v>3006</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="2">
         <v>2</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
         <v>5</v>
       </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O21" s="2">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2">
         <v>2</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="2">
         <v>100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="2">
         <v>30</v>
       </c>
-      <c r="S21" s="4" t="s">
+      <c r="S21" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="T21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U21" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:21" s="3" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="3">
+    <row r="22" spans="1:21" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="2">
         <v>3001</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="2">
         <v>2</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="2">
         <v>2</v>
       </c>
-      <c r="I22" s="3">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O22" s="2">
+        <v>1</v>
+      </c>
+      <c r="P22" s="2">
         <v>2</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="2">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22" s="2">
         <v>30</v>
       </c>
-      <c r="S22" s="4" t="s">
+      <c r="S22" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="T22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U22" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="3">
+    <row r="23" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="2">
         <v>3002</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="2">
         <v>4</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="2">
         <v>3</v>
       </c>
-      <c r="I23" s="3">
-        <v>1</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2">
         <v>5</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O23" s="3">
-        <v>1</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O23" s="2">
+        <v>1</v>
+      </c>
+      <c r="P23" s="2">
         <v>2</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="2">
         <v>100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23" s="2">
         <v>30</v>
       </c>
-      <c r="S23" s="4" t="s">
+      <c r="S23" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="T23" s="3" t="s">
+      <c r="T23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="U23" s="3">
+      <c r="U23" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="3">
+    <row r="24" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="2">
         <v>3003</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="C24" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="2">
         <v>4</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="2">
         <v>4</v>
       </c>
-      <c r="I24" s="3">
-        <v>1</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="I24" s="2">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3" t="s">
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="N24" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="O24" s="3">
-        <v>1</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="O24" s="2">
+        <v>1</v>
+      </c>
+      <c r="P24" s="2">
         <v>2</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="2">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24" s="2">
         <v>30</v>
       </c>
-      <c r="S24" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="T24" s="3" t="s">
+      <c r="S24" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="T24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="U24" s="3">
+      <c r="U24" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="3">
+    <row r="25" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="2">
         <v>3008</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="D25" s="3" t="s">
+      <c r="C25" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="2">
+        <v>4</v>
+      </c>
+      <c r="H25" s="2">
+        <v>4</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2">
+        <v>3</v>
+      </c>
+      <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="O25" s="2">
+        <v>1</v>
+      </c>
+      <c r="P25" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>100</v>
+      </c>
+      <c r="R25" s="2">
+        <v>30</v>
+      </c>
+      <c r="S25" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="G25" s="3">
-        <v>4</v>
-      </c>
-      <c r="H25" s="3">
-        <v>4</v>
-      </c>
-      <c r="I25" s="3">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3">
-        <v>3</v>
-      </c>
-      <c r="L25" s="3">
-        <v>0</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="O25" s="3">
-        <v>1</v>
-      </c>
-      <c r="P25" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q25" s="3">
-        <v>100</v>
-      </c>
-      <c r="R25" s="3">
-        <v>30</v>
-      </c>
-      <c r="S25" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U25" s="3">
+      <c r="T25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U25" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="3">
+    <row r="26" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="2">
         <v>3004</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="C26" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="2">
         <v>4</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1</v>
-      </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O26" s="2">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2">
         <v>2</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="2">
         <v>100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26" s="2">
         <v>30</v>
       </c>
-      <c r="S26" s="4" t="s">
+      <c r="S26" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="T26" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U26" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="3">
+    <row r="27" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="2">
         <v>3007</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="C27" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="G27" s="2">
+        <v>4</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O27" s="2">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>100</v>
+      </c>
+      <c r="R27" s="2">
+        <v>30</v>
+      </c>
+      <c r="S27" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="G27" s="3">
-        <v>4</v>
-      </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1</v>
-      </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3">
-        <v>2</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>100</v>
-      </c>
-      <c r="R27" s="3">
-        <v>30</v>
-      </c>
-      <c r="S27" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="T27" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U27" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="7">
+    <row r="28" spans="1:21" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="6">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="6">
         <v>3005</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="6">
         <v>4</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="6">
         <v>20</v>
       </c>
-      <c r="I28" s="7">
+      <c r="I28" s="6">
         <v>9999</v>
       </c>
-      <c r="J28" s="7">
-        <v>0</v>
-      </c>
-      <c r="K28" s="7">
+      <c r="J28" s="6">
+        <v>0</v>
+      </c>
+      <c r="K28" s="6">
         <v>5</v>
       </c>
-      <c r="L28" s="7">
-        <v>0</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N28" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O28" s="7">
-        <v>1</v>
-      </c>
-      <c r="P28" s="7">
+      <c r="L28" s="6">
+        <v>0</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O28" s="6">
+        <v>1</v>
+      </c>
+      <c r="P28" s="6">
         <v>2</v>
       </c>
-      <c r="Q28" s="7">
+      <c r="Q28" s="6">
         <v>100</v>
       </c>
-      <c r="R28" s="7">
+      <c r="R28" s="6">
         <v>30</v>
       </c>
-      <c r="S28" s="9" t="s">
+      <c r="S28" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="T28" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U28" s="7">
+      <c r="T28" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U28" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="7">
+    <row r="29" spans="1:21" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="6">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="6">
         <v>3005</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="6">
         <v>4</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="6">
         <v>10</v>
       </c>
-      <c r="I29" s="7">
+      <c r="I29" s="6">
         <v>9999</v>
       </c>
-      <c r="J29" s="7">
-        <v>0</v>
-      </c>
-      <c r="K29" s="7">
+      <c r="J29" s="6">
+        <v>0</v>
+      </c>
+      <c r="K29" s="6">
         <v>5</v>
       </c>
-      <c r="L29" s="7">
-        <v>0</v>
-      </c>
-      <c r="M29" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N29" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O29" s="7">
-        <v>1</v>
-      </c>
-      <c r="P29" s="7">
+      <c r="L29" s="6">
+        <v>0</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O29" s="6">
+        <v>1</v>
+      </c>
+      <c r="P29" s="6">
         <v>2</v>
       </c>
-      <c r="Q29" s="7">
+      <c r="Q29" s="6">
         <v>100</v>
       </c>
-      <c r="R29" s="7">
+      <c r="R29" s="6">
         <v>30</v>
       </c>
-      <c r="S29" s="9" t="s">
+      <c r="S29" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="T29" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U29" s="7">
+      <c r="T29" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U29" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="3">
+    <row r="30" spans="1:21" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="2">
         <v>4010</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="2">
         <v>6</v>
       </c>
-      <c r="H30" s="3">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3">
+      <c r="H30" s="2">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2">
         <v>5</v>
       </c>
-      <c r="L30" s="3">
-        <v>0</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O30" s="3">
-        <v>0</v>
-      </c>
-      <c r="P30" s="3">
+      <c r="L30" s="2">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O30" s="2">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2">
         <v>3</v>
       </c>
-      <c r="Q30" s="3">
+      <c r="Q30" s="2">
         <v>100</v>
       </c>
-      <c r="R30" s="3">
+      <c r="R30" s="2">
         <v>30</v>
       </c>
-      <c r="S30" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="T30" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U30" s="3">
+      <c r="S30" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U30" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="3">
+    <row r="31" spans="1:21" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="2">
         <v>4011</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D31" s="3" t="s">
+      <c r="C31" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="2">
         <v>6</v>
       </c>
-      <c r="H31" s="3">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3">
-        <v>1</v>
-      </c>
-      <c r="J31" s="3">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3">
+      <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>1</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2">
         <v>5</v>
       </c>
-      <c r="L31" s="3">
-        <v>0</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O31" s="3">
-        <v>0</v>
-      </c>
-      <c r="P31" s="3">
+      <c r="L31" s="2">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O31" s="2">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2">
         <v>3</v>
       </c>
-      <c r="Q31" s="3">
+      <c r="Q31" s="2">
         <v>100</v>
       </c>
-      <c r="R31" s="3">
+      <c r="R31" s="2">
         <v>30</v>
       </c>
-      <c r="S31" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="T31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U31" s="3">
+      <c r="S31" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U31" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="3">
+    <row r="32" spans="1:21" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="2">
         <v>4001</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="D32" s="3" t="s">
+      <c r="C32" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="F32" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G32" s="2">
         <v>6</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="2">
         <v>2</v>
       </c>
-      <c r="I32" s="3">
-        <v>1</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="I32" s="2">
+        <v>1</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
+      <c r="L32" s="2">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O32" s="2">
+        <v>1</v>
+      </c>
+      <c r="P32" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>85</v>
+      </c>
+      <c r="R32" s="2">
+        <v>30</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O32" s="3">
-        <v>1</v>
-      </c>
-      <c r="P32" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>85</v>
-      </c>
-      <c r="R32" s="3">
-        <v>30</v>
-      </c>
-      <c r="S32" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="T32" s="3" t="s">
+      <c r="T32" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="3">
+    <row r="33" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="2">
         <v>4002</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="C33" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G33" s="3">
-        <v>1</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="G33" s="2">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2">
         <v>4</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2">
         <v>3</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O33" s="3">
-        <v>1</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="L33" s="2">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O33" s="2">
+        <v>1</v>
+      </c>
+      <c r="P33" s="2">
         <v>3</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="2">
         <v>100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33" s="2">
         <v>30</v>
       </c>
-      <c r="S33" s="4" t="s">
+      <c r="S33" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="T33" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U33" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="3">
+    <row r="34" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="2">
         <v>4010</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="D34" s="3" t="s">
+      <c r="C34" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G34" s="3">
-        <v>1</v>
-      </c>
-      <c r="H34" s="3">
+      <c r="G34" s="2">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2">
         <v>4</v>
       </c>
-      <c r="I34" s="3">
-        <v>1</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3">
+      <c r="I34" s="2">
+        <v>1</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2">
         <v>3</v>
       </c>
-      <c r="L34" s="3">
-        <v>0</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O34" s="3">
-        <v>1</v>
-      </c>
-      <c r="P34" s="3">
+      <c r="L34" s="2">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O34" s="2">
+        <v>1</v>
+      </c>
+      <c r="P34" s="2">
         <v>3</v>
       </c>
-      <c r="Q34" s="3">
+      <c r="Q34" s="2">
         <v>100</v>
       </c>
-      <c r="R34" s="3">
+      <c r="R34" s="2">
         <v>30</v>
       </c>
-      <c r="S34" s="4" t="s">
+      <c r="S34" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="T34" s="3" t="s">
+      <c r="T34" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U34" s="3">
+      <c r="U34" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="3">
+    <row r="35" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="2">
         <v>4011</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="C35" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G35" s="3">
-        <v>1</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="G35" s="2">
+        <v>1</v>
+      </c>
+      <c r="H35" s="2">
         <v>4</v>
       </c>
-      <c r="I35" s="3">
-        <v>1</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2">
         <v>3</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O35" s="3">
-        <v>1</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="L35" s="2">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O35" s="2">
+        <v>1</v>
+      </c>
+      <c r="P35" s="2">
         <v>3</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="2">
         <v>100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="R35" s="2">
         <v>30</v>
       </c>
-      <c r="S35" s="4" t="s">
+      <c r="S35" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="T35" s="3" t="s">
+      <c r="T35" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U35" s="3">
+      <c r="U35" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="3">
+    <row r="36" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="2">
         <v>4012</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D36" s="3" t="s">
+      <c r="C36" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="G36" s="3">
-        <v>1</v>
-      </c>
-      <c r="H36" s="3">
+      <c r="G36" s="2">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2">
         <v>4</v>
       </c>
-      <c r="I36" s="3">
-        <v>1</v>
-      </c>
-      <c r="J36" s="3">
-        <v>0</v>
-      </c>
-      <c r="K36" s="3">
-        <v>1</v>
-      </c>
-      <c r="L36" s="3">
-        <v>0</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O36" s="3">
-        <v>1</v>
-      </c>
-      <c r="P36" s="3">
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O36" s="2">
+        <v>1</v>
+      </c>
+      <c r="P36" s="2">
         <v>3</v>
       </c>
-      <c r="Q36" s="3">
+      <c r="Q36" s="2">
         <v>100</v>
       </c>
-      <c r="R36" s="3">
+      <c r="R36" s="2">
         <v>30</v>
       </c>
-      <c r="S36" s="4" t="s">
+      <c r="S36" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="T36" s="3" t="s">
+      <c r="T36" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U36" s="3">
+      <c r="U36" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="3">
+    <row r="37" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="2">
         <v>4012</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G37" s="3">
-        <v>1</v>
-      </c>
-      <c r="H37" s="3">
+      <c r="G37" s="2">
+        <v>1</v>
+      </c>
+      <c r="H37" s="2">
         <v>4</v>
       </c>
-      <c r="I37" s="3">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3">
-        <v>0</v>
-      </c>
-      <c r="K37" s="3">
-        <v>1</v>
-      </c>
-      <c r="L37" s="3">
-        <v>0</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O37" s="3">
-        <v>1</v>
-      </c>
-      <c r="P37" s="3">
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O37" s="2">
+        <v>1</v>
+      </c>
+      <c r="P37" s="2">
         <v>3</v>
       </c>
-      <c r="Q37" s="3">
+      <c r="Q37" s="2">
         <v>100</v>
       </c>
-      <c r="R37" s="3">
+      <c r="R37" s="2">
         <v>30</v>
       </c>
-      <c r="S37" s="4" t="s">
+      <c r="S37" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="T37" s="3" t="s">
+      <c r="T37" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U37" s="3">
+      <c r="U37" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="3">
+    <row r="38" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="2">
         <v>4012</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G38" s="3">
-        <v>1</v>
-      </c>
-      <c r="H38" s="3">
+      <c r="G38" s="2">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2">
         <v>4</v>
       </c>
-      <c r="I38" s="3">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3">
-        <v>0</v>
-      </c>
-      <c r="K38" s="3">
-        <v>1</v>
-      </c>
-      <c r="L38" s="3">
-        <v>0</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O38" s="3">
-        <v>1</v>
-      </c>
-      <c r="P38" s="3">
+      <c r="I38" s="2">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O38" s="2">
+        <v>1</v>
+      </c>
+      <c r="P38" s="2">
         <v>3</v>
       </c>
-      <c r="Q38" s="3">
+      <c r="Q38" s="2">
         <v>100</v>
       </c>
-      <c r="R38" s="3">
+      <c r="R38" s="2">
         <v>30</v>
       </c>
-      <c r="S38" s="4" t="s">
+      <c r="S38" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="T38" s="3" t="s">
+      <c r="T38" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U38" s="3">
+      <c r="U38" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:21" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="7">
+    <row r="39" spans="1:21" s="6" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="6">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="6">
         <v>4003</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G39" s="6">
         <v>3</v>
       </c>
-      <c r="H39" s="7">
+      <c r="H39" s="6">
         <v>2</v>
       </c>
-      <c r="I39" s="7">
+      <c r="I39" s="6">
         <v>9999</v>
       </c>
-      <c r="J39" s="7">
-        <v>0</v>
-      </c>
-      <c r="K39" s="7">
+      <c r="J39" s="6">
+        <v>0</v>
+      </c>
+      <c r="K39" s="6">
         <v>3</v>
       </c>
-      <c r="L39" s="7">
-        <v>0</v>
-      </c>
-      <c r="M39" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N39" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O39" s="7">
-        <v>1</v>
-      </c>
-      <c r="P39" s="7">
+      <c r="L39" s="6">
+        <v>0</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O39" s="6">
+        <v>1</v>
+      </c>
+      <c r="P39" s="6">
         <v>3</v>
       </c>
-      <c r="Q39" s="7">
+      <c r="Q39" s="6">
         <v>100</v>
       </c>
-      <c r="R39" s="7">
+      <c r="R39" s="6">
         <v>30</v>
       </c>
-      <c r="S39" s="9" t="s">
+      <c r="S39" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="T39" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U39" s="7">
+      <c r="T39" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U39" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="3">
+    <row r="40" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="2">
         <v>4004</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D40" s="3" t="s">
+      <c r="C40" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="2">
         <v>3</v>
       </c>
-      <c r="H40" s="3">
+      <c r="H40" s="2">
         <v>3</v>
       </c>
-      <c r="I40" s="3">
-        <v>1</v>
-      </c>
-      <c r="J40" s="3">
-        <v>0</v>
-      </c>
-      <c r="K40" s="3">
+      <c r="I40" s="2">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2">
+        <v>0</v>
+      </c>
+      <c r="K40" s="2">
         <v>3</v>
       </c>
-      <c r="L40" s="3">
-        <v>0</v>
-      </c>
-      <c r="M40" s="3" t="s">
+      <c r="L40" s="2">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="N40" s="3" t="s">
+      <c r="N40" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="O40" s="3">
-        <v>1</v>
-      </c>
-      <c r="P40" s="3">
+      <c r="O40" s="2">
+        <v>1</v>
+      </c>
+      <c r="P40" s="2">
         <v>3</v>
       </c>
-      <c r="Q40" s="3">
+      <c r="Q40" s="2">
         <v>100</v>
       </c>
-      <c r="R40" s="3">
+      <c r="R40" s="2">
         <v>30</v>
       </c>
-      <c r="S40" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="T40" s="3" t="s">
+      <c r="S40" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="T40" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U40" s="3">
+      <c r="U40" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:21" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="7">
+    <row r="41" spans="1:21" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="6">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="6">
         <v>4005</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="6">
         <v>12</v>
       </c>
-      <c r="H41" s="7">
+      <c r="H41" s="6">
         <v>5</v>
       </c>
-      <c r="I41" s="7">
+      <c r="I41" s="6">
         <v>9999</v>
       </c>
-      <c r="J41" s="7">
-        <v>0</v>
-      </c>
-      <c r="K41" s="7">
+      <c r="J41" s="6">
+        <v>0</v>
+      </c>
+      <c r="K41" s="6">
         <v>3</v>
       </c>
-      <c r="L41" s="7">
-        <v>0</v>
-      </c>
-      <c r="M41" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N41" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O41" s="7">
-        <v>1</v>
-      </c>
-      <c r="P41" s="7">
+      <c r="L41" s="6">
+        <v>0</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N41" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O41" s="6">
+        <v>1</v>
+      </c>
+      <c r="P41" s="6">
         <v>3</v>
       </c>
-      <c r="Q41" s="7">
+      <c r="Q41" s="6">
         <v>100</v>
       </c>
-      <c r="R41" s="7">
+      <c r="R41" s="6">
         <v>30</v>
       </c>
-      <c r="S41" s="9" t="s">
+      <c r="S41" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="T41" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U41" s="7">
+      <c r="T41" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U41" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="7">
+    <row r="42" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="6">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="6">
         <v>4006</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F42" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="G42" s="7">
+      <c r="F42" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="G42" s="6">
         <v>3</v>
       </c>
-      <c r="H42" s="7">
+      <c r="H42" s="6">
         <v>5</v>
       </c>
-      <c r="I42" s="7">
+      <c r="I42" s="6">
         <v>9999</v>
       </c>
-      <c r="J42" s="7">
-        <v>0</v>
-      </c>
-      <c r="K42" s="7">
+      <c r="J42" s="6">
+        <v>0</v>
+      </c>
+      <c r="K42" s="6">
         <v>3</v>
       </c>
-      <c r="L42" s="7">
-        <v>0</v>
-      </c>
-      <c r="M42" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N42" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="O42" s="7">
-        <v>1</v>
-      </c>
-      <c r="P42" s="7">
+      <c r="L42" s="6">
+        <v>0</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="O42" s="6">
+        <v>1</v>
+      </c>
+      <c r="P42" s="6">
         <v>3</v>
       </c>
-      <c r="Q42" s="7">
+      <c r="Q42" s="6">
         <v>100</v>
       </c>
-      <c r="R42" s="7">
+      <c r="R42" s="6">
         <v>30</v>
       </c>
-      <c r="S42" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="T42" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U42" s="7">
+      <c r="S42" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="T42" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U42" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="3">
+    <row r="43" spans="1:21" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="2">
         <v>4007</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="F43" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G43" s="2">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="2">
         <v>5</v>
       </c>
-      <c r="I43" s="3">
-        <v>1</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O43" s="3">
-        <v>1</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="I43" s="2">
+        <v>1</v>
+      </c>
+      <c r="J43" s="2">
+        <v>0</v>
+      </c>
+      <c r="K43" s="2">
+        <v>1</v>
+      </c>
+      <c r="L43" s="2">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O43" s="2">
+        <v>1</v>
+      </c>
+      <c r="P43" s="2">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="2">
         <v>100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="R43" s="2">
         <v>30</v>
       </c>
-      <c r="S43" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="T43" s="3" t="s">
+      <c r="S43" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="T43" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="U43" s="3">
+      <c r="U43" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="7">
+    <row r="44" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="6">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="6">
         <v>4007</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="F44" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="G44" s="7">
+      <c r="F44" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="G44" s="6">
         <v>3</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H44" s="6">
         <v>5</v>
       </c>
-      <c r="I44" s="7">
+      <c r="I44" s="6">
         <v>9999</v>
       </c>
-      <c r="J44" s="7">
-        <v>0</v>
-      </c>
-      <c r="K44" s="7">
+      <c r="J44" s="6">
+        <v>0</v>
+      </c>
+      <c r="K44" s="6">
         <v>3</v>
       </c>
-      <c r="L44" s="7">
-        <v>0</v>
-      </c>
-      <c r="M44" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N44" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="O44" s="7">
-        <v>1</v>
-      </c>
-      <c r="P44" s="7">
+      <c r="L44" s="6">
+        <v>0</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="O44" s="6">
+        <v>1</v>
+      </c>
+      <c r="P44" s="6">
         <v>3</v>
       </c>
-      <c r="Q44" s="7">
+      <c r="Q44" s="6">
         <v>100</v>
       </c>
-      <c r="R44" s="7">
+      <c r="R44" s="6">
         <v>30</v>
       </c>
-      <c r="S44" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="T44" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U44" s="7">
+      <c r="S44" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="T44" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U44" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="7">
+    <row r="45" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="6">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="6">
         <v>4008</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F45" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="G45" s="7">
+      <c r="F45" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G45" s="6">
         <v>3</v>
       </c>
-      <c r="H45" s="7">
+      <c r="H45" s="6">
         <v>5</v>
       </c>
-      <c r="I45" s="7">
+      <c r="I45" s="6">
         <v>9999</v>
       </c>
-      <c r="J45" s="7">
-        <v>0</v>
-      </c>
-      <c r="K45" s="7">
+      <c r="J45" s="6">
+        <v>0</v>
+      </c>
+      <c r="K45" s="6">
         <v>3</v>
       </c>
-      <c r="L45" s="7">
-        <v>0</v>
-      </c>
-      <c r="M45" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N45" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="O45" s="7">
-        <v>1</v>
-      </c>
-      <c r="P45" s="7">
+      <c r="L45" s="6">
+        <v>0</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="O45" s="6">
+        <v>1</v>
+      </c>
+      <c r="P45" s="6">
         <v>3</v>
       </c>
-      <c r="Q45" s="7">
+      <c r="Q45" s="6">
         <v>100</v>
       </c>
-      <c r="R45" s="7">
+      <c r="R45" s="6">
         <v>30</v>
       </c>
-      <c r="S45" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="T45" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U45" s="7">
+      <c r="S45" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="T45" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U45" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="7">
+    <row r="46" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="6">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="6">
         <v>4009</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F46" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="G46" s="7">
+      <c r="F46" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="G46" s="6">
         <v>3</v>
       </c>
-      <c r="H46" s="7">
+      <c r="H46" s="6">
         <v>8</v>
       </c>
-      <c r="I46" s="7">
+      <c r="I46" s="6">
         <v>9999</v>
       </c>
-      <c r="J46" s="7">
-        <v>0</v>
-      </c>
-      <c r="K46" s="7">
+      <c r="J46" s="6">
+        <v>0</v>
+      </c>
+      <c r="K46" s="6">
         <v>3</v>
       </c>
-      <c r="L46" s="7">
-        <v>0</v>
-      </c>
-      <c r="M46" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N46" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O46" s="7">
-        <v>1</v>
-      </c>
-      <c r="P46" s="7">
+      <c r="L46" s="6">
+        <v>0</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O46" s="6">
+        <v>1</v>
+      </c>
+      <c r="P46" s="6">
         <v>3</v>
       </c>
-      <c r="Q46" s="7">
+      <c r="Q46" s="6">
         <v>100</v>
       </c>
-      <c r="R46" s="7">
+      <c r="R46" s="6">
         <v>30</v>
       </c>
-      <c r="S46" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="T46" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U46" s="7">
+      <c r="S46" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="T46" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U46" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="7">
+    <row r="47" spans="1:21" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="6">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="6">
         <v>4013</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47" s="6">
         <v>6</v>
       </c>
-      <c r="H47" s="7">
+      <c r="H47" s="6">
         <v>30</v>
       </c>
-      <c r="I47" s="7">
+      <c r="I47" s="6">
         <v>9999</v>
       </c>
-      <c r="J47" s="7">
-        <v>0</v>
-      </c>
-      <c r="K47" s="7">
+      <c r="J47" s="6">
+        <v>0</v>
+      </c>
+      <c r="K47" s="6">
         <v>5</v>
       </c>
-      <c r="L47" s="7">
-        <v>0</v>
-      </c>
-      <c r="M47" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N47" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O47" s="7">
-        <v>1</v>
-      </c>
-      <c r="P47" s="7">
+      <c r="L47" s="6">
+        <v>0</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N47" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O47" s="6">
+        <v>1</v>
+      </c>
+      <c r="P47" s="6">
         <v>3</v>
       </c>
-      <c r="Q47" s="7">
+      <c r="Q47" s="6">
         <v>100</v>
       </c>
-      <c r="R47" s="7">
+      <c r="R47" s="6">
         <v>30</v>
       </c>
-      <c r="S47" s="9" t="s">
+      <c r="S47" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="T47" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U47" s="7">
+      <c r="T47" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U47" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="7">
+    <row r="48" spans="1:21" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="6">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="6">
         <v>5004</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G48" s="6">
         <v>6</v>
       </c>
-      <c r="H48" s="7">
-        <v>0</v>
-      </c>
-      <c r="I48" s="7">
+      <c r="H48" s="6">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6">
         <v>9999</v>
       </c>
-      <c r="J48" s="7">
-        <v>0</v>
-      </c>
-      <c r="K48" s="7">
+      <c r="J48" s="6">
+        <v>0</v>
+      </c>
+      <c r="K48" s="6">
         <v>5</v>
       </c>
-      <c r="L48" s="7">
-        <v>0</v>
-      </c>
-      <c r="M48" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N48" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O48" s="7">
-        <v>0</v>
-      </c>
-      <c r="P48" s="7">
+      <c r="L48" s="6">
+        <v>0</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O48" s="6">
+        <v>0</v>
+      </c>
+      <c r="P48" s="6">
         <v>4</v>
       </c>
-      <c r="Q48" s="7">
+      <c r="Q48" s="6">
         <v>100</v>
       </c>
-      <c r="R48" s="7">
+      <c r="R48" s="6">
         <v>30</v>
       </c>
-      <c r="S48" s="9" t="s">
+      <c r="S48" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="T48" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U48" s="7">
+      <c r="T48" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U48" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="3">
+    <row r="49" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="2">
         <v>5007</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E49" s="3" t="s">
+      <c r="D49" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="E49" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="G49" s="2">
+        <v>6</v>
+      </c>
+      <c r="H49" s="2">
+        <v>0</v>
+      </c>
+      <c r="I49" s="2">
+        <v>1</v>
+      </c>
+      <c r="J49" s="2">
+        <v>0</v>
+      </c>
+      <c r="K49" s="2">
+        <v>3</v>
+      </c>
+      <c r="L49" s="2">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O49" s="2">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>100</v>
+      </c>
+      <c r="R49" s="2">
+        <v>30</v>
+      </c>
+      <c r="S49" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="G49" s="3">
-        <v>6</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>4</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>100</v>
-      </c>
-      <c r="R49" s="3">
-        <v>30</v>
-      </c>
-      <c r="S49" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U49" s="3">
+      <c r="T49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U49" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:21" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="3">
+    <row r="50" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="2">
         <v>5001</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D50" s="3" t="s">
+      <c r="C50" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="2">
         <v>6</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50" s="2">
         <v>3</v>
       </c>
-      <c r="I50" s="3">
-        <v>1</v>
-      </c>
-      <c r="J50" s="3">
-        <v>0</v>
-      </c>
-      <c r="K50" s="3">
+      <c r="I50" s="2">
+        <v>1</v>
+      </c>
+      <c r="J50" s="2">
+        <v>0</v>
+      </c>
+      <c r="K50" s="2">
         <v>3</v>
       </c>
-      <c r="L50" s="3">
-        <v>0</v>
-      </c>
-      <c r="M50" s="3" t="s">
+      <c r="L50" s="2">
+        <v>0</v>
+      </c>
+      <c r="M50" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="N50" s="3" t="s">
+      <c r="N50" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="O50" s="3">
-        <v>1</v>
-      </c>
-      <c r="P50" s="3">
+      <c r="O50" s="2">
+        <v>1</v>
+      </c>
+      <c r="P50" s="2">
         <v>4</v>
       </c>
-      <c r="Q50" s="3">
+      <c r="Q50" s="2">
         <v>100</v>
       </c>
-      <c r="R50" s="3">
+      <c r="R50" s="2">
         <v>30</v>
       </c>
-      <c r="S50" s="4" t="s">
+      <c r="S50" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="T50" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="U50" s="3">
+      <c r="T50" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="U50" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="3">
+    <row r="51" spans="1:21" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="2">
         <v>5002</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="2">
         <v>6</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="2">
         <v>3</v>
       </c>
-      <c r="I51" s="3">
-        <v>1</v>
-      </c>
-      <c r="J51" s="3">
-        <v>0</v>
-      </c>
-      <c r="K51" s="3">
+      <c r="I51" s="2">
+        <v>1</v>
+      </c>
+      <c r="J51" s="2">
+        <v>0</v>
+      </c>
+      <c r="K51" s="2">
         <v>3</v>
       </c>
-      <c r="L51" s="3">
-        <v>0</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O51" s="3">
-        <v>1</v>
-      </c>
-      <c r="P51" s="3">
+      <c r="L51" s="2">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O51" s="2">
+        <v>1</v>
+      </c>
+      <c r="P51" s="2">
         <v>4</v>
       </c>
-      <c r="Q51" s="3">
+      <c r="Q51" s="2">
         <v>100</v>
       </c>
-      <c r="R51" s="3">
+      <c r="R51" s="2">
         <v>30</v>
       </c>
-      <c r="S51" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="T51" s="3" t="s">
+      <c r="S51" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="T51" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="U51" s="3">
+      <c r="U51" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="3">
+    <row r="52" spans="1:21" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="2">
         <v>5003</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="2">
         <v>6</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="2">
         <v>6</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52" s="2">
+        <v>0</v>
+      </c>
+      <c r="K52" s="2">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="L52" s="2">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O52" s="2">
+        <v>1</v>
+      </c>
+      <c r="P52" s="2">
         <v>4</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="2">
         <v>100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="2">
         <v>480</v>
       </c>
-      <c r="S52" s="4" t="s">
+      <c r="S52" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U52" s="3">
+      <c r="T52" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U52" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="3">
+    <row r="53" spans="1:21" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="2">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="2">
         <v>5005</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53" s="2">
         <v>6</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H53" s="2">
         <v>3</v>
       </c>
-      <c r="I53" s="3">
-        <v>1</v>
-      </c>
-      <c r="J53" s="3">
-        <v>0</v>
-      </c>
-      <c r="K53" s="3">
+      <c r="I53" s="2">
+        <v>1</v>
+      </c>
+      <c r="J53" s="2">
+        <v>0</v>
+      </c>
+      <c r="K53" s="2">
         <v>3</v>
       </c>
-      <c r="L53" s="3">
-        <v>0</v>
-      </c>
-      <c r="M53" s="3" t="s">
+      <c r="L53" s="2">
+        <v>0</v>
+      </c>
+      <c r="M53" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="N53" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O53" s="3">
-        <v>1</v>
-      </c>
-      <c r="P53" s="3">
+      <c r="N53" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O53" s="2">
+        <v>1</v>
+      </c>
+      <c r="P53" s="2">
         <v>4</v>
       </c>
-      <c r="Q53" s="3">
+      <c r="Q53" s="2">
         <v>100</v>
       </c>
-      <c r="R53" s="3">
+      <c r="R53" s="2">
         <v>30</v>
       </c>
-      <c r="S53" s="4" t="s">
+      <c r="S53" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="T53" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="U53" s="3">
+      <c r="T53" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="U53" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:21" s="3" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="3">
+    <row r="54" spans="1:21" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="2">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="2">
         <v>5006</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="2">
         <v>6</v>
       </c>
-      <c r="H54" s="3">
+      <c r="H54" s="2">
         <v>8</v>
       </c>
-      <c r="I54" s="3">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3">
-        <v>0</v>
-      </c>
-      <c r="K54" s="3">
-        <v>1</v>
-      </c>
-      <c r="L54" s="3">
-        <v>0</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="O54" s="3">
-        <v>1</v>
-      </c>
-      <c r="P54" s="3">
+      <c r="I54" s="2">
+        <v>0</v>
+      </c>
+      <c r="J54" s="2">
+        <v>0</v>
+      </c>
+      <c r="K54" s="2">
+        <v>1</v>
+      </c>
+      <c r="L54" s="2">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="O54" s="2">
+        <v>1</v>
+      </c>
+      <c r="P54" s="2">
         <v>4</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="2">
         <v>100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54" s="2">
         <v>30</v>
       </c>
-      <c r="S54" s="4" t="s">
+      <c r="S54" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U54" s="3">
+      <c r="T54" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U54" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="7">
+    <row r="55" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="6">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="6">
         <v>6001</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E55" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G55" s="7">
+      <c r="G55" s="6">
         <v>6</v>
       </c>
-      <c r="H55" s="7">
+      <c r="H55" s="6">
         <v>3</v>
       </c>
-      <c r="I55" s="7">
+      <c r="I55" s="6">
         <v>9999</v>
       </c>
-      <c r="J55" s="7">
-        <v>0</v>
-      </c>
-      <c r="K55" s="7">
+      <c r="J55" s="6">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6">
         <v>10</v>
       </c>
-      <c r="L55" s="7">
-        <v>0</v>
-      </c>
-      <c r="M55" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N55" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O55" s="7">
-        <v>1</v>
-      </c>
-      <c r="P55" s="7">
+      <c r="L55" s="6">
+        <v>0</v>
+      </c>
+      <c r="M55" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N55" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O55" s="6">
+        <v>1</v>
+      </c>
+      <c r="P55" s="6">
         <v>5</v>
       </c>
-      <c r="Q55" s="7">
+      <c r="Q55" s="6">
         <v>100</v>
       </c>
-      <c r="R55" s="7">
+      <c r="R55" s="6">
         <v>30</v>
       </c>
-      <c r="S55" s="7" t="s">
+      <c r="S55" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="T55" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U55" s="7">
+      <c r="T55" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U55" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:21" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="3">
+    <row r="56" spans="1:21" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="2">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="2">
         <v>6002</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="D56" s="3" t="s">
+      <c r="C56" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="F56" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56" s="2">
         <v>6</v>
       </c>
-      <c r="H56" s="3">
+      <c r="H56" s="2">
         <v>2</v>
       </c>
-      <c r="I56" s="3">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3">
-        <v>0</v>
-      </c>
-      <c r="K56" s="3">
+      <c r="I56" s="2">
+        <v>0</v>
+      </c>
+      <c r="J56" s="2">
+        <v>0</v>
+      </c>
+      <c r="K56" s="2">
         <v>5</v>
       </c>
-      <c r="L56" s="3">
-        <v>0</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O56" s="3">
-        <v>1</v>
-      </c>
-      <c r="P56" s="3">
+      <c r="L56" s="2">
+        <v>0</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O56" s="2">
+        <v>1</v>
+      </c>
+      <c r="P56" s="2">
         <v>5</v>
       </c>
-      <c r="Q56" s="3">
+      <c r="Q56" s="2">
         <v>100</v>
       </c>
-      <c r="R56" s="3">
+      <c r="R56" s="2">
         <v>30</v>
       </c>
-      <c r="S56" s="4" t="s">
+      <c r="S56" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="T56" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U56" s="3">
+      <c r="T56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U56" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:21" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="3">
+    <row r="57" spans="1:21" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="2">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57" s="2">
         <v>6004</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="F57" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="2">
         <v>6</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="2">
         <v>5</v>
       </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="I57" s="2">
+        <v>0</v>
+      </c>
+      <c r="J57" s="2">
+        <v>0</v>
+      </c>
+      <c r="K57" s="2">
         <v>3</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3" t="s">
+      <c r="L57" s="2">
+        <v>0</v>
+      </c>
+      <c r="M57" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="N57" s="3" t="s">
+      <c r="N57" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="O57" s="3">
-        <v>1</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="O57" s="2">
+        <v>1</v>
+      </c>
+      <c r="P57" s="2">
         <v>5</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="2">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57" s="2">
         <v>30</v>
       </c>
-      <c r="S57" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="T57" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U57" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:21" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="3">
+    <row r="58" spans="1:21" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="2">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="2">
         <v>6005</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="D58" s="3" t="s">
+      <c r="C58" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="G58" s="2">
+        <v>6</v>
+      </c>
+      <c r="H58" s="2">
+        <v>5</v>
+      </c>
+      <c r="I58" s="2">
+        <v>0</v>
+      </c>
+      <c r="J58" s="2">
+        <v>0</v>
+      </c>
+      <c r="K58" s="2">
+        <v>3</v>
+      </c>
+      <c r="L58" s="2">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="O58" s="2">
+        <v>1</v>
+      </c>
+      <c r="P58" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="2">
+        <v>100</v>
+      </c>
+      <c r="R58" s="2">
+        <v>30</v>
+      </c>
+      <c r="S58" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="G58" s="3">
-        <v>6</v>
-      </c>
-      <c r="H58" s="3">
-        <v>5</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="O58" s="3">
-        <v>1</v>
-      </c>
-      <c r="P58" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>100</v>
-      </c>
-      <c r="R58" s="3">
-        <v>30</v>
-      </c>
-      <c r="S58" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U58" s="3">
+      <c r="T58" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U58" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="7">
+    <row r="59" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="6">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="6">
         <v>6003</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="F59" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G59" s="7">
+      <c r="G59" s="6">
         <v>6</v>
       </c>
-      <c r="H59" s="7">
+      <c r="H59" s="6">
         <v>3</v>
       </c>
-      <c r="I59" s="7">
+      <c r="I59" s="6">
         <v>9999</v>
       </c>
-      <c r="J59" s="7">
-        <v>0</v>
-      </c>
-      <c r="K59" s="7">
-        <v>1</v>
-      </c>
-      <c r="L59" s="7">
-        <v>0</v>
-      </c>
-      <c r="M59" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N59" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O59" s="7">
-        <v>1</v>
-      </c>
-      <c r="P59" s="7">
+      <c r="J59" s="6">
+        <v>0</v>
+      </c>
+      <c r="K59" s="6">
+        <v>1</v>
+      </c>
+      <c r="L59" s="6">
+        <v>0</v>
+      </c>
+      <c r="M59" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N59" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O59" s="6">
+        <v>1</v>
+      </c>
+      <c r="P59" s="6">
         <v>5</v>
       </c>
-      <c r="Q59" s="7">
+      <c r="Q59" s="6">
         <v>100</v>
       </c>
-      <c r="R59" s="7">
+      <c r="R59" s="6">
         <v>30</v>
       </c>
-      <c r="S59" s="7" t="s">
+      <c r="S59" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="T59" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U59" s="7">
+      <c r="T59" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U59" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="8">
+    <row r="60" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="7">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="7">
         <v>7001</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E60" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F60" s="8" t="s">
+      <c r="F60" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G60" s="8">
+      <c r="G60" s="7">
         <v>6</v>
       </c>
-      <c r="H60" s="8">
+      <c r="H60" s="7">
         <v>12</v>
       </c>
-      <c r="I60" s="8">
-        <v>0</v>
-      </c>
-      <c r="J60" s="8">
-        <v>0</v>
-      </c>
-      <c r="K60" s="8">
-        <v>1</v>
-      </c>
-      <c r="L60" s="8">
-        <v>0</v>
-      </c>
-      <c r="M60" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="N60" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="O60" s="8">
-        <v>1</v>
-      </c>
-      <c r="P60" s="8">
+      <c r="I60" s="7">
+        <v>0</v>
+      </c>
+      <c r="J60" s="7">
+        <v>0</v>
+      </c>
+      <c r="K60" s="7">
+        <v>1</v>
+      </c>
+      <c r="L60" s="7">
+        <v>0</v>
+      </c>
+      <c r="M60" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N60" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O60" s="7">
+        <v>1</v>
+      </c>
+      <c r="P60" s="7">
         <v>6</v>
       </c>
-      <c r="Q60" s="8">
+      <c r="Q60" s="7">
         <v>100</v>
       </c>
-      <c r="R60" s="8">
+      <c r="R60" s="7">
         <v>30</v>
       </c>
-      <c r="S60" s="8" t="s">
+      <c r="S60" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="T60" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="U60" s="8">
+      <c r="T60" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U60" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:21" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="8">
+    <row r="61" spans="1:21" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="7">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="7">
         <v>7002</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F61" s="8" t="s">
+      <c r="F61" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G61" s="8">
+      <c r="G61" s="7">
         <v>18</v>
       </c>
-      <c r="H61" s="8">
+      <c r="H61" s="7">
         <v>15</v>
       </c>
-      <c r="I61" s="8">
-        <v>0</v>
-      </c>
-      <c r="J61" s="8">
-        <v>0</v>
-      </c>
-      <c r="K61" s="8">
-        <v>1</v>
-      </c>
-      <c r="L61" s="8">
-        <v>0</v>
-      </c>
-      <c r="M61" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="N61" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="O61" s="8">
-        <v>1</v>
-      </c>
-      <c r="P61" s="8">
+      <c r="I61" s="7">
+        <v>0</v>
+      </c>
+      <c r="J61" s="7">
+        <v>0</v>
+      </c>
+      <c r="K61" s="7">
+        <v>1</v>
+      </c>
+      <c r="L61" s="7">
+        <v>0</v>
+      </c>
+      <c r="M61" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N61" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O61" s="7">
+        <v>1</v>
+      </c>
+      <c r="P61" s="7">
         <v>6</v>
       </c>
-      <c r="Q61" s="8">
+      <c r="Q61" s="7">
         <v>100</v>
       </c>
-      <c r="R61" s="8">
+      <c r="R61" s="7">
         <v>30</v>
       </c>
-      <c r="S61" s="10" t="s">
+      <c r="S61" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="T61" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="U61" s="8">
+      <c r="T61" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U61" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="8">
+    <row r="62" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="7">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B62" s="8">
+      <c r="B62" s="7">
         <v>8001</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F62" s="8" t="s">
+      <c r="F62" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G62" s="8">
+      <c r="G62" s="7">
         <v>6</v>
       </c>
-      <c r="H62" s="8">
+      <c r="H62" s="7">
         <v>12</v>
       </c>
-      <c r="I62" s="8">
-        <v>0</v>
-      </c>
-      <c r="J62" s="8">
-        <v>0</v>
-      </c>
-      <c r="K62" s="8">
-        <v>1</v>
-      </c>
-      <c r="L62" s="8">
-        <v>0</v>
-      </c>
-      <c r="M62" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="N62" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="O62" s="8">
-        <v>1</v>
-      </c>
-      <c r="P62" s="8">
+      <c r="I62" s="7">
+        <v>0</v>
+      </c>
+      <c r="J62" s="7">
+        <v>0</v>
+      </c>
+      <c r="K62" s="7">
+        <v>1</v>
+      </c>
+      <c r="L62" s="7">
+        <v>0</v>
+      </c>
+      <c r="M62" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N62" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O62" s="7">
+        <v>1</v>
+      </c>
+      <c r="P62" s="7">
         <v>7</v>
       </c>
-      <c r="Q62" s="8">
+      <c r="Q62" s="7">
         <v>100</v>
       </c>
-      <c r="R62" s="8">
+      <c r="R62" s="7">
         <v>30</v>
       </c>
-      <c r="S62" s="8" t="s">
+      <c r="S62" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="T62" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="U62" s="8">
+      <c r="T62" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U62" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="8">
+    <row r="63" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="7">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B63" s="8">
+      <c r="B63" s="7">
         <v>8002</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D63" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F63" s="8" t="s">
+      <c r="F63" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G63" s="8">
+      <c r="G63" s="7">
         <v>6</v>
       </c>
-      <c r="H63" s="8">
+      <c r="H63" s="7">
         <v>14</v>
       </c>
-      <c r="I63" s="8">
-        <v>0</v>
-      </c>
-      <c r="J63" s="8">
-        <v>0</v>
-      </c>
-      <c r="K63" s="8">
-        <v>1</v>
-      </c>
-      <c r="L63" s="8">
-        <v>0</v>
-      </c>
-      <c r="M63" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="N63" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="O63" s="8">
-        <v>1</v>
-      </c>
-      <c r="P63" s="8">
+      <c r="I63" s="7">
+        <v>0</v>
+      </c>
+      <c r="J63" s="7">
+        <v>0</v>
+      </c>
+      <c r="K63" s="7">
+        <v>1</v>
+      </c>
+      <c r="L63" s="7">
+        <v>0</v>
+      </c>
+      <c r="M63" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N63" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O63" s="7">
+        <v>1</v>
+      </c>
+      <c r="P63" s="7">
         <v>7</v>
       </c>
-      <c r="Q63" s="8">
+      <c r="Q63" s="7">
         <v>100</v>
       </c>
-      <c r="R63" s="8">
+      <c r="R63" s="7">
         <v>30</v>
       </c>
-      <c r="S63" s="8" t="s">
+      <c r="S63" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="T63" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="U63" s="8">
+      <c r="T63" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="U63" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:21" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="3">
+    <row r="64" spans="1:21" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="2">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64" s="2">
         <v>9001</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F64" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G64" s="3">
+      <c r="G64" s="2">
         <v>2</v>
       </c>
-      <c r="H64" s="3">
+      <c r="H64" s="2">
         <v>7</v>
       </c>
-      <c r="I64" s="3">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3">
-        <v>0</v>
-      </c>
-      <c r="K64" s="3">
+      <c r="I64" s="2">
+        <v>0</v>
+      </c>
+      <c r="J64" s="2">
+        <v>0</v>
+      </c>
+      <c r="K64" s="2">
         <v>10</v>
       </c>
-      <c r="L64" s="3">
-        <v>0</v>
-      </c>
-      <c r="M64" s="3" t="s">
+      <c r="L64" s="2">
+        <v>0</v>
+      </c>
+      <c r="M64" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="N64" s="3" t="s">
+      <c r="N64" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="O64" s="3">
-        <v>1</v>
-      </c>
-      <c r="P64" s="3">
+      <c r="O64" s="2">
+        <v>1</v>
+      </c>
+      <c r="P64" s="2">
         <v>8</v>
       </c>
-      <c r="Q64" s="3">
+      <c r="Q64" s="2">
         <v>100</v>
       </c>
-      <c r="R64" s="3">
+      <c r="R64" s="2">
         <v>120</v>
       </c>
-      <c r="S64" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="T64" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U64" s="3">
+      <c r="S64" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="T64" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U64" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:21" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="3">
+    <row r="65" spans="1:21" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="2">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65" s="2">
         <v>9005</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D65" s="3" t="s">
+      <c r="C65" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E65" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="G65" s="3">
+      <c r="G65" s="2">
         <v>2</v>
       </c>
-      <c r="H65" s="3">
+      <c r="H65" s="2">
         <v>4</v>
       </c>
-      <c r="I65" s="3">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3">
-        <v>0</v>
-      </c>
-      <c r="K65" s="3">
+      <c r="I65" s="2">
+        <v>0</v>
+      </c>
+      <c r="J65" s="2">
+        <v>0</v>
+      </c>
+      <c r="K65" s="2">
         <v>3</v>
       </c>
-      <c r="L65" s="3">
-        <v>0</v>
-      </c>
-      <c r="M65" s="3" t="s">
+      <c r="L65" s="2">
+        <v>0</v>
+      </c>
+      <c r="M65" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="N65" s="3" t="s">
+      <c r="N65" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="O65" s="3">
-        <v>1</v>
-      </c>
-      <c r="P65" s="3">
+      <c r="O65" s="2">
+        <v>1</v>
+      </c>
+      <c r="P65" s="2">
         <v>8</v>
       </c>
-      <c r="Q65" s="3">
+      <c r="Q65" s="2">
         <v>100</v>
       </c>
-      <c r="R65" s="3">
+      <c r="R65" s="2">
         <v>30</v>
       </c>
-      <c r="S65" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="T65" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U65" s="3">
+      <c r="S65" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U65" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:21" s="7" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="7">
+    <row r="66" spans="1:21" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="6">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B66" s="7">
+      <c r="B66" s="6">
         <v>9002</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E66" s="7" t="s">
+      <c r="E66" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="F66" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G66" s="7">
+      <c r="G66" s="6">
         <v>6</v>
       </c>
-      <c r="H66" s="7">
+      <c r="H66" s="6">
         <v>5</v>
       </c>
-      <c r="I66" s="7">
+      <c r="I66" s="6">
         <v>9999</v>
       </c>
-      <c r="J66" s="7">
-        <v>0</v>
-      </c>
-      <c r="K66" s="7">
+      <c r="J66" s="6">
+        <v>0</v>
+      </c>
+      <c r="K66" s="6">
         <v>10</v>
       </c>
-      <c r="L66" s="7">
-        <v>0</v>
-      </c>
-      <c r="M66" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N66" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O66" s="7">
-        <v>1</v>
-      </c>
-      <c r="P66" s="7">
+      <c r="L66" s="6">
+        <v>0</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O66" s="6">
+        <v>1</v>
+      </c>
+      <c r="P66" s="6">
         <v>8</v>
       </c>
-      <c r="Q66" s="7">
+      <c r="Q66" s="6">
         <v>100</v>
       </c>
-      <c r="R66" s="7">
+      <c r="R66" s="6">
         <v>30</v>
       </c>
-      <c r="S66" s="9" t="s">
+      <c r="S66" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="T66" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U66" s="7">
+      <c r="T66" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U66" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67">
+    <row r="67" spans="1:21" s="6" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="6">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="6">
         <v>9004</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F67" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="6">
         <v>2</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="6">
         <v>10</v>
       </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>1</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67" t="s">
+      <c r="I67" s="6">
+        <v>0</v>
+      </c>
+      <c r="J67" s="6">
+        <v>0</v>
+      </c>
+      <c r="K67" s="6">
+        <v>1</v>
+      </c>
+      <c r="L67" s="6">
+        <v>0</v>
+      </c>
+      <c r="M67" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="N67" t="s">
-        <v>94</v>
-      </c>
-      <c r="O67">
-        <v>1</v>
-      </c>
-      <c r="P67">
+      <c r="N67" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O67" s="6">
+        <v>1</v>
+      </c>
+      <c r="P67" s="6">
         <v>8</v>
       </c>
-      <c r="Q67">
+      <c r="Q67" s="6">
         <v>100</v>
       </c>
-      <c r="R67">
+      <c r="R67" s="6">
         <v>60</v>
       </c>
-      <c r="S67" s="2" t="s">
+      <c r="S67" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="T67" t="s">
-        <v>94</v>
-      </c>
-      <c r="U67">
+      <c r="T67" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="U67" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:21" s="3" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="3">
+    <row r="68" spans="1:21" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="2">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="2">
         <v>9003</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D68" s="3" t="s">
+      <c r="C68" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G68" s="3">
+      <c r="G68" s="2">
         <v>6</v>
       </c>
-      <c r="H68" s="3">
-        <v>1</v>
-      </c>
-      <c r="I68" s="3">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3">
-        <v>1</v>
-      </c>
-      <c r="K68" s="3">
-        <v>1</v>
-      </c>
-      <c r="L68" s="3">
-        <v>1</v>
-      </c>
-      <c r="M68" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="N68" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O68" s="3">
-        <v>1</v>
-      </c>
-      <c r="P68" s="3">
+      <c r="H68" s="2">
+        <v>1</v>
+      </c>
+      <c r="I68" s="2">
+        <v>0</v>
+      </c>
+      <c r="J68" s="2">
+        <v>1</v>
+      </c>
+      <c r="K68" s="2">
+        <v>1</v>
+      </c>
+      <c r="L68" s="2">
+        <v>1</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O68" s="2">
+        <v>1</v>
+      </c>
+      <c r="P68" s="2">
         <v>8</v>
       </c>
-      <c r="Q68" s="3">
+      <c r="Q68" s="2">
         <v>100</v>
       </c>
-      <c r="R68" s="3">
+      <c r="R68" s="2">
         <v>30</v>
       </c>
-      <c r="S68" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="T68" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U68" s="3">
+      <c r="S68" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="T68" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U68" s="2">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41357C68-8D10-4E4F-A541-3F7F26B7BEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D18FD9-E832-498B-ADFC-28E3A50EF955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3195" yWindow="1110" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="329">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -3844,6 +3844,30 @@
     <rPh sb="96" eb="98">
       <t>シヨウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Nappe</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Wind_Roll</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Wind_Pen</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Spring_Pharmacy</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Statue_of_Bear</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Chocolate_Tempering</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4829,7 +4853,7 @@
         <v>1008</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>64</v>
+        <v>328</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>82</v>
@@ -6215,7 +6239,7 @@
         <v>4010</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>37</v>
+        <v>323</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>152</v>
@@ -6677,7 +6701,7 @@
         <v>4012</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>37</v>
+        <v>324</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>180</v>
@@ -6743,7 +6767,7 @@
         <v>4012</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>37</v>
+        <v>325</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>182</v>
@@ -7073,7 +7097,7 @@
         <v>4007</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>37</v>
+        <v>327</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>85</v>
@@ -7997,7 +8021,7 @@
         <v>6004</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>65</v>
+        <v>326</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>276</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D18FD9-E832-498B-ADFC-28E3A50EF955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD7F6DF-7C08-47F8-9EE1-0BF91091EF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3195" yWindow="1110" windowWidth="25560" windowHeight="14325" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2625" yWindow="795" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4805,7 +4805,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
@@ -4871,7 +4871,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
@@ -8105,7 +8105,7 @@
         <v>5</v>
       </c>
       <c r="I58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD7F6DF-7C08-47F8-9EE1-0BF91091EF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128F144B-FC26-43F7-A213-DC8392CD0D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2625" yWindow="795" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3375" yWindow="855" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="334">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -3868,6 +3868,26 @@
   </si>
   <si>
     <t>skicon_Chocolate_Tempering</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Soda_Study</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Latte_Art</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Magic_Soda</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Rainbow_Rain</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Moonlight_Banana</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -7493,7 +7513,7 @@
         <v>5007</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>66</v>
+        <v>329</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>288</v>
@@ -7625,7 +7645,7 @@
         <v>5002</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>66</v>
+        <v>330</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>121</v>
@@ -7691,7 +7711,7 @@
         <v>5003</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>66</v>
+        <v>333</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>140</v>
@@ -7757,7 +7777,7 @@
         <v>5005</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>66</v>
+        <v>331</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>207</v>
@@ -7823,7 +7843,7 @@
         <v>5006</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>66</v>
+        <v>332</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>222</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128F144B-FC26-43F7-A213-DC8392CD0D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDA8D4E-B45F-42AA-922C-85FC2BC02A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="855" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="335">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -3523,51 +3523,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>豆類を焼いて香りや味を出す。豆殻も一緒に取る。
-派生：
-LV1でテンパリング習得可</t>
-    <rPh sb="0" eb="1">
-      <t>マメ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>ルイ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>カオ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>アジ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>マメ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>カラ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>イッショ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ハセイ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>シュウトク</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>かいがら・パラダイス</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3888,6 +3843,68 @@
   </si>
   <si>
     <t>skicon_Moonlight_Banana</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>豆類を焼いて香りや味を出す。豆殻も一緒に取る。
+LVが上がると、少し成功率も上がる。
+派生：
+LV1でテンパリング習得可</t>
+    <rPh sb="0" eb="1">
+      <t>マメ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ルイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アジ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>マメ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カラ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イッショ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ハセイ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>シュウトク</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill_enshututype</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4319,7 +4336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:U68"/>
+  <dimension ref="A1:V68"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -4329,15 +4346,15 @@
     <col min="7" max="7" width="7.5" customWidth="1"/>
     <col min="8" max="8" width="8.125" customWidth="1"/>
     <col min="9" max="15" width="6.75" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
-    <col min="17" max="17" width="10.375" customWidth="1"/>
-    <col min="18" max="18" width="7.875" customWidth="1"/>
-    <col min="19" max="19" width="25.125" customWidth="1"/>
-    <col min="20" max="20" width="11.625" customWidth="1"/>
-    <col min="21" max="21" width="6.75" customWidth="1"/>
+    <col min="16" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.375" customWidth="1"/>
+    <col min="19" max="19" width="7.875" customWidth="1"/>
+    <col min="20" max="20" width="25.125" customWidth="1"/>
+    <col min="21" max="21" width="11.625" customWidth="1"/>
+    <col min="22" max="22" width="6.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -4387,22 +4404,25 @@
         <v>9</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
         <f t="shared" ref="A2:A68" si="0">ROW()-2</f>
         <v>0</v>
@@ -4453,22 +4473,25 @@
         <v>9</v>
       </c>
       <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
         <v>100</v>
       </c>
-      <c r="R2" s="4">
+      <c r="S2" s="4">
         <v>30</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="T2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="U2" s="4">
+      <c r="U2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V2" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -4519,22 +4542,25 @@
         <v>9</v>
       </c>
       <c r="Q3" s="2">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2">
         <v>100</v>
       </c>
-      <c r="R3" s="2">
+      <c r="S3" s="2">
         <v>30</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U3" s="2">
+      <c r="U3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V3" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:21" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -4585,22 +4611,25 @@
         <v>9</v>
       </c>
       <c r="Q4" s="4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4">
         <v>100</v>
       </c>
-      <c r="R4" s="4">
+      <c r="S4" s="4">
         <v>30</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="T4" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="T4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="U4" s="4">
+      <c r="U4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V4" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:21" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -4609,7 +4638,7 @@
         <v>1010</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>164</v>
@@ -4651,22 +4680,25 @@
         <v>9</v>
       </c>
       <c r="Q5" s="2">
+        <v>0</v>
+      </c>
+      <c r="R5" s="2">
         <v>100</v>
       </c>
-      <c r="R5" s="2">
+      <c r="S5" s="2">
         <v>30</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="T5" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U5" s="2">
+      <c r="U5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V5" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:22" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -4675,7 +4707,7 @@
         <v>1009</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>112</v>
@@ -4717,22 +4749,25 @@
         <v>9</v>
       </c>
       <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2">
         <v>100</v>
       </c>
-      <c r="R6" s="2">
+      <c r="S6" s="2">
         <v>30</v>
       </c>
-      <c r="S6" s="3" t="s">
+      <c r="T6" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="T6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U6" s="2">
+      <c r="U6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V6" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:21" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:22" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -4741,7 +4776,7 @@
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>58</v>
@@ -4783,22 +4818,25 @@
         <v>9</v>
       </c>
       <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
         <v>100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>30</v>
       </c>
-      <c r="S7" s="3" t="s">
+      <c r="T7" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:21" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:22" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -4831,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -4849,22 +4887,25 @@
         <v>9</v>
       </c>
       <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2">
         <v>100</v>
       </c>
-      <c r="R8" s="2">
+      <c r="S8" s="2">
         <v>30</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="T8" s="2" t="s">
+      <c r="T8" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="U8" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="U8" s="2">
+      <c r="V8" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:22" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -4873,7 +4914,7 @@
         <v>1008</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>82</v>
@@ -4915,22 +4956,25 @@
         <v>9</v>
       </c>
       <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2">
         <v>100</v>
       </c>
-      <c r="R9" s="2">
+      <c r="S9" s="2">
         <v>30</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="T9" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="U9" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="U9" s="2">
+      <c r="V9" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:22" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -4939,7 +4983,7 @@
         <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>231</v>
@@ -4981,22 +5025,25 @@
         <v>9</v>
       </c>
       <c r="Q10" s="2">
+        <v>1</v>
+      </c>
+      <c r="R10" s="2">
         <v>100</v>
       </c>
-      <c r="R10" s="2">
+      <c r="S10" s="2">
         <v>30</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="T10" s="2" t="s">
+      <c r="T10" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="U10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U10" s="2">
+      <c r="V10" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:22" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -5047,22 +5094,25 @@
         <v>9</v>
       </c>
       <c r="Q11" s="2">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2">
         <v>100</v>
       </c>
-      <c r="R11" s="2">
+      <c r="S11" s="2">
         <v>30</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="T11" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="T11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U11" s="2">
+      <c r="U11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:21" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:22" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -5112,23 +5162,26 @@
       <c r="P12" s="6">
         <v>9</v>
       </c>
-      <c r="Q12" s="6">
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
+      <c r="R12" s="6">
         <v>100</v>
       </c>
-      <c r="R12" s="6">
+      <c r="S12" s="6">
         <v>30</v>
       </c>
-      <c r="S12" s="6" t="s">
+      <c r="T12" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="T12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U12" s="6">
+      <c r="U12" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V12" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:22" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="6">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -5178,23 +5231,26 @@
       <c r="P13" s="6">
         <v>9</v>
       </c>
-      <c r="Q13" s="6">
+      <c r="Q13" s="2">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6">
         <v>100</v>
       </c>
-      <c r="R13" s="6">
+      <c r="S13" s="6">
         <v>30</v>
       </c>
-      <c r="S13" s="6" t="s">
+      <c r="T13" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="T13" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U13" s="6">
+      <c r="U13" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V13" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:21" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:22" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -5203,7 +5259,7 @@
         <v>2004</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>110</v>
@@ -5245,22 +5301,25 @@
         <v>1</v>
       </c>
       <c r="Q14" s="2">
+        <v>0</v>
+      </c>
+      <c r="R14" s="2">
         <v>100</v>
       </c>
-      <c r="R14" s="2">
+      <c r="S14" s="2">
         <v>30</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="T14" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U14" s="2">
+      <c r="U14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V14" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:22" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -5311,22 +5370,25 @@
         <v>1</v>
       </c>
       <c r="Q15" s="2">
+        <v>0</v>
+      </c>
+      <c r="R15" s="2">
         <v>100</v>
       </c>
-      <c r="R15" s="2">
+      <c r="S15" s="2">
         <v>120</v>
       </c>
-      <c r="S15" s="3" t="s">
+      <c r="T15" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="T15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U15" s="2">
+      <c r="U15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V15" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:22" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -5335,7 +5397,7 @@
         <v>2001</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>177</v>
@@ -5377,22 +5439,25 @@
         <v>1</v>
       </c>
       <c r="Q16" s="2">
+        <v>0</v>
+      </c>
+      <c r="R16" s="2">
         <v>100</v>
       </c>
-      <c r="R16" s="2">
+      <c r="S16" s="2">
         <v>120</v>
       </c>
-      <c r="S16" s="3" t="s">
+      <c r="T16" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="T16" s="2" t="s">
+      <c r="U16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="U16" s="2">
+      <c r="V16" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:22" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -5442,23 +5507,26 @@
       <c r="P17" s="4">
         <v>1</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="Q17" s="2">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4">
         <v>100</v>
       </c>
-      <c r="R17" s="4">
+      <c r="S17" s="4">
         <v>120</v>
       </c>
-      <c r="S17" s="4" t="s">
+      <c r="T17" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="T17" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="U17" s="4">
+      <c r="U17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V17" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:21" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:22" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -5467,13 +5535,13 @@
         <v>2005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>268</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>269</v>
@@ -5509,22 +5577,25 @@
         <v>1</v>
       </c>
       <c r="Q18" s="2">
+        <v>1</v>
+      </c>
+      <c r="R18" s="2">
         <v>100</v>
       </c>
-      <c r="R18" s="2">
+      <c r="S18" s="2">
         <v>30</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="T18" s="2" t="s">
+      <c r="T18" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="U18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="U18" s="2">
+      <c r="V18" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:21" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:22" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -5533,7 +5604,7 @@
         <v>2003</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>118</v>
@@ -5575,22 +5646,25 @@
         <v>1</v>
       </c>
       <c r="Q19" s="2">
+        <v>0</v>
+      </c>
+      <c r="R19" s="2">
         <v>100</v>
       </c>
-      <c r="R19" s="2">
+      <c r="S19" s="2">
         <v>30</v>
       </c>
-      <c r="S19" s="3" t="s">
+      <c r="T19" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="T19" s="2" t="s">
+      <c r="U19" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="U19" s="2">
+      <c r="V19" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:21" s="6" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:22" s="6" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -5640,23 +5714,26 @@
       <c r="P20" s="6">
         <v>1</v>
       </c>
-      <c r="Q20" s="6">
+      <c r="Q20" s="2">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6">
         <v>100</v>
       </c>
-      <c r="R20" s="6">
+      <c r="S20" s="6">
         <v>30</v>
       </c>
-      <c r="S20" s="6" t="s">
+      <c r="T20" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="T20" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U20" s="6">
+      <c r="U20" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V20" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:21" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:22" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -5707,22 +5784,25 @@
         <v>2</v>
       </c>
       <c r="Q21" s="2">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2">
         <v>100</v>
       </c>
-      <c r="R21" s="2">
+      <c r="S21" s="2">
         <v>30</v>
       </c>
-      <c r="S21" s="3" t="s">
+      <c r="T21" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="T21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U21" s="2">
+      <c r="U21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V21" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:21" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:22" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -5773,22 +5853,25 @@
         <v>2</v>
       </c>
       <c r="Q22" s="2">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2">
         <v>100</v>
       </c>
-      <c r="R22" s="2">
+      <c r="S22" s="2">
         <v>30</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="T22" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="T22" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U22" s="2">
+      <c r="U22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V22" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -5839,22 +5922,25 @@
         <v>2</v>
       </c>
       <c r="Q23" s="2">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2">
         <v>100</v>
       </c>
-      <c r="R23" s="2">
+      <c r="S23" s="2">
         <v>30</v>
       </c>
-      <c r="S23" s="3" t="s">
+      <c r="T23" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="T23" s="2" t="s">
+      <c r="U23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="U23" s="2">
+      <c r="V23" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -5863,7 +5949,7 @@
         <v>3003</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>106</v>
@@ -5905,22 +5991,25 @@
         <v>2</v>
       </c>
       <c r="Q24" s="2">
+        <v>1</v>
+      </c>
+      <c r="R24" s="2">
         <v>100</v>
       </c>
-      <c r="R24" s="2">
+      <c r="S24" s="2">
         <v>30</v>
       </c>
-      <c r="S24" s="3" t="s">
+      <c r="T24" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="T24" s="2" t="s">
+      <c r="U24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="U24" s="2">
+      <c r="V24" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -5929,7 +6018,7 @@
         <v>3008</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>271</v>
@@ -5971,22 +6060,25 @@
         <v>2</v>
       </c>
       <c r="Q25" s="2">
+        <v>1</v>
+      </c>
+      <c r="R25" s="2">
         <v>100</v>
       </c>
-      <c r="R25" s="2">
+      <c r="S25" s="2">
         <v>30</v>
       </c>
-      <c r="S25" s="3" t="s">
+      <c r="T25" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="T25" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U25" s="2">
+      <c r="U25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V25" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -5995,7 +6087,7 @@
         <v>3004</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>115</v>
@@ -6037,22 +6129,25 @@
         <v>2</v>
       </c>
       <c r="Q26" s="2">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2">
         <v>100</v>
       </c>
-      <c r="R26" s="2">
+      <c r="S26" s="2">
         <v>30</v>
       </c>
-      <c r="S26" s="3" t="s">
+      <c r="T26" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="T26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U26" s="2">
+      <c r="U26" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V26" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -6061,7 +6156,7 @@
         <v>3007</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>265</v>
@@ -6103,22 +6198,25 @@
         <v>2</v>
       </c>
       <c r="Q27" s="2">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2">
         <v>100</v>
       </c>
-      <c r="R27" s="2">
+      <c r="S27" s="2">
         <v>30</v>
       </c>
-      <c r="S27" s="3" t="s">
+      <c r="T27" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="T27" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U27" s="2">
+      <c r="U27" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V27" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:22" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="6">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -6168,23 +6266,26 @@
       <c r="P28" s="6">
         <v>2</v>
       </c>
-      <c r="Q28" s="6">
+      <c r="Q28" s="2">
+        <v>0</v>
+      </c>
+      <c r="R28" s="6">
         <v>100</v>
       </c>
-      <c r="R28" s="6">
+      <c r="S28" s="6">
         <v>30</v>
       </c>
-      <c r="S28" s="8" t="s">
+      <c r="T28" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="T28" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U28" s="6">
+      <c r="U28" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V28" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:22" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="6">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -6234,23 +6335,26 @@
       <c r="P29" s="6">
         <v>2</v>
       </c>
-      <c r="Q29" s="6">
+      <c r="Q29" s="2">
+        <v>0</v>
+      </c>
+      <c r="R29" s="6">
         <v>100</v>
       </c>
-      <c r="R29" s="6">
+      <c r="S29" s="6">
         <v>30</v>
       </c>
-      <c r="S29" s="8" t="s">
+      <c r="T29" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="T29" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U29" s="6">
+      <c r="U29" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V29" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:22" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -6259,7 +6363,7 @@
         <v>4010</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>152</v>
@@ -6301,22 +6405,25 @@
         <v>3</v>
       </c>
       <c r="Q30" s="2">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2">
         <v>100</v>
       </c>
-      <c r="R30" s="2">
+      <c r="S30" s="2">
         <v>30</v>
       </c>
-      <c r="S30" s="3" t="s">
+      <c r="T30" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="T30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U30" s="2">
+      <c r="U30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V30" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:22" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -6325,7 +6432,7 @@
         <v>4011</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>155</v>
@@ -6367,22 +6474,25 @@
         <v>3</v>
       </c>
       <c r="Q31" s="2">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2">
         <v>100</v>
       </c>
-      <c r="R31" s="2">
+      <c r="S31" s="2">
         <v>30</v>
       </c>
-      <c r="S31" s="3" t="s">
+      <c r="T31" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="T31" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U31" s="2">
+      <c r="U31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V31" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:22" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -6391,7 +6501,7 @@
         <v>4001</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>23</v>
@@ -6433,22 +6543,25 @@
         <v>3</v>
       </c>
       <c r="Q32" s="2">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2">
         <v>85</v>
       </c>
-      <c r="R32" s="2">
+      <c r="S32" s="2">
         <v>30</v>
       </c>
-      <c r="S32" s="3" t="s">
+      <c r="T32" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="T32" s="2" t="s">
+      <c r="U32" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="U32" s="2">
+      <c r="V32" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -6457,7 +6570,7 @@
         <v>4002</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>25</v>
@@ -6499,22 +6612,25 @@
         <v>3</v>
       </c>
       <c r="Q33" s="2">
+        <v>0</v>
+      </c>
+      <c r="R33" s="2">
         <v>100</v>
       </c>
-      <c r="R33" s="2">
+      <c r="S33" s="2">
         <v>30</v>
       </c>
-      <c r="S33" s="3" t="s">
+      <c r="T33" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="T33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U33" s="2">
+      <c r="U33" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V33" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -6523,7 +6639,7 @@
         <v>4010</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>128</v>
@@ -6565,22 +6681,25 @@
         <v>3</v>
       </c>
       <c r="Q34" s="2">
+        <v>0</v>
+      </c>
+      <c r="R34" s="2">
         <v>100</v>
       </c>
-      <c r="R34" s="2">
+      <c r="S34" s="2">
         <v>30</v>
       </c>
-      <c r="S34" s="3" t="s">
+      <c r="T34" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="T34" s="2" t="s">
+      <c r="U34" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U34" s="2">
+      <c r="V34" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -6589,7 +6708,7 @@
         <v>4011</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>173</v>
@@ -6631,22 +6750,25 @@
         <v>3</v>
       </c>
       <c r="Q35" s="2">
+        <v>0</v>
+      </c>
+      <c r="R35" s="2">
         <v>100</v>
       </c>
-      <c r="R35" s="2">
+      <c r="S35" s="2">
         <v>30</v>
       </c>
-      <c r="S35" s="3" t="s">
+      <c r="T35" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="T35" s="2" t="s">
+      <c r="U35" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U35" s="2">
+      <c r="V35" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -6655,7 +6777,7 @@
         <v>4012</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>175</v>
@@ -6697,22 +6819,25 @@
         <v>3</v>
       </c>
       <c r="Q36" s="2">
+        <v>0</v>
+      </c>
+      <c r="R36" s="2">
         <v>100</v>
       </c>
-      <c r="R36" s="2">
+      <c r="S36" s="2">
         <v>30</v>
       </c>
-      <c r="S36" s="3" t="s">
+      <c r="T36" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="T36" s="2" t="s">
+      <c r="U36" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U36" s="2">
+      <c r="V36" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -6721,7 +6846,7 @@
         <v>4012</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>180</v>
@@ -6763,22 +6888,25 @@
         <v>3</v>
       </c>
       <c r="Q37" s="2">
+        <v>0</v>
+      </c>
+      <c r="R37" s="2">
         <v>100</v>
       </c>
-      <c r="R37" s="2">
+      <c r="S37" s="2">
         <v>30</v>
       </c>
-      <c r="S37" s="3" t="s">
+      <c r="T37" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="T37" s="2" t="s">
+      <c r="U37" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U37" s="2">
+      <c r="V37" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -6787,7 +6915,7 @@
         <v>4012</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>182</v>
@@ -6829,22 +6957,25 @@
         <v>3</v>
       </c>
       <c r="Q38" s="2">
+        <v>0</v>
+      </c>
+      <c r="R38" s="2">
         <v>100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>30</v>
       </c>
-      <c r="S38" s="3" t="s">
+      <c r="T38" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="T38" s="2" t="s">
+      <c r="U38" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:21" s="6" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:22" s="6" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="6">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -6894,23 +7025,26 @@
       <c r="P39" s="6">
         <v>3</v>
       </c>
-      <c r="Q39" s="6">
+      <c r="Q39" s="2">
+        <v>0</v>
+      </c>
+      <c r="R39" s="6">
         <v>100</v>
       </c>
-      <c r="R39" s="6">
+      <c r="S39" s="6">
         <v>30</v>
       </c>
-      <c r="S39" s="8" t="s">
+      <c r="T39" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="T39" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U39" s="6">
+      <c r="U39" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V39" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -6919,7 +7053,7 @@
         <v>4004</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>27</v>
@@ -6961,22 +7095,25 @@
         <v>3</v>
       </c>
       <c r="Q40" s="2">
+        <v>1</v>
+      </c>
+      <c r="R40" s="2">
         <v>100</v>
       </c>
-      <c r="R40" s="2">
+      <c r="S40" s="2">
         <v>30</v>
       </c>
-      <c r="S40" s="3" t="s">
+      <c r="T40" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="T40" s="2" t="s">
+      <c r="U40" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U40" s="2">
+      <c r="V40" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:21" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:22" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="6">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -7026,23 +7163,26 @@
       <c r="P41" s="6">
         <v>3</v>
       </c>
-      <c r="Q41" s="6">
+      <c r="Q41" s="2">
+        <v>0</v>
+      </c>
+      <c r="R41" s="6">
         <v>100</v>
       </c>
-      <c r="R41" s="6">
+      <c r="S41" s="6">
         <v>30</v>
       </c>
-      <c r="S41" s="8" t="s">
+      <c r="T41" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="T41" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U41" s="6">
+      <c r="U41" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V41" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A42" s="6">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -7092,23 +7232,26 @@
       <c r="P42" s="6">
         <v>3</v>
       </c>
-      <c r="Q42" s="6">
+      <c r="Q42" s="2">
+        <v>0</v>
+      </c>
+      <c r="R42" s="6">
         <v>100</v>
       </c>
-      <c r="R42" s="6">
+      <c r="S42" s="6">
         <v>30</v>
       </c>
-      <c r="S42" s="6" t="s">
+      <c r="T42" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="T42" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U42" s="6">
+      <c r="U42" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V42" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:22" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -7117,7 +7260,7 @@
         <v>4007</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>85</v>
@@ -7159,22 +7302,25 @@
         <v>3</v>
       </c>
       <c r="Q43" s="2">
+        <v>0</v>
+      </c>
+      <c r="R43" s="2">
         <v>100</v>
       </c>
-      <c r="R43" s="2">
+      <c r="S43" s="2">
         <v>30</v>
       </c>
-      <c r="S43" s="3" t="s">
+      <c r="T43" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="T43" s="2" t="s">
+      <c r="U43" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="U43" s="2">
+      <c r="V43" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A44" s="6">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -7224,23 +7370,26 @@
       <c r="P44" s="6">
         <v>3</v>
       </c>
-      <c r="Q44" s="6">
+      <c r="Q44" s="2">
+        <v>0</v>
+      </c>
+      <c r="R44" s="6">
         <v>100</v>
       </c>
-      <c r="R44" s="6">
+      <c r="S44" s="6">
         <v>30</v>
       </c>
-      <c r="S44" s="6" t="s">
+      <c r="T44" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="T44" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U44" s="6">
+      <c r="U44" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V44" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A45" s="6">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -7290,23 +7439,26 @@
       <c r="P45" s="6">
         <v>3</v>
       </c>
-      <c r="Q45" s="6">
+      <c r="Q45" s="2">
+        <v>0</v>
+      </c>
+      <c r="R45" s="6">
         <v>100</v>
       </c>
-      <c r="R45" s="6">
+      <c r="S45" s="6">
         <v>30</v>
       </c>
-      <c r="S45" s="6" t="s">
+      <c r="T45" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="T45" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U45" s="6">
+      <c r="U45" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V45" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A46" s="6">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -7356,23 +7508,26 @@
       <c r="P46" s="6">
         <v>3</v>
       </c>
-      <c r="Q46" s="6">
+      <c r="Q46" s="2">
+        <v>0</v>
+      </c>
+      <c r="R46" s="6">
         <v>100</v>
       </c>
-      <c r="R46" s="6">
+      <c r="S46" s="6">
         <v>30</v>
       </c>
-      <c r="S46" s="6" t="s">
+      <c r="T46" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="T46" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U46" s="6">
+      <c r="U46" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V46" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:22" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="6">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -7422,23 +7577,26 @@
       <c r="P47" s="6">
         <v>3</v>
       </c>
-      <c r="Q47" s="6">
+      <c r="Q47" s="2">
+        <v>0</v>
+      </c>
+      <c r="R47" s="6">
         <v>100</v>
       </c>
-      <c r="R47" s="6">
+      <c r="S47" s="6">
         <v>30</v>
       </c>
-      <c r="S47" s="8" t="s">
+      <c r="T47" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="T47" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U47" s="6">
+      <c r="U47" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V47" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:21" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:22" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="6">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -7488,23 +7646,26 @@
       <c r="P48" s="6">
         <v>4</v>
       </c>
-      <c r="Q48" s="6">
+      <c r="Q48" s="2">
+        <v>0</v>
+      </c>
+      <c r="R48" s="6">
         <v>100</v>
       </c>
-      <c r="R48" s="6">
+      <c r="S48" s="6">
         <v>30</v>
       </c>
-      <c r="S48" s="8" t="s">
+      <c r="T48" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="T48" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U48" s="6">
+      <c r="U48" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V48" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -7513,7 +7674,7 @@
         <v>5007</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>288</v>
@@ -7555,22 +7716,25 @@
         <v>4</v>
       </c>
       <c r="Q49" s="2">
+        <v>0</v>
+      </c>
+      <c r="R49" s="2">
         <v>100</v>
       </c>
-      <c r="R49" s="2">
+      <c r="S49" s="2">
         <v>30</v>
       </c>
-      <c r="S49" s="3" t="s">
+      <c r="T49" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="T49" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U49" s="2">
+      <c r="U49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V49" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:21" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -7579,7 +7743,7 @@
         <v>5001</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>39</v>
@@ -7621,22 +7785,25 @@
         <v>4</v>
       </c>
       <c r="Q50" s="2">
+        <v>0</v>
+      </c>
+      <c r="R50" s="2">
         <v>100</v>
       </c>
-      <c r="R50" s="2">
+      <c r="S50" s="2">
         <v>30</v>
       </c>
-      <c r="S50" s="3" t="s">
+      <c r="T50" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="T50" s="2" t="s">
+      <c r="U50" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="U50" s="2">
+      <c r="V50" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:21" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -7645,7 +7812,7 @@
         <v>5002</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>121</v>
@@ -7687,22 +7854,25 @@
         <v>4</v>
       </c>
       <c r="Q51" s="2">
+        <v>0</v>
+      </c>
+      <c r="R51" s="2">
         <v>100</v>
       </c>
-      <c r="R51" s="2">
+      <c r="S51" s="2">
         <v>30</v>
       </c>
-      <c r="S51" s="3" t="s">
+      <c r="T51" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="T51" s="2" t="s">
+      <c r="U51" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="U51" s="2">
+      <c r="V51" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:21" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -7711,7 +7881,7 @@
         <v>5003</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>140</v>
@@ -7753,22 +7923,25 @@
         <v>4</v>
       </c>
       <c r="Q52" s="2">
+        <v>0</v>
+      </c>
+      <c r="R52" s="2">
         <v>100</v>
       </c>
-      <c r="R52" s="2">
+      <c r="S52" s="2">
         <v>480</v>
       </c>
-      <c r="S52" s="3" t="s">
+      <c r="T52" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="T52" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U52" s="2">
+      <c r="U52" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V52" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:21" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -7777,7 +7950,7 @@
         <v>5005</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>207</v>
@@ -7819,22 +7992,25 @@
         <v>4</v>
       </c>
       <c r="Q53" s="2">
+        <v>0</v>
+      </c>
+      <c r="R53" s="2">
         <v>100</v>
       </c>
-      <c r="R53" s="2">
+      <c r="S53" s="2">
         <v>30</v>
       </c>
-      <c r="S53" s="3" t="s">
+      <c r="T53" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="T53" s="2" t="s">
+      <c r="U53" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="U53" s="2">
+      <c r="V53" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:21" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -7843,7 +8019,7 @@
         <v>5006</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>222</v>
@@ -7885,22 +8061,25 @@
         <v>4</v>
       </c>
       <c r="Q54" s="2">
+        <v>0</v>
+      </c>
+      <c r="R54" s="2">
         <v>100</v>
       </c>
-      <c r="R54" s="2">
+      <c r="S54" s="2">
         <v>30</v>
       </c>
-      <c r="S54" s="3" t="s">
+      <c r="T54" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="T54" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U54" s="2">
+      <c r="U54" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V54" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A55" s="6">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -7950,23 +8129,26 @@
       <c r="P55" s="6">
         <v>5</v>
       </c>
-      <c r="Q55" s="6">
+      <c r="Q55" s="2">
+        <v>0</v>
+      </c>
+      <c r="R55" s="6">
         <v>100</v>
       </c>
-      <c r="R55" s="6">
+      <c r="S55" s="6">
         <v>30</v>
       </c>
-      <c r="S55" s="6" t="s">
+      <c r="T55" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="T55" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U55" s="6">
+      <c r="U55" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V55" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:21" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:22" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -7975,7 +8157,7 @@
         <v>6002</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>101</v>
@@ -8017,22 +8199,25 @@
         <v>5</v>
       </c>
       <c r="Q56" s="2">
+        <v>0</v>
+      </c>
+      <c r="R56" s="2">
         <v>100</v>
       </c>
-      <c r="R56" s="2">
+      <c r="S56" s="2">
         <v>30</v>
       </c>
-      <c r="S56" s="3" t="s">
+      <c r="T56" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="T56" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U56" s="2">
+      <c r="U56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V56" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:21" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:22" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -8041,7 +8226,7 @@
         <v>6004</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>276</v>
@@ -8083,22 +8268,25 @@
         <v>5</v>
       </c>
       <c r="Q57" s="2">
+        <v>1</v>
+      </c>
+      <c r="R57" s="2">
         <v>100</v>
       </c>
-      <c r="R57" s="2">
+      <c r="S57" s="2">
         <v>30</v>
       </c>
-      <c r="S57" s="3" t="s">
+      <c r="T57" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="T57" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U57" s="2">
+      <c r="U57" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V57" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:21" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:22" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -8107,7 +8295,7 @@
         <v>6005</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>280</v>
@@ -8149,22 +8337,25 @@
         <v>5</v>
       </c>
       <c r="Q58" s="2">
+        <v>1</v>
+      </c>
+      <c r="R58" s="2">
         <v>100</v>
       </c>
-      <c r="R58" s="2">
+      <c r="S58" s="2">
         <v>30</v>
       </c>
-      <c r="S58" s="3" t="s">
+      <c r="T58" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="T58" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U58" s="2">
+      <c r="U58" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V58" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A59" s="6">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -8214,23 +8405,26 @@
       <c r="P59" s="6">
         <v>5</v>
       </c>
-      <c r="Q59" s="6">
+      <c r="Q59" s="2">
+        <v>0</v>
+      </c>
+      <c r="R59" s="6">
         <v>100</v>
       </c>
-      <c r="R59" s="6">
+      <c r="S59" s="6">
         <v>30</v>
       </c>
-      <c r="S59" s="6" t="s">
+      <c r="T59" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="T59" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U59" s="6">
+      <c r="U59" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V59" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A60" s="7">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -8280,23 +8474,26 @@
       <c r="P60" s="7">
         <v>6</v>
       </c>
-      <c r="Q60" s="7">
+      <c r="Q60" s="2">
+        <v>0</v>
+      </c>
+      <c r="R60" s="7">
         <v>100</v>
       </c>
-      <c r="R60" s="7">
+      <c r="S60" s="7">
         <v>30</v>
       </c>
-      <c r="S60" s="7" t="s">
+      <c r="T60" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="T60" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U60" s="7">
+      <c r="U60" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="V60" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:21" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:22" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="7">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -8346,23 +8543,26 @@
       <c r="P61" s="7">
         <v>6</v>
       </c>
-      <c r="Q61" s="7">
+      <c r="Q61" s="2">
+        <v>0</v>
+      </c>
+      <c r="R61" s="7">
         <v>100</v>
       </c>
-      <c r="R61" s="7">
+      <c r="S61" s="7">
         <v>30</v>
       </c>
-      <c r="S61" s="9" t="s">
+      <c r="T61" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="T61" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U61" s="7">
+      <c r="U61" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="V61" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A62" s="7">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -8412,23 +8612,26 @@
       <c r="P62" s="7">
         <v>7</v>
       </c>
-      <c r="Q62" s="7">
+      <c r="Q62" s="2">
+        <v>0</v>
+      </c>
+      <c r="R62" s="7">
         <v>100</v>
       </c>
-      <c r="R62" s="7">
+      <c r="S62" s="7">
         <v>30</v>
       </c>
-      <c r="S62" s="7" t="s">
+      <c r="T62" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="T62" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U62" s="7">
+      <c r="U62" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="V62" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A63" s="7">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -8478,23 +8681,26 @@
       <c r="P63" s="7">
         <v>7</v>
       </c>
-      <c r="Q63" s="7">
+      <c r="Q63" s="2">
+        <v>0</v>
+      </c>
+      <c r="R63" s="7">
         <v>100</v>
       </c>
-      <c r="R63" s="7">
+      <c r="S63" s="7">
         <v>30</v>
       </c>
-      <c r="S63" s="7" t="s">
+      <c r="T63" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="T63" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="U63" s="7">
+      <c r="U63" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="V63" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:21" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:22" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -8545,22 +8751,25 @@
         <v>8</v>
       </c>
       <c r="Q64" s="2">
+        <v>0</v>
+      </c>
+      <c r="R64" s="2">
         <v>100</v>
       </c>
-      <c r="R64" s="2">
+      <c r="S64" s="2">
         <v>120</v>
       </c>
-      <c r="S64" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="T64" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U64" s="2">
+      <c r="T64" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="U64" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V64" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:21" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:22" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -8569,13 +8778,13 @@
         <v>9005</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>274</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>275</v>
@@ -8611,22 +8820,25 @@
         <v>8</v>
       </c>
       <c r="Q65" s="2">
+        <v>1</v>
+      </c>
+      <c r="R65" s="2">
         <v>100</v>
       </c>
-      <c r="R65" s="2">
+      <c r="S65" s="2">
         <v>30</v>
       </c>
-      <c r="S65" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="T65" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U65" s="2">
+      <c r="T65" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="U65" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V65" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:21" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:22" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="6">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -8676,23 +8888,26 @@
       <c r="P66" s="6">
         <v>8</v>
       </c>
-      <c r="Q66" s="6">
+      <c r="Q66" s="2">
+        <v>0</v>
+      </c>
+      <c r="R66" s="6">
         <v>100</v>
       </c>
-      <c r="R66" s="6">
+      <c r="S66" s="6">
         <v>30</v>
       </c>
-      <c r="S66" s="8" t="s">
+      <c r="T66" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="T66" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U66" s="6">
+      <c r="U66" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V66" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:21" s="6" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:22" s="6" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="6">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -8742,23 +8957,26 @@
       <c r="P67" s="6">
         <v>8</v>
       </c>
-      <c r="Q67" s="6">
+      <c r="Q67" s="2">
+        <v>0</v>
+      </c>
+      <c r="R67" s="6">
         <v>100</v>
       </c>
-      <c r="R67" s="6">
+      <c r="S67" s="6">
         <v>60</v>
       </c>
-      <c r="S67" s="8" t="s">
+      <c r="T67" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="T67" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="U67" s="6">
+      <c r="U67" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="V67" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:21" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:22" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -8767,7 +8985,7 @@
         <v>9003</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>108</v>
@@ -8809,18 +9027,21 @@
         <v>8</v>
       </c>
       <c r="Q68" s="2">
+        <v>0</v>
+      </c>
+      <c r="R68" s="2">
         <v>100</v>
       </c>
-      <c r="R68" s="2">
+      <c r="S68" s="2">
         <v>30</v>
       </c>
-      <c r="S68" s="3" t="s">
+      <c r="T68" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="T68" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="U68" s="2">
+      <c r="U68" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V68" s="2">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDA8D4E-B45F-42AA-922C-85FC2BC02A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F072FE6D-2E09-4D76-90EA-6EA254880953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2235" yWindow="1305" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1462,22 +1462,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>風の力で、柔らかいクッキーをくるくる巻く</t>
-    <rPh sb="0" eb="1">
-      <t>カゼ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>チカラ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ヤワ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>マ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Wind_Roll</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1670,47 +1654,6 @@
     </rPh>
     <rPh sb="45" eb="46">
       <t>フ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>風の力で、液体チョコレートを操り、ペンのように模様を描けるようになる。
-液体チョコレートにかけると、チョコのペンが出来上がる。
-◆ブラックチョコペン→クッキーに模様が描ける。
-◆ホワイトチョコペン→チョコレートに文字が描ける。
-お誕生日メッセージなど。</t>
-    <rPh sb="5" eb="7">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>アヤツ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>モヨウ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>エガ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="58" eb="61">
-      <t>デキア</t>
-    </rPh>
-    <rPh sb="82" eb="84">
-      <t>モヨウ</t>
-    </rPh>
-    <rPh sb="85" eb="86">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="108" eb="110">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="111" eb="112">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="117" eb="120">
-      <t>タンジョウビ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1867,33 +1810,6 @@
     </rPh>
     <rPh sb="113" eb="115">
       <t>コテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>風の力で、柔らかいクッキーをくるくる巻く。
-柔らかいクッキーは、焼きたてのラングドシャクッキーのこと。
-巻いたクッキーは、お城のケーキなどを作る際の、部品となる。</t>
-    <rPh sb="22" eb="23">
-      <t>ヤワ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="71" eb="72">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="73" eb="74">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>ブヒン</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3905,6 +3821,69 @@
   </si>
   <si>
     <t>skill_enshututype</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風の力で、クッキーをくるくる巻く</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>マ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風の力で、柔らかいクッキーをくるくる巻く。
+柔らかいクッキーとは、焼きたてのラングドシャクッキーのこと。
+巻いたクッキーは、お城のケーキなどを作る際の、部品となる。</t>
+    <rPh sb="22" eb="23">
+      <t>ヤワ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>ブヒン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風の力で、液体チョコレートを操り、ペンのようにクッキーに模様を描けるようになる。
+液体チョコレートにかけることで、チョコのペンが出来上がる。</t>
+    <rPh sb="5" eb="7">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>アヤツ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>モヨウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>エガ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="65" eb="68">
+      <t>デキア</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4395,7 +4374,7 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -4404,7 +4383,7 @@
         <v>9</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>10</v>
@@ -4551,7 +4530,7 @@
         <v>30</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>94</v>
@@ -4638,7 +4617,7 @@
         <v>1010</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>164</v>
@@ -4689,7 +4668,7 @@
         <v>30</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="U5" s="2" t="s">
         <v>94</v>
@@ -4707,7 +4686,7 @@
         <v>1009</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>112</v>
@@ -4716,7 +4695,7 @@
         <v>133</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G6" s="2">
         <v>6</v>
@@ -4758,7 +4737,7 @@
         <v>30</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="U6" s="2" t="s">
         <v>94</v>
@@ -4776,7 +4755,7 @@
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>58</v>
@@ -4878,7 +4857,7 @@
         <v>94</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O8" s="2">
         <v>1</v>
@@ -4896,7 +4875,7 @@
         <v>30</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>164</v>
@@ -4914,7 +4893,7 @@
         <v>1008</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>82</v>
@@ -4965,7 +4944,7 @@
         <v>30</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>80</v>
@@ -4983,16 +4962,16 @@
         <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G10" s="2">
         <v>6</v>
@@ -5034,7 +5013,7 @@
         <v>30</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>58</v>
@@ -5103,7 +5082,7 @@
         <v>30</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>94</v>
@@ -5127,7 +5106,7 @@
         <v>81</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>105</v>
@@ -5193,13 +5172,13 @@
         <v>64</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G13" s="6">
         <v>6</v>
@@ -5241,7 +5220,7 @@
         <v>30</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="U13" s="6" t="s">
         <v>94</v>
@@ -5259,7 +5238,7 @@
         <v>2004</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>110</v>
@@ -5310,7 +5289,7 @@
         <v>30</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="U14" s="2" t="s">
         <v>94</v>
@@ -5379,7 +5358,7 @@
         <v>120</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="U15" s="2" t="s">
         <v>94</v>
@@ -5397,16 +5376,16 @@
         <v>2001</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>177</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G16" s="2">
         <v>2</v>
@@ -5448,7 +5427,7 @@
         <v>120</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="U16" s="2" t="s">
         <v>51</v>
@@ -5535,16 +5514,16 @@
         <v>2005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G18" s="2">
         <v>2</v>
@@ -5586,7 +5565,7 @@
         <v>30</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="U18" s="2" t="s">
         <v>51</v>
@@ -5604,7 +5583,7 @@
         <v>2003</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>118</v>
@@ -5676,13 +5655,13 @@
         <v>35</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G20" s="6">
         <v>2</v>
@@ -5724,7 +5703,7 @@
         <v>30</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="U20" s="6" t="s">
         <v>94</v>
@@ -5751,7 +5730,7 @@
         <v>157</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G21" s="2">
         <v>2</v>
@@ -5793,7 +5772,7 @@
         <v>30</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="U21" s="2" t="s">
         <v>94</v>
@@ -5817,7 +5796,7 @@
         <v>16</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>15</v>
@@ -5844,7 +5823,7 @@
         <v>94</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O22" s="2">
         <v>1</v>
@@ -5862,7 +5841,7 @@
         <v>30</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="U22" s="2" t="s">
         <v>94</v>
@@ -5913,7 +5892,7 @@
         <v>94</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O23" s="2">
         <v>1</v>
@@ -5931,7 +5910,7 @@
         <v>30</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="U23" s="2" t="s">
         <v>16</v>
@@ -5949,13 +5928,13 @@
         <v>3003</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>106</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>72</v>
@@ -6000,7 +5979,7 @@
         <v>30</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="U24" s="2" t="s">
         <v>20</v>
@@ -6018,16 +5997,16 @@
         <v>3008</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G25" s="2">
         <v>4</v>
@@ -6069,7 +6048,7 @@
         <v>30</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="U25" s="2" t="s">
         <v>94</v>
@@ -6087,7 +6066,7 @@
         <v>3004</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>115</v>
@@ -6138,7 +6117,7 @@
         <v>30</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="U26" s="2" t="s">
         <v>94</v>
@@ -6156,16 +6135,16 @@
         <v>3007</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G27" s="2">
         <v>4</v>
@@ -6207,7 +6186,7 @@
         <v>30</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="U27" s="2" t="s">
         <v>94</v>
@@ -6297,13 +6276,13 @@
         <v>36</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G29" s="6">
         <v>4</v>
@@ -6345,7 +6324,7 @@
         <v>30</v>
       </c>
       <c r="T29" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="U29" s="6" t="s">
         <v>94</v>
@@ -6363,7 +6342,7 @@
         <v>4010</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>152</v>
@@ -6414,7 +6393,7 @@
         <v>30</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="U30" s="2" t="s">
         <v>94</v>
@@ -6432,13 +6411,13 @@
         <v>4011</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>156</v>
@@ -6483,7 +6462,7 @@
         <v>30</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="U31" s="2" t="s">
         <v>94</v>
@@ -6501,7 +6480,7 @@
         <v>4001</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>23</v>
@@ -6510,7 +6489,7 @@
         <v>21</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G32" s="2">
         <v>6</v>
@@ -6531,10 +6510,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O32" s="2">
         <v>1</v>
@@ -6552,7 +6531,7 @@
         <v>30</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="U32" s="2" t="s">
         <v>155</v>
@@ -6570,7 +6549,7 @@
         <v>4002</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>25</v>
@@ -6579,7 +6558,7 @@
         <v>22</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -6603,7 +6582,7 @@
         <v>94</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O33" s="2">
         <v>1</v>
@@ -6621,7 +6600,7 @@
         <v>30</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>94</v>
@@ -6639,7 +6618,7 @@
         <v>4010</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>128</v>
@@ -6648,7 +6627,7 @@
         <v>129</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -6672,7 +6651,7 @@
         <v>94</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O34" s="2">
         <v>1</v>
@@ -6690,7 +6669,7 @@
         <v>30</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="U34" s="2" t="s">
         <v>23</v>
@@ -6708,7 +6687,7 @@
         <v>4011</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>173</v>
@@ -6717,7 +6696,7 @@
         <v>172</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -6741,7 +6720,7 @@
         <v>94</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O35" s="2">
         <v>1</v>
@@ -6759,7 +6738,7 @@
         <v>30</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="U35" s="2" t="s">
         <v>23</v>
@@ -6777,7 +6756,7 @@
         <v>4012</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>175</v>
@@ -6786,7 +6765,7 @@
         <v>174</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -6810,7 +6789,7 @@
         <v>94</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O36" s="2">
         <v>1</v>
@@ -6828,7 +6807,7 @@
         <v>30</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="U36" s="2" t="s">
         <v>23</v>
@@ -6846,16 +6825,16 @@
         <v>4012</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>178</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>179</v>
+        <v>332</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -6864,7 +6843,7 @@
         <v>4</v>
       </c>
       <c r="I37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2">
         <v>0</v>
@@ -6879,7 +6858,7 @@
         <v>94</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O37" s="2">
         <v>1</v>
@@ -6897,7 +6876,7 @@
         <v>30</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>201</v>
+        <v>333</v>
       </c>
       <c r="U37" s="2" t="s">
         <v>23</v>
@@ -6915,16 +6894,16 @@
         <v>4012</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -6933,7 +6912,7 @@
         <v>4</v>
       </c>
       <c r="I38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2">
         <v>0</v>
@@ -6948,7 +6927,7 @@
         <v>94</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O38" s="2">
         <v>1</v>
@@ -6966,7 +6945,7 @@
         <v>30</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>195</v>
+        <v>334</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>23</v>
@@ -7053,16 +7032,16 @@
         <v>4004</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G40" s="2">
         <v>3</v>
@@ -7104,7 +7083,7 @@
         <v>30</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="U40" s="2" t="s">
         <v>23</v>
@@ -7200,7 +7179,7 @@
         <v>176</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G42" s="6">
         <v>3</v>
@@ -7224,7 +7203,7 @@
         <v>94</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O42" s="6">
         <v>1</v>
@@ -7242,7 +7221,7 @@
         <v>30</v>
       </c>
       <c r="T42" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="U42" s="6" t="s">
         <v>94</v>
@@ -7260,7 +7239,7 @@
         <v>4007</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>85</v>
@@ -7269,7 +7248,7 @@
         <v>87</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G43" s="2">
         <v>3</v>
@@ -7293,7 +7272,7 @@
         <v>94</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O43" s="2">
         <v>1</v>
@@ -7311,7 +7290,7 @@
         <v>30</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="U43" s="2" t="s">
         <v>155</v>
@@ -7332,13 +7311,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G44" s="6">
         <v>3</v>
@@ -7362,7 +7341,7 @@
         <v>94</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O44" s="6">
         <v>1</v>
@@ -7380,7 +7359,7 @@
         <v>30</v>
       </c>
       <c r="T44" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="U44" s="6" t="s">
         <v>94</v>
@@ -7407,7 +7386,7 @@
         <v>88</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G45" s="6">
         <v>3</v>
@@ -7431,7 +7410,7 @@
         <v>94</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O45" s="6">
         <v>1</v>
@@ -7449,7 +7428,7 @@
         <v>30</v>
       </c>
       <c r="T45" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="U45" s="6" t="s">
         <v>94</v>
@@ -7476,7 +7455,7 @@
         <v>102</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G46" s="6">
         <v>3</v>
@@ -7518,7 +7497,7 @@
         <v>30</v>
       </c>
       <c r="T46" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="U46" s="6" t="s">
         <v>94</v>
@@ -7542,7 +7521,7 @@
         <v>163</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>161</v>
@@ -7614,7 +7593,7 @@
         <v>159</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G48" s="6">
         <v>6</v>
@@ -7656,7 +7635,7 @@
         <v>30</v>
       </c>
       <c r="T48" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="U48" s="6" t="s">
         <v>94</v>
@@ -7674,16 +7653,16 @@
         <v>5007</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G49" s="2">
         <v>6</v>
@@ -7725,7 +7704,7 @@
         <v>30</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="U49" s="2" t="s">
         <v>94</v>
@@ -7743,7 +7722,7 @@
         <v>5001</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>39</v>
@@ -7794,10 +7773,10 @@
         <v>30</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V50" s="2">
         <v>1</v>
@@ -7812,7 +7791,7 @@
         <v>5002</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>121</v>
@@ -7863,7 +7842,7 @@
         <v>30</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="U51" s="2" t="s">
         <v>39</v>
@@ -7881,13 +7860,13 @@
         <v>5003</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>139</v>
@@ -7932,7 +7911,7 @@
         <v>480</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="U52" s="2" t="s">
         <v>94</v>
@@ -7950,16 +7929,16 @@
         <v>5005</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G53" s="2">
         <v>6</v>
@@ -7980,7 +7959,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>94</v>
@@ -8001,10 +7980,10 @@
         <v>30</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="U53" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="V53" s="2">
         <v>1</v>
@@ -8019,16 +7998,16 @@
         <v>5006</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G54" s="2">
         <v>6</v>
@@ -8052,7 +8031,7 @@
         <v>94</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O54" s="2">
         <v>1</v>
@@ -8070,7 +8049,7 @@
         <v>30</v>
       </c>
       <c r="T54" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="U54" s="2" t="s">
         <v>94</v>
@@ -8157,7 +8136,7 @@
         <v>6002</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>101</v>
@@ -8208,7 +8187,7 @@
         <v>30</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="U56" s="2" t="s">
         <v>94</v>
@@ -8226,16 +8205,16 @@
         <v>6004</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G57" s="2">
         <v>6</v>
@@ -8277,7 +8256,7 @@
         <v>30</v>
       </c>
       <c r="T57" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="U57" s="2" t="s">
         <v>94</v>
@@ -8295,16 +8274,16 @@
         <v>6005</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G58" s="2">
         <v>6</v>
@@ -8346,7 +8325,7 @@
         <v>30</v>
       </c>
       <c r="T58" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="U58" s="2" t="s">
         <v>94</v>
@@ -8553,7 +8532,7 @@
         <v>30</v>
       </c>
       <c r="T61" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="U61" s="7" t="s">
         <v>94</v>
@@ -8760,7 +8739,7 @@
         <v>120</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="U64" s="2" t="s">
         <v>94</v>
@@ -8778,16 +8757,16 @@
         <v>9005</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G65" s="2">
         <v>2</v>
@@ -8796,7 +8775,7 @@
         <v>4</v>
       </c>
       <c r="I65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="2">
         <v>0</v>
@@ -8829,7 +8808,7 @@
         <v>30</v>
       </c>
       <c r="T65" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="U65" s="2" t="s">
         <v>94</v>
@@ -8898,7 +8877,7 @@
         <v>30</v>
       </c>
       <c r="T66" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="U66" s="6" t="s">
         <v>94</v>
@@ -8946,7 +8925,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="N67" s="6" t="s">
         <v>94</v>
@@ -8967,7 +8946,7 @@
         <v>60</v>
       </c>
       <c r="T67" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="U67" s="6" t="s">
         <v>94</v>
@@ -8985,7 +8964,7 @@
         <v>9003</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>108</v>
@@ -9036,7 +9015,7 @@
         <v>30</v>
       </c>
       <c r="T68" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="U68" s="2" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F072FE6D-2E09-4D76-90EA-6EA254880953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A01A5F-08F0-4E1E-8F9E-F815BD568383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2235" yWindow="1305" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2625" yWindow="1245" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A01A5F-08F0-4E1E-8F9E-F815BD568383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718B7890-D311-464F-B122-D242D92774C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2625" yWindow="1245" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5916,7 +5916,7 @@
         <v>16</v>
       </c>
       <c r="V23" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718B7890-D311-464F-B122-D242D92774C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF1B911-2DFC-4BF7-BACD-2C35394B1054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
@@ -1286,66 +1286,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>様々な液体を固めて、
-不思議なシュガーを作り出す。
-ラベンダーポーション　→　ラベンダーシュガー
-砂糖水からは、氷砂糖
-ミルクは、ミルキーシュガー（真っ白で牛乳風味のお砂糖）
-などなど..。
-LVに応じて成功率が上がる。
-LV1: +5%成功Up
-LV2: +10%成功Up
-LV3: +15%成功Up
-LV4: +20%成功Up
-LV5: +25%成功Up</t>
-    <rPh sb="0" eb="2">
-      <t>サマザマ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>フシギ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="50" eb="53">
-      <t>サトウミズ</t>
-    </rPh>
-    <rPh sb="57" eb="60">
-      <t>コオリザトウ</t>
-    </rPh>
-    <rPh sb="75" eb="76">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="77" eb="78">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="79" eb="83">
-      <t>ギュウニュウフウミ</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="102" eb="103">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="105" eb="108">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="109" eb="110">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>プランターに種を植えることができるようになる。</t>
     <rPh sb="6" eb="7">
       <t>タネ</t>
@@ -2540,55 +2480,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>草花のエキスを抽出し、ポーションを作る
-レベルが上がると成功率が上がるほか、一度にできあがる個数も増える。
-LV1: +3%成功Up, 個数1個
-LV2: +6%成功Up , 個数2個
-LV3: +9%成功Up , 個数3個
-LV4: +12%成功Up , 個数4個
-LV5: +15%成功Up , 個数5個</t>
-    <rPh sb="0" eb="2">
-      <t>クサバナ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>チュウシュツ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="29" eb="32">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>コスウ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>コスウ</t>
-    </rPh>
-    <rPh sb="73" eb="74">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="90" eb="92">
-      <t>コスウ</t>
-    </rPh>
-    <rPh sb="93" eb="94">
-      <t>コ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>あわあわ・デコレーション</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3883,6 +3774,145 @@
     </rPh>
     <rPh sb="65" eb="68">
       <t>デキア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>草花のエキスを抽出し、ポーションを作る
+入れた材料は、そのまま1個分に凝縮される。
+ただし、
+レベルが上がると成功率が上がるほか、一度にできあがる個数は増えていく。
+LV1: +3%成功Up, 個数1個
+LV2: +6%成功Up , 個数2個
+LV3: +9%成功Up , 個数3個
+LV4: +12%成功Up , 個数4個
+LV5: +15%成功Up , 個数5個</t>
+    <rPh sb="0" eb="2">
+      <t>クサバナ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>チュウシュツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ギョウシュク</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="57" eb="60">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="100" eb="102">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="103" eb="104">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>様々な液体を固めて、
+不思議なシュガーを作り出す。
+ラベンダーポーション　→　ラベンダーシュガー
+砂糖水からは、氷砂糖
+ミルクは、ミルキーシュガー（真っ白で牛乳風味のお砂糖）
+などなど..。
+入れた材料の数だけ、シュガーが作られる。
+LVに応じて成功率が上がる。
+LV1: +5%成功Up
+LV2: +10%成功Up
+LV3: +15%成功Up
+LV4: +20%成功Up
+LV5: +25%成功Up</t>
+    <rPh sb="0" eb="2">
+      <t>サマザマ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エキタイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>フシギ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="50" eb="53">
+      <t>サトウミズ</t>
+    </rPh>
+    <rPh sb="57" eb="60">
+      <t>コオリザトウ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="79" eb="83">
+      <t>ギュウニュウフウミ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="102" eb="104">
+      <t>ザイリョウ</t>
+    </rPh>
+    <rPh sb="105" eb="106">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="114" eb="115">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="124" eb="125">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="127" eb="130">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="131" eb="132">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4374,7 +4404,7 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -4383,7 +4413,7 @@
         <v>9</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>10</v>
@@ -4530,7 +4560,7 @@
         <v>30</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>94</v>
@@ -4617,13 +4647,13 @@
         <v>1010</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>164</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>150</v>
@@ -4668,7 +4698,7 @@
         <v>30</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="U5" s="2" t="s">
         <v>94</v>
@@ -4686,7 +4716,7 @@
         <v>1009</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>112</v>
@@ -4695,7 +4725,7 @@
         <v>133</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G6" s="2">
         <v>6</v>
@@ -4737,7 +4767,7 @@
         <v>30</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="U6" s="2" t="s">
         <v>94</v>
@@ -4755,7 +4785,7 @@
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>58</v>
@@ -4857,7 +4887,7 @@
         <v>94</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O8" s="2">
         <v>1</v>
@@ -4875,7 +4905,7 @@
         <v>30</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>164</v>
@@ -4893,13 +4923,13 @@
         <v>1008</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>104</v>
@@ -4944,7 +4974,7 @@
         <v>30</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>80</v>
@@ -4962,16 +4992,16 @@
         <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>230</v>
       </c>
       <c r="G10" s="2">
         <v>6</v>
@@ -5013,7 +5043,7 @@
         <v>30</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>58</v>
@@ -5082,7 +5112,7 @@
         <v>30</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>94</v>
@@ -5106,7 +5136,7 @@
         <v>81</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>105</v>
@@ -5172,13 +5202,13 @@
         <v>64</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G13" s="6">
         <v>6</v>
@@ -5220,7 +5250,7 @@
         <v>30</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U13" s="6" t="s">
         <v>94</v>
@@ -5238,7 +5268,7 @@
         <v>2004</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>110</v>
@@ -5289,7 +5319,7 @@
         <v>30</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="U14" s="2" t="s">
         <v>94</v>
@@ -5358,7 +5388,7 @@
         <v>120</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="U15" s="2" t="s">
         <v>94</v>
@@ -5376,16 +5406,16 @@
         <v>2001</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G16" s="2">
         <v>2</v>
@@ -5427,7 +5457,7 @@
         <v>120</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="U16" s="2" t="s">
         <v>51</v>
@@ -5451,7 +5481,7 @@
         <v>90</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>89</v>
@@ -5514,16 +5544,16 @@
         <v>2005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G18" s="2">
         <v>2</v>
@@ -5565,7 +5595,7 @@
         <v>30</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="U18" s="2" t="s">
         <v>51</v>
@@ -5583,7 +5613,7 @@
         <v>2003</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>118</v>
@@ -5616,7 +5646,7 @@
         <v>94</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>94</v>
+        <v>247</v>
       </c>
       <c r="O19" s="2">
         <v>1</v>
@@ -5634,7 +5664,7 @@
         <v>30</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>166</v>
+        <v>334</v>
       </c>
       <c r="U19" s="2" t="s">
         <v>101</v>
@@ -5655,13 +5685,13 @@
         <v>35</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G20" s="6">
         <v>2</v>
@@ -5703,7 +5733,7 @@
         <v>30</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="U20" s="6" t="s">
         <v>94</v>
@@ -5730,7 +5760,7 @@
         <v>157</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G21" s="2">
         <v>2</v>
@@ -5772,7 +5802,7 @@
         <v>30</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="U21" s="2" t="s">
         <v>94</v>
@@ -5796,7 +5826,7 @@
         <v>16</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>15</v>
@@ -5823,7 +5853,7 @@
         <v>94</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O22" s="2">
         <v>1</v>
@@ -5841,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="U22" s="2" t="s">
         <v>94</v>
@@ -5892,7 +5922,7 @@
         <v>94</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O23" s="2">
         <v>1</v>
@@ -5910,7 +5940,7 @@
         <v>30</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U23" s="2" t="s">
         <v>16</v>
@@ -5928,13 +5958,13 @@
         <v>3003</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>106</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>72</v>
@@ -5979,7 +6009,7 @@
         <v>30</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="U24" s="2" t="s">
         <v>20</v>
@@ -5997,16 +6027,16 @@
         <v>3008</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="G25" s="2">
         <v>4</v>
@@ -6048,7 +6078,7 @@
         <v>30</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="U25" s="2" t="s">
         <v>94</v>
@@ -6066,7 +6096,7 @@
         <v>3004</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>115</v>
@@ -6117,7 +6147,7 @@
         <v>30</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="U26" s="2" t="s">
         <v>94</v>
@@ -6135,16 +6165,16 @@
         <v>3007</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G27" s="2">
         <v>4</v>
@@ -6186,7 +6216,7 @@
         <v>30</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="U27" s="2" t="s">
         <v>94</v>
@@ -6276,13 +6306,13 @@
         <v>36</v>
       </c>
       <c r="D29" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>215</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="G29" s="6">
         <v>4</v>
@@ -6324,7 +6354,7 @@
         <v>30</v>
       </c>
       <c r="T29" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="U29" s="6" t="s">
         <v>94</v>
@@ -6342,7 +6372,7 @@
         <v>4010</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>152</v>
@@ -6393,7 +6423,7 @@
         <v>30</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="U30" s="2" t="s">
         <v>94</v>
@@ -6411,13 +6441,13 @@
         <v>4011</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>156</v>
@@ -6462,7 +6492,7 @@
         <v>30</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="U31" s="2" t="s">
         <v>94</v>
@@ -6480,7 +6510,7 @@
         <v>4001</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>23</v>
@@ -6489,7 +6519,7 @@
         <v>21</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G32" s="2">
         <v>6</v>
@@ -6510,10 +6540,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O32" s="2">
         <v>1</v>
@@ -6531,7 +6561,7 @@
         <v>30</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="U32" s="2" t="s">
         <v>155</v>
@@ -6549,7 +6579,7 @@
         <v>4002</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>25</v>
@@ -6558,7 +6588,7 @@
         <v>22</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -6582,7 +6612,7 @@
         <v>94</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O33" s="2">
         <v>1</v>
@@ -6600,7 +6630,7 @@
         <v>30</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>94</v>
@@ -6618,7 +6648,7 @@
         <v>4010</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>128</v>
@@ -6627,7 +6657,7 @@
         <v>129</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -6651,7 +6681,7 @@
         <v>94</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O34" s="2">
         <v>1</v>
@@ -6669,7 +6699,7 @@
         <v>30</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="U34" s="2" t="s">
         <v>23</v>
@@ -6687,16 +6717,16 @@
         <v>4011</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -6720,7 +6750,7 @@
         <v>94</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O35" s="2">
         <v>1</v>
@@ -6738,7 +6768,7 @@
         <v>30</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="U35" s="2" t="s">
         <v>23</v>
@@ -6756,16 +6786,16 @@
         <v>4012</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -6789,7 +6819,7 @@
         <v>94</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O36" s="2">
         <v>1</v>
@@ -6807,7 +6837,7 @@
         <v>30</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U36" s="2" t="s">
         <v>23</v>
@@ -6825,16 +6855,16 @@
         <v>4012</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -6858,7 +6888,7 @@
         <v>94</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O37" s="2">
         <v>1</v>
@@ -6876,7 +6906,7 @@
         <v>30</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="U37" s="2" t="s">
         <v>23</v>
@@ -6894,16 +6924,16 @@
         <v>4012</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="G38" s="2">
         <v>1</v>
@@ -6927,7 +6957,7 @@
         <v>94</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O38" s="2">
         <v>1</v>
@@ -6945,7 +6975,7 @@
         <v>30</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>23</v>
@@ -7032,16 +7062,16 @@
         <v>4004</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G40" s="2">
         <v>3</v>
@@ -7083,7 +7113,7 @@
         <v>30</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="U40" s="2" t="s">
         <v>23</v>
@@ -7152,7 +7182,7 @@
         <v>30</v>
       </c>
       <c r="T41" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="U41" s="6" t="s">
         <v>94</v>
@@ -7176,10 +7206,10 @@
         <v>70</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G42" s="6">
         <v>3</v>
@@ -7203,7 +7233,7 @@
         <v>94</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O42" s="6">
         <v>1</v>
@@ -7221,7 +7251,7 @@
         <v>30</v>
       </c>
       <c r="T42" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="U42" s="6" t="s">
         <v>94</v>
@@ -7239,7 +7269,7 @@
         <v>4007</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>85</v>
@@ -7248,7 +7278,7 @@
         <v>87</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G43" s="2">
         <v>3</v>
@@ -7272,7 +7302,7 @@
         <v>94</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O43" s="2">
         <v>1</v>
@@ -7290,7 +7320,7 @@
         <v>30</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="U43" s="2" t="s">
         <v>155</v>
@@ -7311,13 +7341,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>200</v>
-      </c>
       <c r="F44" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G44" s="6">
         <v>3</v>
@@ -7341,7 +7371,7 @@
         <v>94</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O44" s="6">
         <v>1</v>
@@ -7359,7 +7389,7 @@
         <v>30</v>
       </c>
       <c r="T44" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="U44" s="6" t="s">
         <v>94</v>
@@ -7386,7 +7416,7 @@
         <v>88</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G45" s="6">
         <v>3</v>
@@ -7410,7 +7440,7 @@
         <v>94</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O45" s="6">
         <v>1</v>
@@ -7428,7 +7458,7 @@
         <v>30</v>
       </c>
       <c r="T45" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="U45" s="6" t="s">
         <v>94</v>
@@ -7455,7 +7485,7 @@
         <v>102</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G46" s="6">
         <v>3</v>
@@ -7497,7 +7527,7 @@
         <v>30</v>
       </c>
       <c r="T46" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="U46" s="6" t="s">
         <v>94</v>
@@ -7521,7 +7551,7 @@
         <v>163</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>161</v>
@@ -7593,7 +7623,7 @@
         <v>159</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G48" s="6">
         <v>6</v>
@@ -7635,7 +7665,7 @@
         <v>30</v>
       </c>
       <c r="T48" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U48" s="6" t="s">
         <v>94</v>
@@ -7653,16 +7683,16 @@
         <v>5007</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G49" s="2">
         <v>6</v>
@@ -7704,7 +7734,7 @@
         <v>30</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="U49" s="2" t="s">
         <v>94</v>
@@ -7722,7 +7752,7 @@
         <v>5001</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>39</v>
@@ -7773,10 +7803,10 @@
         <v>30</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="V50" s="2">
         <v>1</v>
@@ -7791,7 +7821,7 @@
         <v>5002</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>121</v>
@@ -7842,7 +7872,7 @@
         <v>30</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="U51" s="2" t="s">
         <v>39</v>
@@ -7860,13 +7890,13 @@
         <v>5003</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>139</v>
@@ -7911,7 +7941,7 @@
         <v>480</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="U52" s="2" t="s">
         <v>94</v>
@@ -7929,16 +7959,16 @@
         <v>5005</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G53" s="2">
         <v>6</v>
@@ -7959,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>94</v>
@@ -7980,10 +8010,10 @@
         <v>30</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="U53" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="V53" s="2">
         <v>1</v>
@@ -7998,16 +8028,16 @@
         <v>5006</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G54" s="2">
         <v>6</v>
@@ -8031,7 +8061,7 @@
         <v>94</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O54" s="2">
         <v>1</v>
@@ -8049,7 +8079,7 @@
         <v>30</v>
       </c>
       <c r="T54" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="U54" s="2" t="s">
         <v>94</v>
@@ -8136,7 +8166,7 @@
         <v>6002</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>101</v>
@@ -8187,7 +8217,7 @@
         <v>30</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>240</v>
+        <v>333</v>
       </c>
       <c r="U56" s="2" t="s">
         <v>94</v>
@@ -8205,16 +8235,16 @@
         <v>6004</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="G57" s="2">
         <v>6</v>
@@ -8256,7 +8286,7 @@
         <v>30</v>
       </c>
       <c r="T57" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="U57" s="2" t="s">
         <v>94</v>
@@ -8274,16 +8304,16 @@
         <v>6005</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="G58" s="2">
         <v>6</v>
@@ -8325,7 +8355,7 @@
         <v>30</v>
       </c>
       <c r="T58" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="U58" s="2" t="s">
         <v>94</v>
@@ -8394,7 +8424,7 @@
         <v>30</v>
       </c>
       <c r="T59" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="U59" s="6" t="s">
         <v>94</v>
@@ -8532,7 +8562,7 @@
         <v>30</v>
       </c>
       <c r="T61" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="U61" s="7" t="s">
         <v>94</v>
@@ -8739,7 +8769,7 @@
         <v>120</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="U64" s="2" t="s">
         <v>94</v>
@@ -8757,16 +8787,16 @@
         <v>9005</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G65" s="2">
         <v>2</v>
@@ -8808,7 +8838,7 @@
         <v>30</v>
       </c>
       <c r="T65" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="U65" s="2" t="s">
         <v>94</v>
@@ -8877,7 +8907,7 @@
         <v>30</v>
       </c>
       <c r="T66" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="U66" s="6" t="s">
         <v>94</v>
@@ -8925,7 +8955,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N67" s="6" t="s">
         <v>94</v>
@@ -8946,7 +8976,7 @@
         <v>60</v>
       </c>
       <c r="T67" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U67" s="6" t="s">
         <v>94</v>
@@ -8964,7 +8994,7 @@
         <v>9003</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>108</v>
@@ -9015,7 +9045,7 @@
         <v>30</v>
       </c>
       <c r="T68" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="U68" s="2" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF1B911-2DFC-4BF7-BACD-2C35394B1054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B1325D-83C2-4744-909C-1337B3F5536C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3180" yWindow="1110" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4770,10 +4770,10 @@
         <v>240</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="V6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:22" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B1325D-83C2-4744-909C-1337B3F5536C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A176A7-3325-46FB-808F-F39B5E9BE181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1110" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1935" yWindow="1095" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2679,32 +2679,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>生地をきれいに混ぜる技術を磨く。
-クレープ生地やケーキ生地など生地系の品質を、少しだけ底上げする。</t>
-    <rPh sb="22" eb="24">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ヒンシツ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ソコア</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>skill_KosuSelect</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3269,60 +3243,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ケーキの見た目をきれいに仕上げる。
-クリームをきれいにぬる技術のこと。
-クリームを塗る工程の際に、成功率を少し上げる。
-LVがあがると、きれいにクリームを塗れて、見た目がよくなる。
-LV1: ふわふわ+15, 成功率+3%
-LV2: ふわふわ+30, 成功率+6%
-LV3: ふわふわ+45, 成功率+9%
-LV4: ふわふわ+60, 成功率+12%
-LV5: ふわふわ+75, 成功率+15%</t>
-    <rPh sb="4" eb="5">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ギジュツ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>コウテイ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="49" eb="52">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="78" eb="79">
-      <t>ヌ</t>
-    </rPh>
-    <rPh sb="82" eb="83">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="84" eb="85">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="107" eb="110">
-      <t>セイコウリツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>レアもの発見+1</t>
     <rPh sb="4" eb="6">
       <t>ハッケン</t>
@@ -3913,6 +3833,106 @@
     </rPh>
     <rPh sb="131" eb="132">
       <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生地をきれいに混ぜる技術を磨く。
+クレープ生地やケーキ生地など生地系の品質を、少しだけ底上げする。
+LV3以上だと、出来上がる生地の個数が+1。
+LV5で+2。</t>
+    <rPh sb="22" eb="24">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ソコア</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="60" eb="63">
+      <t>デキア</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>コスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ケーキの見た目をきれいに仕上げる。
+クリームをきれいにぬる技術のこと。
+クリームを塗る工程の際に、成功率を少し上げる。
+LVがあがると、きれいにクリームを塗れて、見た目がよくなる。
+LV1: ふわふわ+15, 成功率+3%
+LV2: ふわふわ+30, 成功率+6%
+LV3: ふわふわ+45, 成功率+9%, クリーム生地個数+1
+LV4: ふわふわ+60, 成功率+12%, クリーム生地個数+1
+LV5: ふわふわ+75, 成功率+15%, クリーム生地個数+2</t>
+    <rPh sb="4" eb="5">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>コウテイ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="49" eb="52">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ヌ</t>
+    </rPh>
+    <rPh sb="82" eb="83">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="107" eb="110">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="161" eb="163">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="163" eb="165">
+      <t>コスウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4404,7 +4424,7 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -4413,7 +4433,7 @@
         <v>9</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>10</v>
@@ -4647,7 +4667,7 @@
         <v>1010</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>164</v>
@@ -4698,7 +4718,7 @@
         <v>30</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U5" s="2" t="s">
         <v>94</v>
@@ -4716,7 +4736,7 @@
         <v>1009</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>112</v>
@@ -4785,7 +4805,7 @@
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>58</v>
@@ -4887,7 +4907,7 @@
         <v>94</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O8" s="2">
         <v>1</v>
@@ -4905,7 +4925,7 @@
         <v>30</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>164</v>
@@ -4923,7 +4943,7 @@
         <v>1008</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>82</v>
@@ -4974,7 +4994,7 @@
         <v>30</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>80</v>
@@ -4992,7 +5012,7 @@
         <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>227</v>
@@ -5043,7 +5063,7 @@
         <v>30</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>58</v>
@@ -5268,7 +5288,7 @@
         <v>2004</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>110</v>
@@ -5319,7 +5339,7 @@
         <v>30</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="U14" s="2" t="s">
         <v>94</v>
@@ -5406,7 +5426,7 @@
         <v>2001</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>176</v>
@@ -5544,16 +5564,16 @@
         <v>2005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="G18" s="2">
         <v>2</v>
@@ -5595,7 +5615,7 @@
         <v>30</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="U18" s="2" t="s">
         <v>51</v>
@@ -5613,7 +5633,7 @@
         <v>2003</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>118</v>
@@ -5646,7 +5666,7 @@
         <v>94</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O19" s="2">
         <v>1</v>
@@ -5664,7 +5684,7 @@
         <v>30</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="U19" s="2" t="s">
         <v>101</v>
@@ -5853,7 +5873,7 @@
         <v>94</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O22" s="2">
         <v>1</v>
@@ -5922,7 +5942,7 @@
         <v>94</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O23" s="2">
         <v>1</v>
@@ -5958,7 +5978,7 @@
         <v>3003</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>106</v>
@@ -6027,16 +6047,16 @@
         <v>3008</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="G25" s="2">
         <v>4</v>
@@ -6078,7 +6098,7 @@
         <v>30</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="U25" s="2" t="s">
         <v>94</v>
@@ -6096,7 +6116,7 @@
         <v>3004</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>115</v>
@@ -6165,16 +6185,16 @@
         <v>3007</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="G27" s="2">
         <v>4</v>
@@ -6216,7 +6236,7 @@
         <v>30</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="U27" s="2" t="s">
         <v>94</v>
@@ -6372,7 +6392,7 @@
         <v>4010</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>152</v>
@@ -6423,7 +6443,7 @@
         <v>30</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>285</v>
+        <v>334</v>
       </c>
       <c r="U30" s="2" t="s">
         <v>94</v>
@@ -6441,7 +6461,7 @@
         <v>4011</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>155</v>
@@ -6492,7 +6512,7 @@
         <v>30</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>245</v>
+        <v>333</v>
       </c>
       <c r="U31" s="2" t="s">
         <v>94</v>
@@ -6510,7 +6530,7 @@
         <v>4001</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>23</v>
@@ -6519,7 +6539,7 @@
         <v>21</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G32" s="2">
         <v>6</v>
@@ -6540,10 +6560,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O32" s="2">
         <v>1</v>
@@ -6561,7 +6581,7 @@
         <v>30</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="U32" s="2" t="s">
         <v>155</v>
@@ -6579,7 +6599,7 @@
         <v>4002</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>25</v>
@@ -6612,7 +6632,7 @@
         <v>94</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O33" s="2">
         <v>1</v>
@@ -6648,7 +6668,7 @@
         <v>4010</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>128</v>
@@ -6681,7 +6701,7 @@
         <v>94</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O34" s="2">
         <v>1</v>
@@ -6717,7 +6737,7 @@
         <v>4011</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>172</v>
@@ -6750,7 +6770,7 @@
         <v>94</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O35" s="2">
         <v>1</v>
@@ -6786,7 +6806,7 @@
         <v>4012</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>174</v>
@@ -6819,7 +6839,7 @@
         <v>94</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O36" s="2">
         <v>1</v>
@@ -6855,7 +6875,7 @@
         <v>4012</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>178</v>
@@ -6864,7 +6884,7 @@
         <v>177</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -6888,7 +6908,7 @@
         <v>94</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O37" s="2">
         <v>1</v>
@@ -6906,7 +6926,7 @@
         <v>30</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="U37" s="2" t="s">
         <v>23</v>
@@ -6924,7 +6944,7 @@
         <v>4012</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>180</v>
@@ -6957,7 +6977,7 @@
         <v>94</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O38" s="2">
         <v>1</v>
@@ -6975,7 +6995,7 @@
         <v>30</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>23</v>
@@ -7062,7 +7082,7 @@
         <v>4004</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>27</v>
@@ -7113,7 +7133,7 @@
         <v>30</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="U40" s="2" t="s">
         <v>23</v>
@@ -7209,7 +7229,7 @@
         <v>175</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G42" s="6">
         <v>3</v>
@@ -7233,7 +7253,7 @@
         <v>94</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O42" s="6">
         <v>1</v>
@@ -7251,7 +7271,7 @@
         <v>30</v>
       </c>
       <c r="T42" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="U42" s="6" t="s">
         <v>94</v>
@@ -7269,7 +7289,7 @@
         <v>4007</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>85</v>
@@ -7278,7 +7298,7 @@
         <v>87</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G43" s="2">
         <v>3</v>
@@ -7302,7 +7322,7 @@
         <v>94</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O43" s="2">
         <v>1</v>
@@ -7320,7 +7340,7 @@
         <v>30</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="U43" s="2" t="s">
         <v>155</v>
@@ -7347,7 +7367,7 @@
         <v>199</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G44" s="6">
         <v>3</v>
@@ -7371,7 +7391,7 @@
         <v>94</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O44" s="6">
         <v>1</v>
@@ -7389,7 +7409,7 @@
         <v>30</v>
       </c>
       <c r="T44" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="U44" s="6" t="s">
         <v>94</v>
@@ -7416,7 +7436,7 @@
         <v>88</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G45" s="6">
         <v>3</v>
@@ -7440,7 +7460,7 @@
         <v>94</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O45" s="6">
         <v>1</v>
@@ -7458,7 +7478,7 @@
         <v>30</v>
       </c>
       <c r="T45" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="U45" s="6" t="s">
         <v>94</v>
@@ -7485,7 +7505,7 @@
         <v>102</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G46" s="6">
         <v>3</v>
@@ -7527,7 +7547,7 @@
         <v>30</v>
       </c>
       <c r="T46" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="U46" s="6" t="s">
         <v>94</v>
@@ -7683,16 +7703,16 @@
         <v>5007</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E49" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="G49" s="2">
         <v>6</v>
@@ -7734,7 +7754,7 @@
         <v>30</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="U49" s="2" t="s">
         <v>94</v>
@@ -7752,7 +7772,7 @@
         <v>5001</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>39</v>
@@ -7806,7 +7826,7 @@
         <v>241</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V50" s="2">
         <v>1</v>
@@ -7821,7 +7841,7 @@
         <v>5002</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>121</v>
@@ -7890,7 +7910,7 @@
         <v>5003</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>140</v>
@@ -7959,7 +7979,7 @@
         <v>5005</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>203</v>
@@ -8013,7 +8033,7 @@
         <v>200</v>
       </c>
       <c r="U53" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V53" s="2">
         <v>1</v>
@@ -8028,7 +8048,7 @@
         <v>5006</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>218</v>
@@ -8061,7 +8081,7 @@
         <v>94</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O54" s="2">
         <v>1</v>
@@ -8166,7 +8186,7 @@
         <v>6002</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>101</v>
@@ -8217,7 +8237,7 @@
         <v>30</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="U56" s="2" t="s">
         <v>94</v>
@@ -8235,16 +8255,16 @@
         <v>6004</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="G57" s="2">
         <v>6</v>
@@ -8286,7 +8306,7 @@
         <v>30</v>
       </c>
       <c r="T57" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="U57" s="2" t="s">
         <v>94</v>
@@ -8304,16 +8324,16 @@
         <v>6005</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="F58" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>277</v>
       </c>
       <c r="G58" s="2">
         <v>6</v>
@@ -8355,7 +8375,7 @@
         <v>30</v>
       </c>
       <c r="T58" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="U58" s="2" t="s">
         <v>94</v>
@@ -8769,7 +8789,7 @@
         <v>120</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="U64" s="2" t="s">
         <v>94</v>
@@ -8787,16 +8807,16 @@
         <v>9005</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="G65" s="2">
         <v>2</v>
@@ -8838,7 +8858,7 @@
         <v>30</v>
       </c>
       <c r="T65" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="U65" s="2" t="s">
         <v>94</v>
@@ -8994,7 +9014,7 @@
         <v>9003</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>108</v>
@@ -9045,7 +9065,7 @@
         <v>30</v>
       </c>
       <c r="T68" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="U68" s="2" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A176A7-3325-46FB-808F-F39B5E9BE181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F15B15D-3B98-4274-A702-12F01ABA1CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1935" yWindow="1095" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1650" yWindow="960" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1488,33 +1488,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>風の力で、チョコレートを王冠の形に変形する
-お城のケーキなどを作る際の、部品となる。
-ウィンドクラウンをかけたあとは、素材が不安定なため、フリージングで固定する。</t>
-    <rPh sb="12" eb="14">
-      <t>オウカン</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ブヒン</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>ソザイ</t>
-    </rPh>
-    <rPh sb="63" eb="66">
-      <t>フアンテイコテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ウィンド・ペンシル</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1701,55 +1674,6 @@
     </rPh>
     <rPh sb="78" eb="81">
       <t>フアンテイコテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>風の力で、液体・チョコレートを渦まき状にする
-渦巻きのお菓子は、そのまま彫刻のように、場を彩ることができる。
-華やかな場やパーティー向けのお菓子になる。
-ウィンドツイスターをかけたあとは、素材が不安定なため、フリージングで固定する。</t>
-    <rPh sb="0" eb="1">
-      <t>カゼ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>チカラ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ウズマキ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>チョウコク</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>バ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>イロド</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>ハナ</t>
-    </rPh>
-    <rPh sb="60" eb="61">
-      <t>バ</t>
-    </rPh>
-    <rPh sb="67" eb="68">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="71" eb="73">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="96" eb="98">
-      <t>ソザイ</t>
-    </rPh>
-    <rPh sb="99" eb="102">
-      <t>フアンテイ</t>
-    </rPh>
-    <rPh sb="113" eb="115">
-      <t>コテイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3933,6 +3857,108 @@
     </rPh>
     <rPh sb="163" eb="165">
       <t>コスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風の力で、液体・チョコレートを渦まき状にする
+渦巻きのお菓子は、そのまま彫刻のように、場を彩ることができる。
+華やかな場やパーティー向けのお菓子になる。
+見た目は良くなるが、反面チョコを引き延ばすため、なめらかさは若干落ちる。
+ウィンドツイスターをかけたあとは、素材が不安定なため、フリージングで固定する。</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ウズマキ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>チョウコク</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>イロド</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>バ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>ハンメン</t>
+    </rPh>
+    <rPh sb="95" eb="96">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="97" eb="98">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>ジャッカン</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="137" eb="140">
+      <t>フアンテイ</t>
+    </rPh>
+    <rPh sb="151" eb="153">
+      <t>コテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風の力で、チョコレートを王冠の形に変形する
+お城のケーキなどを作る際の、部品となる。
+見た目は良くなるが、反面チョコを引き延ばすため、なめらかさは若干落ちる。
+ウィンドクラウンをかけたあとは、素材が不安定なため、フリージングで固定する。</t>
+    <rPh sb="12" eb="14">
+      <t>オウカン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="101" eb="104">
+      <t>フアンテイコテイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4424,7 +4450,7 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -4433,7 +4459,7 @@
         <v>9</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>10</v>
@@ -4580,7 +4606,7 @@
         <v>30</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>94</v>
@@ -4667,7 +4693,7 @@
         <v>1010</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>164</v>
@@ -4718,7 +4744,7 @@
         <v>30</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="U5" s="2" t="s">
         <v>94</v>
@@ -4736,7 +4762,7 @@
         <v>1009</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>112</v>
@@ -4745,7 +4771,7 @@
         <v>133</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G6" s="2">
         <v>6</v>
@@ -4787,7 +4813,7 @@
         <v>30</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="U6" s="2" t="s">
         <v>54</v>
@@ -4805,7 +4831,7 @@
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>58</v>
@@ -4907,7 +4933,7 @@
         <v>94</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O8" s="2">
         <v>1</v>
@@ -4925,7 +4951,7 @@
         <v>30</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>164</v>
@@ -4943,7 +4969,7 @@
         <v>1008</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>82</v>
@@ -4994,7 +5020,7 @@
         <v>30</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>80</v>
@@ -5012,16 +5038,16 @@
         <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="G10" s="2">
         <v>6</v>
@@ -5063,7 +5089,7 @@
         <v>30</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>58</v>
@@ -5132,7 +5158,7 @@
         <v>30</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>94</v>
@@ -5156,7 +5182,7 @@
         <v>81</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>105</v>
@@ -5222,13 +5248,13 @@
         <v>64</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>207</v>
       </c>
       <c r="G13" s="6">
         <v>6</v>
@@ -5270,7 +5296,7 @@
         <v>30</v>
       </c>
       <c r="T13" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="U13" s="6" t="s">
         <v>94</v>
@@ -5288,7 +5314,7 @@
         <v>2004</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>110</v>
@@ -5339,7 +5365,7 @@
         <v>30</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="U14" s="2" t="s">
         <v>94</v>
@@ -5408,7 +5434,7 @@
         <v>120</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="U15" s="2" t="s">
         <v>94</v>
@@ -5426,7 +5452,7 @@
         <v>2001</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>176</v>
@@ -5435,7 +5461,7 @@
         <v>179</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G16" s="2">
         <v>2</v>
@@ -5477,7 +5503,7 @@
         <v>120</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="U16" s="2" t="s">
         <v>51</v>
@@ -5564,16 +5590,16 @@
         <v>2005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G18" s="2">
         <v>2</v>
@@ -5615,7 +5641,7 @@
         <v>30</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="U18" s="2" t="s">
         <v>51</v>
@@ -5633,7 +5659,7 @@
         <v>2003</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>118</v>
@@ -5666,7 +5692,7 @@
         <v>94</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O19" s="2">
         <v>1</v>
@@ -5684,7 +5710,7 @@
         <v>30</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="U19" s="2" t="s">
         <v>101</v>
@@ -5705,13 +5731,13 @@
         <v>35</v>
       </c>
       <c r="D20" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>206</v>
       </c>
       <c r="G20" s="6">
         <v>2</v>
@@ -5753,7 +5779,7 @@
         <v>30</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="U20" s="6" t="s">
         <v>94</v>
@@ -5780,7 +5806,7 @@
         <v>157</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G21" s="2">
         <v>2</v>
@@ -5822,7 +5848,7 @@
         <v>30</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="U21" s="2" t="s">
         <v>94</v>
@@ -5846,7 +5872,7 @@
         <v>16</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>15</v>
@@ -5873,7 +5899,7 @@
         <v>94</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O22" s="2">
         <v>1</v>
@@ -5891,7 +5917,7 @@
         <v>30</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="U22" s="2" t="s">
         <v>94</v>
@@ -5942,7 +5968,7 @@
         <v>94</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O23" s="2">
         <v>1</v>
@@ -5960,7 +5986,7 @@
         <v>30</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="U23" s="2" t="s">
         <v>16</v>
@@ -5978,13 +6004,13 @@
         <v>3003</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>106</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>72</v>
@@ -6029,7 +6055,7 @@
         <v>30</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="U24" s="2" t="s">
         <v>20</v>
@@ -6047,16 +6073,16 @@
         <v>3008</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="G25" s="2">
         <v>4</v>
@@ -6098,7 +6124,7 @@
         <v>30</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="U25" s="2" t="s">
         <v>94</v>
@@ -6116,7 +6142,7 @@
         <v>3004</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>115</v>
@@ -6167,7 +6193,7 @@
         <v>30</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U26" s="2" t="s">
         <v>94</v>
@@ -6185,16 +6211,16 @@
         <v>3007</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G27" s="2">
         <v>4</v>
@@ -6236,7 +6262,7 @@
         <v>30</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="U27" s="2" t="s">
         <v>94</v>
@@ -6326,13 +6352,13 @@
         <v>36</v>
       </c>
       <c r="D29" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F29" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="G29" s="6">
         <v>4</v>
@@ -6374,7 +6400,7 @@
         <v>30</v>
       </c>
       <c r="T29" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="U29" s="6" t="s">
         <v>94</v>
@@ -6392,7 +6418,7 @@
         <v>4010</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>152</v>
@@ -6443,7 +6469,7 @@
         <v>30</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="U30" s="2" t="s">
         <v>94</v>
@@ -6461,13 +6487,13 @@
         <v>4011</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>156</v>
@@ -6512,7 +6538,7 @@
         <v>30</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="U31" s="2" t="s">
         <v>94</v>
@@ -6530,7 +6556,7 @@
         <v>4001</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>23</v>
@@ -6539,7 +6565,7 @@
         <v>21</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G32" s="2">
         <v>6</v>
@@ -6560,10 +6586,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O32" s="2">
         <v>1</v>
@@ -6581,7 +6607,7 @@
         <v>30</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="U32" s="2" t="s">
         <v>155</v>
@@ -6599,7 +6625,7 @@
         <v>4002</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>25</v>
@@ -6608,7 +6634,7 @@
         <v>22</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -6632,7 +6658,7 @@
         <v>94</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O33" s="2">
         <v>1</v>
@@ -6650,7 +6676,7 @@
         <v>30</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>197</v>
+        <v>333</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>94</v>
@@ -6668,7 +6694,7 @@
         <v>4010</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>128</v>
@@ -6677,7 +6703,7 @@
         <v>129</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G34" s="2">
         <v>1</v>
@@ -6701,7 +6727,7 @@
         <v>94</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O34" s="2">
         <v>1</v>
@@ -6719,7 +6745,7 @@
         <v>30</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="U34" s="2" t="s">
         <v>23</v>
@@ -6737,7 +6763,7 @@
         <v>4011</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>172</v>
@@ -6770,7 +6796,7 @@
         <v>94</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O35" s="2">
         <v>1</v>
@@ -6806,7 +6832,7 @@
         <v>4012</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>174</v>
@@ -6839,7 +6865,7 @@
         <v>94</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O36" s="2">
         <v>1</v>
@@ -6857,7 +6883,7 @@
         <v>30</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>185</v>
+        <v>334</v>
       </c>
       <c r="U36" s="2" t="s">
         <v>23</v>
@@ -6875,7 +6901,7 @@
         <v>4012</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>178</v>
@@ -6884,7 +6910,7 @@
         <v>177</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -6908,7 +6934,7 @@
         <v>94</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O37" s="2">
         <v>1</v>
@@ -6926,7 +6952,7 @@
         <v>30</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="U37" s="2" t="s">
         <v>23</v>
@@ -6944,13 +6970,13 @@
         <v>4012</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>181</v>
@@ -6977,7 +7003,7 @@
         <v>94</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O38" s="2">
         <v>1</v>
@@ -6995,7 +7021,7 @@
         <v>30</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>23</v>
@@ -7082,16 +7108,16 @@
         <v>4004</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G40" s="2">
         <v>3</v>
@@ -7133,7 +7159,7 @@
         <v>30</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="U40" s="2" t="s">
         <v>23</v>
@@ -7229,7 +7255,7 @@
         <v>175</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G42" s="6">
         <v>3</v>
@@ -7253,7 +7279,7 @@
         <v>94</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O42" s="6">
         <v>1</v>
@@ -7271,7 +7297,7 @@
         <v>30</v>
       </c>
       <c r="T42" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="U42" s="6" t="s">
         <v>94</v>
@@ -7289,7 +7315,7 @@
         <v>4007</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>85</v>
@@ -7298,7 +7324,7 @@
         <v>87</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G43" s="2">
         <v>3</v>
@@ -7322,7 +7348,7 @@
         <v>94</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O43" s="2">
         <v>1</v>
@@ -7340,7 +7366,7 @@
         <v>30</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="U43" s="2" t="s">
         <v>155</v>
@@ -7361,13 +7387,13 @@
         <v>37</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G44" s="6">
         <v>3</v>
@@ -7391,7 +7417,7 @@
         <v>94</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O44" s="6">
         <v>1</v>
@@ -7409,7 +7435,7 @@
         <v>30</v>
       </c>
       <c r="T44" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="U44" s="6" t="s">
         <v>94</v>
@@ -7436,7 +7462,7 @@
         <v>88</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G45" s="6">
         <v>3</v>
@@ -7460,7 +7486,7 @@
         <v>94</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O45" s="6">
         <v>1</v>
@@ -7478,7 +7504,7 @@
         <v>30</v>
       </c>
       <c r="T45" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="U45" s="6" t="s">
         <v>94</v>
@@ -7505,7 +7531,7 @@
         <v>102</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G46" s="6">
         <v>3</v>
@@ -7547,7 +7573,7 @@
         <v>30</v>
       </c>
       <c r="T46" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="U46" s="6" t="s">
         <v>94</v>
@@ -7571,7 +7597,7 @@
         <v>163</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>161</v>
@@ -7643,7 +7669,7 @@
         <v>159</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G48" s="6">
         <v>6</v>
@@ -7685,7 +7711,7 @@
         <v>30</v>
       </c>
       <c r="T48" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="U48" s="6" t="s">
         <v>94</v>
@@ -7703,16 +7729,16 @@
         <v>5007</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G49" s="2">
         <v>6</v>
@@ -7754,7 +7780,7 @@
         <v>30</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="U49" s="2" t="s">
         <v>94</v>
@@ -7772,7 +7798,7 @@
         <v>5001</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>39</v>
@@ -7823,10 +7849,10 @@
         <v>30</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="V50" s="2">
         <v>1</v>
@@ -7841,7 +7867,7 @@
         <v>5002</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>121</v>
@@ -7892,7 +7918,7 @@
         <v>30</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="U51" s="2" t="s">
         <v>39</v>
@@ -7910,13 +7936,13 @@
         <v>5003</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>140</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>139</v>
@@ -7961,7 +7987,7 @@
         <v>480</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="U52" s="2" t="s">
         <v>94</v>
@@ -7979,16 +8005,16 @@
         <v>5005</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G53" s="2">
         <v>6</v>
@@ -8009,7 +8035,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>94</v>
@@ -8030,10 +8056,10 @@
         <v>30</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="U53" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="V53" s="2">
         <v>1</v>
@@ -8048,16 +8074,16 @@
         <v>5006</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G54" s="2">
         <v>6</v>
@@ -8081,7 +8107,7 @@
         <v>94</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="O54" s="2">
         <v>1</v>
@@ -8099,7 +8125,7 @@
         <v>30</v>
       </c>
       <c r="T54" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="U54" s="2" t="s">
         <v>94</v>
@@ -8186,7 +8212,7 @@
         <v>6002</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>101</v>
@@ -8237,7 +8263,7 @@
         <v>30</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="U56" s="2" t="s">
         <v>94</v>
@@ -8255,16 +8281,16 @@
         <v>6004</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="G57" s="2">
         <v>6</v>
@@ -8306,7 +8332,7 @@
         <v>30</v>
       </c>
       <c r="T57" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="U57" s="2" t="s">
         <v>94</v>
@@ -8324,16 +8350,16 @@
         <v>6005</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="G58" s="2">
         <v>6</v>
@@ -8375,7 +8401,7 @@
         <v>30</v>
       </c>
       <c r="T58" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="U58" s="2" t="s">
         <v>94</v>
@@ -8582,7 +8608,7 @@
         <v>30</v>
       </c>
       <c r="T61" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="U61" s="7" t="s">
         <v>94</v>
@@ -8789,7 +8815,7 @@
         <v>120</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="U64" s="2" t="s">
         <v>94</v>
@@ -8807,16 +8833,16 @@
         <v>9005</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G65" s="2">
         <v>2</v>
@@ -8858,7 +8884,7 @@
         <v>30</v>
       </c>
       <c r="T65" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="U65" s="2" t="s">
         <v>94</v>
@@ -8927,7 +8953,7 @@
         <v>30</v>
       </c>
       <c r="T66" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="U66" s="6" t="s">
         <v>94</v>
@@ -8975,7 +9001,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="N67" s="6" t="s">
         <v>94</v>
@@ -8996,7 +9022,7 @@
         <v>60</v>
       </c>
       <c r="T67" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="U67" s="6" t="s">
         <v>94</v>
@@ -9014,7 +9040,7 @@
         <v>9003</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>108</v>
@@ -9065,7 +9091,7 @@
         <v>30</v>
       </c>
       <c r="T68" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="U68" s="2" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F15B15D-3B98-4274-A702-12F01ABA1CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0EE3C1-A7AF-4C66-8368-AE43499D28F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="960" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3240" yWindow="1845" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0EE3C1-A7AF-4C66-8368-AE43499D28F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C87BC0-799C-4504-82CD-1342EA16A9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="1845" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C87BC0-799C-4504-82CD-1342EA16A9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23348756-44EA-4319-BA54-A92A67E74C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2520" yWindow="660" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4819,7 +4819,7 @@
         <v>54</v>
       </c>
       <c r="V6" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:22" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23348756-44EA-4319-BA54-A92A67E74C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06372620-D4C7-4CCF-9374-34EA1BA86676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="660" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2010" yWindow="870" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2408,57 +2408,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>クッキーなどの焼き菓子をさらに焼くことで、サクサク感を増す。
-LVが上がると、より効果が高まる。
-ゲージが出現するので、
-焦げるギリギリのポイントでゲージを止めると、
-サクサク感が増す。
-ポイントを超えると、焦げて失敗。
-◆パネルにお菓子がセットされた状態でないと使えない。
-◆仕上げ回数を一回消費する。
-仕上げ回数がないと、使用できない。</t>
-    <rPh sb="7" eb="8">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ガシ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>コウカ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>タカ</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>シュツゲン</t>
-    </rPh>
-    <rPh sb="62" eb="63">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="79" eb="80">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="89" eb="90">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="91" eb="92">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="101" eb="102">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="106" eb="107">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="109" eb="111">
-      <t>シッパイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ほしのかけらを飲み物にトッピングする
 ジュースやソーダとの相性がいい。
 ◆パネルにお菓子がセットされた状態でないと使えない。
@@ -2608,38 +2557,6 @@
   </si>
   <si>
     <t>KetteiKosu</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アイス水溶液に魔法をかけながら混ぜて、アイスクリーム制作時の成功率アップ・制作時間を少し短縮する。
-習得するだけでOK。
-LVに応じて、ほんのわずかになめらかさを出す。
-LV1: 成功率+2, 時間短縮+10%
-LV2: 成功率+4, 時間短縮+20%
-LV3: 成功率+6, 時間短縮+30%
-LV4: 成功率+8, 時間短縮+40%
-LV5: 成功率+10, 時間短縮+50%</t>
-    <rPh sb="26" eb="29">
-      <t>セイサクジ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>シュウトク</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="82" eb="83">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="92" eb="95">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="99" eb="101">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>タンシュク</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3140,33 +3057,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ソーダについて勉強する。
-LVが上がるにつれて、ジュース・ソーダを作る際の成功率が上昇する。
-また、わずかに、ソーダののどごしもアップする。
-LV1: 成功率+5%
-LV2: 成功率+10%
-LV3: 成功率+15%</t>
-    <rPh sb="7" eb="9">
-      <t>ベンキョウ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="37" eb="40">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ジョウショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>レアもの発見+1</t>
     <rPh sb="4" eb="6">
       <t>ハッケン</t>
@@ -3959,6 +3849,122 @@
     </rPh>
     <rPh sb="101" eb="104">
       <t>フアンテイコテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クッキーなどの焼き菓子をさらに焼くことで、サクサク感を増す。
+ゲージが出現するので、
+焦げるギリギリのポイントでゲージを止めると、
+サクサク感が増す。
+ポイントを超えると、焦げて失敗。
+LVが上がると、ゲージの速度がゆっくりになる。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="7" eb="8">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ガシ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="108" eb="110">
+      <t>ソクド</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アイス水溶液に魔法をかけながら混ぜて、アイスクリーム制作時の成功率アップ・制作時間を少し短縮する。
+習得するだけでOK。
+LVに応じて、ほんのわずかになめらかさを出す。
+LV1: 成功率+2, 時間短縮+5%
+LV2: 成功率+4, 時間短縮+10%
+LV3: 成功率+6, 時間短縮+15%
+LV4: 成功率+8, 時間短縮+20%
+LV5: 成功率+10, 時間短縮+25%
+LV6: 成功率+12, 時間短縮+30%
+LV7: 成功率+14, 時間短縮+35%
+LV8: 成功率+16, 時間短縮+40%
+LV9: 成功率+18, 時間短縮+45%
+LV10: 成功率+20, 時間短縮+50%</t>
+    <rPh sb="26" eb="29">
+      <t>セイサクジ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>シュウトク</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="82" eb="83">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="92" eb="95">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ソーダについて勉強する。
+LVが上がるにつれて、ジュース・ソーダを作る際の成功率が上昇する。
+また、わずかに、ソーダののどごしもアップする。
+LV1: 成功率+2%
+LV2: 成功率+4%
+LV3: 成功率+6%
+LV4: 成功率+8%
+LV5: 成功率+10%
+LV6: 成功率+12%
+LV7: 成功率+14%
+LV8: 成功率+16%
+LV9: 成功率+18%
+LV10: 成功率+20%</t>
+    <rPh sb="7" eb="9">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="37" eb="40">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ジョウショウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4450,7 +4456,7 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -4459,7 +4465,7 @@
         <v>9</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>10</v>
@@ -4606,7 +4612,7 @@
         <v>30</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>94</v>
@@ -4693,7 +4699,7 @@
         <v>1010</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>164</v>
@@ -4744,7 +4750,7 @@
         <v>30</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="U5" s="2" t="s">
         <v>94</v>
@@ -4762,7 +4768,7 @@
         <v>1009</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>112</v>
@@ -4813,7 +4819,7 @@
         <v>30</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>238</v>
+        <v>332</v>
       </c>
       <c r="U6" s="2" t="s">
         <v>54</v>
@@ -4831,7 +4837,7 @@
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>58</v>
@@ -4933,7 +4939,7 @@
         <v>94</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O8" s="2">
         <v>1</v>
@@ -4951,7 +4957,7 @@
         <v>30</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>164</v>
@@ -4969,7 +4975,7 @@
         <v>1008</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>82</v>
@@ -5020,7 +5026,7 @@
         <v>30</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>80</v>
@@ -5038,7 +5044,7 @@
         <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>225</v>
@@ -5089,7 +5095,7 @@
         <v>30</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>58</v>
@@ -5314,7 +5320,7 @@
         <v>2004</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>110</v>
@@ -5338,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L14" s="2">
         <v>0</v>
@@ -5365,7 +5371,7 @@
         <v>30</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>245</v>
+        <v>333</v>
       </c>
       <c r="U14" s="2" t="s">
         <v>94</v>
@@ -5452,7 +5458,7 @@
         <v>2001</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>176</v>
@@ -5590,16 +5596,16 @@
         <v>2005</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G18" s="2">
         <v>2</v>
@@ -5641,7 +5647,7 @@
         <v>30</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="U18" s="2" t="s">
         <v>51</v>
@@ -5659,7 +5665,7 @@
         <v>2003</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>118</v>
@@ -5692,7 +5698,7 @@
         <v>94</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O19" s="2">
         <v>1</v>
@@ -5710,7 +5716,7 @@
         <v>30</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="U19" s="2" t="s">
         <v>101</v>
@@ -5899,7 +5905,7 @@
         <v>94</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O22" s="2">
         <v>1</v>
@@ -5968,7 +5974,7 @@
         <v>94</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O23" s="2">
         <v>1</v>
@@ -6004,7 +6010,7 @@
         <v>3003</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>106</v>
@@ -6055,7 +6061,7 @@
         <v>30</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="U24" s="2" t="s">
         <v>20</v>
@@ -6073,16 +6079,16 @@
         <v>3008</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="G25" s="2">
         <v>4</v>
@@ -6124,7 +6130,7 @@
         <v>30</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="U25" s="2" t="s">
         <v>94</v>
@@ -6142,7 +6148,7 @@
         <v>3004</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>115</v>
@@ -6211,16 +6217,16 @@
         <v>3007</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G27" s="2">
         <v>4</v>
@@ -6262,7 +6268,7 @@
         <v>30</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="U27" s="2" t="s">
         <v>94</v>
@@ -6418,7 +6424,7 @@
         <v>4010</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>152</v>
@@ -6469,7 +6475,7 @@
         <v>30</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="U30" s="2" t="s">
         <v>94</v>
@@ -6487,7 +6493,7 @@
         <v>4011</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>155</v>
@@ -6538,7 +6544,7 @@
         <v>30</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="U31" s="2" t="s">
         <v>94</v>
@@ -6556,7 +6562,7 @@
         <v>4001</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>23</v>
@@ -6565,7 +6571,7 @@
         <v>21</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G32" s="2">
         <v>6</v>
@@ -6586,10 +6592,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O32" s="2">
         <v>1</v>
@@ -6607,7 +6613,7 @@
         <v>30</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="U32" s="2" t="s">
         <v>155</v>
@@ -6625,7 +6631,7 @@
         <v>4002</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>25</v>
@@ -6658,7 +6664,7 @@
         <v>94</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O33" s="2">
         <v>1</v>
@@ -6676,7 +6682,7 @@
         <v>30</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>94</v>
@@ -6694,7 +6700,7 @@
         <v>4010</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>128</v>
@@ -6727,7 +6733,7 @@
         <v>94</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O34" s="2">
         <v>1</v>
@@ -6763,7 +6769,7 @@
         <v>4011</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>172</v>
@@ -6796,7 +6802,7 @@
         <v>94</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O35" s="2">
         <v>1</v>
@@ -6832,7 +6838,7 @@
         <v>4012</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>174</v>
@@ -6865,7 +6871,7 @@
         <v>94</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O36" s="2">
         <v>1</v>
@@ -6883,7 +6889,7 @@
         <v>30</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="U36" s="2" t="s">
         <v>23</v>
@@ -6901,7 +6907,7 @@
         <v>4012</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>178</v>
@@ -6910,7 +6916,7 @@
         <v>177</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -6934,7 +6940,7 @@
         <v>94</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O37" s="2">
         <v>1</v>
@@ -6952,7 +6958,7 @@
         <v>30</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="U37" s="2" t="s">
         <v>23</v>
@@ -6970,7 +6976,7 @@
         <v>4012</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>180</v>
@@ -7003,7 +7009,7 @@
         <v>94</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O38" s="2">
         <v>1</v>
@@ -7021,7 +7027,7 @@
         <v>30</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>23</v>
@@ -7108,7 +7114,7 @@
         <v>4004</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>27</v>
@@ -7159,7 +7165,7 @@
         <v>30</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="U40" s="2" t="s">
         <v>23</v>
@@ -7255,7 +7261,7 @@
         <v>175</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G42" s="6">
         <v>3</v>
@@ -7279,7 +7285,7 @@
         <v>94</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O42" s="6">
         <v>1</v>
@@ -7297,7 +7303,7 @@
         <v>30</v>
       </c>
       <c r="T42" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="U42" s="6" t="s">
         <v>94</v>
@@ -7315,7 +7321,7 @@
         <v>4007</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>85</v>
@@ -7324,7 +7330,7 @@
         <v>87</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G43" s="2">
         <v>3</v>
@@ -7348,7 +7354,7 @@
         <v>94</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O43" s="2">
         <v>1</v>
@@ -7366,7 +7372,7 @@
         <v>30</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="U43" s="2" t="s">
         <v>155</v>
@@ -7393,7 +7399,7 @@
         <v>197</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G44" s="6">
         <v>3</v>
@@ -7417,7 +7423,7 @@
         <v>94</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O44" s="6">
         <v>1</v>
@@ -7435,7 +7441,7 @@
         <v>30</v>
       </c>
       <c r="T44" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="U44" s="6" t="s">
         <v>94</v>
@@ -7462,7 +7468,7 @@
         <v>88</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G45" s="6">
         <v>3</v>
@@ -7486,7 +7492,7 @@
         <v>94</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O45" s="6">
         <v>1</v>
@@ -7504,7 +7510,7 @@
         <v>30</v>
       </c>
       <c r="T45" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="U45" s="6" t="s">
         <v>94</v>
@@ -7531,7 +7537,7 @@
         <v>102</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G46" s="6">
         <v>3</v>
@@ -7573,7 +7579,7 @@
         <v>30</v>
       </c>
       <c r="T46" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="U46" s="6" t="s">
         <v>94</v>
@@ -7729,16 +7735,16 @@
         <v>5007</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G49" s="2">
         <v>6</v>
@@ -7753,7 +7759,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L49" s="2">
         <v>0</v>
@@ -7780,7 +7786,7 @@
         <v>30</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>281</v>
+        <v>334</v>
       </c>
       <c r="U49" s="2" t="s">
         <v>94</v>
@@ -7798,7 +7804,7 @@
         <v>5001</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>39</v>
@@ -7849,13 +7855,13 @@
         <v>30</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="V50" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -7867,7 +7873,7 @@
         <v>5002</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>121</v>
@@ -7918,7 +7924,7 @@
         <v>30</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="U51" s="2" t="s">
         <v>39</v>
@@ -7936,7 +7942,7 @@
         <v>5003</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>140</v>
@@ -8005,7 +8011,7 @@
         <v>5005</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>201</v>
@@ -8059,10 +8065,10 @@
         <v>198</v>
       </c>
       <c r="U53" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="V53" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8074,7 +8080,7 @@
         <v>5006</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>216</v>
@@ -8107,7 +8113,7 @@
         <v>94</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O54" s="2">
         <v>1</v>
@@ -8212,7 +8218,7 @@
         <v>6002</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>101</v>
@@ -8263,7 +8269,7 @@
         <v>30</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="U56" s="2" t="s">
         <v>94</v>
@@ -8281,16 +8287,16 @@
         <v>6004</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="G57" s="2">
         <v>6</v>
@@ -8332,7 +8338,7 @@
         <v>30</v>
       </c>
       <c r="T57" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="U57" s="2" t="s">
         <v>94</v>
@@ -8350,16 +8356,16 @@
         <v>6005</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="G58" s="2">
         <v>6</v>
@@ -8401,7 +8407,7 @@
         <v>30</v>
       </c>
       <c r="T58" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="U58" s="2" t="s">
         <v>94</v>
@@ -8815,7 +8821,7 @@
         <v>120</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="U64" s="2" t="s">
         <v>94</v>
@@ -8833,16 +8839,16 @@
         <v>9005</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G65" s="2">
         <v>2</v>
@@ -8884,7 +8890,7 @@
         <v>30</v>
       </c>
       <c r="T65" s="3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="U65" s="2" t="s">
         <v>94</v>
@@ -9040,7 +9046,7 @@
         <v>9003</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>108</v>
@@ -9091,7 +9097,7 @@
         <v>30</v>
       </c>
       <c r="T68" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="U68" s="2" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06372620-D4C7-4CCF-9374-34EA1BA86676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452F8EF7-DF5B-41D8-B3B2-47E561A21A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2010" yWindow="870" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3651,46 +3651,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>生地をきれいに混ぜる技術を磨く。
-クレープ生地やケーキ生地など生地系の品質を、少しだけ底上げする。
-LV3以上だと、出来上がる生地の個数が+1。
-LV5で+2。</t>
-    <rPh sb="22" eb="24">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ヒンシツ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ソコア</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="60" eb="63">
-      <t>デキア</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="68" eb="70">
-      <t>コスウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ケーキの見た目をきれいに仕上げる。
 クリームをきれいにぬる技術のこと。
 クリームを塗る工程の際に、成功率を少し上げる。
@@ -3965,6 +3925,56 @@
     </rPh>
     <rPh sb="41" eb="43">
       <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生地をきれいに混ぜる技術を磨く。
+クレープ生地やケーキ生地など生地系の品質を、少しだけ底上げする。
+また、スポンジケーキを焼くときの時間を短縮する。
+LV3以上だと、出来上がる生地の個数が+1。
+LV5で+2。</t>
+    <rPh sb="22" eb="24">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ソコア</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>タンシュク</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="86" eb="89">
+      <t>デキア</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>コスウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4819,7 +4829,7 @@
         <v>30</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="U6" s="2" t="s">
         <v>54</v>
@@ -5371,7 +5381,7 @@
         <v>30</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="U14" s="2" t="s">
         <v>94</v>
@@ -6475,7 +6485,7 @@
         <v>30</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="U30" s="2" t="s">
         <v>94</v>
@@ -6544,7 +6554,7 @@
         <v>30</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="U31" s="2" t="s">
         <v>94</v>
@@ -6610,7 +6620,7 @@
         <v>85</v>
       </c>
       <c r="S32" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>253</v>
@@ -6679,10 +6689,10 @@
         <v>100</v>
       </c>
       <c r="S33" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>94</v>
@@ -6748,7 +6758,7 @@
         <v>100</v>
       </c>
       <c r="S34" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T34" s="3" t="s">
         <v>195</v>
@@ -6817,7 +6827,7 @@
         <v>100</v>
       </c>
       <c r="S35" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>183</v>
@@ -6886,10 +6896,10 @@
         <v>100</v>
       </c>
       <c r="S36" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="U36" s="2" t="s">
         <v>23</v>
@@ -6955,7 +6965,7 @@
         <v>100</v>
       </c>
       <c r="S37" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T37" s="3" t="s">
         <v>324</v>
@@ -7024,7 +7034,7 @@
         <v>100</v>
       </c>
       <c r="S38" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T38" s="3" t="s">
         <v>325</v>
@@ -7369,7 +7379,7 @@
         <v>100</v>
       </c>
       <c r="S43" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>249</v>
@@ -7786,7 +7796,7 @@
         <v>30</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="U49" s="2" t="s">
         <v>94</v>
@@ -7852,7 +7862,7 @@
         <v>100</v>
       </c>
       <c r="S50" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T50" s="3" t="s">
         <v>238</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452F8EF7-DF5B-41D8-B3B2-47E561A21A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CE9CD6-C719-4CE4-9EE2-088218EB1D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2835" yWindow="1095" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -995,16 +995,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ほしのかけらを飲み物にトッピングする</t>
-    <rPh sb="7" eb="8">
-      <t>ノ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>モノ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ポーションや液体を固めて、シュガーを作り出す</t>
     <rPh sb="6" eb="8">
       <t>エキタイ</t>
@@ -1977,22 +1967,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>雨の力で、ベリーやジュースに虹色を加える。</t>
-    <rPh sb="0" eb="1">
-      <t>アメ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>チカラ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ニジイロ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>クワ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>レインボー・レイン</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2026,35 +2000,6 @@
   </si>
   <si>
     <t>MS</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>雨の力を借りて、ベリーやジュースに、虹色の力を与える。
-与えられたベリーやジュースは、虹色になる。</t>
-    <rPh sb="0" eb="1">
-      <t>アメ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>チカラ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ニジイロ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>チカラ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ニジイロ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2408,17 +2353,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ほしのかけらを飲み物にトッピングする
-ジュースやソーダとの相性がいい。
-◆パネルにお菓子がセットされた状態でないと使えない。
-◆仕上げ回数を一回消費する。
-仕上げ回数がないと、使用できない。</t>
-    <rPh sb="30" eb="32">
-      <t>アイショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>光で作ったちょうちょや葉っぱを飛ばす
 お菓子をさらにかわいく演出できる。
 見た目がアップする。
@@ -3975,6 +3909,91 @@
     </rPh>
     <rPh sb="94" eb="96">
       <t>コスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>雨の力で、ストロベリーやジュースに虹色を加える。</t>
+    <rPh sb="0" eb="1">
+      <t>アメ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニジイロ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>クワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ほしのかけらをお菓子にトッピングする</t>
+    <rPh sb="8" eb="10">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ほしのかけらをおかしにトッピングする
+ジュースやソーダとの相性がいい。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="30" eb="32">
+      <t>アイショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>雨の力を借りて、ストロベリーやジュースに、虹色の力を与える。
+与えられたベリーやジュースは、虹色になる。
+お菓子にかけた場合、
+虹の演出が可能になる。
+◆おかしにかける場合は、仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="0" eb="1">
+      <t>アメ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニジイロ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ニジイロ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>ニジ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4033,12 +4052,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -4046,6 +4059,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4064,7 +4083,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4078,17 +4097,20 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4466,7 +4488,7 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -4475,7 +4497,7 @@
         <v>9</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>10</v>
@@ -4487,10 +4509,10 @@
         <v>53</v>
       </c>
       <c r="U1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -4552,7 +4574,7 @@
       <c r="S2" s="4">
         <v>30</v>
       </c>
-      <c r="T2" s="5" t="s">
+      <c r="T2" s="6" t="s">
         <v>131</v>
       </c>
       <c r="U2" s="4" t="s">
@@ -4562,72 +4584,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2">
+    <row r="3" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3">
         <v>1002</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3">
         <v>6</v>
       </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>10</v>
       </c>
-      <c r="L3" s="2">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O3" s="2">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>9</v>
       </c>
-      <c r="Q3" s="2">
-        <v>0</v>
-      </c>
-      <c r="R3" s="2">
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
         <v>100</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3">
         <v>30</v>
       </c>
-      <c r="T3" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V3" s="2">
+      <c r="T3" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="U3" t="s">
+        <v>94</v>
+      </c>
+      <c r="V3">
         <v>0</v>
       </c>
     </row>
@@ -4690,7 +4712,7 @@
       <c r="S4" s="4">
         <v>30</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="T4" s="6" t="s">
         <v>132</v>
       </c>
       <c r="U4" s="4" t="s">
@@ -4700,831 +4722,831 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="2">
+    <row r="5" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>1010</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="C5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5">
         <v>6</v>
       </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>10</v>
       </c>
-      <c r="L5" s="2">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O5" s="2">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
         <v>9</v>
       </c>
-      <c r="Q5" s="2">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2">
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
         <v>100</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5">
         <v>30</v>
       </c>
-      <c r="T5" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V5" s="2">
+      <c r="T5" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="U5" t="s">
+        <v>94</v>
+      </c>
+      <c r="V5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="2">
+    <row r="6" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>1009</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" t="s">
+        <v>295</v>
+      </c>
+      <c r="D6" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>133</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="F6" t="s">
+        <v>207</v>
+      </c>
+      <c r="G6">
         <v>6</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6">
         <v>5</v>
       </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>3</v>
       </c>
-      <c r="L6" s="2">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O6" s="2">
-        <v>1</v>
-      </c>
-      <c r="P6" s="2">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>135</v>
+      </c>
+      <c r="N6" t="s">
+        <v>135</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
         <v>9</v>
       </c>
-      <c r="Q6" s="2">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2">
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
         <v>100</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6">
         <v>30</v>
       </c>
-      <c r="T6" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="U6" s="2" t="s">
+      <c r="T6" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="U6" t="s">
         <v>54</v>
       </c>
-      <c r="V6" s="2">
+      <c r="V6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2">
+    <row r="7" spans="1:22" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="9">
         <v>1003</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="9">
         <v>2</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="9">
         <v>2</v>
       </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="I7" s="9">
+        <v>1</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
         <v>3</v>
       </c>
-      <c r="L7" s="2">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O7" s="2">
-        <v>1</v>
-      </c>
-      <c r="P7" s="2">
+      <c r="L7" s="9">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O7" s="9">
+        <v>1</v>
+      </c>
+      <c r="P7" s="9">
         <v>9</v>
       </c>
-      <c r="Q7" s="2">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2">
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9">
         <v>100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="S7" s="9">
         <v>30</v>
       </c>
-      <c r="T7" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="U7" s="2" t="s">
+      <c r="T7" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="U7" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="V7" s="2">
+      <c r="V7" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="2">
+    <row r="8" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <v>1006</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8">
         <v>6</v>
       </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>3</v>
       </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O8" s="2">
-        <v>1</v>
-      </c>
-      <c r="P8" s="2">
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
+        <v>94</v>
+      </c>
+      <c r="N8" t="s">
+        <v>239</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
         <v>9</v>
       </c>
-      <c r="Q8" s="2">
-        <v>0</v>
-      </c>
-      <c r="R8" s="2">
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
         <v>100</v>
       </c>
-      <c r="S8" s="2">
+      <c r="S8">
         <v>30</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="V8" s="2">
+      <c r="T8" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="U8" t="s">
+        <v>163</v>
+      </c>
+      <c r="V8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="2">
+    <row r="9" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9">
         <v>1008</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" t="s">
+        <v>311</v>
+      </c>
+      <c r="D9" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="E9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F9" t="s">
         <v>104</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9">
         <v>6</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9">
         <v>2</v>
       </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>3</v>
       </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O9" s="2">
-        <v>1</v>
-      </c>
-      <c r="P9" s="2">
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
         <v>9</v>
       </c>
-      <c r="Q9" s="2">
-        <v>0</v>
-      </c>
-      <c r="R9" s="2">
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
         <v>100</v>
       </c>
-      <c r="S9" s="2">
+      <c r="S9">
         <v>30</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="U9" s="2" t="s">
+      <c r="T9" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="U9" t="s">
         <v>80</v>
       </c>
-      <c r="V9" s="2">
+      <c r="V9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="2">
+    <row r="10" spans="1:22" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="9">
         <v>1006</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G10" s="2">
+      <c r="C10" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="G10" s="9">
         <v>6</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="9">
         <v>4</v>
       </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2">
+      <c r="I10" s="9">
+        <v>1</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
         <v>3</v>
       </c>
-      <c r="L10" s="2">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O10" s="2">
-        <v>1</v>
-      </c>
-      <c r="P10" s="2">
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="O10" s="9">
+        <v>1</v>
+      </c>
+      <c r="P10" s="9">
         <v>9</v>
       </c>
-      <c r="Q10" s="2">
-        <v>1</v>
-      </c>
-      <c r="R10" s="2">
+      <c r="Q10" s="9">
+        <v>1</v>
+      </c>
+      <c r="R10" s="9">
         <v>100</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S10" s="9">
         <v>30</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="U10" s="2" t="s">
+      <c r="T10" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="U10" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="V10" s="2">
+      <c r="V10" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="2">
+    <row r="11" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11">
         <v>1004</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="C11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11">
         <v>2</v>
       </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
-      <c r="L11" s="2">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O11" s="2">
-        <v>0</v>
-      </c>
-      <c r="P11" s="2">
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>94</v>
+      </c>
+      <c r="N11" t="s">
+        <v>94</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
         <v>9</v>
       </c>
-      <c r="Q11" s="2">
-        <v>0</v>
-      </c>
-      <c r="R11" s="2">
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
         <v>100</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S11">
         <v>30</v>
       </c>
-      <c r="T11" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V11" s="2">
+      <c r="T11" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="U11" t="s">
+        <v>94</v>
+      </c>
+      <c r="V11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="6">
+    <row r="12" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>1007</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="F12" s="6" t="s">
+      <c r="E12" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="4">
         <v>6</v>
       </c>
-      <c r="H12" s="6">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6">
+      <c r="H12" s="4">
+        <v>1</v>
+      </c>
+      <c r="I12" s="4">
         <v>9999</v>
       </c>
-      <c r="J12" s="6">
-        <v>0</v>
-      </c>
-      <c r="K12" s="6">
-        <v>1</v>
-      </c>
-      <c r="L12" s="6">
-        <v>0</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O12" s="6">
-        <v>1</v>
-      </c>
-      <c r="P12" s="6">
+      <c r="J12" s="4">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4">
+        <v>1</v>
+      </c>
+      <c r="L12" s="4">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O12" s="4">
+        <v>1</v>
+      </c>
+      <c r="P12" s="4">
         <v>9</v>
       </c>
-      <c r="Q12" s="2">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6">
+      <c r="Q12" s="4">
+        <v>0</v>
+      </c>
+      <c r="R12" s="4">
         <v>100</v>
       </c>
-      <c r="S12" s="6">
+      <c r="S12" s="4">
         <v>30</v>
       </c>
-      <c r="T12" s="6" t="s">
+      <c r="T12" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="U12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V12" s="6">
+      <c r="U12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V12" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="6">
+    <row r="13" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="4">
         <v>1009</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="G13" s="6">
+      <c r="D13" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G13" s="4">
         <v>6</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="4">
         <v>20</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="4">
         <v>9999</v>
       </c>
-      <c r="J13" s="6">
-        <v>0</v>
-      </c>
-      <c r="K13" s="6">
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
         <v>3</v>
       </c>
-      <c r="L13" s="6">
-        <v>0</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O13" s="6">
-        <v>1</v>
-      </c>
-      <c r="P13" s="6">
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O13" s="4">
+        <v>1</v>
+      </c>
+      <c r="P13" s="4">
         <v>9</v>
       </c>
-      <c r="Q13" s="2">
-        <v>0</v>
-      </c>
-      <c r="R13" s="6">
+      <c r="Q13" s="4">
+        <v>0</v>
+      </c>
+      <c r="R13" s="4">
         <v>100</v>
       </c>
-      <c r="S13" s="6">
+      <c r="S13" s="4">
         <v>30</v>
       </c>
-      <c r="T13" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="U13" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V13" s="6">
+      <c r="T13" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V13" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="2">
+    <row r="14" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14">
         <v>2004</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="C14" t="s">
+        <v>294</v>
+      </c>
+      <c r="D14" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" t="s">
         <v>109</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G14" s="2">
+      <c r="F14" t="s">
+        <v>164</v>
+      </c>
+      <c r="G14">
         <v>2</v>
       </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2">
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>10</v>
       </c>
-      <c r="L14" s="2">
-        <v>0</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O14" s="2">
-        <v>0</v>
-      </c>
-      <c r="P14" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="2">
-        <v>0</v>
-      </c>
-      <c r="R14" s="2">
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="s">
+        <v>94</v>
+      </c>
+      <c r="N14" t="s">
+        <v>94</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
         <v>100</v>
       </c>
-      <c r="S14" s="2">
+      <c r="S14">
         <v>30</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V14" s="2">
+      <c r="T14" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="U14" t="s">
+        <v>94</v>
+      </c>
+      <c r="V14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2">
+    <row r="15" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15">
         <v>2001</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="C15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D15" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15">
         <v>2</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15">
         <v>2</v>
       </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2">
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
         <v>5</v>
       </c>
-      <c r="L15" s="2">
-        <v>0</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O15" s="2">
-        <v>1</v>
-      </c>
-      <c r="P15" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="2">
-        <v>0</v>
-      </c>
-      <c r="R15" s="2">
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
+        <v>94</v>
+      </c>
+      <c r="N15" t="s">
+        <v>94</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
         <v>100</v>
       </c>
-      <c r="S15" s="2">
+      <c r="S15">
         <v>120</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="U15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V15" s="2">
+      <c r="T15" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="U15" t="s">
+        <v>94</v>
+      </c>
+      <c r="V15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="2">
+    <row r="16" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16">
         <v>2001</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="C16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D16" t="s">
+        <v>175</v>
+      </c>
+      <c r="E16" t="s">
+        <v>178</v>
+      </c>
+      <c r="F16" t="s">
+        <v>185</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="s">
+        <v>94</v>
+      </c>
+      <c r="N16" t="s">
+        <v>94</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>120</v>
+      </c>
+      <c r="T16" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="G16" s="2">
-        <v>2</v>
-      </c>
-      <c r="H16" s="2">
-        <v>3</v>
-      </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2">
-        <v>0</v>
-      </c>
-      <c r="K16" s="2">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2">
-        <v>0</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O16" s="2">
-        <v>1</v>
-      </c>
-      <c r="P16" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="2">
-        <v>0</v>
-      </c>
-      <c r="R16" s="2">
-        <v>100</v>
-      </c>
-      <c r="S16" s="2">
-        <v>120</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="U16" s="2" t="s">
+      <c r="U16" t="s">
         <v>51</v>
       </c>
-      <c r="V16" s="2">
+      <c r="V16">
         <v>2</v>
       </c>
     </row>
@@ -5543,7 +5565,7 @@
         <v>90</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>89</v>
@@ -5578,7 +5600,7 @@
       <c r="P17" s="4">
         <v>1</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="4">
         <v>0</v>
       </c>
       <c r="R17" s="4">
@@ -5597,3177 +5619,3177 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="2">
+    <row r="18" spans="1:22" s="9" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="9">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="9">
         <v>2005</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="G18" s="2">
+      <c r="C18" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="G18" s="9">
         <v>2</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="9">
         <v>4</v>
       </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2">
-        <v>0</v>
-      </c>
-      <c r="K18" s="2">
+      <c r="I18" s="9">
+        <v>1</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
         <v>3</v>
       </c>
-      <c r="L18" s="2">
-        <v>0</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O18" s="2">
-        <v>1</v>
-      </c>
-      <c r="P18" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="2">
-        <v>1</v>
-      </c>
-      <c r="R18" s="2">
+      <c r="L18" s="9">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="O18" s="9">
+        <v>1</v>
+      </c>
+      <c r="P18" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>1</v>
+      </c>
+      <c r="R18" s="9">
         <v>100</v>
       </c>
-      <c r="S18" s="2">
+      <c r="S18" s="9">
         <v>30</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="U18" s="2" t="s">
+      <c r="T18" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="U18" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="V18" s="2">
+      <c r="V18" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:22" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="2">
+    <row r="19" spans="1:22" s="9" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="9">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="9">
         <v>2003</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="C19" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G19" s="2">
+      <c r="F19" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G19" s="9">
         <v>2</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="9">
         <v>3</v>
       </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2">
-        <v>0</v>
-      </c>
-      <c r="K19" s="2">
+      <c r="I19" s="9">
+        <v>1</v>
+      </c>
+      <c r="J19" s="9">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9">
         <v>5</v>
       </c>
-      <c r="L19" s="2">
-        <v>0</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O19" s="2">
-        <v>1</v>
-      </c>
-      <c r="P19" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="2">
-        <v>0</v>
-      </c>
-      <c r="R19" s="2">
+      <c r="L19" s="9">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O19" s="9">
+        <v>1</v>
+      </c>
+      <c r="P19" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>0</v>
+      </c>
+      <c r="R19" s="9">
         <v>100</v>
       </c>
-      <c r="S19" s="2">
+      <c r="S19" s="9">
         <v>30</v>
       </c>
-      <c r="T19" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="U19" s="2" t="s">
+      <c r="T19" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="U19" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="V19" s="2">
+      <c r="V19" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:22" s="6" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="6">
+    <row r="20" spans="1:22" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="4">
         <v>2003</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="D20" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G20" s="4">
         <v>2</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="4">
         <v>20</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="4">
         <v>9999</v>
       </c>
-      <c r="J20" s="6">
-        <v>0</v>
-      </c>
-      <c r="K20" s="6">
+      <c r="J20" s="4">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4">
         <v>5</v>
       </c>
-      <c r="L20" s="6">
-        <v>0</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O20" s="6">
-        <v>1</v>
-      </c>
-      <c r="P20" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="2">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6">
+      <c r="L20" s="4">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O20" s="4">
+        <v>1</v>
+      </c>
+      <c r="P20" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>0</v>
+      </c>
+      <c r="R20" s="4">
         <v>100</v>
       </c>
-      <c r="S20" s="6">
+      <c r="S20" s="4">
         <v>30</v>
       </c>
-      <c r="T20" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="U20" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V20" s="6">
+      <c r="T20" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V20" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:22" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="2">
+    <row r="21" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21">
         <v>3006</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="C21" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" t="s">
         <v>157</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="G21" s="2">
+      <c r="E21" t="s">
+        <v>156</v>
+      </c>
+      <c r="F21" t="s">
+        <v>232</v>
+      </c>
+      <c r="G21">
         <v>2</v>
       </c>
-      <c r="H21" s="2">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2">
-        <v>0</v>
-      </c>
-      <c r="K21" s="2">
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
         <v>5</v>
       </c>
-      <c r="L21" s="2">
-        <v>0</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O21" s="2">
-        <v>0</v>
-      </c>
-      <c r="P21" s="2">
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="s">
+        <v>94</v>
+      </c>
+      <c r="N21" t="s">
+        <v>94</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
         <v>2</v>
       </c>
-      <c r="Q21" s="2">
-        <v>0</v>
-      </c>
-      <c r="R21" s="2">
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
         <v>100</v>
       </c>
-      <c r="S21" s="2">
+      <c r="S21">
         <v>30</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="U21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V21" s="2">
+      <c r="T21" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="U21" t="s">
+        <v>94</v>
+      </c>
+      <c r="V21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22" s="2" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="2">
+    <row r="22" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22">
         <v>3001</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="C22" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" t="s">
         <v>16</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="E22" t="s">
+        <v>230</v>
+      </c>
+      <c r="F22" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22">
         <v>2</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22">
         <v>2</v>
       </c>
-      <c r="I22" s="2">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2">
-        <v>1</v>
-      </c>
-      <c r="K22" s="2">
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
         <v>5</v>
       </c>
-      <c r="L22" s="2">
-        <v>0</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O22" s="2">
-        <v>1</v>
-      </c>
-      <c r="P22" s="2">
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="s">
+        <v>94</v>
+      </c>
+      <c r="N22" t="s">
+        <v>239</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
         <v>2</v>
       </c>
-      <c r="Q22" s="2">
-        <v>0</v>
-      </c>
-      <c r="R22" s="2">
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
         <v>100</v>
       </c>
-      <c r="S22" s="2">
+      <c r="S22">
         <v>30</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="U22" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V22" s="2">
+      <c r="T22" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="U22" t="s">
+        <v>94</v>
+      </c>
+      <c r="V22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="2">
+    <row r="23" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23">
         <v>3002</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="C23" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23">
         <v>4</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23">
         <v>3</v>
       </c>
-      <c r="I23" s="2">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2">
-        <v>0</v>
-      </c>
-      <c r="K23" s="2">
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
         <v>5</v>
       </c>
-      <c r="L23" s="2">
-        <v>0</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O23" s="2">
-        <v>1</v>
-      </c>
-      <c r="P23" s="2">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="s">
+        <v>94</v>
+      </c>
+      <c r="N23" t="s">
+        <v>239</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
         <v>2</v>
       </c>
-      <c r="Q23" s="2">
-        <v>0</v>
-      </c>
-      <c r="R23" s="2">
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
         <v>100</v>
       </c>
-      <c r="S23" s="2">
+      <c r="S23">
         <v>30</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="U23" s="2" t="s">
+      <c r="T23" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="U23" t="s">
         <v>16</v>
       </c>
-      <c r="V23" s="2">
+      <c r="V23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="2">
+    <row r="24" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="9">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="9">
         <v>3003</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="C24" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="E24" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="9">
         <v>4</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="9">
         <v>4</v>
       </c>
-      <c r="I24" s="2">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2">
-        <v>0</v>
-      </c>
-      <c r="K24" s="2">
+      <c r="I24" s="9">
+        <v>1</v>
+      </c>
+      <c r="J24" s="9">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
         <v>3</v>
       </c>
-      <c r="L24" s="2">
-        <v>0</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O24" s="2">
-        <v>1</v>
-      </c>
-      <c r="P24" s="2">
+      <c r="L24" s="9">
+        <v>0</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="O24" s="9">
+        <v>1</v>
+      </c>
+      <c r="P24" s="9">
         <v>2</v>
       </c>
-      <c r="Q24" s="2">
-        <v>1</v>
-      </c>
-      <c r="R24" s="2">
+      <c r="Q24" s="9">
+        <v>1</v>
+      </c>
+      <c r="R24" s="9">
         <v>100</v>
       </c>
-      <c r="S24" s="2">
+      <c r="S24" s="9">
         <v>30</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="U24" s="2" t="s">
+      <c r="T24" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="U24" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V24" s="2">
+      <c r="V24" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="2">
+    <row r="25" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="9">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="9">
         <v>3008</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="G25" s="2">
+      <c r="C25" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="G25" s="9">
         <v>4</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="9">
         <v>4</v>
       </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2">
-        <v>0</v>
-      </c>
-      <c r="K25" s="2">
+      <c r="I25" s="9">
+        <v>0</v>
+      </c>
+      <c r="J25" s="9">
+        <v>0</v>
+      </c>
+      <c r="K25" s="9">
         <v>3</v>
       </c>
-      <c r="L25" s="2">
-        <v>0</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O25" s="2">
-        <v>1</v>
-      </c>
-      <c r="P25" s="2">
+      <c r="L25" s="9">
+        <v>0</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="O25" s="9">
+        <v>1</v>
+      </c>
+      <c r="P25" s="9">
         <v>2</v>
       </c>
-      <c r="Q25" s="2">
-        <v>1</v>
-      </c>
-      <c r="R25" s="2">
+      <c r="Q25" s="9">
+        <v>1</v>
+      </c>
+      <c r="R25" s="9">
         <v>100</v>
       </c>
-      <c r="S25" s="2">
+      <c r="S25" s="9">
         <v>30</v>
       </c>
-      <c r="T25" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="U25" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V25" s="2">
+      <c r="T25" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="U25" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V25" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="2">
+    <row r="26" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26">
         <v>3004</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="C26" t="s">
+        <v>303</v>
+      </c>
+      <c r="D26" t="s">
         <v>115</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" t="s">
         <v>113</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" t="s">
         <v>114</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26">
         <v>4</v>
       </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2">
-        <v>0</v>
-      </c>
-      <c r="K26" s="2">
-        <v>1</v>
-      </c>
-      <c r="L26" s="2">
-        <v>0</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O26" s="2">
-        <v>0</v>
-      </c>
-      <c r="P26" s="2">
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="s">
+        <v>94</v>
+      </c>
+      <c r="N26" t="s">
+        <v>94</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
         <v>2</v>
       </c>
-      <c r="Q26" s="2">
-        <v>0</v>
-      </c>
-      <c r="R26" s="2">
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
         <v>100</v>
       </c>
-      <c r="S26" s="2">
+      <c r="S26">
         <v>30</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="U26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V26" s="2">
+      <c r="T26" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="U26" t="s">
+        <v>94</v>
+      </c>
+      <c r="V26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="2">
+    <row r="27" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27">
         <v>3007</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="G27" s="2">
+      <c r="C27" t="s">
+        <v>302</v>
+      </c>
+      <c r="D27" t="s">
+        <v>251</v>
+      </c>
+      <c r="E27" t="s">
+        <v>275</v>
+      </c>
+      <c r="F27" t="s">
+        <v>252</v>
+      </c>
+      <c r="G27">
         <v>4</v>
       </c>
-      <c r="H27" s="2">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2">
-        <v>0</v>
-      </c>
-      <c r="K27" s="2">
-        <v>1</v>
-      </c>
-      <c r="L27" s="2">
-        <v>0</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O27" s="2">
-        <v>0</v>
-      </c>
-      <c r="P27" s="2">
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="s">
+        <v>94</v>
+      </c>
+      <c r="N27" t="s">
+        <v>94</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
         <v>2</v>
       </c>
-      <c r="Q27" s="2">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2">
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
         <v>100</v>
       </c>
-      <c r="S27" s="2">
+      <c r="S27">
         <v>30</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="U27" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V27" s="2">
+      <c r="T27" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="U27" t="s">
+        <v>94</v>
+      </c>
+      <c r="V27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:22" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="6">
+    <row r="28" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="4">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="4">
         <v>3005</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="4">
         <v>4</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H28" s="4">
         <v>20</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="4">
         <v>9999</v>
       </c>
-      <c r="J28" s="6">
-        <v>0</v>
-      </c>
-      <c r="K28" s="6">
+      <c r="J28" s="4">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4">
         <v>5</v>
       </c>
-      <c r="L28" s="6">
-        <v>0</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O28" s="6">
-        <v>1</v>
-      </c>
-      <c r="P28" s="6">
+      <c r="L28" s="4">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O28" s="4">
+        <v>1</v>
+      </c>
+      <c r="P28" s="4">
         <v>2</v>
       </c>
-      <c r="Q28" s="2">
-        <v>0</v>
-      </c>
-      <c r="R28" s="6">
+      <c r="Q28" s="4">
+        <v>0</v>
+      </c>
+      <c r="R28" s="4">
         <v>100</v>
       </c>
-      <c r="S28" s="6">
+      <c r="S28" s="4">
         <v>30</v>
       </c>
-      <c r="T28" s="8" t="s">
+      <c r="T28" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="U28" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V28" s="6">
+      <c r="U28" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V28" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:22" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="6">
+    <row r="29" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="4">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="4">
         <v>3005</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="F29" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="G29" s="6">
+      <c r="G29" s="4">
         <v>4</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="4">
         <v>10</v>
       </c>
-      <c r="I29" s="6">
+      <c r="I29" s="4">
         <v>9999</v>
       </c>
-      <c r="J29" s="6">
-        <v>0</v>
-      </c>
-      <c r="K29" s="6">
+      <c r="J29" s="4">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4">
         <v>5</v>
       </c>
-      <c r="L29" s="6">
-        <v>0</v>
-      </c>
-      <c r="M29" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N29" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O29" s="6">
-        <v>1</v>
-      </c>
-      <c r="P29" s="6">
+      <c r="L29" s="4">
+        <v>0</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O29" s="4">
+        <v>1</v>
+      </c>
+      <c r="P29" s="4">
         <v>2</v>
       </c>
-      <c r="Q29" s="2">
-        <v>0</v>
-      </c>
-      <c r="R29" s="6">
+      <c r="Q29" s="4">
+        <v>0</v>
+      </c>
+      <c r="R29" s="4">
         <v>100</v>
       </c>
-      <c r="S29" s="6">
+      <c r="S29" s="4">
         <v>30</v>
       </c>
-      <c r="T29" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="U29" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V29" s="6">
+      <c r="T29" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="U29" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V29" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:22" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="2">
+    <row r="30" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30">
         <v>4010</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="C30" t="s">
+        <v>306</v>
+      </c>
+      <c r="D30" t="s">
+        <v>151</v>
+      </c>
+      <c r="E30" t="s">
         <v>152</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" t="s">
         <v>153</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G30" s="2">
+      <c r="G30">
         <v>6</v>
       </c>
-      <c r="H30" s="2">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2">
-        <v>0</v>
-      </c>
-      <c r="K30" s="2">
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
         <v>5</v>
       </c>
-      <c r="L30" s="2">
-        <v>0</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O30" s="2">
-        <v>0</v>
-      </c>
-      <c r="P30" s="2">
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="s">
+        <v>94</v>
+      </c>
+      <c r="N30" t="s">
+        <v>94</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
         <v>3</v>
       </c>
-      <c r="Q30" s="2">
-        <v>0</v>
-      </c>
-      <c r="R30" s="2">
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
         <v>100</v>
       </c>
-      <c r="S30" s="2">
+      <c r="S30">
         <v>30</v>
       </c>
-      <c r="T30" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="U30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V30" s="2">
+      <c r="T30" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="U30" t="s">
+        <v>94</v>
+      </c>
+      <c r="V30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:22" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="2">
+    <row r="31" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31">
         <v>4011</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="C31" t="s">
+        <v>300</v>
+      </c>
+      <c r="D31" t="s">
+        <v>154</v>
+      </c>
+      <c r="E31" t="s">
+        <v>208</v>
+      </c>
+      <c r="F31" t="s">
         <v>155</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G31" s="2">
+      <c r="G31">
         <v>6</v>
       </c>
-      <c r="H31" s="2">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2">
-        <v>1</v>
-      </c>
-      <c r="J31" s="2">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2">
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
         <v>5</v>
       </c>
-      <c r="L31" s="2">
-        <v>0</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O31" s="2">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2">
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="s">
+        <v>94</v>
+      </c>
+      <c r="N31" t="s">
+        <v>94</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
         <v>3</v>
       </c>
-      <c r="Q31" s="2">
-        <v>0</v>
-      </c>
-      <c r="R31" s="2">
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
         <v>100</v>
       </c>
-      <c r="S31" s="2">
+      <c r="S31">
         <v>30</v>
       </c>
-      <c r="T31" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="U31" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V31" s="2">
+      <c r="T31" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="U31" t="s">
+        <v>94</v>
+      </c>
+      <c r="V31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:22" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="2">
+    <row r="32" spans="1:22" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="9">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="9">
         <v>4001</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="C32" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G32" s="2">
+      <c r="F32" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="G32" s="9">
         <v>6</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="9">
         <v>2</v>
       </c>
-      <c r="I32" s="2">
-        <v>1</v>
-      </c>
-      <c r="J32" s="2">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2">
+      <c r="I32" s="9">
+        <v>1</v>
+      </c>
+      <c r="J32" s="9">
+        <v>0</v>
+      </c>
+      <c r="K32" s="9">
         <v>3</v>
       </c>
-      <c r="L32" s="2">
-        <v>0</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O32" s="2">
-        <v>1</v>
-      </c>
-      <c r="P32" s="2">
+      <c r="L32" s="9">
+        <v>0</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O32" s="9">
+        <v>1</v>
+      </c>
+      <c r="P32" s="9">
         <v>3</v>
       </c>
-      <c r="Q32" s="2">
-        <v>0</v>
-      </c>
-      <c r="R32" s="2">
+      <c r="Q32" s="9">
+        <v>0</v>
+      </c>
+      <c r="R32" s="9">
         <v>85</v>
       </c>
-      <c r="S32" s="2">
+      <c r="S32" s="9">
         <v>10</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="U32" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="V32" s="2">
+      <c r="T32" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="U32" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="V32" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="2">
+    <row r="33" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="9">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="9">
         <v>4002</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="C33" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G33" s="2">
-        <v>1</v>
-      </c>
-      <c r="H33" s="2">
+      <c r="F33" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="G33" s="9">
+        <v>1</v>
+      </c>
+      <c r="H33" s="9">
         <v>4</v>
       </c>
-      <c r="I33" s="2">
-        <v>0</v>
-      </c>
-      <c r="J33" s="2">
-        <v>0</v>
-      </c>
-      <c r="K33" s="2">
+      <c r="I33" s="9">
+        <v>0</v>
+      </c>
+      <c r="J33" s="9">
+        <v>0</v>
+      </c>
+      <c r="K33" s="9">
         <v>3</v>
       </c>
-      <c r="L33" s="2">
-        <v>0</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O33" s="2">
-        <v>1</v>
-      </c>
-      <c r="P33" s="2">
+      <c r="L33" s="9">
+        <v>0</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O33" s="9">
+        <v>1</v>
+      </c>
+      <c r="P33" s="9">
         <v>3</v>
       </c>
-      <c r="Q33" s="2">
-        <v>0</v>
-      </c>
-      <c r="R33" s="2">
+      <c r="Q33" s="9">
+        <v>0</v>
+      </c>
+      <c r="R33" s="9">
         <v>100</v>
       </c>
-      <c r="S33" s="2">
+      <c r="S33" s="9">
         <v>15</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="U33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V33" s="2">
+      <c r="T33" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="U33" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V33" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="2">
+    <row r="34" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="9">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="9">
         <v>4010</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="C34" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="G34" s="9">
+        <v>1</v>
+      </c>
+      <c r="H34" s="9">
+        <v>4</v>
+      </c>
+      <c r="I34" s="9">
+        <v>1</v>
+      </c>
+      <c r="J34" s="9">
+        <v>0</v>
+      </c>
+      <c r="K34" s="9">
+        <v>3</v>
+      </c>
+      <c r="L34" s="9">
+        <v>0</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O34" s="9">
+        <v>1</v>
+      </c>
+      <c r="P34" s="9">
+        <v>3</v>
+      </c>
+      <c r="Q34" s="9">
+        <v>0</v>
+      </c>
+      <c r="R34" s="9">
+        <v>100</v>
+      </c>
+      <c r="S34" s="9">
+        <v>15</v>
+      </c>
+      <c r="T34" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="G34" s="2">
-        <v>1</v>
-      </c>
-      <c r="H34" s="2">
-        <v>4</v>
-      </c>
-      <c r="I34" s="2">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2">
-        <v>0</v>
-      </c>
-      <c r="K34" s="2">
-        <v>3</v>
-      </c>
-      <c r="L34" s="2">
-        <v>0</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O34" s="2">
-        <v>1</v>
-      </c>
-      <c r="P34" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q34" s="2">
-        <v>0</v>
-      </c>
-      <c r="R34" s="2">
-        <v>100</v>
-      </c>
-      <c r="S34" s="2">
-        <v>15</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="U34" s="2" t="s">
+      <c r="U34" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="V34" s="2">
+      <c r="V34" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="2">
+    <row r="35" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="9">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="9">
         <v>4011</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="C35" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="E35" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="G35" s="9">
+        <v>1</v>
+      </c>
+      <c r="H35" s="9">
+        <v>4</v>
+      </c>
+      <c r="I35" s="9">
+        <v>1</v>
+      </c>
+      <c r="J35" s="9">
+        <v>0</v>
+      </c>
+      <c r="K35" s="9">
+        <v>3</v>
+      </c>
+      <c r="L35" s="9">
+        <v>0</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O35" s="9">
+        <v>1</v>
+      </c>
+      <c r="P35" s="9">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>0</v>
+      </c>
+      <c r="R35" s="9">
+        <v>100</v>
+      </c>
+      <c r="S35" s="9">
+        <v>15</v>
+      </c>
+      <c r="T35" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="G35" s="2">
-        <v>1</v>
-      </c>
-      <c r="H35" s="2">
-        <v>4</v>
-      </c>
-      <c r="I35" s="2">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2">
-        <v>0</v>
-      </c>
-      <c r="K35" s="2">
-        <v>3</v>
-      </c>
-      <c r="L35" s="2">
-        <v>0</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O35" s="2">
-        <v>1</v>
-      </c>
-      <c r="P35" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="2">
-        <v>0</v>
-      </c>
-      <c r="R35" s="2">
-        <v>100</v>
-      </c>
-      <c r="S35" s="2">
-        <v>15</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="U35" s="2" t="s">
+      <c r="U35" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="V35" s="2">
+      <c r="V35" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="2">
+    <row r="36" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="9">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="9">
         <v>4012</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="C36" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F36" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G36" s="2">
-        <v>1</v>
-      </c>
-      <c r="H36" s="2">
+      <c r="E36" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="G36" s="9">
+        <v>1</v>
+      </c>
+      <c r="H36" s="9">
         <v>4</v>
       </c>
-      <c r="I36" s="2">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2">
-        <v>0</v>
-      </c>
-      <c r="K36" s="2">
-        <v>1</v>
-      </c>
-      <c r="L36" s="2">
-        <v>0</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O36" s="2">
-        <v>1</v>
-      </c>
-      <c r="P36" s="2">
+      <c r="I36" s="9">
+        <v>1</v>
+      </c>
+      <c r="J36" s="9">
+        <v>0</v>
+      </c>
+      <c r="K36" s="9">
+        <v>1</v>
+      </c>
+      <c r="L36" s="9">
+        <v>0</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N36" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O36" s="9">
+        <v>1</v>
+      </c>
+      <c r="P36" s="9">
         <v>3</v>
       </c>
-      <c r="Q36" s="2">
-        <v>0</v>
-      </c>
-      <c r="R36" s="2">
+      <c r="Q36" s="9">
+        <v>0</v>
+      </c>
+      <c r="R36" s="9">
         <v>100</v>
       </c>
-      <c r="S36" s="2">
+      <c r="S36" s="9">
         <v>15</v>
       </c>
-      <c r="T36" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="U36" s="2" t="s">
+      <c r="T36" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="U36" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="V36" s="2">
+      <c r="V36" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="2">
+    <row r="37" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="9">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="9">
         <v>4012</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="C37" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="G37" s="2">
-        <v>1</v>
-      </c>
-      <c r="H37" s="2">
+      <c r="E37" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="G37" s="9">
+        <v>1</v>
+      </c>
+      <c r="H37" s="9">
         <v>4</v>
       </c>
-      <c r="I37" s="2">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2">
-        <v>0</v>
-      </c>
-      <c r="K37" s="2">
-        <v>1</v>
-      </c>
-      <c r="L37" s="2">
-        <v>0</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O37" s="2">
-        <v>1</v>
-      </c>
-      <c r="P37" s="2">
+      <c r="I37" s="9">
+        <v>1</v>
+      </c>
+      <c r="J37" s="9">
+        <v>0</v>
+      </c>
+      <c r="K37" s="9">
+        <v>1</v>
+      </c>
+      <c r="L37" s="9">
+        <v>0</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N37" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O37" s="9">
+        <v>1</v>
+      </c>
+      <c r="P37" s="9">
         <v>3</v>
       </c>
-      <c r="Q37" s="2">
-        <v>0</v>
-      </c>
-      <c r="R37" s="2">
+      <c r="Q37" s="9">
+        <v>0</v>
+      </c>
+      <c r="R37" s="9">
         <v>100</v>
       </c>
-      <c r="S37" s="2">
+      <c r="S37" s="9">
         <v>15</v>
       </c>
-      <c r="T37" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="U37" s="2" t="s">
+      <c r="T37" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="U37" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="V37" s="2">
+      <c r="V37" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="2">
+    <row r="38" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="9">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="9">
         <v>4012</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="C38" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="F38" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="G38" s="2">
-        <v>1</v>
-      </c>
-      <c r="H38" s="2">
+      <c r="G38" s="9">
+        <v>1</v>
+      </c>
+      <c r="H38" s="9">
         <v>4</v>
       </c>
-      <c r="I38" s="2">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2">
-        <v>0</v>
-      </c>
-      <c r="K38" s="2">
-        <v>1</v>
-      </c>
-      <c r="L38" s="2">
-        <v>0</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O38" s="2">
-        <v>1</v>
-      </c>
-      <c r="P38" s="2">
+      <c r="I38" s="9">
+        <v>1</v>
+      </c>
+      <c r="J38" s="9">
+        <v>0</v>
+      </c>
+      <c r="K38" s="9">
+        <v>1</v>
+      </c>
+      <c r="L38" s="9">
+        <v>0</v>
+      </c>
+      <c r="M38" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N38" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O38" s="9">
+        <v>1</v>
+      </c>
+      <c r="P38" s="9">
         <v>3</v>
       </c>
-      <c r="Q38" s="2">
-        <v>0</v>
-      </c>
-      <c r="R38" s="2">
+      <c r="Q38" s="9">
+        <v>0</v>
+      </c>
+      <c r="R38" s="9">
         <v>100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="S38" s="9">
         <v>15</v>
       </c>
-      <c r="T38" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="U38" s="2" t="s">
+      <c r="T38" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="U38" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="V38" s="2">
+      <c r="V38" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:22" s="6" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="6">
+    <row r="39" spans="1:22" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="4">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="4">
         <v>4003</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G39" s="6">
+      <c r="G39" s="4">
         <v>3</v>
       </c>
-      <c r="H39" s="6">
+      <c r="H39" s="4">
         <v>2</v>
       </c>
-      <c r="I39" s="6">
+      <c r="I39" s="4">
         <v>9999</v>
       </c>
-      <c r="J39" s="6">
-        <v>0</v>
-      </c>
-      <c r="K39" s="6">
+      <c r="J39" s="4">
+        <v>0</v>
+      </c>
+      <c r="K39" s="4">
         <v>3</v>
       </c>
-      <c r="L39" s="6">
-        <v>0</v>
-      </c>
-      <c r="M39" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N39" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O39" s="6">
-        <v>1</v>
-      </c>
-      <c r="P39" s="6">
+      <c r="L39" s="4">
+        <v>0</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O39" s="4">
+        <v>1</v>
+      </c>
+      <c r="P39" s="4">
         <v>3</v>
       </c>
-      <c r="Q39" s="2">
-        <v>0</v>
-      </c>
-      <c r="R39" s="6">
+      <c r="Q39" s="4">
+        <v>0</v>
+      </c>
+      <c r="R39" s="4">
         <v>100</v>
       </c>
-      <c r="S39" s="6">
+      <c r="S39" s="4">
         <v>30</v>
       </c>
-      <c r="T39" s="8" t="s">
+      <c r="T39" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="U39" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V39" s="6">
+      <c r="U39" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V39" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="2">
+    <row r="40" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="9">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="9">
         <v>4004</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="C40" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G40" s="2">
+      <c r="E40" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="G40" s="9">
         <v>3</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="9">
         <v>3</v>
       </c>
-      <c r="I40" s="2">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2">
-        <v>0</v>
-      </c>
-      <c r="K40" s="2">
+      <c r="I40" s="9">
+        <v>1</v>
+      </c>
+      <c r="J40" s="9">
+        <v>0</v>
+      </c>
+      <c r="K40" s="9">
         <v>3</v>
       </c>
-      <c r="L40" s="2">
-        <v>0</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O40" s="2">
-        <v>1</v>
-      </c>
-      <c r="P40" s="2">
+      <c r="L40" s="9">
+        <v>0</v>
+      </c>
+      <c r="M40" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N40" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="O40" s="9">
+        <v>1</v>
+      </c>
+      <c r="P40" s="9">
         <v>3</v>
       </c>
-      <c r="Q40" s="2">
-        <v>1</v>
-      </c>
-      <c r="R40" s="2">
+      <c r="Q40" s="9">
+        <v>1</v>
+      </c>
+      <c r="R40" s="9">
         <v>100</v>
       </c>
-      <c r="S40" s="2">
+      <c r="S40" s="9">
         <v>30</v>
       </c>
-      <c r="T40" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="U40" s="2" t="s">
+      <c r="T40" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="U40" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="V40" s="2">
+      <c r="V40" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:22" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="6">
+    <row r="41" spans="1:22" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="4">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B41" s="4">
         <v>4005</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="4">
         <v>12</v>
       </c>
-      <c r="H41" s="6">
+      <c r="H41" s="4">
         <v>5</v>
       </c>
-      <c r="I41" s="6">
+      <c r="I41" s="4">
         <v>9999</v>
       </c>
-      <c r="J41" s="6">
-        <v>0</v>
-      </c>
-      <c r="K41" s="6">
+      <c r="J41" s="4">
+        <v>0</v>
+      </c>
+      <c r="K41" s="4">
         <v>3</v>
       </c>
-      <c r="L41" s="6">
-        <v>0</v>
-      </c>
-      <c r="M41" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N41" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O41" s="6">
-        <v>1</v>
-      </c>
-      <c r="P41" s="6">
+      <c r="L41" s="4">
+        <v>0</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O41" s="4">
+        <v>1</v>
+      </c>
+      <c r="P41" s="4">
         <v>3</v>
       </c>
-      <c r="Q41" s="2">
-        <v>0</v>
-      </c>
-      <c r="R41" s="6">
+      <c r="Q41" s="4">
+        <v>0</v>
+      </c>
+      <c r="R41" s="4">
         <v>100</v>
       </c>
-      <c r="S41" s="6">
+      <c r="S41" s="4">
         <v>30</v>
       </c>
-      <c r="T41" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="U41" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V41" s="6">
+      <c r="T41" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="U41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V41" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="6">
+    <row r="42" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="4">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B42" s="6">
+      <c r="B42" s="4">
         <v>4006</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="G42" s="6">
+      <c r="E42" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G42" s="4">
         <v>3</v>
       </c>
-      <c r="H42" s="6">
+      <c r="H42" s="4">
         <v>5</v>
       </c>
-      <c r="I42" s="6">
+      <c r="I42" s="4">
         <v>9999</v>
       </c>
-      <c r="J42" s="6">
-        <v>0</v>
-      </c>
-      <c r="K42" s="6">
+      <c r="J42" s="4">
+        <v>0</v>
+      </c>
+      <c r="K42" s="4">
         <v>3</v>
       </c>
-      <c r="L42" s="6">
-        <v>0</v>
-      </c>
-      <c r="M42" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N42" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="O42" s="6">
-        <v>1</v>
-      </c>
-      <c r="P42" s="6">
+      <c r="L42" s="4">
+        <v>0</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="O42" s="4">
+        <v>1</v>
+      </c>
+      <c r="P42" s="4">
         <v>3</v>
       </c>
-      <c r="Q42" s="2">
-        <v>0</v>
-      </c>
-      <c r="R42" s="6">
+      <c r="Q42" s="4">
+        <v>0</v>
+      </c>
+      <c r="R42" s="4">
         <v>100</v>
       </c>
-      <c r="S42" s="6">
+      <c r="S42" s="4">
         <v>30</v>
       </c>
-      <c r="T42" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="U42" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V42" s="6">
+      <c r="T42" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="U42" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V42" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:22" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="2">
+    <row r="43" spans="1:22" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="9">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="9">
         <v>4007</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="C43" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="G43" s="9">
+        <v>3</v>
+      </c>
+      <c r="H43" s="9">
+        <v>5</v>
+      </c>
+      <c r="I43" s="9">
+        <v>1</v>
+      </c>
+      <c r="J43" s="9">
+        <v>0</v>
+      </c>
+      <c r="K43" s="9">
+        <v>1</v>
+      </c>
+      <c r="L43" s="9">
+        <v>0</v>
+      </c>
+      <c r="M43" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N43" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O43" s="9">
+        <v>1</v>
+      </c>
+      <c r="P43" s="9">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>0</v>
+      </c>
+      <c r="R43" s="9">
+        <v>100</v>
+      </c>
+      <c r="S43" s="9">
+        <v>15</v>
+      </c>
+      <c r="T43" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="G43" s="2">
-        <v>3</v>
-      </c>
-      <c r="H43" s="2">
+      <c r="U43" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="V43" s="9">
         <v>5</v>
       </c>
-      <c r="I43" s="2">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2">
-        <v>0</v>
-      </c>
-      <c r="K43" s="2">
-        <v>1</v>
-      </c>
-      <c r="L43" s="2">
-        <v>0</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O43" s="2">
-        <v>1</v>
-      </c>
-      <c r="P43" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="2">
-        <v>0</v>
-      </c>
-      <c r="R43" s="2">
-        <v>100</v>
-      </c>
-      <c r="S43" s="2">
-        <v>15</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="U43" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="V43" s="2">
-        <v>5</v>
-      </c>
     </row>
-    <row r="44" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="6">
+    <row r="44" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="4">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B44" s="6">
+      <c r="B44" s="4">
         <v>4007</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="G44" s="6">
+      <c r="F44" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G44" s="4">
         <v>3</v>
       </c>
-      <c r="H44" s="6">
+      <c r="H44" s="4">
         <v>5</v>
       </c>
-      <c r="I44" s="6">
+      <c r="I44" s="4">
         <v>9999</v>
       </c>
-      <c r="J44" s="6">
-        <v>0</v>
-      </c>
-      <c r="K44" s="6">
+      <c r="J44" s="4">
+        <v>0</v>
+      </c>
+      <c r="K44" s="4">
         <v>3</v>
       </c>
-      <c r="L44" s="6">
-        <v>0</v>
-      </c>
-      <c r="M44" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N44" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="O44" s="6">
-        <v>1</v>
-      </c>
-      <c r="P44" s="6">
+      <c r="L44" s="4">
+        <v>0</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="O44" s="4">
+        <v>1</v>
+      </c>
+      <c r="P44" s="4">
         <v>3</v>
       </c>
-      <c r="Q44" s="2">
-        <v>0</v>
-      </c>
-      <c r="R44" s="6">
+      <c r="Q44" s="4">
+        <v>0</v>
+      </c>
+      <c r="R44" s="4">
         <v>100</v>
       </c>
-      <c r="S44" s="6">
+      <c r="S44" s="4">
         <v>30</v>
       </c>
-      <c r="T44" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="U44" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V44" s="6">
+      <c r="T44" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="U44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V44" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="6">
+    <row r="45" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="4">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="4">
         <v>4008</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F45" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="G45" s="6">
+      <c r="F45" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="G45" s="4">
         <v>3</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45" s="4">
         <v>5</v>
       </c>
-      <c r="I45" s="6">
+      <c r="I45" s="4">
         <v>9999</v>
       </c>
-      <c r="J45" s="6">
-        <v>0</v>
-      </c>
-      <c r="K45" s="6">
+      <c r="J45" s="4">
+        <v>0</v>
+      </c>
+      <c r="K45" s="4">
         <v>3</v>
       </c>
-      <c r="L45" s="6">
-        <v>0</v>
-      </c>
-      <c r="M45" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N45" s="6" t="s">
+      <c r="L45" s="4">
+        <v>0</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="O45" s="4">
+        <v>1</v>
+      </c>
+      <c r="P45" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="4">
+        <v>0</v>
+      </c>
+      <c r="R45" s="4">
+        <v>100</v>
+      </c>
+      <c r="S45" s="4">
+        <v>30</v>
+      </c>
+      <c r="T45" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="O45" s="6">
-        <v>1</v>
-      </c>
-      <c r="P45" s="6">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="2">
-        <v>0</v>
-      </c>
-      <c r="R45" s="6">
-        <v>100</v>
-      </c>
-      <c r="S45" s="6">
-        <v>30</v>
-      </c>
-      <c r="T45" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="U45" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V45" s="6">
+      <c r="U45" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V45" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="6">
+    <row r="46" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="4">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B46" s="6">
+      <c r="B46" s="4">
         <v>4009</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="G46" s="6">
+      <c r="F46" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G46" s="4">
         <v>3</v>
       </c>
-      <c r="H46" s="6">
+      <c r="H46" s="4">
         <v>8</v>
       </c>
-      <c r="I46" s="6">
+      <c r="I46" s="4">
         <v>9999</v>
       </c>
-      <c r="J46" s="6">
-        <v>0</v>
-      </c>
-      <c r="K46" s="6">
+      <c r="J46" s="4">
+        <v>0</v>
+      </c>
+      <c r="K46" s="4">
         <v>3</v>
       </c>
-      <c r="L46" s="6">
-        <v>0</v>
-      </c>
-      <c r="M46" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O46" s="6">
-        <v>1</v>
-      </c>
-      <c r="P46" s="6">
+      <c r="L46" s="4">
+        <v>0</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O46" s="4">
+        <v>1</v>
+      </c>
+      <c r="P46" s="4">
         <v>3</v>
       </c>
-      <c r="Q46" s="2">
-        <v>0</v>
-      </c>
-      <c r="R46" s="6">
+      <c r="Q46" s="4">
+        <v>0</v>
+      </c>
+      <c r="R46" s="4">
         <v>100</v>
       </c>
-      <c r="S46" s="6">
+      <c r="S46" s="4">
         <v>30</v>
       </c>
-      <c r="T46" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="U46" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V46" s="6">
+      <c r="T46" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="U46" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V46" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:22" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="6">
+    <row r="47" spans="1:22" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="4">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="4">
         <v>4013</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="F47" s="6" t="s">
+      <c r="D47" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G47" s="4">
+        <v>6</v>
+      </c>
+      <c r="H47" s="4">
+        <v>30</v>
+      </c>
+      <c r="I47" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J47" s="4">
+        <v>0</v>
+      </c>
+      <c r="K47" s="4">
+        <v>5</v>
+      </c>
+      <c r="L47" s="4">
+        <v>0</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O47" s="4">
+        <v>1</v>
+      </c>
+      <c r="P47" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="4">
+        <v>0</v>
+      </c>
+      <c r="R47" s="4">
+        <v>100</v>
+      </c>
+      <c r="S47" s="4">
+        <v>30</v>
+      </c>
+      <c r="T47" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="G47" s="6">
-        <v>6</v>
-      </c>
-      <c r="H47" s="6">
-        <v>30</v>
-      </c>
-      <c r="I47" s="6">
-        <v>9999</v>
-      </c>
-      <c r="J47" s="6">
-        <v>0</v>
-      </c>
-      <c r="K47" s="6">
-        <v>5</v>
-      </c>
-      <c r="L47" s="6">
-        <v>0</v>
-      </c>
-      <c r="M47" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N47" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O47" s="6">
-        <v>1</v>
-      </c>
-      <c r="P47" s="6">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="2">
-        <v>0</v>
-      </c>
-      <c r="R47" s="6">
-        <v>100</v>
-      </c>
-      <c r="S47" s="6">
-        <v>30</v>
-      </c>
-      <c r="T47" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="U47" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V47" s="6">
+      <c r="U47" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V47" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:22" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="6">
+    <row r="48" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="4">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B48" s="6">
+      <c r="B48" s="4">
         <v>5004</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="E48" s="6" t="s">
+      <c r="D48" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="G48" s="6">
+      <c r="E48" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G48" s="4">
         <v>6</v>
       </c>
-      <c r="H48" s="6">
-        <v>0</v>
-      </c>
-      <c r="I48" s="6">
+      <c r="H48" s="4">
+        <v>0</v>
+      </c>
+      <c r="I48" s="4">
         <v>9999</v>
       </c>
-      <c r="J48" s="6">
-        <v>0</v>
-      </c>
-      <c r="K48" s="6">
+      <c r="J48" s="4">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
         <v>5</v>
       </c>
-      <c r="L48" s="6">
-        <v>0</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O48" s="6">
-        <v>0</v>
-      </c>
-      <c r="P48" s="6">
+      <c r="L48" s="4">
+        <v>0</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O48" s="4">
+        <v>0</v>
+      </c>
+      <c r="P48" s="4">
         <v>4</v>
       </c>
-      <c r="Q48" s="2">
-        <v>0</v>
-      </c>
-      <c r="R48" s="6">
+      <c r="Q48" s="4">
+        <v>0</v>
+      </c>
+      <c r="R48" s="4">
         <v>100</v>
       </c>
-      <c r="S48" s="6">
+      <c r="S48" s="4">
         <v>30</v>
       </c>
-      <c r="T48" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="U48" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V48" s="6">
+      <c r="T48" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="U48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V48" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="2">
+    <row r="49" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49">
         <v>5007</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="G49" s="2">
+      <c r="C49" t="s">
+        <v>312</v>
+      </c>
+      <c r="D49" t="s">
+        <v>274</v>
+      </c>
+      <c r="E49" t="s">
+        <v>272</v>
+      </c>
+      <c r="F49" t="s">
+        <v>273</v>
+      </c>
+      <c r="G49">
         <v>6</v>
       </c>
-      <c r="H49" s="2">
-        <v>0</v>
-      </c>
-      <c r="I49" s="2">
-        <v>1</v>
-      </c>
-      <c r="J49" s="2">
-        <v>0</v>
-      </c>
-      <c r="K49" s="2">
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
         <v>10</v>
       </c>
-      <c r="L49" s="2">
-        <v>0</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O49" s="2">
-        <v>0</v>
-      </c>
-      <c r="P49" s="2">
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="s">
+        <v>94</v>
+      </c>
+      <c r="N49" t="s">
+        <v>94</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
         <v>4</v>
       </c>
-      <c r="Q49" s="2">
-        <v>0</v>
-      </c>
-      <c r="R49" s="2">
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
         <v>100</v>
       </c>
-      <c r="S49" s="2">
+      <c r="S49">
         <v>30</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="U49" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V49" s="2">
+      <c r="T49" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="U49" t="s">
+        <v>94</v>
+      </c>
+      <c r="V49">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:22" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="2">
+    <row r="50" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="9">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="9">
         <v>5001</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="C50" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G50" s="2">
+      <c r="F50" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="G50" s="9">
         <v>6</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="9">
         <v>3</v>
       </c>
-      <c r="I50" s="2">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2">
-        <v>0</v>
-      </c>
-      <c r="K50" s="2">
+      <c r="I50" s="9">
+        <v>1</v>
+      </c>
+      <c r="J50" s="9">
+        <v>0</v>
+      </c>
+      <c r="K50" s="9">
         <v>3</v>
       </c>
-      <c r="L50" s="2">
-        <v>0</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N50" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O50" s="2">
-        <v>1</v>
-      </c>
-      <c r="P50" s="2">
+      <c r="L50" s="9">
+        <v>0</v>
+      </c>
+      <c r="M50" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N50" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="O50" s="9">
+        <v>1</v>
+      </c>
+      <c r="P50" s="9">
         <v>4</v>
       </c>
-      <c r="Q50" s="2">
-        <v>0</v>
-      </c>
-      <c r="R50" s="2">
+      <c r="Q50" s="9">
+        <v>0</v>
+      </c>
+      <c r="R50" s="9">
         <v>100</v>
       </c>
-      <c r="S50" s="2">
+      <c r="S50" s="9">
         <v>15</v>
       </c>
-      <c r="T50" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="U50" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="V50" s="2">
+      <c r="T50" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="U50" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="V50" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="2">
+    <row r="51" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="9">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="9">
         <v>5002</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="C51" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="G51" s="2">
+      <c r="G51" s="9">
         <v>6</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="9">
         <v>3</v>
       </c>
-      <c r="I51" s="2">
-        <v>1</v>
-      </c>
-      <c r="J51" s="2">
-        <v>0</v>
-      </c>
-      <c r="K51" s="2">
+      <c r="I51" s="9">
+        <v>1</v>
+      </c>
+      <c r="J51" s="9">
+        <v>0</v>
+      </c>
+      <c r="K51" s="9">
         <v>3</v>
       </c>
-      <c r="L51" s="2">
-        <v>0</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O51" s="2">
-        <v>1</v>
-      </c>
-      <c r="P51" s="2">
+      <c r="L51" s="9">
+        <v>0</v>
+      </c>
+      <c r="M51" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N51" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O51" s="9">
+        <v>1</v>
+      </c>
+      <c r="P51" s="9">
         <v>4</v>
       </c>
-      <c r="Q51" s="2">
-        <v>0</v>
-      </c>
-      <c r="R51" s="2">
+      <c r="Q51" s="9">
+        <v>0</v>
+      </c>
+      <c r="R51" s="9">
         <v>100</v>
       </c>
-      <c r="S51" s="2">
+      <c r="S51" s="9">
         <v>30</v>
       </c>
-      <c r="T51" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="U51" s="2" t="s">
+      <c r="T51" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="U51" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="V51" s="2">
+      <c r="V51" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="2">
+    <row r="52" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="9">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="9">
         <v>5003</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F52" s="2" t="s">
+      <c r="C52" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="G52" s="2">
+      <c r="E52" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G52" s="9">
         <v>6</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52" s="9">
         <v>6</v>
       </c>
-      <c r="I52" s="2">
-        <v>0</v>
-      </c>
-      <c r="J52" s="2">
-        <v>0</v>
-      </c>
-      <c r="K52" s="2">
+      <c r="I52" s="9">
+        <v>0</v>
+      </c>
+      <c r="J52" s="9">
+        <v>0</v>
+      </c>
+      <c r="K52" s="9">
         <v>3</v>
       </c>
-      <c r="L52" s="2">
-        <v>0</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N52" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O52" s="2">
-        <v>1</v>
-      </c>
-      <c r="P52" s="2">
+      <c r="L52" s="9">
+        <v>0</v>
+      </c>
+      <c r="M52" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N52" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O52" s="9">
+        <v>1</v>
+      </c>
+      <c r="P52" s="9">
         <v>4</v>
       </c>
-      <c r="Q52" s="2">
-        <v>0</v>
-      </c>
-      <c r="R52" s="2">
+      <c r="Q52" s="9">
+        <v>0</v>
+      </c>
+      <c r="R52" s="9">
         <v>100</v>
       </c>
-      <c r="S52" s="2">
+      <c r="S52" s="9">
         <v>480</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="U52" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V52" s="2">
+      <c r="T52" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="U52" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V52" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="2">
+    <row r="53" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="9">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="9">
         <v>5005</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="C53" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D53" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="E53" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="G53" s="2">
+      <c r="F53" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="G53" s="9">
         <v>6</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="9">
         <v>3</v>
       </c>
-      <c r="I53" s="2">
-        <v>1</v>
-      </c>
-      <c r="J53" s="2">
-        <v>0</v>
-      </c>
-      <c r="K53" s="2">
+      <c r="I53" s="9">
+        <v>1</v>
+      </c>
+      <c r="J53" s="9">
+        <v>0</v>
+      </c>
+      <c r="K53" s="9">
         <v>3</v>
       </c>
-      <c r="L53" s="2">
-        <v>0</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O53" s="2">
-        <v>1</v>
-      </c>
-      <c r="P53" s="2">
+      <c r="L53" s="9">
+        <v>0</v>
+      </c>
+      <c r="M53" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="N53" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O53" s="9">
+        <v>1</v>
+      </c>
+      <c r="P53" s="9">
         <v>4</v>
       </c>
-      <c r="Q53" s="2">
-        <v>0</v>
-      </c>
-      <c r="R53" s="2">
+      <c r="Q53" s="9">
+        <v>0</v>
+      </c>
+      <c r="R53" s="9">
         <v>100</v>
       </c>
-      <c r="S53" s="2">
+      <c r="S53" s="9">
         <v>30</v>
       </c>
-      <c r="T53" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="U53" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="V53" s="2">
+      <c r="T53" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="U53" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="V53" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:22" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="2">
+    <row r="54" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="9">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="9">
         <v>5006</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F54" s="2" t="s">
+      <c r="C54" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="D54" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="G54" s="2">
+      <c r="E54" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="G54" s="9">
         <v>6</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54" s="9">
         <v>8</v>
       </c>
-      <c r="I54" s="2">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2">
-        <v>0</v>
-      </c>
-      <c r="K54" s="2">
-        <v>1</v>
-      </c>
-      <c r="L54" s="2">
-        <v>0</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N54" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O54" s="2">
-        <v>1</v>
-      </c>
-      <c r="P54" s="2">
+      <c r="I54" s="9">
+        <v>0</v>
+      </c>
+      <c r="J54" s="9">
+        <v>0</v>
+      </c>
+      <c r="K54" s="9">
+        <v>1</v>
+      </c>
+      <c r="L54" s="9">
+        <v>0</v>
+      </c>
+      <c r="M54" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N54" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="O54" s="9">
+        <v>1</v>
+      </c>
+      <c r="P54" s="9">
         <v>4</v>
       </c>
-      <c r="Q54" s="2">
-        <v>0</v>
-      </c>
-      <c r="R54" s="2">
+      <c r="Q54" s="9">
+        <v>0</v>
+      </c>
+      <c r="R54" s="9">
         <v>100</v>
       </c>
-      <c r="S54" s="2">
+      <c r="S54" s="9">
         <v>30</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="U54" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V54" s="2">
+      <c r="T54" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="U54" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V54" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="6">
+    <row r="55" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="4">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="4">
         <v>6001</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E55" s="6" t="s">
+      <c r="D55" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="E55" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G55" s="4">
         <v>6</v>
       </c>
-      <c r="H55" s="6">
+      <c r="H55" s="4">
         <v>3</v>
       </c>
-      <c r="I55" s="6">
+      <c r="I55" s="4">
         <v>9999</v>
       </c>
-      <c r="J55" s="6">
-        <v>0</v>
-      </c>
-      <c r="K55" s="6">
+      <c r="J55" s="4">
+        <v>0</v>
+      </c>
+      <c r="K55" s="4">
         <v>10</v>
       </c>
-      <c r="L55" s="6">
-        <v>0</v>
-      </c>
-      <c r="M55" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N55" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O55" s="6">
-        <v>1</v>
-      </c>
-      <c r="P55" s="6">
+      <c r="L55" s="4">
+        <v>0</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N55" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O55" s="4">
+        <v>1</v>
+      </c>
+      <c r="P55" s="4">
         <v>5</v>
       </c>
-      <c r="Q55" s="2">
-        <v>0</v>
-      </c>
-      <c r="R55" s="6">
+      <c r="Q55" s="4">
+        <v>0</v>
+      </c>
+      <c r="R55" s="4">
         <v>100</v>
       </c>
-      <c r="S55" s="6">
+      <c r="S55" s="4">
         <v>30</v>
       </c>
-      <c r="T55" s="6" t="s">
+      <c r="T55" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="U55" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V55" s="6">
+      <c r="U55" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V55" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:22" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="2">
+    <row r="56" spans="1:22" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="9">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="9">
         <v>6002</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D56" s="2" t="s">
+      <c r="C56" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D56" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="G56" s="2">
+      <c r="G56" s="9">
         <v>6</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H56" s="9">
         <v>2</v>
       </c>
-      <c r="I56" s="2">
-        <v>0</v>
-      </c>
-      <c r="J56" s="2">
-        <v>0</v>
-      </c>
-      <c r="K56" s="2">
+      <c r="I56" s="9">
+        <v>0</v>
+      </c>
+      <c r="J56" s="9">
+        <v>0</v>
+      </c>
+      <c r="K56" s="9">
         <v>5</v>
       </c>
-      <c r="L56" s="2">
-        <v>0</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N56" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O56" s="2">
-        <v>1</v>
-      </c>
-      <c r="P56" s="2">
+      <c r="L56" s="9">
+        <v>0</v>
+      </c>
+      <c r="M56" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N56" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O56" s="9">
+        <v>1</v>
+      </c>
+      <c r="P56" s="9">
         <v>5</v>
       </c>
-      <c r="Q56" s="2">
-        <v>0</v>
-      </c>
-      <c r="R56" s="2">
+      <c r="Q56" s="9">
+        <v>0</v>
+      </c>
+      <c r="R56" s="9">
         <v>100</v>
       </c>
-      <c r="S56" s="2">
+      <c r="S56" s="9">
         <v>30</v>
       </c>
-      <c r="T56" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="U56" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V56" s="2">
+      <c r="T56" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="U56" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V56" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:22" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="2">
+    <row r="57" spans="1:22" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="9">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="9">
         <v>6004</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G57" s="2">
+      <c r="C57" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="G57" s="9">
         <v>6</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H57" s="9">
         <v>5</v>
       </c>
-      <c r="I57" s="2">
-        <v>0</v>
-      </c>
-      <c r="J57" s="2">
-        <v>0</v>
-      </c>
-      <c r="K57" s="2">
+      <c r="I57" s="9">
+        <v>0</v>
+      </c>
+      <c r="J57" s="9">
+        <v>0</v>
+      </c>
+      <c r="K57" s="9">
         <v>3</v>
       </c>
-      <c r="L57" s="2">
-        <v>0</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N57" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O57" s="2">
-        <v>1</v>
-      </c>
-      <c r="P57" s="2">
+      <c r="L57" s="9">
+        <v>0</v>
+      </c>
+      <c r="M57" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N57" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="O57" s="9">
+        <v>1</v>
+      </c>
+      <c r="P57" s="9">
         <v>5</v>
       </c>
-      <c r="Q57" s="2">
-        <v>1</v>
-      </c>
-      <c r="R57" s="2">
+      <c r="Q57" s="9">
+        <v>1</v>
+      </c>
+      <c r="R57" s="9">
         <v>100</v>
       </c>
-      <c r="S57" s="2">
+      <c r="S57" s="9">
         <v>30</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="U57" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V57" s="2">
+      <c r="T57" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="U57" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V57" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:22" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="2">
+    <row r="58" spans="1:22" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="9">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="9">
         <v>6005</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="G58" s="2">
+      <c r="C58" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="G58" s="9">
         <v>6</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H58" s="9">
         <v>5</v>
       </c>
-      <c r="I58" s="2">
-        <v>1</v>
-      </c>
-      <c r="J58" s="2">
-        <v>0</v>
-      </c>
-      <c r="K58" s="2">
+      <c r="I58" s="9">
+        <v>1</v>
+      </c>
+      <c r="J58" s="9">
+        <v>0</v>
+      </c>
+      <c r="K58" s="9">
         <v>3</v>
       </c>
-      <c r="L58" s="2">
-        <v>0</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N58" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O58" s="2">
-        <v>1</v>
-      </c>
-      <c r="P58" s="2">
+      <c r="L58" s="9">
+        <v>0</v>
+      </c>
+      <c r="M58" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N58" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="O58" s="9">
+        <v>1</v>
+      </c>
+      <c r="P58" s="9">
         <v>5</v>
       </c>
-      <c r="Q58" s="2">
-        <v>1</v>
-      </c>
-      <c r="R58" s="2">
+      <c r="Q58" s="9">
+        <v>1</v>
+      </c>
+      <c r="R58" s="9">
         <v>100</v>
       </c>
-      <c r="S58" s="2">
+      <c r="S58" s="9">
         <v>30</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="U58" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V58" s="2">
+      <c r="T58" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="U58" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V58" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="6">
+    <row r="59" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="4">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="4">
         <v>6003</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D59" s="6" t="s">
+      <c r="C59" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F59" s="6" t="s">
+      <c r="F59" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G59" s="6">
+      <c r="G59" s="4">
         <v>6</v>
       </c>
-      <c r="H59" s="6">
+      <c r="H59" s="4">
         <v>3</v>
       </c>
-      <c r="I59" s="6">
+      <c r="I59" s="4">
         <v>9999</v>
       </c>
-      <c r="J59" s="6">
-        <v>0</v>
-      </c>
-      <c r="K59" s="6">
-        <v>1</v>
-      </c>
-      <c r="L59" s="6">
-        <v>0</v>
-      </c>
-      <c r="M59" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N59" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O59" s="6">
-        <v>1</v>
-      </c>
-      <c r="P59" s="6">
+      <c r="J59" s="4">
+        <v>0</v>
+      </c>
+      <c r="K59" s="4">
+        <v>1</v>
+      </c>
+      <c r="L59" s="4">
+        <v>0</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N59" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O59" s="4">
+        <v>1</v>
+      </c>
+      <c r="P59" s="4">
         <v>5</v>
       </c>
-      <c r="Q59" s="2">
-        <v>0</v>
-      </c>
-      <c r="R59" s="6">
+      <c r="Q59" s="4">
+        <v>0</v>
+      </c>
+      <c r="R59" s="4">
         <v>100</v>
       </c>
-      <c r="S59" s="6">
+      <c r="S59" s="4">
         <v>30</v>
       </c>
-      <c r="T59" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="U59" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V59" s="6">
+      <c r="T59" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="U59" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V59" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="7">
+    <row r="60" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="5">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="5">
         <v>7001</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="E60" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F60" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G60" s="7">
+      <c r="G60" s="5">
         <v>6</v>
       </c>
-      <c r="H60" s="7">
+      <c r="H60" s="5">
         <v>12</v>
       </c>
-      <c r="I60" s="7">
-        <v>0</v>
-      </c>
-      <c r="J60" s="7">
-        <v>0</v>
-      </c>
-      <c r="K60" s="7">
-        <v>1</v>
-      </c>
-      <c r="L60" s="7">
-        <v>0</v>
-      </c>
-      <c r="M60" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N60" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O60" s="7">
-        <v>1</v>
-      </c>
-      <c r="P60" s="7">
+      <c r="I60" s="5">
+        <v>0</v>
+      </c>
+      <c r="J60" s="5">
+        <v>0</v>
+      </c>
+      <c r="K60" s="5">
+        <v>1</v>
+      </c>
+      <c r="L60" s="5">
+        <v>0</v>
+      </c>
+      <c r="M60" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N60" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O60" s="5">
+        <v>1</v>
+      </c>
+      <c r="P60" s="5">
         <v>6</v>
       </c>
       <c r="Q60" s="2">
         <v>0</v>
       </c>
-      <c r="R60" s="7">
+      <c r="R60" s="5">
         <v>100</v>
       </c>
-      <c r="S60" s="7">
+      <c r="S60" s="5">
         <v>30</v>
       </c>
-      <c r="T60" s="7" t="s">
+      <c r="T60" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="U60" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="V60" s="7">
+      <c r="U60" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="V60" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:22" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="7">
+    <row r="61" spans="1:22" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="5">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="5">
         <v>7002</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="E61" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="F61" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G61" s="7">
+      <c r="G61" s="5">
         <v>18</v>
       </c>
-      <c r="H61" s="7">
+      <c r="H61" s="5">
         <v>15</v>
       </c>
-      <c r="I61" s="7">
-        <v>0</v>
-      </c>
-      <c r="J61" s="7">
-        <v>0</v>
-      </c>
-      <c r="K61" s="7">
-        <v>1</v>
-      </c>
-      <c r="L61" s="7">
-        <v>0</v>
-      </c>
-      <c r="M61" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N61" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O61" s="7">
-        <v>1</v>
-      </c>
-      <c r="P61" s="7">
+      <c r="I61" s="5">
+        <v>0</v>
+      </c>
+      <c r="J61" s="5">
+        <v>0</v>
+      </c>
+      <c r="K61" s="5">
+        <v>1</v>
+      </c>
+      <c r="L61" s="5">
+        <v>0</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N61" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O61" s="5">
+        <v>1</v>
+      </c>
+      <c r="P61" s="5">
         <v>6</v>
       </c>
       <c r="Q61" s="2">
         <v>0</v>
       </c>
-      <c r="R61" s="7">
+      <c r="R61" s="5">
         <v>100</v>
       </c>
-      <c r="S61" s="7">
+      <c r="S61" s="5">
         <v>30</v>
       </c>
-      <c r="T61" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="U61" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="V61" s="7">
+      <c r="T61" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="U61" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="V61" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="7">
+    <row r="62" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="5">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="5">
         <v>8001</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="D62" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E62" s="7" t="s">
+      <c r="E62" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="F62" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G62" s="7">
+      <c r="G62" s="5">
         <v>6</v>
       </c>
-      <c r="H62" s="7">
+      <c r="H62" s="5">
         <v>12</v>
       </c>
-      <c r="I62" s="7">
-        <v>0</v>
-      </c>
-      <c r="J62" s="7">
-        <v>0</v>
-      </c>
-      <c r="K62" s="7">
-        <v>1</v>
-      </c>
-      <c r="L62" s="7">
-        <v>0</v>
-      </c>
-      <c r="M62" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N62" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O62" s="7">
-        <v>1</v>
-      </c>
-      <c r="P62" s="7">
+      <c r="I62" s="5">
+        <v>0</v>
+      </c>
+      <c r="J62" s="5">
+        <v>0</v>
+      </c>
+      <c r="K62" s="5">
+        <v>1</v>
+      </c>
+      <c r="L62" s="5">
+        <v>0</v>
+      </c>
+      <c r="M62" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N62" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O62" s="5">
+        <v>1</v>
+      </c>
+      <c r="P62" s="5">
         <v>7</v>
       </c>
       <c r="Q62" s="2">
         <v>0</v>
       </c>
-      <c r="R62" s="7">
+      <c r="R62" s="5">
         <v>100</v>
       </c>
-      <c r="S62" s="7">
+      <c r="S62" s="5">
         <v>30</v>
       </c>
-      <c r="T62" s="7" t="s">
+      <c r="T62" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="U62" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="V62" s="7">
+      <c r="U62" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="V62" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="7">
+    <row r="63" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="5">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="5">
         <v>8002</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D63" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E63" s="7" t="s">
+      <c r="E63" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G63" s="7">
+      <c r="G63" s="5">
         <v>6</v>
       </c>
-      <c r="H63" s="7">
+      <c r="H63" s="5">
         <v>14</v>
       </c>
-      <c r="I63" s="7">
-        <v>0</v>
-      </c>
-      <c r="J63" s="7">
-        <v>0</v>
-      </c>
-      <c r="K63" s="7">
-        <v>1</v>
-      </c>
-      <c r="L63" s="7">
-        <v>0</v>
-      </c>
-      <c r="M63" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N63" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O63" s="7">
-        <v>1</v>
-      </c>
-      <c r="P63" s="7">
+      <c r="I63" s="5">
+        <v>0</v>
+      </c>
+      <c r="J63" s="5">
+        <v>0</v>
+      </c>
+      <c r="K63" s="5">
+        <v>1</v>
+      </c>
+      <c r="L63" s="5">
+        <v>0</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N63" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O63" s="5">
+        <v>1</v>
+      </c>
+      <c r="P63" s="5">
         <v>7</v>
       </c>
       <c r="Q63" s="2">
         <v>0</v>
       </c>
-      <c r="R63" s="7">
+      <c r="R63" s="5">
         <v>100</v>
       </c>
-      <c r="S63" s="7">
+      <c r="S63" s="5">
         <v>30</v>
       </c>
-      <c r="T63" s="7" t="s">
+      <c r="T63" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="U63" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="V63" s="7">
+      <c r="U63" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="V63" s="5">
         <v>0</v>
       </c>
     </row>
@@ -8810,10 +8832,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O64" s="2">
         <v>1</v>
@@ -8831,7 +8853,7 @@
         <v>120</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="U64" s="2" t="s">
         <v>94</v>
@@ -8840,279 +8862,279 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:22" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="2">
+    <row r="65" spans="1:22" s="9" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="9">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="9">
         <v>9005</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G65" s="2">
+      <c r="C65" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="G65" s="9">
         <v>2</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65" s="9">
         <v>4</v>
       </c>
-      <c r="I65" s="2">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2">
-        <v>0</v>
-      </c>
-      <c r="K65" s="2">
+      <c r="I65" s="9">
+        <v>1</v>
+      </c>
+      <c r="J65" s="9">
+        <v>0</v>
+      </c>
+      <c r="K65" s="9">
         <v>3</v>
       </c>
-      <c r="L65" s="2">
-        <v>0</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N65" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O65" s="2">
-        <v>1</v>
-      </c>
-      <c r="P65" s="2">
+      <c r="L65" s="9">
+        <v>0</v>
+      </c>
+      <c r="M65" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N65" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="O65" s="9">
+        <v>1</v>
+      </c>
+      <c r="P65" s="9">
         <v>8</v>
       </c>
-      <c r="Q65" s="2">
-        <v>1</v>
-      </c>
-      <c r="R65" s="2">
+      <c r="Q65" s="9">
+        <v>1</v>
+      </c>
+      <c r="R65" s="9">
         <v>100</v>
       </c>
-      <c r="S65" s="2">
+      <c r="S65" s="9">
         <v>30</v>
       </c>
-      <c r="T65" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="U65" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V65" s="2">
+      <c r="T65" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="U65" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V65" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:22" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="6">
+    <row r="66" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="4">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B66" s="6">
+      <c r="B66" s="4">
         <v>9002</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D66" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E66" s="6" t="s">
+      <c r="E66" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F66" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G66" s="4">
         <v>6</v>
       </c>
-      <c r="H66" s="6">
+      <c r="H66" s="4">
         <v>5</v>
       </c>
-      <c r="I66" s="6">
+      <c r="I66" s="4">
         <v>9999</v>
       </c>
-      <c r="J66" s="6">
-        <v>0</v>
-      </c>
-      <c r="K66" s="6">
+      <c r="J66" s="4">
+        <v>0</v>
+      </c>
+      <c r="K66" s="4">
         <v>10</v>
       </c>
-      <c r="L66" s="6">
-        <v>0</v>
-      </c>
-      <c r="M66" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N66" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O66" s="6">
-        <v>1</v>
-      </c>
-      <c r="P66" s="6">
+      <c r="L66" s="4">
+        <v>0</v>
+      </c>
+      <c r="M66" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N66" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O66" s="4">
+        <v>1</v>
+      </c>
+      <c r="P66" s="4">
         <v>8</v>
       </c>
-      <c r="Q66" s="2">
-        <v>0</v>
-      </c>
-      <c r="R66" s="6">
+      <c r="Q66" s="4">
+        <v>0</v>
+      </c>
+      <c r="R66" s="4">
         <v>100</v>
       </c>
-      <c r="S66" s="6">
+      <c r="S66" s="4">
         <v>30</v>
       </c>
-      <c r="T66" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="U66" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V66" s="6">
+      <c r="T66" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U66" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V66" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:22" s="6" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="6">
+    <row r="67" spans="1:22" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="4">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B67" s="6">
+      <c r="B67" s="4">
         <v>9004</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D67" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E67" s="6" t="s">
+      <c r="E67" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F67" s="6" t="s">
+      <c r="F67" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G67" s="6">
+      <c r="G67" s="4">
         <v>2</v>
       </c>
-      <c r="H67" s="6">
+      <c r="H67" s="4">
         <v>10</v>
       </c>
-      <c r="I67" s="6">
-        <v>0</v>
-      </c>
-      <c r="J67" s="6">
-        <v>0</v>
-      </c>
-      <c r="K67" s="6">
-        <v>1</v>
-      </c>
-      <c r="L67" s="6">
-        <v>0</v>
-      </c>
-      <c r="M67" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="N67" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="O67" s="6">
-        <v>1</v>
-      </c>
-      <c r="P67" s="6">
+      <c r="I67" s="4">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4">
+        <v>0</v>
+      </c>
+      <c r="K67" s="4">
+        <v>1</v>
+      </c>
+      <c r="L67" s="4">
+        <v>0</v>
+      </c>
+      <c r="M67" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="N67" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O67" s="4">
+        <v>1</v>
+      </c>
+      <c r="P67" s="4">
         <v>8</v>
       </c>
-      <c r="Q67" s="2">
-        <v>0</v>
-      </c>
-      <c r="R67" s="6">
+      <c r="Q67" s="4">
+        <v>0</v>
+      </c>
+      <c r="R67" s="4">
         <v>100</v>
       </c>
-      <c r="S67" s="6">
+      <c r="S67" s="4">
         <v>60</v>
       </c>
-      <c r="T67" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="U67" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="V67" s="6">
+      <c r="T67" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="U67" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V67" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:22" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="2">
+    <row r="68" spans="1:22" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="9">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="9">
         <v>9003</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D68" s="2" t="s">
+      <c r="C68" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="D68" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="E68" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="F68" s="2" t="s">
+      <c r="F68" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G68" s="2">
+      <c r="G68" s="9">
         <v>6</v>
       </c>
-      <c r="H68" s="2">
-        <v>1</v>
-      </c>
-      <c r="I68" s="2">
-        <v>0</v>
-      </c>
-      <c r="J68" s="2">
-        <v>1</v>
-      </c>
-      <c r="K68" s="2">
-        <v>1</v>
-      </c>
-      <c r="L68" s="2">
-        <v>1</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N68" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="O68" s="2">
-        <v>1</v>
-      </c>
-      <c r="P68" s="2">
+      <c r="H68" s="9">
+        <v>1</v>
+      </c>
+      <c r="I68" s="9">
+        <v>0</v>
+      </c>
+      <c r="J68" s="9">
+        <v>1</v>
+      </c>
+      <c r="K68" s="9">
+        <v>1</v>
+      </c>
+      <c r="L68" s="9">
+        <v>1</v>
+      </c>
+      <c r="M68" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N68" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O68" s="9">
+        <v>1</v>
+      </c>
+      <c r="P68" s="9">
         <v>8</v>
       </c>
-      <c r="Q68" s="2">
-        <v>0</v>
-      </c>
-      <c r="R68" s="2">
+      <c r="Q68" s="9">
+        <v>0</v>
+      </c>
+      <c r="R68" s="9">
         <v>100</v>
       </c>
-      <c r="S68" s="2">
+      <c r="S68" s="9">
         <v>30</v>
       </c>
-      <c r="T68" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="U68" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V68" s="2">
+      <c r="T68" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="U68" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V68" s="9">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CE9CD6-C719-4CE4-9EE2-088218EB1D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A06E298-74F8-4EFD-B8A6-6F71F154CCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="1095" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2625" yWindow="1380" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6030,7 +6030,7 @@
         <v>16</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A06E298-74F8-4EFD-B8A6-6F71F154CCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AF3A74-6782-472C-9AA4-8C9031504C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2625" yWindow="1380" windowWidth="25560" windowHeight="14355" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2349,10 +2349,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>あわあわ・デコレーション</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>光で作ったちょうちょや葉っぱを飛ばす
 お菓子をさらにかわいく演出できる。
 見た目がアップする。
@@ -3995,6 +3991,10 @@
     <rPh sb="87" eb="89">
       <t>バアイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アロマ・バブル</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4031,7 +4031,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4059,12 +4059,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4109,10 +4103,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4488,7 +4482,7 @@
         <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>8</v>
@@ -4497,7 +4491,7 @@
         <v>9</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>10</v>
@@ -4644,7 +4638,7 @@
         <v>30</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="U3" t="s">
         <v>94</v>
@@ -4731,7 +4725,7 @@
         <v>1010</v>
       </c>
       <c r="C5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D5" t="s">
         <v>163</v>
@@ -4782,7 +4776,7 @@
         <v>30</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="U5" t="s">
         <v>94</v>
@@ -4800,7 +4794,7 @@
         <v>1009</v>
       </c>
       <c r="C6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D6" t="s">
         <v>112</v>
@@ -4851,7 +4845,7 @@
         <v>30</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="U6" t="s">
         <v>54</v>
@@ -4869,7 +4863,7 @@
         <v>1003</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>58</v>
@@ -4971,7 +4965,7 @@
         <v>94</v>
       </c>
       <c r="N8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -4989,7 +4983,7 @@
         <v>30</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="U8" t="s">
         <v>163</v>
@@ -5007,7 +5001,7 @@
         <v>1008</v>
       </c>
       <c r="C9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D9" t="s">
         <v>82</v>
@@ -5058,7 +5052,7 @@
         <v>30</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="U9" t="s">
         <v>80</v>
@@ -5076,7 +5070,7 @@
         <v>1006</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>222</v>
@@ -5127,7 +5121,7 @@
         <v>30</v>
       </c>
       <c r="T10" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="U10" s="9" t="s">
         <v>58</v>
@@ -5352,7 +5346,7 @@
         <v>2004</v>
       </c>
       <c r="C14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D14" t="s">
         <v>110</v>
@@ -5403,7 +5397,7 @@
         <v>30</v>
       </c>
       <c r="T14" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="U14" t="s">
         <v>94</v>
@@ -5490,7 +5484,7 @@
         <v>2001</v>
       </c>
       <c r="C16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D16" t="s">
         <v>175</v>
@@ -5628,16 +5622,16 @@
         <v>2005</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>254</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="G18" s="9">
         <v>2</v>
@@ -5679,7 +5673,7 @@
         <v>30</v>
       </c>
       <c r="T18" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="U18" s="9" t="s">
         <v>51</v>
@@ -5697,7 +5691,7 @@
         <v>2003</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>118</v>
@@ -5730,7 +5724,7 @@
         <v>94</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O19" s="9">
         <v>1</v>
@@ -5748,7 +5742,7 @@
         <v>30</v>
       </c>
       <c r="T19" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="U19" s="9" t="s">
         <v>101</v>
@@ -5937,7 +5931,7 @@
         <v>94</v>
       </c>
       <c r="N22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O22">
         <v>1</v>
@@ -6006,7 +6000,7 @@
         <v>94</v>
       </c>
       <c r="N23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O23">
         <v>1</v>
@@ -6042,7 +6036,7 @@
         <v>3003</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>106</v>
@@ -6093,7 +6087,7 @@
         <v>30</v>
       </c>
       <c r="T24" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="U24" s="9" t="s">
         <v>20</v>
@@ -6111,16 +6105,16 @@
         <v>3008</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>257</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="G25" s="9">
         <v>4</v>
@@ -6162,7 +6156,7 @@
         <v>30</v>
       </c>
       <c r="T25" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="U25" s="9" t="s">
         <v>94</v>
@@ -6180,7 +6174,7 @@
         <v>3004</v>
       </c>
       <c r="C26" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D26" t="s">
         <v>115</v>
@@ -6249,16 +6243,16 @@
         <v>3007</v>
       </c>
       <c r="C27" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D27" t="s">
+        <v>250</v>
+      </c>
+      <c r="E27" t="s">
+        <v>274</v>
+      </c>
+      <c r="F27" t="s">
         <v>251</v>
-      </c>
-      <c r="E27" t="s">
-        <v>275</v>
-      </c>
-      <c r="F27" t="s">
-        <v>252</v>
       </c>
       <c r="G27">
         <v>4</v>
@@ -6300,7 +6294,7 @@
         <v>30</v>
       </c>
       <c r="T27" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="U27" t="s">
         <v>94</v>
@@ -6456,7 +6450,7 @@
         <v>4010</v>
       </c>
       <c r="C30" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D30" t="s">
         <v>151</v>
@@ -6507,7 +6501,7 @@
         <v>30</v>
       </c>
       <c r="T30" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="U30" t="s">
         <v>94</v>
@@ -6525,7 +6519,7 @@
         <v>4011</v>
       </c>
       <c r="C31" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D31" t="s">
         <v>154</v>
@@ -6576,7 +6570,7 @@
         <v>30</v>
       </c>
       <c r="T31" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="U31" t="s">
         <v>94</v>
@@ -6594,7 +6588,7 @@
         <v>4001</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>23</v>
@@ -6603,7 +6597,7 @@
         <v>21</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G32" s="9">
         <v>6</v>
@@ -6624,10 +6618,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O32" s="9">
         <v>1</v>
@@ -6645,7 +6639,7 @@
         <v>10</v>
       </c>
       <c r="T32" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="U32" s="9" t="s">
         <v>154</v>
@@ -6663,7 +6657,7 @@
         <v>4002</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>25</v>
@@ -6696,7 +6690,7 @@
         <v>94</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O33" s="9">
         <v>1</v>
@@ -6714,7 +6708,7 @@
         <v>15</v>
       </c>
       <c r="T33" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="U33" s="9" t="s">
         <v>94</v>
@@ -6732,7 +6726,7 @@
         <v>4010</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>128</v>
@@ -6765,7 +6759,7 @@
         <v>94</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O34" s="9">
         <v>1</v>
@@ -6801,7 +6795,7 @@
         <v>4011</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>171</v>
@@ -6834,7 +6828,7 @@
         <v>94</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O35" s="9">
         <v>1</v>
@@ -6870,7 +6864,7 @@
         <v>4012</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>173</v>
@@ -6903,7 +6897,7 @@
         <v>94</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O36" s="9">
         <v>1</v>
@@ -6921,7 +6915,7 @@
         <v>15</v>
       </c>
       <c r="T36" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="U36" s="9" t="s">
         <v>23</v>
@@ -6939,7 +6933,7 @@
         <v>4012</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>177</v>
@@ -6948,7 +6942,7 @@
         <v>176</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G37" s="9">
         <v>1</v>
@@ -6972,7 +6966,7 @@
         <v>94</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O37" s="9">
         <v>1</v>
@@ -6990,7 +6984,7 @@
         <v>15</v>
       </c>
       <c r="T37" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="U37" s="9" t="s">
         <v>23</v>
@@ -7008,7 +7002,7 @@
         <v>4012</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>179</v>
@@ -7041,7 +7035,7 @@
         <v>94</v>
       </c>
       <c r="N38" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O38" s="9">
         <v>1</v>
@@ -7059,7 +7053,7 @@
         <v>15</v>
       </c>
       <c r="T38" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="U38" s="9" t="s">
         <v>23</v>
@@ -7146,13 +7140,13 @@
         <v>4004</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>234</v>
+        <v>334</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>221</v>
@@ -7197,7 +7191,7 @@
         <v>30</v>
       </c>
       <c r="T40" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="U40" s="9" t="s">
         <v>23</v>
@@ -7293,7 +7287,7 @@
         <v>174</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G42" s="4">
         <v>3</v>
@@ -7317,7 +7311,7 @@
         <v>94</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O42" s="4">
         <v>1</v>
@@ -7335,7 +7329,7 @@
         <v>30</v>
       </c>
       <c r="T42" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="U42" s="4" t="s">
         <v>94</v>
@@ -7353,7 +7347,7 @@
         <v>4007</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>85</v>
@@ -7362,7 +7356,7 @@
         <v>87</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G43" s="9">
         <v>3</v>
@@ -7386,7 +7380,7 @@
         <v>94</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O43" s="9">
         <v>1</v>
@@ -7404,7 +7398,7 @@
         <v>15</v>
       </c>
       <c r="T43" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="U43" s="9" t="s">
         <v>154</v>
@@ -7431,7 +7425,7 @@
         <v>196</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G44" s="4">
         <v>3</v>
@@ -7455,7 +7449,7 @@
         <v>94</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O44" s="4">
         <v>1</v>
@@ -7473,7 +7467,7 @@
         <v>30</v>
       </c>
       <c r="T44" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="U44" s="4" t="s">
         <v>94</v>
@@ -7500,7 +7494,7 @@
         <v>88</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G45" s="4">
         <v>3</v>
@@ -7524,7 +7518,7 @@
         <v>94</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O45" s="4">
         <v>1</v>
@@ -7542,7 +7536,7 @@
         <v>30</v>
       </c>
       <c r="T45" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U45" s="4" t="s">
         <v>94</v>
@@ -7569,7 +7563,7 @@
         <v>102</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G46" s="4">
         <v>3</v>
@@ -7611,7 +7605,7 @@
         <v>30</v>
       </c>
       <c r="T46" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="U46" s="4" t="s">
         <v>94</v>
@@ -7767,16 +7761,16 @@
         <v>5007</v>
       </c>
       <c r="C49" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D49" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E49" t="s">
+        <v>271</v>
+      </c>
+      <c r="F49" t="s">
         <v>272</v>
-      </c>
-      <c r="F49" t="s">
-        <v>273</v>
       </c>
       <c r="G49">
         <v>6</v>
@@ -7818,7 +7812,7 @@
         <v>30</v>
       </c>
       <c r="T49" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="U49" t="s">
         <v>94</v>
@@ -7836,7 +7830,7 @@
         <v>5001</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>39</v>
@@ -7845,7 +7839,7 @@
         <v>38</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G50" s="9">
         <v>6</v>
@@ -7887,10 +7881,10 @@
         <v>15</v>
       </c>
       <c r="T50" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="U50" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="V50" s="9">
         <v>3</v>
@@ -7905,7 +7899,7 @@
         <v>5002</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>121</v>
@@ -7956,7 +7950,7 @@
         <v>30</v>
       </c>
       <c r="T51" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="U51" s="9" t="s">
         <v>39</v>
@@ -7974,7 +7968,7 @@
         <v>5003</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>139</v>
@@ -8043,7 +8037,7 @@
         <v>5005</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>200</v>
@@ -8097,7 +8091,7 @@
         <v>197</v>
       </c>
       <c r="U53" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="V53" s="9">
         <v>3</v>
@@ -8112,7 +8106,7 @@
         <v>5006</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>214</v>
@@ -8121,7 +8115,7 @@
         <v>213</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G54" s="9">
         <v>6</v>
@@ -8145,7 +8139,7 @@
         <v>94</v>
       </c>
       <c r="N54" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O54" s="9">
         <v>1</v>
@@ -8163,7 +8157,7 @@
         <v>30</v>
       </c>
       <c r="T54" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="U54" s="9" t="s">
         <v>94</v>
@@ -8250,7 +8244,7 @@
         <v>6002</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>101</v>
@@ -8301,7 +8295,7 @@
         <v>30</v>
       </c>
       <c r="T56" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="U56" s="9" t="s">
         <v>94</v>
@@ -8319,16 +8313,16 @@
         <v>6004</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D57" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="E57" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="F57" s="9" t="s">
         <v>263</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>264</v>
       </c>
       <c r="G57" s="9">
         <v>6</v>
@@ -8370,7 +8364,7 @@
         <v>30</v>
       </c>
       <c r="T57" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="U57" s="9" t="s">
         <v>94</v>
@@ -8388,16 +8382,16 @@
         <v>6005</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D58" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="E58" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="F58" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="G58" s="9">
         <v>6</v>
@@ -8439,7 +8433,7 @@
         <v>30</v>
       </c>
       <c r="T58" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="U58" s="9" t="s">
         <v>94</v>
@@ -8853,7 +8847,7 @@
         <v>120</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="U64" s="2" t="s">
         <v>94</v>
@@ -8871,16 +8865,16 @@
         <v>9005</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D65" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="F65" s="9" t="s">
         <v>260</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>261</v>
       </c>
       <c r="G65" s="9">
         <v>2</v>
@@ -8922,7 +8916,7 @@
         <v>30</v>
       </c>
       <c r="T65" s="10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="U65" s="9" t="s">
         <v>94</v>
@@ -9078,7 +9072,7 @@
         <v>9003</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D68" s="9" t="s">
         <v>108</v>
@@ -9129,7 +9123,7 @@
         <v>30</v>
       </c>
       <c r="T68" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="U68" s="9" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AF3A74-6782-472C-9AA4-8C9031504C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FAAC6D-9D7C-4016-A42A-1290099678E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2220" yWindow="1110" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4077,7 +4077,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4101,12 +4101,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4854,72 +4848,72 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="9" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="9">
+    <row r="7" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" t="s">
         <v>295</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7">
         <v>2</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7">
         <v>2</v>
       </c>
-      <c r="I7" s="9">
-        <v>1</v>
-      </c>
-      <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>3</v>
       </c>
-      <c r="L7" s="9">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="O7" s="9">
-        <v>1</v>
-      </c>
-      <c r="P7" s="9">
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
         <v>9</v>
       </c>
-      <c r="Q7" s="9">
-        <v>0</v>
-      </c>
-      <c r="R7" s="9">
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
         <v>100</v>
       </c>
-      <c r="S7" s="9">
+      <c r="S7">
         <v>30</v>
       </c>
-      <c r="T7" s="10" t="s">
+      <c r="T7" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="U7" s="9" t="s">
+      <c r="U7" t="s">
         <v>54</v>
       </c>
-      <c r="V7" s="9">
+      <c r="V7">
         <v>1</v>
       </c>
     </row>
@@ -5061,72 +5055,72 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="9">
+    <row r="10" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" t="s">
         <v>298</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" t="s">
         <v>222</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" t="s">
         <v>223</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" t="s">
         <v>224</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10">
         <v>6</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10">
         <v>4</v>
       </c>
-      <c r="I10" s="9">
-        <v>1</v>
-      </c>
-      <c r="J10" s="9">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>3</v>
       </c>
-      <c r="L10" s="9">
-        <v>0</v>
-      </c>
-      <c r="M10" s="9" t="s">
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="s">
         <v>135</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="N10" t="s">
         <v>135</v>
       </c>
-      <c r="O10" s="9">
-        <v>1</v>
-      </c>
-      <c r="P10" s="9">
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
         <v>9</v>
       </c>
-      <c r="Q10" s="9">
-        <v>1</v>
-      </c>
-      <c r="R10" s="9">
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
         <v>100</v>
       </c>
-      <c r="S10" s="9">
+      <c r="S10">
         <v>30</v>
       </c>
-      <c r="T10" s="10" t="s">
+      <c r="T10" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="U10" s="9" t="s">
+      <c r="U10" t="s">
         <v>58</v>
       </c>
-      <c r="V10" s="9">
+      <c r="V10">
         <v>1</v>
       </c>
     </row>
@@ -5613,141 +5607,141 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" s="9" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="9">
+    <row r="18" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18">
         <v>2005</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" t="s">
         <v>292</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" t="s">
         <v>253</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" t="s">
         <v>275</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" t="s">
         <v>254</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18">
         <v>2</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18">
         <v>4</v>
       </c>
-      <c r="I18" s="9">
-        <v>1</v>
-      </c>
-      <c r="J18" s="9">
-        <v>0</v>
-      </c>
-      <c r="K18" s="9">
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
         <v>3</v>
       </c>
-      <c r="L18" s="9">
-        <v>0</v>
-      </c>
-      <c r="M18" s="9" t="s">
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="s">
         <v>135</v>
       </c>
-      <c r="N18" s="9" t="s">
+      <c r="N18" t="s">
         <v>135</v>
       </c>
-      <c r="O18" s="9">
-        <v>1</v>
-      </c>
-      <c r="P18" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="9">
-        <v>1</v>
-      </c>
-      <c r="R18" s="9">
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
         <v>100</v>
       </c>
-      <c r="S18" s="9">
+      <c r="S18">
         <v>30</v>
       </c>
-      <c r="T18" s="10" t="s">
+      <c r="T18" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="U18" s="9" t="s">
+      <c r="U18" t="s">
         <v>51</v>
       </c>
-      <c r="V18" s="9">
+      <c r="V18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:22" s="9" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="9">
+    <row r="19" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19">
         <v>2003</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" t="s">
         <v>290</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" t="s">
         <v>118</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" t="s">
         <v>111</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" t="s">
         <v>134</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19">
         <v>2</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19">
         <v>3</v>
       </c>
-      <c r="I19" s="9">
-        <v>1</v>
-      </c>
-      <c r="J19" s="9">
-        <v>0</v>
-      </c>
-      <c r="K19" s="9">
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
         <v>5</v>
       </c>
-      <c r="L19" s="9">
-        <v>0</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N19" s="9" t="s">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="s">
+        <v>94</v>
+      </c>
+      <c r="N19" t="s">
         <v>238</v>
       </c>
-      <c r="O19" s="9">
-        <v>1</v>
-      </c>
-      <c r="P19" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="9">
-        <v>0</v>
-      </c>
-      <c r="R19" s="9">
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
         <v>100</v>
       </c>
-      <c r="S19" s="9">
+      <c r="S19">
         <v>30</v>
       </c>
-      <c r="T19" s="10" t="s">
+      <c r="T19" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="U19" s="9" t="s">
+      <c r="U19" t="s">
         <v>101</v>
       </c>
-      <c r="V19" s="9">
+      <c r="V19">
         <v>1</v>
       </c>
     </row>
@@ -6027,141 +6021,141 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="9">
+    <row r="24" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24">
         <v>3003</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" t="s">
         <v>300</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" t="s">
         <v>106</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" t="s">
         <v>216</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" t="s">
         <v>72</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24">
         <v>4</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24">
         <v>4</v>
       </c>
-      <c r="I24" s="9">
-        <v>1</v>
-      </c>
-      <c r="J24" s="9">
-        <v>0</v>
-      </c>
-      <c r="K24" s="9">
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
         <v>3</v>
       </c>
-      <c r="L24" s="9">
-        <v>0</v>
-      </c>
-      <c r="M24" s="9" t="s">
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="s">
         <v>135</v>
       </c>
-      <c r="N24" s="9" t="s">
+      <c r="N24" t="s">
         <v>135</v>
       </c>
-      <c r="O24" s="9">
-        <v>1</v>
-      </c>
-      <c r="P24" s="9">
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
         <v>2</v>
       </c>
-      <c r="Q24" s="9">
-        <v>1</v>
-      </c>
-      <c r="R24" s="9">
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
         <v>100</v>
       </c>
-      <c r="S24" s="9">
+      <c r="S24">
         <v>30</v>
       </c>
-      <c r="T24" s="10" t="s">
+      <c r="T24" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="U24" s="9" t="s">
+      <c r="U24" t="s">
         <v>20</v>
       </c>
-      <c r="V24" s="9">
-        <v>3</v>
+      <c r="V24">
+        <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="9">
+    <row r="25" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25">
         <v>3008</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" t="s">
         <v>288</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" t="s">
         <v>256</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" t="s">
         <v>255</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" t="s">
         <v>257</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25">
         <v>4</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25">
         <v>4</v>
       </c>
-      <c r="I25" s="9">
-        <v>0</v>
-      </c>
-      <c r="J25" s="9">
-        <v>0</v>
-      </c>
-      <c r="K25" s="9">
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
         <v>3</v>
       </c>
-      <c r="L25" s="9">
-        <v>0</v>
-      </c>
-      <c r="M25" s="9" t="s">
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="s">
         <v>135</v>
       </c>
-      <c r="N25" s="9" t="s">
+      <c r="N25" t="s">
         <v>135</v>
       </c>
-      <c r="O25" s="9">
-        <v>1</v>
-      </c>
-      <c r="P25" s="9">
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25">
         <v>2</v>
       </c>
-      <c r="Q25" s="9">
-        <v>1</v>
-      </c>
-      <c r="R25" s="9">
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25">
         <v>100</v>
       </c>
-      <c r="S25" s="9">
+      <c r="S25">
         <v>30</v>
       </c>
-      <c r="T25" s="10" t="s">
+      <c r="T25" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="U25" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V25" s="9">
+      <c r="U25" t="s">
+        <v>94</v>
+      </c>
+      <c r="V25">
         <v>0</v>
       </c>
     </row>
@@ -6579,486 +6573,486 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:22" s="9" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="9">
+    <row r="32" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32">
         <v>4001</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" t="s">
         <v>283</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" t="s">
         <v>21</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" t="s">
         <v>245</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32">
         <v>6</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32">
         <v>2</v>
       </c>
-      <c r="I32" s="9">
-        <v>1</v>
-      </c>
-      <c r="J32" s="9">
-        <v>0</v>
-      </c>
-      <c r="K32" s="9">
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
         <v>3</v>
       </c>
-      <c r="L32" s="9">
-        <v>0</v>
-      </c>
-      <c r="M32" s="9" t="s">
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="s">
         <v>247</v>
       </c>
-      <c r="N32" s="9" t="s">
+      <c r="N32" t="s">
         <v>238</v>
       </c>
-      <c r="O32" s="9">
-        <v>1</v>
-      </c>
-      <c r="P32" s="9">
+      <c r="O32">
+        <v>1</v>
+      </c>
+      <c r="P32">
         <v>3</v>
       </c>
-      <c r="Q32" s="9">
-        <v>0</v>
-      </c>
-      <c r="R32" s="9">
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
         <v>85</v>
       </c>
-      <c r="S32" s="9">
+      <c r="S32">
         <v>10</v>
       </c>
-      <c r="T32" s="10" t="s">
+      <c r="T32" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="U32" s="9" t="s">
+      <c r="U32" t="s">
         <v>154</v>
       </c>
-      <c r="V32" s="9">
+      <c r="V32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="9">
+    <row r="33" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33">
         <v>4002</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" t="s">
         <v>284</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" t="s">
         <v>25</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" t="s">
         <v>192</v>
       </c>
-      <c r="G33" s="9">
-        <v>1</v>
-      </c>
-      <c r="H33" s="9">
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
         <v>4</v>
       </c>
-      <c r="I33" s="9">
-        <v>0</v>
-      </c>
-      <c r="J33" s="9">
-        <v>0</v>
-      </c>
-      <c r="K33" s="9">
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
         <v>3</v>
       </c>
-      <c r="L33" s="9">
-        <v>0</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N33" s="9" t="s">
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="s">
+        <v>94</v>
+      </c>
+      <c r="N33" t="s">
         <v>238</v>
       </c>
-      <c r="O33" s="9">
-        <v>1</v>
-      </c>
-      <c r="P33" s="9">
+      <c r="O33">
+        <v>1</v>
+      </c>
+      <c r="P33">
         <v>3</v>
       </c>
-      <c r="Q33" s="9">
-        <v>0</v>
-      </c>
-      <c r="R33" s="9">
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
         <v>100</v>
       </c>
-      <c r="S33" s="9">
+      <c r="S33">
         <v>15</v>
       </c>
-      <c r="T33" s="10" t="s">
+      <c r="T33" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="U33" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V33" s="9">
+      <c r="U33" t="s">
+        <v>94</v>
+      </c>
+      <c r="V33">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="9">
+    <row r="34" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34">
         <v>4010</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" t="s">
         <v>285</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" t="s">
         <v>128</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" t="s">
         <v>129</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" t="s">
         <v>193</v>
       </c>
-      <c r="G34" s="9">
-        <v>1</v>
-      </c>
-      <c r="H34" s="9">
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
         <v>4</v>
       </c>
-      <c r="I34" s="9">
-        <v>1</v>
-      </c>
-      <c r="J34" s="9">
-        <v>0</v>
-      </c>
-      <c r="K34" s="9">
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
         <v>3</v>
       </c>
-      <c r="L34" s="9">
-        <v>0</v>
-      </c>
-      <c r="M34" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N34" s="9" t="s">
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="s">
+        <v>94</v>
+      </c>
+      <c r="N34" t="s">
         <v>238</v>
       </c>
-      <c r="O34" s="9">
-        <v>1</v>
-      </c>
-      <c r="P34" s="9">
+      <c r="O34">
+        <v>1</v>
+      </c>
+      <c r="P34">
         <v>3</v>
       </c>
-      <c r="Q34" s="9">
-        <v>0</v>
-      </c>
-      <c r="R34" s="9">
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
         <v>100</v>
       </c>
-      <c r="S34" s="9">
+      <c r="S34">
         <v>15</v>
       </c>
-      <c r="T34" s="10" t="s">
+      <c r="T34" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="U34" s="9" t="s">
+      <c r="U34" t="s">
         <v>23</v>
       </c>
-      <c r="V34" s="9">
+      <c r="V34">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="9">
+    <row r="35" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35">
         <v>4011</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" t="s">
         <v>286</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" t="s">
         <v>171</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" t="s">
         <v>170</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="9">
-        <v>1</v>
-      </c>
-      <c r="H35" s="9">
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
         <v>4</v>
       </c>
-      <c r="I35" s="9">
-        <v>1</v>
-      </c>
-      <c r="J35" s="9">
-        <v>0</v>
-      </c>
-      <c r="K35" s="9">
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
         <v>3</v>
       </c>
-      <c r="L35" s="9">
-        <v>0</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N35" s="9" t="s">
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="s">
+        <v>94</v>
+      </c>
+      <c r="N35" t="s">
         <v>238</v>
       </c>
-      <c r="O35" s="9">
-        <v>1</v>
-      </c>
-      <c r="P35" s="9">
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35">
         <v>3</v>
       </c>
-      <c r="Q35" s="9">
-        <v>0</v>
-      </c>
-      <c r="R35" s="9">
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
         <v>100</v>
       </c>
-      <c r="S35" s="9">
+      <c r="S35">
         <v>15</v>
       </c>
-      <c r="T35" s="10" t="s">
+      <c r="T35" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="U35" s="9" t="s">
+      <c r="U35" t="s">
         <v>23</v>
       </c>
-      <c r="V35" s="9">
+      <c r="V35">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="9">
+    <row r="36" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36">
         <v>4012</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" t="s">
         <v>287</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" t="s">
         <v>173</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" t="s">
         <v>183</v>
       </c>
-      <c r="G36" s="9">
-        <v>1</v>
-      </c>
-      <c r="H36" s="9">
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
         <v>4</v>
       </c>
-      <c r="I36" s="9">
-        <v>1</v>
-      </c>
-      <c r="J36" s="9">
-        <v>0</v>
-      </c>
-      <c r="K36" s="9">
-        <v>1</v>
-      </c>
-      <c r="L36" s="9">
-        <v>0</v>
-      </c>
-      <c r="M36" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N36" s="9" t="s">
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="s">
+        <v>94</v>
+      </c>
+      <c r="N36" t="s">
         <v>238</v>
       </c>
-      <c r="O36" s="9">
-        <v>1</v>
-      </c>
-      <c r="P36" s="9">
+      <c r="O36">
+        <v>1</v>
+      </c>
+      <c r="P36">
         <v>3</v>
       </c>
-      <c r="Q36" s="9">
-        <v>0</v>
-      </c>
-      <c r="R36" s="9">
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
         <v>100</v>
       </c>
-      <c r="S36" s="9">
+      <c r="S36">
         <v>15</v>
       </c>
-      <c r="T36" s="10" t="s">
+      <c r="T36" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="U36" s="9" t="s">
+      <c r="U36" t="s">
         <v>23</v>
       </c>
-      <c r="V36" s="9">
+      <c r="V36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="9">
+    <row r="37" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37">
         <v>4012</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" t="s">
         <v>306</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" t="s">
         <v>177</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" t="s">
         <v>176</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="F37" t="s">
         <v>318</v>
       </c>
-      <c r="G37" s="9">
-        <v>1</v>
-      </c>
-      <c r="H37" s="9">
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
         <v>4</v>
       </c>
-      <c r="I37" s="9">
-        <v>1</v>
-      </c>
-      <c r="J37" s="9">
-        <v>0</v>
-      </c>
-      <c r="K37" s="9">
-        <v>1</v>
-      </c>
-      <c r="L37" s="9">
-        <v>0</v>
-      </c>
-      <c r="M37" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N37" s="9" t="s">
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="s">
+        <v>94</v>
+      </c>
+      <c r="N37" t="s">
         <v>238</v>
       </c>
-      <c r="O37" s="9">
-        <v>1</v>
-      </c>
-      <c r="P37" s="9">
+      <c r="O37">
+        <v>1</v>
+      </c>
+      <c r="P37">
         <v>3</v>
       </c>
-      <c r="Q37" s="9">
-        <v>0</v>
-      </c>
-      <c r="R37" s="9">
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
         <v>100</v>
       </c>
-      <c r="S37" s="9">
+      <c r="S37">
         <v>15</v>
       </c>
-      <c r="T37" s="10" t="s">
+      <c r="T37" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="U37" s="9" t="s">
+      <c r="U37" t="s">
         <v>23</v>
       </c>
-      <c r="V37" s="9">
+      <c r="V37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="9">
+    <row r="38" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38">
         <v>4012</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" t="s">
         <v>307</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" t="s">
         <v>179</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" t="s">
         <v>184</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" t="s">
         <v>180</v>
       </c>
-      <c r="G38" s="9">
-        <v>1</v>
-      </c>
-      <c r="H38" s="9">
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
         <v>4</v>
       </c>
-      <c r="I38" s="9">
-        <v>1</v>
-      </c>
-      <c r="J38" s="9">
-        <v>0</v>
-      </c>
-      <c r="K38" s="9">
-        <v>1</v>
-      </c>
-      <c r="L38" s="9">
-        <v>0</v>
-      </c>
-      <c r="M38" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N38" s="9" t="s">
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="s">
+        <v>94</v>
+      </c>
+      <c r="N38" t="s">
         <v>238</v>
       </c>
-      <c r="O38" s="9">
-        <v>1</v>
-      </c>
-      <c r="P38" s="9">
+      <c r="O38">
+        <v>1</v>
+      </c>
+      <c r="P38">
         <v>3</v>
       </c>
-      <c r="Q38" s="9">
-        <v>0</v>
-      </c>
-      <c r="R38" s="9">
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
         <v>100</v>
       </c>
-      <c r="S38" s="9">
+      <c r="S38">
         <v>15</v>
       </c>
-      <c r="T38" s="10" t="s">
+      <c r="T38" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="U38" s="9" t="s">
+      <c r="U38" t="s">
         <v>23</v>
       </c>
-      <c r="V38" s="9">
+      <c r="V38">
         <v>1</v>
       </c>
     </row>
@@ -7131,72 +7125,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="9">
+    <row r="40" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40">
         <v>4004</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" t="s">
         <v>289</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" t="s">
         <v>334</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" t="s">
         <v>221</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40">
         <v>3</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40">
         <v>3</v>
       </c>
-      <c r="I40" s="9">
-        <v>1</v>
-      </c>
-      <c r="J40" s="9">
-        <v>0</v>
-      </c>
-      <c r="K40" s="9">
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
         <v>3</v>
       </c>
-      <c r="L40" s="9">
-        <v>0</v>
-      </c>
-      <c r="M40" s="9" t="s">
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" t="s">
         <v>135</v>
       </c>
-      <c r="N40" s="9" t="s">
+      <c r="N40" t="s">
         <v>135</v>
       </c>
-      <c r="O40" s="9">
-        <v>1</v>
-      </c>
-      <c r="P40" s="9">
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="P40">
         <v>3</v>
       </c>
-      <c r="Q40" s="9">
-        <v>1</v>
-      </c>
-      <c r="R40" s="9">
+      <c r="Q40">
+        <v>1</v>
+      </c>
+      <c r="R40">
         <v>100</v>
       </c>
-      <c r="S40" s="9">
+      <c r="S40">
         <v>30</v>
       </c>
-      <c r="T40" s="10" t="s">
+      <c r="T40" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="U40" s="9" t="s">
+      <c r="U40" t="s">
         <v>23</v>
       </c>
-      <c r="V40" s="9">
+      <c r="V40">
         <v>1</v>
       </c>
     </row>
@@ -7338,72 +7332,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:22" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="9">
+    <row r="43" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43">
         <v>4007</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" t="s">
         <v>309</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" t="s">
         <v>85</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" t="s">
         <v>87</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F43" t="s">
         <v>240</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43">
         <v>3</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43">
         <v>5</v>
       </c>
-      <c r="I43" s="9">
-        <v>1</v>
-      </c>
-      <c r="J43" s="9">
-        <v>0</v>
-      </c>
-      <c r="K43" s="9">
-        <v>1</v>
-      </c>
-      <c r="L43" s="9">
-        <v>0</v>
-      </c>
-      <c r="M43" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N43" s="9" t="s">
+      <c r="I43">
+        <v>1</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="s">
+        <v>94</v>
+      </c>
+      <c r="N43" t="s">
         <v>238</v>
       </c>
-      <c r="O43" s="9">
-        <v>1</v>
-      </c>
-      <c r="P43" s="9">
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="P43">
         <v>3</v>
       </c>
-      <c r="Q43" s="9">
-        <v>0</v>
-      </c>
-      <c r="R43" s="9">
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
         <v>100</v>
       </c>
-      <c r="S43" s="9">
+      <c r="S43">
         <v>15</v>
       </c>
-      <c r="T43" s="10" t="s">
+      <c r="T43" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="U43" s="9" t="s">
+      <c r="U43" t="s">
         <v>154</v>
       </c>
-      <c r="V43" s="9">
+      <c r="V43">
         <v>5</v>
       </c>
     </row>
@@ -7779,7 +7773,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -7821,348 +7815,348 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="9">
+    <row r="50" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50">
         <v>5001</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" t="s">
         <v>297</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" t="s">
         <v>38</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="F50" t="s">
         <v>331</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50">
         <v>6</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50">
         <v>3</v>
       </c>
-      <c r="I50" s="9">
-        <v>1</v>
-      </c>
-      <c r="J50" s="9">
-        <v>0</v>
-      </c>
-      <c r="K50" s="9">
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
         <v>3</v>
       </c>
-      <c r="L50" s="9">
-        <v>0</v>
-      </c>
-      <c r="M50" s="9" t="s">
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="s">
         <v>135</v>
       </c>
-      <c r="N50" s="9" t="s">
+      <c r="N50" t="s">
         <v>135</v>
       </c>
-      <c r="O50" s="9">
-        <v>1</v>
-      </c>
-      <c r="P50" s="9">
+      <c r="O50">
+        <v>1</v>
+      </c>
+      <c r="P50">
         <v>4</v>
       </c>
-      <c r="Q50" s="9">
-        <v>0</v>
-      </c>
-      <c r="R50" s="9">
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
         <v>100</v>
       </c>
-      <c r="S50" s="9">
+      <c r="S50">
         <v>15</v>
       </c>
-      <c r="T50" s="10" t="s">
+      <c r="T50" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="U50" s="9" t="s">
+      <c r="U50" t="s">
         <v>273</v>
       </c>
-      <c r="V50" s="9">
+      <c r="V50">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="9">
+    <row r="51" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51">
         <v>5002</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" t="s">
         <v>312</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D51" t="s">
         <v>121</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E51" t="s">
         <v>119</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" t="s">
         <v>120</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51">
         <v>6</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51">
         <v>3</v>
       </c>
-      <c r="I51" s="9">
-        <v>1</v>
-      </c>
-      <c r="J51" s="9">
-        <v>0</v>
-      </c>
-      <c r="K51" s="9">
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
         <v>3</v>
       </c>
-      <c r="L51" s="9">
-        <v>0</v>
-      </c>
-      <c r="M51" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N51" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="O51" s="9">
-        <v>1</v>
-      </c>
-      <c r="P51" s="9">
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="s">
+        <v>94</v>
+      </c>
+      <c r="N51" t="s">
+        <v>94</v>
+      </c>
+      <c r="O51">
+        <v>1</v>
+      </c>
+      <c r="P51">
         <v>4</v>
       </c>
-      <c r="Q51" s="9">
-        <v>0</v>
-      </c>
-      <c r="R51" s="9">
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
         <v>100</v>
       </c>
-      <c r="S51" s="9">
+      <c r="S51">
         <v>30</v>
       </c>
-      <c r="T51" s="10" t="s">
+      <c r="T51" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="U51" s="9" t="s">
+      <c r="U51" t="s">
         <v>39</v>
       </c>
-      <c r="V51" s="9">
+      <c r="V51">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="9">
+    <row r="52" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52">
         <v>5003</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" t="s">
         <v>315</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" t="s">
         <v>139</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" t="s">
         <v>188</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" t="s">
         <v>138</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52">
         <v>6</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52">
         <v>6</v>
       </c>
-      <c r="I52" s="9">
-        <v>0</v>
-      </c>
-      <c r="J52" s="9">
-        <v>0</v>
-      </c>
-      <c r="K52" s="9">
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
         <v>3</v>
       </c>
-      <c r="L52" s="9">
-        <v>0</v>
-      </c>
-      <c r="M52" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N52" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="O52" s="9">
-        <v>1</v>
-      </c>
-      <c r="P52" s="9">
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52" t="s">
+        <v>94</v>
+      </c>
+      <c r="N52" t="s">
+        <v>94</v>
+      </c>
+      <c r="O52">
+        <v>1</v>
+      </c>
+      <c r="P52">
         <v>4</v>
       </c>
-      <c r="Q52" s="9">
-        <v>0</v>
-      </c>
-      <c r="R52" s="9">
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
         <v>100</v>
       </c>
-      <c r="S52" s="9">
+      <c r="S52">
         <v>480</v>
       </c>
-      <c r="T52" s="10" t="s">
+      <c r="T52" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="U52" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V52" s="9">
+      <c r="U52" t="s">
+        <v>94</v>
+      </c>
+      <c r="V52">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="9">
+    <row r="53" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53">
         <v>5005</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" t="s">
         <v>313</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" t="s">
         <v>200</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" t="s">
         <v>199</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F53" t="s">
         <v>198</v>
       </c>
-      <c r="G53" s="9">
+      <c r="G53">
         <v>6</v>
       </c>
-      <c r="H53" s="9">
+      <c r="H53">
         <v>3</v>
       </c>
-      <c r="I53" s="9">
-        <v>1</v>
-      </c>
-      <c r="J53" s="9">
-        <v>0</v>
-      </c>
-      <c r="K53" s="9">
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
         <v>3</v>
       </c>
-      <c r="L53" s="9">
-        <v>0</v>
-      </c>
-      <c r="M53" s="9" t="s">
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" t="s">
         <v>217</v>
       </c>
-      <c r="N53" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="O53" s="9">
-        <v>1</v>
-      </c>
-      <c r="P53" s="9">
+      <c r="N53" t="s">
+        <v>94</v>
+      </c>
+      <c r="O53">
+        <v>1</v>
+      </c>
+      <c r="P53">
         <v>4</v>
       </c>
-      <c r="Q53" s="9">
-        <v>0</v>
-      </c>
-      <c r="R53" s="9">
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
         <v>100</v>
       </c>
-      <c r="S53" s="9">
+      <c r="S53">
         <v>30</v>
       </c>
-      <c r="T53" s="10" t="s">
+      <c r="T53" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="U53" s="9" t="s">
+      <c r="U53" t="s">
         <v>273</v>
       </c>
-      <c r="V53" s="9">
+      <c r="V53">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="9">
+    <row r="54" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B54" s="9">
+      <c r="B54">
         <v>5006</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="C54" t="s">
         <v>314</v>
       </c>
-      <c r="D54" s="9" t="s">
+      <c r="D54" t="s">
         <v>214</v>
       </c>
-      <c r="E54" s="9" t="s">
+      <c r="E54" t="s">
         <v>213</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="F54" t="s">
         <v>330</v>
       </c>
-      <c r="G54" s="9">
+      <c r="G54">
         <v>6</v>
       </c>
-      <c r="H54" s="9">
+      <c r="H54">
         <v>8</v>
       </c>
-      <c r="I54" s="9">
-        <v>0</v>
-      </c>
-      <c r="J54" s="9">
-        <v>0</v>
-      </c>
-      <c r="K54" s="9">
-        <v>1</v>
-      </c>
-      <c r="L54" s="9">
-        <v>0</v>
-      </c>
-      <c r="M54" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N54" s="9" t="s">
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54" t="s">
+        <v>94</v>
+      </c>
+      <c r="N54" t="s">
         <v>238</v>
       </c>
-      <c r="O54" s="9">
-        <v>1</v>
-      </c>
-      <c r="P54" s="9">
+      <c r="O54">
+        <v>1</v>
+      </c>
+      <c r="P54">
         <v>4</v>
       </c>
-      <c r="Q54" s="9">
-        <v>0</v>
-      </c>
-      <c r="R54" s="9">
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
         <v>100</v>
       </c>
-      <c r="S54" s="9">
+      <c r="S54">
         <v>30</v>
       </c>
-      <c r="T54" s="10" t="s">
+      <c r="T54" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="U54" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V54" s="9">
+      <c r="U54" t="s">
+        <v>94</v>
+      </c>
+      <c r="V54">
         <v>0</v>
       </c>
     </row>
@@ -8235,210 +8229,210 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:22" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="9">
+    <row r="56" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56">
         <v>6002</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="C56" t="s">
         <v>282</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D56" t="s">
         <v>101</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E56" t="s">
         <v>100</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="F56" t="s">
         <v>96</v>
       </c>
-      <c r="G56" s="9">
+      <c r="G56">
         <v>6</v>
       </c>
-      <c r="H56" s="9">
+      <c r="H56">
         <v>2</v>
       </c>
-      <c r="I56" s="9">
-        <v>0</v>
-      </c>
-      <c r="J56" s="9">
-        <v>0</v>
-      </c>
-      <c r="K56" s="9">
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
         <v>5</v>
       </c>
-      <c r="L56" s="9">
-        <v>0</v>
-      </c>
-      <c r="M56" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N56" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="O56" s="9">
-        <v>1</v>
-      </c>
-      <c r="P56" s="9">
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" t="s">
+        <v>94</v>
+      </c>
+      <c r="N56" t="s">
+        <v>94</v>
+      </c>
+      <c r="O56">
+        <v>1</v>
+      </c>
+      <c r="P56">
         <v>5</v>
       </c>
-      <c r="Q56" s="9">
-        <v>0</v>
-      </c>
-      <c r="R56" s="9">
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
         <v>100</v>
       </c>
-      <c r="S56" s="9">
+      <c r="S56">
         <v>30</v>
       </c>
-      <c r="T56" s="10" t="s">
+      <c r="T56" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="U56" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V56" s="9">
+      <c r="U56" t="s">
+        <v>94</v>
+      </c>
+      <c r="V56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:22" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="9">
+    <row r="57" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57">
         <v>6004</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" t="s">
         <v>308</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" t="s">
         <v>261</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" t="s">
         <v>262</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" t="s">
         <v>263</v>
       </c>
-      <c r="G57" s="9">
+      <c r="G57">
         <v>6</v>
       </c>
-      <c r="H57" s="9">
+      <c r="H57">
         <v>5</v>
       </c>
-      <c r="I57" s="9">
-        <v>0</v>
-      </c>
-      <c r="J57" s="9">
-        <v>0</v>
-      </c>
-      <c r="K57" s="9">
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
         <v>3</v>
       </c>
-      <c r="L57" s="9">
-        <v>0</v>
-      </c>
-      <c r="M57" s="9" t="s">
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57" t="s">
         <v>135</v>
       </c>
-      <c r="N57" s="9" t="s">
+      <c r="N57" t="s">
         <v>135</v>
       </c>
-      <c r="O57" s="9">
-        <v>1</v>
-      </c>
-      <c r="P57" s="9">
+      <c r="O57">
+        <v>1</v>
+      </c>
+      <c r="P57">
         <v>5</v>
       </c>
-      <c r="Q57" s="9">
-        <v>1</v>
-      </c>
-      <c r="R57" s="9">
+      <c r="Q57">
+        <v>1</v>
+      </c>
+      <c r="R57">
         <v>100</v>
       </c>
-      <c r="S57" s="9">
+      <c r="S57">
         <v>30</v>
       </c>
-      <c r="T57" s="10" t="s">
+      <c r="T57" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="U57" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V57" s="9">
+      <c r="U57" t="s">
+        <v>94</v>
+      </c>
+      <c r="V57">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:22" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="9">
+    <row r="58" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58">
         <v>6005</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" t="s">
         <v>279</v>
       </c>
-      <c r="D58" s="9" t="s">
+      <c r="D58" t="s">
         <v>265</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E58" t="s">
         <v>266</v>
       </c>
-      <c r="F58" s="9" t="s">
+      <c r="F58" t="s">
         <v>267</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G58">
         <v>6</v>
       </c>
-      <c r="H58" s="9">
+      <c r="H58">
         <v>5</v>
       </c>
-      <c r="I58" s="9">
-        <v>1</v>
-      </c>
-      <c r="J58" s="9">
-        <v>0</v>
-      </c>
-      <c r="K58" s="9">
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
         <v>3</v>
       </c>
-      <c r="L58" s="9">
-        <v>0</v>
-      </c>
-      <c r="M58" s="9" t="s">
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58" t="s">
         <v>135</v>
       </c>
-      <c r="N58" s="9" t="s">
+      <c r="N58" t="s">
         <v>135</v>
       </c>
-      <c r="O58" s="9">
-        <v>1</v>
-      </c>
-      <c r="P58" s="9">
+      <c r="O58">
+        <v>1</v>
+      </c>
+      <c r="P58">
         <v>5</v>
       </c>
-      <c r="Q58" s="9">
-        <v>1</v>
-      </c>
-      <c r="R58" s="9">
+      <c r="Q58">
+        <v>1</v>
+      </c>
+      <c r="R58">
         <v>100</v>
       </c>
-      <c r="S58" s="9">
+      <c r="S58">
         <v>30</v>
       </c>
-      <c r="T58" s="10" t="s">
+      <c r="T58" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="U58" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V58" s="9">
+      <c r="U58" t="s">
+        <v>94</v>
+      </c>
+      <c r="V58">
         <v>0</v>
       </c>
     </row>
@@ -8856,72 +8850,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:22" s="9" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="9">
+    <row r="65" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65">
         <v>9005</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" t="s">
         <v>281</v>
       </c>
-      <c r="D65" s="9" t="s">
+      <c r="D65" t="s">
         <v>259</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="E65" t="s">
         <v>278</v>
       </c>
-      <c r="F65" s="9" t="s">
+      <c r="F65" t="s">
         <v>260</v>
       </c>
-      <c r="G65" s="9">
+      <c r="G65">
         <v>2</v>
       </c>
-      <c r="H65" s="9">
+      <c r="H65">
         <v>4</v>
       </c>
-      <c r="I65" s="9">
-        <v>1</v>
-      </c>
-      <c r="J65" s="9">
-        <v>0</v>
-      </c>
-      <c r="K65" s="9">
+      <c r="I65">
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
         <v>3</v>
       </c>
-      <c r="L65" s="9">
-        <v>0</v>
-      </c>
-      <c r="M65" s="9" t="s">
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65" t="s">
         <v>135</v>
       </c>
-      <c r="N65" s="9" t="s">
+      <c r="N65" t="s">
         <v>135</v>
       </c>
-      <c r="O65" s="9">
-        <v>1</v>
-      </c>
-      <c r="P65" s="9">
+      <c r="O65">
+        <v>1</v>
+      </c>
+      <c r="P65">
         <v>8</v>
       </c>
-      <c r="Q65" s="9">
-        <v>1</v>
-      </c>
-      <c r="R65" s="9">
+      <c r="Q65">
+        <v>1</v>
+      </c>
+      <c r="R65">
         <v>100</v>
       </c>
-      <c r="S65" s="9">
+      <c r="S65">
         <v>30</v>
       </c>
-      <c r="T65" s="10" t="s">
+      <c r="T65" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="U65" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V65" s="9">
+      <c r="U65" t="s">
+        <v>94</v>
+      </c>
+      <c r="V65">
         <v>0</v>
       </c>
     </row>
@@ -9063,72 +9057,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:22" s="9" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="9">
+    <row r="68" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68">
         <v>9003</v>
       </c>
-      <c r="C68" s="9" t="s">
+      <c r="C68" t="s">
         <v>280</v>
       </c>
-      <c r="D68" s="9" t="s">
+      <c r="D68" t="s">
         <v>108</v>
       </c>
-      <c r="E68" s="9" t="s">
+      <c r="E68" t="s">
         <v>107</v>
       </c>
-      <c r="F68" s="9" t="s">
+      <c r="F68" t="s">
         <v>91</v>
       </c>
-      <c r="G68" s="9">
+      <c r="G68">
         <v>6</v>
       </c>
-      <c r="H68" s="9">
-        <v>1</v>
-      </c>
-      <c r="I68" s="9">
-        <v>0</v>
-      </c>
-      <c r="J68" s="9">
-        <v>1</v>
-      </c>
-      <c r="K68" s="9">
-        <v>1</v>
-      </c>
-      <c r="L68" s="9">
-        <v>1</v>
-      </c>
-      <c r="M68" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N68" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="O68" s="9">
-        <v>1</v>
-      </c>
-      <c r="P68" s="9">
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="M68" t="s">
+        <v>94</v>
+      </c>
+      <c r="N68" t="s">
+        <v>94</v>
+      </c>
+      <c r="O68">
+        <v>1</v>
+      </c>
+      <c r="P68">
         <v>8</v>
       </c>
-      <c r="Q68" s="9">
-        <v>0</v>
-      </c>
-      <c r="R68" s="9">
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
         <v>100</v>
       </c>
-      <c r="S68" s="9">
+      <c r="S68">
         <v>30</v>
       </c>
-      <c r="T68" s="10" t="s">
+      <c r="T68" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="U68" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V68" s="9">
+      <c r="U68" t="s">
+        <v>94</v>
+      </c>
+      <c r="V68">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FAAC6D-9D7C-4016-A42A-1290099678E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2CD0E0-6F49-40FD-94E5-B79C3F98DEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="1110" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2160" yWindow="1185" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2CD0E0-6F49-40FD-94E5-B79C3F98DEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E428F020-86F6-4788-9E3E-6F442A4DC3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2160" yWindow="1185" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
@@ -4872,7 +4872,7 @@
         <v>2</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5010,7 +5010,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -5079,7 +5079,7 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -5424,7 +5424,7 @@
         <v>2</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -5493,7 +5493,7 @@
         <v>2</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         <v>2</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -5907,7 +5907,7 @@
         <v>2</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -5976,7 +5976,7 @@
         <v>4</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -6045,7 +6045,7 @@
         <v>4</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -6114,7 +6114,7 @@
         <v>4</v>
       </c>
       <c r="H25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -6597,7 +6597,7 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>1</v>
@@ -7149,7 +7149,7 @@
         <v>3</v>
       </c>
       <c r="H40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -7356,7 +7356,7 @@
         <v>3</v>
       </c>
       <c r="H43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I43">
         <v>1</v>
@@ -7839,7 +7839,7 @@
         <v>6</v>
       </c>
       <c r="H50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -8046,7 +8046,7 @@
         <v>6</v>
       </c>
       <c r="H53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -8874,7 +8874,7 @@
         <v>2</v>
       </c>
       <c r="H65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I65">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E428F020-86F6-4788-9E3E-6F442A4DC3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCFECF5-5E93-4FEA-AD82-A4167AA82ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="1185" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2685" yWindow="930" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3788,43 +3788,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>アイス水溶液に魔法をかけながら混ぜて、アイスクリーム制作時の成功率アップ・制作時間を少し短縮する。
-習得するだけでOK。
-LVに応じて、ほんのわずかになめらかさを出す。
-LV1: 成功率+2, 時間短縮+5%
-LV2: 成功率+4, 時間短縮+10%
-LV3: 成功率+6, 時間短縮+15%
-LV4: 成功率+8, 時間短縮+20%
-LV5: 成功率+10, 時間短縮+25%
-LV6: 成功率+12, 時間短縮+30%
-LV7: 成功率+14, 時間短縮+35%
-LV8: 成功率+16, 時間短縮+40%
-LV9: 成功率+18, 時間短縮+45%
-LV10: 成功率+20, 時間短縮+50%</t>
-    <rPh sb="26" eb="29">
-      <t>セイサクジ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>シュウトク</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="82" eb="83">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="92" eb="95">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="99" eb="101">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>タンシュク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ソーダについて勉強する。
 LVが上がるにつれて、ジュース・ソーダを作る際の成功率が上昇する。
 また、わずかに、ソーダののどごしもアップする。
@@ -3995,6 +3958,50 @@
   </si>
   <si>
     <t>アロマ・バブル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アイス水溶液に魔法をかけながら混ぜて、アイスクリーム制作時の成功率アップする。
+また、フリージング使用時の制作時間も短縮する。
+習得するだけでOK。
+LVに応じて、ほんのわずかになめらかさを出す。
+LV1: 成功率+2, 時間短縮+5%
+LV2: 成功率+4, 時間短縮+10%
+LV3: 成功率+6, 時間短縮+15%
+LV4: 成功率+8, 時間短縮+20%
+LV5: 成功率+10, 時間短縮+25%
+LV6: 成功率+12, 時間短縮+30%
+LV7: 成功率+14, 時間短縮+35%
+LV8: 成功率+16, 時間短縮+40%
+LV9: 成功率+18, 時間短縮+45%
+LV10: 成功率+20, 時間短縮+50%</t>
+    <rPh sb="26" eb="29">
+      <t>セイサクジ</t>
+    </rPh>
+    <rPh sb="49" eb="52">
+      <t>シヨウジ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>シュウトク</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="106" eb="109">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="113" eb="115">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>タンシュク</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4737,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -4944,7 +4951,7 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -5013,7 +5020,7 @@
         <v>3</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -5118,10 +5125,10 @@
         <v>276</v>
       </c>
       <c r="U10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="V10">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5391,7 +5398,7 @@
         <v>30</v>
       </c>
       <c r="T14" s="8" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="U14" t="s">
         <v>94</v>
@@ -5673,7 +5680,7 @@
         <v>51</v>
       </c>
       <c r="V18">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -6564,7 +6571,7 @@
         <v>30</v>
       </c>
       <c r="T31" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="U31" t="s">
         <v>94</v>
@@ -6705,10 +6712,10 @@
         <v>324</v>
       </c>
       <c r="U33" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -7140,7 +7147,7 @@
         <v>27</v>
       </c>
       <c r="E40" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F40" t="s">
         <v>221</v>
@@ -7188,10 +7195,10 @@
         <v>264</v>
       </c>
       <c r="U40" t="s">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="V40">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:22" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -7806,7 +7813,7 @@
         <v>30</v>
       </c>
       <c r="T49" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="U49" t="s">
         <v>94</v>
@@ -7833,7 +7840,7 @@
         <v>38</v>
       </c>
       <c r="F50" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G50">
         <v>6</v>
@@ -7875,7 +7882,7 @@
         <v>15</v>
       </c>
       <c r="T50" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="U50" t="s">
         <v>273</v>
@@ -8016,10 +8023,10 @@
         <v>205</v>
       </c>
       <c r="U52" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -8109,7 +8116,7 @@
         <v>213</v>
       </c>
       <c r="F54" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G54">
         <v>6</v>
@@ -8130,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="N54" t="s">
         <v>238</v>
@@ -8151,7 +8158,7 @@
         <v>30</v>
       </c>
       <c r="T54" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="U54" t="s">
         <v>94</v>
@@ -8820,10 +8827,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>135</v>
+        <v>247</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>135</v>
+        <v>238</v>
       </c>
       <c r="O64" s="2">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCFECF5-5E93-4FEA-AD82-A4167AA82ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7945D96E-F236-4C6E-9EDC-192AC34390C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="930" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2565" yWindow="975" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="378">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -4001,6 +4001,466 @@
     </rPh>
     <rPh sb="115" eb="117">
       <t>タンシュク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ラトリア</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Latria</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ラトリア状態になる。一定時間、油っこさや水っぽさを減らす。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ラトリア状態になる。
+ラトリア状態の間は、一定時間、お菓子を作る際の油っこさや水っぽさを減らす。
+※すでに作ったあとのお菓子には効果がない。</t>
+    <rPh sb="16" eb="18">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エピクレイシス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Epiclesis</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>次に作るお菓子の成功率を一時的に上げる。</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>イチジテキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>次に作るお菓子の成功率を一時的に上げる「エピクレイシス状態」になる。
+エピクレイシス状態は、数回で消える。</t>
+    <rPh sb="27" eb="29">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>スウカイ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クレッセント・ムーン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>星の力で、三日月をお菓子に浮かべる。</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ミカヅキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>星の力で、三日月をお菓子に浮かべる。
+星や鉱物に関係するお菓子と相性がよい。
+◆おかしにかける場合は、仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="0" eb="1">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ミカヅキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウブツ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>アイショウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Crescent_Moon</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スリースターズ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Tree_Stars</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スリースターズ状態になる。一定の間、消費MPがすべて１になる。</t>
+    <rPh sb="7" eb="9">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イッテイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ショウヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スリースターズ状態になる。一定の間、消費MPがすべて１になる。
+お菓子を何度か作ると、スリースターズ状態は解除される。</t>
+    <rPh sb="7" eb="9">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イッテイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ナンド</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>カイジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ナイト・バロン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お菓子に大人っぽさの演出効果を加える。</t>
+    <rPh sb="1" eb="3">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>オトナ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>クワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Night_Barron</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お菓子に大人っぽさの演出効果を加える。
+LVが上がると効果が高まる。
+相性が良ければ、お菓子に大人っぽさを追加でき、見た目も上がる。
+◆パネルにお菓子がセットされた状態でないと使えない。
+◆仕上げ回数を一回消費する。
+仕上げ回数がないと、使用できない。</t>
+    <rPh sb="23" eb="24">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>アイショウ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>オトナ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リッチ・マテリアル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素材を、一つ上の品質のよいものに変える</t>
+    <rPh sb="0" eb="2">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Rich_Material</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素材を、一つ上の品質のよいものに変える。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>パーフェクト・プリンセス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Parfect_Princess</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>甘さ・酸味・苦味がパーフェクトに近いとき、さらに点数を上げる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>甘さ・酸味・苦味がパーフェクトに近いとき、さらに点数を上げる。
+習得するだけでOK。</t>
+    <rPh sb="32" eb="34">
+      <t>シュウトク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ファイア・アーク</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生地にかけると、さくさく感をアップする。</t>
+    <rPh sb="0" eb="2">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生地にかけると、さくさく感をアップする。
+LVが上がると、効果もアップする。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Fire_Ark</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ライトニング・グレープ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ぶどうにかけると、ぶどうをすっぱくする</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Lightning_Grape</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>夢見るサファイア</t>
+    <rPh sb="0" eb="2">
+      <t>ユメミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Dreamy_Sapphire</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シュガーにかけると、シュガーの性質を変える</t>
+    <rPh sb="15" eb="17">
+      <t>セイシツ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シュガーにかけると、シュガーの性質を変える。
+サファイアシュガーにのみかけることができる。</t>
+    <rPh sb="15" eb="17">
+      <t>セイシツ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ティーのお勉強</t>
+    <rPh sb="5" eb="7">
+      <t>ベンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Tea_Study</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>紅茶・コーヒーについて勉強する。</t>
+    <rPh sb="0" eb="2">
+      <t>コウチャ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ベンキョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>紅茶とコーヒーについてお勉強する。
+LVが上がるにつれて、ティー・コーヒーを作る際の成功率が上昇する。
+また、わずかに、香りもアップする。
+LV1: 成功率+2%
+LV2: 成功率+4%
+LV3: 成功率+6%
+LV4: 成功率+8%
+LV5: 成功率+10%
+LV6: 成功率+12%
+LV7: 成功率+14%
+LV8: 成功率+16%
+LV9: 成功率+18%
+LV10: 成功率+20%</t>
+    <rPh sb="0" eb="2">
+      <t>コウチャ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ベンキョウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="42" eb="45">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ジョウショウ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>カオ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4038,7 +4498,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4069,6 +4529,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -4084,7 +4550,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4108,6 +4574,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4424,7 +4896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:V68"/>
+  <dimension ref="A1:V79"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -4512,7 +4984,7 @@
     </row>
     <row r="2" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A68" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A79" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="4">
@@ -4855,103 +5327,103 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7">
+    <row r="7" spans="1:22" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>1003</v>
-      </c>
-      <c r="C7" t="s">
-        <v>295</v>
-      </c>
-      <c r="D7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
+      <c r="B7" s="9">
+        <v>1012</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="G7" s="9">
+        <v>6</v>
+      </c>
+      <c r="H7" s="9">
+        <v>5</v>
+      </c>
+      <c r="I7" s="9">
+        <v>1</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
         <v>3</v>
       </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
+      <c r="L7" s="9">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O7" s="9">
+        <v>1</v>
+      </c>
+      <c r="P7" s="9">
+        <v>9</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+      <c r="R7" s="9">
+        <v>100</v>
+      </c>
+      <c r="S7" s="9">
+        <v>30</v>
+      </c>
+      <c r="T7" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="U7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="V7" s="9">
         <v>3</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N7" t="s">
-        <v>94</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>9</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>100</v>
-      </c>
-      <c r="S7">
-        <v>30</v>
-      </c>
-      <c r="T7" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="U7" t="s">
-        <v>54</v>
-      </c>
-      <c r="V7">
-        <v>1</v>
-      </c>
     </row>
-    <row r="8" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B8">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>295</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -4966,7 +5438,7 @@
         <v>94</v>
       </c>
       <c r="N8" t="s">
-        <v>238</v>
+        <v>94</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -4984,10 +5456,10 @@
         <v>30</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>316</v>
+        <v>150</v>
       </c>
       <c r="U8" t="s">
-        <v>163</v>
+        <v>54</v>
       </c>
       <c r="V8">
         <v>1</v>
@@ -4999,25 +5471,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C9" t="s">
-        <v>310</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="G9">
         <v>6</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -5035,7 +5507,7 @@
         <v>94</v>
       </c>
       <c r="N9" t="s">
-        <v>94</v>
+        <v>238</v>
       </c>
       <c r="O9">
         <v>1</v>
@@ -5053,10 +5525,10 @@
         <v>30</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>270</v>
+        <v>316</v>
       </c>
       <c r="U9" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="V9">
         <v>1</v>
@@ -5068,28 +5540,28 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C10" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="D10" t="s">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="F10" t="s">
-        <v>224</v>
+        <v>104</v>
       </c>
       <c r="G10">
         <v>6</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -5101,10 +5573,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="N10" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="O10">
         <v>1</v>
@@ -5113,7 +5585,7 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -5122,67 +5594,67 @@
         <v>30</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="U10" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B11">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>298</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>222</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>223</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>224</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="N11" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11">
         <v>9</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -5191,288 +5663,288 @@
         <v>30</v>
       </c>
       <c r="T11" s="8" t="s">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="U11" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="4">
+    <row r="12" spans="1:22" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="4">
-        <v>1007</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G12" s="4">
+      <c r="B12" s="9">
+        <v>1011</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="G12" s="9">
         <v>6</v>
       </c>
-      <c r="H12" s="4">
-        <v>1</v>
-      </c>
-      <c r="I12" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J12" s="4">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4">
-        <v>1</v>
-      </c>
-      <c r="L12" s="4">
-        <v>0</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O12" s="4">
-        <v>1</v>
-      </c>
-      <c r="P12" s="4">
+      <c r="H12" s="9">
+        <v>5</v>
+      </c>
+      <c r="I12" s="9">
+        <v>1</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>3</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="O12" s="9">
+        <v>1</v>
+      </c>
+      <c r="P12" s="9">
         <v>9</v>
       </c>
-      <c r="Q12" s="4">
-        <v>0</v>
-      </c>
-      <c r="R12" s="4">
+      <c r="Q12" s="9">
+        <v>1</v>
+      </c>
+      <c r="R12" s="9">
         <v>100</v>
       </c>
-      <c r="S12" s="4">
+      <c r="S12" s="9">
         <v>30</v>
       </c>
-      <c r="T12" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="U12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V12" s="4">
-        <v>0</v>
+      <c r="T12" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="U12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="V12" s="9">
+        <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="4">
+    <row r="13" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="4">
-        <v>1009</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="G13" s="4">
-        <v>6</v>
-      </c>
-      <c r="H13" s="4">
-        <v>20</v>
-      </c>
-      <c r="I13" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J13" s="4">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4">
-        <v>3</v>
-      </c>
-      <c r="L13" s="4">
-        <v>0</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O13" s="4">
-        <v>1</v>
-      </c>
-      <c r="P13" s="4">
+      <c r="B13">
+        <v>1004</v>
+      </c>
+      <c r="C13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>94</v>
+      </c>
+      <c r="N13" t="s">
+        <v>94</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
         <v>9</v>
       </c>
-      <c r="Q13" s="4">
-        <v>0</v>
-      </c>
-      <c r="R13" s="4">
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
         <v>100</v>
       </c>
-      <c r="S13" s="4">
+      <c r="S13">
         <v>30</v>
       </c>
-      <c r="T13" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="U13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V13" s="4">
+      <c r="T13" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="U13" t="s">
+        <v>94</v>
+      </c>
+      <c r="V13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14">
+    <row r="14" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14">
-        <v>2004</v>
-      </c>
-      <c r="C14" t="s">
-        <v>293</v>
-      </c>
-      <c r="D14" t="s">
-        <v>110</v>
-      </c>
-      <c r="E14" t="s">
-        <v>109</v>
-      </c>
-      <c r="F14" t="s">
-        <v>164</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>10</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14" t="s">
-        <v>94</v>
-      </c>
-      <c r="N14" t="s">
-        <v>94</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>1</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
+      <c r="B14" s="4">
+        <v>1007</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" s="4">
+        <v>6</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1</v>
+      </c>
+      <c r="I14" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4">
+        <v>1</v>
+      </c>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O14" s="4">
+        <v>1</v>
+      </c>
+      <c r="P14" s="4">
+        <v>9</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>0</v>
+      </c>
+      <c r="R14" s="4">
         <v>100</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="4">
         <v>30</v>
       </c>
-      <c r="T14" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="U14" t="s">
-        <v>94</v>
-      </c>
-      <c r="V14">
+      <c r="T14" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V14" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15">
+    <row r="15" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15">
-        <v>2001</v>
-      </c>
-      <c r="C15" t="s">
-        <v>143</v>
-      </c>
-      <c r="D15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-      <c r="H15">
+      <c r="B15" s="4">
+        <v>1009</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G15" s="4">
+        <v>6</v>
+      </c>
+      <c r="H15" s="4">
+        <v>20</v>
+      </c>
+      <c r="I15" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
         <v>3</v>
       </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>5</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15" t="s">
-        <v>94</v>
-      </c>
-      <c r="N15" t="s">
-        <v>94</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-      <c r="P15">
-        <v>1</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
+      <c r="L15" s="4">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O15" s="4">
+        <v>1</v>
+      </c>
+      <c r="P15" s="4">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>0</v>
+      </c>
+      <c r="R15" s="4">
         <v>100</v>
       </c>
-      <c r="S15">
-        <v>120</v>
-      </c>
-      <c r="T15" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="U15" t="s">
-        <v>94</v>
-      </c>
-      <c r="V15">
+      <c r="S15" s="4">
+        <v>30</v>
+      </c>
+      <c r="T15" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="U15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V15" s="4">
         <v>0</v>
       </c>
     </row>
@@ -5482,34 +5954,34 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="C16" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D16" t="s">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
-        <v>178</v>
+        <v>109</v>
       </c>
       <c r="F16" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="G16">
         <v>2</v>
       </c>
       <c r="H16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -5521,7 +5993,7 @@
         <v>94</v>
       </c>
       <c r="O16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16">
         <v>1</v>
@@ -5533,84 +6005,84 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="T16" s="8" t="s">
-        <v>186</v>
+        <v>334</v>
       </c>
       <c r="U16" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="V16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="4">
+    <row r="17" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="4">
-        <v>2002</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G17" s="4">
+      <c r="B17">
+        <v>2001</v>
+      </c>
+      <c r="C17" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17">
         <v>2</v>
       </c>
-      <c r="H17" s="4">
-        <v>1</v>
-      </c>
-      <c r="I17" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J17" s="4">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4">
-        <v>1</v>
-      </c>
-      <c r="L17" s="4">
-        <v>0</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O17" s="4">
-        <v>1</v>
-      </c>
-      <c r="P17" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="4">
-        <v>0</v>
-      </c>
-      <c r="R17" s="4">
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>5</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
+        <v>94</v>
+      </c>
+      <c r="N17" t="s">
+        <v>94</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
         <v>100</v>
       </c>
-      <c r="S17" s="4">
+      <c r="S17">
         <v>120</v>
       </c>
-      <c r="T17" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="U17" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V17" s="4">
+      <c r="T17" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="U17" t="s">
+        <v>94</v>
+      </c>
+      <c r="V17">
         <v>0</v>
       </c>
     </row>
@@ -5620,43 +6092,43 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D18" t="s">
-        <v>253</v>
+        <v>175</v>
       </c>
       <c r="E18" t="s">
-        <v>275</v>
+        <v>178</v>
       </c>
       <c r="F18" t="s">
-        <v>254</v>
+        <v>185</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="N18" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="O18">
         <v>1</v>
@@ -5665,190 +6137,190 @@
         <v>1</v>
       </c>
       <c r="Q18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="S18">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>277</v>
+        <v>186</v>
       </c>
       <c r="U18" t="s">
         <v>51</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19">
+    <row r="19" spans="1:22" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19">
-        <v>2003</v>
-      </c>
-      <c r="C19" t="s">
-        <v>290</v>
-      </c>
-      <c r="D19" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" t="s">
-        <v>111</v>
-      </c>
-      <c r="F19" t="s">
-        <v>134</v>
-      </c>
-      <c r="G19">
+      <c r="B19" s="4">
+        <v>2002</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="4">
         <v>2</v>
       </c>
-      <c r="H19">
-        <v>3</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>5</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19" t="s">
-        <v>94</v>
-      </c>
-      <c r="N19" t="s">
-        <v>238</v>
-      </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-      <c r="P19">
-        <v>1</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
+      <c r="H19" s="4">
+        <v>1</v>
+      </c>
+      <c r="I19" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4">
+        <v>1</v>
+      </c>
+      <c r="L19" s="4">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O19" s="4">
+        <v>1</v>
+      </c>
+      <c r="P19" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4">
         <v>100</v>
       </c>
-      <c r="S19">
-        <v>30</v>
-      </c>
-      <c r="T19" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="U19" t="s">
-        <v>101</v>
-      </c>
-      <c r="V19">
-        <v>1</v>
+      <c r="S19" s="4">
+        <v>120</v>
+      </c>
+      <c r="T19" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V19" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="4">
+    <row r="20" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="4">
-        <v>2003</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="G20" s="4">
+      <c r="B20">
+        <v>2005</v>
+      </c>
+      <c r="C20" t="s">
+        <v>292</v>
+      </c>
+      <c r="D20" t="s">
+        <v>253</v>
+      </c>
+      <c r="E20" t="s">
+        <v>275</v>
+      </c>
+      <c r="F20" t="s">
+        <v>254</v>
+      </c>
+      <c r="G20">
         <v>2</v>
       </c>
-      <c r="H20" s="4">
-        <v>20</v>
-      </c>
-      <c r="I20" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J20" s="4">
-        <v>0</v>
-      </c>
-      <c r="K20" s="4">
+      <c r="H20">
         <v>5</v>
       </c>
-      <c r="L20" s="4">
-        <v>0</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O20" s="4">
-        <v>1</v>
-      </c>
-      <c r="P20" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="4">
-        <v>0</v>
-      </c>
-      <c r="R20" s="4">
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="s">
+        <v>135</v>
+      </c>
+      <c r="N20" t="s">
+        <v>135</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
         <v>100</v>
       </c>
-      <c r="S20" s="4">
+      <c r="S20">
         <v>30</v>
       </c>
-      <c r="T20" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="U20" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V20" s="4">
-        <v>0</v>
+      <c r="T20" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="U20" t="s">
+        <v>51</v>
+      </c>
+      <c r="V20">
+        <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B21">
-        <v>3006</v>
+        <v>2003</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>290</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="E21" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="F21" t="s">
-        <v>232</v>
+        <v>134</v>
       </c>
       <c r="G21">
         <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -5863,13 +6335,13 @@
         <v>94</v>
       </c>
       <c r="N21" t="s">
-        <v>94</v>
+        <v>238</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5881,112 +6353,112 @@
         <v>30</v>
       </c>
       <c r="T21" s="8" t="s">
-        <v>233</v>
+        <v>322</v>
       </c>
       <c r="U21" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22">
+    <row r="22" spans="1:22" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22">
-        <v>3001</v>
-      </c>
-      <c r="C22" t="s">
-        <v>140</v>
-      </c>
-      <c r="D22" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" t="s">
-        <v>230</v>
-      </c>
-      <c r="F22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22">
+      <c r="B22" s="4">
+        <v>2003</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G22" s="4">
         <v>2</v>
       </c>
-      <c r="H22">
-        <v>3</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22">
+      <c r="H22" s="4">
+        <v>20</v>
+      </c>
+      <c r="I22" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0</v>
+      </c>
+      <c r="K22" s="4">
         <v>5</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22" t="s">
-        <v>94</v>
-      </c>
-      <c r="N22" t="s">
-        <v>238</v>
-      </c>
-      <c r="O22">
-        <v>1</v>
-      </c>
-      <c r="P22">
-        <v>2</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
+      <c r="L22" s="4">
+        <v>0</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O22" s="4">
+        <v>1</v>
+      </c>
+      <c r="P22" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>0</v>
+      </c>
+      <c r="R22" s="4">
         <v>100</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="4">
         <v>30</v>
       </c>
-      <c r="T22" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="U22" t="s">
-        <v>94</v>
-      </c>
-      <c r="V22">
+      <c r="T22" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V22" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B23">
-        <v>3002</v>
+        <v>3006</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>232</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -6001,10 +6473,10 @@
         <v>94</v>
       </c>
       <c r="N23" t="s">
-        <v>238</v>
+        <v>94</v>
       </c>
       <c r="O23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23">
         <v>2</v>
@@ -6019,58 +6491,58 @@
         <v>30</v>
       </c>
       <c r="T23" s="8" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="U23" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B24">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="C24" t="s">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="F24" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
         <v>5</v>
       </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>3</v>
-      </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="N24" t="s">
-        <v>135</v>
+        <v>238</v>
       </c>
       <c r="O24">
         <v>1</v>
@@ -6079,7 +6551,7 @@
         <v>2</v>
       </c>
       <c r="Q24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -6088,13 +6560,13 @@
         <v>30</v>
       </c>
       <c r="T24" s="8" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="U24" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -6103,43 +6575,43 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>3008</v>
+        <v>3002</v>
       </c>
       <c r="C25" t="s">
-        <v>288</v>
+        <v>141</v>
       </c>
       <c r="D25" t="s">
-        <v>256</v>
+        <v>20</v>
       </c>
       <c r="E25" t="s">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="G25">
         <v>4</v>
       </c>
       <c r="H25">
+        <v>4</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
         <v>5</v>
       </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>3</v>
-      </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="N25" t="s">
-        <v>135</v>
+        <v>238</v>
       </c>
       <c r="O25">
         <v>1</v>
@@ -6148,7 +6620,7 @@
         <v>2</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -6157,13 +6629,13 @@
         <v>30</v>
       </c>
       <c r="T25" s="8" t="s">
-        <v>258</v>
+        <v>219</v>
       </c>
       <c r="U25" t="s">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -6172,52 +6644,52 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="C26" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E26" t="s">
-        <v>113</v>
+        <v>216</v>
       </c>
       <c r="F26" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="G26">
         <v>4</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="N26" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26">
         <v>2</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -6226,13 +6698,13 @@
         <v>30</v>
       </c>
       <c r="T26" s="8" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="U26" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -6241,25 +6713,25 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="C27" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="D27" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E27" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="F27" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="G27">
         <v>4</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -6268,25 +6740,25 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="N27" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27">
         <v>2</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -6295,7 +6767,7 @@
         <v>30</v>
       </c>
       <c r="T27" s="8" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="U27" t="s">
         <v>94</v>
@@ -6304,166 +6776,166 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="4">
+    <row r="28" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="9">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="4">
-        <v>3005</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G28" s="4">
+      <c r="B28" s="9">
+        <v>3009</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="G28" s="9">
         <v>4</v>
       </c>
-      <c r="H28" s="4">
-        <v>20</v>
-      </c>
-      <c r="I28" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J28" s="4">
-        <v>0</v>
-      </c>
-      <c r="K28" s="4">
+      <c r="H28" s="9">
         <v>5</v>
       </c>
-      <c r="L28" s="4">
-        <v>0</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N28" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O28" s="4">
-        <v>1</v>
-      </c>
-      <c r="P28" s="4">
+      <c r="I28" s="9">
+        <v>0</v>
+      </c>
+      <c r="J28" s="9">
+        <v>0</v>
+      </c>
+      <c r="K28" s="9">
+        <v>3</v>
+      </c>
+      <c r="L28" s="9">
+        <v>0</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O28" s="9">
+        <v>1</v>
+      </c>
+      <c r="P28" s="9">
         <v>2</v>
       </c>
-      <c r="Q28" s="4">
-        <v>0</v>
-      </c>
-      <c r="R28" s="4">
+      <c r="Q28" s="9">
+        <v>1</v>
+      </c>
+      <c r="R28" s="9">
         <v>100</v>
       </c>
-      <c r="S28" s="4">
+      <c r="S28" s="9">
         <v>30</v>
       </c>
-      <c r="T28" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="U28" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V28" s="4">
+      <c r="T28" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="U28" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V28" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="4">
+    <row r="29" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="9">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="4">
-        <v>3005</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="G29" s="4">
+      <c r="B29" s="9">
+        <v>3010</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="G29" s="9">
         <v>4</v>
       </c>
-      <c r="H29" s="4">
-        <v>10</v>
-      </c>
-      <c r="I29" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J29" s="4">
-        <v>0</v>
-      </c>
-      <c r="K29" s="4">
-        <v>5</v>
-      </c>
-      <c r="L29" s="4">
-        <v>0</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O29" s="4">
-        <v>1</v>
-      </c>
-      <c r="P29" s="4">
+      <c r="H29" s="9">
+        <v>0</v>
+      </c>
+      <c r="I29" s="9">
+        <v>0</v>
+      </c>
+      <c r="J29" s="9">
+        <v>0</v>
+      </c>
+      <c r="K29" s="9">
+        <v>3</v>
+      </c>
+      <c r="L29" s="9">
+        <v>0</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O29" s="9">
+        <v>0</v>
+      </c>
+      <c r="P29" s="9">
         <v>2</v>
       </c>
-      <c r="Q29" s="4">
-        <v>0</v>
-      </c>
-      <c r="R29" s="4">
+      <c r="Q29" s="9">
+        <v>1</v>
+      </c>
+      <c r="R29" s="9">
         <v>100</v>
       </c>
-      <c r="S29" s="4">
+      <c r="S29" s="9">
         <v>30</v>
       </c>
-      <c r="T29" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="U29" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V29" s="4">
+      <c r="T29" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="U29" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V29" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B30">
-        <v>4010</v>
+        <v>3004</v>
       </c>
       <c r="C30" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D30" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="E30" t="s">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="F30" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -6475,7 +6947,7 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -6490,7 +6962,7 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -6502,7 +6974,7 @@
         <v>30</v>
       </c>
       <c r="T30" s="8" t="s">
-        <v>323</v>
+        <v>191</v>
       </c>
       <c r="U30" t="s">
         <v>94</v>
@@ -6511,40 +6983,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B31">
-        <v>4011</v>
+        <v>3007</v>
       </c>
       <c r="C31" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D31" t="s">
-        <v>154</v>
+        <v>250</v>
       </c>
       <c r="E31" t="s">
-        <v>208</v>
+        <v>274</v>
       </c>
       <c r="F31" t="s">
-        <v>155</v>
+        <v>251</v>
       </c>
       <c r="G31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -6559,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -6571,7 +7043,7 @@
         <v>30</v>
       </c>
       <c r="T31" s="8" t="s">
-        <v>328</v>
+        <v>252</v>
       </c>
       <c r="U31" t="s">
         <v>94</v>
@@ -6580,145 +7052,145 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32">
+    <row r="32" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="4">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B32">
-        <v>4001</v>
-      </c>
-      <c r="C32" t="s">
-        <v>283</v>
-      </c>
-      <c r="D32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" t="s">
-        <v>21</v>
-      </c>
-      <c r="F32" t="s">
-        <v>245</v>
-      </c>
-      <c r="G32">
-        <v>6</v>
-      </c>
-      <c r="H32">
+      <c r="B32" s="4">
+        <v>3005</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G32" s="4">
+        <v>4</v>
+      </c>
+      <c r="H32" s="4">
+        <v>20</v>
+      </c>
+      <c r="I32" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J32" s="4">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4">
         <v>5</v>
       </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>3</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32" t="s">
-        <v>247</v>
-      </c>
-      <c r="N32" t="s">
-        <v>238</v>
-      </c>
-      <c r="O32">
-        <v>1</v>
-      </c>
-      <c r="P32">
-        <v>3</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>85</v>
-      </c>
-      <c r="S32">
-        <v>10</v>
-      </c>
-      <c r="T32" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="U32" t="s">
-        <v>154</v>
-      </c>
-      <c r="V32">
-        <v>1</v>
+      <c r="L32" s="4">
+        <v>0</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O32" s="4">
+        <v>1</v>
+      </c>
+      <c r="P32" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>0</v>
+      </c>
+      <c r="R32" s="4">
+        <v>100</v>
+      </c>
+      <c r="S32" s="4">
+        <v>30</v>
+      </c>
+      <c r="T32" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="U32" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V32" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33">
+    <row r="33" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="4">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B33">
-        <v>4002</v>
-      </c>
-      <c r="C33" t="s">
-        <v>284</v>
-      </c>
-      <c r="D33" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" t="s">
-        <v>192</v>
-      </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-      <c r="H33">
+      <c r="B33" s="4">
+        <v>3005</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G33" s="4">
         <v>4</v>
       </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>3</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33" t="s">
-        <v>94</v>
-      </c>
-      <c r="N33" t="s">
-        <v>238</v>
-      </c>
-      <c r="O33">
-        <v>1</v>
-      </c>
-      <c r="P33">
-        <v>3</v>
-      </c>
-      <c r="Q33">
-        <v>0</v>
-      </c>
-      <c r="R33">
+      <c r="H33" s="4">
+        <v>10</v>
+      </c>
+      <c r="I33" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J33" s="4">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4">
+        <v>5</v>
+      </c>
+      <c r="L33" s="4">
+        <v>0</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O33" s="4">
+        <v>1</v>
+      </c>
+      <c r="P33" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q33" s="4">
+        <v>0</v>
+      </c>
+      <c r="R33" s="4">
         <v>100</v>
       </c>
-      <c r="S33">
-        <v>15</v>
-      </c>
-      <c r="T33" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="U33" t="s">
-        <v>23</v>
-      </c>
-      <c r="V33">
-        <v>1</v>
+      <c r="S33" s="4">
+        <v>30</v>
+      </c>
+      <c r="T33" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="U33" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V33" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -6727,22 +7199,22 @@
         <v>4010</v>
       </c>
       <c r="C34" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="D34" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="E34" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="F34" t="s">
-        <v>193</v>
+        <v>153</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -6751,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -6760,10 +7232,10 @@
         <v>94</v>
       </c>
       <c r="N34" t="s">
-        <v>238</v>
+        <v>94</v>
       </c>
       <c r="O34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34">
         <v>3</v>
@@ -6775,19 +7247,19 @@
         <v>100</v>
       </c>
       <c r="S34">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T34" s="8" t="s">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="U34" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="V34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -6796,31 +7268,31 @@
         <v>4011</v>
       </c>
       <c r="C35" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="D35" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="E35" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="F35" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -6829,10 +7301,10 @@
         <v>94</v>
       </c>
       <c r="N35" t="s">
-        <v>238</v>
+        <v>94</v>
       </c>
       <c r="O35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35">
         <v>3</v>
@@ -6844,58 +7316,58 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T35" s="8" t="s">
-        <v>182</v>
+        <v>328</v>
       </c>
       <c r="U35" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="V35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B36">
-        <v>4012</v>
+        <v>4001</v>
       </c>
       <c r="C36" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D36" t="s">
-        <v>173</v>
+        <v>23</v>
       </c>
       <c r="E36" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="F36" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>94</v>
+        <v>247</v>
       </c>
       <c r="N36" t="s">
         <v>238</v>
@@ -6910,16 +7382,16 @@
         <v>0</v>
       </c>
       <c r="R36">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="S36">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" s="8" t="s">
-        <v>325</v>
+        <v>248</v>
       </c>
       <c r="U36" t="s">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="V36">
         <v>1</v>
@@ -6931,19 +7403,19 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>4012</v>
+        <v>4002</v>
       </c>
       <c r="C37" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="D37" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="E37" t="s">
-        <v>176</v>
+        <v>22</v>
       </c>
       <c r="F37" t="s">
-        <v>318</v>
+        <v>192</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -6958,7 +7430,7 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -6985,7 +7457,7 @@
         <v>15</v>
       </c>
       <c r="T37" s="8" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="U37" t="s">
         <v>23</v>
@@ -7000,19 +7472,19 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="C38" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="D38" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="E38" t="s">
-        <v>184</v>
+        <v>129</v>
       </c>
       <c r="F38" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -7027,7 +7499,7 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -7054,7 +7526,7 @@
         <v>15</v>
       </c>
       <c r="T38" s="8" t="s">
-        <v>320</v>
+        <v>194</v>
       </c>
       <c r="U38" t="s">
         <v>23</v>
@@ -7063,73 +7535,73 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:22" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="4">
+    <row r="39" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B39" s="4">
-        <v>4003</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G39" s="4">
+      <c r="B39">
+        <v>4011</v>
+      </c>
+      <c r="C39" t="s">
+        <v>286</v>
+      </c>
+      <c r="D39" t="s">
+        <v>171</v>
+      </c>
+      <c r="E39" t="s">
+        <v>170</v>
+      </c>
+      <c r="F39" t="s">
+        <v>181</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
         <v>3</v>
       </c>
-      <c r="H39" s="4">
-        <v>2</v>
-      </c>
-      <c r="I39" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J39" s="4">
-        <v>0</v>
-      </c>
-      <c r="K39" s="4">
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" t="s">
+        <v>94</v>
+      </c>
+      <c r="N39" t="s">
+        <v>238</v>
+      </c>
+      <c r="O39">
+        <v>1</v>
+      </c>
+      <c r="P39">
         <v>3</v>
       </c>
-      <c r="L39" s="4">
-        <v>0</v>
-      </c>
-      <c r="M39" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N39" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O39" s="4">
-        <v>1</v>
-      </c>
-      <c r="P39" s="4">
-        <v>3</v>
-      </c>
-      <c r="Q39" s="4">
-        <v>0</v>
-      </c>
-      <c r="R39" s="4">
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
         <v>100</v>
       </c>
-      <c r="S39" s="4">
-        <v>30</v>
-      </c>
-      <c r="T39" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="U39" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V39" s="4">
-        <v>0</v>
+      <c r="S39">
+        <v>15</v>
+      </c>
+      <c r="T39" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="U39" t="s">
+        <v>23</v>
+      </c>
+      <c r="V39">
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -7138,25 +7610,25 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>4004</v>
+        <v>4012</v>
       </c>
       <c r="C40" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="E40" t="s">
-        <v>333</v>
+        <v>172</v>
       </c>
       <c r="F40" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -7165,16 +7637,16 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="N40" t="s">
-        <v>135</v>
+        <v>238</v>
       </c>
       <c r="O40">
         <v>1</v>
@@ -7183,394 +7655,394 @@
         <v>3</v>
       </c>
       <c r="Q40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40">
         <v>100</v>
       </c>
       <c r="S40">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T40" s="8" t="s">
-        <v>264</v>
+        <v>325</v>
       </c>
       <c r="U40" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="V40">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:22" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="4">
+    <row r="41" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B41" s="4">
-        <v>4005</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G41" s="4">
-        <v>12</v>
-      </c>
-      <c r="H41" s="4">
-        <v>5</v>
-      </c>
-      <c r="I41" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J41" s="4">
-        <v>0</v>
-      </c>
-      <c r="K41" s="4">
+      <c r="B41">
+        <v>4012</v>
+      </c>
+      <c r="C41" t="s">
+        <v>306</v>
+      </c>
+      <c r="D41" t="s">
+        <v>177</v>
+      </c>
+      <c r="E41" t="s">
+        <v>176</v>
+      </c>
+      <c r="F41" t="s">
+        <v>318</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="s">
+        <v>94</v>
+      </c>
+      <c r="N41" t="s">
+        <v>238</v>
+      </c>
+      <c r="O41">
+        <v>1</v>
+      </c>
+      <c r="P41">
         <v>3</v>
       </c>
-      <c r="L41" s="4">
-        <v>0</v>
-      </c>
-      <c r="M41" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N41" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O41" s="4">
-        <v>1</v>
-      </c>
-      <c r="P41" s="4">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="4">
-        <v>0</v>
-      </c>
-      <c r="R41" s="4">
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
         <v>100</v>
       </c>
-      <c r="S41" s="4">
-        <v>30</v>
-      </c>
-      <c r="T41" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="U41" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V41" s="4">
-        <v>0</v>
+      <c r="S41">
+        <v>15</v>
+      </c>
+      <c r="T41" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="U41" t="s">
+        <v>23</v>
+      </c>
+      <c r="V41">
+        <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="4">
+    <row r="42" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B42" s="4">
-        <v>4006</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="G42" s="4">
+      <c r="B42">
+        <v>4012</v>
+      </c>
+      <c r="C42" t="s">
+        <v>307</v>
+      </c>
+      <c r="D42" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" t="s">
+        <v>184</v>
+      </c>
+      <c r="F42" t="s">
+        <v>180</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="s">
+        <v>94</v>
+      </c>
+      <c r="N42" t="s">
+        <v>238</v>
+      </c>
+      <c r="O42">
+        <v>1</v>
+      </c>
+      <c r="P42">
         <v>3</v>
       </c>
-      <c r="H42" s="4">
-        <v>5</v>
-      </c>
-      <c r="I42" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J42" s="4">
-        <v>0</v>
-      </c>
-      <c r="K42" s="4">
-        <v>3</v>
-      </c>
-      <c r="L42" s="4">
-        <v>0</v>
-      </c>
-      <c r="M42" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N42" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="O42" s="4">
-        <v>1</v>
-      </c>
-      <c r="P42" s="4">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="4">
-        <v>0</v>
-      </c>
-      <c r="R42" s="4">
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
         <v>100</v>
       </c>
-      <c r="S42" s="4">
-        <v>30</v>
-      </c>
-      <c r="T42" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="U42" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V42" s="4">
-        <v>0</v>
+      <c r="S42">
+        <v>15</v>
+      </c>
+      <c r="T42" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="U42" t="s">
+        <v>23</v>
+      </c>
+      <c r="V42">
+        <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43">
+    <row r="43" spans="1:22" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="4">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43">
-        <v>4007</v>
-      </c>
-      <c r="C43" t="s">
-        <v>309</v>
-      </c>
-      <c r="D43" t="s">
-        <v>85</v>
-      </c>
-      <c r="E43" t="s">
-        <v>87</v>
-      </c>
-      <c r="F43" t="s">
-        <v>240</v>
-      </c>
-      <c r="G43">
+      <c r="B43" s="4">
+        <v>4003</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="4">
         <v>3</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="4">
+        <v>2</v>
+      </c>
+      <c r="I43" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J43" s="4">
+        <v>0</v>
+      </c>
+      <c r="K43" s="4">
         <v>3</v>
       </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <v>1</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43" t="s">
-        <v>94</v>
-      </c>
-      <c r="N43" t="s">
-        <v>238</v>
-      </c>
-      <c r="O43">
-        <v>1</v>
-      </c>
-      <c r="P43">
+      <c r="L43" s="4">
+        <v>0</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O43" s="4">
+        <v>1</v>
+      </c>
+      <c r="P43" s="4">
         <v>3</v>
       </c>
-      <c r="Q43">
-        <v>0</v>
-      </c>
-      <c r="R43">
+      <c r="Q43" s="4">
+        <v>0</v>
+      </c>
+      <c r="R43" s="4">
         <v>100</v>
       </c>
-      <c r="S43">
-        <v>15</v>
-      </c>
-      <c r="T43" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="U43" t="s">
-        <v>154</v>
-      </c>
-      <c r="V43">
-        <v>5</v>
+      <c r="S43" s="4">
+        <v>30</v>
+      </c>
+      <c r="T43" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="U43" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V43" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="4">
+    <row r="44" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B44" s="4">
-        <v>4007</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="G44" s="4">
+      <c r="B44">
+        <v>4004</v>
+      </c>
+      <c r="C44" t="s">
+        <v>289</v>
+      </c>
+      <c r="D44" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" t="s">
+        <v>333</v>
+      </c>
+      <c r="F44" t="s">
+        <v>221</v>
+      </c>
+      <c r="G44">
         <v>3</v>
       </c>
-      <c r="H44" s="4">
+      <c r="H44">
         <v>5</v>
       </c>
-      <c r="I44" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J44" s="4">
-        <v>0</v>
-      </c>
-      <c r="K44" s="4">
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
         <v>3</v>
       </c>
-      <c r="L44" s="4">
-        <v>0</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N44" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="O44" s="4">
-        <v>1</v>
-      </c>
-      <c r="P44" s="4">
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="s">
+        <v>135</v>
+      </c>
+      <c r="N44" t="s">
+        <v>135</v>
+      </c>
+      <c r="O44">
+        <v>1</v>
+      </c>
+      <c r="P44">
         <v>3</v>
       </c>
-      <c r="Q44" s="4">
-        <v>0</v>
-      </c>
-      <c r="R44" s="4">
+      <c r="Q44">
+        <v>1</v>
+      </c>
+      <c r="R44">
         <v>100</v>
       </c>
-      <c r="S44" s="4">
+      <c r="S44">
         <v>30</v>
       </c>
-      <c r="T44" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="U44" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V44" s="4">
-        <v>0</v>
+      <c r="T44" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="U44" t="s">
+        <v>154</v>
+      </c>
+      <c r="V44">
+        <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="4">
+    <row r="45" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="9">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45" s="4">
-        <v>4008</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="G45" s="4">
+      <c r="B45" s="9">
+        <v>4013</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="G45" s="9">
         <v>3</v>
       </c>
-      <c r="H45" s="4">
+      <c r="H45" s="9">
+        <v>3</v>
+      </c>
+      <c r="I45" s="9">
+        <v>0</v>
+      </c>
+      <c r="J45" s="9">
+        <v>0</v>
+      </c>
+      <c r="K45" s="9">
+        <v>1</v>
+      </c>
+      <c r="L45" s="9">
+        <v>0</v>
+      </c>
+      <c r="M45" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N45" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O45" s="9">
+        <v>1</v>
+      </c>
+      <c r="P45" s="9">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="9">
+        <v>1</v>
+      </c>
+      <c r="R45" s="9">
+        <v>100</v>
+      </c>
+      <c r="S45" s="9">
+        <v>30</v>
+      </c>
+      <c r="T45" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="U45" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="V45" s="9">
         <v>5</v>
       </c>
-      <c r="I45" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J45" s="4">
-        <v>0</v>
-      </c>
-      <c r="K45" s="4">
-        <v>3</v>
-      </c>
-      <c r="L45" s="4">
-        <v>0</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="O45" s="4">
-        <v>1</v>
-      </c>
-      <c r="P45" s="4">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="4">
-        <v>0</v>
-      </c>
-      <c r="R45" s="4">
-        <v>100</v>
-      </c>
-      <c r="S45" s="4">
-        <v>30</v>
-      </c>
-      <c r="T45" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="U45" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V45" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="46" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:22" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="4">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B46" s="4">
-        <v>4009</v>
+        <v>4005</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>243</v>
+        <v>29</v>
       </c>
       <c r="G46" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H46" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I46" s="4">
         <v>9999</v>
@@ -7605,8 +8077,8 @@
       <c r="S46" s="4">
         <v>30</v>
       </c>
-      <c r="T46" s="4" t="s">
-        <v>243</v>
+      <c r="T46" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="U46" s="4" t="s">
         <v>94</v>
@@ -7615,31 +8087,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:22" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A47" s="4">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B47" s="4">
-        <v>4013</v>
+        <v>4006</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="G47" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H47" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I47" s="4">
         <v>9999</v>
@@ -7648,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L47" s="4">
         <v>0</v>
@@ -7657,7 +8129,7 @@
         <v>94</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>94</v>
+        <v>238</v>
       </c>
       <c r="O47" s="4">
         <v>1</v>
@@ -7674,8 +8146,8 @@
       <c r="S47" s="4">
         <v>30</v>
       </c>
-      <c r="T47" s="6" t="s">
-        <v>161</v>
+      <c r="T47" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="U47" s="4" t="s">
         <v>94</v>
@@ -7684,445 +8156,445 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="4">
+    <row r="48" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B48" s="4">
-        <v>5004</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="G48" s="4">
-        <v>6</v>
-      </c>
-      <c r="H48" s="4">
-        <v>0</v>
-      </c>
-      <c r="I48" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J48" s="4">
-        <v>0</v>
-      </c>
-      <c r="K48" s="4">
+      <c r="B48">
+        <v>4007</v>
+      </c>
+      <c r="C48" t="s">
+        <v>309</v>
+      </c>
+      <c r="D48" t="s">
+        <v>85</v>
+      </c>
+      <c r="E48" t="s">
+        <v>87</v>
+      </c>
+      <c r="F48" t="s">
+        <v>240</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+      <c r="H48">
+        <v>3</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="s">
+        <v>94</v>
+      </c>
+      <c r="N48" t="s">
+        <v>238</v>
+      </c>
+      <c r="O48">
+        <v>1</v>
+      </c>
+      <c r="P48">
+        <v>3</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>100</v>
+      </c>
+      <c r="S48">
+        <v>15</v>
+      </c>
+      <c r="T48" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="U48" t="s">
+        <v>154</v>
+      </c>
+      <c r="V48">
         <v>5</v>
       </c>
-      <c r="L48" s="4">
-        <v>0</v>
-      </c>
-      <c r="M48" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N48" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O48" s="4">
-        <v>0</v>
-      </c>
-      <c r="P48" s="4">
-        <v>4</v>
-      </c>
-      <c r="Q48" s="4">
-        <v>0</v>
-      </c>
-      <c r="R48" s="4">
-        <v>100</v>
-      </c>
-      <c r="S48" s="4">
-        <v>30</v>
-      </c>
-      <c r="T48" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="U48" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V48" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="49" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49">
+    <row r="49" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="4">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B49">
-        <v>5007</v>
-      </c>
-      <c r="C49" t="s">
-        <v>311</v>
-      </c>
-      <c r="D49" t="s">
-        <v>273</v>
-      </c>
-      <c r="E49" t="s">
-        <v>271</v>
-      </c>
-      <c r="F49" t="s">
-        <v>272</v>
-      </c>
-      <c r="G49">
-        <v>6</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>10</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49" t="s">
-        <v>94</v>
-      </c>
-      <c r="N49" t="s">
-        <v>94</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>4</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
+      <c r="B49" s="4">
+        <v>4007</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G49" s="4">
+        <v>3</v>
+      </c>
+      <c r="H49" s="4">
+        <v>5</v>
+      </c>
+      <c r="I49" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J49" s="4">
+        <v>0</v>
+      </c>
+      <c r="K49" s="4">
+        <v>3</v>
+      </c>
+      <c r="L49" s="4">
+        <v>0</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="O49" s="4">
+        <v>1</v>
+      </c>
+      <c r="P49" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="4">
+        <v>0</v>
+      </c>
+      <c r="R49" s="4">
         <v>100</v>
       </c>
-      <c r="S49">
+      <c r="S49" s="4">
         <v>30</v>
       </c>
-      <c r="T49" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="U49" t="s">
-        <v>94</v>
-      </c>
-      <c r="V49">
+      <c r="T49" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="U49" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V49" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50">
+    <row r="50" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="4">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B50">
-        <v>5001</v>
-      </c>
-      <c r="C50" t="s">
-        <v>297</v>
-      </c>
-      <c r="D50" t="s">
-        <v>39</v>
-      </c>
-      <c r="E50" t="s">
-        <v>38</v>
-      </c>
-      <c r="F50" t="s">
-        <v>330</v>
-      </c>
-      <c r="G50">
-        <v>6</v>
-      </c>
-      <c r="H50">
-        <v>4</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
+      <c r="B50" s="4">
+        <v>4008</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G50" s="4">
         <v>3</v>
       </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50" t="s">
-        <v>135</v>
-      </c>
-      <c r="N50" t="s">
-        <v>135</v>
-      </c>
-      <c r="O50">
-        <v>1</v>
-      </c>
-      <c r="P50">
-        <v>4</v>
-      </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
-      <c r="R50">
+      <c r="H50" s="4">
+        <v>5</v>
+      </c>
+      <c r="I50" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J50" s="4">
+        <v>0</v>
+      </c>
+      <c r="K50" s="4">
+        <v>3</v>
+      </c>
+      <c r="L50" s="4">
+        <v>0</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="O50" s="4">
+        <v>1</v>
+      </c>
+      <c r="P50" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q50" s="4">
+        <v>0</v>
+      </c>
+      <c r="R50" s="4">
         <v>100</v>
       </c>
-      <c r="S50">
-        <v>15</v>
-      </c>
-      <c r="T50" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="U50" t="s">
-        <v>273</v>
-      </c>
-      <c r="V50">
-        <v>3</v>
+      <c r="S50" s="4">
+        <v>30</v>
+      </c>
+      <c r="T50" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="U50" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V50" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51">
+    <row r="51" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="4">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B51">
-        <v>5002</v>
-      </c>
-      <c r="C51" t="s">
-        <v>312</v>
-      </c>
-      <c r="D51" t="s">
-        <v>121</v>
-      </c>
-      <c r="E51" t="s">
-        <v>119</v>
-      </c>
-      <c r="F51" t="s">
-        <v>120</v>
-      </c>
-      <c r="G51">
-        <v>6</v>
-      </c>
-      <c r="H51">
+      <c r="B51" s="4">
+        <v>4009</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="G51" s="4">
         <v>3</v>
       </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
+      <c r="H51" s="4">
+        <v>8</v>
+      </c>
+      <c r="I51" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J51" s="4">
+        <v>0</v>
+      </c>
+      <c r="K51" s="4">
         <v>3</v>
       </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51" t="s">
-        <v>94</v>
-      </c>
-      <c r="N51" t="s">
-        <v>94</v>
-      </c>
-      <c r="O51">
-        <v>1</v>
-      </c>
-      <c r="P51">
-        <v>4</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
+      <c r="L51" s="4">
+        <v>0</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O51" s="4">
+        <v>1</v>
+      </c>
+      <c r="P51" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q51" s="4">
+        <v>0</v>
+      </c>
+      <c r="R51" s="4">
         <v>100</v>
       </c>
-      <c r="S51">
+      <c r="S51" s="4">
         <v>30</v>
       </c>
-      <c r="T51" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="U51" t="s">
-        <v>39</v>
-      </c>
-      <c r="V51">
-        <v>1</v>
+      <c r="T51" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="U51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V51" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52">
+    <row r="52" spans="1:22" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="4">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B52">
-        <v>5003</v>
-      </c>
-      <c r="C52" t="s">
-        <v>315</v>
-      </c>
-      <c r="D52" t="s">
-        <v>139</v>
-      </c>
-      <c r="E52" t="s">
-        <v>188</v>
-      </c>
-      <c r="F52" t="s">
-        <v>138</v>
-      </c>
-      <c r="G52">
+      <c r="B52" s="4">
+        <v>4013</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G52" s="4">
         <v>6</v>
       </c>
-      <c r="H52">
-        <v>6</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
+      <c r="H52" s="4">
+        <v>30</v>
+      </c>
+      <c r="I52" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J52" s="4">
+        <v>0</v>
+      </c>
+      <c r="K52" s="4">
+        <v>5</v>
+      </c>
+      <c r="L52" s="4">
+        <v>0</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O52" s="4">
+        <v>1</v>
+      </c>
+      <c r="P52" s="4">
         <v>3</v>
       </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52" t="s">
-        <v>94</v>
-      </c>
-      <c r="N52" t="s">
-        <v>94</v>
-      </c>
-      <c r="O52">
-        <v>1</v>
-      </c>
-      <c r="P52">
-        <v>4</v>
-      </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
-      <c r="R52">
+      <c r="Q52" s="4">
+        <v>0</v>
+      </c>
+      <c r="R52" s="4">
         <v>100</v>
       </c>
-      <c r="S52">
-        <v>480</v>
-      </c>
-      <c r="T52" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="U52" t="s">
-        <v>39</v>
-      </c>
-      <c r="V52">
-        <v>3</v>
+      <c r="S52" s="4">
+        <v>30</v>
+      </c>
+      <c r="T52" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="U52" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V52" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53">
+    <row r="53" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="4">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53">
-        <v>5005</v>
-      </c>
-      <c r="C53" t="s">
-        <v>313</v>
-      </c>
-      <c r="D53" t="s">
-        <v>200</v>
-      </c>
-      <c r="E53" t="s">
-        <v>199</v>
-      </c>
-      <c r="F53" t="s">
-        <v>198</v>
-      </c>
-      <c r="G53">
+      <c r="B53" s="4">
+        <v>5004</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G53" s="4">
         <v>6</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="4">
+        <v>0</v>
+      </c>
+      <c r="I53" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J53" s="4">
+        <v>0</v>
+      </c>
+      <c r="K53" s="4">
+        <v>5</v>
+      </c>
+      <c r="L53" s="4">
+        <v>0</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O53" s="4">
+        <v>0</v>
+      </c>
+      <c r="P53" s="4">
         <v>4</v>
       </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <v>3</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53" t="s">
-        <v>217</v>
-      </c>
-      <c r="N53" t="s">
-        <v>94</v>
-      </c>
-      <c r="O53">
-        <v>1</v>
-      </c>
-      <c r="P53">
-        <v>4</v>
-      </c>
-      <c r="Q53">
-        <v>0</v>
-      </c>
-      <c r="R53">
+      <c r="Q53" s="4">
+        <v>0</v>
+      </c>
+      <c r="R53" s="4">
         <v>100</v>
       </c>
-      <c r="S53">
+      <c r="S53" s="4">
         <v>30</v>
       </c>
-      <c r="T53" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="U53" t="s">
-        <v>273</v>
-      </c>
-      <c r="V53">
-        <v>3</v>
+      <c r="T53" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="U53" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V53" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B54">
-        <v>5006</v>
+        <v>5007</v>
       </c>
       <c r="C54" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D54" t="s">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c r="E54" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="F54" t="s">
-        <v>329</v>
+        <v>272</v>
       </c>
       <c r="G54">
         <v>6</v>
       </c>
       <c r="H54">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -8131,19 +8603,19 @@
         <v>0</v>
       </c>
       <c r="K54">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L54">
         <v>0</v>
       </c>
       <c r="M54" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="N54" t="s">
-        <v>238</v>
+        <v>94</v>
       </c>
       <c r="O54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P54">
         <v>4</v>
@@ -8158,7 +8630,7 @@
         <v>30</v>
       </c>
       <c r="T54" s="8" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="U54" t="s">
         <v>94</v>
@@ -8167,124 +8639,124 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="4">
+    <row r="55" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="9">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" s="4">
-        <v>6001</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G55" s="4">
+      <c r="B55" s="9">
+        <v>5007</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="G55" s="9">
         <v>6</v>
       </c>
-      <c r="H55" s="4">
-        <v>3</v>
-      </c>
-      <c r="I55" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J55" s="4">
-        <v>0</v>
-      </c>
-      <c r="K55" s="4">
+      <c r="H55" s="9">
+        <v>0</v>
+      </c>
+      <c r="I55" s="9">
+        <v>0</v>
+      </c>
+      <c r="J55" s="9">
+        <v>0</v>
+      </c>
+      <c r="K55" s="9">
         <v>10</v>
       </c>
-      <c r="L55" s="4">
-        <v>0</v>
-      </c>
-      <c r="M55" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N55" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O55" s="4">
-        <v>1</v>
-      </c>
-      <c r="P55" s="4">
-        <v>5</v>
-      </c>
-      <c r="Q55" s="4">
-        <v>0</v>
-      </c>
-      <c r="R55" s="4">
+      <c r="L55" s="9">
+        <v>0</v>
+      </c>
+      <c r="M55" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O55" s="9">
+        <v>0</v>
+      </c>
+      <c r="P55" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q55" s="9">
+        <v>0</v>
+      </c>
+      <c r="R55" s="9">
         <v>100</v>
       </c>
-      <c r="S55" s="4">
+      <c r="S55" s="9">
         <v>30</v>
       </c>
-      <c r="T55" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="U55" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V55" s="4">
+      <c r="T55" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="U55" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V55" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B56">
-        <v>6002</v>
+        <v>5001</v>
       </c>
       <c r="C56" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="D56" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="E56" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="F56" t="s">
-        <v>96</v>
+        <v>330</v>
       </c>
       <c r="G56">
         <v>6</v>
       </c>
       <c r="H56">
+        <v>4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
         <v>3</v>
       </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>5</v>
-      </c>
       <c r="L56">
         <v>0</v>
       </c>
       <c r="M56" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="N56" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="O56">
         <v>1</v>
       </c>
       <c r="P56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -8293,43 +8765,43 @@
         <v>100</v>
       </c>
       <c r="S56">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T56" s="8" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="U56" t="s">
-        <v>94</v>
+        <v>273</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B57">
-        <v>6004</v>
+        <v>5002</v>
       </c>
       <c r="C57" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D57" t="s">
-        <v>261</v>
+        <v>121</v>
       </c>
       <c r="E57" t="s">
-        <v>262</v>
+        <v>119</v>
       </c>
       <c r="F57" t="s">
-        <v>263</v>
+        <v>120</v>
       </c>
       <c r="G57">
         <v>6</v>
       </c>
       <c r="H57">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -8344,19 +8816,19 @@
         <v>0</v>
       </c>
       <c r="M57" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="N57" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="O57">
         <v>1</v>
       </c>
       <c r="P57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57">
         <v>100</v>
@@ -8365,43 +8837,43 @@
         <v>30</v>
       </c>
       <c r="T57" s="8" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="U57" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B58">
-        <v>6005</v>
+        <v>5003</v>
       </c>
       <c r="C58" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="D58" t="s">
-        <v>265</v>
+        <v>139</v>
       </c>
       <c r="E58" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="F58" t="s">
-        <v>267</v>
+        <v>138</v>
       </c>
       <c r="G58">
         <v>6</v>
       </c>
       <c r="H58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -8413,502 +8885,502 @@
         <v>0</v>
       </c>
       <c r="M58" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="N58" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="O58">
         <v>1</v>
       </c>
       <c r="P58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58">
         <v>100</v>
       </c>
       <c r="S58">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="T58" s="8" t="s">
-        <v>268</v>
+        <v>205</v>
       </c>
       <c r="U58" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="4">
+    <row r="59" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B59" s="4">
-        <v>6003</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G59" s="4">
+      <c r="B59">
+        <v>5005</v>
+      </c>
+      <c r="C59" t="s">
+        <v>313</v>
+      </c>
+      <c r="D59" t="s">
+        <v>200</v>
+      </c>
+      <c r="E59" t="s">
+        <v>199</v>
+      </c>
+      <c r="F59" t="s">
+        <v>198</v>
+      </c>
+      <c r="G59">
         <v>6</v>
       </c>
-      <c r="H59" s="4">
+      <c r="H59">
+        <v>4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
         <v>3</v>
       </c>
-      <c r="I59" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J59" s="4">
-        <v>0</v>
-      </c>
-      <c r="K59" s="4">
-        <v>1</v>
-      </c>
-      <c r="L59" s="4">
-        <v>0</v>
-      </c>
-      <c r="M59" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N59" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O59" s="4">
-        <v>1</v>
-      </c>
-      <c r="P59" s="4">
-        <v>5</v>
-      </c>
-      <c r="Q59" s="4">
-        <v>0</v>
-      </c>
-      <c r="R59" s="4">
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" t="s">
+        <v>217</v>
+      </c>
+      <c r="N59" t="s">
+        <v>94</v>
+      </c>
+      <c r="O59">
+        <v>1</v>
+      </c>
+      <c r="P59">
+        <v>4</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
         <v>100</v>
       </c>
-      <c r="S59" s="4">
+      <c r="S59">
         <v>30</v>
       </c>
-      <c r="T59" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="U59" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V59" s="4">
-        <v>0</v>
+      <c r="T59" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="U59" t="s">
+        <v>273</v>
+      </c>
+      <c r="V59">
+        <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="5">
+    <row r="60" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B60" s="5">
-        <v>7001</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G60" s="5">
+      <c r="B60">
+        <v>5006</v>
+      </c>
+      <c r="C60" t="s">
+        <v>314</v>
+      </c>
+      <c r="D60" t="s">
+        <v>214</v>
+      </c>
+      <c r="E60" t="s">
+        <v>213</v>
+      </c>
+      <c r="F60" t="s">
+        <v>329</v>
+      </c>
+      <c r="G60">
         <v>6</v>
       </c>
-      <c r="H60" s="5">
-        <v>12</v>
-      </c>
-      <c r="I60" s="5">
-        <v>0</v>
-      </c>
-      <c r="J60" s="5">
-        <v>0</v>
-      </c>
-      <c r="K60" s="5">
-        <v>1</v>
-      </c>
-      <c r="L60" s="5">
-        <v>0</v>
-      </c>
-      <c r="M60" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N60" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O60" s="5">
-        <v>1</v>
-      </c>
-      <c r="P60" s="5">
-        <v>6</v>
-      </c>
-      <c r="Q60" s="2">
-        <v>0</v>
-      </c>
-      <c r="R60" s="5">
+      <c r="H60">
+        <v>8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" t="s">
+        <v>135</v>
+      </c>
+      <c r="N60" t="s">
+        <v>238</v>
+      </c>
+      <c r="O60">
+        <v>1</v>
+      </c>
+      <c r="P60">
+        <v>4</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
         <v>100</v>
       </c>
-      <c r="S60" s="5">
+      <c r="S60">
         <v>30</v>
       </c>
-      <c r="T60" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="U60" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="V60" s="5">
+      <c r="T60" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="U60" t="s">
+        <v>94</v>
+      </c>
+      <c r="V60">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:22" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="5">
+    <row r="61" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="9">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B61" s="5">
-        <v>7002</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G61" s="5">
-        <v>18</v>
-      </c>
-      <c r="H61" s="5">
-        <v>15</v>
-      </c>
-      <c r="I61" s="5">
-        <v>0</v>
-      </c>
-      <c r="J61" s="5">
-        <v>0</v>
-      </c>
-      <c r="K61" s="5">
-        <v>1</v>
-      </c>
-      <c r="L61" s="5">
-        <v>0</v>
-      </c>
-      <c r="M61" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N61" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O61" s="5">
-        <v>1</v>
-      </c>
-      <c r="P61" s="5">
+      <c r="B61" s="9">
+        <v>5006</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="G61" s="9">
         <v>6</v>
       </c>
-      <c r="Q61" s="2">
-        <v>0</v>
-      </c>
-      <c r="R61" s="5">
+      <c r="H61" s="9">
+        <v>8</v>
+      </c>
+      <c r="I61" s="9">
+        <v>0</v>
+      </c>
+      <c r="J61" s="9">
+        <v>0</v>
+      </c>
+      <c r="K61" s="9">
+        <v>1</v>
+      </c>
+      <c r="L61" s="9">
+        <v>0</v>
+      </c>
+      <c r="M61" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N61" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O61" s="9">
+        <v>1</v>
+      </c>
+      <c r="P61" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q61" s="9">
+        <v>0</v>
+      </c>
+      <c r="R61" s="9">
         <v>100</v>
       </c>
-      <c r="S61" s="5">
+      <c r="S61" s="9">
         <v>30</v>
       </c>
-      <c r="T61" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="U61" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="V61" s="5">
+      <c r="T61" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="U61" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V61" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="5">
+    <row r="62" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="9">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B62" s="5">
-        <v>8001</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G62" s="5">
+      <c r="B62" s="9">
+        <v>5007</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="G62" s="9">
         <v>6</v>
       </c>
-      <c r="H62" s="5">
-        <v>12</v>
-      </c>
-      <c r="I62" s="5">
-        <v>0</v>
-      </c>
-      <c r="J62" s="5">
-        <v>0</v>
-      </c>
-      <c r="K62" s="5">
-        <v>1</v>
-      </c>
-      <c r="L62" s="5">
-        <v>0</v>
-      </c>
-      <c r="M62" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N62" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O62" s="5">
-        <v>1</v>
-      </c>
-      <c r="P62" s="5">
-        <v>7</v>
-      </c>
-      <c r="Q62" s="2">
-        <v>0</v>
-      </c>
-      <c r="R62" s="5">
+      <c r="H62" s="9">
+        <v>8</v>
+      </c>
+      <c r="I62" s="9">
+        <v>0</v>
+      </c>
+      <c r="J62" s="9">
+        <v>0</v>
+      </c>
+      <c r="K62" s="9">
+        <v>1</v>
+      </c>
+      <c r="L62" s="9">
+        <v>0</v>
+      </c>
+      <c r="M62" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="N62" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="O62" s="9">
+        <v>1</v>
+      </c>
+      <c r="P62" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="9">
+        <v>0</v>
+      </c>
+      <c r="R62" s="9">
         <v>100</v>
       </c>
-      <c r="S62" s="5">
+      <c r="S62" s="9">
         <v>30</v>
       </c>
-      <c r="T62" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="U62" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="V62" s="5">
+      <c r="T62" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="U62" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V62" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="5">
+    <row r="63" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="9">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B63" s="5">
-        <v>8002</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G63" s="5">
+      <c r="B63" s="9">
+        <v>5007</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="G63" s="9">
         <v>6</v>
       </c>
-      <c r="H63" s="5">
-        <v>14</v>
-      </c>
-      <c r="I63" s="5">
-        <v>0</v>
-      </c>
-      <c r="J63" s="5">
-        <v>0</v>
-      </c>
-      <c r="K63" s="5">
-        <v>1</v>
-      </c>
-      <c r="L63" s="5">
-        <v>0</v>
-      </c>
-      <c r="M63" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N63" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O63" s="5">
-        <v>1</v>
-      </c>
-      <c r="P63" s="5">
-        <v>7</v>
-      </c>
-      <c r="Q63" s="2">
-        <v>0</v>
-      </c>
-      <c r="R63" s="5">
+      <c r="H63" s="9">
+        <v>8</v>
+      </c>
+      <c r="I63" s="9">
+        <v>0</v>
+      </c>
+      <c r="J63" s="9">
+        <v>0</v>
+      </c>
+      <c r="K63" s="9">
+        <v>3</v>
+      </c>
+      <c r="L63" s="9">
+        <v>0</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O63" s="9">
+        <v>1</v>
+      </c>
+      <c r="P63" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q63" s="9">
+        <v>0</v>
+      </c>
+      <c r="R63" s="9">
         <v>100</v>
       </c>
-      <c r="S63" s="5">
+      <c r="S63" s="9">
         <v>30</v>
       </c>
-      <c r="T63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="U63" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="V63" s="5">
+      <c r="T63" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="U63" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V63" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:22" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="2">
+    <row r="64" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="4">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B64" s="2">
-        <v>9001</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G64" s="2">
-        <v>2</v>
-      </c>
-      <c r="H64" s="2">
-        <v>7</v>
-      </c>
-      <c r="I64" s="2">
-        <v>0</v>
-      </c>
-      <c r="J64" s="2">
-        <v>0</v>
-      </c>
-      <c r="K64" s="2">
+      <c r="B64" s="4">
+        <v>6001</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G64" s="4">
+        <v>6</v>
+      </c>
+      <c r="H64" s="4">
+        <v>3</v>
+      </c>
+      <c r="I64" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J64" s="4">
+        <v>0</v>
+      </c>
+      <c r="K64" s="4">
         <v>10</v>
       </c>
-      <c r="L64" s="2">
-        <v>0</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="O64" s="2">
-        <v>1</v>
-      </c>
-      <c r="P64" s="2">
-        <v>8</v>
-      </c>
-      <c r="Q64" s="2">
-        <v>0</v>
-      </c>
-      <c r="R64" s="2">
+      <c r="L64" s="4">
+        <v>0</v>
+      </c>
+      <c r="M64" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N64" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O64" s="4">
+        <v>1</v>
+      </c>
+      <c r="P64" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q64" s="4">
+        <v>0</v>
+      </c>
+      <c r="R64" s="4">
         <v>100</v>
       </c>
-      <c r="S64" s="2">
-        <v>120</v>
-      </c>
-      <c r="T64" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="U64" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V64" s="2">
+      <c r="S64" s="4">
+        <v>30</v>
+      </c>
+      <c r="T64" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="U64" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V64" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="B65">
-        <v>9005</v>
+        <v>6002</v>
       </c>
       <c r="C65" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D65" t="s">
-        <v>259</v>
+        <v>101</v>
       </c>
       <c r="E65" t="s">
-        <v>278</v>
+        <v>100</v>
       </c>
       <c r="F65" t="s">
-        <v>260</v>
+        <v>96</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H65">
         <v>3</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L65">
         <v>0</v>
       </c>
       <c r="M65" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="N65" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="O65">
         <v>1</v>
       </c>
       <c r="P65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65">
         <v>100</v>
@@ -8917,7 +9389,7 @@
         <v>30</v>
       </c>
       <c r="T65" s="8" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="U65" t="s">
         <v>94</v>
@@ -8926,210 +9398,969 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="4">
+    <row r="66" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B66" s="4">
-        <v>9002</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G66" s="4">
+      <c r="B66">
+        <v>6004</v>
+      </c>
+      <c r="C66" t="s">
+        <v>308</v>
+      </c>
+      <c r="D66" t="s">
+        <v>261</v>
+      </c>
+      <c r="E66" t="s">
+        <v>262</v>
+      </c>
+      <c r="F66" t="s">
+        <v>263</v>
+      </c>
+      <c r="G66">
         <v>6</v>
       </c>
-      <c r="H66" s="4">
+      <c r="H66">
         <v>5</v>
       </c>
-      <c r="I66" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J66" s="4">
-        <v>0</v>
-      </c>
-      <c r="K66" s="4">
-        <v>10</v>
-      </c>
-      <c r="L66" s="4">
-        <v>0</v>
-      </c>
-      <c r="M66" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N66" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O66" s="4">
-        <v>1</v>
-      </c>
-      <c r="P66" s="4">
-        <v>8</v>
-      </c>
-      <c r="Q66" s="4">
-        <v>0</v>
-      </c>
-      <c r="R66" s="4">
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>3</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66" t="s">
+        <v>135</v>
+      </c>
+      <c r="N66" t="s">
+        <v>135</v>
+      </c>
+      <c r="O66">
+        <v>1</v>
+      </c>
+      <c r="P66">
+        <v>5</v>
+      </c>
+      <c r="Q66">
+        <v>1</v>
+      </c>
+      <c r="R66">
         <v>100</v>
       </c>
-      <c r="S66" s="4">
+      <c r="S66">
         <v>30</v>
       </c>
-      <c r="T66" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="U66" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V66" s="4">
+      <c r="T66" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="U66" t="s">
+        <v>94</v>
+      </c>
+      <c r="V66">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:22" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="4">
+    <row r="67" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B67" s="4">
-        <v>9004</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G67" s="4">
-        <v>2</v>
-      </c>
-      <c r="H67" s="4">
-        <v>10</v>
-      </c>
-      <c r="I67" s="4">
-        <v>0</v>
-      </c>
-      <c r="J67" s="4">
-        <v>0</v>
-      </c>
-      <c r="K67" s="4">
-        <v>1</v>
-      </c>
-      <c r="L67" s="4">
-        <v>0</v>
-      </c>
-      <c r="M67" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="N67" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O67" s="4">
-        <v>1</v>
-      </c>
-      <c r="P67" s="4">
-        <v>8</v>
-      </c>
-      <c r="Q67" s="4">
-        <v>0</v>
-      </c>
-      <c r="R67" s="4">
+      <c r="B67">
+        <v>6005</v>
+      </c>
+      <c r="C67" t="s">
+        <v>279</v>
+      </c>
+      <c r="D67" t="s">
+        <v>265</v>
+      </c>
+      <c r="E67" t="s">
+        <v>266</v>
+      </c>
+      <c r="F67" t="s">
+        <v>267</v>
+      </c>
+      <c r="G67">
+        <v>6</v>
+      </c>
+      <c r="H67">
+        <v>5</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>3</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="s">
+        <v>135</v>
+      </c>
+      <c r="N67" t="s">
+        <v>135</v>
+      </c>
+      <c r="O67">
+        <v>1</v>
+      </c>
+      <c r="P67">
+        <v>5</v>
+      </c>
+      <c r="Q67">
+        <v>1</v>
+      </c>
+      <c r="R67">
         <v>100</v>
       </c>
-      <c r="S67" s="4">
-        <v>60</v>
-      </c>
-      <c r="T67" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="U67" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V67" s="4">
+      <c r="S67">
+        <v>30</v>
+      </c>
+      <c r="T67" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="U67" t="s">
+        <v>94</v>
+      </c>
+      <c r="V67">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68">
+    <row r="68" spans="1:22" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="9">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="9">
+        <v>6006</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="G68" s="9">
+        <v>6</v>
+      </c>
+      <c r="H68" s="9">
+        <v>12</v>
+      </c>
+      <c r="I68" s="9">
+        <v>1</v>
+      </c>
+      <c r="J68" s="9">
+        <v>0</v>
+      </c>
+      <c r="K68" s="9">
+        <v>3</v>
+      </c>
+      <c r="L68" s="9">
+        <v>0</v>
+      </c>
+      <c r="M68" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N68" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="O68" s="9">
+        <v>1</v>
+      </c>
+      <c r="P68" s="9">
+        <v>5</v>
+      </c>
+      <c r="Q68" s="9">
+        <v>1</v>
+      </c>
+      <c r="R68" s="9">
+        <v>100</v>
+      </c>
+      <c r="S68" s="9">
+        <v>30</v>
+      </c>
+      <c r="T68" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="U68" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V68" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="9">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="B69" s="9">
+        <v>6007</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="G69" s="9">
+        <v>6</v>
+      </c>
+      <c r="H69" s="9">
+        <v>5</v>
+      </c>
+      <c r="I69" s="9">
+        <v>1</v>
+      </c>
+      <c r="J69" s="9">
+        <v>0</v>
+      </c>
+      <c r="K69" s="9">
+        <v>3</v>
+      </c>
+      <c r="L69" s="9">
+        <v>0</v>
+      </c>
+      <c r="M69" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="N69" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="O69" s="9">
+        <v>1</v>
+      </c>
+      <c r="P69" s="9">
+        <v>5</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>1</v>
+      </c>
+      <c r="R69" s="9">
+        <v>50</v>
+      </c>
+      <c r="S69" s="9">
+        <v>30</v>
+      </c>
+      <c r="T69" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="U69" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="V69" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="4">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="B70" s="4">
+        <v>6003</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G70" s="4">
+        <v>6</v>
+      </c>
+      <c r="H70" s="4">
+        <v>3</v>
+      </c>
+      <c r="I70" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J70" s="4">
+        <v>0</v>
+      </c>
+      <c r="K70" s="4">
+        <v>1</v>
+      </c>
+      <c r="L70" s="4">
+        <v>0</v>
+      </c>
+      <c r="M70" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N70" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O70" s="4">
+        <v>1</v>
+      </c>
+      <c r="P70" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q70" s="4">
+        <v>0</v>
+      </c>
+      <c r="R70" s="4">
+        <v>100</v>
+      </c>
+      <c r="S70" s="4">
+        <v>30</v>
+      </c>
+      <c r="T70" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="U70" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V70" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="5">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="B71" s="5">
+        <v>7001</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G71" s="5">
+        <v>6</v>
+      </c>
+      <c r="H71" s="5">
+        <v>12</v>
+      </c>
+      <c r="I71" s="5">
+        <v>0</v>
+      </c>
+      <c r="J71" s="5">
+        <v>0</v>
+      </c>
+      <c r="K71" s="5">
+        <v>1</v>
+      </c>
+      <c r="L71" s="5">
+        <v>0</v>
+      </c>
+      <c r="M71" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N71" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O71" s="5">
+        <v>1</v>
+      </c>
+      <c r="P71" s="5">
+        <v>6</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>0</v>
+      </c>
+      <c r="R71" s="5">
+        <v>100</v>
+      </c>
+      <c r="S71" s="5">
+        <v>30</v>
+      </c>
+      <c r="T71" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="U71" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="V71" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="5">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="B72" s="5">
+        <v>7002</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G72" s="5">
+        <v>18</v>
+      </c>
+      <c r="H72" s="5">
+        <v>15</v>
+      </c>
+      <c r="I72" s="5">
+        <v>0</v>
+      </c>
+      <c r="J72" s="5">
+        <v>0</v>
+      </c>
+      <c r="K72" s="5">
+        <v>1</v>
+      </c>
+      <c r="L72" s="5">
+        <v>0</v>
+      </c>
+      <c r="M72" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N72" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O72" s="5">
+        <v>1</v>
+      </c>
+      <c r="P72" s="5">
+        <v>6</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>0</v>
+      </c>
+      <c r="R72" s="5">
+        <v>100</v>
+      </c>
+      <c r="S72" s="5">
+        <v>30</v>
+      </c>
+      <c r="T72" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="U72" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="V72" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="5">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+      <c r="B73" s="5">
+        <v>8001</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G73" s="5">
+        <v>6</v>
+      </c>
+      <c r="H73" s="5">
+        <v>12</v>
+      </c>
+      <c r="I73" s="5">
+        <v>0</v>
+      </c>
+      <c r="J73" s="5">
+        <v>0</v>
+      </c>
+      <c r="K73" s="5">
+        <v>1</v>
+      </c>
+      <c r="L73" s="5">
+        <v>0</v>
+      </c>
+      <c r="M73" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N73" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O73" s="5">
+        <v>1</v>
+      </c>
+      <c r="P73" s="5">
+        <v>7</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>0</v>
+      </c>
+      <c r="R73" s="5">
+        <v>100</v>
+      </c>
+      <c r="S73" s="5">
+        <v>30</v>
+      </c>
+      <c r="T73" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="U73" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="V73" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="5">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="B74" s="5">
+        <v>8002</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G74" s="5">
+        <v>6</v>
+      </c>
+      <c r="H74" s="5">
+        <v>14</v>
+      </c>
+      <c r="I74" s="5">
+        <v>0</v>
+      </c>
+      <c r="J74" s="5">
+        <v>0</v>
+      </c>
+      <c r="K74" s="5">
+        <v>1</v>
+      </c>
+      <c r="L74" s="5">
+        <v>0</v>
+      </c>
+      <c r="M74" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="N74" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O74" s="5">
+        <v>1</v>
+      </c>
+      <c r="P74" s="5">
+        <v>7</v>
+      </c>
+      <c r="Q74" s="2">
+        <v>0</v>
+      </c>
+      <c r="R74" s="5">
+        <v>100</v>
+      </c>
+      <c r="S74" s="5">
+        <v>30</v>
+      </c>
+      <c r="T74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="U74" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="V74" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="2">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="B75" s="2">
+        <v>9001</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G75" s="2">
+        <v>2</v>
+      </c>
+      <c r="H75" s="2">
+        <v>7</v>
+      </c>
+      <c r="I75" s="2">
+        <v>0</v>
+      </c>
+      <c r="J75" s="2">
+        <v>0</v>
+      </c>
+      <c r="K75" s="2">
+        <v>10</v>
+      </c>
+      <c r="L75" s="2">
+        <v>0</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="O75" s="2">
+        <v>1</v>
+      </c>
+      <c r="P75" s="2">
+        <v>8</v>
+      </c>
+      <c r="Q75" s="2">
+        <v>0</v>
+      </c>
+      <c r="R75" s="2">
+        <v>100</v>
+      </c>
+      <c r="S75" s="2">
+        <v>120</v>
+      </c>
+      <c r="T75" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="U75" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="V75" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A76">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="B76">
+        <v>9005</v>
+      </c>
+      <c r="C76" t="s">
+        <v>281</v>
+      </c>
+      <c r="D76" t="s">
+        <v>259</v>
+      </c>
+      <c r="E76" t="s">
+        <v>278</v>
+      </c>
+      <c r="F76" t="s">
+        <v>260</v>
+      </c>
+      <c r="G76">
+        <v>2</v>
+      </c>
+      <c r="H76">
+        <v>3</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>3</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76" t="s">
+        <v>135</v>
+      </c>
+      <c r="N76" t="s">
+        <v>135</v>
+      </c>
+      <c r="O76">
+        <v>1</v>
+      </c>
+      <c r="P76">
+        <v>8</v>
+      </c>
+      <c r="Q76">
+        <v>1</v>
+      </c>
+      <c r="R76">
+        <v>100</v>
+      </c>
+      <c r="S76">
+        <v>30</v>
+      </c>
+      <c r="T76" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="U76" t="s">
+        <v>94</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="4">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="B77" s="4">
+        <v>9002</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G77" s="4">
+        <v>6</v>
+      </c>
+      <c r="H77" s="4">
+        <v>5</v>
+      </c>
+      <c r="I77" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J77" s="4">
+        <v>0</v>
+      </c>
+      <c r="K77" s="4">
+        <v>10</v>
+      </c>
+      <c r="L77" s="4">
+        <v>0</v>
+      </c>
+      <c r="M77" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O77" s="4">
+        <v>1</v>
+      </c>
+      <c r="P77" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q77" s="4">
+        <v>0</v>
+      </c>
+      <c r="R77" s="4">
+        <v>100</v>
+      </c>
+      <c r="S77" s="4">
+        <v>30</v>
+      </c>
+      <c r="T77" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="U77" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V77" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="4">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="B78" s="4">
+        <v>9004</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G78" s="4">
+        <v>2</v>
+      </c>
+      <c r="H78" s="4">
+        <v>10</v>
+      </c>
+      <c r="I78" s="4">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4">
+        <v>0</v>
+      </c>
+      <c r="K78" s="4">
+        <v>1</v>
+      </c>
+      <c r="L78" s="4">
+        <v>0</v>
+      </c>
+      <c r="M78" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O78" s="4">
+        <v>1</v>
+      </c>
+      <c r="P78" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q78" s="4">
+        <v>0</v>
+      </c>
+      <c r="R78" s="4">
+        <v>100</v>
+      </c>
+      <c r="S78" s="4">
+        <v>60</v>
+      </c>
+      <c r="T78" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="U78" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="V78" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="B79">
         <v>9003</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C79" t="s">
         <v>280</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D79" t="s">
         <v>108</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E79" t="s">
         <v>107</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F79" t="s">
         <v>91</v>
       </c>
-      <c r="G68">
+      <c r="G79">
         <v>6</v>
       </c>
-      <c r="H68">
-        <v>1</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>1</v>
-      </c>
-      <c r="K68">
-        <v>1</v>
-      </c>
-      <c r="L68">
-        <v>1</v>
-      </c>
-      <c r="M68" t="s">
-        <v>94</v>
-      </c>
-      <c r="N68" t="s">
-        <v>94</v>
-      </c>
-      <c r="O68">
-        <v>1</v>
-      </c>
-      <c r="P68">
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79" t="s">
+        <v>94</v>
+      </c>
+      <c r="N79" t="s">
+        <v>94</v>
+      </c>
+      <c r="O79">
+        <v>1</v>
+      </c>
+      <c r="P79">
         <v>8</v>
       </c>
-      <c r="Q68">
-        <v>0</v>
-      </c>
-      <c r="R68">
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
         <v>100</v>
       </c>
-      <c r="S68">
+      <c r="S79">
         <v>30</v>
       </c>
-      <c r="T68" s="8" t="s">
+      <c r="T79" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="U68" t="s">
-        <v>94</v>
-      </c>
-      <c r="V68">
+      <c r="U79" t="s">
+        <v>94</v>
+      </c>
+      <c r="V79">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7945D96E-F236-4C6E-9EDC-192AC34390C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1075B5E3-0872-4590-9052-1A47EFB6725B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="975" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2085" yWindow="795" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="380">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -4017,36 +4017,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ラトリア状態になる。
-ラトリア状態の間は、一定時間、お菓子を作る際の油っこさや水っぽさを減らす。
-※すでに作ったあとのお菓子には効果がない。</t>
-    <rPh sb="16" eb="18">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>コウカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>エピクレイシス</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -4073,23 +4043,6 @@
     </rPh>
     <rPh sb="16" eb="17">
       <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>次に作るお菓子の成功率を一時的に上げる「エピクレイシス状態」になる。
-エピクレイシス状態は、数回で消える。</t>
-    <rPh sb="27" eb="29">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>スウカイ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>キ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4165,10 +4118,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Tree_Stars</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>スリースターズ状態になる。一定の間、消費MPがすべて１になる。</t>
     <rPh sb="7" eb="9">
       <t>ジョウタイ</t>
@@ -4181,38 +4130,6 @@
     </rPh>
     <rPh sb="18" eb="20">
       <t>ショウヒ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>スリースターズ状態になる。一定の間、消費MPがすべて１になる。
-お菓子を何度か作ると、スリースターズ状態は解除される。</t>
-    <rPh sb="7" eb="9">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>イッテイ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ショウヒ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ナンド</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>カイジョ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4317,23 +4234,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>パーフェクト・プリンセス</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Parfect_Princess</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>甘さ・酸味・苦味がパーフェクトに近いとき、さらに点数を上げる</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>甘さ・酸味・苦味がパーフェクトに近いとき、さらに点数を上げる。
-習得するだけでOK。</t>
-    <rPh sb="32" eb="34">
-      <t>シュウトク</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -4462,6 +4367,156 @@
     <rPh sb="61" eb="62">
       <t>カオ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>甘さ・酸味・苦味がパーフェクトに近いとき、さらに点数を上げる。
+習得するだけでOK。
+LV1: 1.2倍
+LV2: 1.5倍
+LV3: 1.8倍
+LV4: 2.1倍
+LV5: 2.4倍</t>
+    <rPh sb="32" eb="34">
+      <t>シュウトク</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>PlayerBuf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Three_Stars</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>status_time</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ラトリア状態になる。
+ラトリア状態の間は、一定時間、お菓子を作る際の油っこさや水っぽさを減らす。
+LVを上げると、効果時間がのびる。
+LV1ごとに2時間のびる。
+※すでに作ったあとのお菓子には効果がない。</t>
+    <rPh sb="16" eb="18">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>次に作るお菓子の成功率を一時的に上げる「エピクレイシス状態」になる。
+しばらくの間、エピクレイシス状態は続く。
+また、一回お菓子・仕上げ・魔法を使用すると消える。
+LVを上げると、効果時間がのびる。
+LV1ごとに2時間のびる。</t>
+    <rPh sb="27" eb="29">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>イッカイ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スリースターズ状態になる。一定の間、消費MPを減少させる。
+一定時間経つと、スリースターズ状態は解除される。
+LVを上げると、効果時間がのびる。
+LV1ごとに1時間のびる。
+LV1: 消費MP1/2
+LV2: 消費MP1/3</t>
+    <rPh sb="7" eb="9">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イッテイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>カイジョ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="64" eb="68">
+      <t>コウカジカン</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>ショウヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>パーフェクト・プリン・プリンセス</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4498,7 +4553,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4535,6 +4590,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -4550,7 +4617,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4580,6 +4647,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4896,7 +4975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:V79"/>
+  <dimension ref="A1:W79"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -4908,13 +4987,13 @@
     <col min="9" max="15" width="6.75" customWidth="1"/>
     <col min="16" max="17" width="9" customWidth="1"/>
     <col min="18" max="18" width="10.375" customWidth="1"/>
-    <col min="19" max="19" width="7.875" customWidth="1"/>
-    <col min="20" max="20" width="25.125" customWidth="1"/>
-    <col min="21" max="21" width="11.625" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
+    <col min="19" max="20" width="7.875" customWidth="1"/>
+    <col min="21" max="21" width="25.125" customWidth="1"/>
+    <col min="22" max="22" width="11.875" customWidth="1"/>
+    <col min="23" max="23" width="6.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -4973,16 +5052,19 @@
         <v>92</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:23" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
         <f t="shared" ref="A2:A79" si="0">ROW()-2</f>
         <v>0</v>
@@ -5041,17 +5123,20 @@
       <c r="S2" s="4">
         <v>30</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="4">
+        <v>0</v>
+      </c>
+      <c r="U2" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="U2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V2" s="4">
+      <c r="V2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W2" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -5110,17 +5195,20 @@
       <c r="S3">
         <v>30</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="U3" t="s">
-        <v>94</v>
-      </c>
-      <c r="V3">
+      <c r="V3" t="s">
+        <v>94</v>
+      </c>
+      <c r="W3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:23" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -5179,17 +5267,20 @@
       <c r="S4" s="4">
         <v>30</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="T4" s="4">
+        <v>0</v>
+      </c>
+      <c r="U4" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="U4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V4" s="4">
+      <c r="V4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W4" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -5248,17 +5339,20 @@
       <c r="S5">
         <v>30</v>
       </c>
-      <c r="T5" s="8" t="s">
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="U5" t="s">
-        <v>94</v>
-      </c>
-      <c r="V5">
+      <c r="V5" t="s">
+        <v>94</v>
+      </c>
+      <c r="W5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -5317,86 +5411,92 @@
       <c r="S6">
         <v>30</v>
       </c>
-      <c r="T6" s="8" t="s">
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="U6" t="s">
+      <c r="V6" t="s">
         <v>54</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="9">
+    <row r="7" spans="1:23" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="11">
         <v>1012</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="G7" s="9">
+      <c r="D7" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="G7" s="11">
         <v>6</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="11">
         <v>5</v>
       </c>
-      <c r="I7" s="9">
-        <v>1</v>
-      </c>
-      <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
+      <c r="I7" s="11">
+        <v>1</v>
+      </c>
+      <c r="J7" s="11">
+        <v>0</v>
+      </c>
+      <c r="K7" s="11">
         <v>3</v>
       </c>
-      <c r="L7" s="9">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9" t="s">
+      <c r="L7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="N7" s="9" t="s">
+      <c r="N7" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="O7" s="9">
-        <v>1</v>
-      </c>
-      <c r="P7" s="9">
+      <c r="O7" s="11">
+        <v>1</v>
+      </c>
+      <c r="P7" s="11">
         <v>9</v>
       </c>
-      <c r="Q7" s="9">
-        <v>0</v>
-      </c>
-      <c r="R7" s="9">
-        <v>100</v>
-      </c>
-      <c r="S7" s="9">
+      <c r="Q7" s="11">
+        <v>0</v>
+      </c>
+      <c r="R7" s="11">
+        <v>70</v>
+      </c>
+      <c r="S7" s="11">
         <v>30</v>
       </c>
-      <c r="T7" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="U7" s="9" t="s">
+      <c r="T7" s="11">
+        <v>0</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="V7" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="V7" s="9">
-        <v>3</v>
+      <c r="W7" s="11">
+        <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -5455,17 +5555,20 @@
       <c r="S8">
         <v>30</v>
       </c>
-      <c r="T8" s="8" t="s">
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="U8" t="s">
+      <c r="V8" t="s">
         <v>54</v>
       </c>
-      <c r="V8">
+      <c r="W8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -5524,17 +5627,20 @@
       <c r="S9">
         <v>30</v>
       </c>
-      <c r="T9" s="8" t="s">
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="U9" t="s">
+      <c r="V9" t="s">
         <v>163</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -5593,17 +5699,20 @@
       <c r="S10">
         <v>30</v>
       </c>
-      <c r="T10" s="8" t="s">
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="U10" t="s">
+      <c r="V10" t="s">
         <v>80</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -5662,17 +5771,20 @@
       <c r="S11">
         <v>30</v>
       </c>
-      <c r="T11" s="8" t="s">
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="U11" t="s">
+      <c r="V11" t="s">
         <v>54</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:23" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -5684,13 +5796,13 @@
         <v>298</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G12" s="9">
         <v>6</v>
@@ -5699,7 +5811,7 @@
         <v>5</v>
       </c>
       <c r="I12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
@@ -5731,17 +5843,20 @@
       <c r="S12" s="9">
         <v>30</v>
       </c>
-      <c r="T12" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="U12" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="V12" s="9">
-        <v>5</v>
+      <c r="T12" s="9">
+        <v>0</v>
+      </c>
+      <c r="U12" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="V12" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="W12" s="9">
+        <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:23" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -5800,17 +5915,20 @@
       <c r="S13">
         <v>30</v>
       </c>
-      <c r="T13" s="8" t="s">
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="U13" t="s">
-        <v>94</v>
-      </c>
-      <c r="V13">
+      <c r="V13" t="s">
+        <v>94</v>
+      </c>
+      <c r="W13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:23" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -5869,17 +5987,20 @@
       <c r="S14" s="4">
         <v>30</v>
       </c>
-      <c r="T14" s="4" t="s">
+      <c r="T14" s="4">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="U14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V14" s="4">
+      <c r="V14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W14" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:23" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -5938,17 +6059,20 @@
       <c r="S15" s="4">
         <v>30</v>
       </c>
-      <c r="T15" s="4" t="s">
+      <c r="T15" s="4">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="U15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V15" s="4">
+      <c r="V15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W15" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -6007,17 +6131,20 @@
       <c r="S16">
         <v>30</v>
       </c>
-      <c r="T16" s="8" t="s">
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="U16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V16">
+      <c r="V16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -6076,17 +6203,20 @@
       <c r="S17">
         <v>120</v>
       </c>
-      <c r="T17" s="8" t="s">
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="U17" t="s">
-        <v>94</v>
-      </c>
-      <c r="V17">
+      <c r="V17" t="s">
+        <v>94</v>
+      </c>
+      <c r="W17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -6145,17 +6275,20 @@
       <c r="S18">
         <v>120</v>
       </c>
-      <c r="T18" s="8" t="s">
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="U18" t="s">
+      <c r="V18" t="s">
         <v>51</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:22" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:23" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -6214,17 +6347,20 @@
       <c r="S19" s="4">
         <v>120</v>
       </c>
-      <c r="T19" s="4" t="s">
+      <c r="T19" s="4">
+        <v>0</v>
+      </c>
+      <c r="U19" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="U19" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V19" s="4">
+      <c r="V19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W19" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -6283,17 +6419,20 @@
       <c r="S20">
         <v>30</v>
       </c>
-      <c r="T20" s="8" t="s">
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="U20" t="s">
+      <c r="V20" t="s">
         <v>51</v>
       </c>
-      <c r="V20">
+      <c r="W20">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -6352,17 +6491,20 @@
       <c r="S21">
         <v>30</v>
       </c>
-      <c r="T21" s="8" t="s">
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="U21" t="s">
+      <c r="V21" t="s">
         <v>101</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:22" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:23" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -6421,17 +6563,20 @@
       <c r="S22" s="4">
         <v>30</v>
       </c>
-      <c r="T22" s="4" t="s">
+      <c r="T22" s="4">
+        <v>0</v>
+      </c>
+      <c r="U22" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="U22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V22" s="4">
+      <c r="V22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W22" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -6490,17 +6635,20 @@
       <c r="S23">
         <v>30</v>
       </c>
-      <c r="T23" s="8" t="s">
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="U23" t="s">
-        <v>94</v>
-      </c>
-      <c r="V23">
+      <c r="V23" t="s">
+        <v>94</v>
+      </c>
+      <c r="W23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -6559,17 +6707,20 @@
       <c r="S24">
         <v>30</v>
       </c>
-      <c r="T24" s="8" t="s">
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="U24" t="s">
-        <v>94</v>
-      </c>
-      <c r="V24">
+      <c r="V24" t="s">
+        <v>94</v>
+      </c>
+      <c r="W24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -6628,17 +6779,20 @@
       <c r="S25">
         <v>30</v>
       </c>
-      <c r="T25" s="8" t="s">
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="U25" t="s">
+      <c r="V25" t="s">
         <v>16</v>
       </c>
-      <c r="V25">
+      <c r="W25">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -6697,17 +6851,20 @@
       <c r="S26">
         <v>30</v>
       </c>
-      <c r="T26" s="8" t="s">
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="U26" t="s">
+      <c r="V26" t="s">
         <v>20</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -6766,155 +6923,164 @@
       <c r="S27">
         <v>30</v>
       </c>
-      <c r="T27" s="8" t="s">
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="U27" t="s">
-        <v>94</v>
-      </c>
-      <c r="V27">
+      <c r="V27" t="s">
+        <v>94</v>
+      </c>
+      <c r="W27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="9">
+    <row r="28" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="13">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="13">
         <v>3009</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="13">
         <v>4</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="13">
         <v>5</v>
       </c>
-      <c r="I28" s="9">
-        <v>0</v>
-      </c>
-      <c r="J28" s="9">
-        <v>0</v>
-      </c>
-      <c r="K28" s="9">
+      <c r="I28" s="13">
+        <v>0</v>
+      </c>
+      <c r="J28" s="13">
+        <v>0</v>
+      </c>
+      <c r="K28" s="13">
         <v>3</v>
       </c>
-      <c r="L28" s="9">
-        <v>0</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N28" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="O28" s="9">
-        <v>1</v>
-      </c>
-      <c r="P28" s="9">
+      <c r="L28" s="13">
+        <v>0</v>
+      </c>
+      <c r="M28" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="N28" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="O28" s="13">
+        <v>1</v>
+      </c>
+      <c r="P28" s="13">
         <v>2</v>
       </c>
-      <c r="Q28" s="9">
-        <v>1</v>
-      </c>
-      <c r="R28" s="9">
+      <c r="Q28" s="13">
+        <v>1</v>
+      </c>
+      <c r="R28" s="13">
         <v>100</v>
       </c>
-      <c r="S28" s="9">
+      <c r="S28" s="13">
         <v>30</v>
       </c>
-      <c r="T28" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="U28" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V28" s="9">
+      <c r="T28" s="13">
+        <v>120</v>
+      </c>
+      <c r="U28" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="V28" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="W28" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="9">
+    <row r="29" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="13">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="13">
         <v>3010</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="G29" s="9">
+      <c r="D29" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="G29" s="13">
         <v>4</v>
       </c>
-      <c r="H29" s="9">
-        <v>0</v>
-      </c>
-      <c r="I29" s="9">
-        <v>0</v>
-      </c>
-      <c r="J29" s="9">
-        <v>0</v>
-      </c>
-      <c r="K29" s="9">
-        <v>3</v>
-      </c>
-      <c r="L29" s="9">
-        <v>0</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="O29" s="9">
-        <v>0</v>
-      </c>
-      <c r="P29" s="9">
+      <c r="H29" s="13">
+        <v>0</v>
+      </c>
+      <c r="I29" s="13">
+        <v>0</v>
+      </c>
+      <c r="J29" s="13">
+        <v>0</v>
+      </c>
+      <c r="K29" s="13">
+        <v>5</v>
+      </c>
+      <c r="L29" s="13">
+        <v>0</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="N29" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="O29" s="13">
+        <v>0</v>
+      </c>
+      <c r="P29" s="13">
         <v>2</v>
       </c>
-      <c r="Q29" s="9">
-        <v>1</v>
-      </c>
-      <c r="R29" s="9">
+      <c r="Q29" s="13">
+        <v>1</v>
+      </c>
+      <c r="R29" s="13">
         <v>100</v>
       </c>
-      <c r="S29" s="9">
+      <c r="S29" s="13">
         <v>30</v>
       </c>
-      <c r="T29" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="U29" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V29" s="9">
+      <c r="T29" s="13">
+        <v>0</v>
+      </c>
+      <c r="U29" s="14" t="s">
+        <v>372</v>
+      </c>
+      <c r="V29" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="W29" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -6947,7 +7113,7 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -6973,17 +7139,20 @@
       <c r="S30">
         <v>30</v>
       </c>
-      <c r="T30" s="8" t="s">
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="U30" t="s">
-        <v>94</v>
-      </c>
-      <c r="V30">
+      <c r="V30" t="s">
+        <v>94</v>
+      </c>
+      <c r="W30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -7042,17 +7211,20 @@
       <c r="S31">
         <v>30</v>
       </c>
-      <c r="T31" s="8" t="s">
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="U31" t="s">
-        <v>94</v>
-      </c>
-      <c r="V31">
+      <c r="V31" t="s">
+        <v>94</v>
+      </c>
+      <c r="W31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:23" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="4">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -7111,17 +7283,20 @@
       <c r="S32" s="4">
         <v>30</v>
       </c>
-      <c r="T32" s="6" t="s">
+      <c r="T32" s="4">
+        <v>0</v>
+      </c>
+      <c r="U32" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="U32" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V32" s="4">
+      <c r="V32" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W32" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:23" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="4">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -7180,17 +7355,20 @@
       <c r="S33" s="4">
         <v>30</v>
       </c>
-      <c r="T33" s="6" t="s">
+      <c r="T33" s="4">
+        <v>0</v>
+      </c>
+      <c r="U33" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="U33" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V33" s="4">
+      <c r="V33" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W33" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -7249,17 +7427,20 @@
       <c r="S34">
         <v>30</v>
       </c>
-      <c r="T34" s="8" t="s">
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="U34" t="s">
-        <v>94</v>
-      </c>
-      <c r="V34">
+      <c r="V34" t="s">
+        <v>94</v>
+      </c>
+      <c r="W34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -7318,17 +7499,20 @@
       <c r="S35">
         <v>30</v>
       </c>
-      <c r="T35" s="8" t="s">
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="U35" t="s">
-        <v>94</v>
-      </c>
-      <c r="V35">
+      <c r="V35" t="s">
+        <v>94</v>
+      </c>
+      <c r="W35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -7382,22 +7566,25 @@
         <v>0</v>
       </c>
       <c r="R36">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="S36">
         <v>10</v>
       </c>
-      <c r="T36" s="8" t="s">
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="U36" t="s">
+      <c r="V36" t="s">
         <v>154</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -7456,17 +7643,20 @@
       <c r="S37">
         <v>15</v>
       </c>
-      <c r="T37" s="8" t="s">
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="U37" t="s">
+      <c r="V37" t="s">
         <v>23</v>
       </c>
-      <c r="V37">
+      <c r="W37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -7525,17 +7715,20 @@
       <c r="S38">
         <v>15</v>
       </c>
-      <c r="T38" s="8" t="s">
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="U38" t="s">
+      <c r="V38" t="s">
         <v>23</v>
       </c>
-      <c r="V38">
+      <c r="W38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -7594,17 +7787,20 @@
       <c r="S39">
         <v>15</v>
       </c>
-      <c r="T39" s="8" t="s">
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="U39" t="s">
+      <c r="V39" t="s">
         <v>23</v>
       </c>
-      <c r="V39">
+      <c r="W39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -7663,17 +7859,20 @@
       <c r="S40">
         <v>15</v>
       </c>
-      <c r="T40" s="8" t="s">
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="U40" t="s">
+      <c r="V40" t="s">
         <v>23</v>
       </c>
-      <c r="V40">
+      <c r="W40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -7732,17 +7931,20 @@
       <c r="S41">
         <v>15</v>
       </c>
-      <c r="T41" s="8" t="s">
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="U41" t="s">
+      <c r="V41" t="s">
         <v>23</v>
       </c>
-      <c r="V41">
+      <c r="W41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -7801,17 +8003,20 @@
       <c r="S42">
         <v>15</v>
       </c>
-      <c r="T42" s="8" t="s">
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="U42" t="s">
+      <c r="V42" t="s">
         <v>23</v>
       </c>
-      <c r="V42">
+      <c r="W42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:22" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:23" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="4">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -7870,17 +8075,20 @@
       <c r="S43" s="4">
         <v>30</v>
       </c>
-      <c r="T43" s="6" t="s">
+      <c r="T43" s="4">
+        <v>0</v>
+      </c>
+      <c r="U43" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="U43" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V43" s="4">
+      <c r="V43" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W43" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -7939,17 +8147,20 @@
       <c r="S44">
         <v>30</v>
       </c>
-      <c r="T44" s="8" t="s">
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="U44" t="s">
+      <c r="V44" t="s">
         <v>154</v>
       </c>
-      <c r="V44">
+      <c r="W44">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:23" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="9">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -7961,13 +8172,13 @@
         <v>289</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="G45" s="9">
         <v>3</v>
@@ -8008,17 +8219,20 @@
       <c r="S45" s="9">
         <v>30</v>
       </c>
-      <c r="T45" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="U45" s="9" t="s">
+      <c r="T45" s="9">
+        <v>0</v>
+      </c>
+      <c r="U45" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="V45" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="V45" s="9">
+      <c r="W45" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:22" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:23" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="4">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -8077,17 +8291,20 @@
       <c r="S46" s="4">
         <v>30</v>
       </c>
-      <c r="T46" s="6" t="s">
+      <c r="T46" s="4">
+        <v>0</v>
+      </c>
+      <c r="U46" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="U46" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V46" s="4">
+      <c r="V46" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W46" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A47" s="4">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -8146,17 +8363,20 @@
       <c r="S47" s="4">
         <v>30</v>
       </c>
-      <c r="T47" s="4" t="s">
+      <c r="T47" s="4">
+        <v>0</v>
+      </c>
+      <c r="U47" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="U47" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V47" s="4">
+      <c r="V47" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W47" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -8215,17 +8435,20 @@
       <c r="S48">
         <v>15</v>
       </c>
-      <c r="T48" s="8" t="s">
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="U48" t="s">
+      <c r="V48" t="s">
         <v>154</v>
       </c>
-      <c r="V48">
+      <c r="W48">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A49" s="4">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -8284,17 +8507,20 @@
       <c r="S49" s="4">
         <v>30</v>
       </c>
-      <c r="T49" s="4" t="s">
+      <c r="T49" s="4">
+        <v>0</v>
+      </c>
+      <c r="U49" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="U49" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V49" s="4">
+      <c r="V49" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W49" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A50" s="4">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -8353,17 +8579,20 @@
       <c r="S50" s="4">
         <v>30</v>
       </c>
-      <c r="T50" s="4" t="s">
+      <c r="T50" s="4">
+        <v>0</v>
+      </c>
+      <c r="U50" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="U50" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V50" s="4">
+      <c r="V50" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W50" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A51" s="4">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -8422,17 +8651,20 @@
       <c r="S51" s="4">
         <v>30</v>
       </c>
-      <c r="T51" s="4" t="s">
+      <c r="T51" s="4">
+        <v>0</v>
+      </c>
+      <c r="U51" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="U51" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V51" s="4">
+      <c r="V51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W51" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:22" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:23" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="4">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -8491,17 +8723,20 @@
       <c r="S52" s="4">
         <v>30</v>
       </c>
-      <c r="T52" s="6" t="s">
+      <c r="T52" s="4">
+        <v>0</v>
+      </c>
+      <c r="U52" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="U52" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V52" s="4">
+      <c r="V52" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W52" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:23" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="4">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -8560,17 +8795,20 @@
       <c r="S53" s="4">
         <v>30</v>
       </c>
-      <c r="T53" s="6" t="s">
+      <c r="T53" s="4">
+        <v>0</v>
+      </c>
+      <c r="U53" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="U53" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V53" s="4">
+      <c r="V53" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W53" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -8629,86 +8867,92 @@
       <c r="S54">
         <v>30</v>
       </c>
-      <c r="T54" s="8" t="s">
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="U54" t="s">
-        <v>94</v>
-      </c>
-      <c r="V54">
+      <c r="V54" t="s">
+        <v>94</v>
+      </c>
+      <c r="W54">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:22" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="9">
+    <row r="55" spans="1:23" s="11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="11">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="11">
         <v>5007</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="D55" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="G55" s="9">
+      <c r="D55" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="G55" s="11">
         <v>6</v>
       </c>
-      <c r="H55" s="9">
-        <v>0</v>
-      </c>
-      <c r="I55" s="9">
-        <v>0</v>
-      </c>
-      <c r="J55" s="9">
-        <v>0</v>
-      </c>
-      <c r="K55" s="9">
+      <c r="H55" s="11">
+        <v>0</v>
+      </c>
+      <c r="I55" s="11">
+        <v>0</v>
+      </c>
+      <c r="J55" s="11">
+        <v>0</v>
+      </c>
+      <c r="K55" s="11">
         <v>10</v>
       </c>
-      <c r="L55" s="9">
-        <v>0</v>
-      </c>
-      <c r="M55" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N55" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="O55" s="9">
-        <v>0</v>
-      </c>
-      <c r="P55" s="9">
+      <c r="L55" s="11">
+        <v>0</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="N55" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="O55" s="11">
+        <v>0</v>
+      </c>
+      <c r="P55" s="11">
         <v>4</v>
       </c>
-      <c r="Q55" s="9">
-        <v>0</v>
-      </c>
-      <c r="R55" s="9">
+      <c r="Q55" s="11">
+        <v>0</v>
+      </c>
+      <c r="R55" s="11">
         <v>100</v>
       </c>
-      <c r="S55" s="9">
+      <c r="S55" s="11">
         <v>30</v>
       </c>
-      <c r="T55" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="U55" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V55" s="9">
+      <c r="T55" s="11">
+        <v>0</v>
+      </c>
+      <c r="U55" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="V55" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="W55" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -8767,17 +9011,20 @@
       <c r="S56">
         <v>15</v>
       </c>
-      <c r="T56" s="8" t="s">
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="U56" t="s">
+      <c r="V56" t="s">
         <v>273</v>
       </c>
-      <c r="V56">
+      <c r="W56">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -8836,17 +9083,20 @@
       <c r="S57">
         <v>30</v>
       </c>
-      <c r="T57" s="8" t="s">
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="U57" t="s">
-        <v>39</v>
-      </c>
-      <c r="V57">
-        <v>1</v>
+      <c r="V57" t="s">
+        <v>369</v>
+      </c>
+      <c r="W57">
+        <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -8905,17 +9155,20 @@
       <c r="S58">
         <v>480</v>
       </c>
-      <c r="T58" s="8" t="s">
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="U58" t="s">
+      <c r="V58" t="s">
         <v>39</v>
       </c>
-      <c r="V58">
+      <c r="W58">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -8974,86 +9227,92 @@
       <c r="S59">
         <v>30</v>
       </c>
-      <c r="T59" s="8" t="s">
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="U59" t="s">
-        <v>273</v>
-      </c>
-      <c r="V59">
-        <v>3</v>
+      <c r="V59" t="s">
+        <v>39</v>
+      </c>
+      <c r="W59">
+        <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60">
+    <row r="60" spans="1:23" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="9">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="9">
         <v>5006</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="9">
         <v>6</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="9">
         <v>8</v>
       </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60">
-        <v>1</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60" t="s">
+      <c r="I60" s="9">
+        <v>0</v>
+      </c>
+      <c r="J60" s="9">
+        <v>0</v>
+      </c>
+      <c r="K60" s="9">
+        <v>1</v>
+      </c>
+      <c r="L60" s="9">
+        <v>0</v>
+      </c>
+      <c r="M60" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="N60" t="s">
+      <c r="N60" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="O60">
-        <v>1</v>
-      </c>
-      <c r="P60">
+      <c r="O60" s="9">
+        <v>1</v>
+      </c>
+      <c r="P60" s="9">
         <v>4</v>
       </c>
-      <c r="Q60">
-        <v>0</v>
-      </c>
-      <c r="R60">
+      <c r="Q60" s="9">
+        <v>0</v>
+      </c>
+      <c r="R60" s="9">
         <v>100</v>
       </c>
-      <c r="S60">
+      <c r="S60" s="9">
         <v>30</v>
       </c>
-      <c r="T60" s="8" t="s">
+      <c r="T60" s="9">
+        <v>0</v>
+      </c>
+      <c r="U60" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="U60" t="s">
-        <v>94</v>
-      </c>
-      <c r="V60">
+      <c r="V60" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="W60" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:23" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="9">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -9065,13 +9324,13 @@
         <v>314</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="G61" s="9">
         <v>6</v>
@@ -9112,17 +9371,20 @@
       <c r="S61" s="9">
         <v>30</v>
       </c>
-      <c r="T61" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="U61" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V61" s="9">
-        <v>0</v>
+      <c r="T61" s="9">
+        <v>0</v>
+      </c>
+      <c r="U61" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="V61" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="W61" s="9">
+        <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:23" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="9">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -9134,13 +9396,13 @@
         <v>314</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G62" s="9">
         <v>6</v>
@@ -9181,86 +9443,92 @@
       <c r="S62" s="9">
         <v>30</v>
       </c>
-      <c r="T62" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="U62" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V62" s="9">
-        <v>0</v>
+      <c r="T62" s="9">
+        <v>0</v>
+      </c>
+      <c r="U62" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="V62" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="W62" s="9">
+        <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:22" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="9">
+    <row r="63" spans="1:23" s="13" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="13">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B63" s="9">
+      <c r="B63" s="13">
         <v>5007</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C63" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="D63" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="G63" s="9">
+      <c r="D63" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="F63" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="G63" s="13">
         <v>6</v>
       </c>
-      <c r="H63" s="9">
-        <v>8</v>
-      </c>
-      <c r="I63" s="9">
-        <v>0</v>
-      </c>
-      <c r="J63" s="9">
-        <v>0</v>
-      </c>
-      <c r="K63" s="9">
-        <v>3</v>
-      </c>
-      <c r="L63" s="9">
-        <v>0</v>
-      </c>
-      <c r="M63" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N63" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="O63" s="9">
-        <v>1</v>
-      </c>
-      <c r="P63" s="9">
+      <c r="H63" s="13">
+        <v>25</v>
+      </c>
+      <c r="I63" s="13">
+        <v>0</v>
+      </c>
+      <c r="J63" s="13">
+        <v>0</v>
+      </c>
+      <c r="K63" s="13">
+        <v>2</v>
+      </c>
+      <c r="L63" s="13">
+        <v>0</v>
+      </c>
+      <c r="M63" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="N63" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="O63" s="13">
+        <v>1</v>
+      </c>
+      <c r="P63" s="13">
         <v>4</v>
       </c>
-      <c r="Q63" s="9">
-        <v>0</v>
-      </c>
-      <c r="R63" s="9">
+      <c r="Q63" s="13">
+        <v>0</v>
+      </c>
+      <c r="R63" s="13">
         <v>100</v>
       </c>
-      <c r="S63" s="9">
+      <c r="S63" s="13">
         <v>30</v>
       </c>
-      <c r="T63" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="U63" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V63" s="9">
+      <c r="T63" s="13">
+        <v>60</v>
+      </c>
+      <c r="U63" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="V63" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="W63" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A64" s="4">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -9319,17 +9587,20 @@
       <c r="S64" s="4">
         <v>30</v>
       </c>
-      <c r="T64" s="4" t="s">
+      <c r="T64" s="4">
+        <v>0</v>
+      </c>
+      <c r="U64" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="U64" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V64" s="4">
+      <c r="V64" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W64" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -9388,17 +9659,20 @@
       <c r="S65">
         <v>30</v>
       </c>
-      <c r="T65" s="8" t="s">
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="U65" t="s">
-        <v>94</v>
-      </c>
-      <c r="V65">
+      <c r="V65" t="s">
+        <v>94</v>
+      </c>
+      <c r="W65">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -9457,17 +9731,20 @@
       <c r="S66">
         <v>30</v>
       </c>
-      <c r="T66" s="8" t="s">
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="U66" t="s">
-        <v>94</v>
-      </c>
-      <c r="V66">
+      <c r="V66" t="s">
+        <v>94</v>
+      </c>
+      <c r="W66">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -9526,155 +9803,164 @@
       <c r="S67">
         <v>30</v>
       </c>
-      <c r="T67" s="8" t="s">
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="U67" t="s">
-        <v>94</v>
-      </c>
-      <c r="V67">
+      <c r="V67" t="s">
+        <v>94</v>
+      </c>
+      <c r="W67">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:22" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="9">
+    <row r="68" spans="1:23" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="13">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="13">
         <v>6006</v>
       </c>
-      <c r="C68" s="9" t="s">
+      <c r="C68" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="D68" s="9" t="s">
+      <c r="D68" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="F68" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="E68" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="G68" s="9">
+      <c r="G68" s="13">
         <v>6</v>
       </c>
-      <c r="H68" s="9">
-        <v>12</v>
-      </c>
-      <c r="I68" s="9">
-        <v>1</v>
-      </c>
-      <c r="J68" s="9">
-        <v>0</v>
-      </c>
-      <c r="K68" s="9">
+      <c r="H68" s="13">
+        <v>18</v>
+      </c>
+      <c r="I68" s="13">
+        <v>0</v>
+      </c>
+      <c r="J68" s="13">
+        <v>0</v>
+      </c>
+      <c r="K68" s="13">
         <v>3</v>
       </c>
-      <c r="L68" s="9">
-        <v>0</v>
-      </c>
-      <c r="M68" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N68" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="O68" s="9">
-        <v>1</v>
-      </c>
-      <c r="P68" s="9">
+      <c r="L68" s="13">
+        <v>0</v>
+      </c>
+      <c r="M68" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="N68" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="O68" s="13">
+        <v>1</v>
+      </c>
+      <c r="P68" s="13">
         <v>5</v>
       </c>
-      <c r="Q68" s="9">
-        <v>1</v>
-      </c>
-      <c r="R68" s="9">
+      <c r="Q68" s="13">
+        <v>1</v>
+      </c>
+      <c r="R68" s="13">
         <v>100</v>
       </c>
-      <c r="S68" s="9">
+      <c r="S68" s="13">
         <v>30</v>
       </c>
-      <c r="T68" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="U68" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V68" s="9">
-        <v>0</v>
+      <c r="T68" s="13">
+        <v>120</v>
+      </c>
+      <c r="U68" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="V68" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="W68" s="13">
+        <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:22" s="9" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="9">
+    <row r="69" spans="1:23" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="4">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="B69" s="9">
+      <c r="B69" s="4">
         <v>6007</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="C69" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="D69" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="G69" s="9">
+      <c r="D69" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="G69" s="4">
         <v>6</v>
       </c>
-      <c r="H69" s="9">
+      <c r="H69" s="4">
         <v>5</v>
       </c>
-      <c r="I69" s="9">
-        <v>1</v>
-      </c>
-      <c r="J69" s="9">
-        <v>0</v>
-      </c>
-      <c r="K69" s="9">
+      <c r="I69" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J69" s="4">
+        <v>0</v>
+      </c>
+      <c r="K69" s="4">
         <v>3</v>
       </c>
-      <c r="L69" s="9">
-        <v>0</v>
-      </c>
-      <c r="M69" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N69" s="9" t="s">
+      <c r="L69" s="4">
+        <v>0</v>
+      </c>
+      <c r="M69" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N69" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="O69" s="9">
-        <v>1</v>
-      </c>
-      <c r="P69" s="9">
+      <c r="O69" s="4">
+        <v>1</v>
+      </c>
+      <c r="P69" s="4">
         <v>5</v>
       </c>
-      <c r="Q69" s="9">
-        <v>1</v>
-      </c>
-      <c r="R69" s="9">
+      <c r="Q69" s="4">
+        <v>1</v>
+      </c>
+      <c r="R69" s="4">
         <v>50</v>
       </c>
-      <c r="S69" s="9">
+      <c r="S69" s="4">
         <v>30</v>
       </c>
-      <c r="T69" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="U69" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="V69" s="9">
+      <c r="T69" s="4">
+        <v>0</v>
+      </c>
+      <c r="U69" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="V69" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W69" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A70" s="4">
         <f t="shared" si="0"/>
         <v>68</v>
@@ -9733,17 +10019,20 @@
       <c r="S70" s="4">
         <v>30</v>
       </c>
-      <c r="T70" s="4" t="s">
+      <c r="T70" s="4">
+        <v>0</v>
+      </c>
+      <c r="U70" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="U70" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V70" s="4">
+      <c r="V70" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W70" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A71" s="5">
         <f t="shared" si="0"/>
         <v>69</v>
@@ -9802,17 +10091,20 @@
       <c r="S71" s="5">
         <v>30</v>
       </c>
-      <c r="T71" s="5" t="s">
+      <c r="T71" s="5">
+        <v>0</v>
+      </c>
+      <c r="U71" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="U71" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="V71" s="5">
+      <c r="V71" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="W71" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:22" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:23" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="5">
         <f t="shared" si="0"/>
         <v>70</v>
@@ -9871,155 +10163,164 @@
       <c r="S72" s="5">
         <v>30</v>
       </c>
-      <c r="T72" s="7" t="s">
+      <c r="T72" s="5">
+        <v>0</v>
+      </c>
+      <c r="U72" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="U72" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="V72" s="5">
+      <c r="V72" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="W72" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="5">
+    <row r="73" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="4">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="B73" s="5">
+      <c r="B73" s="4">
         <v>8001</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C73" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="D73" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="E73" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="F73" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G73" s="5">
+      <c r="G73" s="4">
         <v>6</v>
       </c>
-      <c r="H73" s="5">
+      <c r="H73" s="4">
         <v>12</v>
       </c>
-      <c r="I73" s="5">
-        <v>0</v>
-      </c>
-      <c r="J73" s="5">
-        <v>0</v>
-      </c>
-      <c r="K73" s="5">
-        <v>1</v>
-      </c>
-      <c r="L73" s="5">
-        <v>0</v>
-      </c>
-      <c r="M73" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N73" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O73" s="5">
-        <v>1</v>
-      </c>
-      <c r="P73" s="5">
+      <c r="I73" s="4">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4">
+        <v>0</v>
+      </c>
+      <c r="K73" s="4">
+        <v>1</v>
+      </c>
+      <c r="L73" s="4">
+        <v>0</v>
+      </c>
+      <c r="M73" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N73" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O73" s="4">
+        <v>1</v>
+      </c>
+      <c r="P73" s="4">
         <v>7</v>
       </c>
-      <c r="Q73" s="2">
-        <v>0</v>
-      </c>
-      <c r="R73" s="5">
+      <c r="Q73" s="4">
+        <v>0</v>
+      </c>
+      <c r="R73" s="4">
         <v>100</v>
       </c>
-      <c r="S73" s="5">
+      <c r="S73" s="4">
         <v>30</v>
       </c>
-      <c r="T73" s="5" t="s">
+      <c r="T73" s="4">
+        <v>0</v>
+      </c>
+      <c r="U73" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="U73" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="V73" s="5">
+      <c r="V73" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W73" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:22" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="5">
+    <row r="74" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="4">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="B74" s="5">
+      <c r="B74" s="4">
         <v>8002</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="D74" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="F74" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G74" s="5">
+      <c r="G74" s="4">
         <v>6</v>
       </c>
-      <c r="H74" s="5">
+      <c r="H74" s="4">
         <v>14</v>
       </c>
-      <c r="I74" s="5">
-        <v>0</v>
-      </c>
-      <c r="J74" s="5">
-        <v>0</v>
-      </c>
-      <c r="K74" s="5">
-        <v>1</v>
-      </c>
-      <c r="L74" s="5">
-        <v>0</v>
-      </c>
-      <c r="M74" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N74" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O74" s="5">
-        <v>1</v>
-      </c>
-      <c r="P74" s="5">
+      <c r="I74" s="4">
+        <v>0</v>
+      </c>
+      <c r="J74" s="4">
+        <v>0</v>
+      </c>
+      <c r="K74" s="4">
+        <v>1</v>
+      </c>
+      <c r="L74" s="4">
+        <v>0</v>
+      </c>
+      <c r="M74" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N74" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O74" s="4">
+        <v>1</v>
+      </c>
+      <c r="P74" s="4">
         <v>7</v>
       </c>
-      <c r="Q74" s="2">
-        <v>0</v>
-      </c>
-      <c r="R74" s="5">
+      <c r="Q74" s="4">
+        <v>0</v>
+      </c>
+      <c r="R74" s="4">
         <v>100</v>
       </c>
-      <c r="S74" s="5">
+      <c r="S74" s="4">
         <v>30</v>
       </c>
-      <c r="T74" s="5" t="s">
+      <c r="T74" s="4">
+        <v>0</v>
+      </c>
+      <c r="U74" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="U74" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="V74" s="5">
+      <c r="V74" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W74" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:22" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:23" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="2">
         <f t="shared" si="0"/>
         <v>73</v>
@@ -10078,17 +10379,20 @@
       <c r="S75" s="2">
         <v>120</v>
       </c>
-      <c r="T75" s="3" t="s">
+      <c r="T75" s="2">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="U75" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="V75" s="2">
+      <c r="V75" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="W75" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76">
         <f t="shared" si="0"/>
         <v>74</v>
@@ -10147,17 +10451,20 @@
       <c r="S76">
         <v>30</v>
       </c>
-      <c r="T76" s="8" t="s">
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="U76" t="s">
-        <v>94</v>
-      </c>
-      <c r="V76">
+      <c r="V76" t="s">
+        <v>94</v>
+      </c>
+      <c r="W76">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:22" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:23" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="4">
         <f t="shared" si="0"/>
         <v>75</v>
@@ -10216,17 +10523,20 @@
       <c r="S77" s="4">
         <v>30</v>
       </c>
-      <c r="T77" s="6" t="s">
+      <c r="T77" s="4">
+        <v>0</v>
+      </c>
+      <c r="U77" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="U77" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V77" s="4">
+      <c r="V77" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W77" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:22" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:23" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="4">
         <f t="shared" si="0"/>
         <v>76</v>
@@ -10285,17 +10595,20 @@
       <c r="S78" s="4">
         <v>60</v>
       </c>
-      <c r="T78" s="6" t="s">
+      <c r="T78" s="4">
+        <v>0</v>
+      </c>
+      <c r="U78" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="U78" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="V78" s="4">
+      <c r="V78" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W78" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79">
         <f t="shared" si="0"/>
         <v>77</v>
@@ -10354,13 +10667,16 @@
       <c r="S79">
         <v>30</v>
       </c>
-      <c r="T79" s="8" t="s">
+      <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="U79" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="U79" t="s">
-        <v>94</v>
-      </c>
-      <c r="V79">
+      <c r="V79" t="s">
+        <v>94</v>
+      </c>
+      <c r="W79">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1075B5E3-0872-4590-9052-1A47EFB6725B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84071726-8544-41A7-83E8-8DDEACAAA614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="795" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="389">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -4118,22 +4118,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>スリースターズ状態になる。一定の間、消費MPがすべて１になる。</t>
-    <rPh sb="7" eb="9">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>イッテイ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>アイダ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ショウヒ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ナイト・バロン</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -4516,7 +4500,62 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>パーフェクト・プリン・プリンセス</t>
+    <t>skicon_Fire_Ark</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_NightBarron</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Latria</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Crescent_Moon</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Tea_Study</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Three_Stars</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>パーフェクト・プリンセス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Parfect_Princess</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Epiclesis</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Beautiful_Power</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スリースターズ状態になる。一定の間、消費MPを減らす。</t>
+    <rPh sb="7" eb="9">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イッテイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヘ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4553,7 +4592,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4590,18 +4629,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -4617,7 +4644,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4647,18 +4674,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5052,7 +5067,7 @@
         <v>92</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>53</v>
@@ -5424,75 +5439,75 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="11">
+    <row r="7" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7">
         <v>1012</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="E7" s="11" t="s">
+      <c r="C7" t="s">
+        <v>378</v>
+      </c>
+      <c r="D7" t="s">
+        <v>359</v>
+      </c>
+      <c r="E7" t="s">
+        <v>356</v>
+      </c>
+      <c r="F7" t="s">
         <v>357</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>247</v>
+      </c>
+      <c r="N7" t="s">
+        <v>238</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>9</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>70</v>
+      </c>
+      <c r="S7">
+        <v>30</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="G7" s="11">
-        <v>6</v>
-      </c>
-      <c r="H7" s="11">
-        <v>5</v>
-      </c>
-      <c r="I7" s="11">
-        <v>1</v>
-      </c>
-      <c r="J7" s="11">
-        <v>0</v>
-      </c>
-      <c r="K7" s="11">
-        <v>3</v>
-      </c>
-      <c r="L7" s="11">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="O7" s="11">
-        <v>1</v>
-      </c>
-      <c r="P7" s="11">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="11">
-        <v>0</v>
-      </c>
-      <c r="R7" s="11">
-        <v>70</v>
-      </c>
-      <c r="S7" s="11">
-        <v>30</v>
-      </c>
-      <c r="T7" s="11">
-        <v>0</v>
-      </c>
-      <c r="U7" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="V7" s="11" t="s">
+      <c r="V7" t="s">
         <v>54</v>
       </c>
-      <c r="W7" s="11">
+      <c r="W7">
         <v>5</v>
       </c>
     </row>
@@ -5784,75 +5799,75 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="9">
+    <row r="12" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12">
         <v>1011</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="C12" t="s">
+        <v>379</v>
+      </c>
+      <c r="D12" t="s">
+        <v>348</v>
+      </c>
+      <c r="E12" t="s">
+        <v>346</v>
+      </c>
+      <c r="F12" t="s">
+        <v>347</v>
+      </c>
+      <c r="G12">
+        <v>6</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>3</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>135</v>
+      </c>
+      <c r="N12" t="s">
+        <v>135</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>9</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>30</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="G12" s="9">
-        <v>6</v>
-      </c>
-      <c r="H12" s="9">
-        <v>5</v>
-      </c>
-      <c r="I12" s="9">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9">
-        <v>3</v>
-      </c>
-      <c r="L12" s="9">
-        <v>0</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="O12" s="9">
-        <v>1</v>
-      </c>
-      <c r="P12" s="9">
-        <v>9</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>1</v>
-      </c>
-      <c r="R12" s="9">
-        <v>100</v>
-      </c>
-      <c r="S12" s="9">
-        <v>30</v>
-      </c>
-      <c r="T12" s="9">
-        <v>0</v>
-      </c>
-      <c r="U12" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="V12" s="9" t="s">
+      <c r="V12" t="s">
         <v>163</v>
       </c>
-      <c r="W12" s="9">
+      <c r="W12">
         <v>3</v>
       </c>
     </row>
@@ -6585,7 +6600,7 @@
         <v>3006</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>387</v>
       </c>
       <c r="D23" t="s">
         <v>157</v>
@@ -6936,147 +6951,147 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="13">
+    <row r="28" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28">
         <v>3009</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="D28" s="13" t="s">
+      <c r="C28" t="s">
+        <v>380</v>
+      </c>
+      <c r="D28" t="s">
         <v>336</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" t="s">
         <v>335</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" t="s">
         <v>337</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28">
         <v>4</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28">
         <v>5</v>
       </c>
-      <c r="I28" s="13">
-        <v>0</v>
-      </c>
-      <c r="J28" s="13">
-        <v>0</v>
-      </c>
-      <c r="K28" s="13">
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
         <v>3</v>
       </c>
-      <c r="L28" s="13">
-        <v>0</v>
-      </c>
-      <c r="M28" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="N28" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="O28" s="13">
-        <v>1</v>
-      </c>
-      <c r="P28" s="13">
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="s">
+        <v>372</v>
+      </c>
+      <c r="N28" t="s">
+        <v>94</v>
+      </c>
+      <c r="O28">
+        <v>1</v>
+      </c>
+      <c r="P28">
         <v>2</v>
       </c>
-      <c r="Q28" s="13">
-        <v>1</v>
-      </c>
-      <c r="R28" s="13">
+      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="R28">
         <v>100</v>
       </c>
-      <c r="S28" s="13">
+      <c r="S28">
         <v>30</v>
       </c>
-      <c r="T28" s="13">
+      <c r="T28">
         <v>120</v>
       </c>
-      <c r="U28" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="V28" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="W28" s="13">
+      <c r="U28" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="V28" t="s">
+        <v>94</v>
+      </c>
+      <c r="W28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:23" s="13" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="13">
+    <row r="29" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29">
         <v>3010</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="D29" s="13" t="s">
+      <c r="C29" t="s">
+        <v>385</v>
+      </c>
+      <c r="D29" t="s">
+        <v>354</v>
+      </c>
+      <c r="E29" t="s">
+        <v>384</v>
+      </c>
+      <c r="F29" t="s">
         <v>355</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="G29" s="13">
+      <c r="G29">
         <v>4</v>
       </c>
-      <c r="H29" s="13">
-        <v>0</v>
-      </c>
-      <c r="I29" s="13">
-        <v>0</v>
-      </c>
-      <c r="J29" s="13">
-        <v>0</v>
-      </c>
-      <c r="K29" s="13">
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
         <v>5</v>
       </c>
-      <c r="L29" s="13">
-        <v>0</v>
-      </c>
-      <c r="M29" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="N29" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="O29" s="13">
-        <v>0</v>
-      </c>
-      <c r="P29" s="13">
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="s">
+        <v>94</v>
+      </c>
+      <c r="N29" t="s">
+        <v>94</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
         <v>2</v>
       </c>
-      <c r="Q29" s="13">
-        <v>1</v>
-      </c>
-      <c r="R29" s="13">
+      <c r="Q29">
+        <v>1</v>
+      </c>
+      <c r="R29">
         <v>100</v>
       </c>
-      <c r="S29" s="13">
+      <c r="S29">
         <v>30</v>
       </c>
-      <c r="T29" s="13">
-        <v>0</v>
-      </c>
-      <c r="U29" s="14" t="s">
-        <v>372</v>
-      </c>
-      <c r="V29" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="W29" s="13">
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="V29" t="s">
+        <v>94</v>
+      </c>
+      <c r="W29">
         <v>0</v>
       </c>
     </row>
@@ -8172,13 +8187,13 @@
         <v>289</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E45" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="F45" s="9" t="s">
         <v>361</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>362</v>
       </c>
       <c r="G45" s="9">
         <v>3</v>
@@ -8223,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="V45" s="9" t="s">
         <v>154</v>
@@ -8880,75 +8895,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:23" s="11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="11">
+    <row r="55" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" s="11">
+      <c r="B55">
         <v>5007</v>
       </c>
-      <c r="C55" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="D55" s="11" t="s">
+      <c r="C55" t="s">
+        <v>382</v>
+      </c>
+      <c r="D55" t="s">
+        <v>368</v>
+      </c>
+      <c r="E55" t="s">
+        <v>367</v>
+      </c>
+      <c r="F55" t="s">
         <v>369</v>
       </c>
-      <c r="E55" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="F55" s="11" t="s">
+      <c r="G55">
+        <v>6</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>10</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55" t="s">
+        <v>94</v>
+      </c>
+      <c r="N55" t="s">
+        <v>94</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>4</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>100</v>
+      </c>
+      <c r="S55">
+        <v>30</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="G55" s="11">
-        <v>6</v>
-      </c>
-      <c r="H55" s="11">
-        <v>0</v>
-      </c>
-      <c r="I55" s="11">
-        <v>0</v>
-      </c>
-      <c r="J55" s="11">
-        <v>0</v>
-      </c>
-      <c r="K55" s="11">
-        <v>10</v>
-      </c>
-      <c r="L55" s="11">
-        <v>0</v>
-      </c>
-      <c r="M55" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="N55" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="O55" s="11">
-        <v>0</v>
-      </c>
-      <c r="P55" s="11">
-        <v>4</v>
-      </c>
-      <c r="Q55" s="11">
-        <v>0</v>
-      </c>
-      <c r="R55" s="11">
-        <v>100</v>
-      </c>
-      <c r="S55" s="11">
-        <v>30</v>
-      </c>
-      <c r="T55" s="11">
-        <v>0</v>
-      </c>
-      <c r="U55" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="V55" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="W55" s="11">
+      <c r="V55" t="s">
+        <v>94</v>
+      </c>
+      <c r="W55">
         <v>0</v>
       </c>
     </row>
@@ -9090,7 +9105,7 @@
         <v>236</v>
       </c>
       <c r="V57" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="W57">
         <v>3</v>
@@ -9240,75 +9255,75 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:23" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="9">
+    <row r="60" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60">
         <v>5006</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" t="s">
         <v>314</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D60" t="s">
         <v>214</v>
       </c>
-      <c r="E60" s="9" t="s">
+      <c r="E60" t="s">
         <v>213</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="F60" t="s">
         <v>329</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G60">
         <v>6</v>
       </c>
-      <c r="H60" s="9">
+      <c r="H60">
         <v>8</v>
       </c>
-      <c r="I60" s="9">
-        <v>0</v>
-      </c>
-      <c r="J60" s="9">
-        <v>0</v>
-      </c>
-      <c r="K60" s="9">
-        <v>1</v>
-      </c>
-      <c r="L60" s="9">
-        <v>0</v>
-      </c>
-      <c r="M60" s="9" t="s">
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" t="s">
         <v>135</v>
       </c>
-      <c r="N60" s="9" t="s">
+      <c r="N60" t="s">
         <v>238</v>
       </c>
-      <c r="O60" s="9">
-        <v>1</v>
-      </c>
-      <c r="P60" s="9">
+      <c r="O60">
+        <v>1</v>
+      </c>
+      <c r="P60">
         <v>4</v>
       </c>
-      <c r="Q60" s="9">
-        <v>0</v>
-      </c>
-      <c r="R60" s="9">
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
         <v>100</v>
       </c>
-      <c r="S60" s="9">
+      <c r="S60">
         <v>30</v>
       </c>
-      <c r="T60" s="9">
-        <v>0</v>
-      </c>
-      <c r="U60" s="10" t="s">
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="V60" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="W60" s="9">
+      <c r="V60" t="s">
+        <v>94</v>
+      </c>
+      <c r="W60">
         <v>0</v>
       </c>
     </row>
@@ -9324,13 +9339,13 @@
         <v>314</v>
       </c>
       <c r="D61" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="F61" s="9" t="s">
         <v>365</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>366</v>
       </c>
       <c r="G61" s="9">
         <v>6</v>
@@ -9375,7 +9390,7 @@
         <v>0</v>
       </c>
       <c r="U61" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="V61" s="9" t="s">
         <v>39</v>
@@ -9384,147 +9399,147 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:23" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="9">
+    <row r="62" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62">
         <v>5007</v>
       </c>
-      <c r="C62" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="D62" s="9" t="s">
+      <c r="C62" t="s">
+        <v>381</v>
+      </c>
+      <c r="D62" t="s">
         <v>344</v>
       </c>
-      <c r="E62" s="9" t="s">
+      <c r="E62" t="s">
         <v>341</v>
       </c>
-      <c r="F62" s="9" t="s">
+      <c r="F62" t="s">
         <v>342</v>
       </c>
-      <c r="G62" s="9">
+      <c r="G62">
         <v>6</v>
       </c>
-      <c r="H62" s="9">
+      <c r="H62">
         <v>8</v>
       </c>
-      <c r="I62" s="9">
-        <v>0</v>
-      </c>
-      <c r="J62" s="9">
-        <v>0</v>
-      </c>
-      <c r="K62" s="9">
-        <v>1</v>
-      </c>
-      <c r="L62" s="9">
-        <v>0</v>
-      </c>
-      <c r="M62" s="9" t="s">
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" t="s">
         <v>135</v>
       </c>
-      <c r="N62" s="9" t="s">
+      <c r="N62" t="s">
         <v>135</v>
       </c>
-      <c r="O62" s="9">
-        <v>1</v>
-      </c>
-      <c r="P62" s="9">
+      <c r="O62">
+        <v>1</v>
+      </c>
+      <c r="P62">
         <v>4</v>
       </c>
-      <c r="Q62" s="9">
-        <v>0</v>
-      </c>
-      <c r="R62" s="9">
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
         <v>100</v>
       </c>
-      <c r="S62" s="9">
+      <c r="S62">
         <v>30</v>
       </c>
-      <c r="T62" s="9">
-        <v>0</v>
-      </c>
-      <c r="U62" s="10" t="s">
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="V62" s="9" t="s">
+      <c r="V62" t="s">
         <v>39</v>
       </c>
-      <c r="W62" s="9">
+      <c r="W62">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:23" s="13" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="13">
+    <row r="63" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B63" s="13">
+      <c r="B63">
         <v>5007</v>
       </c>
-      <c r="C63" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="E63" s="13" t="s">
+      <c r="C63" t="s">
+        <v>383</v>
+      </c>
+      <c r="D63" t="s">
+        <v>373</v>
+      </c>
+      <c r="E63" t="s">
         <v>345</v>
       </c>
-      <c r="F63" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="G63" s="13">
+      <c r="F63" t="s">
+        <v>388</v>
+      </c>
+      <c r="G63">
         <v>6</v>
       </c>
-      <c r="H63" s="13">
+      <c r="H63">
         <v>25</v>
       </c>
-      <c r="I63" s="13">
-        <v>0</v>
-      </c>
-      <c r="J63" s="13">
-        <v>0</v>
-      </c>
-      <c r="K63" s="13">
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
         <v>2</v>
       </c>
-      <c r="L63" s="13">
-        <v>0</v>
-      </c>
-      <c r="M63" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="N63" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="O63" s="13">
-        <v>1</v>
-      </c>
-      <c r="P63" s="13">
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63" t="s">
+        <v>372</v>
+      </c>
+      <c r="N63" t="s">
+        <v>94</v>
+      </c>
+      <c r="O63">
+        <v>1</v>
+      </c>
+      <c r="P63">
         <v>4</v>
       </c>
-      <c r="Q63" s="13">
-        <v>0</v>
-      </c>
-      <c r="R63" s="13">
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
         <v>100</v>
       </c>
-      <c r="S63" s="13">
+      <c r="S63">
         <v>30</v>
       </c>
-      <c r="T63" s="13">
+      <c r="T63">
         <v>60</v>
       </c>
-      <c r="U63" s="14" t="s">
-        <v>378</v>
-      </c>
-      <c r="V63" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="W63" s="13">
+      <c r="U63" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="V63" t="s">
+        <v>94</v>
+      </c>
+      <c r="W63">
         <v>0</v>
       </c>
     </row>
@@ -9816,75 +9831,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:23" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="13">
+    <row r="68" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B68" s="13">
+      <c r="B68">
         <v>6006</v>
       </c>
-      <c r="C68" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="D68" s="13" t="s">
+      <c r="C68" t="s">
+        <v>386</v>
+      </c>
+      <c r="D68" t="s">
         <v>339</v>
       </c>
-      <c r="E68" s="13" t="s">
+      <c r="E68" t="s">
         <v>338</v>
       </c>
-      <c r="F68" s="13" t="s">
+      <c r="F68" t="s">
         <v>340</v>
       </c>
-      <c r="G68" s="13">
+      <c r="G68">
         <v>6</v>
       </c>
-      <c r="H68" s="13">
+      <c r="H68">
         <v>18</v>
       </c>
-      <c r="I68" s="13">
-        <v>0</v>
-      </c>
-      <c r="J68" s="13">
-        <v>0</v>
-      </c>
-      <c r="K68" s="13">
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
         <v>3</v>
       </c>
-      <c r="L68" s="13">
-        <v>0</v>
-      </c>
-      <c r="M68" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="N68" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="O68" s="13">
-        <v>1</v>
-      </c>
-      <c r="P68" s="13">
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="s">
+        <v>372</v>
+      </c>
+      <c r="N68" t="s">
+        <v>94</v>
+      </c>
+      <c r="O68">
+        <v>1</v>
+      </c>
+      <c r="P68">
         <v>5</v>
       </c>
-      <c r="Q68" s="13">
-        <v>1</v>
-      </c>
-      <c r="R68" s="13">
+      <c r="Q68">
+        <v>1</v>
+      </c>
+      <c r="R68">
         <v>100</v>
       </c>
-      <c r="S68" s="13">
+      <c r="S68">
         <v>30</v>
       </c>
-      <c r="T68" s="13">
+      <c r="T68">
         <v>120</v>
       </c>
-      <c r="U68" s="14" t="s">
-        <v>377</v>
-      </c>
-      <c r="V68" s="13" t="s">
+      <c r="U68" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="V68" t="s">
         <v>101</v>
       </c>
-      <c r="W68" s="13">
+      <c r="W68">
         <v>5</v>
       </c>
     </row>
@@ -9900,13 +9915,13 @@
         <v>279</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E69" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>351</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>352</v>
       </c>
       <c r="G69" s="4">
         <v>6</v>
@@ -9951,7 +9966,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="V69" s="4" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84071726-8544-41A7-83E8-8DDEACAAA614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1554398A-9DB1-45E3-A376-EE4865747574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3150" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="391">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -640,10 +640,6 @@
   </si>
   <si>
     <t>Non</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>skill_lvSelect</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -4354,22 +4350,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>甘さ・酸味・苦味がパーフェクトに近いとき、さらに点数を上げる。
-習得するだけでOK。
-LV1: 1.2倍
-LV2: 1.5倍
-LV3: 1.8倍
-LV4: 2.1倍
-LV5: 2.4倍</t>
-    <rPh sb="32" eb="34">
-      <t>シュウトク</t>
-    </rPh>
-    <rPh sb="52" eb="53">
-      <t>バイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>PlayerBuf</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -4417,40 +4397,61 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>次に作るお菓子の成功率を一時的に上げる「エピクレイシス状態」になる。
-しばらくの間、エピクレイシス状態は続く。
-また、一回お菓子・仕上げ・魔法を使用すると消える。
-LVを上げると、効果時間がのびる。
-LV1ごとに2時間のびる。</t>
-    <rPh sb="27" eb="29">
+    <t>skicon_Fire_Ark</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_NightBarron</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Latria</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Crescent_Moon</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Tea_Study</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Three_Stars</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>パーフェクト・プリンセス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Parfect_Princess</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Epiclesis</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Beautiful_Power</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スリースターズ状態になる。一定の間、消費MPを減らす。</t>
+    <rPh sb="7" eb="9">
       <t>ジョウタイ</t>
     </rPh>
-    <rPh sb="41" eb="42">
+    <rPh sb="13" eb="15">
+      <t>イッテイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
       <t>アイダ</t>
     </rPh>
-    <rPh sb="50" eb="52">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>ツヅ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>イッカイ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="66" eb="68">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="78" eb="79">
-      <t>キ</t>
+    <rPh sb="18" eb="20">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ヘ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4458,7 +4459,7 @@
     <t>スリースターズ状態になる。一定の間、消費MPを減少させる。
 一定時間経つと、スリースターズ状態は解除される。
 LVを上げると、効果時間がのびる。
-LV1ごとに1時間のびる。
+LV1ごとに2時間のびる。
 LV1: 消費MP1/2
 LV2: 消費MP1/3</t>
     <rPh sb="7" eb="9">
@@ -4500,62 +4501,69 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>skicon_Fire_Ark</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>skicon_NightBarron</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>skicon_Latria</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>skicon_Crescent_Moon</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>skicon_Tea_Study</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>skicon_Three_Stars</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>パーフェクト・プリンセス</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>skicon_Parfect_Princess</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>skicon_Epiclesis</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>skicon_Beautiful_Power</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>スリースターズ状態になる。一定の間、消費MPを減らす。</t>
-    <rPh sb="7" eb="9">
+    <t>甘さ・酸味・苦味がパーフェクトに近いとき、さらに点数を上げる。
+習得するだけでOK。</t>
+    <rPh sb="32" eb="34">
+      <t>シュウトク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>次に作るお菓子の成功率を一時的に上げる「エピクレイシス状態」になる。
+しばらくの間、エピクレイシス状態は続く。
+また、一回お菓子・仕上げ・魔法を使用すると消える。
+LVを上げると、確率を上昇させることができる。
+LV1: +30%
+LV2: +40%
+LV3: +50%</t>
+    <rPh sb="27" eb="29">
       <t>ジョウタイ</t>
     </rPh>
-    <rPh sb="13" eb="15">
-      <t>イッテイ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
+    <rPh sb="41" eb="42">
       <t>アイダ</t>
     </rPh>
-    <rPh sb="18" eb="20">
-      <t>ショウヒ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ヘ</t>
-    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>イッカイ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill_AddOriginalSelect</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>AddOriginal</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill_CompSelect</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4990,7 +4998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117D94E9-DB74-4E9B-8C36-2C34A645DC43}">
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:X79"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="13.25" customWidth="1"/>
@@ -4999,16 +5007,16 @@
     <col min="6" max="6" width="19.75" customWidth="1"/>
     <col min="7" max="7" width="7.5" customWidth="1"/>
     <col min="8" max="8" width="8.125" customWidth="1"/>
-    <col min="9" max="15" width="6.75" customWidth="1"/>
-    <col min="16" max="17" width="9" customWidth="1"/>
-    <col min="18" max="18" width="10.375" customWidth="1"/>
-    <col min="19" max="20" width="7.875" customWidth="1"/>
-    <col min="21" max="21" width="25.125" customWidth="1"/>
-    <col min="22" max="22" width="11.875" customWidth="1"/>
-    <col min="23" max="23" width="6.75" customWidth="1"/>
+    <col min="9" max="16" width="6.75" customWidth="1"/>
+    <col min="17" max="18" width="9" customWidth="1"/>
+    <col min="19" max="19" width="10.375" customWidth="1"/>
+    <col min="20" max="21" width="7.875" customWidth="1"/>
+    <col min="22" max="22" width="25.125" customWidth="1"/>
+    <col min="23" max="23" width="11.875" customWidth="1"/>
+    <col min="24" max="24" width="6.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -5046,40 +5054,43 @@
         <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>95</v>
+        <v>390</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="U1" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>148</v>
-      </c>
     </row>
-    <row r="2" spans="1:23" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:24" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4">
         <f t="shared" ref="A2:A79" si="0">ROW()-2</f>
         <v>0</v>
@@ -5094,7 +5105,7 @@
         <v>17</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
@@ -5123,35 +5134,38 @@
       <c r="N2" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O2" s="4">
-        <v>1</v>
+      <c r="O2" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P2" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="4">
         <v>9</v>
       </c>
-      <c r="Q2" s="4">
-        <v>0</v>
-      </c>
       <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
         <v>100</v>
       </c>
-      <c r="S2" s="4">
+      <c r="T2" s="4">
         <v>30</v>
       </c>
-      <c r="T2" s="4">
-        <v>0</v>
-      </c>
-      <c r="U2" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W2" s="4">
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X2" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -5160,16 +5174,16 @@
         <v>1002</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
         <v>54</v>
       </c>
       <c r="E3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" t="s">
         <v>116</v>
-      </c>
-      <c r="F3" t="s">
-        <v>117</v>
       </c>
       <c r="G3">
         <v>6</v>
@@ -5195,35 +5209,38 @@
       <c r="N3" t="s">
         <v>94</v>
       </c>
-      <c r="O3">
-        <v>0</v>
+      <c r="O3" t="s">
+        <v>94</v>
       </c>
       <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
         <v>9</v>
       </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
       <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
         <v>100</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>30</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="V3" t="s">
-        <v>94</v>
-      </c>
-      <c r="W3">
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="W3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:24" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -5238,7 +5255,7 @@
         <v>76</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>83</v>
@@ -5267,35 +5284,38 @@
       <c r="N4" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O4" s="4">
-        <v>1</v>
+      <c r="O4" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P4" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="4">
         <v>9</v>
       </c>
-      <c r="Q4" s="4">
-        <v>0</v>
-      </c>
       <c r="R4" s="4">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4">
         <v>100</v>
       </c>
-      <c r="S4" s="4">
+      <c r="T4" s="4">
         <v>30</v>
       </c>
-      <c r="T4" s="4">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W4" s="4">
+      <c r="U4" s="4">
+        <v>0</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X4" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -5304,16 +5324,16 @@
         <v>1010</v>
       </c>
       <c r="C5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G5">
         <v>6</v>
@@ -5339,35 +5359,38 @@
       <c r="N5" t="s">
         <v>94</v>
       </c>
-      <c r="O5">
-        <v>0</v>
+      <c r="O5" t="s">
+        <v>94</v>
       </c>
       <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
         <v>9</v>
       </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
       <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>100</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>30</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="V5" t="s">
-        <v>94</v>
-      </c>
-      <c r="W5">
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="W5" t="s">
+        <v>94</v>
+      </c>
+      <c r="X5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -5376,16 +5399,16 @@
         <v>1009</v>
       </c>
       <c r="C6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -5406,40 +5429,43 @@
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N6" t="s">
-        <v>135</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="O6" t="s">
+        <v>94</v>
       </c>
       <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
         <v>9</v>
       </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
       <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>100</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>30</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="W6" t="s">
         <v>54</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -5448,16 +5474,16 @@
         <v>1012</v>
       </c>
       <c r="C7" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E7" t="s">
+        <v>355</v>
+      </c>
+      <c r="F7" t="s">
         <v>356</v>
-      </c>
-      <c r="F7" t="s">
-        <v>357</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -5478,40 +5504,43 @@
         <v>0</v>
       </c>
       <c r="M7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N7" t="s">
-        <v>238</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O7" t="s">
+        <v>94</v>
       </c>
       <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
         <v>9</v>
       </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
       <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>70</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>30</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="W7" t="s">
         <v>54</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -5520,7 +5549,7 @@
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D8" t="s">
         <v>58</v>
@@ -5555,35 +5584,38 @@
       <c r="N8" t="s">
         <v>94</v>
       </c>
-      <c r="O8">
-        <v>1</v>
+      <c r="O8" t="s">
+        <v>94</v>
       </c>
       <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
         <v>9</v>
       </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
       <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <v>100</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>30</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="V8" t="s">
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="W8" t="s">
         <v>54</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -5592,7 +5624,7 @@
         <v>1006</v>
       </c>
       <c r="C9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
         <v>80</v>
@@ -5625,37 +5657,40 @@
         <v>94</v>
       </c>
       <c r="N9" t="s">
-        <v>238</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O9" t="s">
+        <v>94</v>
       </c>
       <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
         <v>9</v>
       </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
       <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
         <v>100</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>30</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="V9" t="s">
-        <v>163</v>
-      </c>
-      <c r="W9">
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="W9" t="s">
+        <v>162</v>
+      </c>
+      <c r="X9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -5664,16 +5699,16 @@
         <v>1008</v>
       </c>
       <c r="C10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D10" t="s">
         <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G10">
         <v>6</v>
@@ -5699,35 +5734,38 @@
       <c r="N10" t="s">
         <v>94</v>
       </c>
-      <c r="O10">
-        <v>1</v>
+      <c r="O10" t="s">
+        <v>94</v>
       </c>
       <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
         <v>9</v>
       </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
       <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
         <v>100</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>30</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="W10" t="s">
         <v>80</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -5736,16 +5774,16 @@
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D11" t="s">
+        <v>221</v>
+      </c>
+      <c r="E11" t="s">
         <v>222</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>223</v>
-      </c>
-      <c r="F11" t="s">
-        <v>224</v>
       </c>
       <c r="G11">
         <v>6</v>
@@ -5766,40 +5804,43 @@
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N11" t="s">
-        <v>135</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="O11" t="s">
+        <v>94</v>
       </c>
       <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
         <v>9</v>
       </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
       <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
         <v>100</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>30</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="V11" t="s">
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="W11" t="s">
         <v>54</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -5808,16 +5849,16 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E12" t="s">
+        <v>345</v>
+      </c>
+      <c r="F12" t="s">
         <v>346</v>
-      </c>
-      <c r="F12" t="s">
-        <v>347</v>
       </c>
       <c r="G12">
         <v>6</v>
@@ -5838,40 +5879,43 @@
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N12" t="s">
-        <v>135</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="O12" t="s">
+        <v>94</v>
       </c>
       <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
         <v>9</v>
       </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
       <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
         <v>100</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>30</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="V12" t="s">
-        <v>163</v>
-      </c>
-      <c r="W12">
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="W12" t="s">
+        <v>162</v>
+      </c>
+      <c r="X12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -5880,7 +5924,7 @@
         <v>1004</v>
       </c>
       <c r="C13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D13" t="s">
         <v>61</v>
@@ -5915,35 +5959,38 @@
       <c r="N13" t="s">
         <v>94</v>
       </c>
-      <c r="O13">
-        <v>0</v>
+      <c r="O13" t="s">
+        <v>94</v>
       </c>
       <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
         <v>9</v>
       </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
       <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
         <v>100</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>30</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="V13" t="s">
-        <v>94</v>
-      </c>
-      <c r="W13">
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="W13" t="s">
+        <v>94</v>
+      </c>
+      <c r="X13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:24" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -5958,10 +6005,10 @@
         <v>81</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G14" s="4">
         <v>6</v>
@@ -5987,35 +6034,38 @@
       <c r="N14" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O14" s="4">
-        <v>1</v>
+      <c r="O14" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P14" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="4">
         <v>9</v>
       </c>
-      <c r="Q14" s="4">
-        <v>0</v>
-      </c>
       <c r="R14" s="4">
+        <v>0</v>
+      </c>
+      <c r="S14" s="4">
         <v>100</v>
       </c>
-      <c r="S14" s="4">
+      <c r="T14" s="4">
         <v>30</v>
       </c>
-      <c r="T14" s="4">
-        <v>0</v>
-      </c>
-      <c r="U14" s="4" t="s">
-        <v>105</v>
+      <c r="U14" s="4">
+        <v>0</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W14" s="4">
+        <v>104</v>
+      </c>
+      <c r="W14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X14" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:24" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -6027,13 +6077,13 @@
         <v>64</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G15" s="4">
         <v>6</v>
@@ -6059,35 +6109,38 @@
       <c r="N15" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O15" s="4">
-        <v>1</v>
+      <c r="O15" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P15" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="4">
         <v>9</v>
       </c>
-      <c r="Q15" s="4">
-        <v>0</v>
-      </c>
       <c r="R15" s="4">
+        <v>0</v>
+      </c>
+      <c r="S15" s="4">
         <v>100</v>
       </c>
-      <c r="S15" s="4">
+      <c r="T15" s="4">
         <v>30</v>
       </c>
-      <c r="T15" s="4">
-        <v>0</v>
-      </c>
-      <c r="U15" s="4" t="s">
-        <v>204</v>
+      <c r="U15" s="4">
+        <v>0</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W15" s="4">
+        <v>203</v>
+      </c>
+      <c r="W15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X15" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -6096,16 +6149,16 @@
         <v>2004</v>
       </c>
       <c r="C16" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -6131,35 +6184,38 @@
       <c r="N16" t="s">
         <v>94</v>
       </c>
-      <c r="O16">
-        <v>0</v>
+      <c r="O16" t="s">
+        <v>94</v>
       </c>
       <c r="P16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
         <v>100</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>30</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="V16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W16">
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="W16" t="s">
+        <v>94</v>
+      </c>
+      <c r="X16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -6168,7 +6224,7 @@
         <v>2001</v>
       </c>
       <c r="C17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D17" t="s">
         <v>51</v>
@@ -6203,35 +6259,38 @@
       <c r="N17" t="s">
         <v>94</v>
       </c>
-      <c r="O17">
-        <v>1</v>
+      <c r="O17" t="s">
+        <v>94</v>
       </c>
       <c r="P17">
         <v>1</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
         <v>100</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <v>120</v>
       </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="V17" t="s">
-        <v>94</v>
-      </c>
-      <c r="W17">
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="W17" t="s">
+        <v>94</v>
+      </c>
+      <c r="X17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -6240,16 +6299,16 @@
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -6275,35 +6334,38 @@
       <c r="N18" t="s">
         <v>94</v>
       </c>
-      <c r="O18">
-        <v>1</v>
+      <c r="O18" t="s">
+        <v>94</v>
       </c>
       <c r="P18">
         <v>1</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
         <v>100</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>120</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="V18" t="s">
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="W18" t="s">
         <v>51</v>
       </c>
-      <c r="W18">
+      <c r="X18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:23" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:24" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -6318,7 +6380,7 @@
         <v>90</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>89</v>
@@ -6347,35 +6409,38 @@
       <c r="N19" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O19" s="4">
-        <v>1</v>
+      <c r="O19" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P19" s="4">
         <v>1</v>
       </c>
       <c r="Q19" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="4">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4">
         <v>100</v>
       </c>
-      <c r="S19" s="4">
+      <c r="T19" s="4">
         <v>120</v>
       </c>
-      <c r="T19" s="4">
-        <v>0</v>
-      </c>
-      <c r="U19" s="4" t="s">
+      <c r="U19" s="4">
+        <v>0</v>
+      </c>
+      <c r="V19" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="V19" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W19" s="4">
+      <c r="W19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X19" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -6384,16 +6449,16 @@
         <v>2005</v>
       </c>
       <c r="C20" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D20" t="s">
+        <v>252</v>
+      </c>
+      <c r="E20" t="s">
+        <v>274</v>
+      </c>
+      <c r="F20" t="s">
         <v>253</v>
-      </c>
-      <c r="E20" t="s">
-        <v>275</v>
-      </c>
-      <c r="F20" t="s">
-        <v>254</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -6414,13 +6479,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N20" t="s">
-        <v>135</v>
-      </c>
-      <c r="O20">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="O20" t="s">
+        <v>94</v>
       </c>
       <c r="P20">
         <v>1</v>
@@ -6429,25 +6494,28 @@
         <v>1</v>
       </c>
       <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
         <v>100</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>30</v>
       </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="V20" t="s">
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="W20" t="s">
         <v>51</v>
       </c>
-      <c r="W20">
+      <c r="X20">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -6456,16 +6524,16 @@
         <v>2003</v>
       </c>
       <c r="C21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -6489,37 +6557,40 @@
         <v>94</v>
       </c>
       <c r="N21" t="s">
-        <v>238</v>
-      </c>
-      <c r="O21">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O21" t="s">
+        <v>94</v>
       </c>
       <c r="P21">
         <v>1</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
         <v>100</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>30</v>
       </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="V21" t="s">
-        <v>101</v>
-      </c>
-      <c r="W21">
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="W21" t="s">
+        <v>100</v>
+      </c>
+      <c r="X21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:23" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:24" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -6531,13 +6602,13 @@
         <v>35</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G22" s="4">
         <v>2</v>
@@ -6563,35 +6634,38 @@
       <c r="N22" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O22" s="4">
-        <v>1</v>
+      <c r="O22" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P22" s="4">
         <v>1</v>
       </c>
       <c r="Q22" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="4">
+        <v>0</v>
+      </c>
+      <c r="S22" s="4">
         <v>100</v>
       </c>
-      <c r="S22" s="4">
+      <c r="T22" s="4">
         <v>30</v>
       </c>
-      <c r="T22" s="4">
-        <v>0</v>
-      </c>
-      <c r="U22" s="4" t="s">
-        <v>203</v>
+      <c r="U22" s="4">
+        <v>0</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W22" s="4">
+        <v>202</v>
+      </c>
+      <c r="W22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X22" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -6600,16 +6674,16 @@
         <v>3006</v>
       </c>
       <c r="C23" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -6635,35 +6709,38 @@
       <c r="N23" t="s">
         <v>94</v>
       </c>
-      <c r="O23">
-        <v>0</v>
+      <c r="O23" t="s">
+        <v>94</v>
       </c>
       <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
         <v>2</v>
       </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
       <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
         <v>100</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>30</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="V23" t="s">
-        <v>94</v>
-      </c>
-      <c r="W23">
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="W23" t="s">
+        <v>94</v>
+      </c>
+      <c r="X23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -6672,13 +6749,13 @@
         <v>3001</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
         <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
@@ -6705,37 +6782,40 @@
         <v>94</v>
       </c>
       <c r="N24" t="s">
-        <v>238</v>
-      </c>
-      <c r="O24">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O24" t="s">
+        <v>94</v>
       </c>
       <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
         <v>2</v>
       </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
       <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
         <v>100</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <v>30</v>
       </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="V24" t="s">
-        <v>94</v>
-      </c>
-      <c r="W24">
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="W24" t="s">
+        <v>94</v>
+      </c>
+      <c r="X24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -6744,7 +6824,7 @@
         <v>3002</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
         <v>20</v>
@@ -6777,37 +6857,40 @@
         <v>94</v>
       </c>
       <c r="N25" t="s">
-        <v>238</v>
-      </c>
-      <c r="O25">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O25" t="s">
+        <v>94</v>
       </c>
       <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
         <v>2</v>
       </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
       <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
         <v>100</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <v>30</v>
       </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="V25" t="s">
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="W25" t="s">
         <v>16</v>
       </c>
-      <c r="W25">
+      <c r="X25">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -6816,13 +6899,13 @@
         <v>3003</v>
       </c>
       <c r="C26" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F26" t="s">
         <v>72</v>
@@ -6846,40 +6929,43 @@
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N26" t="s">
-        <v>135</v>
-      </c>
-      <c r="O26">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="O26" t="s">
+        <v>94</v>
       </c>
       <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
         <v>2</v>
       </c>
-      <c r="Q26">
-        <v>1</v>
-      </c>
       <c r="R26">
+        <v>1</v>
+      </c>
+      <c r="S26">
         <v>100</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <v>30</v>
       </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="V26" t="s">
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="W26" t="s">
         <v>20</v>
       </c>
-      <c r="W26">
+      <c r="X26">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -6888,16 +6974,16 @@
         <v>3008</v>
       </c>
       <c r="C27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D27" t="s">
+        <v>255</v>
+      </c>
+      <c r="E27" t="s">
+        <v>254</v>
+      </c>
+      <c r="F27" t="s">
         <v>256</v>
-      </c>
-      <c r="E27" t="s">
-        <v>255</v>
-      </c>
-      <c r="F27" t="s">
-        <v>257</v>
       </c>
       <c r="G27">
         <v>4</v>
@@ -6918,40 +7004,43 @@
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N27" t="s">
-        <v>135</v>
-      </c>
-      <c r="O27">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="O27" t="s">
+        <v>94</v>
       </c>
       <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
         <v>2</v>
       </c>
-      <c r="Q27">
-        <v>1</v>
-      </c>
       <c r="R27">
+        <v>1</v>
+      </c>
+      <c r="S27">
         <v>100</v>
       </c>
-      <c r="S27">
+      <c r="T27">
         <v>30</v>
       </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="V27" t="s">
-        <v>94</v>
-      </c>
-      <c r="W27">
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="W27" t="s">
+        <v>94</v>
+      </c>
+      <c r="X27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -6960,22 +7049,22 @@
         <v>3009</v>
       </c>
       <c r="C28" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D28" t="s">
+        <v>335</v>
+      </c>
+      <c r="E28" t="s">
+        <v>334</v>
+      </c>
+      <c r="F28" t="s">
         <v>336</v>
-      </c>
-      <c r="E28" t="s">
-        <v>335</v>
-      </c>
-      <c r="F28" t="s">
-        <v>337</v>
       </c>
       <c r="G28">
         <v>4</v>
       </c>
       <c r="H28">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -6990,40 +7079,43 @@
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="N28" t="s">
         <v>94</v>
       </c>
-      <c r="O28">
-        <v>1</v>
+      <c r="O28" t="s">
+        <v>94</v>
       </c>
       <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28">
         <v>2</v>
       </c>
-      <c r="Q28">
-        <v>1</v>
-      </c>
       <c r="R28">
+        <v>1</v>
+      </c>
+      <c r="S28">
         <v>100</v>
       </c>
-      <c r="S28">
+      <c r="T28">
         <v>30</v>
       </c>
-      <c r="T28">
+      <c r="U28">
         <v>120</v>
       </c>
-      <c r="U28" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="V28" t="s">
-        <v>94</v>
-      </c>
-      <c r="W28">
+      <c r="V28" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="W28" t="s">
+        <v>94</v>
+      </c>
+      <c r="X28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -7032,16 +7124,16 @@
         <v>3010</v>
       </c>
       <c r="C29" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D29" t="s">
+        <v>353</v>
+      </c>
+      <c r="E29" t="s">
+        <v>380</v>
+      </c>
+      <c r="F29" t="s">
         <v>354</v>
-      </c>
-      <c r="E29" t="s">
-        <v>384</v>
-      </c>
-      <c r="F29" t="s">
-        <v>355</v>
       </c>
       <c r="G29">
         <v>4</v>
@@ -7067,35 +7159,38 @@
       <c r="N29" t="s">
         <v>94</v>
       </c>
-      <c r="O29">
-        <v>0</v>
+      <c r="O29" t="s">
+        <v>94</v>
       </c>
       <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
         <v>2</v>
       </c>
-      <c r="Q29">
-        <v>1</v>
-      </c>
       <c r="R29">
+        <v>1</v>
+      </c>
+      <c r="S29">
         <v>100</v>
       </c>
-      <c r="S29">
+      <c r="T29">
         <v>30</v>
       </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="V29" t="s">
-        <v>94</v>
-      </c>
-      <c r="W29">
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="W29" t="s">
+        <v>94</v>
+      </c>
+      <c r="X29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -7104,16 +7199,16 @@
         <v>3004</v>
       </c>
       <c r="C30" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E30" t="s">
+        <v>112</v>
+      </c>
+      <c r="F30" t="s">
         <v>113</v>
-      </c>
-      <c r="F30" t="s">
-        <v>114</v>
       </c>
       <c r="G30">
         <v>4</v>
@@ -7139,35 +7234,38 @@
       <c r="N30" t="s">
         <v>94</v>
       </c>
-      <c r="O30">
-        <v>0</v>
+      <c r="O30" t="s">
+        <v>94</v>
       </c>
       <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
         <v>2</v>
       </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
       <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
         <v>100</v>
       </c>
-      <c r="S30">
+      <c r="T30">
         <v>30</v>
       </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="V30" t="s">
-        <v>94</v>
-      </c>
-      <c r="W30">
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="W30" t="s">
+        <v>94</v>
+      </c>
+      <c r="X30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -7176,16 +7274,16 @@
         <v>3007</v>
       </c>
       <c r="C31" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D31" t="s">
+        <v>249</v>
+      </c>
+      <c r="E31" t="s">
+        <v>273</v>
+      </c>
+      <c r="F31" t="s">
         <v>250</v>
-      </c>
-      <c r="E31" t="s">
-        <v>274</v>
-      </c>
-      <c r="F31" t="s">
-        <v>251</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -7211,35 +7309,38 @@
       <c r="N31" t="s">
         <v>94</v>
       </c>
-      <c r="O31">
-        <v>0</v>
+      <c r="O31" t="s">
+        <v>94</v>
       </c>
       <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
         <v>2</v>
       </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
       <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
         <v>100</v>
       </c>
-      <c r="S31">
+      <c r="T31">
         <v>30</v>
       </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="V31" t="s">
-        <v>94</v>
-      </c>
-      <c r="W31">
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="W31" t="s">
+        <v>94</v>
+      </c>
+      <c r="X31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:23" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:24" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="4">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -7251,13 +7352,13 @@
         <v>36</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G32" s="4">
         <v>4</v>
@@ -7283,35 +7384,38 @@
       <c r="N32" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O32" s="4">
-        <v>1</v>
+      <c r="O32" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P32" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="4">
         <v>2</v>
       </c>
-      <c r="Q32" s="4">
-        <v>0</v>
-      </c>
       <c r="R32" s="4">
+        <v>0</v>
+      </c>
+      <c r="S32" s="4">
         <v>100</v>
       </c>
-      <c r="S32" s="4">
+      <c r="T32" s="4">
         <v>30</v>
       </c>
-      <c r="T32" s="4">
-        <v>0</v>
-      </c>
-      <c r="U32" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="V32" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W32" s="4">
+      <c r="U32" s="4">
+        <v>0</v>
+      </c>
+      <c r="V32" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="W32" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X32" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:23" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:24" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="4">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -7323,13 +7427,13 @@
         <v>36</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="F33" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="G33" s="4">
         <v>4</v>
@@ -7355,35 +7459,38 @@
       <c r="N33" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O33" s="4">
-        <v>1</v>
+      <c r="O33" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P33" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="4">
         <v>2</v>
       </c>
-      <c r="Q33" s="4">
-        <v>0</v>
-      </c>
       <c r="R33" s="4">
+        <v>0</v>
+      </c>
+      <c r="S33" s="4">
         <v>100</v>
       </c>
-      <c r="S33" s="4">
+      <c r="T33" s="4">
         <v>30</v>
       </c>
-      <c r="T33" s="4">
-        <v>0</v>
-      </c>
-      <c r="U33" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="V33" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W33" s="4">
+      <c r="U33" s="4">
+        <v>0</v>
+      </c>
+      <c r="V33" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="W33" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X33" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -7392,16 +7499,16 @@
         <v>4010</v>
       </c>
       <c r="C34" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D34" t="s">
+        <v>150</v>
+      </c>
+      <c r="E34" t="s">
         <v>151</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>152</v>
-      </c>
-      <c r="F34" t="s">
-        <v>153</v>
       </c>
       <c r="G34">
         <v>6</v>
@@ -7427,35 +7534,38 @@
       <c r="N34" t="s">
         <v>94</v>
       </c>
-      <c r="O34">
-        <v>0</v>
+      <c r="O34" t="s">
+        <v>94</v>
       </c>
       <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
         <v>3</v>
       </c>
-      <c r="Q34">
-        <v>0</v>
-      </c>
       <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
         <v>100</v>
       </c>
-      <c r="S34">
+      <c r="T34">
         <v>30</v>
       </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="V34" t="s">
-        <v>94</v>
-      </c>
-      <c r="W34">
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="W34" t="s">
+        <v>94</v>
+      </c>
+      <c r="X34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -7464,16 +7574,16 @@
         <v>4011</v>
       </c>
       <c r="C35" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D35" t="s">
+        <v>153</v>
+      </c>
+      <c r="E35" t="s">
+        <v>207</v>
+      </c>
+      <c r="F35" t="s">
         <v>154</v>
-      </c>
-      <c r="E35" t="s">
-        <v>208</v>
-      </c>
-      <c r="F35" t="s">
-        <v>155</v>
       </c>
       <c r="G35">
         <v>6</v>
@@ -7499,35 +7609,38 @@
       <c r="N35" t="s">
         <v>94</v>
       </c>
-      <c r="O35">
-        <v>0</v>
+      <c r="O35" t="s">
+        <v>94</v>
       </c>
       <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
         <v>3</v>
       </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
       <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
         <v>100</v>
       </c>
-      <c r="S35">
+      <c r="T35">
         <v>30</v>
       </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="V35" t="s">
-        <v>94</v>
-      </c>
-      <c r="W35">
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="W35" t="s">
+        <v>94</v>
+      </c>
+      <c r="X35">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:24" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -7536,7 +7649,7 @@
         <v>4001</v>
       </c>
       <c r="C36" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D36" t="s">
         <v>23</v>
@@ -7545,7 +7658,7 @@
         <v>21</v>
       </c>
       <c r="F36" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G36">
         <v>6</v>
@@ -7566,40 +7679,43 @@
         <v>0</v>
       </c>
       <c r="M36" t="s">
+        <v>246</v>
+      </c>
+      <c r="N36" t="s">
+        <v>237</v>
+      </c>
+      <c r="O36" t="s">
+        <v>94</v>
+      </c>
+      <c r="P36">
+        <v>1</v>
+      </c>
+      <c r="Q36">
+        <v>3</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>70</v>
+      </c>
+      <c r="T36">
+        <v>10</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="N36" t="s">
-        <v>238</v>
-      </c>
-      <c r="O36">
-        <v>1</v>
-      </c>
-      <c r="P36">
-        <v>3</v>
-      </c>
-      <c r="Q36">
-        <v>0</v>
-      </c>
-      <c r="R36">
-        <v>70</v>
-      </c>
-      <c r="S36">
-        <v>10</v>
-      </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-      <c r="U36" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="V36" t="s">
-        <v>154</v>
-      </c>
-      <c r="W36">
+      <c r="W36" t="s">
+        <v>153</v>
+      </c>
+      <c r="X36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -7608,7 +7724,7 @@
         <v>4002</v>
       </c>
       <c r="C37" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D37" t="s">
         <v>25</v>
@@ -7617,7 +7733,7 @@
         <v>22</v>
       </c>
       <c r="F37" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -7641,37 +7757,40 @@
         <v>94</v>
       </c>
       <c r="N37" t="s">
-        <v>238</v>
-      </c>
-      <c r="O37">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O37" t="s">
+        <v>94</v>
       </c>
       <c r="P37">
+        <v>1</v>
+      </c>
+      <c r="Q37">
         <v>3</v>
       </c>
-      <c r="Q37">
-        <v>0</v>
-      </c>
       <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
         <v>100</v>
       </c>
-      <c r="S37">
+      <c r="T37">
         <v>15</v>
       </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
-      <c r="U37" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="V37" t="s">
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="W37" t="s">
         <v>23</v>
       </c>
-      <c r="W37">
+      <c r="X37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -7680,16 +7799,16 @@
         <v>4010</v>
       </c>
       <c r="C38" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E38" t="s">
         <v>128</v>
       </c>
-      <c r="E38" t="s">
-        <v>129</v>
-      </c>
       <c r="F38" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -7713,37 +7832,40 @@
         <v>94</v>
       </c>
       <c r="N38" t="s">
-        <v>238</v>
-      </c>
-      <c r="O38">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O38" t="s">
+        <v>94</v>
       </c>
       <c r="P38">
+        <v>1</v>
+      </c>
+      <c r="Q38">
         <v>3</v>
       </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
       <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
         <v>100</v>
       </c>
-      <c r="S38">
+      <c r="T38">
         <v>15</v>
       </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="V38" t="s">
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="W38" t="s">
         <v>23</v>
       </c>
-      <c r="W38">
+      <c r="X38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -7752,16 +7874,16 @@
         <v>4011</v>
       </c>
       <c r="C39" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E39" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F39" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -7785,37 +7907,40 @@
         <v>94</v>
       </c>
       <c r="N39" t="s">
-        <v>238</v>
-      </c>
-      <c r="O39">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O39" t="s">
+        <v>94</v>
       </c>
       <c r="P39">
+        <v>1</v>
+      </c>
+      <c r="Q39">
         <v>3</v>
       </c>
-      <c r="Q39">
-        <v>0</v>
-      </c>
       <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
         <v>100</v>
       </c>
-      <c r="S39">
+      <c r="T39">
         <v>15</v>
       </c>
-      <c r="T39">
-        <v>0</v>
-      </c>
-      <c r="U39" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="V39" t="s">
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="W39" t="s">
         <v>23</v>
       </c>
-      <c r="W39">
+      <c r="X39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -7824,16 +7949,16 @@
         <v>4012</v>
       </c>
       <c r="C40" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F40" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -7857,37 +7982,40 @@
         <v>94</v>
       </c>
       <c r="N40" t="s">
-        <v>238</v>
-      </c>
-      <c r="O40">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O40" t="s">
+        <v>94</v>
       </c>
       <c r="P40">
+        <v>1</v>
+      </c>
+      <c r="Q40">
         <v>3</v>
       </c>
-      <c r="Q40">
-        <v>0</v>
-      </c>
       <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
         <v>100</v>
       </c>
-      <c r="S40">
+      <c r="T40">
         <v>15</v>
       </c>
-      <c r="T40">
-        <v>0</v>
-      </c>
-      <c r="U40" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="V40" t="s">
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="W40" t="s">
         <v>23</v>
       </c>
-      <c r="W40">
+      <c r="X40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -7896,16 +8024,16 @@
         <v>4012</v>
       </c>
       <c r="C41" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -7929,37 +8057,40 @@
         <v>94</v>
       </c>
       <c r="N41" t="s">
-        <v>238</v>
-      </c>
-      <c r="O41">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O41" t="s">
+        <v>94</v>
       </c>
       <c r="P41">
+        <v>1</v>
+      </c>
+      <c r="Q41">
         <v>3</v>
       </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
       <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
         <v>100</v>
       </c>
-      <c r="S41">
+      <c r="T41">
         <v>15</v>
       </c>
-      <c r="T41">
-        <v>0</v>
-      </c>
-      <c r="U41" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="V41" t="s">
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="W41" t="s">
         <v>23</v>
       </c>
-      <c r="W41">
+      <c r="X41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -7968,16 +8099,16 @@
         <v>4012</v>
       </c>
       <c r="C42" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D42" t="s">
+        <v>178</v>
+      </c>
+      <c r="E42" t="s">
+        <v>183</v>
+      </c>
+      <c r="F42" t="s">
         <v>179</v>
-      </c>
-      <c r="E42" t="s">
-        <v>184</v>
-      </c>
-      <c r="F42" t="s">
-        <v>180</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -8001,37 +8132,40 @@
         <v>94</v>
       </c>
       <c r="N42" t="s">
-        <v>238</v>
-      </c>
-      <c r="O42">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O42" t="s">
+        <v>94</v>
       </c>
       <c r="P42">
+        <v>1</v>
+      </c>
+      <c r="Q42">
         <v>3</v>
       </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
       <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
         <v>100</v>
       </c>
-      <c r="S42">
+      <c r="T42">
         <v>15</v>
       </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
-      <c r="U42" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="V42" t="s">
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="W42" t="s">
         <v>23</v>
       </c>
-      <c r="W42">
+      <c r="X42">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:23" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:24" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="4">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -8075,35 +8209,38 @@
       <c r="N43" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O43" s="4">
-        <v>1</v>
+      <c r="O43" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P43" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="4">
         <v>3</v>
       </c>
-      <c r="Q43" s="4">
-        <v>0</v>
-      </c>
       <c r="R43" s="4">
+        <v>0</v>
+      </c>
+      <c r="S43" s="4">
         <v>100</v>
       </c>
-      <c r="S43" s="4">
+      <c r="T43" s="4">
         <v>30</v>
       </c>
-      <c r="T43" s="4">
-        <v>0</v>
-      </c>
-      <c r="U43" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="V43" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W43" s="4">
+      <c r="U43" s="4">
+        <v>0</v>
+      </c>
+      <c r="V43" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="W43" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X43" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -8112,16 +8249,16 @@
         <v>4004</v>
       </c>
       <c r="C44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D44" t="s">
         <v>27</v>
       </c>
       <c r="E44" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G44">
         <v>3</v>
@@ -8142,133 +8279,139 @@
         <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N44" t="s">
-        <v>135</v>
-      </c>
-      <c r="O44">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="O44" t="s">
+        <v>94</v>
       </c>
       <c r="P44">
+        <v>1</v>
+      </c>
+      <c r="Q44">
         <v>3</v>
       </c>
-      <c r="Q44">
-        <v>1</v>
-      </c>
       <c r="R44">
+        <v>1</v>
+      </c>
+      <c r="S44">
         <v>100</v>
       </c>
-      <c r="S44">
+      <c r="T44">
         <v>30</v>
       </c>
-      <c r="T44">
-        <v>0</v>
-      </c>
-      <c r="U44" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="V44" t="s">
-        <v>154</v>
-      </c>
-      <c r="W44">
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="W44" t="s">
+        <v>153</v>
+      </c>
+      <c r="X44">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:23" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="9">
+    <row r="45" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="4">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45" s="9">
-        <v>4013</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="G45" s="9">
+      <c r="B45" s="4">
+        <v>4005</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45" s="4">
+        <v>12</v>
+      </c>
+      <c r="H45" s="4">
+        <v>5</v>
+      </c>
+      <c r="I45" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J45" s="4">
+        <v>0</v>
+      </c>
+      <c r="K45" s="4">
         <v>3</v>
       </c>
-      <c r="H45" s="9">
+      <c r="L45" s="4">
+        <v>0</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="P45" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="4">
         <v>3</v>
       </c>
-      <c r="I45" s="9">
-        <v>0</v>
-      </c>
-      <c r="J45" s="9">
-        <v>0</v>
-      </c>
-      <c r="K45" s="9">
-        <v>1</v>
-      </c>
-      <c r="L45" s="9">
-        <v>0</v>
-      </c>
-      <c r="M45" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="N45" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="O45" s="9">
-        <v>1</v>
-      </c>
-      <c r="P45" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="9">
-        <v>1</v>
-      </c>
-      <c r="R45" s="9">
+      <c r="R45" s="4">
+        <v>0</v>
+      </c>
+      <c r="S45" s="4">
         <v>100</v>
       </c>
-      <c r="S45" s="9">
+      <c r="T45" s="4">
         <v>30</v>
       </c>
-      <c r="T45" s="9">
-        <v>0</v>
-      </c>
-      <c r="U45" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="V45" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="W45" s="9">
-        <v>5</v>
+      <c r="U45" s="4">
+        <v>0</v>
+      </c>
+      <c r="V45" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="W45" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X45" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:23" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A46" s="4">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B46" s="4">
-        <v>4005</v>
+        <v>4006</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>29</v>
+        <v>238</v>
       </c>
       <c r="G46" s="4">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H46" s="4">
         <v>5</v>
@@ -8289,196 +8432,205 @@
         <v>94</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O46" s="4">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P46" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="4">
         <v>3</v>
       </c>
-      <c r="Q46" s="4">
-        <v>0</v>
-      </c>
       <c r="R46" s="4">
+        <v>0</v>
+      </c>
+      <c r="S46" s="4">
         <v>100</v>
       </c>
-      <c r="S46" s="4">
+      <c r="T46" s="4">
         <v>30</v>
       </c>
-      <c r="T46" s="4">
-        <v>0</v>
-      </c>
-      <c r="U46" s="6" t="s">
-        <v>166</v>
+      <c r="U46" s="4">
+        <v>0</v>
       </c>
       <c r="V46" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W46" s="4">
+        <v>238</v>
+      </c>
+      <c r="W46" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X46" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="4">
+    <row r="47" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B47" s="4">
-        <v>4006</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F47" s="4" t="s">
+      <c r="B47">
+        <v>4007</v>
+      </c>
+      <c r="C47" t="s">
+        <v>308</v>
+      </c>
+      <c r="D47" t="s">
+        <v>85</v>
+      </c>
+      <c r="E47" t="s">
+        <v>87</v>
+      </c>
+      <c r="F47" t="s">
         <v>239</v>
       </c>
-      <c r="G47" s="4">
+      <c r="G47">
         <v>3</v>
       </c>
-      <c r="H47" s="4">
+      <c r="H47">
+        <v>3</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="s">
+        <v>94</v>
+      </c>
+      <c r="N47" t="s">
+        <v>237</v>
+      </c>
+      <c r="O47" t="s">
+        <v>94</v>
+      </c>
+      <c r="P47">
+        <v>1</v>
+      </c>
+      <c r="Q47">
+        <v>3</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>100</v>
+      </c>
+      <c r="T47">
+        <v>15</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="W47" t="s">
+        <v>153</v>
+      </c>
+      <c r="X47">
         <v>5</v>
       </c>
-      <c r="I47" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J47" s="4">
-        <v>0</v>
-      </c>
-      <c r="K47" s="4">
-        <v>3</v>
-      </c>
-      <c r="L47" s="4">
-        <v>0</v>
-      </c>
-      <c r="M47" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N47" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="O47" s="4">
-        <v>1</v>
-      </c>
-      <c r="P47" s="4">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="4">
-        <v>0</v>
-      </c>
-      <c r="R47" s="4">
-        <v>100</v>
-      </c>
-      <c r="S47" s="4">
-        <v>30</v>
-      </c>
-      <c r="T47" s="4">
-        <v>0</v>
-      </c>
-      <c r="U47" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="V47" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W47" s="4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="48" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48">
+    <row r="48" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="4">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="4">
         <v>4007</v>
       </c>
-      <c r="C48" t="s">
-        <v>309</v>
-      </c>
-      <c r="D48" t="s">
-        <v>85</v>
-      </c>
-      <c r="E48" t="s">
-        <v>87</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="C48" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="4">
         <v>3</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="4">
+        <v>5</v>
+      </c>
+      <c r="I48" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J48" s="4">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4">
         <v>3</v>
       </c>
-      <c r="I48">
-        <v>1</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>1</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48" t="s">
-        <v>94</v>
-      </c>
-      <c r="N48" t="s">
-        <v>238</v>
-      </c>
-      <c r="O48">
-        <v>1</v>
-      </c>
-      <c r="P48">
+      <c r="L48" s="4">
+        <v>0</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="P48" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="4">
         <v>3</v>
       </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
+      <c r="R48" s="4">
+        <v>0</v>
+      </c>
+      <c r="S48" s="4">
         <v>100</v>
       </c>
-      <c r="S48">
-        <v>15</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="V48" t="s">
-        <v>154</v>
-      </c>
-      <c r="W48">
-        <v>5</v>
+      <c r="T48" s="4">
+        <v>30</v>
+      </c>
+      <c r="U48" s="4">
+        <v>0</v>
+      </c>
+      <c r="V48" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="W48" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X48" s="4">
+        <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A49" s="4">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B49" s="4">
-        <v>4007</v>
+        <v>4008</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>195</v>
+        <v>86</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>196</v>
+        <v>88</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>241</v>
@@ -8505,52 +8657,55 @@
         <v>94</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="O49" s="4">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P49" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="4">
         <v>3</v>
       </c>
-      <c r="Q49" s="4">
-        <v>0</v>
-      </c>
       <c r="R49" s="4">
+        <v>0</v>
+      </c>
+      <c r="S49" s="4">
         <v>100</v>
       </c>
-      <c r="S49" s="4">
+      <c r="T49" s="4">
         <v>30</v>
       </c>
-      <c r="T49" s="4">
-        <v>0</v>
-      </c>
-      <c r="U49" s="4" t="s">
+      <c r="U49" s="4">
+        <v>0</v>
+      </c>
+      <c r="V49" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="V49" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W49" s="4">
+      <c r="W49" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X49" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A50" s="4">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B50" s="4">
-        <v>4008</v>
+        <v>4009</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>242</v>
@@ -8559,7 +8714,7 @@
         <v>3</v>
       </c>
       <c r="H50" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I50" s="4">
         <v>9999</v>
@@ -8577,61 +8732,64 @@
         <v>94</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="O50" s="4">
-        <v>1</v>
+        <v>94</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P50" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="4">
         <v>3</v>
       </c>
-      <c r="Q50" s="4">
-        <v>0</v>
-      </c>
       <c r="R50" s="4">
+        <v>0</v>
+      </c>
+      <c r="S50" s="4">
         <v>100</v>
       </c>
-      <c r="S50" s="4">
+      <c r="T50" s="4">
         <v>30</v>
       </c>
-      <c r="T50" s="4">
-        <v>0</v>
-      </c>
-      <c r="U50" s="4" t="s">
+      <c r="U50" s="4">
+        <v>0</v>
+      </c>
+      <c r="V50" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="V50" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W50" s="4">
+      <c r="W50" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X50" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:24" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="4">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B51" s="4">
-        <v>4009</v>
+        <v>4013</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>102</v>
+        <v>226</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>243</v>
+        <v>159</v>
       </c>
       <c r="G51" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H51" s="4">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I51" s="4">
         <v>9999</v>
@@ -8640,70 +8798,73 @@
         <v>0</v>
       </c>
       <c r="K51" s="4">
+        <v>5</v>
+      </c>
+      <c r="L51" s="4">
+        <v>0</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="P51" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="4">
         <v>3</v>
       </c>
-      <c r="L51" s="4">
-        <v>0</v>
-      </c>
-      <c r="M51" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N51" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O51" s="4">
-        <v>1</v>
-      </c>
-      <c r="P51" s="4">
-        <v>3</v>
-      </c>
-      <c r="Q51" s="4">
-        <v>0</v>
-      </c>
       <c r="R51" s="4">
+        <v>0</v>
+      </c>
+      <c r="S51" s="4">
         <v>100</v>
       </c>
-      <c r="S51" s="4">
+      <c r="T51" s="4">
         <v>30</v>
       </c>
-      <c r="T51" s="4">
-        <v>0</v>
-      </c>
-      <c r="U51" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="V51" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W51" s="4">
+      <c r="U51" s="4">
+        <v>0</v>
+      </c>
+      <c r="V51" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="W51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X51" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:23" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:24" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="4">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B52" s="4">
-        <v>4013</v>
+        <v>5004</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>227</v>
+        <v>157</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="G52" s="4">
         <v>6</v>
       </c>
       <c r="H52" s="4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I52" s="4">
         <v>9999</v>
@@ -8723,107 +8884,113 @@
       <c r="N52" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O52" s="4">
-        <v>1</v>
+      <c r="O52" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P52" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R52" s="4">
+        <v>0</v>
+      </c>
+      <c r="S52" s="4">
         <v>100</v>
       </c>
-      <c r="S52" s="4">
+      <c r="T52" s="4">
         <v>30</v>
       </c>
-      <c r="T52" s="4">
-        <v>0</v>
-      </c>
-      <c r="U52" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="V52" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W52" s="4">
+      <c r="U52" s="4">
+        <v>0</v>
+      </c>
+      <c r="V52" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="W52" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X52" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:23" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="4">
+    <row r="53" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53" s="4">
-        <v>5004</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="G53" s="4">
+      <c r="B53">
+        <v>5007</v>
+      </c>
+      <c r="C53" t="s">
+        <v>310</v>
+      </c>
+      <c r="D53" t="s">
+        <v>272</v>
+      </c>
+      <c r="E53" t="s">
+        <v>270</v>
+      </c>
+      <c r="F53" t="s">
+        <v>271</v>
+      </c>
+      <c r="G53">
         <v>6</v>
       </c>
-      <c r="H53" s="4">
-        <v>0</v>
-      </c>
-      <c r="I53" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J53" s="4">
-        <v>0</v>
-      </c>
-      <c r="K53" s="4">
-        <v>5</v>
-      </c>
-      <c r="L53" s="4">
-        <v>0</v>
-      </c>
-      <c r="M53" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N53" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O53" s="4">
-        <v>0</v>
-      </c>
-      <c r="P53" s="4">
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>10</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" t="s">
+        <v>94</v>
+      </c>
+      <c r="N53" t="s">
+        <v>94</v>
+      </c>
+      <c r="O53" t="s">
+        <v>94</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
         <v>4</v>
       </c>
-      <c r="Q53" s="4">
-        <v>0</v>
-      </c>
-      <c r="R53" s="4">
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
         <v>100</v>
       </c>
-      <c r="S53" s="4">
+      <c r="T53">
         <v>30</v>
       </c>
-      <c r="T53" s="4">
-        <v>0</v>
-      </c>
-      <c r="U53" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="V53" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W53" s="4">
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="W53" t="s">
+        <v>94</v>
+      </c>
+      <c r="X53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -8832,16 +8999,16 @@
         <v>5007</v>
       </c>
       <c r="C54" t="s">
-        <v>311</v>
+        <v>378</v>
       </c>
       <c r="D54" t="s">
-        <v>273</v>
+        <v>367</v>
       </c>
       <c r="E54" t="s">
-        <v>271</v>
+        <v>366</v>
       </c>
       <c r="F54" t="s">
-        <v>272</v>
+        <v>368</v>
       </c>
       <c r="G54">
         <v>6</v>
@@ -8867,59 +9034,62 @@
       <c r="N54" t="s">
         <v>94</v>
       </c>
-      <c r="O54">
-        <v>0</v>
+      <c r="O54" t="s">
+        <v>94</v>
       </c>
       <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
         <v>4</v>
       </c>
-      <c r="Q54">
-        <v>0</v>
-      </c>
       <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
         <v>100</v>
       </c>
-      <c r="S54">
+      <c r="T54">
         <v>30</v>
       </c>
-      <c r="T54">
-        <v>0</v>
-      </c>
-      <c r="U54" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="V54" t="s">
-        <v>94</v>
-      </c>
-      <c r="W54">
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="W54" t="s">
+        <v>94</v>
+      </c>
+      <c r="X54">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B55">
-        <v>5007</v>
+        <v>5001</v>
       </c>
       <c r="C55" t="s">
-        <v>382</v>
+        <v>296</v>
       </c>
       <c r="D55" t="s">
-        <v>368</v>
+        <v>39</v>
       </c>
       <c r="E55" t="s">
-        <v>367</v>
+        <v>38</v>
       </c>
       <c r="F55" t="s">
-        <v>369</v>
+        <v>329</v>
       </c>
       <c r="G55">
         <v>6</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -8928,70 +9098,73 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L55">
         <v>0</v>
       </c>
       <c r="M55" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="N55" t="s">
-        <v>94</v>
-      </c>
-      <c r="O55">
-        <v>0</v>
+        <v>134</v>
+      </c>
+      <c r="O55" t="s">
+        <v>94</v>
       </c>
       <c r="P55">
+        <v>1</v>
+      </c>
+      <c r="Q55">
         <v>4</v>
       </c>
-      <c r="Q55">
-        <v>0</v>
-      </c>
       <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
         <v>100</v>
       </c>
-      <c r="S55">
-        <v>30</v>
-      </c>
       <c r="T55">
-        <v>0</v>
-      </c>
-      <c r="U55" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="V55" t="s">
-        <v>94</v>
-      </c>
-      <c r="W55">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="W55" t="s">
+        <v>272</v>
+      </c>
+      <c r="X55">
+        <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B56">
-        <v>5001</v>
+        <v>5002</v>
       </c>
       <c r="C56" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="D56" t="s">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="E56" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="F56" t="s">
-        <v>330</v>
+        <v>119</v>
       </c>
       <c r="G56">
         <v>6</v>
       </c>
       <c r="H56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -9006,64 +9179,67 @@
         <v>0</v>
       </c>
       <c r="M56" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="N56" t="s">
-        <v>135</v>
-      </c>
-      <c r="O56">
-        <v>1</v>
+        <v>94</v>
+      </c>
+      <c r="O56" t="s">
+        <v>94</v>
       </c>
       <c r="P56">
+        <v>1</v>
+      </c>
+      <c r="Q56">
         <v>4</v>
       </c>
-      <c r="Q56">
-        <v>0</v>
-      </c>
       <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
         <v>100</v>
       </c>
-      <c r="S56">
-        <v>15</v>
-      </c>
       <c r="T56">
-        <v>0</v>
-      </c>
-      <c r="U56" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="V56" t="s">
-        <v>273</v>
-      </c>
-      <c r="W56">
+        <v>30</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="W56" t="s">
+        <v>367</v>
+      </c>
+      <c r="X56">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B57">
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="C57" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D57" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="E57" t="s">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="F57" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="G57">
         <v>6</v>
       </c>
       <c r="H57">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -9083,59 +9259,62 @@
       <c r="N57" t="s">
         <v>94</v>
       </c>
-      <c r="O57">
-        <v>1</v>
+      <c r="O57" t="s">
+        <v>94</v>
       </c>
       <c r="P57">
+        <v>1</v>
+      </c>
+      <c r="Q57">
         <v>4</v>
       </c>
-      <c r="Q57">
-        <v>0</v>
-      </c>
       <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
         <v>100</v>
       </c>
-      <c r="S57">
-        <v>30</v>
-      </c>
       <c r="T57">
-        <v>0</v>
-      </c>
-      <c r="U57" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="V57" t="s">
-        <v>368</v>
-      </c>
-      <c r="W57">
+        <v>480</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="W57" t="s">
+        <v>39</v>
+      </c>
+      <c r="X57">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B58">
-        <v>5003</v>
+        <v>5005</v>
       </c>
       <c r="C58" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D58" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="E58" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F58" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="G58">
         <v>6</v>
       </c>
       <c r="H58">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -9150,256 +9329,268 @@
         <v>0</v>
       </c>
       <c r="M58" t="s">
-        <v>94</v>
+        <v>216</v>
       </c>
       <c r="N58" t="s">
         <v>94</v>
       </c>
-      <c r="O58">
-        <v>1</v>
+      <c r="O58" t="s">
+        <v>94</v>
       </c>
       <c r="P58">
+        <v>1</v>
+      </c>
+      <c r="Q58">
         <v>4</v>
       </c>
-      <c r="Q58">
-        <v>0</v>
-      </c>
       <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
         <v>100</v>
       </c>
-      <c r="S58">
-        <v>480</v>
-      </c>
       <c r="T58">
-        <v>0</v>
-      </c>
-      <c r="U58" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="V58" t="s">
+        <v>30</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="W58" t="s">
         <v>39</v>
       </c>
-      <c r="W58">
-        <v>3</v>
+      <c r="X58">
+        <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B59">
-        <v>5005</v>
+        <v>5006</v>
       </c>
       <c r="C59" t="s">
         <v>313</v>
       </c>
       <c r="D59" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="E59" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="F59" t="s">
-        <v>198</v>
+        <v>328</v>
       </c>
       <c r="G59">
         <v>6</v>
       </c>
       <c r="H59">
+        <v>8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>1</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" t="s">
+        <v>134</v>
+      </c>
+      <c r="N59" t="s">
+        <v>237</v>
+      </c>
+      <c r="O59" t="s">
+        <v>94</v>
+      </c>
+      <c r="P59">
+        <v>1</v>
+      </c>
+      <c r="Q59">
         <v>4</v>
       </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <v>3</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
-      <c r="M59" t="s">
-        <v>217</v>
-      </c>
-      <c r="N59" t="s">
-        <v>94</v>
-      </c>
-      <c r="O59">
-        <v>1</v>
-      </c>
-      <c r="P59">
-        <v>4</v>
-      </c>
-      <c r="Q59">
-        <v>0</v>
-      </c>
       <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
         <v>100</v>
       </c>
-      <c r="S59">
+      <c r="T59">
         <v>30</v>
       </c>
-      <c r="T59">
-        <v>0</v>
-      </c>
-      <c r="U59" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="V59" t="s">
-        <v>39</v>
-      </c>
-      <c r="W59">
-        <v>1</v>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="W59" t="s">
+        <v>94</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60">
+    <row r="60" spans="1:24" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="9">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="9">
         <v>5006</v>
       </c>
-      <c r="C60" t="s">
-        <v>314</v>
-      </c>
-      <c r="D60" t="s">
-        <v>214</v>
-      </c>
-      <c r="E60" t="s">
-        <v>213</v>
-      </c>
-      <c r="F60" t="s">
-        <v>329</v>
-      </c>
-      <c r="G60">
+      <c r="C60" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="G60" s="9">
         <v>6</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="9">
         <v>8</v>
       </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60">
-        <v>1</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60" t="s">
-        <v>135</v>
-      </c>
-      <c r="N60" t="s">
-        <v>238</v>
-      </c>
-      <c r="O60">
-        <v>1</v>
-      </c>
-      <c r="P60">
+      <c r="I60" s="9">
+        <v>0</v>
+      </c>
+      <c r="J60" s="9">
+        <v>0</v>
+      </c>
+      <c r="K60" s="9">
+        <v>1</v>
+      </c>
+      <c r="L60" s="9">
+        <v>0</v>
+      </c>
+      <c r="M60" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="N60" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O60" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="P60" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="9">
         <v>4</v>
       </c>
-      <c r="Q60">
-        <v>0</v>
-      </c>
-      <c r="R60">
+      <c r="R60" s="9">
+        <v>0</v>
+      </c>
+      <c r="S60" s="9">
         <v>100</v>
       </c>
-      <c r="S60">
+      <c r="T60" s="9">
         <v>30</v>
       </c>
-      <c r="T60">
-        <v>0</v>
-      </c>
-      <c r="U60" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="V60" t="s">
-        <v>94</v>
-      </c>
-      <c r="W60">
-        <v>0</v>
+      <c r="U60" s="9">
+        <v>0</v>
+      </c>
+      <c r="V60" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="W60" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="X60" s="9">
+        <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:23" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="9">
+    <row r="61" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B61" s="9">
-        <v>5006</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="D61" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="G61" s="9">
+      <c r="B61">
+        <v>5007</v>
+      </c>
+      <c r="C61" t="s">
+        <v>377</v>
+      </c>
+      <c r="D61" t="s">
+        <v>343</v>
+      </c>
+      <c r="E61" t="s">
+        <v>340</v>
+      </c>
+      <c r="F61" t="s">
+        <v>341</v>
+      </c>
+      <c r="G61">
         <v>6</v>
       </c>
-      <c r="H61" s="9">
+      <c r="H61">
         <v>8</v>
       </c>
-      <c r="I61" s="9">
-        <v>0</v>
-      </c>
-      <c r="J61" s="9">
-        <v>0</v>
-      </c>
-      <c r="K61" s="9">
-        <v>1</v>
-      </c>
-      <c r="L61" s="9">
-        <v>0</v>
-      </c>
-      <c r="M61" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="N61" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="O61" s="9">
-        <v>1</v>
-      </c>
-      <c r="P61" s="9">
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61" t="s">
+        <v>134</v>
+      </c>
+      <c r="N61" t="s">
+        <v>134</v>
+      </c>
+      <c r="O61" t="s">
+        <v>94</v>
+      </c>
+      <c r="P61">
+        <v>1</v>
+      </c>
+      <c r="Q61">
         <v>4</v>
       </c>
-      <c r="Q61" s="9">
-        <v>0</v>
-      </c>
-      <c r="R61" s="9">
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
         <v>100</v>
       </c>
-      <c r="S61" s="9">
+      <c r="T61">
         <v>30</v>
       </c>
-      <c r="T61" s="9">
-        <v>0</v>
-      </c>
-      <c r="U61" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="V61" s="9" t="s">
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="W61" t="s">
         <v>39</v>
       </c>
-      <c r="W61" s="9">
-        <v>3</v>
+      <c r="X61">
+        <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -9408,22 +9599,22 @@
         <v>5007</v>
       </c>
       <c r="C62" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D62" t="s">
+        <v>371</v>
+      </c>
+      <c r="E62" t="s">
         <v>344</v>
       </c>
-      <c r="E62" t="s">
-        <v>341</v>
-      </c>
       <c r="F62" t="s">
-        <v>342</v>
+        <v>384</v>
       </c>
       <c r="G62">
         <v>6</v>
       </c>
       <c r="H62">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -9432,262 +9623,274 @@
         <v>0</v>
       </c>
       <c r="K62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62">
         <v>0</v>
       </c>
       <c r="M62" t="s">
-        <v>135</v>
+        <v>370</v>
       </c>
       <c r="N62" t="s">
-        <v>135</v>
-      </c>
-      <c r="O62">
-        <v>1</v>
+        <v>94</v>
+      </c>
+      <c r="O62" t="s">
+        <v>94</v>
       </c>
       <c r="P62">
+        <v>1</v>
+      </c>
+      <c r="Q62">
         <v>4</v>
       </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
       <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
         <v>100</v>
       </c>
-      <c r="S62">
+      <c r="T62">
         <v>30</v>
       </c>
-      <c r="T62">
-        <v>0</v>
-      </c>
-      <c r="U62" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="V62" t="s">
-        <v>39</v>
-      </c>
-      <c r="W62">
-        <v>1</v>
+      <c r="U62">
+        <v>120</v>
+      </c>
+      <c r="V62" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="W62" t="s">
+        <v>94</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:23" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63">
+    <row r="63" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="4">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B63">
-        <v>5007</v>
-      </c>
-      <c r="C63" t="s">
-        <v>383</v>
-      </c>
-      <c r="D63" t="s">
-        <v>373</v>
-      </c>
-      <c r="E63" t="s">
-        <v>345</v>
-      </c>
-      <c r="F63" t="s">
-        <v>388</v>
-      </c>
-      <c r="G63">
+      <c r="B63" s="4">
+        <v>6001</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G63" s="4">
         <v>6</v>
       </c>
-      <c r="H63">
-        <v>25</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>2</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63" t="s">
-        <v>372</v>
-      </c>
-      <c r="N63" t="s">
-        <v>94</v>
-      </c>
-      <c r="O63">
-        <v>1</v>
-      </c>
-      <c r="P63">
-        <v>4</v>
-      </c>
-      <c r="Q63">
-        <v>0</v>
-      </c>
-      <c r="R63">
+      <c r="H63" s="4">
+        <v>3</v>
+      </c>
+      <c r="I63" s="4">
+        <v>9999</v>
+      </c>
+      <c r="J63" s="4">
+        <v>0</v>
+      </c>
+      <c r="K63" s="4">
+        <v>10</v>
+      </c>
+      <c r="L63" s="4">
+        <v>0</v>
+      </c>
+      <c r="M63" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N63" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O63" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="P63" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="4">
+        <v>5</v>
+      </c>
+      <c r="R63" s="4">
+        <v>0</v>
+      </c>
+      <c r="S63" s="4">
         <v>100</v>
       </c>
-      <c r="S63">
+      <c r="T63" s="4">
         <v>30</v>
       </c>
-      <c r="T63">
-        <v>60</v>
-      </c>
-      <c r="U63" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="V63" t="s">
-        <v>94</v>
-      </c>
-      <c r="W63">
+      <c r="U63" s="4">
+        <v>0</v>
+      </c>
+      <c r="V63" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W63" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X63" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="4">
+    <row r="64" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A64">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B64" s="4">
-        <v>6001</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G64" s="4">
+      <c r="B64">
+        <v>6002</v>
+      </c>
+      <c r="C64" t="s">
+        <v>281</v>
+      </c>
+      <c r="D64" t="s">
+        <v>100</v>
+      </c>
+      <c r="E64" t="s">
+        <v>99</v>
+      </c>
+      <c r="F64" t="s">
+        <v>95</v>
+      </c>
+      <c r="G64">
         <v>6</v>
       </c>
-      <c r="H64" s="4">
+      <c r="H64">
         <v>3</v>
       </c>
-      <c r="I64" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J64" s="4">
-        <v>0</v>
-      </c>
-      <c r="K64" s="4">
-        <v>10</v>
-      </c>
-      <c r="L64" s="4">
-        <v>0</v>
-      </c>
-      <c r="M64" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N64" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O64" s="4">
-        <v>1</v>
-      </c>
-      <c r="P64" s="4">
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
         <v>5</v>
       </c>
-      <c r="Q64" s="4">
-        <v>0</v>
-      </c>
-      <c r="R64" s="4">
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" t="s">
+        <v>94</v>
+      </c>
+      <c r="N64" t="s">
+        <v>94</v>
+      </c>
+      <c r="O64" t="s">
+        <v>94</v>
+      </c>
+      <c r="P64">
+        <v>1</v>
+      </c>
+      <c r="Q64">
+        <v>5</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
         <v>100</v>
       </c>
-      <c r="S64" s="4">
+      <c r="T64">
         <v>30</v>
       </c>
-      <c r="T64" s="4">
-        <v>0</v>
-      </c>
-      <c r="U64" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="V64" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W64" s="4">
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="W64" t="s">
+        <v>94</v>
+      </c>
+      <c r="X64">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65">
+    <row r="65" spans="1:24" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="9">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B65">
-        <v>6002</v>
-      </c>
-      <c r="C65" t="s">
-        <v>282</v>
-      </c>
-      <c r="D65" t="s">
-        <v>101</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="B65" s="9">
+        <v>6008</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="G65" s="9">
+        <v>6</v>
+      </c>
+      <c r="H65" s="9">
+        <v>3</v>
+      </c>
+      <c r="I65" s="9">
+        <v>0</v>
+      </c>
+      <c r="J65" s="9">
+        <v>0</v>
+      </c>
+      <c r="K65" s="9">
+        <v>1</v>
+      </c>
+      <c r="L65" s="9">
+        <v>0</v>
+      </c>
+      <c r="M65" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="N65" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="O65" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="P65" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="9">
+        <v>3</v>
+      </c>
+      <c r="R65" s="9">
+        <v>1</v>
+      </c>
+      <c r="S65" s="9">
+        <v>85</v>
+      </c>
+      <c r="T65" s="9">
+        <v>10</v>
+      </c>
+      <c r="U65" s="9">
+        <v>0</v>
+      </c>
+      <c r="V65" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="W65" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F65" t="s">
-        <v>96</v>
-      </c>
-      <c r="G65">
-        <v>6</v>
-      </c>
-      <c r="H65">
+      <c r="X65" s="9">
         <v>3</v>
       </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>5</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65" t="s">
-        <v>94</v>
-      </c>
-      <c r="N65" t="s">
-        <v>94</v>
-      </c>
-      <c r="O65">
-        <v>1</v>
-      </c>
-      <c r="P65">
-        <v>5</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <v>100</v>
-      </c>
-      <c r="S65">
-        <v>30</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
-      <c r="U65" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="V65" t="s">
-        <v>94</v>
-      </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
     </row>
-    <row r="66" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -9696,16 +9899,16 @@
         <v>6004</v>
       </c>
       <c r="C66" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D66" t="s">
+        <v>260</v>
+      </c>
+      <c r="E66" t="s">
         <v>261</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>262</v>
-      </c>
-      <c r="F66" t="s">
-        <v>263</v>
       </c>
       <c r="G66">
         <v>6</v>
@@ -9726,40 +9929,43 @@
         <v>0</v>
       </c>
       <c r="M66" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N66" t="s">
-        <v>135</v>
-      </c>
-      <c r="O66">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="O66" t="s">
+        <v>94</v>
       </c>
       <c r="P66">
+        <v>1</v>
+      </c>
+      <c r="Q66">
         <v>5</v>
       </c>
-      <c r="Q66">
-        <v>1</v>
-      </c>
       <c r="R66">
+        <v>1</v>
+      </c>
+      <c r="S66">
         <v>100</v>
       </c>
-      <c r="S66">
+      <c r="T66">
         <v>30</v>
       </c>
-      <c r="T66">
-        <v>0</v>
-      </c>
-      <c r="U66" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="V66" t="s">
-        <v>94</v>
-      </c>
-      <c r="W66">
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="W66" t="s">
+        <v>94</v>
+      </c>
+      <c r="X66">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -9768,16 +9974,16 @@
         <v>6005</v>
       </c>
       <c r="C67" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D67" t="s">
+        <v>264</v>
+      </c>
+      <c r="E67" t="s">
         <v>265</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>266</v>
-      </c>
-      <c r="F67" t="s">
-        <v>267</v>
       </c>
       <c r="G67">
         <v>6</v>
@@ -9798,40 +10004,43 @@
         <v>0</v>
       </c>
       <c r="M67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N67" t="s">
-        <v>135</v>
-      </c>
-      <c r="O67">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="O67" t="s">
+        <v>94</v>
       </c>
       <c r="P67">
+        <v>1</v>
+      </c>
+      <c r="Q67">
         <v>5</v>
       </c>
-      <c r="Q67">
-        <v>1</v>
-      </c>
       <c r="R67">
+        <v>1</v>
+      </c>
+      <c r="S67">
         <v>100</v>
       </c>
-      <c r="S67">
+      <c r="T67">
         <v>30</v>
       </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="V67" t="s">
-        <v>94</v>
-      </c>
-      <c r="W67">
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="W67" t="s">
+        <v>94</v>
+      </c>
+      <c r="X67">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -9840,16 +10049,16 @@
         <v>6006</v>
       </c>
       <c r="C68" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D68" t="s">
+        <v>338</v>
+      </c>
+      <c r="E68" t="s">
+        <v>337</v>
+      </c>
+      <c r="F68" t="s">
         <v>339</v>
-      </c>
-      <c r="E68" t="s">
-        <v>338</v>
-      </c>
-      <c r="F68" t="s">
-        <v>340</v>
       </c>
       <c r="G68">
         <v>6</v>
@@ -9870,40 +10079,43 @@
         <v>0</v>
       </c>
       <c r="M68" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="N68" t="s">
         <v>94</v>
       </c>
-      <c r="O68">
-        <v>1</v>
+      <c r="O68" t="s">
+        <v>94</v>
       </c>
       <c r="P68">
+        <v>1</v>
+      </c>
+      <c r="Q68">
         <v>5</v>
       </c>
-      <c r="Q68">
-        <v>1</v>
-      </c>
       <c r="R68">
+        <v>1</v>
+      </c>
+      <c r="S68">
         <v>100</v>
       </c>
-      <c r="S68">
+      <c r="T68">
         <v>30</v>
       </c>
-      <c r="T68">
+      <c r="U68">
         <v>120</v>
       </c>
-      <c r="U68" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="V68" t="s">
-        <v>101</v>
-      </c>
-      <c r="W68">
+      <c r="V68" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="W68" t="s">
+        <v>100</v>
+      </c>
+      <c r="X68">
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:23" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:24" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="4">
         <f t="shared" si="0"/>
         <v>67</v>
@@ -9912,16 +10124,16 @@
         <v>6007</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E69" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>351</v>
       </c>
       <c r="G69" s="4">
         <v>6</v>
@@ -9945,37 +10157,40 @@
         <v>94</v>
       </c>
       <c r="N69" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="O69" s="4">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O69" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P69" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="4">
         <v>5</v>
       </c>
-      <c r="Q69" s="4">
-        <v>1</v>
-      </c>
       <c r="R69" s="4">
+        <v>1</v>
+      </c>
+      <c r="S69" s="4">
         <v>50</v>
       </c>
-      <c r="S69" s="4">
+      <c r="T69" s="4">
         <v>30</v>
       </c>
-      <c r="T69" s="4">
-        <v>0</v>
-      </c>
-      <c r="U69" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="V69" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W69" s="4">
+      <c r="U69" s="4">
+        <v>0</v>
+      </c>
+      <c r="V69" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="W69" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X69" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A70" s="4">
         <f t="shared" si="0"/>
         <v>68</v>
@@ -9984,7 +10199,7 @@
         <v>6003</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>42</v>
@@ -10019,35 +10234,38 @@
       <c r="N70" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O70" s="4">
-        <v>1</v>
+      <c r="O70" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P70" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="4">
         <v>5</v>
       </c>
-      <c r="Q70" s="4">
-        <v>0</v>
-      </c>
       <c r="R70" s="4">
+        <v>0</v>
+      </c>
+      <c r="S70" s="4">
         <v>100</v>
       </c>
-      <c r="S70" s="4">
+      <c r="T70" s="4">
         <v>30</v>
       </c>
-      <c r="T70" s="4">
-        <v>0</v>
-      </c>
-      <c r="U70" s="4" t="s">
-        <v>165</v>
+      <c r="U70" s="4">
+        <v>0</v>
       </c>
       <c r="V70" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W70" s="4">
+        <v>164</v>
+      </c>
+      <c r="W70" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X70" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:23" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A71" s="5">
         <f t="shared" si="0"/>
         <v>69</v>
@@ -10091,35 +10309,38 @@
       <c r="N71" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="O71" s="5">
-        <v>1</v>
+      <c r="O71" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="P71" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="5">
         <v>6</v>
       </c>
-      <c r="Q71" s="2">
-        <v>0</v>
-      </c>
-      <c r="R71" s="5">
+      <c r="R71" s="2">
+        <v>0</v>
+      </c>
+      <c r="S71" s="5">
         <v>100</v>
       </c>
-      <c r="S71" s="5">
+      <c r="T71" s="5">
         <v>30</v>
       </c>
-      <c r="T71" s="5">
-        <v>0</v>
-      </c>
-      <c r="U71" s="5" t="s">
+      <c r="U71" s="5">
+        <v>0</v>
+      </c>
+      <c r="V71" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="V71" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="W71" s="5">
+      <c r="W71" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="X71" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:23" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:24" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="5">
         <f t="shared" si="0"/>
         <v>70</v>
@@ -10163,35 +10384,38 @@
       <c r="N72" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="O72" s="5">
-        <v>1</v>
+      <c r="O72" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="P72" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="5">
         <v>6</v>
       </c>
-      <c r="Q72" s="2">
-        <v>0</v>
-      </c>
-      <c r="R72" s="5">
+      <c r="R72" s="2">
+        <v>0</v>
+      </c>
+      <c r="S72" s="5">
         <v>100</v>
       </c>
-      <c r="S72" s="5">
+      <c r="T72" s="5">
         <v>30</v>
       </c>
-      <c r="T72" s="5">
-        <v>0</v>
-      </c>
-      <c r="U72" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="V72" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="W72" s="5">
+      <c r="U72" s="5">
+        <v>0</v>
+      </c>
+      <c r="V72" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="W72" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="X72" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A73" s="4">
         <f t="shared" si="0"/>
         <v>71</v>
@@ -10235,35 +10459,38 @@
       <c r="N73" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O73" s="4">
-        <v>1</v>
+      <c r="O73" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P73" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="4">
         <v>7</v>
       </c>
-      <c r="Q73" s="4">
-        <v>0</v>
-      </c>
       <c r="R73" s="4">
+        <v>0</v>
+      </c>
+      <c r="S73" s="4">
         <v>100</v>
       </c>
-      <c r="S73" s="4">
+      <c r="T73" s="4">
         <v>30</v>
       </c>
-      <c r="T73" s="4">
-        <v>0</v>
-      </c>
-      <c r="U73" s="4" t="s">
+      <c r="U73" s="4">
+        <v>0</v>
+      </c>
+      <c r="V73" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="V73" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W73" s="4">
+      <c r="W73" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X73" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:23" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A74" s="4">
         <f t="shared" si="0"/>
         <v>72</v>
@@ -10307,35 +10534,38 @@
       <c r="N74" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O74" s="4">
-        <v>1</v>
+      <c r="O74" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P74" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="4">
         <v>7</v>
       </c>
-      <c r="Q74" s="4">
-        <v>0</v>
-      </c>
       <c r="R74" s="4">
+        <v>0</v>
+      </c>
+      <c r="S74" s="4">
         <v>100</v>
       </c>
-      <c r="S74" s="4">
+      <c r="T74" s="4">
         <v>30</v>
       </c>
-      <c r="T74" s="4">
-        <v>0</v>
-      </c>
-      <c r="U74" s="4" t="s">
+      <c r="U74" s="4">
+        <v>0</v>
+      </c>
+      <c r="V74" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="V74" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W74" s="4">
+      <c r="W74" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X74" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:23" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:24" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="2">
         <f t="shared" si="0"/>
         <v>73</v>
@@ -10374,40 +10604,43 @@
         <v>0</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="O75" s="2">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="P75" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="2">
         <v>8</v>
       </c>
-      <c r="Q75" s="2">
-        <v>0</v>
-      </c>
       <c r="R75" s="2">
+        <v>0</v>
+      </c>
+      <c r="S75" s="2">
         <v>100</v>
       </c>
-      <c r="S75" s="2">
+      <c r="T75" s="2">
         <v>120</v>
       </c>
-      <c r="T75" s="2">
-        <v>0</v>
-      </c>
-      <c r="U75" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="V75" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="W75" s="2">
+      <c r="U75" s="2">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="W75" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="X75" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76">
         <f t="shared" si="0"/>
         <v>74</v>
@@ -10416,16 +10649,16 @@
         <v>9005</v>
       </c>
       <c r="C76" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D76" t="s">
+        <v>258</v>
+      </c>
+      <c r="E76" t="s">
+        <v>277</v>
+      </c>
+      <c r="F76" t="s">
         <v>259</v>
-      </c>
-      <c r="E76" t="s">
-        <v>278</v>
-      </c>
-      <c r="F76" t="s">
-        <v>260</v>
       </c>
       <c r="G76">
         <v>2</v>
@@ -10446,40 +10679,43 @@
         <v>0</v>
       </c>
       <c r="M76" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N76" t="s">
-        <v>135</v>
-      </c>
-      <c r="O76">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="O76" t="s">
+        <v>94</v>
       </c>
       <c r="P76">
+        <v>1</v>
+      </c>
+      <c r="Q76">
         <v>8</v>
       </c>
-      <c r="Q76">
-        <v>1</v>
-      </c>
       <c r="R76">
+        <v>1</v>
+      </c>
+      <c r="S76">
         <v>100</v>
       </c>
-      <c r="S76">
+      <c r="T76">
         <v>30</v>
       </c>
-      <c r="T76">
-        <v>0</v>
-      </c>
-      <c r="U76" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="V76" t="s">
-        <v>94</v>
-      </c>
-      <c r="W76">
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="V76" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="W76" t="s">
+        <v>94</v>
+      </c>
+      <c r="X76">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:23" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:24" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="4">
         <f t="shared" si="0"/>
         <v>75</v>
@@ -10523,35 +10759,38 @@
       <c r="N77" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O77" s="4">
-        <v>1</v>
+      <c r="O77" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P77" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="4">
         <v>8</v>
       </c>
-      <c r="Q77" s="4">
-        <v>0</v>
-      </c>
       <c r="R77" s="4">
+        <v>0</v>
+      </c>
+      <c r="S77" s="4">
         <v>100</v>
       </c>
-      <c r="S77" s="4">
+      <c r="T77" s="4">
         <v>30</v>
       </c>
-      <c r="T77" s="4">
-        <v>0</v>
-      </c>
-      <c r="U77" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="V77" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W77" s="4">
+      <c r="U77" s="4">
+        <v>0</v>
+      </c>
+      <c r="V77" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="W77" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X77" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:23" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:24" s="4" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="4">
         <f t="shared" si="0"/>
         <v>76</v>
@@ -10563,13 +10802,13 @@
         <v>68</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E78" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F78" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="G78" s="4">
         <v>2</v>
@@ -10590,40 +10829,43 @@
         <v>0</v>
       </c>
       <c r="M78" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N78" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="O78" s="4">
-        <v>1</v>
+      <c r="O78" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="P78" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="4">
         <v>8</v>
       </c>
-      <c r="Q78" s="4">
-        <v>0</v>
-      </c>
       <c r="R78" s="4">
+        <v>0</v>
+      </c>
+      <c r="S78" s="4">
         <v>100</v>
       </c>
-      <c r="S78" s="4">
+      <c r="T78" s="4">
         <v>60</v>
       </c>
-      <c r="T78" s="4">
-        <v>0</v>
-      </c>
-      <c r="U78" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="V78" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="W78" s="4">
+      <c r="U78" s="4">
+        <v>0</v>
+      </c>
+      <c r="V78" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="W78" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X78" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79">
         <f t="shared" si="0"/>
         <v>77</v>
@@ -10632,13 +10874,13 @@
         <v>9003</v>
       </c>
       <c r="C79" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F79" t="s">
         <v>91</v>
@@ -10667,31 +10909,34 @@
       <c r="N79" t="s">
         <v>94</v>
       </c>
-      <c r="O79">
-        <v>1</v>
+      <c r="O79" t="s">
+        <v>94</v>
       </c>
       <c r="P79">
+        <v>1</v>
+      </c>
+      <c r="Q79">
         <v>8</v>
       </c>
-      <c r="Q79">
-        <v>0</v>
-      </c>
       <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
         <v>100</v>
       </c>
-      <c r="S79">
+      <c r="T79">
         <v>30</v>
       </c>
-      <c r="T79">
-        <v>0</v>
-      </c>
-      <c r="U79" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="V79" t="s">
-        <v>94</v>
-      </c>
-      <c r="W79">
+      <c r="U79">
+        <v>0</v>
+      </c>
+      <c r="V79" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="W79" t="s">
+        <v>94</v>
+      </c>
+      <c r="X79">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1554398A-9DB1-45E3-A376-EE4865747574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6D813F-79DD-4223-9E4A-3E71BFCAD65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="1530" yWindow="855" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3818,56 +3818,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>生地をきれいに混ぜる技術を磨く。
-クレープ生地やケーキ生地など生地系の品質を、少しだけ底上げする。
-また、スポンジケーキを焼くときの時間を短縮する。
-LV3以上だと、出来上がる生地の個数が+1。
-LV5で+2。</t>
-    <rPh sb="22" eb="24">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ヒンシツ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>スコ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ソコア</t>
-    </rPh>
-    <rPh sb="63" eb="64">
-      <t>ヤ</t>
-    </rPh>
-    <rPh sb="68" eb="70">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="71" eb="73">
-      <t>タンシュク</t>
-    </rPh>
-    <rPh sb="81" eb="83">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="86" eb="89">
-      <t>デキア</t>
-    </rPh>
-    <rPh sb="91" eb="93">
-      <t>キジ</t>
-    </rPh>
-    <rPh sb="94" eb="96">
-      <t>コスウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>雨の力で、ストロベリーやジュースに虹色を加える。</t>
     <rPh sb="0" eb="1">
       <t>アメ</t>
@@ -4114,10 +4064,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ナイト・バロン</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>お菓子に大人っぽさの演出効果を加える。</t>
     <rPh sb="1" eb="3">
       <t>カシ</t>
@@ -4269,17 +4215,6 @@
   </si>
   <si>
     <t>シュガーにかけると、シュガーの性質を変える</t>
-    <rPh sb="15" eb="17">
-      <t>セイシツ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>シュガーにかけると、シュガーの性質を変える。
-サファイアシュガーにのみかけることができる。</t>
     <rPh sb="15" eb="17">
       <t>セイシツ</t>
     </rPh>
@@ -4564,6 +4499,86 @@
   </si>
   <si>
     <t>skill_CompSelect</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シュガーにかけると、シュガーの性質を変える。
+サファイアシュガーにのみかけることができる。
+甘さを減らし、見た目をほんの少しアップする。</t>
+    <rPh sb="15" eb="17">
+      <t>セイシツ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>スコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ナイトバロン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生地をきれいに混ぜる技術を磨く。
+クレープ生地やケーキ生地など生地系の品質を、少しだけ底上げする。
+また、スポンジケーキを焼くときの時間を短縮する。
+LV5習得で、出来上がる生地の個数が+1。</t>
+    <rPh sb="22" eb="24">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ソコア</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>タンシュク</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>シュウトク</t>
+    </rPh>
+    <rPh sb="85" eb="88">
+      <t>デキア</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>コスウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -5054,13 +5069,13 @@
         <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>236</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>8</v>
@@ -5078,7 +5093,7 @@
         <v>92</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>53</v>
@@ -5474,16 +5489,16 @@
         <v>1012</v>
       </c>
       <c r="C7" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -5531,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="8" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="W7" t="s">
         <v>54</v>
@@ -5849,16 +5864,16 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E12" t="s">
-        <v>345</v>
+        <v>389</v>
       </c>
       <c r="F12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G12">
         <v>6</v>
@@ -5906,7 +5921,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="8" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="W12" t="s">
         <v>162</v>
@@ -6206,7 +6221,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="W16" t="s">
         <v>94</v>
@@ -6674,7 +6689,7 @@
         <v>3006</v>
       </c>
       <c r="C23" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D23" t="s">
         <v>156</v>
@@ -7049,16 +7064,16 @@
         <v>3009</v>
       </c>
       <c r="C28" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D28" t="s">
+        <v>334</v>
+      </c>
+      <c r="E28" t="s">
+        <v>333</v>
+      </c>
+      <c r="F28" t="s">
         <v>335</v>
-      </c>
-      <c r="E28" t="s">
-        <v>334</v>
-      </c>
-      <c r="F28" t="s">
-        <v>336</v>
       </c>
       <c r="G28">
         <v>4</v>
@@ -7079,7 +7094,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N28" t="s">
         <v>94</v>
@@ -7106,7 +7121,7 @@
         <v>120</v>
       </c>
       <c r="V28" s="8" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="W28" t="s">
         <v>94</v>
@@ -7124,16 +7139,16 @@
         <v>3010</v>
       </c>
       <c r="C29" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D29" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E29" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F29" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G29">
         <v>4</v>
@@ -7181,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="8" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="W29" t="s">
         <v>94</v>
@@ -7631,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="8" t="s">
-        <v>327</v>
+        <v>390</v>
       </c>
       <c r="W35" t="s">
         <v>94</v>
@@ -8255,7 +8270,7 @@
         <v>27</v>
       </c>
       <c r="E44" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F44" t="s">
         <v>220</v>
@@ -8999,16 +9014,16 @@
         <v>5007</v>
       </c>
       <c r="C54" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D54" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E54" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F54" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G54">
         <v>6</v>
@@ -9056,7 +9071,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="8" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="W54" t="s">
         <v>94</v>
@@ -9083,7 +9098,7 @@
         <v>38</v>
       </c>
       <c r="F55" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G55">
         <v>6</v>
@@ -9131,7 +9146,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="W55" t="s">
         <v>272</v>
@@ -9209,7 +9224,7 @@
         <v>235</v>
       </c>
       <c r="W56" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="X56">
         <v>3</v>
@@ -9383,7 +9398,7 @@
         <v>212</v>
       </c>
       <c r="F59" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G59">
         <v>6</v>
@@ -9431,7 +9446,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="W59" t="s">
         <v>94</v>
@@ -9452,13 +9467,13 @@
         <v>313</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E60" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="F60" s="9" t="s">
         <v>362</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>364</v>
       </c>
       <c r="G60" s="9">
         <v>6</v>
@@ -9485,7 +9500,7 @@
         <v>237</v>
       </c>
       <c r="O60" s="9" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="P60" s="9">
         <v>1</v>
@@ -9506,7 +9521,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="10" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="W60" s="9" t="s">
         <v>39</v>
@@ -9524,16 +9539,16 @@
         <v>5007</v>
       </c>
       <c r="C61" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D61" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E61" t="s">
+        <v>339</v>
+      </c>
+      <c r="F61" t="s">
         <v>340</v>
-      </c>
-      <c r="F61" t="s">
-        <v>341</v>
       </c>
       <c r="G61">
         <v>6</v>
@@ -9581,7 +9596,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="W61" t="s">
         <v>39</v>
@@ -9599,16 +9614,16 @@
         <v>5007</v>
       </c>
       <c r="C62" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D62" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E62" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F62" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G62">
         <v>6</v>
@@ -9629,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N62" t="s">
         <v>94</v>
@@ -9656,7 +9671,7 @@
         <v>120</v>
       </c>
       <c r="V62" s="8" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="W62" t="s">
         <v>94</v>
@@ -9827,13 +9842,13 @@
         <v>288</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G65" s="9">
         <v>6</v>
@@ -9860,7 +9875,7 @@
         <v>237</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="P65" s="9">
         <v>1</v>
@@ -9881,7 +9896,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="W65" s="9" t="s">
         <v>100</v>
@@ -10049,16 +10064,16 @@
         <v>6006</v>
       </c>
       <c r="C68" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D68" t="s">
+        <v>337</v>
+      </c>
+      <c r="E68" t="s">
+        <v>336</v>
+      </c>
+      <c r="F68" t="s">
         <v>338</v>
-      </c>
-      <c r="E68" t="s">
-        <v>337</v>
-      </c>
-      <c r="F68" t="s">
-        <v>339</v>
       </c>
       <c r="G68">
         <v>6</v>
@@ -10079,7 +10094,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N68" t="s">
         <v>94</v>
@@ -10106,7 +10121,7 @@
         <v>120</v>
       </c>
       <c r="V68" s="8" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="W68" t="s">
         <v>100</v>
@@ -10127,13 +10142,13 @@
         <v>278</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G69" s="4">
         <v>6</v>
@@ -10181,7 +10196,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="6" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="W69" s="4" t="s">
         <v>94</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6D813F-79DD-4223-9E4A-3E71BFCAD65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87BF039-A9FF-45CC-85AC-AADBA21ABACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="855" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2580" yWindow="1395" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87BF039-A9FF-45CC-85AC-AADBA21ABACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E82B52-AA60-41D0-A492-3CAF35372A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="1395" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="660" yWindow="525" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5852,7 +5852,7 @@
         <v>54</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.4">

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E82B52-AA60-41D0-A492-3CAF35372A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F15265-ECA3-4C8F-A465-7DC74E174DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="525" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="915" yWindow="390" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -9881,7 +9881,7 @@
         <v>1</v>
       </c>
       <c r="Q65" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R65" s="9">
         <v>1</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F15265-ECA3-4C8F-A465-7DC74E174DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B801842B-500E-4447-9836-775A4618BDA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="915" yWindow="390" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
@@ -4648,7 +4648,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -9488,7 +9488,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60" s="9">
         <v>0</v>
@@ -9512,10 +9512,10 @@
         <v>0</v>
       </c>
       <c r="S60" s="9">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="T60" s="9">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="U60" s="9">
         <v>0</v>
@@ -9863,7 +9863,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="9">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B801842B-500E-4447-9836-775A4618BDA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45EBD3A-D694-438F-9C47-E2E2C5380029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="390" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2460" yWindow="660" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45EBD3A-D694-438F-9C47-E2E2C5380029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6BDA08-F0DE-4CEA-B7EF-4DF1D515D6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="660" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2115" yWindow="1170" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="393">
   <si>
     <t>file_name</t>
     <phoneticPr fontId="2"/>
@@ -4579,6 +4579,14 @@
     <rPh sb="93" eb="95">
       <t>コスウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Lightning_Grape</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skicon_Dreamy_Sapphire</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4615,7 +4623,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4643,12 +4651,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4693,10 +4695,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9464,7 +9466,7 @@
         <v>5006</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>313</v>
+        <v>392</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>361</v>
@@ -9839,7 +9841,7 @@
         <v>6008</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>288</v>
+        <v>391</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>359</v>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6BDA08-F0DE-4CEA-B7EF-4DF1D515D6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCB61DC-F38E-4669-B19F-AFF0A3845B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="1170" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4502,33 +4502,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>シュガーにかけると、シュガーの性質を変える。
-サファイアシュガーにのみかけることができる。
-甘さを減らし、見た目をほんの少しアップする。</t>
-    <rPh sb="15" eb="17">
-      <t>セイシツ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>アマ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>ヘ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>スコ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ナイトバロン</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -4587,6 +4560,34 @@
   </si>
   <si>
     <t>skicon_Dreamy_Sapphire</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>シュガーにかけると、シュガーの性質を変える。
+甘さを減らし、見た目をほんの少しアップする。
+Lv1: サファイアシュガー
+Lv2: すべてのシュガー</t>
+    <rPh sb="15" eb="17">
+      <t>セイシツ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ヘ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>スコ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4669,7 +4670,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4693,12 +4694,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5872,7 +5867,7 @@
         <v>345</v>
       </c>
       <c r="E12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F12" t="s">
         <v>344</v>
@@ -7648,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="W35" t="s">
         <v>94</v>
@@ -9457,78 +9452,78 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="9" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="9">
+    <row r="60" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60">
         <v>5006</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" t="s">
+        <v>391</v>
+      </c>
+      <c r="D60" t="s">
+        <v>361</v>
+      </c>
+      <c r="E60" t="s">
+        <v>360</v>
+      </c>
+      <c r="F60" t="s">
+        <v>362</v>
+      </c>
+      <c r="G60">
+        <v>6</v>
+      </c>
+      <c r="H60">
+        <v>8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>2</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" t="s">
+        <v>246</v>
+      </c>
+      <c r="N60" t="s">
+        <v>237</v>
+      </c>
+      <c r="O60" t="s">
+        <v>386</v>
+      </c>
+      <c r="P60">
+        <v>1</v>
+      </c>
+      <c r="Q60">
+        <v>4</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>85</v>
+      </c>
+      <c r="T60">
+        <v>10</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="D60" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="G60" s="9">
-        <v>6</v>
-      </c>
-      <c r="H60" s="9">
-        <v>8</v>
-      </c>
-      <c r="I60" s="9">
-        <v>0</v>
-      </c>
-      <c r="J60" s="9">
-        <v>0</v>
-      </c>
-      <c r="K60" s="9">
-        <v>2</v>
-      </c>
-      <c r="L60" s="9">
-        <v>0</v>
-      </c>
-      <c r="M60" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="N60" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="O60" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="P60" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q60" s="9">
-        <v>4</v>
-      </c>
-      <c r="R60" s="9">
-        <v>0</v>
-      </c>
-      <c r="S60" s="9">
-        <v>85</v>
-      </c>
-      <c r="T60" s="9">
-        <v>10</v>
-      </c>
-      <c r="U60" s="9">
-        <v>0</v>
-      </c>
-      <c r="V60" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="W60" s="9" t="s">
+      <c r="W60" t="s">
         <v>39</v>
       </c>
-      <c r="X60" s="9">
+      <c r="X60">
         <v>3</v>
       </c>
     </row>
@@ -9832,78 +9827,78 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:24" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="9">
+    <row r="65" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65">
         <v>6008</v>
       </c>
-      <c r="C65" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="D65" s="9" t="s">
+      <c r="C65" t="s">
+        <v>390</v>
+      </c>
+      <c r="D65" t="s">
         <v>359</v>
       </c>
-      <c r="E65" s="9" t="s">
+      <c r="E65" t="s">
         <v>357</v>
       </c>
-      <c r="F65" s="9" t="s">
+      <c r="F65" t="s">
         <v>358</v>
       </c>
-      <c r="G65" s="9">
+      <c r="G65">
         <v>6</v>
       </c>
-      <c r="H65" s="9">
+      <c r="H65">
         <v>3</v>
       </c>
-      <c r="I65" s="9">
-        <v>0</v>
-      </c>
-      <c r="J65" s="9">
-        <v>0</v>
-      </c>
-      <c r="K65" s="9">
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
         <v>2</v>
       </c>
-      <c r="L65" s="9">
-        <v>0</v>
-      </c>
-      <c r="M65" s="9" t="s">
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65" t="s">
         <v>246</v>
       </c>
-      <c r="N65" s="9" t="s">
+      <c r="N65" t="s">
         <v>237</v>
       </c>
-      <c r="O65" s="9" t="s">
+      <c r="O65" t="s">
         <v>386</v>
       </c>
-      <c r="P65" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="9">
+      <c r="P65">
+        <v>1</v>
+      </c>
+      <c r="Q65">
         <v>5</v>
       </c>
-      <c r="R65" s="9">
-        <v>1</v>
-      </c>
-      <c r="S65" s="9">
+      <c r="R65">
+        <v>1</v>
+      </c>
+      <c r="S65">
         <v>85</v>
       </c>
-      <c r="T65" s="9">
+      <c r="T65">
         <v>10</v>
       </c>
-      <c r="U65" s="9">
-        <v>0</v>
-      </c>
-      <c r="V65" s="10" t="s">
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="W65" s="9" t="s">
+      <c r="W65" t="s">
         <v>100</v>
       </c>
-      <c r="X65" s="9">
+      <c r="X65">
         <v>3</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_magicSkillListDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCB61DC-F38E-4669-B19F-AFF0A3845B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A3F83A-0DF3-439B-BDFE-9BC3EE0D5891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="2310" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2067,63 +2067,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>様々な物体を凍らせる
-ゼリー凍る。
-砂糖水とジュース　アイスキャンデーに。
-お花　フリーズフラワー　トッピングに使える。
-くだもの　冷凍フルーツを作れる
-クレープ　冷凍クレープの自販機
-LV1　アイスクリームの水溶液
-LV2　みず・ミルク・液体チョコ系
-LV3　くだもの
-LV4　お花
-LV5　おかし全般
-LVに応じて凍らせられる素材が増えていく。
-派生：
-LV2で、ジェラートフリーズ習得可
-※ただし、本が必要。</t>
-    <rPh sb="0" eb="2">
-      <t>サマザマ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ブッタイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>コオ</t>
-    </rPh>
-    <rPh sb="83" eb="85">
-      <t>レイトウ</t>
-    </rPh>
-    <rPh sb="90" eb="93">
-      <t>ジハンキ</t>
-    </rPh>
-    <rPh sb="122" eb="124">
-      <t>エキタイ</t>
-    </rPh>
-    <rPh sb="158" eb="159">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="161" eb="162">
-      <t>コオ</t>
-    </rPh>
-    <rPh sb="167" eb="169">
-      <t>ソザイ</t>
-    </rPh>
-    <rPh sb="170" eb="171">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="178" eb="180">
-      <t>ハセイ</t>
-    </rPh>
-    <rPh sb="205" eb="206">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="207" eb="209">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>アロマの泡をお菓子の周りに浮かせる</t>
     <rPh sb="4" eb="5">
       <t>アワ</t>
@@ -3907,50 +3850,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>アイス水溶液に魔法をかけながら混ぜて、アイスクリーム制作時の成功率アップする。
-また、フリージング使用時の制作時間も短縮する。
-習得するだけでOK。
-LVに応じて、ほんのわずかになめらかさを出す。
-LV1: 成功率+2, 時間短縮+5%
-LV2: 成功率+4, 時間短縮+10%
-LV3: 成功率+6, 時間短縮+15%
-LV4: 成功率+8, 時間短縮+20%
-LV5: 成功率+10, 時間短縮+25%
-LV6: 成功率+12, 時間短縮+30%
-LV7: 成功率+14, 時間短縮+35%
-LV8: 成功率+16, 時間短縮+40%
-LV9: 成功率+18, 時間短縮+45%
-LV10: 成功率+20, 時間短縮+50%</t>
-    <rPh sb="26" eb="29">
-      <t>セイサクジ</t>
-    </rPh>
-    <rPh sb="49" eb="52">
-      <t>シヨウジ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>シュウトク</t>
-    </rPh>
-    <rPh sb="79" eb="80">
-      <t>オウ</t>
-    </rPh>
-    <rPh sb="96" eb="97">
-      <t>ダ</t>
-    </rPh>
-    <rPh sb="106" eb="109">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="113" eb="115">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>タンシュク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ラトリア</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -4587,6 +4486,99 @@
     </rPh>
     <rPh sb="38" eb="39">
       <t>スコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>様々な物体を凍らせる
+ゼリー凍る。
+砂糖水とジュース　アイスキャンデーに。
+お花　フリーズフラワー　トッピングに使える。
+くだもの　冷凍フルーツを作れる
+クレープ　冷凍クレープの自販機
+LV1　アイスクリームの水溶液・液体チョコ系
+LV2　みず・ミルク
+LV3　くだもの
+LV4　お花
+LV5　おかし全般
+LVに応じて凍らせられる素材が増えていく。
+派生：
+LV2で、ジェラートフリーズ習得可
+※ただし、本が必要。</t>
+    <rPh sb="0" eb="2">
+      <t>サマザマ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ブッタイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コオ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>レイトウ</t>
+    </rPh>
+    <rPh sb="90" eb="93">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="158" eb="159">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="161" eb="162">
+      <t>コオ</t>
+    </rPh>
+    <rPh sb="167" eb="169">
+      <t>ソザイ</t>
+    </rPh>
+    <rPh sb="170" eb="171">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="178" eb="180">
+      <t>ハセイ</t>
+    </rPh>
+    <rPh sb="205" eb="206">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="207" eb="209">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アイス水溶液に魔法をかけながら混ぜて、アイスクリーム制作時の成功率アップする。
+また、フリージング使用時の制作時間も短縮する。
+習得するだけでOK。
+LVに応じて、ほんのわずかになめらかさを出す。
+LV1: 成功率+4, 時間短縮+10%
+LV2: 成功率+8, 時間短縮+20%
+LV3: 成功率+12, 時間短縮+30%
+LV4: 成功率+16, 時間短縮+40%
+LV5: 成功率+20, 時間短縮+50%</t>
+    <rPh sb="26" eb="29">
+      <t>セイサクジ</t>
+    </rPh>
+    <rPh sb="49" eb="52">
+      <t>シヨウジ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>シュウトク</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="106" eb="109">
+      <t>セイコウリツ</t>
+    </rPh>
+    <rPh sb="113" eb="115">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>タンシュク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4670,16 +4662,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
@@ -4694,6 +4683,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5066,13 +5061,13 @@
         <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>8</v>
@@ -5081,7 +5076,7 @@
         <v>9</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>10</v>
@@ -5090,7 +5085,7 @@
         <v>92</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>53</v>
@@ -5102,78 +5097,78 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="3">
         <f t="shared" ref="A2:A79" si="0">ROW()-2</f>
         <v>0</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>1001</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>6</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="3">
         <v>3</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="3">
         <v>9999</v>
       </c>
-      <c r="J2" s="4">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4">
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3">
         <v>5</v>
       </c>
-      <c r="L2" s="4">
-        <v>0</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P2" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="4">
+      <c r="L2" s="3">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P2" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="3">
         <v>9</v>
       </c>
-      <c r="R2" s="4">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4">
+      <c r="R2" s="3">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3">
         <v>100</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="3">
         <v>30</v>
       </c>
-      <c r="U2" s="4">
-        <v>0</v>
-      </c>
-      <c r="V2" s="6" t="s">
+      <c r="U2" s="3">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="W2" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X2" s="4">
+      <c r="W2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X2" s="3">
         <v>0</v>
       </c>
     </row>
@@ -5242,8 +5237,8 @@
       <c r="U3">
         <v>0</v>
       </c>
-      <c r="V3" s="8" t="s">
-        <v>234</v>
+      <c r="V3" s="7" t="s">
+        <v>233</v>
       </c>
       <c r="W3" t="s">
         <v>94</v>
@@ -5252,78 +5247,78 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:24" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>1005</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>6</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <v>3</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="3">
         <v>9999</v>
       </c>
-      <c r="J4" s="4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4">
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
         <v>5</v>
       </c>
-      <c r="L4" s="4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P4" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="4">
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P4" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="3">
         <v>9</v>
       </c>
-      <c r="R4" s="4">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4">
+      <c r="R4" s="3">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3">
         <v>100</v>
       </c>
-      <c r="T4" s="4">
+      <c r="T4" s="3">
         <v>30</v>
       </c>
-      <c r="U4" s="4">
-        <v>0</v>
-      </c>
-      <c r="V4" s="6" t="s">
+      <c r="U4" s="3">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="W4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X4" s="4">
+      <c r="W4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X4" s="3">
         <v>0</v>
       </c>
     </row>
@@ -5336,7 +5331,7 @@
         <v>1010</v>
       </c>
       <c r="C5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D5" t="s">
         <v>162</v>
@@ -5392,8 +5387,8 @@
       <c r="U5">
         <v>0</v>
       </c>
-      <c r="V5" s="8" t="s">
-        <v>245</v>
+      <c r="V5" s="7" t="s">
+        <v>244</v>
       </c>
       <c r="W5" t="s">
         <v>94</v>
@@ -5411,7 +5406,7 @@
         <v>1009</v>
       </c>
       <c r="C6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D6" t="s">
         <v>111</v>
@@ -5426,7 +5421,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -5467,14 +5462,14 @@
       <c r="U6">
         <v>0</v>
       </c>
-      <c r="V6" s="8" t="s">
-        <v>325</v>
+      <c r="V6" s="7" t="s">
+        <v>324</v>
       </c>
       <c r="W6" t="s">
         <v>54</v>
       </c>
       <c r="X6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -5486,22 +5481,22 @@
         <v>1012</v>
       </c>
       <c r="C7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G7">
         <v>6</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5516,10 +5511,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O7" t="s">
         <v>94</v>
@@ -5534,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="T7">
         <v>30</v>
@@ -5542,14 +5537,14 @@
       <c r="U7">
         <v>0</v>
       </c>
-      <c r="V7" s="8" t="s">
-        <v>355</v>
+      <c r="V7" s="7" t="s">
+        <v>353</v>
       </c>
       <c r="W7" t="s">
         <v>54</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.4">
@@ -5561,7 +5556,7 @@
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D8" t="s">
         <v>58</v>
@@ -5617,7 +5612,7 @@
       <c r="U8">
         <v>0</v>
       </c>
-      <c r="V8" s="8" t="s">
+      <c r="V8" s="7" t="s">
         <v>149</v>
       </c>
       <c r="W8" t="s">
@@ -5669,7 +5664,7 @@
         <v>94</v>
       </c>
       <c r="N9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O9" t="s">
         <v>94</v>
@@ -5692,8 +5687,8 @@
       <c r="U9">
         <v>0</v>
       </c>
-      <c r="V9" s="8" t="s">
-        <v>315</v>
+      <c r="V9" s="7" t="s">
+        <v>314</v>
       </c>
       <c r="W9" t="s">
         <v>162</v>
@@ -5711,7 +5706,7 @@
         <v>1008</v>
       </c>
       <c r="C10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D10" t="s">
         <v>82</v>
@@ -5767,8 +5762,8 @@
       <c r="U10">
         <v>0</v>
       </c>
-      <c r="V10" s="8" t="s">
-        <v>269</v>
+      <c r="V10" s="7" t="s">
+        <v>268</v>
       </c>
       <c r="W10" t="s">
         <v>80</v>
@@ -5786,16 +5781,16 @@
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E11" t="s">
         <v>221</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>222</v>
-      </c>
-      <c r="F11" t="s">
-        <v>223</v>
       </c>
       <c r="G11">
         <v>6</v>
@@ -5842,14 +5837,14 @@
       <c r="U11">
         <v>0</v>
       </c>
-      <c r="V11" s="8" t="s">
-        <v>275</v>
+      <c r="V11" s="7" t="s">
+        <v>274</v>
       </c>
       <c r="W11" t="s">
         <v>54</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.4">
@@ -5861,16 +5856,16 @@
         <v>1011</v>
       </c>
       <c r="C12" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E12" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G12">
         <v>6</v>
@@ -5917,14 +5912,14 @@
       <c r="U12">
         <v>0</v>
       </c>
-      <c r="V12" s="8" t="s">
-        <v>346</v>
+      <c r="V12" s="7" t="s">
+        <v>344</v>
       </c>
       <c r="W12" t="s">
         <v>162</v>
       </c>
       <c r="X12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -5992,7 +5987,7 @@
       <c r="U13">
         <v>0</v>
       </c>
-      <c r="V13" s="8" t="s">
+      <c r="V13" s="7" t="s">
         <v>205</v>
       </c>
       <c r="W13" t="s">
@@ -6002,153 +5997,153 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="4">
+    <row r="14" spans="1:24" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>1007</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="3">
         <v>6</v>
       </c>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-      <c r="I14" s="4">
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3">
         <v>9999</v>
       </c>
-      <c r="J14" s="4">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4">
-        <v>1</v>
-      </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P14" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="4">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P14" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="3">
         <v>9</v>
       </c>
-      <c r="R14" s="4">
-        <v>0</v>
-      </c>
-      <c r="S14" s="4">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="4">
+      <c r="T14" s="3">
         <v>30</v>
       </c>
-      <c r="U14" s="4">
-        <v>0</v>
-      </c>
-      <c r="V14" s="4" t="s">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="W14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X14" s="4">
+      <c r="W14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="4">
+    <row r="15" spans="1:24" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>1009</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="E15" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="3">
         <v>6</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="3">
         <v>20</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="3">
         <v>9999</v>
       </c>
-      <c r="J15" s="4">
-        <v>0</v>
-      </c>
-      <c r="K15" s="4">
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>3</v>
       </c>
-      <c r="L15" s="4">
-        <v>0</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P15" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="4">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P15" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="3">
         <v>9</v>
       </c>
-      <c r="R15" s="4">
-        <v>0</v>
-      </c>
-      <c r="S15" s="4">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
         <v>100</v>
       </c>
-      <c r="T15" s="4">
+      <c r="T15" s="3">
         <v>30</v>
       </c>
-      <c r="U15" s="4">
-        <v>0</v>
-      </c>
-      <c r="V15" s="4" t="s">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="W15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X15" s="4">
+      <c r="W15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X15" s="3">
         <v>0</v>
       </c>
     </row>
@@ -6161,7 +6156,7 @@
         <v>2004</v>
       </c>
       <c r="C16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -6185,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -6217,8 +6212,8 @@
       <c r="U16">
         <v>0</v>
       </c>
-      <c r="V16" s="8" t="s">
-        <v>332</v>
+      <c r="V16" s="7" t="s">
+        <v>392</v>
       </c>
       <c r="W16" t="s">
         <v>94</v>
@@ -6251,7 +6246,7 @@
         <v>2</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -6292,8 +6287,8 @@
       <c r="U17">
         <v>0</v>
       </c>
-      <c r="V17" s="8" t="s">
-        <v>219</v>
+      <c r="V17" s="7" t="s">
+        <v>391</v>
       </c>
       <c r="W17" t="s">
         <v>94</v>
@@ -6311,7 +6306,7 @@
         <v>2001</v>
       </c>
       <c r="C18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D18" t="s">
         <v>174</v>
@@ -6326,7 +6321,7 @@
         <v>2</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -6367,7 +6362,7 @@
       <c r="U18">
         <v>0</v>
       </c>
-      <c r="V18" s="8" t="s">
+      <c r="V18" s="7" t="s">
         <v>185</v>
       </c>
       <c r="W18" t="s">
@@ -6377,78 +6372,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="4">
+    <row r="19" spans="1:24" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="3">
         <v>2002</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="3">
         <v>2</v>
       </c>
-      <c r="H19" s="4">
-        <v>1</v>
-      </c>
-      <c r="I19" s="4">
+      <c r="H19" s="3">
+        <v>1</v>
+      </c>
+      <c r="I19" s="3">
         <v>9999</v>
       </c>
-      <c r="J19" s="4">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4">
-        <v>1</v>
-      </c>
-      <c r="L19" s="4">
-        <v>0</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O19" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P19" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="4">
-        <v>1</v>
-      </c>
-      <c r="R19" s="4">
-        <v>0</v>
-      </c>
-      <c r="S19" s="4">
+      <c r="J19" s="3">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <v>1</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P19" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>1</v>
+      </c>
+      <c r="R19" s="3">
+        <v>0</v>
+      </c>
+      <c r="S19" s="3">
         <v>100</v>
       </c>
-      <c r="T19" s="4">
+      <c r="T19" s="3">
         <v>120</v>
       </c>
-      <c r="U19" s="4">
-        <v>0</v>
-      </c>
-      <c r="V19" s="4" t="s">
+      <c r="U19" s="3">
+        <v>0</v>
+      </c>
+      <c r="V19" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="W19" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X19" s="4">
+      <c r="W19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X19" s="3">
         <v>0</v>
       </c>
     </row>
@@ -6461,16 +6456,16 @@
         <v>2005</v>
       </c>
       <c r="C20" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D20" t="s">
+        <v>251</v>
+      </c>
+      <c r="E20" t="s">
+        <v>273</v>
+      </c>
+      <c r="F20" t="s">
         <v>252</v>
-      </c>
-      <c r="E20" t="s">
-        <v>274</v>
-      </c>
-      <c r="F20" t="s">
-        <v>253</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -6517,14 +6512,14 @@
       <c r="U20">
         <v>0</v>
       </c>
-      <c r="V20" s="8" t="s">
-        <v>276</v>
+      <c r="V20" s="7" t="s">
+        <v>275</v>
       </c>
       <c r="W20" t="s">
         <v>51</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -6536,7 +6531,7 @@
         <v>2003</v>
       </c>
       <c r="C21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D21" t="s">
         <v>117</v>
@@ -6569,7 +6564,7 @@
         <v>94</v>
       </c>
       <c r="N21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O21" t="s">
         <v>94</v>
@@ -6592,8 +6587,8 @@
       <c r="U21">
         <v>0</v>
       </c>
-      <c r="V21" s="8" t="s">
-        <v>321</v>
+      <c r="V21" s="7" t="s">
+        <v>320</v>
       </c>
       <c r="W21" t="s">
         <v>100</v>
@@ -6602,78 +6597,78 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="4" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="4">
+    <row r="22" spans="1:24" s="3" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="3">
         <v>2003</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="F22" s="4" t="s">
+      <c r="E22" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="3">
         <v>2</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="3">
         <v>20</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I22" s="3">
         <v>9999</v>
       </c>
-      <c r="J22" s="4">
-        <v>0</v>
-      </c>
-      <c r="K22" s="4">
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>5</v>
       </c>
-      <c r="L22" s="4">
-        <v>0</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P22" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="4">
-        <v>1</v>
-      </c>
-      <c r="R22" s="4">
-        <v>0</v>
-      </c>
-      <c r="S22" s="4">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P22" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>1</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="4">
+      <c r="T22" s="3">
         <v>30</v>
       </c>
-      <c r="U22" s="4">
-        <v>0</v>
-      </c>
-      <c r="V22" s="4" t="s">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="W22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X22" s="4">
+      <c r="W22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X22" s="3">
         <v>0</v>
       </c>
     </row>
@@ -6686,7 +6681,7 @@
         <v>3006</v>
       </c>
       <c r="C23" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D23" t="s">
         <v>156</v>
@@ -6695,7 +6690,7 @@
         <v>155</v>
       </c>
       <c r="F23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -6742,8 +6737,8 @@
       <c r="U23">
         <v>0</v>
       </c>
-      <c r="V23" s="8" t="s">
-        <v>232</v>
+      <c r="V23" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="W23" t="s">
         <v>94</v>
@@ -6767,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
@@ -6776,7 +6771,7 @@
         <v>2</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -6794,7 +6789,7 @@
         <v>94</v>
       </c>
       <c r="N24" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O24" t="s">
         <v>94</v>
@@ -6817,7 +6812,7 @@
       <c r="U24">
         <v>0</v>
       </c>
-      <c r="V24" s="8" t="s">
+      <c r="V24" s="7" t="s">
         <v>217</v>
       </c>
       <c r="W24" t="s">
@@ -6851,7 +6846,7 @@
         <v>4</v>
       </c>
       <c r="H25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -6869,7 +6864,7 @@
         <v>94</v>
       </c>
       <c r="N25" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O25" t="s">
         <v>94</v>
@@ -6892,14 +6887,14 @@
       <c r="U25">
         <v>0</v>
       </c>
-      <c r="V25" s="8" t="s">
+      <c r="V25" s="7" t="s">
         <v>218</v>
       </c>
       <c r="W25" t="s">
         <v>16</v>
       </c>
       <c r="X25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -6911,7 +6906,7 @@
         <v>3003</v>
       </c>
       <c r="C26" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D26" t="s">
         <v>105</v>
@@ -6967,14 +6962,14 @@
       <c r="U26">
         <v>0</v>
       </c>
-      <c r="V26" s="8" t="s">
-        <v>233</v>
+      <c r="V26" s="7" t="s">
+        <v>232</v>
       </c>
       <c r="W26" t="s">
         <v>20</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="21" customHeight="1" x14ac:dyDescent="0.4">
@@ -6986,16 +6981,16 @@
         <v>3008</v>
       </c>
       <c r="C27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D27" t="s">
+        <v>254</v>
+      </c>
+      <c r="E27" t="s">
+        <v>253</v>
+      </c>
+      <c r="F27" t="s">
         <v>255</v>
-      </c>
-      <c r="E27" t="s">
-        <v>254</v>
-      </c>
-      <c r="F27" t="s">
-        <v>256</v>
       </c>
       <c r="G27">
         <v>4</v>
@@ -7042,8 +7037,8 @@
       <c r="U27">
         <v>0</v>
       </c>
-      <c r="V27" s="8" t="s">
-        <v>257</v>
+      <c r="V27" s="7" t="s">
+        <v>256</v>
       </c>
       <c r="W27" t="s">
         <v>94</v>
@@ -7061,22 +7056,22 @@
         <v>3009</v>
       </c>
       <c r="C28" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D28" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E28" t="s">
+        <v>331</v>
+      </c>
+      <c r="F28" t="s">
         <v>333</v>
-      </c>
-      <c r="F28" t="s">
-        <v>335</v>
       </c>
       <c r="G28">
         <v>4</v>
       </c>
       <c r="H28">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -7091,7 +7086,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="N28" t="s">
         <v>94</v>
@@ -7117,8 +7112,8 @@
       <c r="U28">
         <v>120</v>
       </c>
-      <c r="V28" s="8" t="s">
-        <v>370</v>
+      <c r="V28" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="W28" t="s">
         <v>94</v>
@@ -7136,16 +7131,16 @@
         <v>3010</v>
       </c>
       <c r="C29" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D29" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E29" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F29" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G29">
         <v>4</v>
@@ -7192,8 +7187,8 @@
       <c r="U29">
         <v>0</v>
       </c>
-      <c r="V29" s="8" t="s">
-        <v>383</v>
+      <c r="V29" s="7" t="s">
+        <v>381</v>
       </c>
       <c r="W29" t="s">
         <v>94</v>
@@ -7211,7 +7206,7 @@
         <v>3004</v>
       </c>
       <c r="C30" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D30" t="s">
         <v>114</v>
@@ -7267,7 +7262,7 @@
       <c r="U30">
         <v>0</v>
       </c>
-      <c r="V30" s="8" t="s">
+      <c r="V30" s="7" t="s">
         <v>190</v>
       </c>
       <c r="W30" t="s">
@@ -7286,16 +7281,16 @@
         <v>3007</v>
       </c>
       <c r="C31" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D31" t="s">
+        <v>248</v>
+      </c>
+      <c r="E31" t="s">
+        <v>272</v>
+      </c>
+      <c r="F31" t="s">
         <v>249</v>
-      </c>
-      <c r="E31" t="s">
-        <v>273</v>
-      </c>
-      <c r="F31" t="s">
-        <v>250</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -7342,8 +7337,8 @@
       <c r="U31">
         <v>0</v>
       </c>
-      <c r="V31" s="8" t="s">
-        <v>251</v>
+      <c r="V31" s="7" t="s">
+        <v>250</v>
       </c>
       <c r="W31" t="s">
         <v>94</v>
@@ -7352,153 +7347,153 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="4">
+    <row r="32" spans="1:24" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="3">
         <v>3005</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="3">
         <v>4</v>
       </c>
-      <c r="H32" s="4">
+      <c r="H32" s="3">
         <v>20</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I32" s="3">
         <v>9999</v>
       </c>
-      <c r="J32" s="4">
-        <v>0</v>
-      </c>
-      <c r="K32" s="4">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>5</v>
       </c>
-      <c r="L32" s="4">
-        <v>0</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O32" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P32" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="4">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P32" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="3">
         <v>2</v>
       </c>
-      <c r="R32" s="4">
-        <v>0</v>
-      </c>
-      <c r="S32" s="4">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="4">
+      <c r="T32" s="3">
         <v>30</v>
       </c>
-      <c r="U32" s="4">
-        <v>0</v>
-      </c>
-      <c r="V32" s="6" t="s">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="W32" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X32" s="4">
+      <c r="W32" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="4">
+    <row r="33" spans="1:24" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="3">
         <v>3005</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G33" s="3">
         <v>4</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H33" s="3">
         <v>10</v>
       </c>
-      <c r="I33" s="4">
+      <c r="I33" s="3">
         <v>9999</v>
       </c>
-      <c r="J33" s="4">
-        <v>0</v>
-      </c>
-      <c r="K33" s="4">
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>5</v>
       </c>
-      <c r="L33" s="4">
-        <v>0</v>
-      </c>
-      <c r="M33" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N33" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O33" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P33" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q33" s="4">
+      <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P33" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="3">
         <v>2</v>
       </c>
-      <c r="R33" s="4">
-        <v>0</v>
-      </c>
-      <c r="S33" s="4">
+      <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>100</v>
       </c>
-      <c r="T33" s="4">
+      <c r="T33" s="3">
         <v>30</v>
       </c>
-      <c r="U33" s="4">
-        <v>0</v>
-      </c>
-      <c r="V33" s="6" t="s">
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="W33" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X33" s="4">
+      <c r="W33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X33" s="3">
         <v>0</v>
       </c>
     </row>
@@ -7511,7 +7506,7 @@
         <v>4010</v>
       </c>
       <c r="C34" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D34" t="s">
         <v>150</v>
@@ -7567,8 +7562,8 @@
       <c r="U34">
         <v>0</v>
       </c>
-      <c r="V34" s="8" t="s">
-        <v>322</v>
+      <c r="V34" s="7" t="s">
+        <v>321</v>
       </c>
       <c r="W34" t="s">
         <v>94</v>
@@ -7586,7 +7581,7 @@
         <v>4011</v>
       </c>
       <c r="C35" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D35" t="s">
         <v>153</v>
@@ -7642,8 +7637,8 @@
       <c r="U35">
         <v>0</v>
       </c>
-      <c r="V35" s="8" t="s">
-        <v>389</v>
+      <c r="V35" s="7" t="s">
+        <v>387</v>
       </c>
       <c r="W35" t="s">
         <v>94</v>
@@ -7661,7 +7656,7 @@
         <v>4001</v>
       </c>
       <c r="C36" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D36" t="s">
         <v>23</v>
@@ -7670,13 +7665,13 @@
         <v>21</v>
       </c>
       <c r="F36" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G36">
         <v>6</v>
       </c>
       <c r="H36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -7691,10 +7686,10 @@
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O36" t="s">
         <v>94</v>
@@ -7709,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="S36">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -7717,8 +7712,8 @@
       <c r="U36">
         <v>0</v>
       </c>
-      <c r="V36" s="8" t="s">
-        <v>247</v>
+      <c r="V36" s="7" t="s">
+        <v>246</v>
       </c>
       <c r="W36" t="s">
         <v>153</v>
@@ -7736,7 +7731,7 @@
         <v>4002</v>
       </c>
       <c r="C37" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D37" t="s">
         <v>25</v>
@@ -7754,7 +7749,7 @@
         <v>4</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -7769,7 +7764,7 @@
         <v>94</v>
       </c>
       <c r="N37" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O37" t="s">
         <v>94</v>
@@ -7792,8 +7787,8 @@
       <c r="U37">
         <v>0</v>
       </c>
-      <c r="V37" s="8" t="s">
-        <v>323</v>
+      <c r="V37" s="7" t="s">
+        <v>322</v>
       </c>
       <c r="W37" t="s">
         <v>23</v>
@@ -7811,7 +7806,7 @@
         <v>4010</v>
       </c>
       <c r="C38" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D38" t="s">
         <v>127</v>
@@ -7826,16 +7821,16 @@
         <v>1</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -7844,7 +7839,7 @@
         <v>94</v>
       </c>
       <c r="N38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O38" t="s">
         <v>94</v>
@@ -7867,7 +7862,7 @@
       <c r="U38">
         <v>0</v>
       </c>
-      <c r="V38" s="8" t="s">
+      <c r="V38" s="7" t="s">
         <v>193</v>
       </c>
       <c r="W38" t="s">
@@ -7886,7 +7881,7 @@
         <v>4011</v>
       </c>
       <c r="C39" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D39" t="s">
         <v>170</v>
@@ -7901,16 +7896,16 @@
         <v>1</v>
       </c>
       <c r="H39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -7919,7 +7914,7 @@
         <v>94</v>
       </c>
       <c r="N39" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O39" t="s">
         <v>94</v>
@@ -7942,7 +7937,7 @@
       <c r="U39">
         <v>0</v>
       </c>
-      <c r="V39" s="8" t="s">
+      <c r="V39" s="7" t="s">
         <v>181</v>
       </c>
       <c r="W39" t="s">
@@ -7961,7 +7956,7 @@
         <v>4012</v>
       </c>
       <c r="C40" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D40" t="s">
         <v>172</v>
@@ -7976,10 +7971,10 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -7994,7 +7989,7 @@
         <v>94</v>
       </c>
       <c r="N40" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O40" t="s">
         <v>94</v>
@@ -8017,8 +8012,8 @@
       <c r="U40">
         <v>0</v>
       </c>
-      <c r="V40" s="8" t="s">
-        <v>324</v>
+      <c r="V40" s="7" t="s">
+        <v>323</v>
       </c>
       <c r="W40" t="s">
         <v>23</v>
@@ -8036,7 +8031,7 @@
         <v>4012</v>
       </c>
       <c r="C41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D41" t="s">
         <v>176</v>
@@ -8045,16 +8040,16 @@
         <v>175</v>
       </c>
       <c r="F41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -8069,7 +8064,7 @@
         <v>94</v>
       </c>
       <c r="N41" t="s">
-        <v>237</v>
+        <v>94</v>
       </c>
       <c r="O41" t="s">
         <v>94</v>
@@ -8092,8 +8087,8 @@
       <c r="U41">
         <v>0</v>
       </c>
-      <c r="V41" s="8" t="s">
-        <v>318</v>
+      <c r="V41" s="7" t="s">
+        <v>317</v>
       </c>
       <c r="W41" t="s">
         <v>23</v>
@@ -8111,7 +8106,7 @@
         <v>4012</v>
       </c>
       <c r="C42" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D42" t="s">
         <v>178</v>
@@ -8126,10 +8121,10 @@
         <v>1</v>
       </c>
       <c r="H42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -8144,7 +8139,7 @@
         <v>94</v>
       </c>
       <c r="N42" t="s">
-        <v>237</v>
+        <v>94</v>
       </c>
       <c r="O42" t="s">
         <v>94</v>
@@ -8167,8 +8162,8 @@
       <c r="U42">
         <v>0</v>
       </c>
-      <c r="V42" s="8" t="s">
-        <v>319</v>
+      <c r="V42" s="7" t="s">
+        <v>318</v>
       </c>
       <c r="W42" t="s">
         <v>23</v>
@@ -8177,78 +8172,78 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="4">
+    <row r="43" spans="1:24" s="3" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="3">
         <v>4003</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G43" s="4">
+      <c r="G43" s="3">
         <v>3</v>
       </c>
-      <c r="H43" s="4">
+      <c r="H43" s="3">
         <v>2</v>
       </c>
-      <c r="I43" s="4">
+      <c r="I43" s="3">
         <v>9999</v>
       </c>
-      <c r="J43" s="4">
-        <v>0</v>
-      </c>
-      <c r="K43" s="4">
+      <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
         <v>3</v>
       </c>
-      <c r="L43" s="4">
-        <v>0</v>
-      </c>
-      <c r="M43" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N43" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O43" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P43" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q43" s="4">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P43" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="3">
         <v>3</v>
       </c>
-      <c r="R43" s="4">
-        <v>0</v>
-      </c>
-      <c r="S43" s="4">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="4">
+      <c r="T43" s="3">
         <v>30</v>
       </c>
-      <c r="U43" s="4">
-        <v>0</v>
-      </c>
-      <c r="V43" s="6" t="s">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="W43" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X43" s="4">
+      <c r="W43" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X43" s="3">
         <v>0</v>
       </c>
     </row>
@@ -8261,16 +8256,16 @@
         <v>4004</v>
       </c>
       <c r="C44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D44" t="s">
         <v>27</v>
       </c>
       <c r="E44" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F44" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G44">
         <v>3</v>
@@ -8317,163 +8312,163 @@
       <c r="U44">
         <v>0</v>
       </c>
-      <c r="V44" s="8" t="s">
-        <v>263</v>
+      <c r="V44" s="7" t="s">
+        <v>262</v>
       </c>
       <c r="W44" t="s">
         <v>153</v>
       </c>
       <c r="X44">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="4">
+    <row r="45" spans="1:24" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="3">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="3">
         <v>4005</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G45" s="3">
         <v>12</v>
       </c>
-      <c r="H45" s="4">
+      <c r="H45" s="3">
         <v>5</v>
       </c>
-      <c r="I45" s="4">
+      <c r="I45" s="3">
         <v>9999</v>
       </c>
-      <c r="J45" s="4">
-        <v>0</v>
-      </c>
-      <c r="K45" s="4">
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>3</v>
       </c>
-      <c r="L45" s="4">
-        <v>0</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O45" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P45" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q45" s="4">
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P45" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="3">
         <v>3</v>
       </c>
-      <c r="R45" s="4">
-        <v>0</v>
-      </c>
-      <c r="S45" s="4">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="4">
+      <c r="T45" s="3">
         <v>30</v>
       </c>
-      <c r="U45" s="4">
-        <v>0</v>
-      </c>
-      <c r="V45" s="6" t="s">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="W45" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X45" s="4">
+      <c r="W45" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X45" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="4">
+    <row r="46" spans="1:24" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="3">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="3">
         <v>4006</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="G46" s="4">
+      <c r="F46" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G46" s="3">
         <v>3</v>
       </c>
-      <c r="H46" s="4">
+      <c r="H46" s="3">
         <v>5</v>
       </c>
-      <c r="I46" s="4">
+      <c r="I46" s="3">
         <v>9999</v>
       </c>
-      <c r="J46" s="4">
-        <v>0</v>
-      </c>
-      <c r="K46" s="4">
+      <c r="J46" s="3">
+        <v>0</v>
+      </c>
+      <c r="K46" s="3">
         <v>3</v>
       </c>
-      <c r="L46" s="4">
-        <v>0</v>
-      </c>
-      <c r="M46" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N46" s="4" t="s">
+      <c r="L46" s="3">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P46" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3">
+        <v>100</v>
+      </c>
+      <c r="T46" s="3">
+        <v>30</v>
+      </c>
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+      <c r="V46" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="O46" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P46" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q46" s="4">
-        <v>3</v>
-      </c>
-      <c r="R46" s="4">
-        <v>0</v>
-      </c>
-      <c r="S46" s="4">
-        <v>100</v>
-      </c>
-      <c r="T46" s="4">
-        <v>30</v>
-      </c>
-      <c r="U46" s="4">
-        <v>0</v>
-      </c>
-      <c r="V46" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="W46" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X46" s="4">
+      <c r="W46" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X46" s="3">
         <v>0</v>
       </c>
     </row>
@@ -8486,7 +8481,7 @@
         <v>4007</v>
       </c>
       <c r="C47" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D47" t="s">
         <v>85</v>
@@ -8495,7 +8490,7 @@
         <v>87</v>
       </c>
       <c r="F47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G47">
         <v>3</v>
@@ -8519,7 +8514,7 @@
         <v>94</v>
       </c>
       <c r="N47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O47" t="s">
         <v>94</v>
@@ -8542,8 +8537,8 @@
       <c r="U47">
         <v>0</v>
       </c>
-      <c r="V47" s="8" t="s">
-        <v>243</v>
+      <c r="V47" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="W47" t="s">
         <v>153</v>
@@ -8552,378 +8547,378 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="4">
+    <row r="48" spans="1:24" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="3">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="3">
         <v>4007</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="G48" s="4">
+      <c r="F48" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G48" s="3">
         <v>3</v>
       </c>
-      <c r="H48" s="4">
+      <c r="H48" s="3">
         <v>5</v>
       </c>
-      <c r="I48" s="4">
+      <c r="I48" s="3">
         <v>9999</v>
       </c>
-      <c r="J48" s="4">
-        <v>0</v>
-      </c>
-      <c r="K48" s="4">
+      <c r="J48" s="3">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3">
         <v>3</v>
       </c>
-      <c r="L48" s="4">
-        <v>0</v>
-      </c>
-      <c r="M48" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N48" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="O48" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P48" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q48" s="4">
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P48" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="3">
         <v>3</v>
       </c>
-      <c r="R48" s="4">
-        <v>0</v>
-      </c>
-      <c r="S48" s="4">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
         <v>100</v>
       </c>
-      <c r="T48" s="4">
+      <c r="T48" s="3">
         <v>30</v>
       </c>
-      <c r="U48" s="4">
-        <v>0</v>
-      </c>
-      <c r="V48" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="W48" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X48" s="4">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X48" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="4">
+    <row r="49" spans="1:24" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="3">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="3">
         <v>4008</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="G49" s="4">
+      <c r="F49" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G49" s="3">
         <v>3</v>
       </c>
-      <c r="H49" s="4">
+      <c r="H49" s="3">
         <v>5</v>
       </c>
-      <c r="I49" s="4">
+      <c r="I49" s="3">
         <v>9999</v>
       </c>
-      <c r="J49" s="4">
-        <v>0</v>
-      </c>
-      <c r="K49" s="4">
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>3</v>
       </c>
-      <c r="L49" s="4">
-        <v>0</v>
-      </c>
-      <c r="M49" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N49" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="O49" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P49" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q49" s="4">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P49" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="3">
         <v>3</v>
       </c>
-      <c r="R49" s="4">
-        <v>0</v>
-      </c>
-      <c r="S49" s="4">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
         <v>100</v>
       </c>
-      <c r="T49" s="4">
+      <c r="T49" s="3">
         <v>30</v>
       </c>
-      <c r="U49" s="4">
-        <v>0</v>
-      </c>
-      <c r="V49" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="W49" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X49" s="4">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X49" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="4">
+    <row r="50" spans="1:24" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="3">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B50" s="4">
+      <c r="B50" s="3">
         <v>4009</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="G50" s="4">
+      <c r="F50" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G50" s="3">
         <v>3</v>
       </c>
-      <c r="H50" s="4">
+      <c r="H50" s="3">
         <v>8</v>
       </c>
-      <c r="I50" s="4">
+      <c r="I50" s="3">
         <v>9999</v>
       </c>
-      <c r="J50" s="4">
-        <v>0</v>
-      </c>
-      <c r="K50" s="4">
+      <c r="J50" s="3">
+        <v>0</v>
+      </c>
+      <c r="K50" s="3">
         <v>3</v>
       </c>
-      <c r="L50" s="4">
-        <v>0</v>
-      </c>
-      <c r="M50" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N50" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O50" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P50" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q50" s="4">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P50" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="3">
         <v>3</v>
       </c>
-      <c r="R50" s="4">
-        <v>0</v>
-      </c>
-      <c r="S50" s="4">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
         <v>100</v>
       </c>
-      <c r="T50" s="4">
+      <c r="T50" s="3">
         <v>30</v>
       </c>
-      <c r="U50" s="4">
-        <v>0</v>
-      </c>
-      <c r="V50" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="W50" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X50" s="4">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="W50" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X50" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="4" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="4">
+    <row r="51" spans="1:24" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="3">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B51" s="4">
+      <c r="B51" s="3">
         <v>4013</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E51" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="F51" s="4" t="s">
+      <c r="E51" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G51" s="4">
+      <c r="G51" s="3">
         <v>6</v>
       </c>
-      <c r="H51" s="4">
+      <c r="H51" s="3">
         <v>30</v>
       </c>
-      <c r="I51" s="4">
+      <c r="I51" s="3">
         <v>9999</v>
       </c>
-      <c r="J51" s="4">
-        <v>0</v>
-      </c>
-      <c r="K51" s="4">
+      <c r="J51" s="3">
+        <v>0</v>
+      </c>
+      <c r="K51" s="3">
         <v>5</v>
       </c>
-      <c r="L51" s="4">
-        <v>0</v>
-      </c>
-      <c r="M51" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N51" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O51" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P51" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q51" s="4">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P51" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="3">
         <v>3</v>
       </c>
-      <c r="R51" s="4">
-        <v>0</v>
-      </c>
-      <c r="S51" s="4">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
         <v>100</v>
       </c>
-      <c r="T51" s="4">
+      <c r="T51" s="3">
         <v>30</v>
       </c>
-      <c r="U51" s="4">
-        <v>0</v>
-      </c>
-      <c r="V51" s="6" t="s">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="W51" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X51" s="4">
+      <c r="W51" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X51" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="4" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="4">
+    <row r="52" spans="1:24" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="3">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B52" s="4">
+      <c r="B52" s="3">
         <v>5004</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G52" s="4">
+      <c r="G52" s="3">
         <v>6</v>
       </c>
-      <c r="H52" s="4">
-        <v>0</v>
-      </c>
-      <c r="I52" s="4">
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
         <v>9999</v>
       </c>
-      <c r="J52" s="4">
-        <v>0</v>
-      </c>
-      <c r="K52" s="4">
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>5</v>
       </c>
-      <c r="L52" s="4">
-        <v>0</v>
-      </c>
-      <c r="M52" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N52" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O52" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P52" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="4">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>4</v>
       </c>
-      <c r="R52" s="4">
-        <v>0</v>
-      </c>
-      <c r="S52" s="4">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="4">
+      <c r="T52" s="3">
         <v>30</v>
       </c>
-      <c r="U52" s="4">
-        <v>0</v>
-      </c>
-      <c r="V52" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="W52" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X52" s="4">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X52" s="3">
         <v>0</v>
       </c>
     </row>
@@ -8936,16 +8931,16 @@
         <v>5007</v>
       </c>
       <c r="C53" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D53" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E53" t="s">
+        <v>269</v>
+      </c>
+      <c r="F53" t="s">
         <v>270</v>
-      </c>
-      <c r="F53" t="s">
-        <v>271</v>
       </c>
       <c r="G53">
         <v>6</v>
@@ -8992,8 +8987,8 @@
       <c r="U53">
         <v>0</v>
       </c>
-      <c r="V53" s="8" t="s">
-        <v>326</v>
+      <c r="V53" s="7" t="s">
+        <v>325</v>
       </c>
       <c r="W53" t="s">
         <v>94</v>
@@ -9011,16 +9006,16 @@
         <v>5007</v>
       </c>
       <c r="C54" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D54" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E54" t="s">
+        <v>361</v>
+      </c>
+      <c r="F54" t="s">
         <v>363</v>
-      </c>
-      <c r="F54" t="s">
-        <v>365</v>
       </c>
       <c r="G54">
         <v>6</v>
@@ -9067,8 +9062,8 @@
       <c r="U54">
         <v>0</v>
       </c>
-      <c r="V54" s="8" t="s">
-        <v>366</v>
+      <c r="V54" s="7" t="s">
+        <v>364</v>
       </c>
       <c r="W54" t="s">
         <v>94</v>
@@ -9086,7 +9081,7 @@
         <v>5001</v>
       </c>
       <c r="C55" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D55" t="s">
         <v>39</v>
@@ -9095,13 +9090,13 @@
         <v>38</v>
       </c>
       <c r="F55" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G55">
         <v>6</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -9142,14 +9137,14 @@
       <c r="U55">
         <v>0</v>
       </c>
-      <c r="V55" s="8" t="s">
-        <v>329</v>
+      <c r="V55" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="W55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="X55">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9161,7 +9156,7 @@
         <v>5002</v>
       </c>
       <c r="C56" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D56" t="s">
         <v>120</v>
@@ -9217,14 +9212,14 @@
       <c r="U56">
         <v>0</v>
       </c>
-      <c r="V56" s="8" t="s">
-        <v>235</v>
+      <c r="V56" s="7" t="s">
+        <v>234</v>
       </c>
       <c r="W56" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="X56">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9236,7 +9231,7 @@
         <v>5003</v>
       </c>
       <c r="C57" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D57" t="s">
         <v>138</v>
@@ -9292,7 +9287,7 @@
       <c r="U57">
         <v>0</v>
       </c>
-      <c r="V57" s="8" t="s">
+      <c r="V57" s="7" t="s">
         <v>204</v>
       </c>
       <c r="W57" t="s">
@@ -9311,7 +9306,7 @@
         <v>5005</v>
       </c>
       <c r="C58" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D58" t="s">
         <v>199</v>
@@ -9326,7 +9321,7 @@
         <v>6</v>
       </c>
       <c r="H58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -9367,7 +9362,7 @@
       <c r="U58">
         <v>0</v>
       </c>
-      <c r="V58" s="8" t="s">
+      <c r="V58" s="7" t="s">
         <v>196</v>
       </c>
       <c r="W58" t="s">
@@ -9386,7 +9381,7 @@
         <v>5006</v>
       </c>
       <c r="C59" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D59" t="s">
         <v>213</v>
@@ -9395,13 +9390,13 @@
         <v>212</v>
       </c>
       <c r="F59" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G59">
         <v>6</v>
       </c>
       <c r="H59">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -9419,7 +9414,7 @@
         <v>134</v>
       </c>
       <c r="N59" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O59" t="s">
         <v>94</v>
@@ -9442,8 +9437,8 @@
       <c r="U59">
         <v>0</v>
       </c>
-      <c r="V59" s="8" t="s">
-        <v>330</v>
+      <c r="V59" s="7" t="s">
+        <v>329</v>
       </c>
       <c r="W59" t="s">
         <v>94</v>
@@ -9461,22 +9456,22 @@
         <v>5006</v>
       </c>
       <c r="C60" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D60" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E60" t="s">
+        <v>358</v>
+      </c>
+      <c r="F60" t="s">
         <v>360</v>
-      </c>
-      <c r="F60" t="s">
-        <v>362</v>
       </c>
       <c r="G60">
         <v>6</v>
       </c>
       <c r="H60">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -9491,13 +9486,13 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N60" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O60" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P60">
         <v>1</v>
@@ -9517,14 +9512,14 @@
       <c r="U60">
         <v>0</v>
       </c>
-      <c r="V60" s="8" t="s">
-        <v>392</v>
+      <c r="V60" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="W60" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="X60">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:24" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -9536,22 +9531,22 @@
         <v>5007</v>
       </c>
       <c r="C61" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D61" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E61" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F61" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G61">
         <v>6</v>
       </c>
       <c r="H61">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -9592,8 +9587,8 @@
       <c r="U61">
         <v>0</v>
       </c>
-      <c r="V61" s="8" t="s">
-        <v>341</v>
+      <c r="V61" s="7" t="s">
+        <v>339</v>
       </c>
       <c r="W61" t="s">
         <v>39</v>
@@ -9611,16 +9606,16 @@
         <v>5007</v>
       </c>
       <c r="C62" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D62" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E62" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F62" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G62">
         <v>6</v>
@@ -9641,7 +9636,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="N62" t="s">
         <v>94</v>
@@ -9667,8 +9662,8 @@
       <c r="U62">
         <v>120</v>
       </c>
-      <c r="V62" s="8" t="s">
-        <v>382</v>
+      <c r="V62" s="7" t="s">
+        <v>380</v>
       </c>
       <c r="W62" t="s">
         <v>94</v>
@@ -9677,78 +9672,78 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="4">
+    <row r="63" spans="1:24" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="3">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="3">
         <v>6001</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="F63" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G63" s="4">
+      <c r="G63" s="3">
         <v>6</v>
       </c>
-      <c r="H63" s="4">
+      <c r="H63" s="3">
         <v>3</v>
       </c>
-      <c r="I63" s="4">
+      <c r="I63" s="3">
         <v>9999</v>
       </c>
-      <c r="J63" s="4">
-        <v>0</v>
-      </c>
-      <c r="K63" s="4">
+      <c r="J63" s="3">
+        <v>0</v>
+      </c>
+      <c r="K63" s="3">
         <v>10</v>
       </c>
-      <c r="L63" s="4">
-        <v>0</v>
-      </c>
-      <c r="M63" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N63" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O63" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P63" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q63" s="4">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P63" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="3">
         <v>5</v>
       </c>
-      <c r="R63" s="4">
-        <v>0</v>
-      </c>
-      <c r="S63" s="4">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
         <v>100</v>
       </c>
-      <c r="T63" s="4">
+      <c r="T63" s="3">
         <v>30</v>
       </c>
-      <c r="U63" s="4">
-        <v>0</v>
-      </c>
-      <c r="V63" s="4" t="s">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="W63" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X63" s="4">
+      <c r="W63" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X63" s="3">
         <v>0</v>
       </c>
     </row>
@@ -9761,7 +9756,7 @@
         <v>6002</v>
       </c>
       <c r="C64" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D64" t="s">
         <v>100</v>
@@ -9776,7 +9771,7 @@
         <v>6</v>
       </c>
       <c r="H64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -9817,8 +9812,8 @@
       <c r="U64">
         <v>0</v>
       </c>
-      <c r="V64" s="8" t="s">
-        <v>320</v>
+      <c r="V64" s="7" t="s">
+        <v>319</v>
       </c>
       <c r="W64" t="s">
         <v>94</v>
@@ -9836,22 +9831,22 @@
         <v>6008</v>
       </c>
       <c r="C65" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D65" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E65" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F65" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G65">
         <v>6</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -9866,13 +9861,13 @@
         <v>0</v>
       </c>
       <c r="M65" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N65" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O65" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P65">
         <v>1</v>
@@ -9892,14 +9887,14 @@
       <c r="U65">
         <v>0</v>
       </c>
-      <c r="V65" s="8" t="s">
-        <v>358</v>
+      <c r="V65" s="7" t="s">
+        <v>356</v>
       </c>
       <c r="W65" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="X65">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -9911,16 +9906,16 @@
         <v>6004</v>
       </c>
       <c r="C66" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D66" t="s">
+        <v>259</v>
+      </c>
+      <c r="E66" t="s">
         <v>260</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>261</v>
-      </c>
-      <c r="F66" t="s">
-        <v>262</v>
       </c>
       <c r="G66">
         <v>6</v>
@@ -9967,8 +9962,8 @@
       <c r="U66">
         <v>0</v>
       </c>
-      <c r="V66" s="8" t="s">
-        <v>268</v>
+      <c r="V66" s="7" t="s">
+        <v>267</v>
       </c>
       <c r="W66" t="s">
         <v>94</v>
@@ -9986,16 +9981,16 @@
         <v>6005</v>
       </c>
       <c r="C67" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D67" t="s">
+        <v>263</v>
+      </c>
+      <c r="E67" t="s">
         <v>264</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>265</v>
-      </c>
-      <c r="F67" t="s">
-        <v>266</v>
       </c>
       <c r="G67">
         <v>6</v>
@@ -10042,8 +10037,8 @@
       <c r="U67">
         <v>0</v>
       </c>
-      <c r="V67" s="8" t="s">
-        <v>267</v>
+      <c r="V67" s="7" t="s">
+        <v>266</v>
       </c>
       <c r="W67" t="s">
         <v>94</v>
@@ -10061,16 +10056,16 @@
         <v>6006</v>
       </c>
       <c r="C68" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D68" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E68" t="s">
+        <v>334</v>
+      </c>
+      <c r="F68" t="s">
         <v>336</v>
-      </c>
-      <c r="F68" t="s">
-        <v>338</v>
       </c>
       <c r="G68">
         <v>6</v>
@@ -10091,7 +10086,7 @@
         <v>0</v>
       </c>
       <c r="M68" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="N68" t="s">
         <v>94</v>
@@ -10117,538 +10112,538 @@
       <c r="U68">
         <v>120</v>
       </c>
-      <c r="V68" s="8" t="s">
-        <v>384</v>
+      <c r="V68" s="7" t="s">
+        <v>382</v>
       </c>
       <c r="W68" t="s">
         <v>100</v>
       </c>
       <c r="X68">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:24" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="4">
+    <row r="69" spans="1:24" s="3" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="3">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="B69" s="4">
+      <c r="B69" s="3">
         <v>6007</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="E69" s="4" t="s">
+      <c r="C69" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="E69" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G69" s="3">
+        <v>6</v>
+      </c>
+      <c r="H69" s="3">
+        <v>5</v>
+      </c>
+      <c r="I69" s="3">
+        <v>9999</v>
+      </c>
+      <c r="J69" s="3">
+        <v>0</v>
+      </c>
+      <c r="K69" s="3">
+        <v>3</v>
+      </c>
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P69" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>5</v>
+      </c>
+      <c r="R69" s="3">
+        <v>1</v>
+      </c>
+      <c r="S69" s="3">
+        <v>50</v>
+      </c>
+      <c r="T69" s="3">
+        <v>30</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="G69" s="4">
-        <v>6</v>
-      </c>
-      <c r="H69" s="4">
-        <v>5</v>
-      </c>
-      <c r="I69" s="4">
-        <v>9999</v>
-      </c>
-      <c r="J69" s="4">
-        <v>0</v>
-      </c>
-      <c r="K69" s="4">
-        <v>3</v>
-      </c>
-      <c r="L69" s="4">
-        <v>0</v>
-      </c>
-      <c r="M69" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N69" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="O69" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P69" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q69" s="4">
-        <v>5</v>
-      </c>
-      <c r="R69" s="4">
-        <v>1</v>
-      </c>
-      <c r="S69" s="4">
-        <v>50</v>
-      </c>
-      <c r="T69" s="4">
-        <v>30</v>
-      </c>
-      <c r="U69" s="4">
-        <v>0</v>
-      </c>
-      <c r="V69" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="W69" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X69" s="4">
+      <c r="W69" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X69" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="4">
+    <row r="70" spans="1:24" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="3">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="3">
         <v>6003</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="E70" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="F70" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G70" s="4">
+      <c r="G70" s="3">
         <v>6</v>
       </c>
-      <c r="H70" s="4">
+      <c r="H70" s="3">
         <v>3</v>
       </c>
-      <c r="I70" s="4">
+      <c r="I70" s="3">
         <v>9999</v>
       </c>
-      <c r="J70" s="4">
-        <v>0</v>
-      </c>
-      <c r="K70" s="4">
-        <v>1</v>
-      </c>
-      <c r="L70" s="4">
-        <v>0</v>
-      </c>
-      <c r="M70" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N70" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O70" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P70" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="4">
+      <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
+        <v>1</v>
+      </c>
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P70" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="3">
         <v>5</v>
       </c>
-      <c r="R70" s="4">
-        <v>0</v>
-      </c>
-      <c r="S70" s="4">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>100</v>
       </c>
-      <c r="T70" s="4">
+      <c r="T70" s="3">
         <v>30</v>
       </c>
-      <c r="U70" s="4">
-        <v>0</v>
-      </c>
-      <c r="V70" s="4" t="s">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="W70" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X70" s="4">
+      <c r="W70" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X70" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="5">
+    <row r="71" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="4">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="B71" s="5">
+      <c r="B71" s="4">
         <v>7001</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="D71" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E71" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="F71" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G71" s="5">
+      <c r="G71" s="4">
         <v>6</v>
       </c>
-      <c r="H71" s="5">
+      <c r="H71" s="4">
         <v>12</v>
       </c>
-      <c r="I71" s="5">
-        <v>0</v>
-      </c>
-      <c r="J71" s="5">
-        <v>0</v>
-      </c>
-      <c r="K71" s="5">
-        <v>1</v>
-      </c>
-      <c r="L71" s="5">
-        <v>0</v>
-      </c>
-      <c r="M71" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N71" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O71" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="P71" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q71" s="5">
+      <c r="I71" s="4">
+        <v>0</v>
+      </c>
+      <c r="J71" s="4">
+        <v>0</v>
+      </c>
+      <c r="K71" s="4">
+        <v>1</v>
+      </c>
+      <c r="L71" s="4">
+        <v>0</v>
+      </c>
+      <c r="M71" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N71" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O71" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="P71" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="4">
         <v>6</v>
       </c>
       <c r="R71" s="2">
         <v>0</v>
       </c>
-      <c r="S71" s="5">
+      <c r="S71" s="4">
         <v>100</v>
       </c>
-      <c r="T71" s="5">
+      <c r="T71" s="4">
         <v>30</v>
       </c>
-      <c r="U71" s="5">
-        <v>0</v>
-      </c>
-      <c r="V71" s="5" t="s">
+      <c r="U71" s="4">
+        <v>0</v>
+      </c>
+      <c r="V71" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="W71" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="X71" s="5">
+      <c r="W71" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X71" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:24" s="5" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="5">
+    <row r="72" spans="1:24" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="4">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="B72" s="5">
+      <c r="B72" s="4">
         <v>7002</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="D72" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="E72" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="F72" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G72" s="5">
+      <c r="G72" s="4">
         <v>18</v>
       </c>
-      <c r="H72" s="5">
+      <c r="H72" s="4">
         <v>15</v>
       </c>
-      <c r="I72" s="5">
-        <v>0</v>
-      </c>
-      <c r="J72" s="5">
-        <v>0</v>
-      </c>
-      <c r="K72" s="5">
-        <v>1</v>
-      </c>
-      <c r="L72" s="5">
-        <v>0</v>
-      </c>
-      <c r="M72" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="N72" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="O72" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="P72" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q72" s="5">
+      <c r="I72" s="4">
+        <v>0</v>
+      </c>
+      <c r="J72" s="4">
+        <v>0</v>
+      </c>
+      <c r="K72" s="4">
+        <v>1</v>
+      </c>
+      <c r="L72" s="4">
+        <v>0</v>
+      </c>
+      <c r="M72" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="O72" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="P72" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="4">
         <v>6</v>
       </c>
       <c r="R72" s="2">
         <v>0</v>
       </c>
-      <c r="S72" s="5">
+      <c r="S72" s="4">
         <v>100</v>
       </c>
-      <c r="T72" s="5">
+      <c r="T72" s="4">
         <v>30</v>
       </c>
-      <c r="U72" s="5">
-        <v>0</v>
-      </c>
-      <c r="V72" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="W72" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="X72" s="5">
+      <c r="U72" s="4">
+        <v>0</v>
+      </c>
+      <c r="V72" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="W72" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X72" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="4">
+    <row r="73" spans="1:24" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="3">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B73" s="3">
         <v>8001</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="E73" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F73" s="4" t="s">
+      <c r="F73" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G73" s="4">
+      <c r="G73" s="3">
         <v>6</v>
       </c>
-      <c r="H73" s="4">
+      <c r="H73" s="3">
         <v>12</v>
       </c>
-      <c r="I73" s="4">
-        <v>0</v>
-      </c>
-      <c r="J73" s="4">
-        <v>0</v>
-      </c>
-      <c r="K73" s="4">
-        <v>1</v>
-      </c>
-      <c r="L73" s="4">
-        <v>0</v>
-      </c>
-      <c r="M73" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N73" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O73" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P73" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q73" s="4">
+      <c r="I73" s="3">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3">
+        <v>0</v>
+      </c>
+      <c r="K73" s="3">
+        <v>1</v>
+      </c>
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N73" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P73" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="3">
         <v>7</v>
       </c>
-      <c r="R73" s="4">
-        <v>0</v>
-      </c>
-      <c r="S73" s="4">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
         <v>100</v>
       </c>
-      <c r="T73" s="4">
+      <c r="T73" s="3">
         <v>30</v>
       </c>
-      <c r="U73" s="4">
-        <v>0</v>
-      </c>
-      <c r="V73" s="4" t="s">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="W73" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="X73" s="4">
+      <c r="W73" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X73" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:24" s="4" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="4">
+    <row r="74" spans="1:24" s="3" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="3">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="B74" s="4">
+      <c r="B74" s="3">
         <v>8002</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="E74" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="F74" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G74" s="4">
+      <c r="G74" s="3">
         <v>6</v>
       </c>
-      <c r="H74" s="4">
+      <c r="H74" s="3">
         <v>14</v>
       </c>
-      <c r="I74" s="4">
-        <v>0</v>
-      </c>
-      <c r="J74" s="4">
-        <v>0</v>
-      </c>
-      <c r="K74" s="4">
-        <v>1</v>
-      </c>
-      <c r="L74" s="4">
-        <v>0</v>
-      </c>
-      <c r="M74" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="N74" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O74" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="P74" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q74" s="4">
+      <c r="I74" s="3">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3">
+        <v>0</v>
+      </c>
+  